--- a/docs/exports/geotech-news-archive.xlsx
+++ b/docs/exports/geotech-news-archive.xlsx
@@ -25,7 +25,7 @@
     <numFmt numFmtId="165" formatCode="dd mmm yyyy"/>
     <numFmt numFmtId="166" formatCode="0.0"/>
   </numFmts>
-  <fonts count="18">
+  <fonts count="24">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -90,7 +90,31 @@
     </font>
     <font>
       <b val="1"/>
+      <color rgb="002563D6"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00C23D7B"/>
+    </font>
+    <font>
+      <b val="1"/>
       <color rgb="00B8C0CA"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00D38B00"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="001F9D63"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="008A94A3"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="006B4FD6"/>
     </font>
     <font>
       <b val="1"/>
@@ -109,7 +133,7 @@
       <u val="single"/>
     </font>
   </fonts>
-  <fills count="15">
+  <fills count="17">
     <fill>
       <patternFill/>
     </fill>
@@ -194,8 +218,20 @@
         <bgColor rgb="00F9DFD9"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00D8E3F8"/>
+        <bgColor rgb="00D8E3F8"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F4DCE7"/>
+        <bgColor rgb="00F4DCE7"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="4">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -221,11 +257,27 @@
         <color rgb="00D9DEE3"/>
       </bottom>
     </border>
+    <border>
+      <left style="thick">
+        <color rgb="002563D6"/>
+      </left>
+      <bottom style="thin">
+        <color rgb="00D9DEE3"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thick">
+        <color rgb="00C23D7B"/>
+      </left>
+      <bottom style="thin">
+        <color rgb="00D9DEE3"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="47">
+  <cellXfs count="62">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" indent="1"/>
@@ -289,28 +341,52 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="13" fillId="15" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="16" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -328,13 +404,34 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="15" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="16" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -507,14 +604,42 @@
               </a:ln>
             </spPr>
           </dPt>
+          <dPt>
+            <idx val="1"/>
+            <spPr>
+              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:srgbClr val="2563D6"/>
+              </a:solidFill>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:solidFill>
+                  <a:srgbClr val="2563D6"/>
+                </a:solidFill>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </dPt>
+          <dPt>
+            <idx val="2"/>
+            <spPr>
+              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:srgbClr val="C23D7B"/>
+              </a:solidFill>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:solidFill>
+                  <a:srgbClr val="C23D7B"/>
+                </a:solidFill>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </dPt>
           <cat>
             <numRef>
-              <f>'Dashboard'!$A$11</f>
+              <f>'Dashboard'!$A$11:$A$13</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Dashboard'!$B$11</f>
+              <f>'Dashboard'!$B$11:$B$13</f>
             </numRef>
           </val>
         </ser>
@@ -606,14 +731,84 @@
               </a:ln>
             </spPr>
           </dPt>
+          <dPt>
+            <idx val="1"/>
+            <spPr>
+              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:srgbClr val="2563D6"/>
+              </a:solidFill>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:solidFill>
+                  <a:srgbClr val="2563D6"/>
+                </a:solidFill>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </dPt>
+          <dPt>
+            <idx val="2"/>
+            <spPr>
+              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:srgbClr val="D38B00"/>
+              </a:solidFill>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:solidFill>
+                  <a:srgbClr val="D38B00"/>
+                </a:solidFill>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </dPt>
+          <dPt>
+            <idx val="3"/>
+            <spPr>
+              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:srgbClr val="1F9D63"/>
+              </a:solidFill>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:solidFill>
+                  <a:srgbClr val="1F9D63"/>
+                </a:solidFill>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </dPt>
+          <dPt>
+            <idx val="4"/>
+            <spPr>
+              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:srgbClr val="8A94A3"/>
+              </a:solidFill>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:solidFill>
+                  <a:srgbClr val="8A94A3"/>
+                </a:solidFill>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </dPt>
+          <dPt>
+            <idx val="5"/>
+            <spPr>
+              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:srgbClr val="6B4FD6"/>
+              </a:solidFill>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:solidFill>
+                  <a:srgbClr val="6B4FD6"/>
+                </a:solidFill>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </dPt>
           <cat>
             <numRef>
-              <f>'Dashboard'!$A$30</f>
+              <f>'Dashboard'!$A$30:$A$35</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Dashboard'!$B$30</f>
+              <f>'Dashboard'!$B$30:$B$35</f>
             </numRef>
           </val>
         </ser>
@@ -959,8 +1154,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Stories" displayName="Stories" ref="A1:M61" headerRowCount="1">
-  <autoFilter ref="A1:M61"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Stories" displayName="Stories" ref="A1:M81" headerRowCount="1">
+  <autoFilter ref="A1:M81"/>
   <tableColumns count="13">
     <tableColumn id="1" name="Digest date"/>
     <tableColumn id="2" name="Issue window"/>
@@ -1269,7 +1464,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:N65"/>
+  <dimension ref="A1:N67"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="36" customWidth="1" min="1" max="1"/>
@@ -1325,7 +1520,7 @@
     </row>
     <row r="5" ht="36" customHeight="1">
       <c r="A5" s="4" t="n">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="B5" s="5" t="n">
         <v>1</v>
@@ -1336,11 +1531,11 @@
       </c>
       <c r="E5" s="8" t="n"/>
       <c r="F5" s="9" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="G5" s="10" t="n"/>
       <c r="H5" s="11" t="n">
-        <v>40</v>
+        <v>56</v>
       </c>
       <c r="I5" s="12" t="n"/>
     </row>
@@ -1420,16 +1615,54 @@
         </is>
       </c>
       <c r="B11" s="27" t="n">
-        <v>60</v>
+        <v>76</v>
       </c>
       <c r="C11" s="28" t="n">
         <v>0</v>
       </c>
       <c r="D11" s="28" t="n">
+        <v>11</v>
+      </c>
+      <c r="E11" s="28" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="29" t="inlineStr">
+        <is>
+          <t>Infrastructure &amp; the Underground City</t>
+        </is>
+      </c>
+      <c r="B12" s="27" t="n">
+        <v>3</v>
+      </c>
+      <c r="C12" s="28" t="n">
         <v>0</v>
       </c>
-      <c r="E11" s="28" t="n">
+      <c r="D12" s="28" t="n">
+        <v>1</v>
+      </c>
+      <c r="E12" s="28" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="30" t="inlineStr">
+        <is>
+          <t>Characterisation &amp; Modelling</t>
+        </is>
+      </c>
+      <c r="B13" s="27" t="n">
+        <v>1</v>
+      </c>
+      <c r="C13" s="28" t="n">
         <v>0</v>
+      </c>
+      <c r="D13" s="28" t="n">
+        <v>1</v>
+      </c>
+      <c r="E13" s="28" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="28">
@@ -1469,7 +1702,7 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="29" t="inlineStr">
+      <c r="A30" s="31" t="inlineStr">
         <is>
           <t>Not rated</t>
         </is>
@@ -1477,10 +1710,10 @@
       <c r="B30" s="28" t="n">
         <v>60</v>
       </c>
-      <c r="C30" s="30" t="n">
-        <v>1</v>
-      </c>
-      <c r="E30" s="31" t="inlineStr">
+      <c r="C30" s="32" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="E30" s="33" t="inlineStr">
         <is>
           <t>5 / 5</t>
         </is>
@@ -1490,27 +1723,60 @@
       </c>
     </row>
     <row r="31">
-      <c r="E31" s="32" t="inlineStr">
+      <c r="A31" s="34" t="inlineStr">
+        <is>
+          <t>News brief</t>
+        </is>
+      </c>
+      <c r="B31" s="28" t="n">
+        <v>9</v>
+      </c>
+      <c r="C31" s="32" t="n">
+        <v>0.1125</v>
+      </c>
+      <c r="E31" s="35" t="inlineStr">
         <is>
           <t>4 / 5</t>
         </is>
       </c>
       <c r="F31" s="28" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
     </row>
     <row r="32">
-      <c r="E32" s="33" t="inlineStr">
+      <c r="A32" s="36" t="inlineStr">
+        <is>
+          <t>Feature lead</t>
+        </is>
+      </c>
+      <c r="B32" s="28" t="n">
+        <v>6</v>
+      </c>
+      <c r="C32" s="32" t="n">
+        <v>0.075</v>
+      </c>
+      <c r="E32" s="37" t="inlineStr">
         <is>
           <t>3 / 5</t>
         </is>
       </c>
       <c r="F32" s="28" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="33">
-      <c r="E33" s="34" t="inlineStr">
+      <c r="A33" s="38" t="inlineStr">
+        <is>
+          <t>Regional insight</t>
+        </is>
+      </c>
+      <c r="B33" s="28" t="n">
+        <v>2</v>
+      </c>
+      <c r="C33" s="32" t="n">
+        <v>0.025</v>
+      </c>
+      <c r="E33" s="39" t="inlineStr">
         <is>
           <t>Keyword-ranked</t>
         </is>
@@ -1519,6 +1785,32 @@
         <v>60</v>
       </c>
     </row>
+    <row r="34">
+      <c r="A34" s="40" t="inlineStr">
+        <is>
+          <t>Watch only</t>
+        </is>
+      </c>
+      <c r="B34" s="28" t="n">
+        <v>2</v>
+      </c>
+      <c r="C34" s="32" t="n">
+        <v>0.025</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="41" t="inlineStr">
+        <is>
+          <t>Academia-to-Industry topic</t>
+        </is>
+      </c>
+      <c r="B35" s="28" t="n">
+        <v>1</v>
+      </c>
+      <c r="C35" s="32" t="n">
+        <v>0.0125</v>
+      </c>
+    </row>
     <row r="45">
       <c r="A45" s="22" t="inlineStr">
         <is>
@@ -1540,13 +1832,13 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="35" t="inlineStr">
+      <c r="A47" s="42" t="inlineStr">
         <is>
           <t>Q4 2026</t>
         </is>
       </c>
       <c r="B47" s="28" t="n">
-        <v>60</v>
+        <v>80</v>
       </c>
     </row>
     <row r="63">
@@ -1600,28 +1892,78 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="36" t="inlineStr">
+      <c r="A65" s="43" t="inlineStr">
         <is>
           <t>Hazards &amp; Resilience</t>
         </is>
       </c>
       <c r="B65" s="28" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="C65" s="28" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="D65" s="28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E65" s="28" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F65" s="28" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G65" s="28" t="n">
         <v>60</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="34" t="inlineStr">
+        <is>
+          <t>Infrastructure &amp; the Underground City</t>
+        </is>
+      </c>
+      <c r="B66" s="28" t="n">
+        <v>1</v>
+      </c>
+      <c r="C66" s="28" t="n">
+        <v>2</v>
+      </c>
+      <c r="D66" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="E66" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="F66" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="G66" s="28" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="44" t="inlineStr">
+        <is>
+          <t>Characterisation &amp; Modelling</t>
+        </is>
+      </c>
+      <c r="B67" s="28" t="n">
+        <v>1</v>
+      </c>
+      <c r="C67" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="D67" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="E67" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="F67" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="G67" s="28" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1637,7 +1979,7 @@
     <mergeCell ref="H5:I5"/>
     <mergeCell ref="A1:N1"/>
   </mergeCells>
-  <conditionalFormatting sqref="B65:G65">
+  <conditionalFormatting sqref="B65:G67">
     <cfRule type="colorScale" priority="1">
       <colorScale>
         <cfvo type="min"/>
@@ -1661,7 +2003,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:M61"/>
+  <dimension ref="A1:M81"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -1680,2894 +2022,4074 @@
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
-      <c r="A1" s="37" t="inlineStr">
+      <c r="A1" s="45" t="inlineStr">
         <is>
           <t>Digest date</t>
         </is>
       </c>
-      <c r="B1" s="37" t="inlineStr">
+      <c r="B1" s="45" t="inlineStr">
         <is>
           <t>Issue window</t>
         </is>
       </c>
-      <c r="C1" s="37" t="inlineStr">
+      <c r="C1" s="45" t="inlineStr">
         <is>
           <t>Theme</t>
         </is>
       </c>
-      <c r="D1" s="37" t="inlineStr">
+      <c r="D1" s="45" t="inlineStr">
         <is>
           <t>Relevance</t>
         </is>
       </c>
-      <c r="E1" s="37" t="inlineStr">
+      <c r="E1" s="45" t="inlineStr">
         <is>
           <t>Suggested use</t>
         </is>
       </c>
-      <c r="F1" s="37" t="inlineStr">
+      <c r="F1" s="45" t="inlineStr">
         <is>
           <t>Headline (English)</t>
         </is>
       </c>
-      <c r="G1" s="37" t="inlineStr">
+      <c r="G1" s="45" t="inlineStr">
         <is>
           <t>Original headline</t>
         </is>
       </c>
-      <c r="H1" s="37" t="inlineStr">
+      <c r="H1" s="45" t="inlineStr">
         <is>
           <t>Magazine angle</t>
         </is>
       </c>
-      <c r="I1" s="37" t="inlineStr">
+      <c r="I1" s="45" t="inlineStr">
         <is>
           <t>Source</t>
         </is>
       </c>
-      <c r="J1" s="37" t="inlineStr">
+      <c r="J1" s="45" t="inlineStr">
         <is>
           <t>Google News edition</t>
         </is>
       </c>
-      <c r="K1" s="37" t="inlineStr">
+      <c r="K1" s="45" t="inlineStr">
         <is>
           <t>Published</t>
         </is>
       </c>
-      <c r="L1" s="37" t="inlineStr">
+      <c r="L1" s="45" t="inlineStr">
         <is>
           <t>Keywords</t>
         </is>
       </c>
-      <c r="M1" s="37" t="inlineStr">
+      <c r="M1" s="45" t="inlineStr">
         <is>
           <t>Link</t>
         </is>
       </c>
     </row>
     <row r="2" ht="48" customHeight="1">
-      <c r="A2" s="38" t="n">
-        <v>46319</v>
-      </c>
-      <c r="B2" s="39" t="inlineStr">
-        <is>
-          <t>2026-Q4</t>
-        </is>
-      </c>
-      <c r="C2" s="40" t="inlineStr">
-        <is>
-          <t>Hazards &amp; Resilience</t>
-        </is>
-      </c>
-      <c r="D2" s="41" t="n"/>
-      <c r="E2" s="42" t="inlineStr"/>
-      <c r="F2" s="43" t="inlineStr">
+      <c r="A2" s="46" t="n">
+        <v>46319</v>
+      </c>
+      <c r="B2" s="47" t="inlineStr">
+        <is>
+          <t>2026-Q4</t>
+        </is>
+      </c>
+      <c r="C2" s="48" t="inlineStr">
+        <is>
+          <t>Hazards &amp; Resilience</t>
+        </is>
+      </c>
+      <c r="D2" s="49" t="n">
+        <v>4</v>
+      </c>
+      <c r="E2" s="50" t="inlineStr">
+        <is>
+          <t>Feature lead</t>
+        </is>
+      </c>
+      <c r="F2" s="51" t="inlineStr">
+        <is>
+          <t>Landslide-prevention embankment threatens residential area</t>
+        </is>
+      </c>
+      <c r="G2" s="51" t="inlineStr">
+        <is>
+          <t>Tanggul pencegah tanah longsor 'mengancam' kawasan permukiman.</t>
+        </is>
+      </c>
+      <c r="H2" s="51" t="inlineStr">
+        <is>
+          <t>Can retaining and protective embankments be designed to resist landslide loading from upslope slopes beside settlements, and how should such risk be assessed?</t>
+        </is>
+      </c>
+      <c r="I2" s="47" t="inlineStr">
+        <is>
+          <t>Vietnam.vn</t>
+        </is>
+      </c>
+      <c r="J2" s="47" t="inlineStr">
+        <is>
+          <t>Indonesia</t>
+        </is>
+      </c>
+      <c r="K2" s="46" t="n">
+        <v>46318</v>
+      </c>
+      <c r="L2" s="51" t="inlineStr">
+        <is>
+          <t>landslide, embankment</t>
+        </is>
+      </c>
+      <c r="M2" s="52" t="inlineStr">
+        <is>
+          <t>Open article</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="48" customHeight="1">
+      <c r="A3" s="46" t="n">
+        <v>46319</v>
+      </c>
+      <c r="B3" s="47" t="inlineStr">
+        <is>
+          <t>2026-Q4</t>
+        </is>
+      </c>
+      <c r="C3" s="48" t="inlineStr">
+        <is>
+          <t>Hazards &amp; Resilience</t>
+        </is>
+      </c>
+      <c r="D3" s="49" t="n">
+        <v>4</v>
+      </c>
+      <c r="E3" s="53" t="inlineStr">
+        <is>
+          <t>News brief</t>
+        </is>
+      </c>
+      <c r="F3" s="51" t="inlineStr">
+        <is>
+          <t>Storms in Liguria, major landslide in Savona: the collapse destroyed a city road</t>
+        </is>
+      </c>
+      <c r="G3" s="51" t="inlineStr">
+        <is>
+          <t>RAINEWS * CRONACA: «MALTEMPO IN LIGURIA, GRANDE FRANA A SAVONA: IL CROLLO HA DISTRUTTO UNA STRADA CITTADINA</t>
+        </is>
+      </c>
+      <c r="H3" s="51" t="inlineStr">
+        <is>
+          <t>What triggered this large rock or soil slope failure in Savona during heavy rain, and what does the collapse reveal about slope stability in Liguria?</t>
+        </is>
+      </c>
+      <c r="I3" s="47" t="inlineStr">
+        <is>
+          <t>agenzia giornalistica opinione</t>
+        </is>
+      </c>
+      <c r="J3" s="47" t="inlineStr">
+        <is>
+          <t>Italy</t>
+        </is>
+      </c>
+      <c r="K3" s="46" t="n">
+        <v>46317</v>
+      </c>
+      <c r="L3" s="51" t="inlineStr">
+        <is>
+          <t>landslide, collapse</t>
+        </is>
+      </c>
+      <c r="M3" s="52" t="inlineStr">
+        <is>
+          <t>Open article</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="48" customHeight="1">
+      <c r="A4" s="46" t="n">
+        <v>46319</v>
+      </c>
+      <c r="B4" s="47" t="inlineStr">
+        <is>
+          <t>2026-Q4</t>
+        </is>
+      </c>
+      <c r="C4" s="48" t="inlineStr">
+        <is>
+          <t>Hazards &amp; Resilience</t>
+        </is>
+      </c>
+      <c r="D4" s="49" t="n">
+        <v>4</v>
+      </c>
+      <c r="E4" s="50" t="inlineStr">
+        <is>
+          <t>Feature lead</t>
+        </is>
+      </c>
+      <c r="F4" s="51" t="inlineStr">
+        <is>
+          <t>At Khanh Le pass, traffic will be interrupted at 30-minute intervals to deal with landslides; road users should plan accordingly</t>
+        </is>
+      </c>
+      <c r="G4" s="51" t="inlineStr">
+        <is>
+          <t>En el paso de Khanh Le, el tráfico se interrumpirá a intervalos de 30 minutos para hacer frente a los deslizamientos de tierra; los usuarios de la carretera deben tenerlo en cuenta.</t>
+        </is>
+      </c>
+      <c r="H4" s="51" t="inlineStr">
+        <is>
+          <t>How should traffic management and monitoring be combined with slope stabilisation on mountain passes subject to recurrent landslides?</t>
+        </is>
+      </c>
+      <c r="I4" s="47" t="inlineStr">
+        <is>
+          <t>Vietnam.vn</t>
+        </is>
+      </c>
+      <c r="J4" s="47" t="inlineStr">
+        <is>
+          <t>Spain</t>
+        </is>
+      </c>
+      <c r="K4" s="46" t="n">
+        <v>46319</v>
+      </c>
+      <c r="L4" s="51" t="inlineStr">
+        <is>
+          <t>landslide</t>
+        </is>
+      </c>
+      <c r="M4" s="52" t="inlineStr">
+        <is>
+          <t>Open article</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="48" customHeight="1">
+      <c r="A5" s="46" t="n">
+        <v>46319</v>
+      </c>
+      <c r="B5" s="47" t="inlineStr">
+        <is>
+          <t>2026-Q4</t>
+        </is>
+      </c>
+      <c r="C5" s="48" t="inlineStr">
+        <is>
+          <t>Hazards &amp; Resilience</t>
+        </is>
+      </c>
+      <c r="D5" s="49" t="n">
+        <v>4</v>
+      </c>
+      <c r="E5" s="53" t="inlineStr">
+        <is>
+          <t>News brief</t>
+        </is>
+      </c>
+      <c r="F5" s="51" t="inlineStr">
+        <is>
+          <t>Valmontone, bad weather: tuff slope collapses onto Prenestina road, road partially closed</t>
+        </is>
+      </c>
+      <c r="G5" s="51" t="inlineStr">
+        <is>
+          <t>Valmontone, maltempo: frana costone di tufo sulla via Prenestina, strada parzialmente chiusa</t>
+        </is>
+      </c>
+      <c r="H5" s="51" t="inlineStr">
+        <is>
+          <t>What causes tuff cliff collapse in volcanic deposits under rainfall, and how can such slopes be assessed and stabilised near roads?</t>
+        </is>
+      </c>
+      <c r="I5" s="47" t="inlineStr">
+        <is>
+          <t>Il Giornale dei Castelli Romani</t>
+        </is>
+      </c>
+      <c r="J5" s="47" t="inlineStr">
+        <is>
+          <t>Italy</t>
+        </is>
+      </c>
+      <c r="K5" s="46" t="n">
+        <v>46319</v>
+      </c>
+      <c r="L5" s="51" t="inlineStr">
+        <is>
+          <t>landslide</t>
+        </is>
+      </c>
+      <c r="M5" s="52" t="inlineStr">
+        <is>
+          <t>Open article</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="48" customHeight="1">
+      <c r="A6" s="46" t="n">
+        <v>46319</v>
+      </c>
+      <c r="B6" s="47" t="inlineStr">
+        <is>
+          <t>2026-Q4</t>
+        </is>
+      </c>
+      <c r="C6" s="48" t="inlineStr">
+        <is>
+          <t>Hazards &amp; Resilience</t>
+        </is>
+      </c>
+      <c r="D6" s="49" t="n">
+        <v>4</v>
+      </c>
+      <c r="E6" s="53" t="inlineStr">
+        <is>
+          <t>News brief</t>
+        </is>
+      </c>
+      <c r="F6" s="51" t="inlineStr">
+        <is>
+          <t>Bonea, landslide in Capo locality: mayor closes three roads by urgent order</t>
+        </is>
+      </c>
+      <c r="G6" s="51" t="inlineStr">
+        <is>
+          <t>BONEA, FRANA IN LOCALITÀ CAPO: IL SINDACO CHIUDE TRE STRADE CON ORDINANZA URGENTE</t>
+        </is>
+      </c>
+      <c r="H6" s="51" t="inlineStr">
+        <is>
+          <t>What ground investigation would confirm the landslide mechanism at Capo locality and guide safe reopening of the three closed roads?</t>
+        </is>
+      </c>
+      <c r="I6" s="47" t="inlineStr">
+        <is>
+          <t>Tv7 Benevento</t>
+        </is>
+      </c>
+      <c r="J6" s="47" t="inlineStr">
+        <is>
+          <t>Italy</t>
+        </is>
+      </c>
+      <c r="K6" s="46" t="n">
+        <v>46319</v>
+      </c>
+      <c r="L6" s="51" t="inlineStr">
+        <is>
+          <t>landslide</t>
+        </is>
+      </c>
+      <c r="M6" s="52" t="inlineStr">
+        <is>
+          <t>Open article</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="48" customHeight="1">
+      <c r="A7" s="46" t="n">
+        <v>46319</v>
+      </c>
+      <c r="B7" s="47" t="inlineStr">
+        <is>
+          <t>2026-Q4</t>
+        </is>
+      </c>
+      <c r="C7" s="48" t="inlineStr">
+        <is>
+          <t>Hazards &amp; Resilience</t>
+        </is>
+      </c>
+      <c r="D7" s="49" t="n">
+        <v>4</v>
+      </c>
+      <c r="E7" s="53" t="inlineStr">
+        <is>
+          <t>News brief</t>
+        </is>
+      </c>
+      <c r="F7" s="51" t="inlineStr">
+        <is>
+          <t>Valmontone – Landslide near homes due to bad weather, partial road closure</t>
+        </is>
+      </c>
+      <c r="G7" s="51" t="inlineStr">
+        <is>
+          <t>Valmontone – Frana vicino ad abitazioni per maltempo, chiusura parziale della strada</t>
+        </is>
+      </c>
+      <c r="H7" s="51" t="inlineStr">
+        <is>
+          <t>What slope failure mechanism threatens homes near this Valmontone landslide, and what monitoring is needed before residents return?</t>
+        </is>
+      </c>
+      <c r="I7" s="47" t="inlineStr">
+        <is>
+          <t>lacronaca24.it</t>
+        </is>
+      </c>
+      <c r="J7" s="47" t="inlineStr">
+        <is>
+          <t>Italy</t>
+        </is>
+      </c>
+      <c r="K7" s="46" t="n">
+        <v>46319</v>
+      </c>
+      <c r="L7" s="51" t="inlineStr">
+        <is>
+          <t>landslide</t>
+        </is>
+      </c>
+      <c r="M7" s="52" t="inlineStr">
+        <is>
+          <t>Open article</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="48" customHeight="1">
+      <c r="A8" s="46" t="n">
+        <v>46319</v>
+      </c>
+      <c r="B8" s="47" t="inlineStr">
+        <is>
+          <t>2026-Q4</t>
+        </is>
+      </c>
+      <c r="C8" s="48" t="inlineStr">
+        <is>
+          <t>Hazards &amp; Resilience</t>
+        </is>
+      </c>
+      <c r="D8" s="49" t="n">
+        <v>4</v>
+      </c>
+      <c r="E8" s="50" t="inlineStr">
+        <is>
+          <t>Feature lead</t>
+        </is>
+      </c>
+      <c r="F8" s="51" t="inlineStr">
+        <is>
+          <t>La frana del Cencione Tra fango e polemiche Le ruspe sono al lavoro</t>
+        </is>
+      </c>
+      <c r="G8" s="51" t="inlineStr"/>
+      <c r="H8" s="51" t="inlineStr">
+        <is>
+          <t>How should authorities balance urgent earthworks with geotechnical investigation and accountability when a landslide site becomes politically contested?</t>
+        </is>
+      </c>
+      <c r="I8" s="47" t="inlineStr">
+        <is>
+          <t>Zazoom Social News</t>
+        </is>
+      </c>
+      <c r="J8" s="47" t="inlineStr">
+        <is>
+          <t>Italy</t>
+        </is>
+      </c>
+      <c r="K8" s="46" t="n">
+        <v>46318</v>
+      </c>
+      <c r="L8" s="51" t="inlineStr">
+        <is>
+          <t>landslide</t>
+        </is>
+      </c>
+      <c r="M8" s="52" t="inlineStr">
+        <is>
+          <t>Open article</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="48" customHeight="1">
+      <c r="A9" s="46" t="n">
+        <v>46319</v>
+      </c>
+      <c r="B9" s="47" t="inlineStr">
+        <is>
+          <t>2026-Q4</t>
+        </is>
+      </c>
+      <c r="C9" s="48" t="inlineStr">
+        <is>
+          <t>Hazards &amp; Resilience</t>
+        </is>
+      </c>
+      <c r="D9" s="49" t="n">
+        <v>4</v>
+      </c>
+      <c r="E9" s="53" t="inlineStr">
+        <is>
+          <t>News brief</t>
+        </is>
+      </c>
+      <c r="F9" s="51" t="inlineStr">
+        <is>
+          <t>TNI helps landslide victims in Lae Ikan, Subulussalam</t>
+        </is>
+      </c>
+      <c r="G9" s="51" t="inlineStr">
+        <is>
+          <t>TNI Bantu Korban Longsor di Lae Ikan Subulussalam</t>
+        </is>
+      </c>
+      <c r="H9" s="51" t="inlineStr">
+        <is>
+          <t>What role can emergency response and rapid geotechnical assessment play after a landslide in a mountainous Indonesian village?</t>
+        </is>
+      </c>
+      <c r="I9" s="47" t="inlineStr">
+        <is>
+          <t>RRI.co.id</t>
+        </is>
+      </c>
+      <c r="J9" s="47" t="inlineStr">
+        <is>
+          <t>Indonesia</t>
+        </is>
+      </c>
+      <c r="K9" s="46" t="n">
+        <v>46319</v>
+      </c>
+      <c r="L9" s="51" t="inlineStr">
+        <is>
+          <t>landslide</t>
+        </is>
+      </c>
+      <c r="M9" s="52" t="inlineStr">
+        <is>
+          <t>Open article</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="48" customHeight="1">
+      <c r="A10" s="46" t="n">
+        <v>46319</v>
+      </c>
+      <c r="B10" s="47" t="inlineStr">
+        <is>
+          <t>2026-Q4</t>
+        </is>
+      </c>
+      <c r="C10" s="48" t="inlineStr">
+        <is>
+          <t>Hazards &amp; Resilience</t>
+        </is>
+      </c>
+      <c r="D10" s="49" t="n">
+        <v>4</v>
+      </c>
+      <c r="E10" s="53" t="inlineStr">
+        <is>
+          <t>News brief</t>
+        </is>
+      </c>
+      <c r="F10" s="51" t="inlineStr">
+        <is>
+          <t>Source: no casualties in Tanta building collapse and 4 cars destroyed - video and photos</t>
+        </is>
+      </c>
+      <c r="G10" s="51" t="inlineStr">
+        <is>
+          <t>مصدر: لاضحايا في انهيار عقار طنطا وتحطم 4 سيارات - فيديو وصور</t>
+        </is>
+      </c>
+      <c r="H10" s="51" t="inlineStr">
+        <is>
+          <t>What caused the collapse of this Tanta building, and what foundation or excavation failure lessons does it offer?</t>
+        </is>
+      </c>
+      <c r="I10" s="47" t="inlineStr">
+        <is>
+          <t>Masrawy</t>
+        </is>
+      </c>
+      <c r="J10" s="47" t="inlineStr">
+        <is>
+          <t>Egypt</t>
+        </is>
+      </c>
+      <c r="K10" s="46" t="n">
+        <v>46319</v>
+      </c>
+      <c r="L10" s="51" t="inlineStr">
+        <is>
+          <t>collapse</t>
+        </is>
+      </c>
+      <c r="M10" s="52" t="inlineStr">
+        <is>
+          <t>Open article</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="48" customHeight="1">
+      <c r="A11" s="46" t="n">
+        <v>46319</v>
+      </c>
+      <c r="B11" s="47" t="inlineStr">
+        <is>
+          <t>2026-Q4</t>
+        </is>
+      </c>
+      <c r="C11" s="48" t="inlineStr">
+        <is>
+          <t>Hazards &amp; Resilience</t>
+        </is>
+      </c>
+      <c r="D11" s="49" t="n">
+        <v>4</v>
+      </c>
+      <c r="E11" s="54" t="inlineStr">
+        <is>
+          <t>Regional insight</t>
+        </is>
+      </c>
+      <c r="F11" s="51" t="inlineStr">
+        <is>
+          <t>25 subdistricts in Bandung Regency classified as medium-high landslide potential</t>
+        </is>
+      </c>
+      <c r="G11" s="51" t="inlineStr">
+        <is>
+          <t>25 Kecamatan di Kabupaten Bandung Masuk Kategori Potensi Gerakan Tanah Menengah-Tinggi</t>
+        </is>
+      </c>
+      <c r="H11" s="51" t="inlineStr">
+        <is>
+          <t>How are landslide susceptibility maps produced for districts, and how should medium-high hazard classes inform land-use planning?</t>
+        </is>
+      </c>
+      <c r="I11" s="47" t="inlineStr">
+        <is>
+          <t>Pikiran-Rakyat.com</t>
+        </is>
+      </c>
+      <c r="J11" s="47" t="inlineStr">
+        <is>
+          <t>Indonesia</t>
+        </is>
+      </c>
+      <c r="K11" s="46" t="n">
+        <v>46319</v>
+      </c>
+      <c r="L11" s="51" t="inlineStr"/>
+      <c r="M11" s="52" t="inlineStr">
+        <is>
+          <t>Open article</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="48" customHeight="1">
+      <c r="A12" s="46" t="n">
+        <v>46319</v>
+      </c>
+      <c r="B12" s="47" t="inlineStr">
+        <is>
+          <t>2026-Q4</t>
+        </is>
+      </c>
+      <c r="C12" s="55" t="inlineStr">
+        <is>
+          <t>Infrastructure &amp; the Underground City</t>
+        </is>
+      </c>
+      <c r="D12" s="49" t="n">
+        <v>4</v>
+      </c>
+      <c r="E12" s="53" t="inlineStr">
+        <is>
+          <t>News brief</t>
+        </is>
+      </c>
+      <c r="F12" s="51" t="inlineStr">
+        <is>
+          <t>Gochang-Buan Noeuldaegyo Enters Geotechnical Survey Phase; Construction Targeted for January 2028</t>
+        </is>
+      </c>
+      <c r="G12" s="51" t="inlineStr"/>
+      <c r="H12" s="51" t="inlineStr">
+        <is>
+          <t>What ground conditions will the geotechnical survey reveal for this Korean nuclear-related or major construction project, and how will they shape the 2028 schedule?</t>
+        </is>
+      </c>
+      <c r="I12" s="47" t="inlineStr">
+        <is>
+          <t>아시아경제</t>
+        </is>
+      </c>
+      <c r="J12" s="47" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="K12" s="46" t="n">
+        <v>46317</v>
+      </c>
+      <c r="L12" s="51" t="inlineStr">
+        <is>
+          <t>geotechnical</t>
+        </is>
+      </c>
+      <c r="M12" s="52" t="inlineStr">
+        <is>
+          <t>Open article</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="48" customHeight="1">
+      <c r="A13" s="46" t="n">
+        <v>46319</v>
+      </c>
+      <c r="B13" s="47" t="inlineStr">
+        <is>
+          <t>2026-Q4</t>
+        </is>
+      </c>
+      <c r="C13" s="56" t="inlineStr">
+        <is>
+          <t>Characterisation &amp; Modelling</t>
+        </is>
+      </c>
+      <c r="D13" s="49" t="n">
+        <v>4</v>
+      </c>
+      <c r="E13" s="50" t="inlineStr">
+        <is>
+          <t>Feature lead</t>
+        </is>
+      </c>
+      <c r="F13" s="51" t="inlineStr">
+        <is>
+          <t>Giant sinkhole discovered in Phong Nha-Ke Bang National Park</t>
+        </is>
+      </c>
+      <c r="G13" s="51" t="inlineStr">
+        <is>
+          <t>Giant sinkhole discovered in Phong Nha-Ke Bang National Park</t>
+        </is>
+      </c>
+      <c r="H13" s="51" t="inlineStr">
+        <is>
+          <t>How are giant karst sinkholes detected and characterised in limestone terrain, and what hazards do they pose to park access and infrastructure?</t>
+        </is>
+      </c>
+      <c r="I13" s="47" t="inlineStr">
+        <is>
+          <t>Baolangson.vn</t>
+        </is>
+      </c>
+      <c r="J13" s="47" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="K13" s="46" t="n">
+        <v>46319</v>
+      </c>
+      <c r="L13" s="51" t="inlineStr">
+        <is>
+          <t>sinkhole</t>
+        </is>
+      </c>
+      <c r="M13" s="52" t="inlineStr">
+        <is>
+          <t>Open article</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="48" customHeight="1">
+      <c r="A14" s="46" t="n">
+        <v>46319</v>
+      </c>
+      <c r="B14" s="47" t="inlineStr">
+        <is>
+          <t>2026-Q4</t>
+        </is>
+      </c>
+      <c r="C14" s="48" t="inlineStr">
+        <is>
+          <t>Hazards &amp; Resilience</t>
+        </is>
+      </c>
+      <c r="D14" s="49" t="n">
+        <v>4</v>
+      </c>
+      <c r="E14" s="50" t="inlineStr">
+        <is>
+          <t>Feature lead</t>
+        </is>
+      </c>
+      <c r="F14" s="51" t="inlineStr">
+        <is>
+          <t>In Massachusetts, sinkhole questions linger as mill demolition clears way for housing units</t>
+        </is>
+      </c>
+      <c r="G14" s="51" t="inlineStr"/>
+      <c r="H14" s="51" t="inlineStr">
+        <is>
+          <t>How should sinkhole origin be investigated beneath a former mill site before redevelopment for housing, and what ground remediation is needed?</t>
+        </is>
+      </c>
+      <c r="I14" s="47" t="inlineStr">
+        <is>
+          <t>Yahoo</t>
+        </is>
+      </c>
+      <c r="J14" s="47" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="K14" s="46" t="n">
+        <v>46318</v>
+      </c>
+      <c r="L14" s="51" t="inlineStr">
+        <is>
+          <t>sinkhole</t>
+        </is>
+      </c>
+      <c r="M14" s="52" t="inlineStr">
+        <is>
+          <t>Open article</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="48" customHeight="1">
+      <c r="A15" s="46" t="n">
+        <v>46319</v>
+      </c>
+      <c r="B15" s="47" t="inlineStr">
+        <is>
+          <t>2026-Q4</t>
+        </is>
+      </c>
+      <c r="C15" s="48" t="inlineStr">
+        <is>
+          <t>Hazards &amp; Resilience</t>
+        </is>
+      </c>
+      <c r="D15" s="49" t="n">
+        <v>3</v>
+      </c>
+      <c r="E15" s="57" t="inlineStr">
+        <is>
+          <t>Watch only</t>
+        </is>
+      </c>
+      <c r="F15" s="51" t="inlineStr">
+        <is>
+          <t>Frana tra via Gentile e via Genova: scatta il senso unico alternato con il semaforo</t>
+        </is>
+      </c>
+      <c r="G15" s="51" t="inlineStr"/>
+      <c r="H15" s="51" t="inlineStr">
+        <is>
+          <t>Does a landslide on an urban road indicate ground instability requiring geotechnical investigation before reopening?</t>
+        </is>
+      </c>
+      <c r="I15" s="47" t="inlineStr">
+        <is>
+          <t>Savona News</t>
+        </is>
+      </c>
+      <c r="J15" s="47" t="inlineStr">
+        <is>
+          <t>Italy</t>
+        </is>
+      </c>
+      <c r="K15" s="46" t="n">
+        <v>46319</v>
+      </c>
+      <c r="L15" s="51" t="inlineStr">
+        <is>
+          <t>landslide</t>
+        </is>
+      </c>
+      <c r="M15" s="52" t="inlineStr">
+        <is>
+          <t>Open article</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="48" customHeight="1">
+      <c r="A16" s="46" t="n">
+        <v>46319</v>
+      </c>
+      <c r="B16" s="47" t="inlineStr">
+        <is>
+          <t>2026-Q4</t>
+        </is>
+      </c>
+      <c r="C16" s="48" t="inlineStr">
+        <is>
+          <t>Hazards &amp; Resilience</t>
+        </is>
+      </c>
+      <c r="D16" s="49" t="n">
+        <v>3</v>
+      </c>
+      <c r="E16" s="57" t="inlineStr">
+        <is>
+          <t>Watch only</t>
+        </is>
+      </c>
+      <c r="F16" s="51" t="inlineStr">
+        <is>
+          <t>Torrential rain brings hidden hazards: mountain floods and landslides must be strictly prevented; public service advertisement</t>
+        </is>
+      </c>
+      <c r="G16" s="51" t="inlineStr">
+        <is>
+          <t>暴雨来袭隐患藏 山洪滑坡需严防｜公益广告</t>
+        </is>
+      </c>
+      <c r="H16" s="51" t="inlineStr">
+        <is>
+          <t>How do mountain flood and landslide hazards during intense rainfall get prevented through early warning and slope management?</t>
+        </is>
+      </c>
+      <c r="I16" s="47" t="inlineStr">
+        <is>
+          <t>凤凰网</t>
+        </is>
+      </c>
+      <c r="J16" s="47" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="K16" s="46" t="n">
+        <v>46318</v>
+      </c>
+      <c r="L16" s="51" t="inlineStr">
+        <is>
+          <t>landslide</t>
+        </is>
+      </c>
+      <c r="M16" s="52" t="inlineStr">
+        <is>
+          <t>Open article</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="48" customHeight="1">
+      <c r="A17" s="46" t="n">
+        <v>46319</v>
+      </c>
+      <c r="B17" s="47" t="inlineStr">
+        <is>
+          <t>2026-Q4</t>
+        </is>
+      </c>
+      <c r="C17" s="48" t="inlineStr">
+        <is>
+          <t>Hazards &amp; Resilience</t>
+        </is>
+      </c>
+      <c r="D17" s="49" t="n">
+        <v>3</v>
+      </c>
+      <c r="E17" s="54" t="inlineStr">
+        <is>
+          <t>Regional insight</t>
+        </is>
+      </c>
+      <c r="F17" s="51" t="inlineStr">
+        <is>
+          <t>At Khanh Le pass, vehicles are stopped in groups to face rockfall risk</t>
+        </is>
+      </c>
+      <c r="G17" s="51" t="inlineStr">
+        <is>
+          <t>Au col de Khanh Le, les véhicules sont arrêtés par groupes pour faire face au risque de chutes de pierres.</t>
+        </is>
+      </c>
+      <c r="H17" s="51" t="inlineStr">
+        <is>
+          <t>How should rockfall risk on mountain roads be assessed and mitigated, and when is traffic control sufficient versus slope engineering?</t>
+        </is>
+      </c>
+      <c r="I17" s="47" t="inlineStr">
+        <is>
+          <t>Vietnam.vn</t>
+        </is>
+      </c>
+      <c r="J17" s="47" t="inlineStr">
+        <is>
+          <t>France</t>
+        </is>
+      </c>
+      <c r="K17" s="46" t="n">
+        <v>46317</v>
+      </c>
+      <c r="L17" s="51" t="inlineStr"/>
+      <c r="M17" s="52" t="inlineStr">
+        <is>
+          <t>Open article</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="48" customHeight="1">
+      <c r="A18" s="46" t="n">
+        <v>46319</v>
+      </c>
+      <c r="B18" s="47" t="inlineStr">
+        <is>
+          <t>2026-Q4</t>
+        </is>
+      </c>
+      <c r="C18" s="55" t="inlineStr">
+        <is>
+          <t>Infrastructure &amp; the Underground City</t>
+        </is>
+      </c>
+      <c r="D18" s="49" t="n">
+        <v>3</v>
+      </c>
+      <c r="E18" s="50" t="inlineStr">
+        <is>
+          <t>Feature lead</t>
+        </is>
+      </c>
+      <c r="F18" s="51" t="inlineStr">
+        <is>
+          <t>What options exist for Mot Mountain in Quy Nhon: levelling it or preserving the historic site?</t>
+        </is>
+      </c>
+      <c r="G18" s="51" t="inlineStr">
+        <is>
+          <t>Apa saja pilihan yang tersedia untuk Gunung Mot di Quy Nhon: meratakannya atau melestarikan situs bersejarah tersebut?</t>
+        </is>
+      </c>
+      <c r="H18" s="51" t="inlineStr">
+        <is>
+          <t>What geotechnical and heritage considerations should guide levelling versus preserving a rocky hill site in an urban coastal city?</t>
+        </is>
+      </c>
+      <c r="I18" s="47" t="inlineStr">
+        <is>
+          <t>Vietnam.vn</t>
+        </is>
+      </c>
+      <c r="J18" s="47" t="inlineStr">
+        <is>
+          <t>Indonesia</t>
+        </is>
+      </c>
+      <c r="K18" s="46" t="n">
+        <v>46319</v>
+      </c>
+      <c r="L18" s="51" t="inlineStr"/>
+      <c r="M18" s="52" t="inlineStr">
+        <is>
+          <t>Open article</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="48" customHeight="1">
+      <c r="A19" s="46" t="n">
+        <v>46319</v>
+      </c>
+      <c r="B19" s="47" t="inlineStr">
+        <is>
+          <t>2026-Q4</t>
+        </is>
+      </c>
+      <c r="C19" s="48" t="inlineStr">
+        <is>
+          <t>Hazards &amp; Resilience</t>
+        </is>
+      </c>
+      <c r="D19" s="49" t="n">
+        <v>3</v>
+      </c>
+      <c r="E19" s="58" t="inlineStr">
+        <is>
+          <t>Academia-to-Industry topic</t>
+        </is>
+      </c>
+      <c r="F19" s="51" t="inlineStr">
+        <is>
+          <t>From landslide alerts to drone safety, young innovators showcase AI solutions at IIT Guwahati</t>
+        </is>
+      </c>
+      <c r="G19" s="51" t="inlineStr"/>
+      <c r="H19" s="51" t="inlineStr">
+        <is>
+          <t>Can low-cost AI and sensor systems from student innovators provide reliable landslide early warning for practitioners?</t>
+        </is>
+      </c>
+      <c r="I19" s="47" t="inlineStr">
+        <is>
+          <t>Hub News</t>
+        </is>
+      </c>
+      <c r="J19" s="47" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="K19" s="46" t="n">
+        <v>46319</v>
+      </c>
+      <c r="L19" s="51" t="inlineStr">
+        <is>
+          <t>landslide</t>
+        </is>
+      </c>
+      <c r="M19" s="52" t="inlineStr">
+        <is>
+          <t>Open article</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="48" customHeight="1">
+      <c r="A20" s="46" t="n">
+        <v>46319</v>
+      </c>
+      <c r="B20" s="47" t="inlineStr">
+        <is>
+          <t>2026-Q4</t>
+        </is>
+      </c>
+      <c r="C20" s="55" t="inlineStr">
+        <is>
+          <t>Infrastructure &amp; the Underground City</t>
+        </is>
+      </c>
+      <c r="D20" s="49" t="n">
+        <v>3</v>
+      </c>
+      <c r="E20" s="53" t="inlineStr">
+        <is>
+          <t>News brief</t>
+        </is>
+      </c>
+      <c r="F20" s="51" t="inlineStr">
+        <is>
+          <t>Landslide Derails Locomotive in Keralam, Train Services Restored</t>
+        </is>
+      </c>
+      <c r="G20" s="51" t="inlineStr"/>
+      <c r="H20" s="51" t="inlineStr">
+        <is>
+          <t>What slope or embankment failure caused the locomotive derailment, and how should rail corridors be assessed for landslide risk?</t>
+        </is>
+      </c>
+      <c r="I20" s="47" t="inlineStr">
+        <is>
+          <t>Deccan Chronicle</t>
+        </is>
+      </c>
+      <c r="J20" s="47" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="K20" s="46" t="n">
+        <v>46317</v>
+      </c>
+      <c r="L20" s="51" t="inlineStr">
+        <is>
+          <t>landslide</t>
+        </is>
+      </c>
+      <c r="M20" s="52" t="inlineStr">
+        <is>
+          <t>Open article</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="48" customHeight="1">
+      <c r="A21" s="46" t="n">
+        <v>46319</v>
+      </c>
+      <c r="B21" s="47" t="inlineStr">
+        <is>
+          <t>2026-Q4</t>
+        </is>
+      </c>
+      <c r="C21" s="48" t="inlineStr">
+        <is>
+          <t>Hazards &amp; Resilience</t>
+        </is>
+      </c>
+      <c r="D21" s="49" t="n">
+        <v>3</v>
+      </c>
+      <c r="E21" s="53" t="inlineStr">
+        <is>
+          <t>News brief</t>
+        </is>
+      </c>
+      <c r="F21" s="51" t="inlineStr">
+        <is>
+          <t>Gas Leak, Sinkhole Shut Down Businesses Near Riverview Plaza</t>
+        </is>
+      </c>
+      <c r="G21" s="51" t="inlineStr"/>
+      <c r="H21" s="51" t="inlineStr">
+        <is>
+          <t>What caused the sinkhole near Riverview Plaza, and how do subsurface voids and utility leaks interact to create ground collapse hazards?</t>
+        </is>
+      </c>
+      <c r="I21" s="47" t="inlineStr">
+        <is>
+          <t>NewsRadio WFLA</t>
+        </is>
+      </c>
+      <c r="J21" s="47" t="inlineStr">
+        <is>
+          <t>Australia</t>
+        </is>
+      </c>
+      <c r="K21" s="46" t="n">
+        <v>46318</v>
+      </c>
+      <c r="L21" s="51" t="inlineStr">
+        <is>
+          <t>sinkhole</t>
+        </is>
+      </c>
+      <c r="M21" s="52" t="inlineStr">
+        <is>
+          <t>Open article</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="48" customHeight="1">
+      <c r="A22" s="46" t="n">
+        <v>46319</v>
+      </c>
+      <c r="B22" s="47" t="inlineStr">
+        <is>
+          <t>2026-Q4</t>
+        </is>
+      </c>
+      <c r="C22" s="48" t="inlineStr">
+        <is>
+          <t>Hazards &amp; Resilience</t>
+        </is>
+      </c>
+      <c r="D22" s="49" t="n"/>
+      <c r="E22" s="59" t="inlineStr"/>
+      <c r="F22" s="51" t="inlineStr">
         <is>
           <t>PTPP traite 31 points de glissement de terrain dans le nord de Sumatra, le projet de Lampaui est en cours Indonesian: PTPP Tangani 31 Titik Longsor di Sumut, Progres Proyek Lampaui Target</t>
         </is>
       </c>
-      <c r="G2" s="43" t="inlineStr"/>
-      <c r="H2" s="43" t="inlineStr"/>
-      <c r="I2" s="39" t="inlineStr">
+      <c r="G22" s="51" t="inlineStr"/>
+      <c r="H22" s="51" t="inlineStr"/>
+      <c r="I22" s="47" t="inlineStr">
         <is>
           <t>VOI.ID</t>
         </is>
       </c>
-      <c r="J2" s="39" t="inlineStr">
+      <c r="J22" s="47" t="inlineStr">
         <is>
           <t>France</t>
         </is>
       </c>
-      <c r="K2" s="38" t="n">
+      <c r="K22" s="46" t="n">
         <v>46318</v>
       </c>
-      <c r="L2" s="43" t="inlineStr">
+      <c r="L22" s="51" t="inlineStr">
         <is>
           <t>landslide</t>
         </is>
       </c>
-      <c r="M2" s="44" t="inlineStr">
-        <is>
-          <t>Open article</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="30" customHeight="1">
-      <c r="A3" s="38" t="n">
-        <v>46319</v>
-      </c>
-      <c r="B3" s="39" t="inlineStr">
-        <is>
-          <t>2026-Q4</t>
-        </is>
-      </c>
-      <c r="C3" s="40" t="inlineStr">
-        <is>
-          <t>Hazards &amp; Resilience</t>
-        </is>
-      </c>
-      <c r="D3" s="41" t="n"/>
-      <c r="E3" s="42" t="inlineStr"/>
-      <c r="F3" s="43" t="inlineStr">
+      <c r="M22" s="52" t="inlineStr">
+        <is>
+          <t>Open article</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="30" customHeight="1">
+      <c r="A23" s="46" t="n">
+        <v>46319</v>
+      </c>
+      <c r="B23" s="47" t="inlineStr">
+        <is>
+          <t>2026-Q4</t>
+        </is>
+      </c>
+      <c r="C23" s="48" t="inlineStr">
+        <is>
+          <t>Hazards &amp; Resilience</t>
+        </is>
+      </c>
+      <c r="D23" s="49" t="n"/>
+      <c r="E23" s="59" t="inlineStr"/>
+      <c r="F23" s="51" t="inlineStr">
         <is>
           <t>Tak Lagi Takut Tanah Longsor, Warga Desa Mengulak Lega Talud Dibangun Kokoh</t>
         </is>
       </c>
-      <c r="G3" s="43" t="inlineStr"/>
-      <c r="H3" s="43" t="inlineStr"/>
-      <c r="I3" s="39" t="inlineStr">
+      <c r="G23" s="51" t="inlineStr"/>
+      <c r="H23" s="51" t="inlineStr"/>
+      <c r="I23" s="47" t="inlineStr">
         <is>
           <t>https://investigasi.news/</t>
         </is>
       </c>
-      <c r="J3" s="39" t="inlineStr">
+      <c r="J23" s="47" t="inlineStr">
         <is>
           <t>Indonesia</t>
         </is>
       </c>
-      <c r="K3" s="38" t="n">
+      <c r="K23" s="46" t="n">
         <v>46318</v>
       </c>
-      <c r="L3" s="43" t="inlineStr">
+      <c r="L23" s="51" t="inlineStr">
         <is>
           <t>landslide, retaining wall</t>
         </is>
       </c>
-      <c r="M3" s="44" t="inlineStr">
-        <is>
-          <t>Open article</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="48" customHeight="1">
-      <c r="A4" s="38" t="n">
-        <v>46319</v>
-      </c>
-      <c r="B4" s="39" t="inlineStr">
-        <is>
-          <t>2026-Q4</t>
-        </is>
-      </c>
-      <c r="C4" s="40" t="inlineStr">
-        <is>
-          <t>Hazards &amp; Resilience</t>
-        </is>
-      </c>
-      <c r="D4" s="41" t="n"/>
-      <c r="E4" s="42" t="inlineStr"/>
-      <c r="F4" s="43" t="inlineStr">
+      <c r="M23" s="52" t="inlineStr">
+        <is>
+          <t>Open article</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="48" customHeight="1">
+      <c r="A24" s="46" t="n">
+        <v>46319</v>
+      </c>
+      <c r="B24" s="47" t="inlineStr">
+        <is>
+          <t>2026-Q4</t>
+        </is>
+      </c>
+      <c r="C24" s="48" t="inlineStr">
+        <is>
+          <t>Hazards &amp; Resilience</t>
+        </is>
+      </c>
+      <c r="D24" s="49" t="n"/>
+      <c r="E24" s="59" t="inlineStr"/>
+      <c r="F24" s="51" t="inlineStr">
         <is>
           <t>Antisipasi Longsor Jelang Musim Hujan, Satgas TMMD Kejar Penyelesaian Talud di Kalebarembeng</t>
         </is>
       </c>
-      <c r="G4" s="43" t="inlineStr"/>
-      <c r="H4" s="43" t="inlineStr"/>
-      <c r="I4" s="39" t="inlineStr">
+      <c r="G24" s="51" t="inlineStr"/>
+      <c r="H24" s="51" t="inlineStr"/>
+      <c r="I24" s="47" t="inlineStr">
         <is>
           <t>XPOSE TV</t>
         </is>
       </c>
-      <c r="J4" s="39" t="inlineStr">
+      <c r="J24" s="47" t="inlineStr">
         <is>
           <t>Indonesia</t>
         </is>
       </c>
-      <c r="K4" s="38" t="n">
+      <c r="K24" s="46" t="n">
         <v>46318</v>
       </c>
-      <c r="L4" s="43" t="inlineStr">
+      <c r="L24" s="51" t="inlineStr">
         <is>
           <t>landslide, retaining wall</t>
         </is>
       </c>
-      <c r="M4" s="44" t="inlineStr">
-        <is>
-          <t>Open article</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="30" customHeight="1">
-      <c r="A5" s="38" t="n">
-        <v>46319</v>
-      </c>
-      <c r="B5" s="39" t="inlineStr">
-        <is>
-          <t>2026-Q4</t>
-        </is>
-      </c>
-      <c r="C5" s="40" t="inlineStr">
-        <is>
-          <t>Hazards &amp; Resilience</t>
-        </is>
-      </c>
-      <c r="D5" s="41" t="n"/>
-      <c r="E5" s="42" t="inlineStr"/>
-      <c r="F5" s="43" t="inlineStr">
+      <c r="M24" s="52" t="inlineStr">
+        <is>
+          <t>Open article</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="30" customHeight="1">
+      <c r="A25" s="46" t="n">
+        <v>46319</v>
+      </c>
+      <c r="B25" s="47" t="inlineStr">
+        <is>
+          <t>2026-Q4</t>
+        </is>
+      </c>
+      <c r="C25" s="48" t="inlineStr">
+        <is>
+          <t>Hazards &amp; Resilience</t>
+        </is>
+      </c>
+      <c r="D25" s="49" t="n"/>
+      <c r="E25" s="59" t="inlineStr"/>
+      <c r="F25" s="51" t="inlineStr">
         <is>
           <t>Gard : un nouveau glissement de terrain bloque un boulevard à Villeneuve-lès-Avignon</t>
         </is>
       </c>
-      <c r="G5" s="43" t="inlineStr"/>
-      <c r="H5" s="43" t="inlineStr"/>
-      <c r="I5" s="39" t="inlineStr">
+      <c r="G25" s="51" t="inlineStr"/>
+      <c r="H25" s="51" t="inlineStr"/>
+      <c r="I25" s="47" t="inlineStr">
         <is>
           <t>Seven Radio</t>
         </is>
       </c>
-      <c r="J5" s="39" t="inlineStr">
+      <c r="J25" s="47" t="inlineStr">
         <is>
           <t>France</t>
         </is>
       </c>
-      <c r="K5" s="38" t="n">
+      <c r="K25" s="46" t="n">
         <v>46317</v>
       </c>
-      <c r="L5" s="43" t="inlineStr">
+      <c r="L25" s="51" t="inlineStr">
         <is>
           <t>landslide</t>
         </is>
       </c>
-      <c r="M5" s="44" t="inlineStr">
-        <is>
-          <t>Open article</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="30" customHeight="1">
-      <c r="A6" s="38" t="n">
-        <v>46319</v>
-      </c>
-      <c r="B6" s="39" t="inlineStr">
-        <is>
-          <t>2026-Q4</t>
-        </is>
-      </c>
-      <c r="C6" s="40" t="inlineStr">
-        <is>
-          <t>Hazards &amp; Resilience</t>
-        </is>
-      </c>
-      <c r="D6" s="41" t="n"/>
-      <c r="E6" s="42" t="inlineStr"/>
-      <c r="F6" s="43" t="inlineStr">
+      <c r="M25" s="52" t="inlineStr">
+        <is>
+          <t>Open article</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="30" customHeight="1">
+      <c r="A26" s="46" t="n">
+        <v>46319</v>
+      </c>
+      <c r="B26" s="47" t="inlineStr">
+        <is>
+          <t>2026-Q4</t>
+        </is>
+      </c>
+      <c r="C26" s="48" t="inlineStr">
+        <is>
+          <t>Hazards &amp; Resilience</t>
+        </is>
+      </c>
+      <c r="D26" s="49" t="n"/>
+      <c r="E26" s="59" t="inlineStr"/>
+      <c r="F26" s="51" t="inlineStr">
         <is>
           <t>Fr glissement de terrain : mesures d'urgence à Bonea</t>
         </is>
       </c>
-      <c r="G6" s="43" t="inlineStr"/>
-      <c r="H6" s="43" t="inlineStr"/>
-      <c r="I6" s="39" t="inlineStr">
+      <c r="G26" s="51" t="inlineStr"/>
+      <c r="H26" s="51" t="inlineStr"/>
+      <c r="I26" s="47" t="inlineStr">
         <is>
           <t>Il Mattino</t>
         </is>
       </c>
-      <c r="J6" s="39" t="inlineStr">
+      <c r="J26" s="47" t="inlineStr">
         <is>
           <t>France</t>
         </is>
       </c>
-      <c r="K6" s="38" t="n">
+      <c r="K26" s="46" t="n">
         <v>46318</v>
       </c>
-      <c r="L6" s="43" t="inlineStr">
+      <c r="L26" s="51" t="inlineStr">
         <is>
           <t>landslide</t>
         </is>
       </c>
-      <c r="M6" s="44" t="inlineStr">
-        <is>
-          <t>Open article</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="30" customHeight="1">
-      <c r="A7" s="38" t="n">
-        <v>46319</v>
-      </c>
-      <c r="B7" s="39" t="inlineStr">
-        <is>
-          <t>2026-Q4</t>
-        </is>
-      </c>
-      <c r="C7" s="40" t="inlineStr">
-        <is>
-          <t>Hazards &amp; Resilience</t>
-        </is>
-      </c>
-      <c r="D7" s="41" t="n"/>
-      <c r="E7" s="42" t="inlineStr"/>
-      <c r="F7" s="43" t="inlineStr">
+      <c r="M26" s="52" t="inlineStr">
+        <is>
+          <t>Open article</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="30" customHeight="1">
+      <c r="A27" s="46" t="n">
+        <v>46319</v>
+      </c>
+      <c r="B27" s="47" t="inlineStr">
+        <is>
+          <t>2026-Q4</t>
+        </is>
+      </c>
+      <c r="C27" s="48" t="inlineStr">
+        <is>
+          <t>Hazards &amp; Resilience</t>
+        </is>
+      </c>
+      <c r="D27" s="49" t="n"/>
+      <c r="E27" s="59" t="inlineStr"/>
+      <c r="F27" s="51" t="inlineStr">
         <is>
           <t>Grave glissement de terrain dans le sud de Chiayi</t>
         </is>
       </c>
-      <c r="G7" s="43" t="inlineStr"/>
-      <c r="H7" s="43" t="inlineStr"/>
-      <c r="I7" s="39" t="inlineStr">
+      <c r="G27" s="51" t="inlineStr"/>
+      <c r="H27" s="51" t="inlineStr"/>
+      <c r="I27" s="47" t="inlineStr">
         <is>
           <t>Vietnam.vn</t>
         </is>
       </c>
-      <c r="J7" s="39" t="inlineStr">
+      <c r="J27" s="47" t="inlineStr">
         <is>
           <t>France</t>
         </is>
       </c>
-      <c r="K7" s="38" t="n">
+      <c r="K27" s="46" t="n">
         <v>46318</v>
       </c>
-      <c r="L7" s="43" t="inlineStr">
+      <c r="L27" s="51" t="inlineStr">
         <is>
           <t>landslide</t>
         </is>
       </c>
-      <c r="M7" s="44" t="inlineStr">
-        <is>
-          <t>Open article</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="48" customHeight="1">
-      <c r="A8" s="38" t="n">
-        <v>46319</v>
-      </c>
-      <c r="B8" s="39" t="inlineStr">
-        <is>
-          <t>2026-Q4</t>
-        </is>
-      </c>
-      <c r="C8" s="40" t="inlineStr">
-        <is>
-          <t>Hazards &amp; Resilience</t>
-        </is>
-      </c>
-      <c r="D8" s="41" t="n"/>
-      <c r="E8" s="42" t="inlineStr"/>
-      <c r="F8" s="43" t="inlineStr">
+      <c r="M27" s="52" t="inlineStr">
+        <is>
+          <t>Open article</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="48" customHeight="1">
+      <c r="A28" s="46" t="n">
+        <v>46319</v>
+      </c>
+      <c r="B28" s="47" t="inlineStr">
+        <is>
+          <t>2026-Q4</t>
+        </is>
+      </c>
+      <c r="C28" s="48" t="inlineStr">
+        <is>
+          <t>Hazards &amp; Resilience</t>
+        </is>
+      </c>
+      <c r="D28" s="49" t="n"/>
+      <c r="E28" s="59" t="inlineStr"/>
+      <c r="F28" s="51" t="inlineStr">
         <is>
           <t>Nghe An : Il est urgent d'agir face au glissement de terrain sur le talus le long de la route côtière.</t>
         </is>
       </c>
-      <c r="G8" s="43" t="inlineStr"/>
-      <c r="H8" s="43" t="inlineStr"/>
-      <c r="I8" s="39" t="inlineStr">
+      <c r="G28" s="51" t="inlineStr"/>
+      <c r="H28" s="51" t="inlineStr"/>
+      <c r="I28" s="47" t="inlineStr">
         <is>
           <t>Vietnam.vn</t>
         </is>
       </c>
-      <c r="J8" s="39" t="inlineStr">
+      <c r="J28" s="47" t="inlineStr">
         <is>
           <t>France</t>
         </is>
       </c>
-      <c r="K8" s="38" t="n">
+      <c r="K28" s="46" t="n">
         <v>46318</v>
       </c>
-      <c r="L8" s="43" t="inlineStr">
+      <c r="L28" s="51" t="inlineStr">
         <is>
           <t>landslide, slope</t>
         </is>
       </c>
-      <c r="M8" s="44" t="inlineStr">
-        <is>
-          <t>Open article</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="48" customHeight="1">
-      <c r="A9" s="38" t="n">
-        <v>46319</v>
-      </c>
-      <c r="B9" s="39" t="inlineStr">
-        <is>
-          <t>2026-Q4</t>
-        </is>
-      </c>
-      <c r="C9" s="40" t="inlineStr">
-        <is>
-          <t>Hazards &amp; Resilience</t>
-        </is>
-      </c>
-      <c r="D9" s="41" t="n"/>
-      <c r="E9" s="42" t="inlineStr"/>
-      <c r="F9" s="43" t="inlineStr">
+      <c r="M28" s="52" t="inlineStr">
+        <is>
+          <t>Open article</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="48" customHeight="1">
+      <c r="A29" s="46" t="n">
+        <v>46319</v>
+      </c>
+      <c r="B29" s="47" t="inlineStr">
+        <is>
+          <t>2026-Q4</t>
+        </is>
+      </c>
+      <c r="C29" s="48" t="inlineStr">
+        <is>
+          <t>Hazards &amp; Resilience</t>
+        </is>
+      </c>
+      <c r="D29" s="49" t="n"/>
+      <c r="E29" s="59" t="inlineStr"/>
+      <c r="F29" s="51" t="inlineStr">
         <is>
           <t>Evalúan estabilización de laderas y subsidios para familias ante deslizamiento de tierra en Lota</t>
         </is>
       </c>
-      <c r="G9" s="43" t="inlineStr"/>
-      <c r="H9" s="43" t="inlineStr"/>
-      <c r="I9" s="39" t="inlineStr">
+      <c r="G29" s="51" t="inlineStr"/>
+      <c r="H29" s="51" t="inlineStr"/>
+      <c r="I29" s="47" t="inlineStr">
         <is>
           <t>Diario Concepción</t>
         </is>
       </c>
-      <c r="J9" s="39" t="inlineStr">
+      <c r="J29" s="47" t="inlineStr">
         <is>
           <t>Spain</t>
         </is>
       </c>
-      <c r="K9" s="38" t="n">
+      <c r="K29" s="46" t="n">
         <v>46318</v>
       </c>
-      <c r="L9" s="43" t="inlineStr">
+      <c r="L29" s="51" t="inlineStr">
         <is>
           <t>landslide, slope</t>
         </is>
       </c>
-      <c r="M9" s="44" t="inlineStr">
-        <is>
-          <t>Open article</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="30" customHeight="1">
-      <c r="A10" s="38" t="n">
-        <v>46319</v>
-      </c>
-      <c r="B10" s="39" t="inlineStr">
-        <is>
-          <t>2026-Q4</t>
-        </is>
-      </c>
-      <c r="C10" s="40" t="inlineStr">
-        <is>
-          <t>Hazards &amp; Resilience</t>
-        </is>
-      </c>
-      <c r="D10" s="41" t="n"/>
-      <c r="E10" s="42" t="inlineStr"/>
-      <c r="F10" s="43" t="inlineStr">
+      <c r="M29" s="52" t="inlineStr">
+        <is>
+          <t>Open article</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="30" customHeight="1">
+      <c r="A30" s="46" t="n">
+        <v>46319</v>
+      </c>
+      <c r="B30" s="47" t="inlineStr">
+        <is>
+          <t>2026-Q4</t>
+        </is>
+      </c>
+      <c r="C30" s="48" t="inlineStr">
+        <is>
+          <t>Hazards &amp; Resilience</t>
+        </is>
+      </c>
+      <c r="D30" s="49" t="n"/>
+      <c r="E30" s="59" t="inlineStr"/>
+      <c r="F30" s="51" t="inlineStr">
         <is>
           <t>Concepción: trabajos de despeje avanzan tras deslizamiento de tierra en Juan Riquelme</t>
         </is>
       </c>
-      <c r="G10" s="43" t="inlineStr"/>
-      <c r="H10" s="43" t="inlineStr"/>
-      <c r="I10" s="39" t="inlineStr">
+      <c r="G30" s="51" t="inlineStr"/>
+      <c r="H30" s="51" t="inlineStr"/>
+      <c r="I30" s="47" t="inlineStr">
         <is>
           <t>Canal 9 Bío Bío Televisión</t>
         </is>
       </c>
-      <c r="J10" s="39" t="inlineStr">
+      <c r="J30" s="47" t="inlineStr">
         <is>
           <t>Spain</t>
         </is>
       </c>
-      <c r="K10" s="38" t="n">
+      <c r="K30" s="46" t="n">
         <v>46318</v>
       </c>
-      <c r="L10" s="43" t="inlineStr">
+      <c r="L30" s="51" t="inlineStr">
         <is>
           <t>landslide</t>
         </is>
       </c>
-      <c r="M10" s="44" t="inlineStr">
-        <is>
-          <t>Open article</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="30" customHeight="1">
-      <c r="A11" s="38" t="n">
-        <v>46319</v>
-      </c>
-      <c r="B11" s="39" t="inlineStr">
-        <is>
-          <t>2026-Q4</t>
-        </is>
-      </c>
-      <c r="C11" s="40" t="inlineStr">
-        <is>
-          <t>Hazards &amp; Resilience</t>
-        </is>
-      </c>
-      <c r="D11" s="41" t="n"/>
-      <c r="E11" s="42" t="inlineStr"/>
-      <c r="F11" s="43" t="inlineStr">
+      <c r="M30" s="52" t="inlineStr">
+        <is>
+          <t>Open article</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="30" customHeight="1">
+      <c r="A31" s="46" t="n">
+        <v>46319</v>
+      </c>
+      <c r="B31" s="47" t="inlineStr">
+        <is>
+          <t>2026-Q4</t>
+        </is>
+      </c>
+      <c r="C31" s="48" t="inlineStr">
+        <is>
+          <t>Hazards &amp; Resilience</t>
+        </is>
+      </c>
+      <c r="D31" s="49" t="n"/>
+      <c r="E31" s="59" t="inlineStr"/>
+      <c r="F31" s="51" t="inlineStr">
         <is>
           <t>Viviendas Colapsan por Deslizamiento de Tierra en Lomas Conjunto Residencial, Tijuana</t>
         </is>
       </c>
-      <c r="G11" s="43" t="inlineStr"/>
-      <c r="H11" s="43" t="inlineStr"/>
-      <c r="I11" s="39" t="inlineStr">
+      <c r="G31" s="51" t="inlineStr"/>
+      <c r="H31" s="51" t="inlineStr"/>
+      <c r="I31" s="47" t="inlineStr">
         <is>
           <t>N+</t>
         </is>
       </c>
-      <c r="J11" s="39" t="inlineStr">
+      <c r="J31" s="47" t="inlineStr">
         <is>
           <t>Spain</t>
         </is>
       </c>
-      <c r="K11" s="38" t="n">
+      <c r="K31" s="46" t="n">
         <v>46318</v>
       </c>
-      <c r="L11" s="43" t="inlineStr">
+      <c r="L31" s="51" t="inlineStr">
         <is>
           <t>landslide</t>
         </is>
       </c>
-      <c r="M11" s="44" t="inlineStr">
-        <is>
-          <t>Open article</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="48" customHeight="1">
-      <c r="A12" s="38" t="n">
-        <v>46319</v>
-      </c>
-      <c r="B12" s="39" t="inlineStr">
-        <is>
-          <t>2026-Q4</t>
-        </is>
-      </c>
-      <c r="C12" s="40" t="inlineStr">
-        <is>
-          <t>Hazards &amp; Resilience</t>
-        </is>
-      </c>
-      <c r="D12" s="41" t="n"/>
-      <c r="E12" s="42" t="inlineStr"/>
-      <c r="F12" s="43" t="inlineStr">
+      <c r="M31" s="52" t="inlineStr">
+        <is>
+          <t>Open article</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="48" customHeight="1">
+      <c r="A32" s="46" t="n">
+        <v>46319</v>
+      </c>
+      <c r="B32" s="47" t="inlineStr">
+        <is>
+          <t>2026-Q4</t>
+        </is>
+      </c>
+      <c r="C32" s="48" t="inlineStr">
+        <is>
+          <t>Hazards &amp; Resilience</t>
+        </is>
+      </c>
+      <c r="D32" s="49" t="n"/>
+      <c r="E32" s="59" t="inlineStr"/>
+      <c r="F32" s="51" t="inlineStr">
         <is>
           <t>La atención se centra en la reparación de los deslizamientos de tierra en la Carretera Nacional 15C.</t>
         </is>
       </c>
-      <c r="G12" s="43" t="inlineStr"/>
-      <c r="H12" s="43" t="inlineStr"/>
-      <c r="I12" s="39" t="inlineStr">
+      <c r="G32" s="51" t="inlineStr"/>
+      <c r="H32" s="51" t="inlineStr"/>
+      <c r="I32" s="47" t="inlineStr">
         <is>
           <t>Vietnam.vn</t>
         </is>
       </c>
-      <c r="J12" s="39" t="inlineStr">
+      <c r="J32" s="47" t="inlineStr">
         <is>
           <t>Spain</t>
         </is>
       </c>
-      <c r="K12" s="38" t="n">
+      <c r="K32" s="46" t="n">
         <v>46318</v>
       </c>
-      <c r="L12" s="43" t="inlineStr">
+      <c r="L32" s="51" t="inlineStr">
         <is>
           <t>landslide</t>
         </is>
       </c>
-      <c r="M12" s="44" t="inlineStr">
-        <is>
-          <t>Open article</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="30" customHeight="1">
-      <c r="A13" s="38" t="n">
-        <v>46319</v>
-      </c>
-      <c r="B13" s="39" t="inlineStr">
-        <is>
-          <t>2026-Q4</t>
-        </is>
-      </c>
-      <c r="C13" s="40" t="inlineStr">
-        <is>
-          <t>Hazards &amp; Resilience</t>
-        </is>
-      </c>
-      <c r="D13" s="41" t="n"/>
-      <c r="E13" s="42" t="inlineStr"/>
-      <c r="F13" s="43" t="inlineStr">
+      <c r="M32" s="52" t="inlineStr">
+        <is>
+          <t>Open article</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="30" customHeight="1">
+      <c r="A33" s="46" t="n">
+        <v>46319</v>
+      </c>
+      <c r="B33" s="47" t="inlineStr">
+        <is>
+          <t>2026-Q4</t>
+        </is>
+      </c>
+      <c r="C33" s="48" t="inlineStr">
+        <is>
+          <t>Hazards &amp; Resilience</t>
+        </is>
+      </c>
+      <c r="D33" s="49" t="n"/>
+      <c r="E33" s="59" t="inlineStr"/>
+      <c r="F33" s="51" t="inlineStr">
         <is>
           <t>Limpieza tras deslizamiento habilitó la vía Riobamba–Cebadas</t>
         </is>
       </c>
-      <c r="G13" s="43" t="inlineStr"/>
-      <c r="H13" s="43" t="inlineStr"/>
-      <c r="I13" s="39" t="inlineStr">
+      <c r="G33" s="51" t="inlineStr"/>
+      <c r="H33" s="51" t="inlineStr"/>
+      <c r="I33" s="47" t="inlineStr">
         <is>
           <t>diariolosandes.com.ec</t>
         </is>
       </c>
-      <c r="J13" s="39" t="inlineStr">
+      <c r="J33" s="47" t="inlineStr">
         <is>
           <t>Spain</t>
         </is>
       </c>
-      <c r="K13" s="38" t="n">
-        <v>46319</v>
-      </c>
-      <c r="L13" s="43" t="inlineStr">
+      <c r="K33" s="46" t="n">
+        <v>46319</v>
+      </c>
+      <c r="L33" s="51" t="inlineStr">
         <is>
           <t>landslide</t>
         </is>
       </c>
-      <c r="M13" s="44" t="inlineStr">
-        <is>
-          <t>Open article</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="48" customHeight="1">
-      <c r="A14" s="38" t="n">
-        <v>46319</v>
-      </c>
-      <c r="B14" s="39" t="inlineStr">
-        <is>
-          <t>2026-Q4</t>
-        </is>
-      </c>
-      <c r="C14" s="40" t="inlineStr">
-        <is>
-          <t>Hazards &amp; Resilience</t>
-        </is>
-      </c>
-      <c r="D14" s="41" t="n"/>
-      <c r="E14" s="42" t="inlineStr"/>
-      <c r="F14" s="43" t="inlineStr">
+      <c r="M33" s="52" t="inlineStr">
+        <is>
+          <t>Open article</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="48" customHeight="1">
+      <c r="A34" s="46" t="n">
+        <v>46319</v>
+      </c>
+      <c r="B34" s="47" t="inlineStr">
+        <is>
+          <t>2026-Q4</t>
+        </is>
+      </c>
+      <c r="C34" s="48" t="inlineStr">
+        <is>
+          <t>Hazards &amp; Resilience</t>
+        </is>
+      </c>
+      <c r="D34" s="49" t="n"/>
+      <c r="E34" s="59" t="inlineStr"/>
+      <c r="F34" s="51" t="inlineStr">
         <is>
           <t>Emergencia en Moniquirá, Boyacá, por deslizamiento de tierra en la vereda de Pajales tras fuertes lluvias: se reportan tres casas afectadas</t>
         </is>
       </c>
-      <c r="G14" s="43" t="inlineStr"/>
-      <c r="H14" s="43" t="inlineStr"/>
-      <c r="I14" s="39" t="inlineStr">
+      <c r="G34" s="51" t="inlineStr"/>
+      <c r="H34" s="51" t="inlineStr"/>
+      <c r="I34" s="47" t="inlineStr">
         <is>
           <t>El Tiempo</t>
         </is>
       </c>
-      <c r="J14" s="39" t="inlineStr">
+      <c r="J34" s="47" t="inlineStr">
         <is>
           <t>Spain</t>
         </is>
       </c>
-      <c r="K14" s="38" t="n">
+      <c r="K34" s="46" t="n">
         <v>46318</v>
       </c>
-      <c r="L14" s="43" t="inlineStr">
+      <c r="L34" s="51" t="inlineStr">
         <is>
           <t>landslide</t>
         </is>
       </c>
-      <c r="M14" s="44" t="inlineStr">
-        <is>
-          <t>Open article</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="30" customHeight="1">
-      <c r="A15" s="38" t="n">
-        <v>46319</v>
-      </c>
-      <c r="B15" s="39" t="inlineStr">
-        <is>
-          <t>2026-Q4</t>
-        </is>
-      </c>
-      <c r="C15" s="40" t="inlineStr">
-        <is>
-          <t>Hazards &amp; Resilience</t>
-        </is>
-      </c>
-      <c r="D15" s="41" t="n"/>
-      <c r="E15" s="42" t="inlineStr"/>
-      <c r="F15" s="43" t="inlineStr">
+      <c r="M34" s="52" t="inlineStr">
+        <is>
+          <t>Open article</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="30" customHeight="1">
+      <c r="A35" s="46" t="n">
+        <v>46319</v>
+      </c>
+      <c r="B35" s="47" t="inlineStr">
+        <is>
+          <t>2026-Q4</t>
+        </is>
+      </c>
+      <c r="C35" s="48" t="inlineStr">
+        <is>
+          <t>Hazards &amp; Resilience</t>
+        </is>
+      </c>
+      <c r="D35" s="49" t="n"/>
+      <c r="E35" s="59" t="inlineStr"/>
+      <c r="F35" s="51" t="inlineStr">
         <is>
           <t>Deslizamiento de tierra en Pahuatlán</t>
         </is>
       </c>
-      <c r="G15" s="43" t="inlineStr"/>
-      <c r="H15" s="43" t="inlineStr"/>
-      <c r="I15" s="39" t="inlineStr">
+      <c r="G35" s="51" t="inlineStr"/>
+      <c r="H35" s="51" t="inlineStr"/>
+      <c r="I35" s="47" t="inlineStr">
         <is>
           <t>Diario sin Secretos</t>
         </is>
       </c>
-      <c r="J15" s="39" t="inlineStr">
+      <c r="J35" s="47" t="inlineStr">
         <is>
           <t>Spain</t>
         </is>
       </c>
-      <c r="K15" s="38" t="n">
-        <v>46319</v>
-      </c>
-      <c r="L15" s="43" t="inlineStr">
+      <c r="K35" s="46" t="n">
+        <v>46319</v>
+      </c>
+      <c r="L35" s="51" t="inlineStr">
         <is>
           <t>landslide</t>
         </is>
       </c>
-      <c r="M15" s="44" t="inlineStr">
-        <is>
-          <t>Open article</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="48" customHeight="1">
-      <c r="A16" s="38" t="n">
-        <v>46319</v>
-      </c>
-      <c r="B16" s="39" t="inlineStr">
-        <is>
-          <t>2026-Q4</t>
-        </is>
-      </c>
-      <c r="C16" s="40" t="inlineStr">
-        <is>
-          <t>Hazards &amp; Resilience</t>
-        </is>
-      </c>
-      <c r="D16" s="41" t="n"/>
-      <c r="E16" s="42" t="inlineStr"/>
-      <c r="F16" s="43" t="inlineStr">
+      <c r="M35" s="52" t="inlineStr">
+        <is>
+          <t>Open article</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="48" customHeight="1">
+      <c r="A36" s="46" t="n">
+        <v>46319</v>
+      </c>
+      <c r="B36" s="47" t="inlineStr">
+        <is>
+          <t>2026-Q4</t>
+        </is>
+      </c>
+      <c r="C36" s="48" t="inlineStr">
+        <is>
+          <t>Hazards &amp; Resilience</t>
+        </is>
+      </c>
+      <c r="D36" s="49" t="n"/>
+      <c r="E36" s="59" t="inlineStr"/>
+      <c r="F36" s="51" t="inlineStr">
         <is>
           <t>Calle intransitable por el barro: deslizamiento de tierra afecta a sector Juan Riquelme de Concepción</t>
         </is>
       </c>
-      <c r="G16" s="43" t="inlineStr"/>
-      <c r="H16" s="43" t="inlineStr"/>
-      <c r="I16" s="39" t="inlineStr">
+      <c r="G36" s="51" t="inlineStr"/>
+      <c r="H36" s="51" t="inlineStr"/>
+      <c r="I36" s="47" t="inlineStr">
         <is>
           <t>BioBioChile</t>
         </is>
       </c>
-      <c r="J16" s="39" t="inlineStr">
+      <c r="J36" s="47" t="inlineStr">
         <is>
           <t>Spain</t>
         </is>
       </c>
-      <c r="K16" s="38" t="n">
+      <c r="K36" s="46" t="n">
         <v>46317</v>
       </c>
-      <c r="L16" s="43" t="inlineStr">
+      <c r="L36" s="51" t="inlineStr">
         <is>
           <t>landslide</t>
         </is>
       </c>
-      <c r="M16" s="44" t="inlineStr">
-        <is>
-          <t>Open article</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="30" customHeight="1">
-      <c r="A17" s="38" t="n">
-        <v>46319</v>
-      </c>
-      <c r="B17" s="39" t="inlineStr">
-        <is>
-          <t>2026-Q4</t>
-        </is>
-      </c>
-      <c r="C17" s="40" t="inlineStr">
-        <is>
-          <t>Hazards &amp; Resilience</t>
-        </is>
-      </c>
-      <c r="D17" s="41" t="n"/>
-      <c r="E17" s="42" t="inlineStr"/>
-      <c r="F17" s="43" t="inlineStr">
+      <c r="M36" s="52" t="inlineStr">
+        <is>
+          <t>Open article</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="30" customHeight="1">
+      <c r="A37" s="46" t="n">
+        <v>46319</v>
+      </c>
+      <c r="B37" s="47" t="inlineStr">
+        <is>
+          <t>2026-Q4</t>
+        </is>
+      </c>
+      <c r="C37" s="48" t="inlineStr">
+        <is>
+          <t>Hazards &amp; Resilience</t>
+        </is>
+      </c>
+      <c r="D37" s="49" t="n"/>
+      <c r="E37" s="59" t="inlineStr"/>
+      <c r="F37" s="51" t="inlineStr">
         <is>
           <t>Deslizamiento de Tierra Obliga al Cierre Total en Bonea</t>
         </is>
       </c>
-      <c r="G17" s="43" t="inlineStr"/>
-      <c r="H17" s="43" t="inlineStr"/>
-      <c r="I17" s="39" t="inlineStr">
+      <c r="G37" s="51" t="inlineStr"/>
+      <c r="H37" s="51" t="inlineStr"/>
+      <c r="I37" s="47" t="inlineStr">
         <is>
           <t>Il Mattino</t>
         </is>
       </c>
-      <c r="J17" s="39" t="inlineStr">
+      <c r="J37" s="47" t="inlineStr">
         <is>
           <t>Spain</t>
         </is>
       </c>
-      <c r="K17" s="38" t="n">
+      <c r="K37" s="46" t="n">
         <v>46318</v>
       </c>
-      <c r="L17" s="43" t="inlineStr">
+      <c r="L37" s="51" t="inlineStr">
         <is>
           <t>landslide</t>
         </is>
       </c>
-      <c r="M17" s="44" t="inlineStr">
-        <is>
-          <t>Open article</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="48" customHeight="1">
-      <c r="A18" s="38" t="n">
-        <v>46319</v>
-      </c>
-      <c r="B18" s="39" t="inlineStr">
-        <is>
-          <t>2026-Q4</t>
-        </is>
-      </c>
-      <c r="C18" s="40" t="inlineStr">
-        <is>
-          <t>Hazards &amp; Resilience</t>
-        </is>
-      </c>
-      <c r="D18" s="41" t="n"/>
-      <c r="E18" s="42" t="inlineStr"/>
-      <c r="F18" s="43" t="inlineStr">
+      <c r="M37" s="52" t="inlineStr">
+        <is>
+          <t>Open article</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="48" customHeight="1">
+      <c r="A38" s="46" t="n">
+        <v>46319</v>
+      </c>
+      <c r="B38" s="47" t="inlineStr">
+        <is>
+          <t>2026-Q4</t>
+        </is>
+      </c>
+      <c r="C38" s="48" t="inlineStr">
+        <is>
+          <t>Hazards &amp; Resilience</t>
+        </is>
+      </c>
+      <c r="D38" s="49" t="n"/>
+      <c r="E38" s="59" t="inlineStr"/>
+      <c r="F38" s="51" t="inlineStr">
         <is>
           <t>Evalúan riesgos por deslizamiento de tierra en Lota y analizan apoyo habitacional para familias afectadas</t>
         </is>
       </c>
-      <c r="G18" s="43" t="inlineStr"/>
-      <c r="H18" s="43" t="inlineStr"/>
-      <c r="I18" s="39" t="inlineStr">
+      <c r="G38" s="51" t="inlineStr"/>
+      <c r="H38" s="51" t="inlineStr"/>
+      <c r="I38" s="47" t="inlineStr">
         <is>
           <t>La Tribuna</t>
         </is>
       </c>
-      <c r="J18" s="39" t="inlineStr">
+      <c r="J38" s="47" t="inlineStr">
         <is>
           <t>Spain</t>
         </is>
       </c>
-      <c r="K18" s="38" t="n">
+      <c r="K38" s="46" t="n">
         <v>46318</v>
       </c>
-      <c r="L18" s="43" t="inlineStr">
+      <c r="L38" s="51" t="inlineStr">
         <is>
           <t>landslide</t>
         </is>
       </c>
-      <c r="M18" s="44" t="inlineStr">
-        <is>
-          <t>Open article</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="30" customHeight="1">
-      <c r="A19" s="38" t="n">
-        <v>46319</v>
-      </c>
-      <c r="B19" s="39" t="inlineStr">
-        <is>
-          <t>2026-Q4</t>
-        </is>
-      </c>
-      <c r="C19" s="40" t="inlineStr">
-        <is>
-          <t>Hazards &amp; Resilience</t>
-        </is>
-      </c>
-      <c r="D19" s="41" t="n"/>
-      <c r="E19" s="42" t="inlineStr"/>
-      <c r="F19" s="43" t="inlineStr">
+      <c r="M38" s="52" t="inlineStr">
+        <is>
+          <t>Open article</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="30" customHeight="1">
+      <c r="A39" s="46" t="n">
+        <v>46319</v>
+      </c>
+      <c r="B39" s="47" t="inlineStr">
+        <is>
+          <t>2026-Q4</t>
+        </is>
+      </c>
+      <c r="C39" s="48" t="inlineStr">
+        <is>
+          <t>Hazards &amp; Resilience</t>
+        </is>
+      </c>
+      <c r="D39" s="49" t="n"/>
+      <c r="E39" s="59" t="inlineStr"/>
+      <c r="F39" s="51" t="inlineStr">
         <is>
           <t>Deslizamiento de tierra cierra la vía Alóag–Santo Domingo en ambos sentidos</t>
         </is>
       </c>
-      <c r="G19" s="43" t="inlineStr"/>
-      <c r="H19" s="43" t="inlineStr"/>
-      <c r="I19" s="39" t="inlineStr">
+      <c r="G39" s="51" t="inlineStr"/>
+      <c r="H39" s="51" t="inlineStr"/>
+      <c r="I39" s="47" t="inlineStr">
         <is>
           <t>Teleamazonas</t>
         </is>
       </c>
-      <c r="J19" s="39" t="inlineStr">
+      <c r="J39" s="47" t="inlineStr">
         <is>
           <t>Spain</t>
         </is>
       </c>
-      <c r="K19" s="38" t="n">
+      <c r="K39" s="46" t="n">
         <v>46318</v>
       </c>
-      <c r="L19" s="43" t="inlineStr">
+      <c r="L39" s="51" t="inlineStr">
         <is>
           <t>landslide</t>
         </is>
       </c>
-      <c r="M19" s="44" t="inlineStr">
-        <is>
-          <t>Open article</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="48" customHeight="1">
-      <c r="A20" s="38" t="n">
-        <v>46319</v>
-      </c>
-      <c r="B20" s="39" t="inlineStr">
-        <is>
-          <t>2026-Q4</t>
-        </is>
-      </c>
-      <c r="C20" s="40" t="inlineStr">
-        <is>
-          <t>Hazards &amp; Resilience</t>
-        </is>
-      </c>
-      <c r="D20" s="41" t="n"/>
-      <c r="E20" s="42" t="inlineStr"/>
-      <c r="F20" s="43" t="inlineStr">
+      <c r="M39" s="52" t="inlineStr">
+        <is>
+          <t>Open article</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="48" customHeight="1">
+      <c r="A40" s="46" t="n">
+        <v>46319</v>
+      </c>
+      <c r="B40" s="47" t="inlineStr">
+        <is>
+          <t>2026-Q4</t>
+        </is>
+      </c>
+      <c r="C40" s="48" t="inlineStr">
+        <is>
+          <t>Hazards &amp; Resilience</t>
+        </is>
+      </c>
+      <c r="D40" s="49" t="n"/>
+      <c r="E40" s="59" t="inlineStr"/>
+      <c r="F40" s="51" t="inlineStr">
         <is>
           <t>Deslizamiento de tierra en la vía Salinas-Lita moviliza maquinaria para habilitar el tránsito en Imbabura</t>
         </is>
       </c>
-      <c r="G20" s="43" t="inlineStr"/>
-      <c r="H20" s="43" t="inlineStr"/>
-      <c r="I20" s="39" t="inlineStr">
+      <c r="G40" s="51" t="inlineStr"/>
+      <c r="H40" s="51" t="inlineStr"/>
+      <c r="I40" s="47" t="inlineStr">
         <is>
           <t>El Universo</t>
         </is>
       </c>
-      <c r="J20" s="39" t="inlineStr">
+      <c r="J40" s="47" t="inlineStr">
         <is>
           <t>Spain</t>
         </is>
       </c>
-      <c r="K20" s="38" t="n">
+      <c r="K40" s="46" t="n">
         <v>46317</v>
       </c>
-      <c r="L20" s="43" t="inlineStr">
+      <c r="L40" s="51" t="inlineStr">
         <is>
           <t>landslide</t>
         </is>
       </c>
-      <c r="M20" s="44" t="inlineStr">
-        <is>
-          <t>Open article</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="48" customHeight="1">
-      <c r="A21" s="38" t="n">
-        <v>46319</v>
-      </c>
-      <c r="B21" s="39" t="inlineStr">
-        <is>
-          <t>2026-Q4</t>
-        </is>
-      </c>
-      <c r="C21" s="40" t="inlineStr">
-        <is>
-          <t>Hazards &amp; Resilience</t>
-        </is>
-      </c>
-      <c r="D21" s="41" t="n"/>
-      <c r="E21" s="42" t="inlineStr"/>
-      <c r="F21" s="43" t="inlineStr">
+      <c r="M40" s="52" t="inlineStr">
+        <is>
+          <t>Open article</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="48" customHeight="1">
+      <c r="A41" s="46" t="n">
+        <v>46319</v>
+      </c>
+      <c r="B41" s="47" t="inlineStr">
+        <is>
+          <t>2026-Q4</t>
+        </is>
+      </c>
+      <c r="C41" s="48" t="inlineStr">
+        <is>
+          <t>Hazards &amp; Resilience</t>
+        </is>
+      </c>
+      <c r="D41" s="49" t="n"/>
+      <c r="E41" s="59" t="inlineStr"/>
+      <c r="F41" s="51" t="inlineStr">
         <is>
           <t>Ministerio de Salud mantiene vigilancia tras deslizamiento de tierra en zona minera de Remance</t>
         </is>
       </c>
-      <c r="G21" s="43" t="inlineStr"/>
-      <c r="H21" s="43" t="inlineStr"/>
-      <c r="I21" s="39" t="inlineStr">
+      <c r="G41" s="51" t="inlineStr"/>
+      <c r="H41" s="51" t="inlineStr"/>
+      <c r="I41" s="47" t="inlineStr">
         <is>
           <t>Destino Panamá</t>
         </is>
       </c>
-      <c r="J21" s="39" t="inlineStr">
+      <c r="J41" s="47" t="inlineStr">
         <is>
           <t>Spain</t>
         </is>
       </c>
-      <c r="K21" s="38" t="n">
-        <v>46319</v>
-      </c>
-      <c r="L21" s="43" t="inlineStr">
+      <c r="K41" s="46" t="n">
+        <v>46319</v>
+      </c>
+      <c r="L41" s="51" t="inlineStr">
         <is>
           <t>landslide</t>
         </is>
       </c>
-      <c r="M21" s="44" t="inlineStr">
-        <is>
-          <t>Open article</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="48" customHeight="1">
-      <c r="A22" s="38" t="n">
-        <v>46319</v>
-      </c>
-      <c r="B22" s="39" t="inlineStr">
-        <is>
-          <t>2026-Q4</t>
-        </is>
-      </c>
-      <c r="C22" s="40" t="inlineStr">
-        <is>
-          <t>Hazards &amp; Resilience</t>
-        </is>
-      </c>
-      <c r="D22" s="41" t="n"/>
-      <c r="E22" s="42" t="inlineStr"/>
-      <c r="F22" s="43" t="inlineStr">
+      <c r="M41" s="52" t="inlineStr">
+        <is>
+          <t>Open article</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="48" customHeight="1">
+      <c r="A42" s="46" t="n">
+        <v>46319</v>
+      </c>
+      <c r="B42" s="47" t="inlineStr">
+        <is>
+          <t>2026-Q4</t>
+        </is>
+      </c>
+      <c r="C42" s="48" t="inlineStr">
+        <is>
+          <t>Hazards &amp; Resilience</t>
+        </is>
+      </c>
+      <c r="D42" s="49" t="n"/>
+      <c r="E42" s="59" t="inlineStr"/>
+      <c r="F42" s="51" t="inlineStr">
         <is>
           <t>El 24 de octubre de 2026 se emitió una alerta por alto riesgo de inundaciones repentinas y deslizamientos de tierra en muchas zonas de Tuyen Quang.</t>
         </is>
       </c>
-      <c r="G22" s="43" t="inlineStr"/>
-      <c r="H22" s="43" t="inlineStr"/>
-      <c r="I22" s="39" t="inlineStr">
+      <c r="G42" s="51" t="inlineStr"/>
+      <c r="H42" s="51" t="inlineStr"/>
+      <c r="I42" s="47" t="inlineStr">
         <is>
           <t>Vietnam.vn</t>
         </is>
       </c>
-      <c r="J22" s="39" t="inlineStr">
+      <c r="J42" s="47" t="inlineStr">
         <is>
           <t>Spain</t>
         </is>
       </c>
-      <c r="K22" s="38" t="n">
+      <c r="K42" s="46" t="n">
         <v>46318</v>
       </c>
-      <c r="L22" s="43" t="inlineStr">
+      <c r="L42" s="51" t="inlineStr">
         <is>
           <t>landslide</t>
         </is>
       </c>
-      <c r="M22" s="44" t="inlineStr">
-        <is>
-          <t>Open article</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="30" customHeight="1">
-      <c r="A23" s="38" t="n">
-        <v>46319</v>
-      </c>
-      <c r="B23" s="39" t="inlineStr">
-        <is>
-          <t>2026-Q4</t>
-        </is>
-      </c>
-      <c r="C23" s="40" t="inlineStr">
-        <is>
-          <t>Hazards &amp; Resilience</t>
-        </is>
-      </c>
-      <c r="D23" s="41" t="n"/>
-      <c r="E23" s="42" t="inlineStr"/>
-      <c r="F23" s="43" t="inlineStr">
+      <c r="M42" s="52" t="inlineStr">
+        <is>
+          <t>Open article</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="30" customHeight="1">
+      <c r="A43" s="46" t="n">
+        <v>46319</v>
+      </c>
+      <c r="B43" s="47" t="inlineStr">
+        <is>
+          <t>2026-Q4</t>
+        </is>
+      </c>
+      <c r="C43" s="48" t="inlineStr">
+        <is>
+          <t>Hazards &amp; Resilience</t>
+        </is>
+      </c>
+      <c r="D43" s="49" t="n"/>
+      <c r="E43" s="59" t="inlineStr"/>
+      <c r="F43" s="51" t="inlineStr">
         <is>
           <t>Concepción: lluvias activan aluvión y deslizamiento de tierra en Juan Riquelme</t>
         </is>
       </c>
-      <c r="G23" s="43" t="inlineStr"/>
-      <c r="H23" s="43" t="inlineStr"/>
-      <c r="I23" s="39" t="inlineStr">
+      <c r="G43" s="51" t="inlineStr"/>
+      <c r="H43" s="51" t="inlineStr"/>
+      <c r="I43" s="47" t="inlineStr">
         <is>
           <t>Diario Concepción</t>
         </is>
       </c>
-      <c r="J23" s="39" t="inlineStr">
+      <c r="J43" s="47" t="inlineStr">
         <is>
           <t>Spain</t>
         </is>
       </c>
-      <c r="K23" s="38" t="n">
+      <c r="K43" s="46" t="n">
         <v>46317</v>
       </c>
-      <c r="L23" s="43" t="inlineStr">
+      <c r="L43" s="51" t="inlineStr">
         <is>
           <t>landslide</t>
         </is>
       </c>
-      <c r="M23" s="44" t="inlineStr">
-        <is>
-          <t>Open article</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="30" customHeight="1">
-      <c r="A24" s="38" t="n">
-        <v>46319</v>
-      </c>
-      <c r="B24" s="39" t="inlineStr">
-        <is>
-          <t>2026-Q4</t>
-        </is>
-      </c>
-      <c r="C24" s="40" t="inlineStr">
-        <is>
-          <t>Hazards &amp; Resilience</t>
-        </is>
-      </c>
-      <c r="D24" s="41" t="n"/>
-      <c r="E24" s="42" t="inlineStr"/>
-      <c r="F24" s="43" t="inlineStr">
+      <c r="M43" s="52" t="inlineStr">
+        <is>
+          <t>Open article</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="30" customHeight="1">
+      <c r="A44" s="46" t="n">
+        <v>46319</v>
+      </c>
+      <c r="B44" s="47" t="inlineStr">
+        <is>
+          <t>2026-Q4</t>
+        </is>
+      </c>
+      <c r="C44" s="48" t="inlineStr">
+        <is>
+          <t>Hazards &amp; Resilience</t>
+        </is>
+      </c>
+      <c r="D44" s="49" t="n"/>
+      <c r="E44" s="59" t="inlineStr"/>
+      <c r="F44" s="51" t="inlineStr">
         <is>
           <t>Dos casas se derrumbaron debido a deslizamientos de tierra a lo largo del río Tien.</t>
         </is>
       </c>
-      <c r="G24" s="43" t="inlineStr"/>
-      <c r="H24" s="43" t="inlineStr"/>
-      <c r="I24" s="39" t="inlineStr">
+      <c r="G44" s="51" t="inlineStr"/>
+      <c r="H44" s="51" t="inlineStr"/>
+      <c r="I44" s="47" t="inlineStr">
         <is>
           <t>Vietnam.vn</t>
         </is>
       </c>
-      <c r="J24" s="39" t="inlineStr">
+      <c r="J44" s="47" t="inlineStr">
         <is>
           <t>Spain</t>
         </is>
       </c>
-      <c r="K24" s="38" t="n">
+      <c r="K44" s="46" t="n">
         <v>46318</v>
       </c>
-      <c r="L24" s="43" t="inlineStr">
+      <c r="L44" s="51" t="inlineStr">
         <is>
           <t>landslide</t>
         </is>
       </c>
-      <c r="M24" s="44" t="inlineStr">
-        <is>
-          <t>Open article</t>
-        </is>
-      </c>
-    </row>
-    <row r="25" ht="48" customHeight="1">
-      <c r="A25" s="38" t="n">
-        <v>46319</v>
-      </c>
-      <c r="B25" s="39" t="inlineStr">
-        <is>
-          <t>2026-Q4</t>
-        </is>
-      </c>
-      <c r="C25" s="40" t="inlineStr">
-        <is>
-          <t>Hazards &amp; Resilience</t>
-        </is>
-      </c>
-      <c r="D25" s="41" t="n"/>
-      <c r="E25" s="42" t="inlineStr"/>
-      <c r="F25" s="43" t="inlineStr">
+      <c r="M44" s="52" t="inlineStr">
+        <is>
+          <t>Open article</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" ht="48" customHeight="1">
+      <c r="A45" s="46" t="n">
+        <v>46319</v>
+      </c>
+      <c r="B45" s="47" t="inlineStr">
+        <is>
+          <t>2026-Q4</t>
+        </is>
+      </c>
+      <c r="C45" s="48" t="inlineStr">
+        <is>
+          <t>Hazards &amp; Resilience</t>
+        </is>
+      </c>
+      <c r="D45" s="49" t="n"/>
+      <c r="E45" s="59" t="inlineStr"/>
+      <c r="F45" s="51" t="inlineStr">
         <is>
           <t>Nghe An: Se necesitan medidas urgentes para solucionar el deslizamiento de tierra en el terraplén a lo largo de la carretera costera.</t>
         </is>
       </c>
-      <c r="G25" s="43" t="inlineStr"/>
-      <c r="H25" s="43" t="inlineStr"/>
-      <c r="I25" s="39" t="inlineStr">
+      <c r="G45" s="51" t="inlineStr"/>
+      <c r="H45" s="51" t="inlineStr"/>
+      <c r="I45" s="47" t="inlineStr">
         <is>
           <t>Vietnam.vn</t>
         </is>
       </c>
-      <c r="J25" s="39" t="inlineStr">
+      <c r="J45" s="47" t="inlineStr">
         <is>
           <t>Spain</t>
         </is>
       </c>
-      <c r="K25" s="38" t="n">
+      <c r="K45" s="46" t="n">
         <v>46318</v>
       </c>
-      <c r="L25" s="43" t="inlineStr">
+      <c r="L45" s="51" t="inlineStr">
         <is>
           <t>landslide, embankment</t>
         </is>
       </c>
-      <c r="M25" s="44" t="inlineStr">
-        <is>
-          <t>Open article</t>
-        </is>
-      </c>
-    </row>
-    <row r="26" ht="48" customHeight="1">
-      <c r="A26" s="38" t="n">
-        <v>46319</v>
-      </c>
-      <c r="B26" s="39" t="inlineStr">
-        <is>
-          <t>2026-Q4</t>
-        </is>
-      </c>
-      <c r="C26" s="40" t="inlineStr">
-        <is>
-          <t>Hazards &amp; Resilience</t>
-        </is>
-      </c>
-      <c r="D26" s="41" t="n"/>
-      <c r="E26" s="42" t="inlineStr"/>
-      <c r="F26" s="43" t="inlineStr">
+      <c r="M45" s="52" t="inlineStr">
+        <is>
+          <t>Open article</t>
+        </is>
+      </c>
+    </row>
+    <row r="46" ht="48" customHeight="1">
+      <c r="A46" s="46" t="n">
+        <v>46319</v>
+      </c>
+      <c r="B46" s="47" t="inlineStr">
+        <is>
+          <t>2026-Q4</t>
+        </is>
+      </c>
+      <c r="C46" s="48" t="inlineStr">
+        <is>
+          <t>Hazards &amp; Resilience</t>
+        </is>
+      </c>
+      <c r="D46" s="49" t="n"/>
+      <c r="E46" s="59" t="inlineStr"/>
+      <c r="F46" s="51" t="inlineStr">
         <is>
           <t>Concepción: deslizamiento de tierra afecta 2 viviendas y bloquea calle en Juan Riquelme por el barro</t>
         </is>
       </c>
-      <c r="G26" s="43" t="inlineStr"/>
-      <c r="H26" s="43" t="inlineStr"/>
-      <c r="I26" s="39" t="inlineStr">
+      <c r="G46" s="51" t="inlineStr"/>
+      <c r="H46" s="51" t="inlineStr"/>
+      <c r="I46" s="47" t="inlineStr">
         <is>
           <t>Canal 9 Bío Bío Televisión</t>
         </is>
       </c>
-      <c r="J26" s="39" t="inlineStr">
+      <c r="J46" s="47" t="inlineStr">
         <is>
           <t>Spain</t>
         </is>
       </c>
-      <c r="K26" s="38" t="n">
+      <c r="K46" s="46" t="n">
         <v>46318</v>
       </c>
-      <c r="L26" s="43" t="inlineStr">
+      <c r="L46" s="51" t="inlineStr">
         <is>
           <t>landslide</t>
         </is>
       </c>
-      <c r="M26" s="44" t="inlineStr">
-        <is>
-          <t>Open article</t>
-        </is>
-      </c>
-    </row>
-    <row r="27" ht="30" customHeight="1">
-      <c r="A27" s="38" t="n">
-        <v>46319</v>
-      </c>
-      <c r="B27" s="39" t="inlineStr">
-        <is>
-          <t>2026-Q4</t>
-        </is>
-      </c>
-      <c r="C27" s="40" t="inlineStr">
-        <is>
-          <t>Hazards &amp; Resilience</t>
-        </is>
-      </c>
-      <c r="D27" s="41" t="n"/>
-      <c r="E27" s="42" t="inlineStr"/>
-      <c r="F27" s="43" t="inlineStr">
+      <c r="M46" s="52" t="inlineStr">
+        <is>
+          <t>Open article</t>
+        </is>
+      </c>
+    </row>
+    <row r="47" ht="30" customHeight="1">
+      <c r="A47" s="46" t="n">
+        <v>46319</v>
+      </c>
+      <c r="B47" s="47" t="inlineStr">
+        <is>
+          <t>2026-Q4</t>
+        </is>
+      </c>
+      <c r="C47" s="48" t="inlineStr">
+        <is>
+          <t>Hazards &amp; Resilience</t>
+        </is>
+      </c>
+      <c r="D47" s="49" t="n"/>
+      <c r="E47" s="59" t="inlineStr"/>
+      <c r="F47" s="51" t="inlineStr">
         <is>
           <t>Arcata comprará el parcela del barranco y comenzará la reparación de deslizamientos</t>
         </is>
       </c>
-      <c r="G27" s="43" t="inlineStr"/>
-      <c r="H27" s="43" t="inlineStr"/>
-      <c r="I27" s="39" t="inlineStr">
+      <c r="G47" s="51" t="inlineStr"/>
+      <c r="H47" s="51" t="inlineStr"/>
+      <c r="I47" s="47" t="inlineStr">
         <is>
           <t>Lost Coast Outpost</t>
         </is>
       </c>
-      <c r="J27" s="39" t="inlineStr">
+      <c r="J47" s="47" t="inlineStr">
         <is>
           <t>Spain</t>
         </is>
       </c>
-      <c r="K27" s="38" t="n">
+      <c r="K47" s="46" t="n">
         <v>46317</v>
       </c>
-      <c r="L27" s="43" t="inlineStr">
+      <c r="L47" s="51" t="inlineStr">
         <is>
           <t>landslide</t>
         </is>
       </c>
-      <c r="M27" s="44" t="inlineStr">
-        <is>
-          <t>Open article</t>
-        </is>
-      </c>
-    </row>
-    <row r="28" ht="30" customHeight="1">
-      <c r="A28" s="38" t="n">
-        <v>46319</v>
-      </c>
-      <c r="B28" s="39" t="inlineStr">
-        <is>
-          <t>2026-Q4</t>
-        </is>
-      </c>
-      <c r="C28" s="40" t="inlineStr">
-        <is>
-          <t>Hazards &amp; Resilience</t>
-        </is>
-      </c>
-      <c r="D28" s="41" t="n"/>
-      <c r="E28" s="42" t="inlineStr"/>
-      <c r="F28" s="43" t="inlineStr">
+      <c r="M47" s="52" t="inlineStr">
+        <is>
+          <t>Open article</t>
+        </is>
+      </c>
+    </row>
+    <row r="48" ht="30" customHeight="1">
+      <c r="A48" s="46" t="n">
+        <v>46319</v>
+      </c>
+      <c r="B48" s="47" t="inlineStr">
+        <is>
+          <t>2026-Q4</t>
+        </is>
+      </c>
+      <c r="C48" s="48" t="inlineStr">
+        <is>
+          <t>Hazards &amp; Resilience</t>
+        </is>
+      </c>
+      <c r="D48" s="49" t="n"/>
+      <c r="E48" s="59" t="inlineStr"/>
+      <c r="F48" s="51" t="inlineStr">
         <is>
           <t>Auto y viviendas afectadas tras deslizamiento de tierra en Concepción</t>
         </is>
       </c>
-      <c r="G28" s="43" t="inlineStr"/>
-      <c r="H28" s="43" t="inlineStr"/>
-      <c r="I28" s="39" t="inlineStr">
+      <c r="G48" s="51" t="inlineStr"/>
+      <c r="H48" s="51" t="inlineStr"/>
+      <c r="I48" s="47" t="inlineStr">
         <is>
           <t>Meganoticias</t>
         </is>
       </c>
-      <c r="J28" s="39" t="inlineStr">
+      <c r="J48" s="47" t="inlineStr">
         <is>
           <t>Spain</t>
         </is>
       </c>
-      <c r="K28" s="38" t="n">
+      <c r="K48" s="46" t="n">
         <v>46317</v>
       </c>
-      <c r="L28" s="43" t="inlineStr">
+      <c r="L48" s="51" t="inlineStr">
         <is>
           <t>landslide</t>
         </is>
       </c>
-      <c r="M28" s="44" t="inlineStr">
-        <is>
-          <t>Open article</t>
-        </is>
-      </c>
-    </row>
-    <row r="29" ht="30" customHeight="1">
-      <c r="A29" s="38" t="n">
-        <v>46319</v>
-      </c>
-      <c r="B29" s="39" t="inlineStr">
-        <is>
-          <t>2026-Q4</t>
-        </is>
-      </c>
-      <c r="C29" s="40" t="inlineStr">
-        <is>
-          <t>Hazards &amp; Resilience</t>
-        </is>
-      </c>
-      <c r="D29" s="41" t="n"/>
-      <c r="E29" s="42" t="inlineStr"/>
-      <c r="F29" s="43" t="inlineStr">
+      <c r="M48" s="52" t="inlineStr">
+        <is>
+          <t>Open article</t>
+        </is>
+      </c>
+    </row>
+    <row r="49" ht="30" customHeight="1">
+      <c r="A49" s="46" t="n">
+        <v>46319</v>
+      </c>
+      <c r="B49" s="47" t="inlineStr">
+        <is>
+          <t>2026-Q4</t>
+        </is>
+      </c>
+      <c r="C49" s="48" t="inlineStr">
+        <is>
+          <t>Hazards &amp; Resilience</t>
+        </is>
+      </c>
+      <c r="D49" s="49" t="n"/>
+      <c r="E49" s="59" t="inlineStr"/>
+      <c r="F49" s="51" t="inlineStr">
         <is>
           <t>En peligro vecinos del bulevar Felipe J. Mery por deslizamiento de tierra</t>
         </is>
       </c>
-      <c r="G29" s="43" t="inlineStr"/>
-      <c r="H29" s="43" t="inlineStr"/>
-      <c r="I29" s="39" t="inlineStr">
+      <c r="G49" s="51" t="inlineStr"/>
+      <c r="H49" s="51" t="inlineStr"/>
+      <c r="I49" s="47" t="inlineStr">
         <is>
           <t>RCG Media</t>
         </is>
       </c>
-      <c r="J29" s="39" t="inlineStr">
+      <c r="J49" s="47" t="inlineStr">
         <is>
           <t>Spain</t>
         </is>
       </c>
-      <c r="K29" s="38" t="n">
+      <c r="K49" s="46" t="n">
         <v>46317</v>
       </c>
-      <c r="L29" s="43" t="inlineStr">
+      <c r="L49" s="51" t="inlineStr">
         <is>
           <t>landslide</t>
         </is>
       </c>
-      <c r="M29" s="44" t="inlineStr">
-        <is>
-          <t>Open article</t>
-        </is>
-      </c>
-    </row>
-    <row r="30" ht="30" customHeight="1">
-      <c r="A30" s="38" t="n">
-        <v>46319</v>
-      </c>
-      <c r="B30" s="39" t="inlineStr">
-        <is>
-          <t>2026-Q4</t>
-        </is>
-      </c>
-      <c r="C30" s="40" t="inlineStr">
-        <is>
-          <t>Hazards &amp; Resilience</t>
-        </is>
-      </c>
-      <c r="D30" s="41" t="n"/>
-      <c r="E30" s="42" t="inlineStr"/>
-      <c r="F30" s="43" t="inlineStr">
+      <c r="M49" s="52" t="inlineStr">
+        <is>
+          <t>Open article</t>
+        </is>
+      </c>
+    </row>
+    <row r="50" ht="30" customHeight="1">
+      <c r="A50" s="46" t="n">
+        <v>46319</v>
+      </c>
+      <c r="B50" s="47" t="inlineStr">
+        <is>
+          <t>2026-Q4</t>
+        </is>
+      </c>
+      <c r="C50" s="48" t="inlineStr">
+        <is>
+          <t>Hazards &amp; Resilience</t>
+        </is>
+      </c>
+      <c r="D50" s="49" t="n"/>
+      <c r="E50" s="59" t="inlineStr"/>
+      <c r="F50" s="51" t="inlineStr">
         <is>
           <t>Un terraplén de prevención de deslizamientos de tierra "amenaza" una zona residencial.</t>
         </is>
       </c>
-      <c r="G30" s="43" t="inlineStr"/>
-      <c r="H30" s="43" t="inlineStr"/>
-      <c r="I30" s="39" t="inlineStr">
+      <c r="G50" s="51" t="inlineStr"/>
+      <c r="H50" s="51" t="inlineStr"/>
+      <c r="I50" s="47" t="inlineStr">
         <is>
           <t>Vietnam.vn</t>
         </is>
       </c>
-      <c r="J30" s="39" t="inlineStr">
+      <c r="J50" s="47" t="inlineStr">
         <is>
           <t>Spain</t>
         </is>
       </c>
-      <c r="K30" s="38" t="n">
+      <c r="K50" s="46" t="n">
         <v>46318</v>
       </c>
-      <c r="L30" s="43" t="inlineStr">
+      <c r="L50" s="51" t="inlineStr">
         <is>
           <t>landslide, embankment</t>
         </is>
       </c>
-      <c r="M30" s="44" t="inlineStr">
-        <is>
-          <t>Open article</t>
-        </is>
-      </c>
-    </row>
-    <row r="31" ht="48" customHeight="1">
-      <c r="A31" s="38" t="n">
-        <v>46319</v>
-      </c>
-      <c r="B31" s="39" t="inlineStr">
-        <is>
-          <t>2026-Q4</t>
-        </is>
-      </c>
-      <c r="C31" s="40" t="inlineStr">
-        <is>
-          <t>Hazards &amp; Resilience</t>
-        </is>
-      </c>
-      <c r="D31" s="41" t="n"/>
-      <c r="E31" s="42" t="inlineStr"/>
-      <c r="F31" s="43" t="inlineStr">
+      <c r="M50" s="52" t="inlineStr">
+        <is>
+          <t>Open article</t>
+        </is>
+      </c>
+    </row>
+    <row r="51" ht="48" customHeight="1">
+      <c r="A51" s="46" t="n">
+        <v>46319</v>
+      </c>
+      <c r="B51" s="47" t="inlineStr">
+        <is>
+          <t>2026-Q4</t>
+        </is>
+      </c>
+      <c r="C51" s="48" t="inlineStr">
+        <is>
+          <t>Hazards &amp; Resilience</t>
+        </is>
+      </c>
+      <c r="D51" s="49" t="n"/>
+      <c r="E51" s="59" t="inlineStr"/>
+      <c r="F51" s="51" t="inlineStr">
         <is>
           <t>Fuertes lluvias provocan deslizamientos en Moniquirá: en la vereda Pajales la tierra se abrió en dos</t>
         </is>
       </c>
-      <c r="G31" s="43" t="inlineStr"/>
-      <c r="H31" s="43" t="inlineStr"/>
-      <c r="I31" s="39" t="inlineStr">
+      <c r="G51" s="51" t="inlineStr"/>
+      <c r="H51" s="51" t="inlineStr"/>
+      <c r="I51" s="47" t="inlineStr">
         <is>
           <t>Revista Semana</t>
         </is>
       </c>
-      <c r="J31" s="39" t="inlineStr">
+      <c r="J51" s="47" t="inlineStr">
         <is>
           <t>Spain</t>
         </is>
       </c>
-      <c r="K31" s="38" t="n">
+      <c r="K51" s="46" t="n">
         <v>46318</v>
       </c>
-      <c r="L31" s="43" t="inlineStr">
+      <c r="L51" s="51" t="inlineStr">
         <is>
           <t>landslide</t>
         </is>
       </c>
-      <c r="M31" s="44" t="inlineStr">
-        <is>
-          <t>Open article</t>
-        </is>
-      </c>
-    </row>
-    <row r="32" ht="48" customHeight="1">
-      <c r="A32" s="38" t="n">
-        <v>46319</v>
-      </c>
-      <c r="B32" s="39" t="inlineStr">
-        <is>
-          <t>2026-Q4</t>
-        </is>
-      </c>
-      <c r="C32" s="40" t="inlineStr">
-        <is>
-          <t>Hazards &amp; Resilience</t>
-        </is>
-      </c>
-      <c r="D32" s="41" t="n"/>
-      <c r="E32" s="42" t="inlineStr"/>
-      <c r="F32" s="43" t="inlineStr">
+      <c r="M51" s="52" t="inlineStr">
+        <is>
+          <t>Open article</t>
+        </is>
+      </c>
+    </row>
+    <row r="52" ht="48" customHeight="1">
+      <c r="A52" s="46" t="n">
+        <v>46319</v>
+      </c>
+      <c r="B52" s="47" t="inlineStr">
+        <is>
+          <t>2026-Q4</t>
+        </is>
+      </c>
+      <c r="C52" s="48" t="inlineStr">
+        <is>
+          <t>Hazards &amp; Resilience</t>
+        </is>
+      </c>
+      <c r="D52" s="49" t="n"/>
+      <c r="E52" s="59" t="inlineStr"/>
+      <c r="F52" s="51" t="inlineStr">
         <is>
           <t>Alcaldía de Villavicencio adecua paso peatonal provisional tras deslizamiento en Buenavista</t>
         </is>
       </c>
-      <c r="G32" s="43" t="inlineStr"/>
-      <c r="H32" s="43" t="inlineStr"/>
-      <c r="I32" s="39" t="inlineStr">
+      <c r="G52" s="51" t="inlineStr"/>
+      <c r="H52" s="51" t="inlineStr"/>
+      <c r="I52" s="47" t="inlineStr">
         <is>
           <t>Periódico del Meta</t>
         </is>
       </c>
-      <c r="J32" s="39" t="inlineStr">
+      <c r="J52" s="47" t="inlineStr">
         <is>
           <t>Spain</t>
         </is>
       </c>
-      <c r="K32" s="38" t="n">
+      <c r="K52" s="46" t="n">
         <v>46318</v>
       </c>
-      <c r="L32" s="43" t="inlineStr">
+      <c r="L52" s="51" t="inlineStr">
         <is>
           <t>landslide</t>
         </is>
       </c>
-      <c r="M32" s="44" t="inlineStr">
-        <is>
-          <t>Open article</t>
-        </is>
-      </c>
-    </row>
-    <row r="33" ht="30" customHeight="1">
-      <c r="A33" s="38" t="n">
-        <v>46319</v>
-      </c>
-      <c r="B33" s="39" t="inlineStr">
-        <is>
-          <t>2026-Q4</t>
-        </is>
-      </c>
-      <c r="C33" s="40" t="inlineStr">
-        <is>
-          <t>Hazards &amp; Resilience</t>
-        </is>
-      </c>
-      <c r="D33" s="41" t="n"/>
-      <c r="E33" s="42" t="inlineStr"/>
-      <c r="F33" s="43" t="inlineStr">
+      <c r="M52" s="52" t="inlineStr">
+        <is>
+          <t>Open article</t>
+        </is>
+      </c>
+    </row>
+    <row r="53" ht="30" customHeight="1">
+      <c r="A53" s="46" t="n">
+        <v>46319</v>
+      </c>
+      <c r="B53" s="47" t="inlineStr">
+        <is>
+          <t>2026-Q4</t>
+        </is>
+      </c>
+      <c r="C53" s="48" t="inlineStr">
+        <is>
+          <t>Hazards &amp; Resilience</t>
+        </is>
+      </c>
+      <c r="D53" s="49" t="n"/>
+      <c r="E53" s="59" t="inlineStr"/>
+      <c r="F53" s="51" t="inlineStr">
         <is>
           <t>Advierten por Posible Deslizamiento en el Bulevar Mar de Cortés en Tijuana, BC</t>
         </is>
       </c>
-      <c r="G33" s="43" t="inlineStr"/>
-      <c r="H33" s="43" t="inlineStr"/>
-      <c r="I33" s="39" t="inlineStr">
+      <c r="G53" s="51" t="inlineStr"/>
+      <c r="H53" s="51" t="inlineStr"/>
+      <c r="I53" s="47" t="inlineStr">
         <is>
           <t>N+</t>
         </is>
       </c>
-      <c r="J33" s="39" t="inlineStr">
+      <c r="J53" s="47" t="inlineStr">
         <is>
           <t>Spain</t>
         </is>
       </c>
-      <c r="K33" s="38" t="n">
+      <c r="K53" s="46" t="n">
         <v>46318</v>
       </c>
-      <c r="L33" s="43" t="inlineStr">
+      <c r="L53" s="51" t="inlineStr">
         <is>
           <t>landslide</t>
         </is>
       </c>
-      <c r="M33" s="44" t="inlineStr">
-        <is>
-          <t>Open article</t>
-        </is>
-      </c>
-    </row>
-    <row r="34" ht="30" customHeight="1">
-      <c r="A34" s="38" t="n">
-        <v>46319</v>
-      </c>
-      <c r="B34" s="39" t="inlineStr">
-        <is>
-          <t>2026-Q4</t>
-        </is>
-      </c>
-      <c r="C34" s="40" t="inlineStr">
-        <is>
-          <t>Hazards &amp; Resilience</t>
-        </is>
-      </c>
-      <c r="D34" s="41" t="n"/>
-      <c r="E34" s="42" t="inlineStr"/>
-      <c r="F34" s="43" t="inlineStr">
+      <c r="M53" s="52" t="inlineStr">
+        <is>
+          <t>Open article</t>
+        </is>
+      </c>
+    </row>
+    <row r="54" ht="30" customHeight="1">
+      <c r="A54" s="46" t="n">
+        <v>46319</v>
+      </c>
+      <c r="B54" s="47" t="inlineStr">
+        <is>
+          <t>2026-Q4</t>
+        </is>
+      </c>
+      <c r="C54" s="48" t="inlineStr">
+        <is>
+          <t>Hazards &amp; Resilience</t>
+        </is>
+      </c>
+      <c r="D54" s="49" t="n"/>
+      <c r="E54" s="59" t="inlineStr"/>
+      <c r="F54" s="51" t="inlineStr">
         <is>
           <t>Grave deslizamiento de tierra en el sur de Chiayi.</t>
         </is>
       </c>
-      <c r="G34" s="43" t="inlineStr"/>
-      <c r="H34" s="43" t="inlineStr"/>
-      <c r="I34" s="39" t="inlineStr">
+      <c r="G54" s="51" t="inlineStr"/>
+      <c r="H54" s="51" t="inlineStr"/>
+      <c r="I54" s="47" t="inlineStr">
         <is>
           <t>Vietnam.vn</t>
         </is>
       </c>
-      <c r="J34" s="39" t="inlineStr">
+      <c r="J54" s="47" t="inlineStr">
         <is>
           <t>Spain</t>
         </is>
       </c>
-      <c r="K34" s="38" t="n">
+      <c r="K54" s="46" t="n">
         <v>46317</v>
       </c>
-      <c r="L34" s="43" t="inlineStr">
+      <c r="L54" s="51" t="inlineStr">
         <is>
           <t>landslide</t>
         </is>
       </c>
-      <c r="M34" s="44" t="inlineStr">
-        <is>
-          <t>Open article</t>
-        </is>
-      </c>
-    </row>
-    <row r="35" ht="48" customHeight="1">
-      <c r="A35" s="38" t="n">
-        <v>46319</v>
-      </c>
-      <c r="B35" s="39" t="inlineStr">
-        <is>
-          <t>2026-Q4</t>
-        </is>
-      </c>
-      <c r="C35" s="40" t="inlineStr">
-        <is>
-          <t>Hazards &amp; Resilience</t>
-        </is>
-      </c>
-      <c r="D35" s="41" t="n"/>
-      <c r="E35" s="42" t="inlineStr"/>
-      <c r="F35" s="43" t="inlineStr">
+      <c r="M54" s="52" t="inlineStr">
+        <is>
+          <t>Open article</t>
+        </is>
+      </c>
+    </row>
+    <row r="55" ht="48" customHeight="1">
+      <c r="A55" s="46" t="n">
+        <v>46319</v>
+      </c>
+      <c r="B55" s="47" t="inlineStr">
+        <is>
+          <t>2026-Q4</t>
+        </is>
+      </c>
+      <c r="C55" s="48" t="inlineStr">
+        <is>
+          <t>Hazards &amp; Resilience</t>
+        </is>
+      </c>
+      <c r="D55" s="49" t="n"/>
+      <c r="E55" s="59" t="inlineStr"/>
+      <c r="F55" s="51" t="inlineStr">
         <is>
           <t>Deslizamiento en Muzo afecta colegio y deja sin clases a 120 estudiantes por las fuertes lluvias</t>
         </is>
       </c>
-      <c r="G35" s="43" t="inlineStr"/>
-      <c r="H35" s="43" t="inlineStr"/>
-      <c r="I35" s="39" t="inlineStr">
+      <c r="G55" s="51" t="inlineStr"/>
+      <c r="H55" s="51" t="inlineStr"/>
+      <c r="I55" s="47" t="inlineStr">
         <is>
           <t>Caracol Radio</t>
         </is>
       </c>
-      <c r="J35" s="39" t="inlineStr">
+      <c r="J55" s="47" t="inlineStr">
         <is>
           <t>Spain</t>
         </is>
       </c>
-      <c r="K35" s="38" t="n">
+      <c r="K55" s="46" t="n">
         <v>46318</v>
       </c>
-      <c r="L35" s="43" t="inlineStr">
+      <c r="L55" s="51" t="inlineStr">
         <is>
           <t>landslide</t>
         </is>
       </c>
-      <c r="M35" s="44" t="inlineStr">
-        <is>
-          <t>Open article</t>
-        </is>
-      </c>
-    </row>
-    <row r="36" ht="48" customHeight="1">
-      <c r="A36" s="38" t="n">
-        <v>46319</v>
-      </c>
-      <c r="B36" s="39" t="inlineStr">
-        <is>
-          <t>2026-Q4</t>
-        </is>
-      </c>
-      <c r="C36" s="40" t="inlineStr">
-        <is>
-          <t>Hazards &amp; Resilience</t>
-        </is>
-      </c>
-      <c r="D36" s="41" t="n"/>
-      <c r="E36" s="42" t="inlineStr"/>
-      <c r="F36" s="43" t="inlineStr">
+      <c r="M55" s="52" t="inlineStr">
+        <is>
+          <t>Open article</t>
+        </is>
+      </c>
+    </row>
+    <row r="56" ht="48" customHeight="1">
+      <c r="A56" s="46" t="n">
+        <v>46319</v>
+      </c>
+      <c r="B56" s="47" t="inlineStr">
+        <is>
+          <t>2026-Q4</t>
+        </is>
+      </c>
+      <c r="C56" s="48" t="inlineStr">
+        <is>
+          <t>Hazards &amp; Resilience</t>
+        </is>
+      </c>
+      <c r="D56" s="49" t="n"/>
+      <c r="E56" s="59" t="inlineStr"/>
+      <c r="F56" s="51" t="inlineStr">
         <is>
           <t>Organismos de emergencia atendieron ayer varios deslizamientos en Manizales por las lluvias. 🔗 Encuentre el link de la noticia en el primer comentario 🗞️</t>
         </is>
       </c>
-      <c r="G36" s="43" t="inlineStr"/>
-      <c r="H36" s="43" t="inlineStr"/>
-      <c r="I36" s="39" t="inlineStr">
+      <c r="G56" s="51" t="inlineStr"/>
+      <c r="H56" s="51" t="inlineStr"/>
+      <c r="I56" s="47" t="inlineStr">
         <is>
           <t>Facebook</t>
         </is>
       </c>
-      <c r="J36" s="39" t="inlineStr">
+      <c r="J56" s="47" t="inlineStr">
         <is>
           <t>Spain</t>
         </is>
       </c>
-      <c r="K36" s="38" t="n">
+      <c r="K56" s="46" t="n">
         <v>46317</v>
       </c>
-      <c r="L36" s="43" t="inlineStr">
+      <c r="L56" s="51" t="inlineStr">
         <is>
           <t>landslide</t>
         </is>
       </c>
-      <c r="M36" s="44" t="inlineStr">
-        <is>
-          <t>Open article</t>
-        </is>
-      </c>
-    </row>
-    <row r="37" ht="30" customHeight="1">
-      <c r="A37" s="38" t="n">
-        <v>46319</v>
-      </c>
-      <c r="B37" s="39" t="inlineStr">
-        <is>
-          <t>2026-Q4</t>
-        </is>
-      </c>
-      <c r="C37" s="40" t="inlineStr">
-        <is>
-          <t>Hazards &amp; Resilience</t>
-        </is>
-      </c>
-      <c r="D37" s="41" t="n"/>
-      <c r="E37" s="42" t="inlineStr"/>
-      <c r="F37" s="43" t="inlineStr">
+      <c r="M56" s="52" t="inlineStr">
+        <is>
+          <t>Open article</t>
+        </is>
+      </c>
+    </row>
+    <row r="57" ht="30" customHeight="1">
+      <c r="A57" s="46" t="n">
+        <v>46319</v>
+      </c>
+      <c r="B57" s="47" t="inlineStr">
+        <is>
+          <t>2026-Q4</t>
+        </is>
+      </c>
+      <c r="C57" s="48" t="inlineStr">
+        <is>
+          <t>Hazards &amp; Resilience</t>
+        </is>
+      </c>
+      <c r="D57" s="49" t="n"/>
+      <c r="E57" s="59" t="inlineStr"/>
+      <c r="F57" s="51" t="inlineStr">
         <is>
           <t>Fuertes lluvias provocan deslizamientos en Moniquirá, Boyacá</t>
         </is>
       </c>
-      <c r="G37" s="43" t="inlineStr"/>
-      <c r="H37" s="43" t="inlineStr"/>
-      <c r="I37" s="39" t="inlineStr">
+      <c r="G57" s="51" t="inlineStr"/>
+      <c r="H57" s="51" t="inlineStr"/>
+      <c r="I57" s="47" t="inlineStr">
         <is>
           <t>Agencia de Periodismo Investigativo</t>
         </is>
       </c>
-      <c r="J37" s="39" t="inlineStr">
+      <c r="J57" s="47" t="inlineStr">
         <is>
           <t>Spain</t>
         </is>
       </c>
-      <c r="K37" s="38" t="n">
+      <c r="K57" s="46" t="n">
         <v>46318</v>
       </c>
-      <c r="L37" s="43" t="inlineStr">
+      <c r="L57" s="51" t="inlineStr">
         <is>
           <t>landslide</t>
         </is>
       </c>
-      <c r="M37" s="44" t="inlineStr">
-        <is>
-          <t>Open article</t>
-        </is>
-      </c>
-    </row>
-    <row r="38" ht="48" customHeight="1">
-      <c r="A38" s="38" t="n">
-        <v>46319</v>
-      </c>
-      <c r="B38" s="39" t="inlineStr">
-        <is>
-          <t>2026-Q4</t>
-        </is>
-      </c>
-      <c r="C38" s="40" t="inlineStr">
-        <is>
-          <t>Hazards &amp; Resilience</t>
-        </is>
-      </c>
-      <c r="D38" s="41" t="n"/>
-      <c r="E38" s="42" t="inlineStr"/>
-      <c r="F38" s="43" t="inlineStr">
+      <c r="M57" s="52" t="inlineStr">
+        <is>
+          <t>Open article</t>
+        </is>
+      </c>
+    </row>
+    <row r="58" ht="48" customHeight="1">
+      <c r="A58" s="46" t="n">
+        <v>46319</v>
+      </c>
+      <c r="B58" s="47" t="inlineStr">
+        <is>
+          <t>2026-Q4</t>
+        </is>
+      </c>
+      <c r="C58" s="48" t="inlineStr">
+        <is>
+          <t>Hazards &amp; Resilience</t>
+        </is>
+      </c>
+      <c r="D58" s="49" t="n"/>
+      <c r="E58" s="59" t="inlineStr"/>
+      <c r="F58" s="51" t="inlineStr">
         <is>
           <t>Deslizamiento de tierra mantiene totalmente suspendido el tránsito en la Ruta 5 Norte en Canela</t>
         </is>
       </c>
-      <c r="G38" s="43" t="inlineStr"/>
-      <c r="H38" s="43" t="inlineStr"/>
-      <c r="I38" s="39" t="inlineStr">
+      <c r="G58" s="51" t="inlineStr"/>
+      <c r="H58" s="51" t="inlineStr"/>
+      <c r="I58" s="47" t="inlineStr">
         <is>
           <t>Mi Radio</t>
         </is>
       </c>
-      <c r="J38" s="39" t="inlineStr">
+      <c r="J58" s="47" t="inlineStr">
         <is>
           <t>Spain</t>
         </is>
       </c>
-      <c r="K38" s="38" t="n">
+      <c r="K58" s="46" t="n">
         <v>46317</v>
       </c>
-      <c r="L38" s="43" t="inlineStr">
+      <c r="L58" s="51" t="inlineStr">
         <is>
           <t>landslide</t>
         </is>
       </c>
-      <c r="M38" s="44" t="inlineStr">
-        <is>
-          <t>Open article</t>
-        </is>
-      </c>
-    </row>
-    <row r="39" ht="30" customHeight="1">
-      <c r="A39" s="38" t="n">
-        <v>46319</v>
-      </c>
-      <c r="B39" s="39" t="inlineStr">
-        <is>
-          <t>2026-Q4</t>
-        </is>
-      </c>
-      <c r="C39" s="40" t="inlineStr">
-        <is>
-          <t>Hazards &amp; Resilience</t>
-        </is>
-      </c>
-      <c r="D39" s="41" t="n"/>
-      <c r="E39" s="42" t="inlineStr"/>
-      <c r="F39" s="43" t="inlineStr">
+      <c r="M58" s="52" t="inlineStr">
+        <is>
+          <t>Open article</t>
+        </is>
+      </c>
+    </row>
+    <row r="59" ht="30" customHeight="1">
+      <c r="A59" s="46" t="n">
+        <v>46319</v>
+      </c>
+      <c r="B59" s="47" t="inlineStr">
+        <is>
+          <t>2026-Q4</t>
+        </is>
+      </c>
+      <c r="C59" s="48" t="inlineStr">
+        <is>
+          <t>Hazards &amp; Resilience</t>
+        </is>
+      </c>
+      <c r="D59" s="49" t="n"/>
+      <c r="E59" s="59" t="inlineStr"/>
+      <c r="F59" s="51" t="inlineStr">
         <is>
           <t>Rabren vía Las Tablas–Tonosí tras deslizamiento de tierra por fuertes lluvias</t>
         </is>
       </c>
-      <c r="G39" s="43" t="inlineStr"/>
-      <c r="H39" s="43" t="inlineStr"/>
-      <c r="I39" s="39" t="inlineStr">
+      <c r="G59" s="51" t="inlineStr"/>
+      <c r="H59" s="51" t="inlineStr"/>
+      <c r="I59" s="47" t="inlineStr">
         <is>
           <t>Telemetro</t>
         </is>
       </c>
-      <c r="J39" s="39" t="inlineStr">
+      <c r="J59" s="47" t="inlineStr">
         <is>
           <t>Spain</t>
         </is>
       </c>
-      <c r="K39" s="38" t="n">
+      <c r="K59" s="46" t="n">
         <v>46317</v>
       </c>
-      <c r="L39" s="43" t="inlineStr">
+      <c r="L59" s="51" t="inlineStr">
         <is>
           <t>landslide</t>
         </is>
       </c>
-      <c r="M39" s="44" t="inlineStr">
-        <is>
-          <t>Open article</t>
-        </is>
-      </c>
-    </row>
-    <row r="40" ht="30" customHeight="1">
-      <c r="A40" s="38" t="n">
-        <v>46319</v>
-      </c>
-      <c r="B40" s="39" t="inlineStr">
-        <is>
-          <t>2026-Q4</t>
-        </is>
-      </c>
-      <c r="C40" s="40" t="inlineStr">
-        <is>
-          <t>Hazards &amp; Resilience</t>
-        </is>
-      </c>
-      <c r="D40" s="41" t="n"/>
-      <c r="E40" s="42" t="inlineStr"/>
-      <c r="F40" s="43" t="inlineStr">
+      <c r="M59" s="52" t="inlineStr">
+        <is>
+          <t>Open article</t>
+        </is>
+      </c>
+    </row>
+    <row r="60" ht="30" customHeight="1">
+      <c r="A60" s="46" t="n">
+        <v>46319</v>
+      </c>
+      <c r="B60" s="47" t="inlineStr">
+        <is>
+          <t>2026-Q4</t>
+        </is>
+      </c>
+      <c r="C60" s="48" t="inlineStr">
+        <is>
+          <t>Hazards &amp; Resilience</t>
+        </is>
+      </c>
+      <c r="D60" s="49" t="n"/>
+      <c r="E60" s="59" t="inlineStr"/>
+      <c r="F60" s="51" t="inlineStr">
         <is>
           <t>Deslizamiento destruyó cuatro viviendas y mantiene en riesgo a familias en el Moniquirá</t>
         </is>
       </c>
-      <c r="G40" s="43" t="inlineStr"/>
-      <c r="H40" s="43" t="inlineStr"/>
-      <c r="I40" s="39" t="inlineStr">
+      <c r="G60" s="51" t="inlineStr"/>
+      <c r="H60" s="51" t="inlineStr"/>
+      <c r="I60" s="47" t="inlineStr">
         <is>
           <t>Caracol Radio</t>
         </is>
       </c>
-      <c r="J40" s="39" t="inlineStr">
+      <c r="J60" s="47" t="inlineStr">
         <is>
           <t>Spain</t>
         </is>
       </c>
-      <c r="K40" s="38" t="n">
+      <c r="K60" s="46" t="n">
         <v>46317</v>
       </c>
-      <c r="L40" s="43" t="inlineStr">
+      <c r="L60" s="51" t="inlineStr">
         <is>
           <t>landslide</t>
         </is>
       </c>
-      <c r="M40" s="44" t="inlineStr">
-        <is>
-          <t>Open article</t>
-        </is>
-      </c>
-    </row>
-    <row r="41" ht="48" customHeight="1">
-      <c r="A41" s="38" t="n">
-        <v>46319</v>
-      </c>
-      <c r="B41" s="39" t="inlineStr">
-        <is>
-          <t>2026-Q4</t>
-        </is>
-      </c>
-      <c r="C41" s="40" t="inlineStr">
-        <is>
-          <t>Hazards &amp; Resilience</t>
-        </is>
-      </c>
-      <c r="D41" s="41" t="n"/>
-      <c r="E41" s="42" t="inlineStr"/>
-      <c r="F41" s="43" t="inlineStr">
+      <c r="M60" s="52" t="inlineStr">
+        <is>
+          <t>Open article</t>
+        </is>
+      </c>
+    </row>
+    <row r="61" ht="48" customHeight="1">
+      <c r="A61" s="46" t="n">
+        <v>46319</v>
+      </c>
+      <c r="B61" s="47" t="inlineStr">
+        <is>
+          <t>2026-Q4</t>
+        </is>
+      </c>
+      <c r="C61" s="48" t="inlineStr">
+        <is>
+          <t>Hazards &amp; Resilience</t>
+        </is>
+      </c>
+      <c r="D61" s="49" t="n"/>
+      <c r="E61" s="59" t="inlineStr"/>
+      <c r="F61" s="51" t="inlineStr">
         <is>
           <t>La provincia de Dong Thap destina 330 mil millones de VND para hacer frente a las zonas afectadas por graves deslizamientos de tierra.</t>
         </is>
       </c>
-      <c r="G41" s="43" t="inlineStr"/>
-      <c r="H41" s="43" t="inlineStr"/>
-      <c r="I41" s="39" t="inlineStr">
+      <c r="G61" s="51" t="inlineStr"/>
+      <c r="H61" s="51" t="inlineStr"/>
+      <c r="I61" s="47" t="inlineStr">
         <is>
           <t>Vietnam.vn</t>
         </is>
       </c>
-      <c r="J41" s="39" t="inlineStr">
+      <c r="J61" s="47" t="inlineStr">
         <is>
           <t>Spain</t>
         </is>
       </c>
-      <c r="K41" s="38" t="n">
+      <c r="K61" s="46" t="n">
         <v>46318</v>
       </c>
-      <c r="L41" s="43" t="inlineStr">
+      <c r="L61" s="51" t="inlineStr">
         <is>
           <t>landslide</t>
         </is>
       </c>
-      <c r="M41" s="44" t="inlineStr">
-        <is>
-          <t>Open article</t>
-        </is>
-      </c>
-    </row>
-    <row r="42" ht="48" customHeight="1">
-      <c r="A42" s="38" t="n">
-        <v>46319</v>
-      </c>
-      <c r="B42" s="39" t="inlineStr">
-        <is>
-          <t>2026-Q4</t>
-        </is>
-      </c>
-      <c r="C42" s="40" t="inlineStr">
-        <is>
-          <t>Hazards &amp; Resilience</t>
-        </is>
-      </c>
-      <c r="D42" s="41" t="n"/>
-      <c r="E42" s="42" t="inlineStr"/>
-      <c r="F42" s="43" t="inlineStr">
+      <c r="M61" s="52" t="inlineStr">
+        <is>
+          <t>Open article</t>
+        </is>
+      </c>
+    </row>
+    <row r="62" ht="48" customHeight="1">
+      <c r="A62" s="46" t="n">
+        <v>46319</v>
+      </c>
+      <c r="B62" s="47" t="inlineStr">
+        <is>
+          <t>2026-Q4</t>
+        </is>
+      </c>
+      <c r="C62" s="48" t="inlineStr">
+        <is>
+          <t>Hazards &amp; Resilience</t>
+        </is>
+      </c>
+      <c r="D62" s="49" t="n"/>
+      <c r="E62" s="59" t="inlineStr"/>
+      <c r="F62" s="51" t="inlineStr">
         <is>
           <t>Vista de cerca de 500 metros de calle en la provincia de Lam Dong, gravemente afectada por hundimientos y deslizamientos de tierra.</t>
         </is>
       </c>
-      <c r="G42" s="43" t="inlineStr"/>
-      <c r="H42" s="43" t="inlineStr"/>
-      <c r="I42" s="39" t="inlineStr">
+      <c r="G62" s="51" t="inlineStr"/>
+      <c r="H62" s="51" t="inlineStr"/>
+      <c r="I62" s="47" t="inlineStr">
         <is>
           <t>Vietnam.vn</t>
         </is>
       </c>
-      <c r="J42" s="39" t="inlineStr">
+      <c r="J62" s="47" t="inlineStr">
         <is>
           <t>Spain</t>
         </is>
       </c>
-      <c r="K42" s="38" t="n">
+      <c r="K62" s="46" t="n">
         <v>46317</v>
       </c>
-      <c r="L42" s="43" t="inlineStr">
+      <c r="L62" s="51" t="inlineStr">
         <is>
           <t>landslide, subsidence</t>
         </is>
       </c>
-      <c r="M42" s="44" t="inlineStr">
-        <is>
-          <t>Open article</t>
-        </is>
-      </c>
-    </row>
-    <row r="43" ht="48" customHeight="1">
-      <c r="A43" s="38" t="n">
-        <v>46319</v>
-      </c>
-      <c r="B43" s="39" t="inlineStr">
-        <is>
-          <t>2026-Q4</t>
-        </is>
-      </c>
-      <c r="C43" s="40" t="inlineStr">
-        <is>
-          <t>Hazards &amp; Resilience</t>
-        </is>
-      </c>
-      <c r="D43" s="41" t="n"/>
-      <c r="E43" s="42" t="inlineStr"/>
-      <c r="F43" s="43" t="inlineStr">
+      <c r="M62" s="52" t="inlineStr">
+        <is>
+          <t>Open article</t>
+        </is>
+      </c>
+    </row>
+    <row r="63" ht="48" customHeight="1">
+      <c r="A63" s="46" t="n">
+        <v>46319</v>
+      </c>
+      <c r="B63" s="47" t="inlineStr">
+        <is>
+          <t>2026-Q4</t>
+        </is>
+      </c>
+      <c r="C63" s="48" t="inlineStr">
+        <is>
+          <t>Hazards &amp; Resilience</t>
+        </is>
+      </c>
+      <c r="D63" s="49" t="n"/>
+      <c r="E63" s="59" t="inlineStr"/>
+      <c r="F63" s="51" t="inlineStr">
         <is>
           <t>Lam Dong: La carretera en Nam Gia Nghia sufre graves hundimientos y deslizamientos de tierra.</t>
         </is>
       </c>
-      <c r="G43" s="43" t="inlineStr"/>
-      <c r="H43" s="43" t="inlineStr"/>
-      <c r="I43" s="39" t="inlineStr">
+      <c r="G63" s="51" t="inlineStr"/>
+      <c r="H63" s="51" t="inlineStr"/>
+      <c r="I63" s="47" t="inlineStr">
         <is>
           <t>Vietnam.vn</t>
         </is>
       </c>
-      <c r="J43" s="39" t="inlineStr">
+      <c r="J63" s="47" t="inlineStr">
         <is>
           <t>Spain</t>
         </is>
       </c>
-      <c r="K43" s="38" t="n">
+      <c r="K63" s="46" t="n">
         <v>46317</v>
       </c>
-      <c r="L43" s="43" t="inlineStr">
+      <c r="L63" s="51" t="inlineStr">
         <is>
           <t>landslide, subsidence</t>
         </is>
       </c>
-      <c r="M43" s="44" t="inlineStr">
-        <is>
-          <t>Open article</t>
-        </is>
-      </c>
-    </row>
-    <row r="44" ht="48" customHeight="1">
-      <c r="A44" s="38" t="n">
-        <v>46319</v>
-      </c>
-      <c r="B44" s="39" t="inlineStr">
-        <is>
-          <t>2026-Q4</t>
-        </is>
-      </c>
-      <c r="C44" s="40" t="inlineStr">
-        <is>
-          <t>Hazards &amp; Resilience</t>
-        </is>
-      </c>
-      <c r="D44" s="41" t="n"/>
-      <c r="E44" s="42" t="inlineStr"/>
-      <c r="F44" s="43" t="inlineStr">
+      <c r="M63" s="52" t="inlineStr">
+        <is>
+          <t>Open article</t>
+        </is>
+      </c>
+    </row>
+    <row r="64" ht="48" customHeight="1">
+      <c r="A64" s="46" t="n">
+        <v>46319</v>
+      </c>
+      <c r="B64" s="47" t="inlineStr">
+        <is>
+          <t>2026-Q4</t>
+        </is>
+      </c>
+      <c r="C64" s="48" t="inlineStr">
+        <is>
+          <t>Hazards &amp; Resilience</t>
+        </is>
+      </c>
+      <c r="D64" s="49" t="n"/>
+      <c r="E64" s="59" t="inlineStr"/>
+      <c r="F64" s="51" t="inlineStr">
         <is>
           <t>Reabren parcialmente la vía a Buenaventura tras deslizamiento en Dagua: hay paso a un carril</t>
         </is>
       </c>
-      <c r="G44" s="43" t="inlineStr"/>
-      <c r="H44" s="43" t="inlineStr"/>
-      <c r="I44" s="39" t="inlineStr">
+      <c r="G64" s="51" t="inlineStr"/>
+      <c r="H64" s="51" t="inlineStr"/>
+      <c r="I64" s="47" t="inlineStr">
         <is>
           <t>El País</t>
         </is>
       </c>
-      <c r="J44" s="39" t="inlineStr">
+      <c r="J64" s="47" t="inlineStr">
         <is>
           <t>Spain</t>
         </is>
       </c>
-      <c r="K44" s="38" t="n">
+      <c r="K64" s="46" t="n">
         <v>46317</v>
       </c>
-      <c r="L44" s="43" t="inlineStr">
+      <c r="L64" s="51" t="inlineStr">
         <is>
           <t>landslide</t>
         </is>
       </c>
-      <c r="M44" s="44" t="inlineStr">
-        <is>
-          <t>Open article</t>
-        </is>
-      </c>
-    </row>
-    <row r="45" ht="30" customHeight="1">
-      <c r="A45" s="38" t="n">
-        <v>46319</v>
-      </c>
-      <c r="B45" s="39" t="inlineStr">
-        <is>
-          <t>2026-Q4</t>
-        </is>
-      </c>
-      <c r="C45" s="40" t="inlineStr">
-        <is>
-          <t>Hazards &amp; Resilience</t>
-        </is>
-      </c>
-      <c r="D45" s="41" t="n"/>
-      <c r="E45" s="42" t="inlineStr"/>
-      <c r="F45" s="43" t="inlineStr">
+      <c r="M64" s="52" t="inlineStr">
+        <is>
+          <t>Open article</t>
+        </is>
+      </c>
+    </row>
+    <row r="65" ht="30" customHeight="1">
+      <c r="A65" s="46" t="n">
+        <v>46319</v>
+      </c>
+      <c r="B65" s="47" t="inlineStr">
+        <is>
+          <t>2026-Q4</t>
+        </is>
+      </c>
+      <c r="C65" s="48" t="inlineStr">
+        <is>
+          <t>Hazards &amp; Resilience</t>
+        </is>
+      </c>
+      <c r="D65" s="49" t="n"/>
+      <c r="E65" s="59" t="inlineStr"/>
+      <c r="F65" s="51" t="inlineStr">
         <is>
           <t>Detectan coliformes en muestras de agua tras deslizamiento en mina El Remance</t>
         </is>
       </c>
-      <c r="G45" s="43" t="inlineStr"/>
-      <c r="H45" s="43" t="inlineStr"/>
-      <c r="I45" s="39" t="inlineStr">
+      <c r="G65" s="51" t="inlineStr"/>
+      <c r="H65" s="51" t="inlineStr"/>
+      <c r="I65" s="47" t="inlineStr">
         <is>
           <t>CRÍTICA</t>
         </is>
       </c>
-      <c r="J45" s="39" t="inlineStr">
+      <c r="J65" s="47" t="inlineStr">
         <is>
           <t>Spain</t>
         </is>
       </c>
-      <c r="K45" s="38" t="n">
-        <v>46319</v>
-      </c>
-      <c r="L45" s="43" t="inlineStr">
+      <c r="K65" s="46" t="n">
+        <v>46319</v>
+      </c>
+      <c r="L65" s="51" t="inlineStr">
         <is>
           <t>landslide</t>
         </is>
       </c>
-      <c r="M45" s="44" t="inlineStr">
-        <is>
-          <t>Open article</t>
-        </is>
-      </c>
-    </row>
-    <row r="46" ht="30" customHeight="1">
-      <c r="A46" s="38" t="n">
-        <v>46319</v>
-      </c>
-      <c r="B46" s="39" t="inlineStr">
-        <is>
-          <t>2026-Q4</t>
-        </is>
-      </c>
-      <c r="C46" s="40" t="inlineStr">
-        <is>
-          <t>Hazards &amp; Resilience</t>
-        </is>
-      </c>
-      <c r="D46" s="41" t="n"/>
-      <c r="E46" s="42" t="inlineStr"/>
-      <c r="F46" s="43" t="inlineStr">
+      <c r="M65" s="52" t="inlineStr">
+        <is>
+          <t>Open article</t>
+        </is>
+      </c>
+    </row>
+    <row r="66" ht="30" customHeight="1">
+      <c r="A66" s="46" t="n">
+        <v>46319</v>
+      </c>
+      <c r="B66" s="47" t="inlineStr">
+        <is>
+          <t>2026-Q4</t>
+        </is>
+      </c>
+      <c r="C66" s="48" t="inlineStr">
+        <is>
+          <t>Hazards &amp; Resilience</t>
+        </is>
+      </c>
+      <c r="D66" s="49" t="n"/>
+      <c r="E66" s="59" t="inlineStr"/>
+      <c r="F66" s="51" t="inlineStr">
         <is>
           <t>IMÁGENES SENSIBLES | Deslizamiento en mina deja 14 personas fallecidas</t>
         </is>
       </c>
-      <c r="G46" s="43" t="inlineStr"/>
-      <c r="H46" s="43" t="inlineStr"/>
-      <c r="I46" s="39" t="inlineStr">
+      <c r="G66" s="51" t="inlineStr"/>
+      <c r="H66" s="51" t="inlineStr"/>
+      <c r="I66" s="47" t="inlineStr">
         <is>
           <t>Azteca Bajío</t>
         </is>
       </c>
-      <c r="J46" s="39" t="inlineStr">
+      <c r="J66" s="47" t="inlineStr">
         <is>
           <t>Spain</t>
         </is>
       </c>
-      <c r="K46" s="38" t="n">
+      <c r="K66" s="46" t="n">
         <v>46317</v>
       </c>
-      <c r="L46" s="43" t="inlineStr">
+      <c r="L66" s="51" t="inlineStr">
         <is>
           <t>landslide</t>
         </is>
       </c>
-      <c r="M46" s="44" t="inlineStr">
-        <is>
-          <t>Open article</t>
-        </is>
-      </c>
-    </row>
-    <row r="47" ht="30" customHeight="1">
-      <c r="A47" s="38" t="n">
-        <v>46319</v>
-      </c>
-      <c r="B47" s="39" t="inlineStr">
-        <is>
-          <t>2026-Q4</t>
-        </is>
-      </c>
-      <c r="C47" s="40" t="inlineStr">
-        <is>
-          <t>Hazards &amp; Resilience</t>
-        </is>
-      </c>
-      <c r="D47" s="41" t="n"/>
-      <c r="E47" s="42" t="inlineStr"/>
-      <c r="F47" s="43" t="inlineStr">
+      <c r="M66" s="52" t="inlineStr">
+        <is>
+          <t>Open article</t>
+        </is>
+      </c>
+    </row>
+    <row r="67" ht="30" customHeight="1">
+      <c r="A67" s="46" t="n">
+        <v>46319</v>
+      </c>
+      <c r="B67" s="47" t="inlineStr">
+        <is>
+          <t>2026-Q4</t>
+        </is>
+      </c>
+      <c r="C67" s="48" t="inlineStr">
+        <is>
+          <t>Hazards &amp; Resilience</t>
+        </is>
+      </c>
+      <c r="D67" s="49" t="n"/>
+      <c r="E67" s="59" t="inlineStr"/>
+      <c r="F67" s="51" t="inlineStr">
         <is>
           <t>¡Emergencia en Italia! Fuertes lluvias provocan aludes y deslizamientos de tierra</t>
         </is>
       </c>
-      <c r="G47" s="43" t="inlineStr"/>
-      <c r="H47" s="43" t="inlineStr"/>
-      <c r="I47" s="39" t="inlineStr">
+      <c r="G67" s="51" t="inlineStr"/>
+      <c r="H67" s="51" t="inlineStr"/>
+      <c r="I67" s="47" t="inlineStr">
         <is>
           <t>TV Azteca Baja California</t>
         </is>
       </c>
-      <c r="J47" s="39" t="inlineStr">
+      <c r="J67" s="47" t="inlineStr">
         <is>
           <t>Spain</t>
         </is>
       </c>
-      <c r="K47" s="38" t="n">
+      <c r="K67" s="46" t="n">
         <v>46317</v>
       </c>
-      <c r="L47" s="43" t="inlineStr">
+      <c r="L67" s="51" t="inlineStr">
         <is>
           <t>landslide</t>
         </is>
       </c>
-      <c r="M47" s="44" t="inlineStr">
-        <is>
-          <t>Open article</t>
-        </is>
-      </c>
-    </row>
-    <row r="48" ht="48" customHeight="1">
-      <c r="A48" s="38" t="n">
-        <v>46319</v>
-      </c>
-      <c r="B48" s="39" t="inlineStr">
-        <is>
-          <t>2026-Q4</t>
-        </is>
-      </c>
-      <c r="C48" s="40" t="inlineStr">
-        <is>
-          <t>Hazards &amp; Resilience</t>
-        </is>
-      </c>
-      <c r="D48" s="41" t="n"/>
-      <c r="E48" s="42" t="inlineStr"/>
-      <c r="F48" s="43" t="inlineStr">
+      <c r="M67" s="52" t="inlineStr">
+        <is>
+          <t>Open article</t>
+        </is>
+      </c>
+    </row>
+    <row r="68" ht="48" customHeight="1">
+      <c r="A68" s="46" t="n">
+        <v>46319</v>
+      </c>
+      <c r="B68" s="47" t="inlineStr">
+        <is>
+          <t>2026-Q4</t>
+        </is>
+      </c>
+      <c r="C68" s="48" t="inlineStr">
+        <is>
+          <t>Hazards &amp; Resilience</t>
+        </is>
+      </c>
+      <c r="D68" s="49" t="n"/>
+      <c r="E68" s="59" t="inlineStr"/>
+      <c r="F68" s="51" t="inlineStr">
         <is>
           <t>¡La tierra se movió en Moniquirá! Deslizamiento dejó cuatro casas destruidas y otras cinco en riesgo</t>
         </is>
       </c>
-      <c r="G48" s="43" t="inlineStr"/>
-      <c r="H48" s="43" t="inlineStr"/>
-      <c r="I48" s="39" t="inlineStr">
+      <c r="G68" s="51" t="inlineStr"/>
+      <c r="H68" s="51" t="inlineStr"/>
+      <c r="I68" s="47" t="inlineStr">
         <is>
           <t>Minuto30</t>
         </is>
       </c>
-      <c r="J48" s="39" t="inlineStr">
+      <c r="J68" s="47" t="inlineStr">
         <is>
           <t>Spain</t>
         </is>
       </c>
-      <c r="K48" s="38" t="n">
+      <c r="K68" s="46" t="n">
         <v>46317</v>
       </c>
-      <c r="L48" s="43" t="inlineStr">
+      <c r="L68" s="51" t="inlineStr">
         <is>
           <t>landslide</t>
         </is>
       </c>
-      <c r="M48" s="44" t="inlineStr">
-        <is>
-          <t>Open article</t>
-        </is>
-      </c>
-    </row>
-    <row r="49" ht="30" customHeight="1">
-      <c r="A49" s="38" t="n">
-        <v>46319</v>
-      </c>
-      <c r="B49" s="39" t="inlineStr">
-        <is>
-          <t>2026-Q4</t>
-        </is>
-      </c>
-      <c r="C49" s="40" t="inlineStr">
-        <is>
-          <t>Hazards &amp; Resilience</t>
-        </is>
-      </c>
-      <c r="D49" s="41" t="n"/>
-      <c r="E49" s="42" t="inlineStr"/>
-      <c r="F49" s="43" t="inlineStr">
+      <c r="M68" s="52" t="inlineStr">
+        <is>
+          <t>Open article</t>
+        </is>
+      </c>
+    </row>
+    <row r="69" ht="30" customHeight="1">
+      <c r="A69" s="46" t="n">
+        <v>46319</v>
+      </c>
+      <c r="B69" s="47" t="inlineStr">
+        <is>
+          <t>2026-Q4</t>
+        </is>
+      </c>
+      <c r="C69" s="48" t="inlineStr">
+        <is>
+          <t>Hazards &amp; Resilience</t>
+        </is>
+      </c>
+      <c r="D69" s="49" t="n"/>
+      <c r="E69" s="59" t="inlineStr"/>
+      <c r="F69" s="51" t="inlineStr">
         <is>
           <t>Deslizamiento destruyó cuatro viviendas en Moniquirá, Boyacá, y dejó a varias familias</t>
         </is>
       </c>
-      <c r="G49" s="43" t="inlineStr"/>
-      <c r="H49" s="43" t="inlineStr"/>
-      <c r="I49" s="39" t="inlineStr">
+      <c r="G69" s="51" t="inlineStr"/>
+      <c r="H69" s="51" t="inlineStr"/>
+      <c r="I69" s="47" t="inlineStr">
         <is>
           <t>Diario del Sur</t>
         </is>
       </c>
-      <c r="J49" s="39" t="inlineStr">
+      <c r="J69" s="47" t="inlineStr">
         <is>
           <t>Spain</t>
         </is>
       </c>
-      <c r="K49" s="38" t="n">
+      <c r="K69" s="46" t="n">
         <v>46318</v>
       </c>
-      <c r="L49" s="43" t="inlineStr">
+      <c r="L69" s="51" t="inlineStr">
         <is>
           <t>landslide</t>
         </is>
       </c>
-      <c r="M49" s="44" t="inlineStr">
-        <is>
-          <t>Open article</t>
-        </is>
-      </c>
-    </row>
-    <row r="50" ht="30" customHeight="1">
-      <c r="A50" s="38" t="n">
-        <v>46319</v>
-      </c>
-      <c r="B50" s="39" t="inlineStr">
-        <is>
-          <t>2026-Q4</t>
-        </is>
-      </c>
-      <c r="C50" s="40" t="inlineStr">
-        <is>
-          <t>Hazards &amp; Resilience</t>
-        </is>
-      </c>
-      <c r="D50" s="41" t="n"/>
-      <c r="E50" s="42" t="inlineStr"/>
-      <c r="F50" s="43" t="inlineStr">
+      <c r="M69" s="52" t="inlineStr">
+        <is>
+          <t>Open article</t>
+        </is>
+      </c>
+    </row>
+    <row r="70" ht="30" customHeight="1">
+      <c r="A70" s="46" t="n">
+        <v>46319</v>
+      </c>
+      <c r="B70" s="47" t="inlineStr">
+        <is>
+          <t>2026-Q4</t>
+        </is>
+      </c>
+      <c r="C70" s="48" t="inlineStr">
+        <is>
+          <t>Hazards &amp; Resilience</t>
+        </is>
+      </c>
+      <c r="D70" s="49" t="n"/>
+      <c r="E70" s="59" t="inlineStr"/>
+      <c r="F70" s="51" t="inlineStr">
         <is>
           <t>Por tercera vez, un deslizamiento afecta al Pedregal de Santa Julia en Tijuana</t>
         </is>
       </c>
-      <c r="G50" s="43" t="inlineStr"/>
-      <c r="H50" s="43" t="inlineStr"/>
-      <c r="I50" s="39" t="inlineStr">
+      <c r="G70" s="51" t="inlineStr"/>
+      <c r="H70" s="51" t="inlineStr"/>
+      <c r="I70" s="47" t="inlineStr">
         <is>
           <t>TV Azteca Baja California</t>
         </is>
       </c>
-      <c r="J50" s="39" t="inlineStr">
+      <c r="J70" s="47" t="inlineStr">
         <is>
           <t>Spain</t>
         </is>
       </c>
-      <c r="K50" s="38" t="n">
+      <c r="K70" s="46" t="n">
         <v>46318</v>
       </c>
-      <c r="L50" s="43" t="inlineStr">
+      <c r="L70" s="51" t="inlineStr">
         <is>
           <t>landslide</t>
         </is>
       </c>
-      <c r="M50" s="44" t="inlineStr">
-        <is>
-          <t>Open article</t>
-        </is>
-      </c>
-    </row>
-    <row r="51" ht="30" customHeight="1">
-      <c r="A51" s="38" t="n">
-        <v>46319</v>
-      </c>
-      <c r="B51" s="39" t="inlineStr">
-        <is>
-          <t>2026-Q4</t>
-        </is>
-      </c>
-      <c r="C51" s="40" t="inlineStr">
-        <is>
-          <t>Hazards &amp; Resilience</t>
-        </is>
-      </c>
-      <c r="D51" s="41" t="n"/>
-      <c r="E51" s="42" t="inlineStr"/>
-      <c r="F51" s="43" t="inlineStr">
+      <c r="M70" s="52" t="inlineStr">
+        <is>
+          <t>Open article</t>
+        </is>
+      </c>
+    </row>
+    <row r="71" ht="30" customHeight="1">
+      <c r="A71" s="46" t="n">
+        <v>46319</v>
+      </c>
+      <c r="B71" s="47" t="inlineStr">
+        <is>
+          <t>2026-Q4</t>
+        </is>
+      </c>
+      <c r="C71" s="48" t="inlineStr">
+        <is>
+          <t>Hazards &amp; Resilience</t>
+        </is>
+      </c>
+      <c r="D71" s="49" t="n"/>
+      <c r="E71" s="59" t="inlineStr"/>
+      <c r="F71" s="51" t="inlineStr">
         <is>
           <t>Deslizamiento en Moniquirá, Boyacá: 3 casas destruidas por lluvias</t>
         </is>
       </c>
-      <c r="G51" s="43" t="inlineStr"/>
-      <c r="H51" s="43" t="inlineStr"/>
-      <c r="I51" s="39" t="inlineStr">
+      <c r="G71" s="51" t="inlineStr"/>
+      <c r="H71" s="51" t="inlineStr"/>
+      <c r="I71" s="47" t="inlineStr">
         <is>
           <t>Estrella Digital Colombia</t>
         </is>
       </c>
-      <c r="J51" s="39" t="inlineStr">
+      <c r="J71" s="47" t="inlineStr">
         <is>
           <t>Spain</t>
         </is>
       </c>
-      <c r="K51" s="38" t="n">
+      <c r="K71" s="46" t="n">
         <v>46318</v>
       </c>
-      <c r="L51" s="43" t="inlineStr">
+      <c r="L71" s="51" t="inlineStr">
         <is>
           <t>landslide</t>
         </is>
       </c>
-      <c r="M51" s="44" t="inlineStr">
-        <is>
-          <t>Open article</t>
-        </is>
-      </c>
-    </row>
-    <row r="52" ht="48" customHeight="1">
-      <c r="A52" s="38" t="n">
-        <v>46319</v>
-      </c>
-      <c r="B52" s="39" t="inlineStr">
-        <is>
-          <t>2026-Q4</t>
-        </is>
-      </c>
-      <c r="C52" s="40" t="inlineStr">
-        <is>
-          <t>Hazards &amp; Resilience</t>
-        </is>
-      </c>
-      <c r="D52" s="41" t="n"/>
-      <c r="E52" s="42" t="inlineStr"/>
-      <c r="F52" s="43" t="inlineStr">
+      <c r="M71" s="52" t="inlineStr">
+        <is>
+          <t>Open article</t>
+        </is>
+      </c>
+    </row>
+    <row r="72" ht="48" customHeight="1">
+      <c r="A72" s="46" t="n">
+        <v>46319</v>
+      </c>
+      <c r="B72" s="47" t="inlineStr">
+        <is>
+          <t>2026-Q4</t>
+        </is>
+      </c>
+      <c r="C72" s="48" t="inlineStr">
+        <is>
+          <t>Hazards &amp; Resilience</t>
+        </is>
+      </c>
+      <c r="D72" s="49" t="n"/>
+      <c r="E72" s="59" t="inlineStr"/>
+      <c r="F72" s="51" t="inlineStr">
         <is>
           <t>Obrero permaneció sepultado por casi cuatro horas tras colapso de muro de contención en Ventanilla: fue rescatado con vida</t>
         </is>
       </c>
-      <c r="G52" s="43" t="inlineStr"/>
-      <c r="H52" s="43" t="inlineStr"/>
-      <c r="I52" s="39" t="inlineStr">
+      <c r="G72" s="51" t="inlineStr"/>
+      <c r="H72" s="51" t="inlineStr"/>
+      <c r="I72" s="47" t="inlineStr">
         <is>
           <t>Infobae</t>
         </is>
       </c>
-      <c r="J52" s="39" t="inlineStr">
+      <c r="J72" s="47" t="inlineStr">
         <is>
           <t>Mexico</t>
         </is>
       </c>
-      <c r="K52" s="38" t="n">
+      <c r="K72" s="46" t="n">
         <v>46318</v>
       </c>
-      <c r="L52" s="43" t="inlineStr">
+      <c r="L72" s="51" t="inlineStr">
         <is>
           <t>retaining wall, collapse</t>
         </is>
       </c>
-      <c r="M52" s="44" t="inlineStr">
-        <is>
-          <t>Open article</t>
-        </is>
-      </c>
-    </row>
-    <row r="53" ht="30" customHeight="1">
-      <c r="A53" s="38" t="n">
-        <v>46319</v>
-      </c>
-      <c r="B53" s="39" t="inlineStr">
-        <is>
-          <t>2026-Q4</t>
-        </is>
-      </c>
-      <c r="C53" s="40" t="inlineStr">
-        <is>
-          <t>Hazards &amp; Resilience</t>
-        </is>
-      </c>
-      <c r="D53" s="41" t="n"/>
-      <c r="E53" s="42" t="inlineStr"/>
-      <c r="F53" s="43" t="inlineStr">
+      <c r="M72" s="52" t="inlineStr">
+        <is>
+          <t>Open article</t>
+        </is>
+      </c>
+    </row>
+    <row r="73" ht="30" customHeight="1">
+      <c r="A73" s="46" t="n">
+        <v>46319</v>
+      </c>
+      <c r="B73" s="47" t="inlineStr">
+        <is>
+          <t>2026-Q4</t>
+        </is>
+      </c>
+      <c r="C73" s="48" t="inlineStr">
+        <is>
+          <t>Hazards &amp; Resilience</t>
+        </is>
+      </c>
+      <c r="D73" s="49" t="n"/>
+      <c r="E73" s="59" t="inlineStr"/>
+      <c r="F73" s="51" t="inlineStr">
         <is>
           <t>Tres viviendas quedaron destruidas tras deslizamiento en zona rural de Moniquirá</t>
         </is>
       </c>
-      <c r="G53" s="43" t="inlineStr"/>
-      <c r="H53" s="43" t="inlineStr"/>
-      <c r="I53" s="39" t="inlineStr">
+      <c r="G73" s="51" t="inlineStr"/>
+      <c r="H73" s="51" t="inlineStr"/>
+      <c r="I73" s="47" t="inlineStr">
         <is>
           <t>Noticias Caracol</t>
         </is>
       </c>
-      <c r="J53" s="39" t="inlineStr">
+      <c r="J73" s="47" t="inlineStr">
         <is>
           <t>Mexico</t>
         </is>
       </c>
-      <c r="K53" s="38" t="n">
+      <c r="K73" s="46" t="n">
         <v>46318</v>
       </c>
-      <c r="L53" s="43" t="inlineStr">
+      <c r="L73" s="51" t="inlineStr">
         <is>
           <t>landslide</t>
         </is>
       </c>
-      <c r="M53" s="44" t="inlineStr">
-        <is>
-          <t>Open article</t>
-        </is>
-      </c>
-    </row>
-    <row r="54" ht="30" customHeight="1">
-      <c r="A54" s="38" t="n">
-        <v>46319</v>
-      </c>
-      <c r="B54" s="39" t="inlineStr">
-        <is>
-          <t>2026-Q4</t>
-        </is>
-      </c>
-      <c r="C54" s="40" t="inlineStr">
-        <is>
-          <t>Hazards &amp; Resilience</t>
-        </is>
-      </c>
-      <c r="D54" s="41" t="n"/>
-      <c r="E54" s="42" t="inlineStr"/>
-      <c r="F54" s="43" t="inlineStr">
+      <c r="M73" s="52" t="inlineStr">
+        <is>
+          <t>Open article</t>
+        </is>
+      </c>
+    </row>
+    <row r="74" ht="30" customHeight="1">
+      <c r="A74" s="46" t="n">
+        <v>46319</v>
+      </c>
+      <c r="B74" s="47" t="inlineStr">
+        <is>
+          <t>2026-Q4</t>
+        </is>
+      </c>
+      <c r="C74" s="48" t="inlineStr">
+        <is>
+          <t>Hazards &amp; Resilience</t>
+        </is>
+      </c>
+      <c r="D74" s="49" t="n"/>
+      <c r="E74" s="59" t="inlineStr"/>
+      <c r="F74" s="51" t="inlineStr">
         <is>
           <t>Quito bajo la lluvia: 321 barrios están expuestos a inundaciones y deslizamientos</t>
         </is>
       </c>
-      <c r="G54" s="43" t="inlineStr"/>
-      <c r="H54" s="43" t="inlineStr"/>
-      <c r="I54" s="39" t="inlineStr">
+      <c r="G74" s="51" t="inlineStr"/>
+      <c r="H74" s="51" t="inlineStr"/>
+      <c r="I74" s="47" t="inlineStr">
         <is>
           <t>Diario Extra</t>
         </is>
       </c>
-      <c r="J54" s="39" t="inlineStr">
+      <c r="J74" s="47" t="inlineStr">
         <is>
           <t>Mexico</t>
         </is>
       </c>
-      <c r="K54" s="38" t="n">
+      <c r="K74" s="46" t="n">
         <v>46318</v>
       </c>
-      <c r="L54" s="43" t="inlineStr">
+      <c r="L74" s="51" t="inlineStr">
         <is>
           <t>landslide</t>
         </is>
       </c>
-      <c r="M54" s="44" t="inlineStr">
-        <is>
-          <t>Open article</t>
-        </is>
-      </c>
-    </row>
-    <row r="55" ht="30" customHeight="1">
-      <c r="A55" s="38" t="n">
-        <v>46319</v>
-      </c>
-      <c r="B55" s="39" t="inlineStr">
-        <is>
-          <t>2026-Q4</t>
-        </is>
-      </c>
-      <c r="C55" s="40" t="inlineStr">
-        <is>
-          <t>Hazards &amp; Resilience</t>
-        </is>
-      </c>
-      <c r="D55" s="41" t="n"/>
-      <c r="E55" s="42" t="inlineStr"/>
-      <c r="F55" s="43" t="inlineStr">
+      <c r="M74" s="52" t="inlineStr">
+        <is>
+          <t>Open article</t>
+        </is>
+      </c>
+    </row>
+    <row r="75" ht="30" customHeight="1">
+      <c r="A75" s="46" t="n">
+        <v>46319</v>
+      </c>
+      <c r="B75" s="47" t="inlineStr">
+        <is>
+          <t>2026-Q4</t>
+        </is>
+      </c>
+      <c r="C75" s="48" t="inlineStr">
+        <is>
+          <t>Hazards &amp; Resilience</t>
+        </is>
+      </c>
+      <c r="D75" s="49" t="n"/>
+      <c r="E75" s="59" t="inlineStr"/>
+      <c r="F75" s="51" t="inlineStr">
         <is>
           <t>Deslizamento de terra em mina de ouro ilegal na Colômbia deixa nove mortos</t>
         </is>
       </c>
-      <c r="G55" s="43" t="inlineStr"/>
-      <c r="H55" s="43" t="inlineStr"/>
-      <c r="I55" s="39" t="inlineStr">
+      <c r="G75" s="51" t="inlineStr"/>
+      <c r="H75" s="51" t="inlineStr"/>
+      <c r="I75" s="47" t="inlineStr">
         <is>
           <t>Estadão</t>
         </is>
       </c>
-      <c r="J55" s="39" t="inlineStr">
+      <c r="J75" s="47" t="inlineStr">
         <is>
           <t>Brazil</t>
         </is>
       </c>
-      <c r="K55" s="38" t="n">
-        <v>46319</v>
-      </c>
-      <c r="L55" s="43" t="inlineStr">
+      <c r="K75" s="46" t="n">
+        <v>46319</v>
+      </c>
+      <c r="L75" s="51" t="inlineStr">
         <is>
           <t>landslide</t>
         </is>
       </c>
-      <c r="M55" s="44" t="inlineStr">
-        <is>
-          <t>Open article</t>
-        </is>
-      </c>
-    </row>
-    <row r="56" ht="30" customHeight="1">
-      <c r="A56" s="38" t="n">
-        <v>46319</v>
-      </c>
-      <c r="B56" s="39" t="inlineStr">
-        <is>
-          <t>2026-Q4</t>
-        </is>
-      </c>
-      <c r="C56" s="40" t="inlineStr">
-        <is>
-          <t>Hazards &amp; Resilience</t>
-        </is>
-      </c>
-      <c r="D56" s="41" t="n"/>
-      <c r="E56" s="42" t="inlineStr"/>
-      <c r="F56" s="43" t="inlineStr">
+      <c r="M75" s="52" t="inlineStr">
+        <is>
+          <t>Open article</t>
+        </is>
+      </c>
+    </row>
+    <row r="76" ht="30" customHeight="1">
+      <c r="A76" s="46" t="n">
+        <v>46319</v>
+      </c>
+      <c r="B76" s="47" t="inlineStr">
+        <is>
+          <t>2026-Q4</t>
+        </is>
+      </c>
+      <c r="C76" s="48" t="inlineStr">
+        <is>
+          <t>Hazards &amp; Resilience</t>
+        </is>
+      </c>
+      <c r="D76" s="49" t="n"/>
+      <c r="E76" s="59" t="inlineStr"/>
+      <c r="F76" s="51" t="inlineStr">
         <is>
           <t>Deslizamento de terra interdita rua em Presidente Getúlio</t>
         </is>
       </c>
-      <c r="G56" s="43" t="inlineStr"/>
-      <c r="H56" s="43" t="inlineStr"/>
-      <c r="I56" s="39" t="inlineStr">
+      <c r="G76" s="51" t="inlineStr"/>
+      <c r="H76" s="51" t="inlineStr"/>
+      <c r="I76" s="47" t="inlineStr">
         <is>
           <t>Rádio Mirador</t>
         </is>
       </c>
-      <c r="J56" s="39" t="inlineStr">
+      <c r="J76" s="47" t="inlineStr">
         <is>
           <t>Brazil</t>
         </is>
       </c>
-      <c r="K56" s="38" t="n">
+      <c r="K76" s="46" t="n">
         <v>46318</v>
       </c>
-      <c r="L56" s="43" t="inlineStr">
+      <c r="L76" s="51" t="inlineStr">
         <is>
           <t>landslide</t>
         </is>
       </c>
-      <c r="M56" s="44" t="inlineStr">
-        <is>
-          <t>Open article</t>
-        </is>
-      </c>
-    </row>
-    <row r="57" ht="30" customHeight="1">
-      <c r="A57" s="38" t="n">
-        <v>46319</v>
-      </c>
-      <c r="B57" s="39" t="inlineStr">
-        <is>
-          <t>2026-Q4</t>
-        </is>
-      </c>
-      <c r="C57" s="40" t="inlineStr">
-        <is>
-          <t>Hazards &amp; Resilience</t>
-        </is>
-      </c>
-      <c r="D57" s="41" t="n"/>
-      <c r="E57" s="42" t="inlineStr"/>
-      <c r="F57" s="43" t="inlineStr">
+      <c r="M76" s="52" t="inlineStr">
+        <is>
+          <t>Open article</t>
+        </is>
+      </c>
+    </row>
+    <row r="77" ht="30" customHeight="1">
+      <c r="A77" s="46" t="n">
+        <v>46319</v>
+      </c>
+      <c r="B77" s="47" t="inlineStr">
+        <is>
+          <t>2026-Q4</t>
+        </is>
+      </c>
+      <c r="C77" s="48" t="inlineStr">
+        <is>
+          <t>Hazards &amp; Resilience</t>
+        </is>
+      </c>
+      <c r="D77" s="49" t="n"/>
+      <c r="E77" s="59" t="inlineStr"/>
+      <c r="F77" s="51" t="inlineStr">
         <is>
           <t>Deslizamento e obras exigem atenção de motoristas na Serra Dona Francisca</t>
         </is>
       </c>
-      <c r="G57" s="43" t="inlineStr"/>
-      <c r="H57" s="43" t="inlineStr"/>
-      <c r="I57" s="39" t="inlineStr">
+      <c r="G77" s="51" t="inlineStr"/>
+      <c r="H77" s="51" t="inlineStr"/>
+      <c r="I77" s="47" t="inlineStr">
         <is>
           <t>ND Mais</t>
         </is>
       </c>
-      <c r="J57" s="39" t="inlineStr">
+      <c r="J77" s="47" t="inlineStr">
         <is>
           <t>Brazil</t>
         </is>
       </c>
-      <c r="K57" s="38" t="n">
+      <c r="K77" s="46" t="n">
         <v>46318</v>
       </c>
-      <c r="L57" s="43" t="inlineStr">
+      <c r="L77" s="51" t="inlineStr">
         <is>
           <t>landslide</t>
         </is>
       </c>
-      <c r="M57" s="44" t="inlineStr">
-        <is>
-          <t>Open article</t>
-        </is>
-      </c>
-    </row>
-    <row r="58" ht="30" customHeight="1">
-      <c r="A58" s="38" t="n">
-        <v>46319</v>
-      </c>
-      <c r="B58" s="39" t="inlineStr">
-        <is>
-          <t>2026-Q4</t>
-        </is>
-      </c>
-      <c r="C58" s="40" t="inlineStr">
-        <is>
-          <t>Hazards &amp; Resilience</t>
-        </is>
-      </c>
-      <c r="D58" s="41" t="n"/>
-      <c r="E58" s="42" t="inlineStr"/>
-      <c r="F58" s="43" t="inlineStr">
+      <c r="M77" s="52" t="inlineStr">
+        <is>
+          <t>Open article</t>
+        </is>
+      </c>
+    </row>
+    <row r="78" ht="30" customHeight="1">
+      <c r="A78" s="46" t="n">
+        <v>46319</v>
+      </c>
+      <c r="B78" s="47" t="inlineStr">
+        <is>
+          <t>2026-Q4</t>
+        </is>
+      </c>
+      <c r="C78" s="48" t="inlineStr">
+        <is>
+          <t>Hazards &amp; Resilience</t>
+        </is>
+      </c>
+      <c r="D78" s="49" t="n"/>
+      <c r="E78" s="59" t="inlineStr"/>
+      <c r="F78" s="51" t="inlineStr">
         <is>
           <t>Barreira de contenção de deslizamentos de terra 'ameaça' área residencial.</t>
         </is>
       </c>
-      <c r="G58" s="43" t="inlineStr"/>
-      <c r="H58" s="43" t="inlineStr"/>
-      <c r="I58" s="39" t="inlineStr">
+      <c r="G78" s="51" t="inlineStr"/>
+      <c r="H78" s="51" t="inlineStr"/>
+      <c r="I78" s="47" t="inlineStr">
         <is>
           <t>Vietnam.vn</t>
         </is>
       </c>
-      <c r="J58" s="39" t="inlineStr">
+      <c r="J78" s="47" t="inlineStr">
         <is>
           <t>Brazil</t>
         </is>
       </c>
-      <c r="K58" s="38" t="n">
+      <c r="K78" s="46" t="n">
         <v>46318</v>
       </c>
-      <c r="L58" s="43" t="inlineStr">
+      <c r="L78" s="51" t="inlineStr">
         <is>
           <t>landslide</t>
         </is>
       </c>
-      <c r="M58" s="44" t="inlineStr">
-        <is>
-          <t>Open article</t>
-        </is>
-      </c>
-    </row>
-    <row r="59" ht="48" customHeight="1">
-      <c r="A59" s="38" t="n">
-        <v>46319</v>
-      </c>
-      <c r="B59" s="39" t="inlineStr">
-        <is>
-          <t>2026-Q4</t>
-        </is>
-      </c>
-      <c r="C59" s="40" t="inlineStr">
-        <is>
-          <t>Hazards &amp; Resilience</t>
-        </is>
-      </c>
-      <c r="D59" s="41" t="n"/>
-      <c r="E59" s="42" t="inlineStr"/>
-      <c r="F59" s="43" t="inlineStr">
+      <c r="M78" s="52" t="inlineStr">
+        <is>
+          <t>Open article</t>
+        </is>
+      </c>
+    </row>
+    <row r="79" ht="48" customHeight="1">
+      <c r="A79" s="46" t="n">
+        <v>46319</v>
+      </c>
+      <c r="B79" s="47" t="inlineStr">
+        <is>
+          <t>2026-Q4</t>
+        </is>
+      </c>
+      <c r="C79" s="48" t="inlineStr">
+        <is>
+          <t>Hazards &amp; Resilience</t>
+        </is>
+      </c>
+      <c r="D79" s="49" t="n"/>
+      <c r="E79" s="59" t="inlineStr"/>
+      <c r="F79" s="51" t="inlineStr">
         <is>
           <t>O Passo de Khanh Le está parcialmente fechado para lidar com o risco de deslizamentos de rochas.</t>
         </is>
       </c>
-      <c r="G59" s="43" t="inlineStr"/>
-      <c r="H59" s="43" t="inlineStr"/>
-      <c r="I59" s="39" t="inlineStr">
+      <c r="G79" s="51" t="inlineStr"/>
+      <c r="H79" s="51" t="inlineStr"/>
+      <c r="I79" s="47" t="inlineStr">
         <is>
           <t>Vietnam.vn</t>
         </is>
       </c>
-      <c r="J59" s="39" t="inlineStr">
+      <c r="J79" s="47" t="inlineStr">
         <is>
           <t>Brazil</t>
         </is>
       </c>
-      <c r="K59" s="38" t="n">
+      <c r="K79" s="46" t="n">
         <v>46317</v>
       </c>
-      <c r="L59" s="43" t="inlineStr">
+      <c r="L79" s="51" t="inlineStr">
         <is>
           <t>landslide</t>
         </is>
       </c>
-      <c r="M59" s="44" t="inlineStr">
-        <is>
-          <t>Open article</t>
-        </is>
-      </c>
-    </row>
-    <row r="60" ht="48" customHeight="1">
-      <c r="A60" s="38" t="n">
-        <v>46319</v>
-      </c>
-      <c r="B60" s="39" t="inlineStr">
-        <is>
-          <t>2026-Q4</t>
-        </is>
-      </c>
-      <c r="C60" s="40" t="inlineStr">
-        <is>
-          <t>Hazards &amp; Resilience</t>
-        </is>
-      </c>
-      <c r="D60" s="41" t="n"/>
-      <c r="E60" s="42" t="inlineStr"/>
-      <c r="F60" s="43" t="inlineStr">
+      <c r="M79" s="52" t="inlineStr">
+        <is>
+          <t>Open article</t>
+        </is>
+      </c>
+    </row>
+    <row r="80" ht="48" customHeight="1">
+      <c r="A80" s="46" t="n">
+        <v>46319</v>
+      </c>
+      <c r="B80" s="47" t="inlineStr">
+        <is>
+          <t>2026-Q4</t>
+        </is>
+      </c>
+      <c r="C80" s="48" t="inlineStr">
+        <is>
+          <t>Hazards &amp; Resilience</t>
+        </is>
+      </c>
+      <c r="D80" s="49" t="n"/>
+      <c r="E80" s="59" t="inlineStr"/>
+      <c r="F80" s="51" t="inlineStr">
         <is>
           <t>Nghe An: É necessária uma ação urgente para resolver o deslizamento de terra no aterro ao longo da estrada costeira.</t>
         </is>
       </c>
-      <c r="G60" s="43" t="inlineStr"/>
-      <c r="H60" s="43" t="inlineStr"/>
-      <c r="I60" s="39" t="inlineStr">
+      <c r="G80" s="51" t="inlineStr"/>
+      <c r="H80" s="51" t="inlineStr"/>
+      <c r="I80" s="47" t="inlineStr">
         <is>
           <t>Vietnam.vn</t>
         </is>
       </c>
-      <c r="J60" s="39" t="inlineStr">
+      <c r="J80" s="47" t="inlineStr">
         <is>
           <t>Brazil</t>
         </is>
       </c>
-      <c r="K60" s="38" t="n">
+      <c r="K80" s="46" t="n">
         <v>46318</v>
       </c>
-      <c r="L60" s="43" t="inlineStr">
+      <c r="L80" s="51" t="inlineStr">
         <is>
           <t>landslide, embankment</t>
         </is>
       </c>
-      <c r="M60" s="44" t="inlineStr">
-        <is>
-          <t>Open article</t>
-        </is>
-      </c>
-    </row>
-    <row r="61" ht="48" customHeight="1">
-      <c r="A61" s="38" t="n">
-        <v>46319</v>
-      </c>
-      <c r="B61" s="39" t="inlineStr">
-        <is>
-          <t>2026-Q4</t>
-        </is>
-      </c>
-      <c r="C61" s="40" t="inlineStr">
-        <is>
-          <t>Hazards &amp; Resilience</t>
-        </is>
-      </c>
-      <c r="D61" s="41" t="n"/>
-      <c r="E61" s="42" t="inlineStr"/>
-      <c r="F61" s="43" t="inlineStr">
+      <c r="M80" s="52" t="inlineStr">
+        <is>
+          <t>Open article</t>
+        </is>
+      </c>
+    </row>
+    <row r="81" ht="48" customHeight="1">
+      <c r="A81" s="46" t="n">
+        <v>46319</v>
+      </c>
+      <c r="B81" s="47" t="inlineStr">
+        <is>
+          <t>2026-Q4</t>
+        </is>
+      </c>
+      <c r="C81" s="48" t="inlineStr">
+        <is>
+          <t>Hazards &amp; Resilience</t>
+        </is>
+      </c>
+      <c r="D81" s="49" t="n"/>
+      <c r="E81" s="59" t="inlineStr"/>
+      <c r="F81" s="51" t="inlineStr">
         <is>
           <t>Embora concordem em se mudar para evitar deslizamentos de terra, os moradores de Nui Mot estão preocupados com a indenização e o reassentamento.</t>
         </is>
       </c>
-      <c r="G61" s="43" t="inlineStr"/>
-      <c r="H61" s="43" t="inlineStr"/>
-      <c r="I61" s="39" t="inlineStr">
+      <c r="G81" s="51" t="inlineStr"/>
+      <c r="H81" s="51" t="inlineStr"/>
+      <c r="I81" s="47" t="inlineStr">
         <is>
           <t>Vietnam.vn</t>
         </is>
       </c>
-      <c r="J61" s="39" t="inlineStr">
+      <c r="J81" s="47" t="inlineStr">
         <is>
           <t>Brazil</t>
         </is>
       </c>
-      <c r="K61" s="38" t="n">
+      <c r="K81" s="46" t="n">
         <v>46317</v>
       </c>
-      <c r="L61" s="43" t="inlineStr">
+      <c r="L81" s="51" t="inlineStr">
         <is>
           <t>landslide</t>
         </is>
       </c>
-      <c r="M61" s="44" t="inlineStr">
+      <c r="M81" s="52" t="inlineStr">
         <is>
           <t>Open article</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="D2:D61">
+  <conditionalFormatting sqref="D2:D81">
     <cfRule type="cellIs" priority="1" operator="equal" dxfId="0">
       <formula>5</formula>
     </cfRule>
@@ -4639,11 +6161,31 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M59" r:id="rId58"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M60" r:id="rId59"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M65" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M66" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M67" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M68" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M69" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M70" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M71" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M72" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M73" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M74" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M75" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M76" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M77" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M78" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M79" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M80" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M81" r:id="rId80"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
   <tableParts count="1">
-    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId61"/>
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId81"/>
   </tableParts>
 </worksheet>
 </file>
@@ -4654,7 +6196,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D41"/>
+  <dimension ref="A1:D57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -4686,23 +6228,25 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="45" t="inlineStr">
+      <c r="A2" s="60" t="inlineStr">
         <is>
           <t>Vietnam.vn</t>
         </is>
       </c>
       <c r="B2" s="28" t="n">
-        <v>15</v>
-      </c>
-      <c r="C2" s="46" t="n"/>
-      <c r="D2" s="36" t="inlineStr">
+        <v>19</v>
+      </c>
+      <c r="C2" s="61" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="D2" s="43" t="inlineStr">
         <is>
           <t>Hazards &amp; Resilience</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="45" t="inlineStr">
+      <c r="A3" s="60" t="inlineStr">
         <is>
           <t>Il Mattino</t>
         </is>
@@ -4710,15 +6254,15 @@
       <c r="B3" s="28" t="n">
         <v>2</v>
       </c>
-      <c r="C3" s="46" t="n"/>
-      <c r="D3" s="36" t="inlineStr">
+      <c r="C3" s="61" t="n"/>
+      <c r="D3" s="43" t="inlineStr">
         <is>
           <t>Hazards &amp; Resilience</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="45" t="inlineStr">
+      <c r="A4" s="60" t="inlineStr">
         <is>
           <t>Diario Concepción</t>
         </is>
@@ -4726,15 +6270,15 @@
       <c r="B4" s="28" t="n">
         <v>2</v>
       </c>
-      <c r="C4" s="46" t="n"/>
-      <c r="D4" s="36" t="inlineStr">
+      <c r="C4" s="61" t="n"/>
+      <c r="D4" s="43" t="inlineStr">
         <is>
           <t>Hazards &amp; Resilience</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="45" t="inlineStr">
+      <c r="A5" s="60" t="inlineStr">
         <is>
           <t>Canal 9 Bío Bío Televisión</t>
         </is>
@@ -4742,15 +6286,15 @@
       <c r="B5" s="28" t="n">
         <v>2</v>
       </c>
-      <c r="C5" s="46" t="n"/>
-      <c r="D5" s="36" t="inlineStr">
+      <c r="C5" s="61" t="n"/>
+      <c r="D5" s="43" t="inlineStr">
         <is>
           <t>Hazards &amp; Resilience</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="45" t="inlineStr">
+      <c r="A6" s="60" t="inlineStr">
         <is>
           <t>N+</t>
         </is>
@@ -4758,15 +6302,15 @@
       <c r="B6" s="28" t="n">
         <v>2</v>
       </c>
-      <c r="C6" s="46" t="n"/>
-      <c r="D6" s="36" t="inlineStr">
+      <c r="C6" s="61" t="n"/>
+      <c r="D6" s="43" t="inlineStr">
         <is>
           <t>Hazards &amp; Resilience</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="45" t="inlineStr">
+      <c r="A7" s="60" t="inlineStr">
         <is>
           <t>Caracol Radio</t>
         </is>
@@ -4774,15 +6318,15 @@
       <c r="B7" s="28" t="n">
         <v>2</v>
       </c>
-      <c r="C7" s="46" t="n"/>
-      <c r="D7" s="36" t="inlineStr">
+      <c r="C7" s="61" t="n"/>
+      <c r="D7" s="43" t="inlineStr">
         <is>
           <t>Hazards &amp; Resilience</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="45" t="inlineStr">
+      <c r="A8" s="60" t="inlineStr">
         <is>
           <t>TV Azteca Baja California</t>
         </is>
@@ -4790,543 +6334,831 @@
       <c r="B8" s="28" t="n">
         <v>2</v>
       </c>
-      <c r="C8" s="46" t="n"/>
-      <c r="D8" s="36" t="inlineStr">
+      <c r="C8" s="61" t="n"/>
+      <c r="D8" s="43" t="inlineStr">
         <is>
           <t>Hazards &amp; Resilience</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="45" t="inlineStr">
-        <is>
-          <t>VOI.ID</t>
+      <c r="A9" s="60" t="inlineStr">
+        <is>
+          <t>agenzia giornalistica opinione</t>
         </is>
       </c>
       <c r="B9" s="28" t="n">
         <v>1</v>
       </c>
-      <c r="C9" s="46" t="n"/>
-      <c r="D9" s="36" t="inlineStr">
+      <c r="C9" s="61" t="n">
+        <v>4</v>
+      </c>
+      <c r="D9" s="43" t="inlineStr">
         <is>
           <t>Hazards &amp; Resilience</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="45" t="inlineStr">
-        <is>
-          <t>https://investigasi.news/</t>
+      <c r="A10" s="60" t="inlineStr">
+        <is>
+          <t>Il Giornale dei Castelli Romani</t>
         </is>
       </c>
       <c r="B10" s="28" t="n">
         <v>1</v>
       </c>
-      <c r="C10" s="46" t="n"/>
-      <c r="D10" s="36" t="inlineStr">
+      <c r="C10" s="61" t="n">
+        <v>4</v>
+      </c>
+      <c r="D10" s="43" t="inlineStr">
         <is>
           <t>Hazards &amp; Resilience</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="45" t="inlineStr">
-        <is>
-          <t>XPOSE TV</t>
+      <c r="A11" s="60" t="inlineStr">
+        <is>
+          <t>Tv7 Benevento</t>
         </is>
       </c>
       <c r="B11" s="28" t="n">
         <v>1</v>
       </c>
-      <c r="C11" s="46" t="n"/>
-      <c r="D11" s="36" t="inlineStr">
+      <c r="C11" s="61" t="n">
+        <v>4</v>
+      </c>
+      <c r="D11" s="43" t="inlineStr">
         <is>
           <t>Hazards &amp; Resilience</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="45" t="inlineStr">
-        <is>
-          <t>Seven Radio</t>
+      <c r="A12" s="60" t="inlineStr">
+        <is>
+          <t>lacronaca24.it</t>
         </is>
       </c>
       <c r="B12" s="28" t="n">
         <v>1</v>
       </c>
-      <c r="C12" s="46" t="n"/>
-      <c r="D12" s="36" t="inlineStr">
+      <c r="C12" s="61" t="n">
+        <v>4</v>
+      </c>
+      <c r="D12" s="43" t="inlineStr">
         <is>
           <t>Hazards &amp; Resilience</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="45" t="inlineStr">
-        <is>
-          <t>diariolosandes.com.ec</t>
+      <c r="A13" s="60" t="inlineStr">
+        <is>
+          <t>Zazoom Social News</t>
         </is>
       </c>
       <c r="B13" s="28" t="n">
         <v>1</v>
       </c>
-      <c r="C13" s="46" t="n"/>
-      <c r="D13" s="36" t="inlineStr">
+      <c r="C13" s="61" t="n">
+        <v>4</v>
+      </c>
+      <c r="D13" s="43" t="inlineStr">
         <is>
           <t>Hazards &amp; Resilience</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="45" t="inlineStr">
-        <is>
-          <t>El Tiempo</t>
+      <c r="A14" s="60" t="inlineStr">
+        <is>
+          <t>RRI.co.id</t>
         </is>
       </c>
       <c r="B14" s="28" t="n">
         <v>1</v>
       </c>
-      <c r="C14" s="46" t="n"/>
-      <c r="D14" s="36" t="inlineStr">
+      <c r="C14" s="61" t="n">
+        <v>4</v>
+      </c>
+      <c r="D14" s="43" t="inlineStr">
         <is>
           <t>Hazards &amp; Resilience</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="45" t="inlineStr">
-        <is>
-          <t>Diario sin Secretos</t>
+      <c r="A15" s="60" t="inlineStr">
+        <is>
+          <t>Masrawy</t>
         </is>
       </c>
       <c r="B15" s="28" t="n">
         <v>1</v>
       </c>
-      <c r="C15" s="46" t="n"/>
-      <c r="D15" s="36" t="inlineStr">
+      <c r="C15" s="61" t="n">
+        <v>4</v>
+      </c>
+      <c r="D15" s="43" t="inlineStr">
         <is>
           <t>Hazards &amp; Resilience</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="45" t="inlineStr">
-        <is>
-          <t>BioBioChile</t>
+      <c r="A16" s="60" t="inlineStr">
+        <is>
+          <t>Pikiran-Rakyat.com</t>
         </is>
       </c>
       <c r="B16" s="28" t="n">
         <v>1</v>
       </c>
-      <c r="C16" s="46" t="n"/>
-      <c r="D16" s="36" t="inlineStr">
+      <c r="C16" s="61" t="n">
+        <v>4</v>
+      </c>
+      <c r="D16" s="43" t="inlineStr">
         <is>
           <t>Hazards &amp; Resilience</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="45" t="inlineStr">
-        <is>
-          <t>La Tribuna</t>
+      <c r="A17" s="60" t="inlineStr">
+        <is>
+          <t>아시아경제</t>
         </is>
       </c>
       <c r="B17" s="28" t="n">
         <v>1</v>
       </c>
-      <c r="C17" s="46" t="n"/>
-      <c r="D17" s="36" t="inlineStr">
-        <is>
-          <t>Hazards &amp; Resilience</t>
+      <c r="C17" s="61" t="n">
+        <v>4</v>
+      </c>
+      <c r="D17" s="34" t="inlineStr">
+        <is>
+          <t>Infrastructure &amp; the Underground City</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="45" t="inlineStr">
-        <is>
-          <t>Teleamazonas</t>
+      <c r="A18" s="60" t="inlineStr">
+        <is>
+          <t>Baolangson.vn</t>
         </is>
       </c>
       <c r="B18" s="28" t="n">
         <v>1</v>
       </c>
-      <c r="C18" s="46" t="n"/>
-      <c r="D18" s="36" t="inlineStr">
-        <is>
-          <t>Hazards &amp; Resilience</t>
+      <c r="C18" s="61" t="n">
+        <v>4</v>
+      </c>
+      <c r="D18" s="44" t="inlineStr">
+        <is>
+          <t>Characterisation &amp; Modelling</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="45" t="inlineStr">
-        <is>
-          <t>El Universo</t>
+      <c r="A19" s="60" t="inlineStr">
+        <is>
+          <t>Yahoo</t>
         </is>
       </c>
       <c r="B19" s="28" t="n">
         <v>1</v>
       </c>
-      <c r="C19" s="46" t="n"/>
-      <c r="D19" s="36" t="inlineStr">
+      <c r="C19" s="61" t="n">
+        <v>4</v>
+      </c>
+      <c r="D19" s="43" t="inlineStr">
         <is>
           <t>Hazards &amp; Resilience</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="45" t="inlineStr">
-        <is>
-          <t>Destino Panamá</t>
+      <c r="A20" s="60" t="inlineStr">
+        <is>
+          <t>Savona News</t>
         </is>
       </c>
       <c r="B20" s="28" t="n">
         <v>1</v>
       </c>
-      <c r="C20" s="46" t="n"/>
-      <c r="D20" s="36" t="inlineStr">
+      <c r="C20" s="61" t="n">
+        <v>3</v>
+      </c>
+      <c r="D20" s="43" t="inlineStr">
         <is>
           <t>Hazards &amp; Resilience</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="45" t="inlineStr">
-        <is>
-          <t>Lost Coast Outpost</t>
+      <c r="A21" s="60" t="inlineStr">
+        <is>
+          <t>凤凰网</t>
         </is>
       </c>
       <c r="B21" s="28" t="n">
         <v>1</v>
       </c>
-      <c r="C21" s="46" t="n"/>
-      <c r="D21" s="36" t="inlineStr">
+      <c r="C21" s="61" t="n">
+        <v>3</v>
+      </c>
+      <c r="D21" s="43" t="inlineStr">
         <is>
           <t>Hazards &amp; Resilience</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="45" t="inlineStr">
-        <is>
-          <t>Meganoticias</t>
+      <c r="A22" s="60" t="inlineStr">
+        <is>
+          <t>Hub News</t>
         </is>
       </c>
       <c r="B22" s="28" t="n">
         <v>1</v>
       </c>
-      <c r="C22" s="46" t="n"/>
-      <c r="D22" s="36" t="inlineStr">
+      <c r="C22" s="61" t="n">
+        <v>3</v>
+      </c>
+      <c r="D22" s="43" t="inlineStr">
         <is>
           <t>Hazards &amp; Resilience</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="45" t="inlineStr">
-        <is>
-          <t>RCG Media</t>
+      <c r="A23" s="60" t="inlineStr">
+        <is>
+          <t>Deccan Chronicle</t>
         </is>
       </c>
       <c r="B23" s="28" t="n">
         <v>1</v>
       </c>
-      <c r="C23" s="46" t="n"/>
-      <c r="D23" s="36" t="inlineStr">
-        <is>
-          <t>Hazards &amp; Resilience</t>
+      <c r="C23" s="61" t="n">
+        <v>3</v>
+      </c>
+      <c r="D23" s="34" t="inlineStr">
+        <is>
+          <t>Infrastructure &amp; the Underground City</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="45" t="inlineStr">
-        <is>
-          <t>Revista Semana</t>
+      <c r="A24" s="60" t="inlineStr">
+        <is>
+          <t>NewsRadio WFLA</t>
         </is>
       </c>
       <c r="B24" s="28" t="n">
         <v>1</v>
       </c>
-      <c r="C24" s="46" t="n"/>
-      <c r="D24" s="36" t="inlineStr">
+      <c r="C24" s="61" t="n">
+        <v>3</v>
+      </c>
+      <c r="D24" s="43" t="inlineStr">
         <is>
           <t>Hazards &amp; Resilience</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="45" t="inlineStr">
-        <is>
-          <t>Periódico del Meta</t>
+      <c r="A25" s="60" t="inlineStr">
+        <is>
+          <t>VOI.ID</t>
         </is>
       </c>
       <c r="B25" s="28" t="n">
         <v>1</v>
       </c>
-      <c r="C25" s="46" t="n"/>
-      <c r="D25" s="36" t="inlineStr">
+      <c r="C25" s="61" t="n"/>
+      <c r="D25" s="43" t="inlineStr">
         <is>
           <t>Hazards &amp; Resilience</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="45" t="inlineStr">
-        <is>
-          <t>Facebook</t>
+      <c r="A26" s="60" t="inlineStr">
+        <is>
+          <t>https://investigasi.news/</t>
         </is>
       </c>
       <c r="B26" s="28" t="n">
         <v>1</v>
       </c>
-      <c r="C26" s="46" t="n"/>
-      <c r="D26" s="36" t="inlineStr">
+      <c r="C26" s="61" t="n"/>
+      <c r="D26" s="43" t="inlineStr">
         <is>
           <t>Hazards &amp; Resilience</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="45" t="inlineStr">
-        <is>
-          <t>Agencia de Periodismo Investigativo</t>
+      <c r="A27" s="60" t="inlineStr">
+        <is>
+          <t>XPOSE TV</t>
         </is>
       </c>
       <c r="B27" s="28" t="n">
         <v>1</v>
       </c>
-      <c r="C27" s="46" t="n"/>
-      <c r="D27" s="36" t="inlineStr">
+      <c r="C27" s="61" t="n"/>
+      <c r="D27" s="43" t="inlineStr">
         <is>
           <t>Hazards &amp; Resilience</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="45" t="inlineStr">
-        <is>
-          <t>Mi Radio</t>
+      <c r="A28" s="60" t="inlineStr">
+        <is>
+          <t>Seven Radio</t>
         </is>
       </c>
       <c r="B28" s="28" t="n">
         <v>1</v>
       </c>
-      <c r="C28" s="46" t="n"/>
-      <c r="D28" s="36" t="inlineStr">
+      <c r="C28" s="61" t="n"/>
+      <c r="D28" s="43" t="inlineStr">
         <is>
           <t>Hazards &amp; Resilience</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="45" t="inlineStr">
-        <is>
-          <t>Telemetro</t>
+      <c r="A29" s="60" t="inlineStr">
+        <is>
+          <t>diariolosandes.com.ec</t>
         </is>
       </c>
       <c r="B29" s="28" t="n">
         <v>1</v>
       </c>
-      <c r="C29" s="46" t="n"/>
-      <c r="D29" s="36" t="inlineStr">
+      <c r="C29" s="61" t="n"/>
+      <c r="D29" s="43" t="inlineStr">
         <is>
           <t>Hazards &amp; Resilience</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="45" t="inlineStr">
-        <is>
-          <t>El País</t>
+      <c r="A30" s="60" t="inlineStr">
+        <is>
+          <t>El Tiempo</t>
         </is>
       </c>
       <c r="B30" s="28" t="n">
         <v>1</v>
       </c>
-      <c r="C30" s="46" t="n"/>
-      <c r="D30" s="36" t="inlineStr">
+      <c r="C30" s="61" t="n"/>
+      <c r="D30" s="43" t="inlineStr">
         <is>
           <t>Hazards &amp; Resilience</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="45" t="inlineStr">
-        <is>
-          <t>CRÍTICA</t>
+      <c r="A31" s="60" t="inlineStr">
+        <is>
+          <t>Diario sin Secretos</t>
         </is>
       </c>
       <c r="B31" s="28" t="n">
         <v>1</v>
       </c>
-      <c r="C31" s="46" t="n"/>
-      <c r="D31" s="36" t="inlineStr">
+      <c r="C31" s="61" t="n"/>
+      <c r="D31" s="43" t="inlineStr">
         <is>
           <t>Hazards &amp; Resilience</t>
         </is>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="45" t="inlineStr">
-        <is>
-          <t>Azteca Bajío</t>
+      <c r="A32" s="60" t="inlineStr">
+        <is>
+          <t>BioBioChile</t>
         </is>
       </c>
       <c r="B32" s="28" t="n">
         <v>1</v>
       </c>
-      <c r="C32" s="46" t="n"/>
-      <c r="D32" s="36" t="inlineStr">
+      <c r="C32" s="61" t="n"/>
+      <c r="D32" s="43" t="inlineStr">
         <is>
           <t>Hazards &amp; Resilience</t>
         </is>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="45" t="inlineStr">
-        <is>
-          <t>Minuto30</t>
+      <c r="A33" s="60" t="inlineStr">
+        <is>
+          <t>La Tribuna</t>
         </is>
       </c>
       <c r="B33" s="28" t="n">
         <v>1</v>
       </c>
-      <c r="C33" s="46" t="n"/>
-      <c r="D33" s="36" t="inlineStr">
+      <c r="C33" s="61" t="n"/>
+      <c r="D33" s="43" t="inlineStr">
         <is>
           <t>Hazards &amp; Resilience</t>
         </is>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="45" t="inlineStr">
-        <is>
-          <t>Diario del Sur</t>
+      <c r="A34" s="60" t="inlineStr">
+        <is>
+          <t>Teleamazonas</t>
         </is>
       </c>
       <c r="B34" s="28" t="n">
         <v>1</v>
       </c>
-      <c r="C34" s="46" t="n"/>
-      <c r="D34" s="36" t="inlineStr">
+      <c r="C34" s="61" t="n"/>
+      <c r="D34" s="43" t="inlineStr">
         <is>
           <t>Hazards &amp; Resilience</t>
         </is>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="45" t="inlineStr">
-        <is>
-          <t>Estrella Digital Colombia</t>
+      <c r="A35" s="60" t="inlineStr">
+        <is>
+          <t>El Universo</t>
         </is>
       </c>
       <c r="B35" s="28" t="n">
         <v>1</v>
       </c>
-      <c r="C35" s="46" t="n"/>
-      <c r="D35" s="36" t="inlineStr">
+      <c r="C35" s="61" t="n"/>
+      <c r="D35" s="43" t="inlineStr">
         <is>
           <t>Hazards &amp; Resilience</t>
         </is>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="45" t="inlineStr">
-        <is>
-          <t>Infobae</t>
+      <c r="A36" s="60" t="inlineStr">
+        <is>
+          <t>Destino Panamá</t>
         </is>
       </c>
       <c r="B36" s="28" t="n">
         <v>1</v>
       </c>
-      <c r="C36" s="46" t="n"/>
-      <c r="D36" s="36" t="inlineStr">
+      <c r="C36" s="61" t="n"/>
+      <c r="D36" s="43" t="inlineStr">
         <is>
           <t>Hazards &amp; Resilience</t>
         </is>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="45" t="inlineStr">
-        <is>
-          <t>Noticias Caracol</t>
+      <c r="A37" s="60" t="inlineStr">
+        <is>
+          <t>Lost Coast Outpost</t>
         </is>
       </c>
       <c r="B37" s="28" t="n">
         <v>1</v>
       </c>
-      <c r="C37" s="46" t="n"/>
-      <c r="D37" s="36" t="inlineStr">
+      <c r="C37" s="61" t="n"/>
+      <c r="D37" s="43" t="inlineStr">
         <is>
           <t>Hazards &amp; Resilience</t>
         </is>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="45" t="inlineStr">
-        <is>
-          <t>Diario Extra</t>
+      <c r="A38" s="60" t="inlineStr">
+        <is>
+          <t>Meganoticias</t>
         </is>
       </c>
       <c r="B38" s="28" t="n">
         <v>1</v>
       </c>
-      <c r="C38" s="46" t="n"/>
-      <c r="D38" s="36" t="inlineStr">
+      <c r="C38" s="61" t="n"/>
+      <c r="D38" s="43" t="inlineStr">
         <is>
           <t>Hazards &amp; Resilience</t>
         </is>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="45" t="inlineStr">
-        <is>
-          <t>Estadão</t>
+      <c r="A39" s="60" t="inlineStr">
+        <is>
+          <t>RCG Media</t>
         </is>
       </c>
       <c r="B39" s="28" t="n">
         <v>1</v>
       </c>
-      <c r="C39" s="46" t="n"/>
-      <c r="D39" s="36" t="inlineStr">
+      <c r="C39" s="61" t="n"/>
+      <c r="D39" s="43" t="inlineStr">
         <is>
           <t>Hazards &amp; Resilience</t>
         </is>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="45" t="inlineStr">
-        <is>
-          <t>Rádio Mirador</t>
+      <c r="A40" s="60" t="inlineStr">
+        <is>
+          <t>Revista Semana</t>
         </is>
       </c>
       <c r="B40" s="28" t="n">
         <v>1</v>
       </c>
-      <c r="C40" s="46" t="n"/>
-      <c r="D40" s="36" t="inlineStr">
+      <c r="C40" s="61" t="n"/>
+      <c r="D40" s="43" t="inlineStr">
         <is>
           <t>Hazards &amp; Resilience</t>
         </is>
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="45" t="inlineStr">
-        <is>
-          <t>ND Mais</t>
+      <c r="A41" s="60" t="inlineStr">
+        <is>
+          <t>Periódico del Meta</t>
         </is>
       </c>
       <c r="B41" s="28" t="n">
         <v>1</v>
       </c>
-      <c r="C41" s="46" t="n"/>
-      <c r="D41" s="36" t="inlineStr">
+      <c r="C41" s="61" t="n"/>
+      <c r="D41" s="43" t="inlineStr">
+        <is>
+          <t>Hazards &amp; Resilience</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="60" t="inlineStr">
+        <is>
+          <t>Facebook</t>
+        </is>
+      </c>
+      <c r="B42" s="28" t="n">
+        <v>1</v>
+      </c>
+      <c r="C42" s="61" t="n"/>
+      <c r="D42" s="43" t="inlineStr">
+        <is>
+          <t>Hazards &amp; Resilience</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="60" t="inlineStr">
+        <is>
+          <t>Agencia de Periodismo Investigativo</t>
+        </is>
+      </c>
+      <c r="B43" s="28" t="n">
+        <v>1</v>
+      </c>
+      <c r="C43" s="61" t="n"/>
+      <c r="D43" s="43" t="inlineStr">
+        <is>
+          <t>Hazards &amp; Resilience</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="60" t="inlineStr">
+        <is>
+          <t>Mi Radio</t>
+        </is>
+      </c>
+      <c r="B44" s="28" t="n">
+        <v>1</v>
+      </c>
+      <c r="C44" s="61" t="n"/>
+      <c r="D44" s="43" t="inlineStr">
+        <is>
+          <t>Hazards &amp; Resilience</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="60" t="inlineStr">
+        <is>
+          <t>Telemetro</t>
+        </is>
+      </c>
+      <c r="B45" s="28" t="n">
+        <v>1</v>
+      </c>
+      <c r="C45" s="61" t="n"/>
+      <c r="D45" s="43" t="inlineStr">
+        <is>
+          <t>Hazards &amp; Resilience</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="60" t="inlineStr">
+        <is>
+          <t>El País</t>
+        </is>
+      </c>
+      <c r="B46" s="28" t="n">
+        <v>1</v>
+      </c>
+      <c r="C46" s="61" t="n"/>
+      <c r="D46" s="43" t="inlineStr">
+        <is>
+          <t>Hazards &amp; Resilience</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="60" t="inlineStr">
+        <is>
+          <t>CRÍTICA</t>
+        </is>
+      </c>
+      <c r="B47" s="28" t="n">
+        <v>1</v>
+      </c>
+      <c r="C47" s="61" t="n"/>
+      <c r="D47" s="43" t="inlineStr">
+        <is>
+          <t>Hazards &amp; Resilience</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="60" t="inlineStr">
+        <is>
+          <t>Azteca Bajío</t>
+        </is>
+      </c>
+      <c r="B48" s="28" t="n">
+        <v>1</v>
+      </c>
+      <c r="C48" s="61" t="n"/>
+      <c r="D48" s="43" t="inlineStr">
+        <is>
+          <t>Hazards &amp; Resilience</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="60" t="inlineStr">
+        <is>
+          <t>Minuto30</t>
+        </is>
+      </c>
+      <c r="B49" s="28" t="n">
+        <v>1</v>
+      </c>
+      <c r="C49" s="61" t="n"/>
+      <c r="D49" s="43" t="inlineStr">
+        <is>
+          <t>Hazards &amp; Resilience</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="60" t="inlineStr">
+        <is>
+          <t>Diario del Sur</t>
+        </is>
+      </c>
+      <c r="B50" s="28" t="n">
+        <v>1</v>
+      </c>
+      <c r="C50" s="61" t="n"/>
+      <c r="D50" s="43" t="inlineStr">
+        <is>
+          <t>Hazards &amp; Resilience</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="60" t="inlineStr">
+        <is>
+          <t>Estrella Digital Colombia</t>
+        </is>
+      </c>
+      <c r="B51" s="28" t="n">
+        <v>1</v>
+      </c>
+      <c r="C51" s="61" t="n"/>
+      <c r="D51" s="43" t="inlineStr">
+        <is>
+          <t>Hazards &amp; Resilience</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="60" t="inlineStr">
+        <is>
+          <t>Infobae</t>
+        </is>
+      </c>
+      <c r="B52" s="28" t="n">
+        <v>1</v>
+      </c>
+      <c r="C52" s="61" t="n"/>
+      <c r="D52" s="43" t="inlineStr">
+        <is>
+          <t>Hazards &amp; Resilience</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="60" t="inlineStr">
+        <is>
+          <t>Noticias Caracol</t>
+        </is>
+      </c>
+      <c r="B53" s="28" t="n">
+        <v>1</v>
+      </c>
+      <c r="C53" s="61" t="n"/>
+      <c r="D53" s="43" t="inlineStr">
+        <is>
+          <t>Hazards &amp; Resilience</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="60" t="inlineStr">
+        <is>
+          <t>Diario Extra</t>
+        </is>
+      </c>
+      <c r="B54" s="28" t="n">
+        <v>1</v>
+      </c>
+      <c r="C54" s="61" t="n"/>
+      <c r="D54" s="43" t="inlineStr">
+        <is>
+          <t>Hazards &amp; Resilience</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="60" t="inlineStr">
+        <is>
+          <t>Estadão</t>
+        </is>
+      </c>
+      <c r="B55" s="28" t="n">
+        <v>1</v>
+      </c>
+      <c r="C55" s="61" t="n"/>
+      <c r="D55" s="43" t="inlineStr">
+        <is>
+          <t>Hazards &amp; Resilience</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="60" t="inlineStr">
+        <is>
+          <t>Rádio Mirador</t>
+        </is>
+      </c>
+      <c r="B56" s="28" t="n">
+        <v>1</v>
+      </c>
+      <c r="C56" s="61" t="n"/>
+      <c r="D56" s="43" t="inlineStr">
+        <is>
+          <t>Hazards &amp; Resilience</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="60" t="inlineStr">
+        <is>
+          <t>ND Mais</t>
+        </is>
+      </c>
+      <c r="B57" s="28" t="n">
+        <v>1</v>
+      </c>
+      <c r="C57" s="61" t="n"/>
+      <c r="D57" s="43" t="inlineStr">
         <is>
           <t>Hazards &amp; Resilience</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="B2:B41">
+  <conditionalFormatting sqref="B2:B57">
     <cfRule type="colorScale" priority="1">
       <colorScale>
         <cfvo type="min"/>

--- a/docs/exports/geotech-news-archive.xlsx
+++ b/docs/exports/geotech-news-archive.xlsx
@@ -12,8 +12,9 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Stories" sheetId="3" state="visible" r:id="rId3"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="By theme" sheetId="4" state="visible" r:id="rId4"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Research" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sources" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Lists" sheetId="7" state="hidden" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Events" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sources" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Lists" sheetId="8" state="hidden" r:id="rId8"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">'Start here'!$1:$3</definedName>
@@ -23,8 +24,9 @@
     <definedName name="_xlnm.Print_Titles" localSheetId="3">'By theme'!$1:$2</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="4">'Research'!$3:$3</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="4">'Research'!$A$1:$K$23</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="5">'Sources'!$3:$3</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="6">'Lists'!$1:$1</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="5">'Events'!$1:$2</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="6">'Sources'!$3:$3</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="7">'Lists'!$1:$1</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -40,7 +42,7 @@
     <numFmt numFmtId="168" formatCode="0.0"/>
     <numFmt numFmtId="169" formatCode="dd mmm yy;;"/>
   </numFmts>
-  <fonts count="69">
+  <fonts count="73">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -223,14 +225,50 @@
     <font>
       <name val="Arial"/>
       <b val="1"/>
+      <color rgb="0016324F"/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
       <color rgb="00FFFFFF"/>
-      <sz val="12"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="00C9A227"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="0036506C"/>
+      <sz val="9"/>
     </font>
     <font>
       <name val="Arial"/>
       <color rgb="001D5A8A"/>
       <sz val="9"/>
       <u val="single"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="000A6D78"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="007D5A0C"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="12"/>
     </font>
     <font>
       <name val="Arial"/>
@@ -303,18 +341,6 @@
       <b val="1"/>
       <color rgb="002563D6"/>
       <sz val="8"/>
-    </font>
-    <font>
-      <name val="Arial"/>
-      <b val="1"/>
-      <color rgb="0016324F"/>
-      <sz val="12"/>
-    </font>
-    <font>
-      <name val="Arial"/>
-      <b val="1"/>
-      <color rgb="00FFFFFF"/>
-      <sz val="9"/>
     </font>
     <font>
       <name val="Arial"/>
@@ -747,6 +773,11 @@
       <diagonal/>
     </border>
     <border>
+      <bottom style="medium">
+        <color rgb="00C9A227"/>
+      </bottom>
+    </border>
+    <border>
       <bottom style="thin">
         <color rgb="001F9D63"/>
       </bottom>
@@ -828,11 +859,6 @@
       <right style="thick">
         <color rgb="00FFFFFF"/>
       </right>
-    </border>
-    <border>
-      <bottom style="medium">
-        <color rgb="00C9A227"/>
-      </bottom>
     </border>
     <border>
       <left style="thick">
@@ -918,248 +944,248 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="250">
+  <cellXfs count="257">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="32" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="38" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="29" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="33" fillId="29" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="39" fillId="29" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="60" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="64" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="44" fillId="0" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="bottom"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="54" fillId="37" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="58" fillId="37" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="55" fillId="38" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="59" fillId="38" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="56" fillId="39" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="60" fillId="39" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="57" fillId="40" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="61" fillId="40" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="58" fillId="41" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="62" fillId="41" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="33" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="33" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="42" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="42" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="43" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="43" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="44" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="9" fillId="44" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="45" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="9" fillId="45" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="46" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="9" fillId="46" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="61" fillId="14" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="65" fillId="14" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="62" fillId="16" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="66" fillId="16" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="63" fillId="18" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="67" fillId="18" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="64" fillId="20" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="68" fillId="20" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="65" fillId="22" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="69" fillId="22" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="66" fillId="24" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="70" fillId="24" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="67" fillId="26" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="71" fillId="26" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="68" fillId="28" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="72" fillId="28" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="47" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="51" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="34" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="40" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="bottom"/>
     </xf>
-    <xf numFmtId="0" fontId="36" fillId="31" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="42" fillId="31" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="31" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="35" fillId="30" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="41" fillId="30" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="30" borderId="11" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="30" borderId="12" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="30" borderId="13" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="3" fontId="37" fillId="2" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="3" fontId="43" fillId="2" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="13" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="3" fontId="37" fillId="23" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="14" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="43" fillId="23" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="23" borderId="13" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="3" fontId="37" fillId="33" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="23" borderId="14" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="43" fillId="33" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="33" borderId="13" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="3" fontId="37" fillId="19" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="33" borderId="14" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="43" fillId="19" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="19" borderId="13" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="3" fontId="37" fillId="15" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="19" borderId="14" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="43" fillId="15" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="15" borderId="13" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="3" fontId="37" fillId="21" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="15" borderId="14" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="43" fillId="21" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="21" borderId="13" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="38" fillId="32" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="21" borderId="14" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="44" fillId="32" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="32" borderId="13" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="39" fillId="24" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="32" borderId="14" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="45" fillId="24" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="24" borderId="13" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="40" fillId="34" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="24" borderId="14" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="46" fillId="34" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="34" borderId="13" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="41" fillId="20" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="34" borderId="14" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="47" fillId="20" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="20" borderId="13" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="42" fillId="16" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="20" borderId="14" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="48" fillId="16" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="16" borderId="13" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="43" fillId="22" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="16" borderId="14" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="49" fillId="22" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="22" borderId="13" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="14" fillId="32" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="22" borderId="14" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="14" fillId="32" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="24" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="14" fillId="24" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="34" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="14" fillId="34" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="20" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="14" fillId="20" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="16" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="14" fillId="16" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="22" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="14" fillId="22" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="45" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="31" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="45" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="31" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="46" fillId="35" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="50" fillId="35" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="47" fillId="35" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="51" fillId="35" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="35" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="169" fontId="13" fillId="35" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="35" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="169" fontId="13" fillId="35" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="48" fillId="35" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="52" fillId="35" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="35" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="9" fillId="35" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="35" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="13" fillId="35" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="35" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="35" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="49" fillId="35" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="53" fillId="35" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="46" fillId="31" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="50" fillId="31" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="47" fillId="31" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="51" fillId="31" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="31" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="169" fontId="13" fillId="31" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="31" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="169" fontId="13" fillId="31" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="48" fillId="31" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="52" fillId="31" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="31" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="9" fillId="31" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="31" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="13" fillId="31" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="31" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="31" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="49" fillId="31" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="53" fillId="31" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="36" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="42" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="25" fillId="14" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="14" borderId="15" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="9" fontId="6" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="9" fontId="6" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="26" fillId="16" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -1190,54 +1216,54 @@
       <alignment vertical="center" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="28" borderId="22" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="50" fillId="36" borderId="23" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="54" fillId="36" borderId="23" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="36" borderId="23" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="54" fillId="37" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="58" fillId="37" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="37" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="37" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="52" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="56" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="55" fillId="38" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="59" fillId="38" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="38" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="38" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="53" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="57" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="56" fillId="39" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="60" fillId="39" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="39" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="39" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="57" fillId="40" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="61" fillId="40" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="40" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="51" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="40" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="55" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="58" fillId="41" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="62" fillId="41" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="41" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="41" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="25" fillId="0" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" indent="1"/>
     </xf>
@@ -1273,14 +1299,14 @@
       <alignment vertical="center" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="22" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="50" fillId="0" borderId="23" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="54" fillId="0" borderId="23" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="23" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="59" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="63" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -1332,10 +1358,10 @@
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -1378,117 +1404,117 @@
     <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="30" fillId="13" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="37" fillId="13" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="13" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="19" fillId="14" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="19" fillId="14" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="14" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="19" fillId="14" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="31" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="34" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="166" fontId="13" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="166" fontId="13" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="30" fillId="15" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="37" fillId="15" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="15" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="10" fillId="16" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="10" fillId="16" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="16" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="10" fillId="16" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="30" fillId="17" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="37" fillId="17" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="17" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="18" fillId="18" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="18" fillId="18" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="18" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="18" fillId="18" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="30" fillId="19" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="37" fillId="19" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="19" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="8" fillId="20" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="20" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="20" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="20" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="30" fillId="21" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="37" fillId="21" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="21" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="17" fillId="22" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="17" fillId="22" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="22" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="17" fillId="22" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="30" fillId="23" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="37" fillId="23" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="23" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="16" fillId="24" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="16" fillId="24" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="24" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="16" fillId="24" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="30" fillId="25" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="37" fillId="25" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="25" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="20" fillId="26" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="20" fillId="26" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="26" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="20" fillId="26" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="30" fillId="27" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="37" fillId="27" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="27" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="21" fillId="28" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="21" fillId="28" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="28" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="21" fillId="28" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -1508,6 +1534,25 @@
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="9" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
@@ -3119,9 +3164,9 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="StoriesTable" displayName="StoriesTable" ref="A3:U63" headerRowCount="1">
-  <autoFilter ref="A3:U63"/>
-  <tableColumns count="21">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="StoriesTable" displayName="StoriesTable" ref="A3:X63" headerRowCount="1">
+  <autoFilter ref="A3:X63"/>
+  <tableColumns count="24">
     <tableColumn id="1" name="No."/>
     <tableColumn id="2" name="Headline (English)"/>
     <tableColumn id="3" name="Theme"/>
@@ -3135,14 +3180,17 @@
     <tableColumn id="11" name="Digest date"/>
     <tableColumn id="12" name="Original headline"/>
     <tableColumn id="13" name="Summary"/>
-    <tableColumn id="14" name="Google News edition"/>
-    <tableColumn id="15" name="Published"/>
-    <tableColumn id="16" name="Issue window"/>
-    <tableColumn id="17" name="Keywords"/>
-    <tableColumn id="18" name="Keyword score"/>
-    <tableColumn id="19" name="Article URL"/>
-    <tableColumn id="20" name="In Dashboard selection"/>
-    <tableColumn id="21" name="Top-10 key (helper)"/>
+    <tableColumn id="14" name="Country"/>
+    <tableColumn id="15" name="Place"/>
+    <tableColumn id="16" name="Developing story"/>
+    <tableColumn id="17" name="Google News edition"/>
+    <tableColumn id="18" name="Published"/>
+    <tableColumn id="19" name="Issue window"/>
+    <tableColumn id="20" name="Keywords"/>
+    <tableColumn id="21" name="Keyword score"/>
+    <tableColumn id="22" name="Article URL"/>
+    <tableColumn id="23" name="In Dashboard selection"/>
+    <tableColumn id="24" name="Top-10 key (helper)"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight1" showRowStripes="1"/>
 </table>
@@ -3479,7 +3527,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:E50"/>
+  <dimension ref="A1:E51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="2" customWidth="1" min="1" max="1"/>
@@ -3547,7 +3595,7 @@
       </c>
       <c r="D8" s="11" t="n"/>
     </row>
-    <row r="9" ht="31" customHeight="1">
+    <row r="9" ht="44" customHeight="1">
       <c r="B9" s="9" t="inlineStr">
         <is>
           <t>Stories →</t>
@@ -3555,7 +3603,7 @@
       </c>
       <c r="C9" s="10" t="inlineStr">
         <is>
-          <t>Every story as a filterable Excel table, newest digest first; click a headline to open the article. The gold columns – Status, Assigned to and Editor notes – are for you to fill in.</t>
+          <t>Every story as a filterable Excel table, newest digest first; click a headline to open the article. The gold columns – Status, Assigned to and Editor notes – are for you to fill in. Further right: where each story happened (Country, Place) and the Developing story it belongs to.</t>
         </is>
       </c>
       <c r="D9" s="11" t="n"/>
@@ -3589,47 +3637,47 @@
     <row r="12" ht="31" customHeight="1">
       <c r="B12" s="9" t="inlineStr">
         <is>
+          <t>Events →</t>
+        </is>
+      </c>
+      <c r="C12" s="10" t="inlineStr">
+        <is>
+          <t>The events calendar on 24 Oct 2026: 0 open call-for-papers deadlines with the days left, and 6 upcoming events (ISSMGE conferences, other conferences, courses and webinars), each linked to its website.</t>
+        </is>
+      </c>
+      <c r="D12" s="11" t="n"/>
+    </row>
+    <row r="13" ht="31" customHeight="1">
+      <c r="B13" s="9" t="inlineStr">
+        <is>
           <t>Sources →</t>
         </is>
       </c>
-      <c r="C12" s="10" t="inlineStr">
+      <c r="C13" s="10" t="inlineStr">
         <is>
           <t>The outlets that supplied stories: how many, average relevance, main theme and how many match the current Dashboard selection.</t>
         </is>
       </c>
-      <c r="D12" s="11" t="n"/>
-    </row>
-    <row r="14" ht="22" customHeight="1">
-      <c r="B14" s="7" t="inlineStr">
+      <c r="D13" s="11" t="n"/>
+    </row>
+    <row r="15" ht="22" customHeight="1">
+      <c r="B15" s="7" t="inlineStr">
         <is>
           <t>How to use the Dashboard selectors</t>
         </is>
       </c>
-      <c r="C14" s="8" t="n"/>
-      <c r="D14" s="8" t="n"/>
-    </row>
-    <row r="15" ht="31" customHeight="1">
-      <c r="B15" s="12" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="C15" s="10" t="inlineStr">
-        <is>
-          <t>Open the Dashboard. The yellow boxes at the top are selectors: Theme, Suggested use, Minimum relevance and Issue window.</t>
-        </is>
-      </c>
-      <c r="D15" s="11" t="n"/>
+      <c r="C15" s="8" t="n"/>
+      <c r="D15" s="8" t="n"/>
     </row>
     <row r="16" ht="31" customHeight="1">
       <c r="B16" s="12" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C16" s="10" t="inlineStr">
         <is>
-          <t>Click a yellow box, then the ▼ arrow that appears beside it, and pick a value. Choose “All …” or “Any” to clear that selector.</t>
+          <t>Open the Dashboard. The yellow boxes at the top are selectors: Theme, Suggested use, Minimum relevance and Issue window.</t>
         </is>
       </c>
       <c r="D16" s="11" t="n"/>
@@ -3637,12 +3685,12 @@
     <row r="17" ht="31" customHeight="1">
       <c r="B17" s="12" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C17" s="10" t="inlineStr">
         <is>
-          <t>The key figures, tables, charts, heat map and the Top 10 list recalculate at once. Headlines in the Top 10 open the article.</t>
+          <t>Click a yellow box, then the ▼ arrow that appears beside it, and pick a value. Choose “All …” or “Any” to clear that selector.</t>
         </is>
       </c>
       <c r="D17" s="11" t="n"/>
@@ -3650,12 +3698,12 @@
     <row r="18" ht="31" customHeight="1">
       <c r="B18" s="12" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C18" s="10" t="inlineStr">
         <is>
-          <t>In Stories, set each story’s Status as you plan the issue. The Dashboard’s Planning status table and chart, and the PLANNED figure, count them straight away.</t>
+          <t>The key figures, tables, charts, heat map and the Top 10 list recalculate at once. Headlines in the Top 10 open the article.</t>
         </is>
       </c>
       <c r="D18" s="11" t="n"/>
@@ -3663,334 +3711,334 @@
     <row r="19" ht="31" customHeight="1">
       <c r="B19" s="12" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="C19" s="10" t="inlineStr">
+        <is>
+          <t>In Stories, set each story’s Status as you plan the issue. The Dashboard’s Planning status table and chart, and the PLANNED figure, count them straight away.</t>
+        </is>
+      </c>
+      <c r="D19" s="11" t="n"/>
+    </row>
+    <row r="20" ht="31" customHeight="1">
+      <c r="B20" s="12" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="C19" s="10" t="inlineStr">
+      <c r="C20" s="10" t="inlineStr">
         <is>
           <t>Filters in the Stories table (▼ in its header) only hide rows; the Dashboard follows the selectors. To list exactly what the Dashboard shows, filter the ‘In Dashboard selection’ column of Stories to ✓.</t>
         </is>
       </c>
-      <c r="D19" s="11" t="n"/>
-    </row>
-    <row r="21" ht="22" customHeight="1">
-      <c r="B21" s="7" t="inlineStr">
+      <c r="D20" s="11" t="n"/>
+    </row>
+    <row r="22" ht="22" customHeight="1">
+      <c r="B22" s="7" t="inlineStr">
         <is>
           <t>Planning status (Stories › Status)</t>
         </is>
       </c>
-      <c r="C21" s="8" t="n"/>
-      <c r="D21" s="8" t="n"/>
-    </row>
-    <row r="22" ht="18" customHeight="1">
-      <c r="B22" s="13" t="inlineStr">
+      <c r="C22" s="8" t="n"/>
+      <c r="D22" s="8" t="n"/>
+    </row>
+    <row r="23" ht="18" customHeight="1">
+      <c r="B23" s="13" t="inlineStr">
         <is>
           <t>To review</t>
         </is>
       </c>
-      <c r="C22" s="10" t="inlineStr">
+      <c r="C23" s="10" t="inlineStr">
         <is>
           <t>New from the scan, not looked at yet (every story starts here)</t>
         </is>
       </c>
-      <c r="D22" s="11" t="n"/>
-    </row>
-    <row r="23" ht="18" customHeight="1">
-      <c r="B23" s="14" t="inlineStr">
+      <c r="D23" s="11" t="n"/>
+    </row>
+    <row r="24" ht="18" customHeight="1">
+      <c r="B24" s="14" t="inlineStr">
         <is>
           <t>Shortlisted</t>
         </is>
       </c>
-      <c r="C23" s="10" t="inlineStr">
+      <c r="C24" s="10" t="inlineStr">
         <is>
           <t>Worth considering for the issue</t>
         </is>
       </c>
-      <c r="D23" s="11" t="n"/>
-    </row>
-    <row r="24" ht="18" customHeight="1">
-      <c r="B24" s="15" t="inlineStr">
+      <c r="D24" s="11" t="n"/>
+    </row>
+    <row r="25" ht="18" customHeight="1">
+      <c r="B25" s="15" t="inlineStr">
         <is>
           <t>Commissioned</t>
         </is>
       </c>
-      <c r="C24" s="10" t="inlineStr">
+      <c r="C25" s="10" t="inlineStr">
         <is>
           <t>A writer or contributor has been asked to cover it</t>
         </is>
       </c>
-      <c r="D24" s="11" t="n"/>
-    </row>
-    <row r="25" ht="18" customHeight="1">
-      <c r="B25" s="16" t="inlineStr">
+      <c r="D25" s="11" t="n"/>
+    </row>
+    <row r="26" ht="18" customHeight="1">
+      <c r="B26" s="16" t="inlineStr">
         <is>
           <t>Published</t>
         </is>
       </c>
-      <c r="C25" s="10" t="inlineStr">
+      <c r="C26" s="10" t="inlineStr">
         <is>
           <t>Used in a published issue or newsletter</t>
         </is>
       </c>
-      <c r="D25" s="11" t="n"/>
-    </row>
-    <row r="26" ht="18" customHeight="1">
-      <c r="B26" s="17" t="inlineStr">
+      <c r="D26" s="11" t="n"/>
+    </row>
+    <row r="27" ht="18" customHeight="1">
+      <c r="B27" s="17" t="inlineStr">
         <is>
           <t>Not used</t>
         </is>
       </c>
-      <c r="C26" s="10" t="inlineStr">
+      <c r="C27" s="10" t="inlineStr">
         <is>
           <t>Reviewed and set aside</t>
         </is>
       </c>
-      <c r="D26" s="11" t="n"/>
-    </row>
-    <row r="28" ht="22" customHeight="1">
-      <c r="B28" s="7" t="inlineStr">
+      <c r="D27" s="11" t="n"/>
+    </row>
+    <row r="29" ht="22" customHeight="1">
+      <c r="B29" s="7" t="inlineStr">
         <is>
           <t>Relevance scale (AI triage)</t>
         </is>
       </c>
-      <c r="C28" s="8" t="n"/>
-      <c r="D28" s="8" t="n"/>
-    </row>
-    <row r="29" ht="18" customHeight="1">
-      <c r="B29" s="18" t="inlineStr">
+      <c r="C29" s="8" t="n"/>
+      <c r="D29" s="8" t="n"/>
+    </row>
+    <row r="30" ht="18" customHeight="1">
+      <c r="B30" s="18" t="inlineStr">
         <is>
           <t>5 / 5</t>
         </is>
       </c>
-      <c r="C29" s="10" t="inlineStr">
+      <c r="C30" s="10" t="inlineStr">
         <is>
           <t>Rich geotechnical lesson or a major ground-related event</t>
         </is>
       </c>
-      <c r="D29" s="11" t="n"/>
-    </row>
-    <row r="30" ht="18" customHeight="1">
-      <c r="B30" s="19" t="inlineStr">
+      <c r="D30" s="11" t="n"/>
+    </row>
+    <row r="31" ht="18" customHeight="1">
+      <c r="B31" s="19" t="inlineStr">
         <is>
           <t>4 / 5</t>
         </is>
       </c>
-      <c r="C30" s="10" t="inlineStr">
+      <c r="C31" s="10" t="inlineStr">
         <is>
           <t>Strong ground-engineering content</t>
         </is>
       </c>
-      <c r="D30" s="11" t="n"/>
-    </row>
-    <row r="31" ht="18" customHeight="1">
-      <c r="B31" s="20" t="inlineStr">
+      <c r="D31" s="11" t="n"/>
+    </row>
+    <row r="32" ht="18" customHeight="1">
+      <c r="B32" s="20" t="inlineStr">
         <is>
           <t>3 / 5</t>
         </is>
       </c>
-      <c r="C31" s="10" t="inlineStr">
+      <c r="C32" s="10" t="inlineStr">
         <is>
           <t>Clear ground-engineering element, worth a brief</t>
         </is>
       </c>
-      <c r="D31" s="11" t="n"/>
-    </row>
-    <row r="32" ht="18" customHeight="1">
-      <c r="B32" s="21" t="inlineStr">
+      <c r="D32" s="11" t="n"/>
+    </row>
+    <row r="33" ht="18" customHeight="1">
+      <c r="B33" s="21" t="inlineStr">
         <is>
           <t>2 / 5</t>
         </is>
       </c>
-      <c r="C32" s="10" t="inlineStr">
+      <c r="C33" s="10" t="inlineStr">
         <is>
           <t>Weak link to geotechnics</t>
         </is>
       </c>
-      <c r="D32" s="11" t="n"/>
-    </row>
-    <row r="33" ht="18" customHeight="1">
-      <c r="B33" s="22" t="inlineStr">
+      <c r="D33" s="11" t="n"/>
+    </row>
+    <row r="34" ht="18" customHeight="1">
+      <c r="B34" s="22" t="inlineStr">
         <is>
           <t>1 / 5</t>
         </is>
       </c>
-      <c r="C33" s="10" t="inlineStr">
+      <c r="C34" s="10" t="inlineStr">
         <is>
           <t>Not really geotechnical</t>
         </is>
       </c>
-      <c r="D33" s="11" t="n"/>
-    </row>
-    <row r="34" ht="18" customHeight="1">
-      <c r="B34" s="23" t="inlineStr">
+      <c r="D34" s="11" t="n"/>
+    </row>
+    <row r="35" ht="18" customHeight="1">
+      <c r="B35" s="23" t="inlineStr">
         <is>
           <t>–</t>
         </is>
       </c>
-      <c r="C34" s="10" t="inlineStr">
+      <c r="C35" s="10" t="inlineStr">
         <is>
           <t>Shown as –. Not rated by AI: ranked on keyword matches only</t>
         </is>
       </c>
-      <c r="D34" s="11" t="n"/>
-    </row>
-    <row r="36" ht="22" customHeight="1">
-      <c r="B36" s="7" t="inlineStr">
+      <c r="D35" s="11" t="n"/>
+    </row>
+    <row r="37" ht="22" customHeight="1">
+      <c r="B37" s="7" t="inlineStr">
         <is>
           <t>Jump to a theme (opens its section in By theme)</t>
         </is>
       </c>
-      <c r="C36" s="8" t="n"/>
-      <c r="D36" s="8" t="n"/>
-    </row>
-    <row r="37" ht="18" customHeight="1">
-      <c r="B37" s="24" t="inlineStr">
+      <c r="C37" s="8" t="n"/>
+      <c r="D37" s="8" t="n"/>
+    </row>
+    <row r="38" ht="18" customHeight="1">
+      <c r="B38" s="24" t="inlineStr">
         <is>
           <t>Sustainability &amp; the Energy Transition</t>
         </is>
       </c>
-      <c r="C37" s="10" t="inlineStr">
+      <c r="C38" s="10" t="inlineStr">
         <is>
           <t>3 stories · 0 rated 5 / 5 · 0 feature leads</t>
         </is>
       </c>
-      <c r="D37" s="11" t="n"/>
-    </row>
-    <row r="38" ht="18" customHeight="1">
-      <c r="B38" s="25" t="inlineStr">
+      <c r="D38" s="11" t="n"/>
+    </row>
+    <row r="39" ht="18" customHeight="1">
+      <c r="B39" s="25" t="inlineStr">
         <is>
           <t>Digital Geotechnics</t>
         </is>
       </c>
-      <c r="C38" s="10" t="inlineStr">
+      <c r="C39" s="10" t="inlineStr">
         <is>
           <t>1 story · 1 rated 5 / 5 · 0 feature leads</t>
         </is>
       </c>
-      <c r="D38" s="11" t="n"/>
-    </row>
-    <row r="39" ht="18" customHeight="1">
-      <c r="B39" s="26" t="inlineStr">
+      <c r="D39" s="11" t="n"/>
+    </row>
+    <row r="40" ht="18" customHeight="1">
+      <c r="B40" s="26" t="inlineStr">
         <is>
           <t>Hazards &amp; Resilience</t>
         </is>
       </c>
-      <c r="C39" s="10" t="inlineStr">
+      <c r="C40" s="10" t="inlineStr">
         <is>
           <t>17 stories · 1 rated 5 / 5 · 8 feature leads</t>
         </is>
       </c>
-      <c r="D39" s="11" t="n"/>
-    </row>
-    <row r="40" ht="18" customHeight="1">
-      <c r="B40" s="27" t="inlineStr">
+      <c r="D40" s="11" t="n"/>
+    </row>
+    <row r="41" ht="18" customHeight="1">
+      <c r="B41" s="27" t="inlineStr">
         <is>
           <t>Ground Improvement &amp; Innovation</t>
         </is>
       </c>
-      <c r="C40" s="10" t="inlineStr">
+      <c r="C41" s="10" t="inlineStr">
         <is>
           <t>2 stories · 2 rated 5 / 5 · 1 feature lead</t>
         </is>
       </c>
-      <c r="D40" s="11" t="n"/>
-    </row>
-    <row r="41" ht="18" customHeight="1">
-      <c r="B41" s="28" t="inlineStr">
+      <c r="D41" s="11" t="n"/>
+    </row>
+    <row r="42" ht="18" customHeight="1">
+      <c r="B42" s="28" t="inlineStr">
         <is>
           <t>Infrastructure &amp; the Underground City</t>
         </is>
       </c>
-      <c r="C41" s="10" t="inlineStr">
+      <c r="C42" s="10" t="inlineStr">
         <is>
           <t>17 stories · 1 rated 5 / 5 · 7 feature leads</t>
         </is>
       </c>
-      <c r="D41" s="11" t="n"/>
-    </row>
-    <row r="42" ht="18" customHeight="1">
-      <c r="B42" s="29" t="inlineStr">
+      <c r="D42" s="11" t="n"/>
+    </row>
+    <row r="43" ht="18" customHeight="1">
+      <c r="B43" s="29" t="inlineStr">
         <is>
           <t>Offshore, Coasts &amp; Water</t>
         </is>
       </c>
-      <c r="C42" s="10" t="inlineStr">
+      <c r="C43" s="10" t="inlineStr">
         <is>
           <t>10 stories · 1 rated 5 / 5 · 3 feature leads</t>
         </is>
       </c>
-      <c r="D42" s="11" t="n"/>
-    </row>
-    <row r="43" ht="18" customHeight="1">
-      <c r="B43" s="30" t="inlineStr">
+      <c r="D43" s="11" t="n"/>
+    </row>
+    <row r="44" ht="18" customHeight="1">
+      <c r="B44" s="30" t="inlineStr">
         <is>
           <t>Characterisation &amp; Modelling</t>
         </is>
       </c>
-      <c r="C43" s="10" t="inlineStr">
+      <c r="C44" s="10" t="inlineStr">
         <is>
           <t>6 stories · 0 rated 5 / 5 · 4 feature leads</t>
         </is>
       </c>
-      <c r="D43" s="11" t="n"/>
-    </row>
-    <row r="44" ht="18" customHeight="1">
-      <c r="B44" s="31" t="inlineStr">
+      <c r="D44" s="11" t="n"/>
+    </row>
+    <row r="45" ht="18" customHeight="1">
+      <c r="B45" s="31" t="inlineStr">
         <is>
           <t>Geotechnics &amp; Society</t>
         </is>
       </c>
-      <c r="C44" s="10" t="inlineStr">
+      <c r="C45" s="10" t="inlineStr">
         <is>
           <t>4 stories · 0 rated 5 / 5 · 1 feature lead</t>
         </is>
       </c>
-      <c r="D44" s="11" t="n"/>
-    </row>
-    <row r="45" ht="18" customHeight="1">
-      <c r="B45" s="32" t="inlineStr">
+      <c r="D45" s="11" t="n"/>
+    </row>
+    <row r="46" ht="18" customHeight="1">
+      <c r="B46" s="32" t="inlineStr">
         <is>
           <t>No stories yet</t>
         </is>
       </c>
-      <c r="C45" s="10" t="inlineStr">
+      <c r="C46" s="10" t="inlineStr">
         <is>
           <t>General</t>
         </is>
       </c>
-      <c r="D45" s="11" t="n"/>
-    </row>
-    <row r="47" ht="22" customHeight="1">
-      <c r="B47" s="7" t="inlineStr">
+      <c r="D46" s="11" t="n"/>
+    </row>
+    <row r="48" ht="22" customHeight="1">
+      <c r="B48" s="7" t="inlineStr">
         <is>
           <t>Good to know</t>
         </is>
       </c>
-      <c r="C47" s="8" t="n"/>
-      <c r="D47" s="8" t="n"/>
-    </row>
-    <row r="48" ht="44" customHeight="1">
-      <c r="B48" s="33" t="inlineStr">
+      <c r="C48" s="8" t="n"/>
+      <c r="D48" s="8" t="n"/>
+    </row>
+    <row r="49" ht="44" customHeight="1">
+      <c r="B49" s="33" t="inlineStr">
         <is>
           <t>Blank figures?</t>
         </is>
       </c>
-      <c r="C48" s="10" t="inlineStr">
+      <c r="C49" s="10" t="inlineStr">
         <is>
           <t>The Dashboard is calculated when the file opens. If it shows blanks or zeros in Excel, click Enable Editing in the yellow bar at the top (files from the internet open in Protected View); in LibreOffice press Ctrl+Shift+F9.</t>
-        </is>
-      </c>
-      <c r="D48" s="11" t="n"/>
-    </row>
-    <row r="49" ht="31" customHeight="1">
-      <c r="B49" s="33" t="inlineStr">
-        <is>
-          <t>Your edits</t>
-        </is>
-      </c>
-      <c r="C49" s="10" t="inlineStr">
-        <is>
-          <t>This file is generated again after every scan. Status, Assigned to and Editor notes are kept only in the copy you save, so keep one working copy per issue.</t>
         </is>
       </c>
       <c r="D49" s="11" t="n"/>
@@ -3998,43 +4046,57 @@
     <row r="50" ht="31" customHeight="1">
       <c r="B50" s="33" t="inlineStr">
         <is>
+          <t>Your edits</t>
+        </is>
+      </c>
+      <c r="C50" s="10" t="inlineStr">
+        <is>
+          <t>This file is generated again after every scan. Status, Assigned to and Editor notes are kept only in the copy you save, so keep one working copy per issue.</t>
+        </is>
+      </c>
+      <c r="D50" s="11" t="n"/>
+    </row>
+    <row r="51" ht="31" customHeight="1">
+      <c r="B51" s="33" t="inlineStr">
+        <is>
           <t>Lists sheet</t>
         </is>
       </c>
-      <c r="C50" s="10" t="inlineStr">
+      <c r="C51" s="10" t="inlineStr">
         <is>
           <t>A hidden sheet holds the values offered by the dropdowns and some helper cells. There is no need to change it.</t>
         </is>
       </c>
-      <c r="D50" s="11" t="n"/>
+      <c r="D51" s="11" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="36">
+  <mergeCells count="37">
     <mergeCell ref="C34:D34"/>
     <mergeCell ref="C24:D24"/>
     <mergeCell ref="C30:D30"/>
-    <mergeCell ref="C15:D15"/>
     <mergeCell ref="C33:D33"/>
     <mergeCell ref="B1:D1"/>
     <mergeCell ref="C42:D42"/>
     <mergeCell ref="C45:D45"/>
     <mergeCell ref="C26:D26"/>
-    <mergeCell ref="C29:D29"/>
+    <mergeCell ref="C35:D35"/>
+    <mergeCell ref="C20:D20"/>
     <mergeCell ref="C10:D10"/>
     <mergeCell ref="C16:D16"/>
     <mergeCell ref="C25:D25"/>
     <mergeCell ref="C41:D41"/>
     <mergeCell ref="C50:D50"/>
     <mergeCell ref="C44:D44"/>
-    <mergeCell ref="C22:D22"/>
     <mergeCell ref="C40:D40"/>
     <mergeCell ref="C9:D9"/>
     <mergeCell ref="C31:D31"/>
     <mergeCell ref="C43:D43"/>
     <mergeCell ref="C12:D12"/>
     <mergeCell ref="B5:D5"/>
+    <mergeCell ref="C46:D46"/>
     <mergeCell ref="C11:D11"/>
-    <mergeCell ref="C48:D48"/>
+    <mergeCell ref="C51:D51"/>
+    <mergeCell ref="C27:D27"/>
     <mergeCell ref="C23:D23"/>
     <mergeCell ref="C17:D17"/>
     <mergeCell ref="C39:D39"/>
@@ -4042,7 +4104,7 @@
     <mergeCell ref="C32:D32"/>
     <mergeCell ref="C38:D38"/>
     <mergeCell ref="C19:D19"/>
-    <mergeCell ref="C37:D37"/>
+    <mergeCell ref="C13:D13"/>
     <mergeCell ref="C18:D18"/>
     <mergeCell ref="B2:D2"/>
     <mergeCell ref="C49:D49"/>
@@ -4052,15 +4114,16 @@
     <hyperlink ref="B9" location="'Stories'!A1" display="Stories →"/>
     <hyperlink ref="B10" location="'By theme'!A1" display="By theme →"/>
     <hyperlink ref="B11" location="'Research'!A1" display="Research →"/>
-    <hyperlink ref="B12" location="'Sources'!A1" display="Sources →"/>
-    <hyperlink ref="B37" location="'By theme'!A4" display="Sustainability &amp; the Energy Transition"/>
-    <hyperlink ref="B38" location="'By theme'!A10" display="Digital Geotechnics"/>
-    <hyperlink ref="B39" location="'By theme'!A14" display="Hazards &amp; Resilience"/>
-    <hyperlink ref="B40" location="'By theme'!A34" display="Ground Improvement &amp; Innovation"/>
-    <hyperlink ref="B41" location="'By theme'!A39" display="Infrastructure &amp; the Underground City"/>
-    <hyperlink ref="B42" location="'By theme'!A59" display="Offshore, Coasts &amp; Water"/>
-    <hyperlink ref="B43" location="'By theme'!A72" display="Characterisation &amp; Modelling"/>
-    <hyperlink ref="B44" location="'By theme'!A81" display="Geotechnics &amp; Society"/>
+    <hyperlink ref="B12" location="'Events'!A1" display="Events →"/>
+    <hyperlink ref="B13" location="'Sources'!A1" display="Sources →"/>
+    <hyperlink ref="B38" location="'By theme'!A4" display="Sustainability &amp; the Energy Transition"/>
+    <hyperlink ref="B39" location="'By theme'!A10" display="Digital Geotechnics"/>
+    <hyperlink ref="B40" location="'By theme'!A14" display="Hazards &amp; Resilience"/>
+    <hyperlink ref="B41" location="'By theme'!A34" display="Ground Improvement &amp; Innovation"/>
+    <hyperlink ref="B42" location="'By theme'!A39" display="Infrastructure &amp; the Underground City"/>
+    <hyperlink ref="B43" location="'By theme'!A59" display="Offshore, Coasts &amp; Water"/>
+    <hyperlink ref="B44" location="'By theme'!A72" display="Characterisation &amp; Modelling"/>
+    <hyperlink ref="B45" location="'By theme'!A81" display="Geotechnics &amp; Society"/>
   </hyperlinks>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.55" header="0.25" footer="0.25"/>
@@ -4268,19 +4331,19 @@
       <c r="F8" s="44" t="n"/>
       <c r="G8" s="44" t="n"/>
       <c r="H8" s="45">
-        <f>COUNTIFS(Stories!$T$4:$T$63,1,Stories!$D$4:$D$63,5)</f>
+        <f>COUNTIFS(Stories!$W$4:$W$63,1,Stories!$D$4:$D$63,5)</f>
         <v/>
       </c>
       <c r="I8" s="46" t="n"/>
       <c r="J8" s="46" t="n"/>
       <c r="K8" s="47">
-        <f>COUNTIFS(Stories!$T$4:$T$63,1,Stories!$E$4:$E$63,"Feature lead")</f>
+        <f>COUNTIFS(Stories!$W$4:$W$63,1,Stories!$E$4:$E$63,"Feature lead")</f>
         <v/>
       </c>
       <c r="L8" s="48" t="n"/>
       <c r="M8" s="48" t="n"/>
       <c r="N8" s="49">
-        <f>COUNTIFS(Stories!$T$4:$T$63,1,Stories!$F$4:$F$63,"Shortlisted")+COUNTIFS(Stories!$T$4:$T$63,1,Stories!$F$4:$F$63,"Commissioned")+COUNTIFS(Stories!$T$4:$T$63,1,Stories!$F$4:$F$63,"Published")</f>
+        <f>COUNTIFS(Stories!$W$4:$W$63,1,Stories!$F$4:$F$63,"Shortlisted")+COUNTIFS(Stories!$W$4:$W$63,1,Stories!$F$4:$F$63,"Commissioned")+COUNTIFS(Stories!$W$4:$W$63,1,Stories!$F$4:$F$63,"Published")</f>
         <v/>
       </c>
       <c r="O8" s="50" t="n"/>
@@ -4349,19 +4412,19 @@
       <c r="F10" s="56" t="n"/>
       <c r="G10" s="56" t="n"/>
       <c r="H10" s="67">
-        <f>"rated 4 / 5: "&amp;COUNTIFS(Stories!$T$4:$T$63,1,Stories!$D$4:$D$63,4)</f>
+        <f>"rated 4 / 5: "&amp;COUNTIFS(Stories!$W$4:$W$63,1,Stories!$D$4:$D$63,4)</f>
         <v/>
       </c>
       <c r="I10" s="58" t="n"/>
       <c r="J10" s="58" t="n"/>
       <c r="K10" s="68">
-        <f>"news briefs: "&amp;COUNTIFS(Stories!$T$4:$T$63,1,Stories!$E$4:$E$63,"News brief")</f>
+        <f>"news briefs: "&amp;COUNTIFS(Stories!$W$4:$W$63,1,Stories!$E$4:$E$63,"News brief")</f>
         <v/>
       </c>
       <c r="L10" s="60" t="n"/>
       <c r="M10" s="60" t="n"/>
       <c r="N10" s="69">
-        <f>"shortlisted or later · to review: "&amp;COUNTIFS(Stories!$T$4:$T$63,1,Stories!$F$4:$F$63,"To review")</f>
+        <f>"shortlisted or later · to review: "&amp;COUNTIFS(Stories!$W$4:$W$63,1,Stories!$F$4:$F$63,"To review")</f>
         <v/>
       </c>
       <c r="O10" s="62" t="n"/>
@@ -4992,19 +5055,19 @@
       <c r="D28" s="93" t="n"/>
       <c r="E28" s="93" t="n"/>
       <c r="F28" s="94">
-        <f>SUMPRODUCT(Stories!$T$4:$T$63,--(Stories!$C$4:$C$63=$B28))</f>
+        <f>SUMPRODUCT(Stories!$W$4:$W$63,--(Stories!$C$4:$C$63=$B28))</f>
         <v/>
       </c>
       <c r="G28" s="95">
-        <f>SUMPRODUCT(Stories!$T$4:$T$63,--(Stories!$C$4:$C$63=$B28),--(Stories!$D$4:$D$63=5))</f>
+        <f>SUMPRODUCT(Stories!$W$4:$W$63,--(Stories!$C$4:$C$63=$B28),--(Stories!$D$4:$D$63=5))</f>
         <v/>
       </c>
       <c r="H28" s="95">
-        <f>SUMPRODUCT(Stories!$T$4:$T$63,--(Stories!$C$4:$C$63=$B28),--(Stories!$D$4:$D$63=4))</f>
+        <f>SUMPRODUCT(Stories!$W$4:$W$63,--(Stories!$C$4:$C$63=$B28),--(Stories!$D$4:$D$63=4))</f>
         <v/>
       </c>
       <c r="I28" s="95">
-        <f>SUMPRODUCT(Stories!$T$4:$T$63,--(Stories!$C$4:$C$63=$B28),--(Stories!$E$4:$E$63="Feature lead"))</f>
+        <f>SUMPRODUCT(Stories!$W$4:$W$63,--(Stories!$C$4:$C$63=$B28),--(Stories!$E$4:$E$63="Feature lead"))</f>
         <v/>
       </c>
       <c r="J28" s="96">
@@ -5022,19 +5085,19 @@
       <c r="D29" s="98" t="n"/>
       <c r="E29" s="98" t="n"/>
       <c r="F29" s="94">
-        <f>SUMPRODUCT(Stories!$T$4:$T$63,--(Stories!$C$4:$C$63=$B29))</f>
+        <f>SUMPRODUCT(Stories!$W$4:$W$63,--(Stories!$C$4:$C$63=$B29))</f>
         <v/>
       </c>
       <c r="G29" s="95">
-        <f>SUMPRODUCT(Stories!$T$4:$T$63,--(Stories!$C$4:$C$63=$B29),--(Stories!$D$4:$D$63=5))</f>
+        <f>SUMPRODUCT(Stories!$W$4:$W$63,--(Stories!$C$4:$C$63=$B29),--(Stories!$D$4:$D$63=5))</f>
         <v/>
       </c>
       <c r="H29" s="95">
-        <f>SUMPRODUCT(Stories!$T$4:$T$63,--(Stories!$C$4:$C$63=$B29),--(Stories!$D$4:$D$63=4))</f>
+        <f>SUMPRODUCT(Stories!$W$4:$W$63,--(Stories!$C$4:$C$63=$B29),--(Stories!$D$4:$D$63=4))</f>
         <v/>
       </c>
       <c r="I29" s="95">
-        <f>SUMPRODUCT(Stories!$T$4:$T$63,--(Stories!$C$4:$C$63=$B29),--(Stories!$E$4:$E$63="Feature lead"))</f>
+        <f>SUMPRODUCT(Stories!$W$4:$W$63,--(Stories!$C$4:$C$63=$B29),--(Stories!$E$4:$E$63="Feature lead"))</f>
         <v/>
       </c>
       <c r="J29" s="96">
@@ -5052,19 +5115,19 @@
       <c r="D30" s="100" t="n"/>
       <c r="E30" s="100" t="n"/>
       <c r="F30" s="94">
-        <f>SUMPRODUCT(Stories!$T$4:$T$63,--(Stories!$C$4:$C$63=$B30))</f>
+        <f>SUMPRODUCT(Stories!$W$4:$W$63,--(Stories!$C$4:$C$63=$B30))</f>
         <v/>
       </c>
       <c r="G30" s="95">
-        <f>SUMPRODUCT(Stories!$T$4:$T$63,--(Stories!$C$4:$C$63=$B30),--(Stories!$D$4:$D$63=5))</f>
+        <f>SUMPRODUCT(Stories!$W$4:$W$63,--(Stories!$C$4:$C$63=$B30),--(Stories!$D$4:$D$63=5))</f>
         <v/>
       </c>
       <c r="H30" s="95">
-        <f>SUMPRODUCT(Stories!$T$4:$T$63,--(Stories!$C$4:$C$63=$B30),--(Stories!$D$4:$D$63=4))</f>
+        <f>SUMPRODUCT(Stories!$W$4:$W$63,--(Stories!$C$4:$C$63=$B30),--(Stories!$D$4:$D$63=4))</f>
         <v/>
       </c>
       <c r="I30" s="95">
-        <f>SUMPRODUCT(Stories!$T$4:$T$63,--(Stories!$C$4:$C$63=$B30),--(Stories!$E$4:$E$63="Feature lead"))</f>
+        <f>SUMPRODUCT(Stories!$W$4:$W$63,--(Stories!$C$4:$C$63=$B30),--(Stories!$E$4:$E$63="Feature lead"))</f>
         <v/>
       </c>
       <c r="J30" s="96">
@@ -5082,19 +5145,19 @@
       <c r="D31" s="102" t="n"/>
       <c r="E31" s="102" t="n"/>
       <c r="F31" s="94">
-        <f>SUMPRODUCT(Stories!$T$4:$T$63,--(Stories!$C$4:$C$63=$B31))</f>
+        <f>SUMPRODUCT(Stories!$W$4:$W$63,--(Stories!$C$4:$C$63=$B31))</f>
         <v/>
       </c>
       <c r="G31" s="95">
-        <f>SUMPRODUCT(Stories!$T$4:$T$63,--(Stories!$C$4:$C$63=$B31),--(Stories!$D$4:$D$63=5))</f>
+        <f>SUMPRODUCT(Stories!$W$4:$W$63,--(Stories!$C$4:$C$63=$B31),--(Stories!$D$4:$D$63=5))</f>
         <v/>
       </c>
       <c r="H31" s="95">
-        <f>SUMPRODUCT(Stories!$T$4:$T$63,--(Stories!$C$4:$C$63=$B31),--(Stories!$D$4:$D$63=4))</f>
+        <f>SUMPRODUCT(Stories!$W$4:$W$63,--(Stories!$C$4:$C$63=$B31),--(Stories!$D$4:$D$63=4))</f>
         <v/>
       </c>
       <c r="I31" s="95">
-        <f>SUMPRODUCT(Stories!$T$4:$T$63,--(Stories!$C$4:$C$63=$B31),--(Stories!$E$4:$E$63="Feature lead"))</f>
+        <f>SUMPRODUCT(Stories!$W$4:$W$63,--(Stories!$C$4:$C$63=$B31),--(Stories!$E$4:$E$63="Feature lead"))</f>
         <v/>
       </c>
       <c r="J31" s="96">
@@ -5112,19 +5175,19 @@
       <c r="D32" s="104" t="n"/>
       <c r="E32" s="104" t="n"/>
       <c r="F32" s="94">
-        <f>SUMPRODUCT(Stories!$T$4:$T$63,--(Stories!$C$4:$C$63=$B32))</f>
+        <f>SUMPRODUCT(Stories!$W$4:$W$63,--(Stories!$C$4:$C$63=$B32))</f>
         <v/>
       </c>
       <c r="G32" s="95">
-        <f>SUMPRODUCT(Stories!$T$4:$T$63,--(Stories!$C$4:$C$63=$B32),--(Stories!$D$4:$D$63=5))</f>
+        <f>SUMPRODUCT(Stories!$W$4:$W$63,--(Stories!$C$4:$C$63=$B32),--(Stories!$D$4:$D$63=5))</f>
         <v/>
       </c>
       <c r="H32" s="95">
-        <f>SUMPRODUCT(Stories!$T$4:$T$63,--(Stories!$C$4:$C$63=$B32),--(Stories!$D$4:$D$63=4))</f>
+        <f>SUMPRODUCT(Stories!$W$4:$W$63,--(Stories!$C$4:$C$63=$B32),--(Stories!$D$4:$D$63=4))</f>
         <v/>
       </c>
       <c r="I32" s="95">
-        <f>SUMPRODUCT(Stories!$T$4:$T$63,--(Stories!$C$4:$C$63=$B32),--(Stories!$E$4:$E$63="Feature lead"))</f>
+        <f>SUMPRODUCT(Stories!$W$4:$W$63,--(Stories!$C$4:$C$63=$B32),--(Stories!$E$4:$E$63="Feature lead"))</f>
         <v/>
       </c>
       <c r="J32" s="96">
@@ -5142,19 +5205,19 @@
       <c r="D33" s="106" t="n"/>
       <c r="E33" s="106" t="n"/>
       <c r="F33" s="94">
-        <f>SUMPRODUCT(Stories!$T$4:$T$63,--(Stories!$C$4:$C$63=$B33))</f>
+        <f>SUMPRODUCT(Stories!$W$4:$W$63,--(Stories!$C$4:$C$63=$B33))</f>
         <v/>
       </c>
       <c r="G33" s="95">
-        <f>SUMPRODUCT(Stories!$T$4:$T$63,--(Stories!$C$4:$C$63=$B33),--(Stories!$D$4:$D$63=5))</f>
+        <f>SUMPRODUCT(Stories!$W$4:$W$63,--(Stories!$C$4:$C$63=$B33),--(Stories!$D$4:$D$63=5))</f>
         <v/>
       </c>
       <c r="H33" s="95">
-        <f>SUMPRODUCT(Stories!$T$4:$T$63,--(Stories!$C$4:$C$63=$B33),--(Stories!$D$4:$D$63=4))</f>
+        <f>SUMPRODUCT(Stories!$W$4:$W$63,--(Stories!$C$4:$C$63=$B33),--(Stories!$D$4:$D$63=4))</f>
         <v/>
       </c>
       <c r="I33" s="95">
-        <f>SUMPRODUCT(Stories!$T$4:$T$63,--(Stories!$C$4:$C$63=$B33),--(Stories!$E$4:$E$63="Feature lead"))</f>
+        <f>SUMPRODUCT(Stories!$W$4:$W$63,--(Stories!$C$4:$C$63=$B33),--(Stories!$E$4:$E$63="Feature lead"))</f>
         <v/>
       </c>
       <c r="J33" s="96">
@@ -5172,19 +5235,19 @@
       <c r="D34" s="108" t="n"/>
       <c r="E34" s="108" t="n"/>
       <c r="F34" s="94">
-        <f>SUMPRODUCT(Stories!$T$4:$T$63,--(Stories!$C$4:$C$63=$B34))</f>
+        <f>SUMPRODUCT(Stories!$W$4:$W$63,--(Stories!$C$4:$C$63=$B34))</f>
         <v/>
       </c>
       <c r="G34" s="95">
-        <f>SUMPRODUCT(Stories!$T$4:$T$63,--(Stories!$C$4:$C$63=$B34),--(Stories!$D$4:$D$63=5))</f>
+        <f>SUMPRODUCT(Stories!$W$4:$W$63,--(Stories!$C$4:$C$63=$B34),--(Stories!$D$4:$D$63=5))</f>
         <v/>
       </c>
       <c r="H34" s="95">
-        <f>SUMPRODUCT(Stories!$T$4:$T$63,--(Stories!$C$4:$C$63=$B34),--(Stories!$D$4:$D$63=4))</f>
+        <f>SUMPRODUCT(Stories!$W$4:$W$63,--(Stories!$C$4:$C$63=$B34),--(Stories!$D$4:$D$63=4))</f>
         <v/>
       </c>
       <c r="I34" s="95">
-        <f>SUMPRODUCT(Stories!$T$4:$T$63,--(Stories!$C$4:$C$63=$B34),--(Stories!$E$4:$E$63="Feature lead"))</f>
+        <f>SUMPRODUCT(Stories!$W$4:$W$63,--(Stories!$C$4:$C$63=$B34),--(Stories!$E$4:$E$63="Feature lead"))</f>
         <v/>
       </c>
       <c r="J34" s="96">
@@ -5202,19 +5265,19 @@
       <c r="D35" s="110" t="n"/>
       <c r="E35" s="110" t="n"/>
       <c r="F35" s="94">
-        <f>SUMPRODUCT(Stories!$T$4:$T$63,--(Stories!$C$4:$C$63=$B35))</f>
+        <f>SUMPRODUCT(Stories!$W$4:$W$63,--(Stories!$C$4:$C$63=$B35))</f>
         <v/>
       </c>
       <c r="G35" s="95">
-        <f>SUMPRODUCT(Stories!$T$4:$T$63,--(Stories!$C$4:$C$63=$B35),--(Stories!$D$4:$D$63=5))</f>
+        <f>SUMPRODUCT(Stories!$W$4:$W$63,--(Stories!$C$4:$C$63=$B35),--(Stories!$D$4:$D$63=5))</f>
         <v/>
       </c>
       <c r="H35" s="95">
-        <f>SUMPRODUCT(Stories!$T$4:$T$63,--(Stories!$C$4:$C$63=$B35),--(Stories!$D$4:$D$63=4))</f>
+        <f>SUMPRODUCT(Stories!$W$4:$W$63,--(Stories!$C$4:$C$63=$B35),--(Stories!$D$4:$D$63=4))</f>
         <v/>
       </c>
       <c r="I35" s="95">
-        <f>SUMPRODUCT(Stories!$T$4:$T$63,--(Stories!$C$4:$C$63=$B35),--(Stories!$E$4:$E$63="Feature lead"))</f>
+        <f>SUMPRODUCT(Stories!$W$4:$W$63,--(Stories!$C$4:$C$63=$B35),--(Stories!$E$4:$E$63="Feature lead"))</f>
         <v/>
       </c>
       <c r="J35" s="96">
@@ -5232,19 +5295,19 @@
       <c r="D36" s="112" t="n"/>
       <c r="E36" s="112" t="n"/>
       <c r="F36" s="94">
-        <f>SUMPRODUCT(Stories!$T$4:$T$63,--(Stories!$C$4:$C$63=$B36))</f>
+        <f>SUMPRODUCT(Stories!$W$4:$W$63,--(Stories!$C$4:$C$63=$B36))</f>
         <v/>
       </c>
       <c r="G36" s="95">
-        <f>SUMPRODUCT(Stories!$T$4:$T$63,--(Stories!$C$4:$C$63=$B36),--(Stories!$D$4:$D$63=5))</f>
+        <f>SUMPRODUCT(Stories!$W$4:$W$63,--(Stories!$C$4:$C$63=$B36),--(Stories!$D$4:$D$63=5))</f>
         <v/>
       </c>
       <c r="H36" s="95">
-        <f>SUMPRODUCT(Stories!$T$4:$T$63,--(Stories!$C$4:$C$63=$B36),--(Stories!$D$4:$D$63=4))</f>
+        <f>SUMPRODUCT(Stories!$W$4:$W$63,--(Stories!$C$4:$C$63=$B36),--(Stories!$D$4:$D$63=4))</f>
         <v/>
       </c>
       <c r="I36" s="95">
-        <f>SUMPRODUCT(Stories!$T$4:$T$63,--(Stories!$C$4:$C$63=$B36),--(Stories!$E$4:$E$63="Feature lead"))</f>
+        <f>SUMPRODUCT(Stories!$W$4:$W$63,--(Stories!$C$4:$C$63=$B36),--(Stories!$E$4:$E$63="Feature lead"))</f>
         <v/>
       </c>
       <c r="J36" s="96">
@@ -5344,7 +5407,7 @@
       <c r="C40" s="11" t="n"/>
       <c r="D40" s="11" t="n"/>
       <c r="E40" s="94">
-        <f>SUMPRODUCT(Stories!$T$4:$T$63,--(Stories!$E$4:$E$63=$B40))</f>
+        <f>SUMPRODUCT(Stories!$W$4:$W$63,--(Stories!$E$4:$E$63=$B40))</f>
         <v/>
       </c>
       <c r="F40" s="96">
@@ -5359,7 +5422,7 @@
       <c r="I40" s="11" t="n"/>
       <c r="J40" s="11" t="n"/>
       <c r="K40" s="94">
-        <f>COUNTIFS(Stories!$T$4:$T$63,1,Stories!$D$4:$D$63,5)</f>
+        <f>COUNTIFS(Stories!$W$4:$W$63,1,Stories!$D$4:$D$63,5)</f>
         <v/>
       </c>
       <c r="L40" s="96">
@@ -5374,7 +5437,7 @@
       <c r="O40" s="116" t="n"/>
       <c r="P40" s="116" t="n"/>
       <c r="Q40" s="94">
-        <f>COUNTIFS(Stories!$T$4:$T$63,1,Stories!$F$4:$F$63,"To review")</f>
+        <f>COUNTIFS(Stories!$W$4:$W$63,1,Stories!$F$4:$F$63,"To review")</f>
         <v/>
       </c>
       <c r="R40" s="96">
@@ -5391,7 +5454,7 @@
       <c r="C41" s="11" t="n"/>
       <c r="D41" s="11" t="n"/>
       <c r="E41" s="94">
-        <f>SUMPRODUCT(Stories!$T$4:$T$63,--(Stories!$E$4:$E$63=$B41))</f>
+        <f>SUMPRODUCT(Stories!$W$4:$W$63,--(Stories!$E$4:$E$63=$B41))</f>
         <v/>
       </c>
       <c r="F41" s="96">
@@ -5406,7 +5469,7 @@
       <c r="I41" s="11" t="n"/>
       <c r="J41" s="11" t="n"/>
       <c r="K41" s="94">
-        <f>COUNTIFS(Stories!$T$4:$T$63,1,Stories!$D$4:$D$63,4)</f>
+        <f>COUNTIFS(Stories!$W$4:$W$63,1,Stories!$D$4:$D$63,4)</f>
         <v/>
       </c>
       <c r="L41" s="96">
@@ -5421,7 +5484,7 @@
       <c r="O41" s="120" t="n"/>
       <c r="P41" s="120" t="n"/>
       <c r="Q41" s="94">
-        <f>COUNTIFS(Stories!$T$4:$T$63,1,Stories!$F$4:$F$63,"Shortlisted")</f>
+        <f>COUNTIFS(Stories!$W$4:$W$63,1,Stories!$F$4:$F$63,"Shortlisted")</f>
         <v/>
       </c>
       <c r="R41" s="96">
@@ -5438,7 +5501,7 @@
       <c r="C42" s="11" t="n"/>
       <c r="D42" s="11" t="n"/>
       <c r="E42" s="94">
-        <f>SUMPRODUCT(Stories!$T$4:$T$63,--(Stories!$E$4:$E$63=$B42))</f>
+        <f>SUMPRODUCT(Stories!$W$4:$W$63,--(Stories!$E$4:$E$63=$B42))</f>
         <v/>
       </c>
       <c r="F42" s="96">
@@ -5453,7 +5516,7 @@
       <c r="I42" s="11" t="n"/>
       <c r="J42" s="11" t="n"/>
       <c r="K42" s="94">
-        <f>COUNTIFS(Stories!$T$4:$T$63,1,Stories!$D$4:$D$63,3)</f>
+        <f>COUNTIFS(Stories!$W$4:$W$63,1,Stories!$D$4:$D$63,3)</f>
         <v/>
       </c>
       <c r="L42" s="96">
@@ -5468,7 +5531,7 @@
       <c r="O42" s="124" t="n"/>
       <c r="P42" s="124" t="n"/>
       <c r="Q42" s="94">
-        <f>COUNTIFS(Stories!$T$4:$T$63,1,Stories!$F$4:$F$63,"Commissioned")</f>
+        <f>COUNTIFS(Stories!$W$4:$W$63,1,Stories!$F$4:$F$63,"Commissioned")</f>
         <v/>
       </c>
       <c r="R42" s="96">
@@ -5485,7 +5548,7 @@
       <c r="C43" s="11" t="n"/>
       <c r="D43" s="11" t="n"/>
       <c r="E43" s="94">
-        <f>SUMPRODUCT(Stories!$T$4:$T$63,--(Stories!$E$4:$E$63=$B43))</f>
+        <f>SUMPRODUCT(Stories!$W$4:$W$63,--(Stories!$E$4:$E$63=$B43))</f>
         <v/>
       </c>
       <c r="F43" s="96">
@@ -5500,7 +5563,7 @@
       <c r="O43" s="127" t="n"/>
       <c r="P43" s="127" t="n"/>
       <c r="Q43" s="94">
-        <f>COUNTIFS(Stories!$T$4:$T$63,1,Stories!$F$4:$F$63,"Published")</f>
+        <f>COUNTIFS(Stories!$W$4:$W$63,1,Stories!$F$4:$F$63,"Published")</f>
         <v/>
       </c>
       <c r="R43" s="96">
@@ -5517,7 +5580,7 @@
       <c r="C44" s="11" t="n"/>
       <c r="D44" s="11" t="n"/>
       <c r="E44" s="94">
-        <f>SUMPRODUCT(Stories!$T$4:$T$63,--(Stories!$E$4:$E$63=$B44))</f>
+        <f>SUMPRODUCT(Stories!$W$4:$W$63,--(Stories!$E$4:$E$63=$B44))</f>
         <v/>
       </c>
       <c r="F44" s="96">
@@ -5532,7 +5595,7 @@
       <c r="O44" s="130" t="n"/>
       <c r="P44" s="130" t="n"/>
       <c r="Q44" s="94">
-        <f>COUNTIFS(Stories!$T$4:$T$63,1,Stories!$F$4:$F$63,"Not used")</f>
+        <f>COUNTIFS(Stories!$W$4:$W$63,1,Stories!$F$4:$F$63,"Not used")</f>
         <v/>
       </c>
       <c r="R44" s="96">
@@ -5620,23 +5683,23 @@
       <c r="D61" s="132" t="n"/>
       <c r="E61" s="132" t="n"/>
       <c r="F61" s="133">
-        <f>SUMPRODUCT(Stories!$T$4:$T$63,--(Stories!$C$4:$C$63=$B61),--(Stories!$E$4:$E$63=F$60))</f>
+        <f>SUMPRODUCT(Stories!$W$4:$W$63,--(Stories!$C$4:$C$63=$B61),--(Stories!$E$4:$E$63=F$60))</f>
         <v/>
       </c>
       <c r="G61" s="133">
-        <f>SUMPRODUCT(Stories!$T$4:$T$63,--(Stories!$C$4:$C$63=$B61),--(Stories!$E$4:$E$63=G$60))</f>
+        <f>SUMPRODUCT(Stories!$W$4:$W$63,--(Stories!$C$4:$C$63=$B61),--(Stories!$E$4:$E$63=G$60))</f>
         <v/>
       </c>
       <c r="H61" s="133">
-        <f>SUMPRODUCT(Stories!$T$4:$T$63,--(Stories!$C$4:$C$63=$B61),--(Stories!$E$4:$E$63=H$60))</f>
+        <f>SUMPRODUCT(Stories!$W$4:$W$63,--(Stories!$C$4:$C$63=$B61),--(Stories!$E$4:$E$63=H$60))</f>
         <v/>
       </c>
       <c r="I61" s="133">
-        <f>SUMPRODUCT(Stories!$T$4:$T$63,--(Stories!$C$4:$C$63=$B61),--(Stories!$E$4:$E$63=I$60))</f>
+        <f>SUMPRODUCT(Stories!$W$4:$W$63,--(Stories!$C$4:$C$63=$B61),--(Stories!$E$4:$E$63=I$60))</f>
         <v/>
       </c>
       <c r="J61" s="133">
-        <f>SUMPRODUCT(Stories!$T$4:$T$63,--(Stories!$C$4:$C$63=$B61),--(Stories!$E$4:$E$63=J$60))</f>
+        <f>SUMPRODUCT(Stories!$W$4:$W$63,--(Stories!$C$4:$C$63=$B61),--(Stories!$E$4:$E$63=J$60))</f>
         <v/>
       </c>
       <c r="K61" s="94">
@@ -5654,23 +5717,23 @@
       <c r="D62" s="135" t="n"/>
       <c r="E62" s="135" t="n"/>
       <c r="F62" s="133">
-        <f>SUMPRODUCT(Stories!$T$4:$T$63,--(Stories!$C$4:$C$63=$B62),--(Stories!$E$4:$E$63=F$60))</f>
+        <f>SUMPRODUCT(Stories!$W$4:$W$63,--(Stories!$C$4:$C$63=$B62),--(Stories!$E$4:$E$63=F$60))</f>
         <v/>
       </c>
       <c r="G62" s="133">
-        <f>SUMPRODUCT(Stories!$T$4:$T$63,--(Stories!$C$4:$C$63=$B62),--(Stories!$E$4:$E$63=G$60))</f>
+        <f>SUMPRODUCT(Stories!$W$4:$W$63,--(Stories!$C$4:$C$63=$B62),--(Stories!$E$4:$E$63=G$60))</f>
         <v/>
       </c>
       <c r="H62" s="133">
-        <f>SUMPRODUCT(Stories!$T$4:$T$63,--(Stories!$C$4:$C$63=$B62),--(Stories!$E$4:$E$63=H$60))</f>
+        <f>SUMPRODUCT(Stories!$W$4:$W$63,--(Stories!$C$4:$C$63=$B62),--(Stories!$E$4:$E$63=H$60))</f>
         <v/>
       </c>
       <c r="I62" s="133">
-        <f>SUMPRODUCT(Stories!$T$4:$T$63,--(Stories!$C$4:$C$63=$B62),--(Stories!$E$4:$E$63=I$60))</f>
+        <f>SUMPRODUCT(Stories!$W$4:$W$63,--(Stories!$C$4:$C$63=$B62),--(Stories!$E$4:$E$63=I$60))</f>
         <v/>
       </c>
       <c r="J62" s="133">
-        <f>SUMPRODUCT(Stories!$T$4:$T$63,--(Stories!$C$4:$C$63=$B62),--(Stories!$E$4:$E$63=J$60))</f>
+        <f>SUMPRODUCT(Stories!$W$4:$W$63,--(Stories!$C$4:$C$63=$B62),--(Stories!$E$4:$E$63=J$60))</f>
         <v/>
       </c>
       <c r="K62" s="94">
@@ -5688,23 +5751,23 @@
       <c r="D63" s="137" t="n"/>
       <c r="E63" s="137" t="n"/>
       <c r="F63" s="133">
-        <f>SUMPRODUCT(Stories!$T$4:$T$63,--(Stories!$C$4:$C$63=$B63),--(Stories!$E$4:$E$63=F$60))</f>
+        <f>SUMPRODUCT(Stories!$W$4:$W$63,--(Stories!$C$4:$C$63=$B63),--(Stories!$E$4:$E$63=F$60))</f>
         <v/>
       </c>
       <c r="G63" s="133">
-        <f>SUMPRODUCT(Stories!$T$4:$T$63,--(Stories!$C$4:$C$63=$B63),--(Stories!$E$4:$E$63=G$60))</f>
+        <f>SUMPRODUCT(Stories!$W$4:$W$63,--(Stories!$C$4:$C$63=$B63),--(Stories!$E$4:$E$63=G$60))</f>
         <v/>
       </c>
       <c r="H63" s="133">
-        <f>SUMPRODUCT(Stories!$T$4:$T$63,--(Stories!$C$4:$C$63=$B63),--(Stories!$E$4:$E$63=H$60))</f>
+        <f>SUMPRODUCT(Stories!$W$4:$W$63,--(Stories!$C$4:$C$63=$B63),--(Stories!$E$4:$E$63=H$60))</f>
         <v/>
       </c>
       <c r="I63" s="133">
-        <f>SUMPRODUCT(Stories!$T$4:$T$63,--(Stories!$C$4:$C$63=$B63),--(Stories!$E$4:$E$63=I$60))</f>
+        <f>SUMPRODUCT(Stories!$W$4:$W$63,--(Stories!$C$4:$C$63=$B63),--(Stories!$E$4:$E$63=I$60))</f>
         <v/>
       </c>
       <c r="J63" s="133">
-        <f>SUMPRODUCT(Stories!$T$4:$T$63,--(Stories!$C$4:$C$63=$B63),--(Stories!$E$4:$E$63=J$60))</f>
+        <f>SUMPRODUCT(Stories!$W$4:$W$63,--(Stories!$C$4:$C$63=$B63),--(Stories!$E$4:$E$63=J$60))</f>
         <v/>
       </c>
       <c r="K63" s="94">
@@ -5722,23 +5785,23 @@
       <c r="D64" s="139" t="n"/>
       <c r="E64" s="139" t="n"/>
       <c r="F64" s="133">
-        <f>SUMPRODUCT(Stories!$T$4:$T$63,--(Stories!$C$4:$C$63=$B64),--(Stories!$E$4:$E$63=F$60))</f>
+        <f>SUMPRODUCT(Stories!$W$4:$W$63,--(Stories!$C$4:$C$63=$B64),--(Stories!$E$4:$E$63=F$60))</f>
         <v/>
       </c>
       <c r="G64" s="133">
-        <f>SUMPRODUCT(Stories!$T$4:$T$63,--(Stories!$C$4:$C$63=$B64),--(Stories!$E$4:$E$63=G$60))</f>
+        <f>SUMPRODUCT(Stories!$W$4:$W$63,--(Stories!$C$4:$C$63=$B64),--(Stories!$E$4:$E$63=G$60))</f>
         <v/>
       </c>
       <c r="H64" s="133">
-        <f>SUMPRODUCT(Stories!$T$4:$T$63,--(Stories!$C$4:$C$63=$B64),--(Stories!$E$4:$E$63=H$60))</f>
+        <f>SUMPRODUCT(Stories!$W$4:$W$63,--(Stories!$C$4:$C$63=$B64),--(Stories!$E$4:$E$63=H$60))</f>
         <v/>
       </c>
       <c r="I64" s="133">
-        <f>SUMPRODUCT(Stories!$T$4:$T$63,--(Stories!$C$4:$C$63=$B64),--(Stories!$E$4:$E$63=I$60))</f>
+        <f>SUMPRODUCT(Stories!$W$4:$W$63,--(Stories!$C$4:$C$63=$B64),--(Stories!$E$4:$E$63=I$60))</f>
         <v/>
       </c>
       <c r="J64" s="133">
-        <f>SUMPRODUCT(Stories!$T$4:$T$63,--(Stories!$C$4:$C$63=$B64),--(Stories!$E$4:$E$63=J$60))</f>
+        <f>SUMPRODUCT(Stories!$W$4:$W$63,--(Stories!$C$4:$C$63=$B64),--(Stories!$E$4:$E$63=J$60))</f>
         <v/>
       </c>
       <c r="K64" s="94">
@@ -5756,23 +5819,23 @@
       <c r="D65" s="141" t="n"/>
       <c r="E65" s="141" t="n"/>
       <c r="F65" s="133">
-        <f>SUMPRODUCT(Stories!$T$4:$T$63,--(Stories!$C$4:$C$63=$B65),--(Stories!$E$4:$E$63=F$60))</f>
+        <f>SUMPRODUCT(Stories!$W$4:$W$63,--(Stories!$C$4:$C$63=$B65),--(Stories!$E$4:$E$63=F$60))</f>
         <v/>
       </c>
       <c r="G65" s="133">
-        <f>SUMPRODUCT(Stories!$T$4:$T$63,--(Stories!$C$4:$C$63=$B65),--(Stories!$E$4:$E$63=G$60))</f>
+        <f>SUMPRODUCT(Stories!$W$4:$W$63,--(Stories!$C$4:$C$63=$B65),--(Stories!$E$4:$E$63=G$60))</f>
         <v/>
       </c>
       <c r="H65" s="133">
-        <f>SUMPRODUCT(Stories!$T$4:$T$63,--(Stories!$C$4:$C$63=$B65),--(Stories!$E$4:$E$63=H$60))</f>
+        <f>SUMPRODUCT(Stories!$W$4:$W$63,--(Stories!$C$4:$C$63=$B65),--(Stories!$E$4:$E$63=H$60))</f>
         <v/>
       </c>
       <c r="I65" s="133">
-        <f>SUMPRODUCT(Stories!$T$4:$T$63,--(Stories!$C$4:$C$63=$B65),--(Stories!$E$4:$E$63=I$60))</f>
+        <f>SUMPRODUCT(Stories!$W$4:$W$63,--(Stories!$C$4:$C$63=$B65),--(Stories!$E$4:$E$63=I$60))</f>
         <v/>
       </c>
       <c r="J65" s="133">
-        <f>SUMPRODUCT(Stories!$T$4:$T$63,--(Stories!$C$4:$C$63=$B65),--(Stories!$E$4:$E$63=J$60))</f>
+        <f>SUMPRODUCT(Stories!$W$4:$W$63,--(Stories!$C$4:$C$63=$B65),--(Stories!$E$4:$E$63=J$60))</f>
         <v/>
       </c>
       <c r="K65" s="94">
@@ -5790,23 +5853,23 @@
       <c r="D66" s="143" t="n"/>
       <c r="E66" s="143" t="n"/>
       <c r="F66" s="133">
-        <f>SUMPRODUCT(Stories!$T$4:$T$63,--(Stories!$C$4:$C$63=$B66),--(Stories!$E$4:$E$63=F$60))</f>
+        <f>SUMPRODUCT(Stories!$W$4:$W$63,--(Stories!$C$4:$C$63=$B66),--(Stories!$E$4:$E$63=F$60))</f>
         <v/>
       </c>
       <c r="G66" s="133">
-        <f>SUMPRODUCT(Stories!$T$4:$T$63,--(Stories!$C$4:$C$63=$B66),--(Stories!$E$4:$E$63=G$60))</f>
+        <f>SUMPRODUCT(Stories!$W$4:$W$63,--(Stories!$C$4:$C$63=$B66),--(Stories!$E$4:$E$63=G$60))</f>
         <v/>
       </c>
       <c r="H66" s="133">
-        <f>SUMPRODUCT(Stories!$T$4:$T$63,--(Stories!$C$4:$C$63=$B66),--(Stories!$E$4:$E$63=H$60))</f>
+        <f>SUMPRODUCT(Stories!$W$4:$W$63,--(Stories!$C$4:$C$63=$B66),--(Stories!$E$4:$E$63=H$60))</f>
         <v/>
       </c>
       <c r="I66" s="133">
-        <f>SUMPRODUCT(Stories!$T$4:$T$63,--(Stories!$C$4:$C$63=$B66),--(Stories!$E$4:$E$63=I$60))</f>
+        <f>SUMPRODUCT(Stories!$W$4:$W$63,--(Stories!$C$4:$C$63=$B66),--(Stories!$E$4:$E$63=I$60))</f>
         <v/>
       </c>
       <c r="J66" s="133">
-        <f>SUMPRODUCT(Stories!$T$4:$T$63,--(Stories!$C$4:$C$63=$B66),--(Stories!$E$4:$E$63=J$60))</f>
+        <f>SUMPRODUCT(Stories!$W$4:$W$63,--(Stories!$C$4:$C$63=$B66),--(Stories!$E$4:$E$63=J$60))</f>
         <v/>
       </c>
       <c r="K66" s="94">
@@ -5824,23 +5887,23 @@
       <c r="D67" s="145" t="n"/>
       <c r="E67" s="145" t="n"/>
       <c r="F67" s="133">
-        <f>SUMPRODUCT(Stories!$T$4:$T$63,--(Stories!$C$4:$C$63=$B67),--(Stories!$E$4:$E$63=F$60))</f>
+        <f>SUMPRODUCT(Stories!$W$4:$W$63,--(Stories!$C$4:$C$63=$B67),--(Stories!$E$4:$E$63=F$60))</f>
         <v/>
       </c>
       <c r="G67" s="133">
-        <f>SUMPRODUCT(Stories!$T$4:$T$63,--(Stories!$C$4:$C$63=$B67),--(Stories!$E$4:$E$63=G$60))</f>
+        <f>SUMPRODUCT(Stories!$W$4:$W$63,--(Stories!$C$4:$C$63=$B67),--(Stories!$E$4:$E$63=G$60))</f>
         <v/>
       </c>
       <c r="H67" s="133">
-        <f>SUMPRODUCT(Stories!$T$4:$T$63,--(Stories!$C$4:$C$63=$B67),--(Stories!$E$4:$E$63=H$60))</f>
+        <f>SUMPRODUCT(Stories!$W$4:$W$63,--(Stories!$C$4:$C$63=$B67),--(Stories!$E$4:$E$63=H$60))</f>
         <v/>
       </c>
       <c r="I67" s="133">
-        <f>SUMPRODUCT(Stories!$T$4:$T$63,--(Stories!$C$4:$C$63=$B67),--(Stories!$E$4:$E$63=I$60))</f>
+        <f>SUMPRODUCT(Stories!$W$4:$W$63,--(Stories!$C$4:$C$63=$B67),--(Stories!$E$4:$E$63=I$60))</f>
         <v/>
       </c>
       <c r="J67" s="133">
-        <f>SUMPRODUCT(Stories!$T$4:$T$63,--(Stories!$C$4:$C$63=$B67),--(Stories!$E$4:$E$63=J$60))</f>
+        <f>SUMPRODUCT(Stories!$W$4:$W$63,--(Stories!$C$4:$C$63=$B67),--(Stories!$E$4:$E$63=J$60))</f>
         <v/>
       </c>
       <c r="K67" s="94">
@@ -5858,23 +5921,23 @@
       <c r="D68" s="147" t="n"/>
       <c r="E68" s="147" t="n"/>
       <c r="F68" s="133">
-        <f>SUMPRODUCT(Stories!$T$4:$T$63,--(Stories!$C$4:$C$63=$B68),--(Stories!$E$4:$E$63=F$60))</f>
+        <f>SUMPRODUCT(Stories!$W$4:$W$63,--(Stories!$C$4:$C$63=$B68),--(Stories!$E$4:$E$63=F$60))</f>
         <v/>
       </c>
       <c r="G68" s="133">
-        <f>SUMPRODUCT(Stories!$T$4:$T$63,--(Stories!$C$4:$C$63=$B68),--(Stories!$E$4:$E$63=G$60))</f>
+        <f>SUMPRODUCT(Stories!$W$4:$W$63,--(Stories!$C$4:$C$63=$B68),--(Stories!$E$4:$E$63=G$60))</f>
         <v/>
       </c>
       <c r="H68" s="133">
-        <f>SUMPRODUCT(Stories!$T$4:$T$63,--(Stories!$C$4:$C$63=$B68),--(Stories!$E$4:$E$63=H$60))</f>
+        <f>SUMPRODUCT(Stories!$W$4:$W$63,--(Stories!$C$4:$C$63=$B68),--(Stories!$E$4:$E$63=H$60))</f>
         <v/>
       </c>
       <c r="I68" s="133">
-        <f>SUMPRODUCT(Stories!$T$4:$T$63,--(Stories!$C$4:$C$63=$B68),--(Stories!$E$4:$E$63=I$60))</f>
+        <f>SUMPRODUCT(Stories!$W$4:$W$63,--(Stories!$C$4:$C$63=$B68),--(Stories!$E$4:$E$63=I$60))</f>
         <v/>
       </c>
       <c r="J68" s="133">
-        <f>SUMPRODUCT(Stories!$T$4:$T$63,--(Stories!$C$4:$C$63=$B68),--(Stories!$E$4:$E$63=J$60))</f>
+        <f>SUMPRODUCT(Stories!$W$4:$W$63,--(Stories!$C$4:$C$63=$B68),--(Stories!$E$4:$E$63=J$60))</f>
         <v/>
       </c>
       <c r="K68" s="94">
@@ -5892,23 +5955,23 @@
       <c r="D69" s="149" t="n"/>
       <c r="E69" s="149" t="n"/>
       <c r="F69" s="133">
-        <f>SUMPRODUCT(Stories!$T$4:$T$63,--(Stories!$C$4:$C$63=$B69),--(Stories!$E$4:$E$63=F$60))</f>
+        <f>SUMPRODUCT(Stories!$W$4:$W$63,--(Stories!$C$4:$C$63=$B69),--(Stories!$E$4:$E$63=F$60))</f>
         <v/>
       </c>
       <c r="G69" s="133">
-        <f>SUMPRODUCT(Stories!$T$4:$T$63,--(Stories!$C$4:$C$63=$B69),--(Stories!$E$4:$E$63=G$60))</f>
+        <f>SUMPRODUCT(Stories!$W$4:$W$63,--(Stories!$C$4:$C$63=$B69),--(Stories!$E$4:$E$63=G$60))</f>
         <v/>
       </c>
       <c r="H69" s="133">
-        <f>SUMPRODUCT(Stories!$T$4:$T$63,--(Stories!$C$4:$C$63=$B69),--(Stories!$E$4:$E$63=H$60))</f>
+        <f>SUMPRODUCT(Stories!$W$4:$W$63,--(Stories!$C$4:$C$63=$B69),--(Stories!$E$4:$E$63=H$60))</f>
         <v/>
       </c>
       <c r="I69" s="133">
-        <f>SUMPRODUCT(Stories!$T$4:$T$63,--(Stories!$C$4:$C$63=$B69),--(Stories!$E$4:$E$63=I$60))</f>
+        <f>SUMPRODUCT(Stories!$W$4:$W$63,--(Stories!$C$4:$C$63=$B69),--(Stories!$E$4:$E$63=I$60))</f>
         <v/>
       </c>
       <c r="J69" s="133">
-        <f>SUMPRODUCT(Stories!$T$4:$T$63,--(Stories!$C$4:$C$63=$B69),--(Stories!$E$4:$E$63=J$60))</f>
+        <f>SUMPRODUCT(Stories!$W$4:$W$63,--(Stories!$C$4:$C$63=$B69),--(Stories!$E$4:$E$63=J$60))</f>
         <v/>
       </c>
       <c r="K69" s="94">
@@ -5975,7 +6038,7 @@
         <v>60</v>
       </c>
       <c r="G74" s="94">
-        <f>COUNTIFS(Stories!$T$4:$T$63,1,Stories!$P$4:$P$63,"2026-Q4")</f>
+        <f>COUNTIFS(Stories!$W$4:$W$63,1,Stories!$S$4:$S$63,"2026-Q4")</f>
         <v/>
       </c>
     </row>
@@ -6228,7 +6291,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:U63"/>
+  <dimension ref="A1:X63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -6244,14 +6307,17 @@
     <col width="12" customWidth="1" min="11" max="11"/>
     <col width="38" customWidth="1" min="12" max="12"/>
     <col width="40" customWidth="1" min="13" max="13"/>
-    <col width="15" customWidth="1" min="14" max="14"/>
-    <col width="12" customWidth="1" min="15" max="15"/>
-    <col width="11" customWidth="1" min="16" max="16"/>
-    <col width="26" customWidth="1" min="17" max="17"/>
-    <col width="9" customWidth="1" min="18" max="18"/>
-    <col width="30" customWidth="1" min="19" max="19"/>
-    <col width="12" customWidth="1" min="20" max="20"/>
-    <col hidden="1" width="12" customWidth="1" min="21" max="21"/>
+    <col width="16" customWidth="1" min="14" max="14"/>
+    <col width="22" customWidth="1" min="15" max="15"/>
+    <col width="36" customWidth="1" min="16" max="16"/>
+    <col width="15" customWidth="1" min="17" max="17"/>
+    <col width="12" customWidth="1" min="18" max="18"/>
+    <col width="11" customWidth="1" min="19" max="19"/>
+    <col width="26" customWidth="1" min="20" max="20"/>
+    <col width="9" customWidth="1" min="21" max="21"/>
+    <col width="30" customWidth="1" min="22" max="22"/>
+    <col width="12" customWidth="1" min="23" max="23"/>
+    <col hidden="1" width="12" customWidth="1" min="24" max="24"/>
   </cols>
   <sheetData>
     <row r="1" ht="26" customHeight="1">
@@ -6351,40 +6417,55 @@
       </c>
       <c r="N3" s="156" t="inlineStr">
         <is>
+          <t>Country</t>
+        </is>
+      </c>
+      <c r="O3" s="156" t="inlineStr">
+        <is>
+          <t>Place</t>
+        </is>
+      </c>
+      <c r="P3" s="156" t="inlineStr">
+        <is>
+          <t>Developing story</t>
+        </is>
+      </c>
+      <c r="Q3" s="156" t="inlineStr">
+        <is>
           <t>Google News edition</t>
         </is>
       </c>
-      <c r="O3" s="155" t="inlineStr">
+      <c r="R3" s="155" t="inlineStr">
         <is>
           <t>Published</t>
         </is>
       </c>
-      <c r="P3" s="155" t="inlineStr">
+      <c r="S3" s="155" t="inlineStr">
         <is>
           <t>Issue window</t>
         </is>
       </c>
-      <c r="Q3" s="156" t="inlineStr">
+      <c r="T3" s="156" t="inlineStr">
         <is>
           <t>Keywords</t>
         </is>
       </c>
-      <c r="R3" s="155" t="inlineStr">
+      <c r="U3" s="155" t="inlineStr">
         <is>
           <t>Keyword score</t>
         </is>
       </c>
-      <c r="S3" s="156" t="inlineStr">
+      <c r="V3" s="156" t="inlineStr">
         <is>
           <t>Article URL</t>
         </is>
       </c>
-      <c r="T3" s="155" t="inlineStr">
+      <c r="W3" s="155" t="inlineStr">
         <is>
           <t>In Dashboard selection</t>
         </is>
       </c>
-      <c r="U3" s="155" t="inlineStr">
+      <c r="X3" s="155" t="inlineStr">
         <is>
           <t>Top-10 key (helper)</t>
         </is>
@@ -6434,38 +6515,41 @@
       </c>
       <c r="L4" s="166" t="n"/>
       <c r="M4" s="168" t="n"/>
-      <c r="N4" s="169" t="inlineStr">
+      <c r="N4" s="169" t="n"/>
+      <c r="O4" s="166" t="n"/>
+      <c r="P4" s="166" t="n"/>
+      <c r="Q4" s="170" t="inlineStr">
         <is>
           <t>United States</t>
         </is>
       </c>
-      <c r="O4" s="167" t="n">
+      <c r="R4" s="167" t="n">
         <v>46318</v>
       </c>
-      <c r="P4" s="170" t="inlineStr">
+      <c r="S4" s="169" t="inlineStr">
         <is>
           <t>2026-Q4</t>
         </is>
       </c>
-      <c r="Q4" s="171" t="inlineStr">
+      <c r="T4" s="171" t="inlineStr">
         <is>
           <t>pile, shaft</t>
         </is>
       </c>
-      <c r="R4" s="158" t="n">
+      <c r="U4" s="158" t="n">
         <v>7</v>
       </c>
-      <c r="S4" s="172" t="inlineStr">
+      <c r="V4" s="172" t="inlineStr">
         <is>
           <t>https://news.google.com/rss/articles/CBMiowFBVV95cUxNbDZHMUZRd0NyUDliQlNXWEZ4bUdaWFJJbk1NRHZIdUlpRzFObmV2bzBkUVpKbzhuUmkxZHI1U0JENHktOGIxOGlvbEtwS3RScWJ0SWhGR0gtNU9lWWNSc1RoMmtsWjJIT3F2ZzByazhRVUViN2FLa3RqSGt5VkxKZUM3WjdrT2NGc2tYeWJWQmR2RmxEZzlYUmczNFBjMlpXVVNB?oc=5</t>
         </is>
       </c>
-      <c r="T4" s="173">
-        <f>IF($B4="",0,IF(AND(OR(OR(Dashboard!$B$5="All themes",Dashboard!$B$5=""),$C4=Dashboard!$B$5),OR(OR(Dashboard!$G$5="All uses",Dashboard!$G$5=""),$E4=Dashboard!$G$5),N($D4)&gt;=Lists!$H$2,OR(OR(Dashboard!$N$5="All windows",Dashboard!$N$5=""),$P4=Dashboard!$N$5)),1,0))</f>
-        <v/>
-      </c>
-      <c r="U4" s="174">
-        <f>IF($T4=1,N($D4)*1E14+MIN(MAX(N($R4),0),9999)*1E10+MIN(N($K4),99999)*1E5+99999-MIN(ROW(),99999),"")</f>
+      <c r="W4" s="173">
+        <f>IF($B4="",0,IF(AND(OR(OR(Dashboard!$B$5="All themes",Dashboard!$B$5=""),$C4=Dashboard!$B$5),OR(OR(Dashboard!$G$5="All uses",Dashboard!$G$5=""),$E4=Dashboard!$G$5),N($D4)&gt;=Lists!$H$2,OR(OR(Dashboard!$N$5="All windows",Dashboard!$N$5=""),$S4=Dashboard!$N$5)),1,0))</f>
+        <v/>
+      </c>
+      <c r="X4" s="174">
+        <f>IF($W4=1,N($D4)*1E14+MIN(MAX(N($U4),0),9999)*1E10+MIN(N($K4),99999)*1E5+99999-MIN(ROW(),99999),"")</f>
         <v/>
       </c>
     </row>
@@ -6518,33 +6602,36 @@
         </is>
       </c>
       <c r="N5" s="169" t="n"/>
-      <c r="O5" s="167" t="n">
+      <c r="O5" s="166" t="n"/>
+      <c r="P5" s="166" t="n"/>
+      <c r="Q5" s="170" t="n"/>
+      <c r="R5" s="167" t="n">
         <v>46318</v>
       </c>
-      <c r="P5" s="170" t="inlineStr">
+      <c r="S5" s="169" t="inlineStr">
         <is>
           <t>2026-Q4</t>
         </is>
       </c>
-      <c r="Q5" s="171" t="inlineStr">
+      <c r="T5" s="171" t="inlineStr">
         <is>
           <t>offshore wind</t>
         </is>
       </c>
-      <c r="R5" s="158" t="n">
+      <c r="U5" s="158" t="n">
         <v>6</v>
       </c>
-      <c r="S5" s="172" t="inlineStr">
+      <c r="V5" s="172" t="inlineStr">
         <is>
           <t>https://www.geplus.co.uk/key-topics/sustainability/floating-wind-needs-grounded-solutions-23-10-2026/</t>
         </is>
       </c>
-      <c r="T5" s="173">
-        <f>IF($B5="",0,IF(AND(OR(OR(Dashboard!$B$5="All themes",Dashboard!$B$5=""),$C5=Dashboard!$B$5),OR(OR(Dashboard!$G$5="All uses",Dashboard!$G$5=""),$E5=Dashboard!$G$5),N($D5)&gt;=Lists!$H$2,OR(OR(Dashboard!$N$5="All windows",Dashboard!$N$5=""),$P5=Dashboard!$N$5)),1,0))</f>
-        <v/>
-      </c>
-      <c r="U5" s="174">
-        <f>IF($T5=1,N($D5)*1E14+MIN(MAX(N($R5),0),9999)*1E10+MIN(N($K5),99999)*1E5+99999-MIN(ROW(),99999),"")</f>
+      <c r="W5" s="173">
+        <f>IF($B5="",0,IF(AND(OR(OR(Dashboard!$B$5="All themes",Dashboard!$B$5=""),$C5=Dashboard!$B$5),OR(OR(Dashboard!$G$5="All uses",Dashboard!$G$5=""),$E5=Dashboard!$G$5),N($D5)&gt;=Lists!$H$2,OR(OR(Dashboard!$N$5="All windows",Dashboard!$N$5=""),$S5=Dashboard!$N$5)),1,0))</f>
+        <v/>
+      </c>
+      <c r="X5" s="174">
+        <f>IF($W5=1,N($D5)*1E14+MIN(MAX(N($U5),0),9999)*1E10+MIN(N($K5),99999)*1E5+99999-MIN(ROW(),99999),"")</f>
         <v/>
       </c>
     </row>
@@ -6596,38 +6683,41 @@
         </is>
       </c>
       <c r="M6" s="168" t="n"/>
-      <c r="N6" s="169" t="inlineStr">
+      <c r="N6" s="169" t="n"/>
+      <c r="O6" s="166" t="n"/>
+      <c r="P6" s="166" t="n"/>
+      <c r="Q6" s="170" t="inlineStr">
         <is>
           <t>South Korea</t>
         </is>
       </c>
-      <c r="O6" s="167" t="n">
+      <c r="R6" s="167" t="n">
         <v>46317</v>
       </c>
-      <c r="P6" s="170" t="inlineStr">
+      <c r="S6" s="169" t="inlineStr">
         <is>
           <t>2026-Q4</t>
         </is>
       </c>
-      <c r="Q6" s="171" t="inlineStr">
+      <c r="T6" s="171" t="inlineStr">
         <is>
           <t>sinkhole, excavation</t>
         </is>
       </c>
-      <c r="R6" s="158" t="n">
+      <c r="U6" s="158" t="n">
         <v>6</v>
       </c>
-      <c r="S6" s="172" t="inlineStr">
+      <c r="V6" s="172" t="inlineStr">
         <is>
           <t>https://news.google.com/rss/articles/CBMibkFVX3lxTE9HOUMyWW5vRXVWOG5ZemlXOFFsQWYwVl9lRW53VTV1MVFFQUF4eGgwWTRKQ0p5RGlWLUgzdUNUSW9aQXRRMkduTGFBVmhOVWluT19OLXU5REgzMVdVOUwtTVRmY3Y5WGdwaE9RcG9B0gFuQVVfeXFMT0c5QzJZbm9FdVY4bll6aVc4UWxBZjBWX2VFbndVNXUxUUVBQXh4aDBZNEpDSnlEaVYtSDN1Q1RJb1pBdFEyR25MYUFWaE5VaW5PX04tdTlESDMxV1U5TC1NVGZjdjlYZ3BoT1Fwb0E?oc=5</t>
         </is>
       </c>
-      <c r="T6" s="173">
-        <f>IF($B6="",0,IF(AND(OR(OR(Dashboard!$B$5="All themes",Dashboard!$B$5=""),$C6=Dashboard!$B$5),OR(OR(Dashboard!$G$5="All uses",Dashboard!$G$5=""),$E6=Dashboard!$G$5),N($D6)&gt;=Lists!$H$2,OR(OR(Dashboard!$N$5="All windows",Dashboard!$N$5=""),$P6=Dashboard!$N$5)),1,0))</f>
-        <v/>
-      </c>
-      <c r="U6" s="174">
-        <f>IF($T6=1,N($D6)*1E14+MIN(MAX(N($R6),0),9999)*1E10+MIN(N($K6),99999)*1E5+99999-MIN(ROW(),99999),"")</f>
+      <c r="W6" s="173">
+        <f>IF($B6="",0,IF(AND(OR(OR(Dashboard!$B$5="All themes",Dashboard!$B$5=""),$C6=Dashboard!$B$5),OR(OR(Dashboard!$G$5="All uses",Dashboard!$G$5=""),$E6=Dashboard!$G$5),N($D6)&gt;=Lists!$H$2,OR(OR(Dashboard!$N$5="All windows",Dashboard!$N$5=""),$S6=Dashboard!$N$5)),1,0))</f>
+        <v/>
+      </c>
+      <c r="X6" s="174">
+        <f>IF($W6=1,N($D6)*1E14+MIN(MAX(N($U6),0),9999)*1E10+MIN(N($K6),99999)*1E5+99999-MIN(ROW(),99999),"")</f>
         <v/>
       </c>
     </row>
@@ -6679,38 +6769,41 @@
         </is>
       </c>
       <c r="M7" s="168" t="n"/>
-      <c r="N7" s="169" t="inlineStr">
+      <c r="N7" s="169" t="n"/>
+      <c r="O7" s="166" t="n"/>
+      <c r="P7" s="166" t="n"/>
+      <c r="Q7" s="170" t="inlineStr">
         <is>
           <t>Senegal</t>
         </is>
       </c>
-      <c r="O7" s="167" t="n">
-        <v>46319</v>
-      </c>
-      <c r="P7" s="170" t="inlineStr">
+      <c r="R7" s="167" t="n">
+        <v>46319</v>
+      </c>
+      <c r="S7" s="169" t="inlineStr">
         <is>
           <t>2026-Q4</t>
         </is>
       </c>
-      <c r="Q7" s="171" t="inlineStr">
+      <c r="T7" s="171" t="inlineStr">
         <is>
           <t>foundation</t>
         </is>
       </c>
-      <c r="R7" s="158" t="n">
+      <c r="U7" s="158" t="n">
         <v>2</v>
       </c>
-      <c r="S7" s="172" t="inlineStr">
+      <c r="V7" s="172" t="inlineStr">
         <is>
           <t>https://news.google.com/rss/articles/CBMiiAJBVV95cUxPQkl0dnN1WVR0endSWTZuYVpjZTBnV2VWTnVTVjdyb1NJTlFKVjJWY21lS0dPZzFrSkdlSlI2VU5Cc1NMQ0VHNTlPWUFkSVRZWEhWbFRxaU91bXRRMTF6LW9kYWVKSHFBOUptTVZuTGdTX1lZYzBDQkZ5QTJGUmVXcVd3c3lmU01zM3Zjd1VmZ183aFkxOERqQWJHbVlqMU5EbzBRSWpHRjNMeFVHRXlVSURpZHFnRXZIX1Q0X3RSMW8zcVZKVFZoOWViVlYzVnNWZloxTW5LNThJTWV2bURLSjJ1eEZiRFhnd2phLVVjUV9mdHVjN0Q0dE93WE9wRVR1ZlFFTE8tNnk?oc=5</t>
         </is>
       </c>
-      <c r="T7" s="173">
-        <f>IF($B7="",0,IF(AND(OR(OR(Dashboard!$B$5="All themes",Dashboard!$B$5=""),$C7=Dashboard!$B$5),OR(OR(Dashboard!$G$5="All uses",Dashboard!$G$5=""),$E7=Dashboard!$G$5),N($D7)&gt;=Lists!$H$2,OR(OR(Dashboard!$N$5="All windows",Dashboard!$N$5=""),$P7=Dashboard!$N$5)),1,0))</f>
-        <v/>
-      </c>
-      <c r="U7" s="174">
-        <f>IF($T7=1,N($D7)*1E14+MIN(MAX(N($R7),0),9999)*1E10+MIN(N($K7),99999)*1E5+99999-MIN(ROW(),99999),"")</f>
+      <c r="W7" s="173">
+        <f>IF($B7="",0,IF(AND(OR(OR(Dashboard!$B$5="All themes",Dashboard!$B$5=""),$C7=Dashboard!$B$5),OR(OR(Dashboard!$G$5="All uses",Dashboard!$G$5=""),$E7=Dashboard!$G$5),N($D7)&gt;=Lists!$H$2,OR(OR(Dashboard!$N$5="All windows",Dashboard!$N$5=""),$S7=Dashboard!$N$5)),1,0))</f>
+        <v/>
+      </c>
+      <c r="X7" s="174">
+        <f>IF($W7=1,N($D7)*1E14+MIN(MAX(N($U7),0),9999)*1E10+MIN(N($K7),99999)*1E5+99999-MIN(ROW(),99999),"")</f>
         <v/>
       </c>
     </row>
@@ -6762,34 +6855,37 @@
         </is>
       </c>
       <c r="M8" s="168" t="n"/>
-      <c r="N8" s="169" t="inlineStr">
+      <c r="N8" s="169" t="n"/>
+      <c r="O8" s="166" t="n"/>
+      <c r="P8" s="166" t="n"/>
+      <c r="Q8" s="170" t="inlineStr">
         <is>
           <t>Vietnam</t>
         </is>
       </c>
-      <c r="O8" s="167" t="n">
+      <c r="R8" s="167" t="n">
         <v>46317</v>
       </c>
-      <c r="P8" s="170" t="inlineStr">
+      <c r="S8" s="169" t="inlineStr">
         <is>
           <t>2026-Q4</t>
         </is>
       </c>
-      <c r="Q8" s="171" t="n"/>
-      <c r="R8" s="158" t="n">
+      <c r="T8" s="171" t="n"/>
+      <c r="U8" s="158" t="n">
         <v>0</v>
       </c>
-      <c r="S8" s="172" t="inlineStr">
+      <c r="V8" s="172" t="inlineStr">
         <is>
           <t>https://news.google.com/rss/articles/CBMic0FVX3lxTE1zSGZTbjJtMlg2SGZxUUtTSjJMZVdlSUkxSjZBeEV1WExBUUh4ZjdOZWIzcGRHczE1dVZiOWgyQUxTdkZWOEJfM0Y1dk1mcGpKekl0dGR4VE1YRVhoYTFjV09IZGQ3dUNQcl9BSlN0QzhUSkE?oc=5</t>
         </is>
       </c>
-      <c r="T8" s="173">
-        <f>IF($B8="",0,IF(AND(OR(OR(Dashboard!$B$5="All themes",Dashboard!$B$5=""),$C8=Dashboard!$B$5),OR(OR(Dashboard!$G$5="All uses",Dashboard!$G$5=""),$E8=Dashboard!$G$5),N($D8)&gt;=Lists!$H$2,OR(OR(Dashboard!$N$5="All windows",Dashboard!$N$5=""),$P8=Dashboard!$N$5)),1,0))</f>
-        <v/>
-      </c>
-      <c r="U8" s="174">
-        <f>IF($T8=1,N($D8)*1E14+MIN(MAX(N($R8),0),9999)*1E10+MIN(N($K8),99999)*1E5+99999-MIN(ROW(),99999),"")</f>
+      <c r="W8" s="173">
+        <f>IF($B8="",0,IF(AND(OR(OR(Dashboard!$B$5="All themes",Dashboard!$B$5=""),$C8=Dashboard!$B$5),OR(OR(Dashboard!$G$5="All uses",Dashboard!$G$5=""),$E8=Dashboard!$G$5),N($D8)&gt;=Lists!$H$2,OR(OR(Dashboard!$N$5="All windows",Dashboard!$N$5=""),$S8=Dashboard!$N$5)),1,0))</f>
+        <v/>
+      </c>
+      <c r="X8" s="174">
+        <f>IF($W8=1,N($D8)*1E14+MIN(MAX(N($U8),0),9999)*1E10+MIN(N($K8),99999)*1E5+99999-MIN(ROW(),99999),"")</f>
         <v/>
       </c>
     </row>
@@ -6841,34 +6937,37 @@
         </is>
       </c>
       <c r="M9" s="168" t="n"/>
-      <c r="N9" s="169" t="inlineStr">
+      <c r="N9" s="169" t="n"/>
+      <c r="O9" s="166" t="n"/>
+      <c r="P9" s="166" t="n"/>
+      <c r="Q9" s="170" t="inlineStr">
         <is>
           <t>China</t>
         </is>
       </c>
-      <c r="O9" s="167" t="n">
+      <c r="R9" s="167" t="n">
         <v>46318</v>
       </c>
-      <c r="P9" s="170" t="inlineStr">
+      <c r="S9" s="169" t="inlineStr">
         <is>
           <t>2026-Q4</t>
         </is>
       </c>
-      <c r="Q9" s="171" t="n"/>
-      <c r="R9" s="158" t="n">
+      <c r="T9" s="171" t="n"/>
+      <c r="U9" s="158" t="n">
         <v>0</v>
       </c>
-      <c r="S9" s="172" t="inlineStr">
+      <c r="V9" s="172" t="inlineStr">
         <is>
           <t>https://news.google.com/rss/articles/CBMibkFVX3lxTE8wdVhYVXYyQ3RwMHAtOTNnUkh5TnhCcEtVem9XenhDMFo2UVFHbWtIaGIzVHhLb1BFQmd2akRLZkFMd1pQNWJDRElESUY1SUdvLWFfd1ZaUW5tZ0ZFcmIxckZxbXg1Z1RrbXI5V0Zn?oc=5</t>
         </is>
       </c>
-      <c r="T9" s="173">
-        <f>IF($B9="",0,IF(AND(OR(OR(Dashboard!$B$5="All themes",Dashboard!$B$5=""),$C9=Dashboard!$B$5),OR(OR(Dashboard!$G$5="All uses",Dashboard!$G$5=""),$E9=Dashboard!$G$5),N($D9)&gt;=Lists!$H$2,OR(OR(Dashboard!$N$5="All windows",Dashboard!$N$5=""),$P9=Dashboard!$N$5)),1,0))</f>
-        <v/>
-      </c>
-      <c r="U9" s="174">
-        <f>IF($T9=1,N($D9)*1E14+MIN(MAX(N($R9),0),9999)*1E10+MIN(N($K9),99999)*1E5+99999-MIN(ROW(),99999),"")</f>
+      <c r="W9" s="173">
+        <f>IF($B9="",0,IF(AND(OR(OR(Dashboard!$B$5="All themes",Dashboard!$B$5=""),$C9=Dashboard!$B$5),OR(OR(Dashboard!$G$5="All uses",Dashboard!$G$5=""),$E9=Dashboard!$G$5),N($D9)&gt;=Lists!$H$2,OR(OR(Dashboard!$N$5="All windows",Dashboard!$N$5=""),$S9=Dashboard!$N$5)),1,0))</f>
+        <v/>
+      </c>
+      <c r="X9" s="174">
+        <f>IF($W9=1,N($D9)*1E14+MIN(MAX(N($U9),0),9999)*1E10+MIN(N($K9),99999)*1E5+99999-MIN(ROW(),99999),"")</f>
         <v/>
       </c>
     </row>
@@ -6921,33 +7020,36 @@
         </is>
       </c>
       <c r="N10" s="169" t="n"/>
-      <c r="O10" s="167" t="n">
+      <c r="O10" s="166" t="n"/>
+      <c r="P10" s="166" t="n"/>
+      <c r="Q10" s="170" t="n"/>
+      <c r="R10" s="167" t="n">
         <v>46318</v>
       </c>
-      <c r="P10" s="170" t="inlineStr">
+      <c r="S10" s="169" t="inlineStr">
         <is>
           <t>2026-Q4</t>
         </is>
       </c>
-      <c r="Q10" s="171" t="inlineStr">
+      <c r="T10" s="171" t="inlineStr">
         <is>
           <t>landslide, landslip, embankment</t>
         </is>
       </c>
-      <c r="R10" s="158" t="n">
+      <c r="U10" s="158" t="n">
         <v>14</v>
       </c>
-      <c r="S10" s="172" t="inlineStr">
+      <c r="V10" s="172" t="inlineStr">
         <is>
           <t>https://www.geplus.co.uk/news/project-news/m4-landslip-work-begins-as-part-of-wider-repair-programme-23-10-2026/</t>
         </is>
       </c>
-      <c r="T10" s="173">
-        <f>IF($B10="",0,IF(AND(OR(OR(Dashboard!$B$5="All themes",Dashboard!$B$5=""),$C10=Dashboard!$B$5),OR(OR(Dashboard!$G$5="All uses",Dashboard!$G$5=""),$E10=Dashboard!$G$5),N($D10)&gt;=Lists!$H$2,OR(OR(Dashboard!$N$5="All windows",Dashboard!$N$5=""),$P10=Dashboard!$N$5)),1,0))</f>
-        <v/>
-      </c>
-      <c r="U10" s="174">
-        <f>IF($T10=1,N($D10)*1E14+MIN(MAX(N($R10),0),9999)*1E10+MIN(N($K10),99999)*1E5+99999-MIN(ROW(),99999),"")</f>
+      <c r="W10" s="173">
+        <f>IF($B10="",0,IF(AND(OR(OR(Dashboard!$B$5="All themes",Dashboard!$B$5=""),$C10=Dashboard!$B$5),OR(OR(Dashboard!$G$5="All uses",Dashboard!$G$5=""),$E10=Dashboard!$G$5),N($D10)&gt;=Lists!$H$2,OR(OR(Dashboard!$N$5="All windows",Dashboard!$N$5=""),$S10=Dashboard!$N$5)),1,0))</f>
+        <v/>
+      </c>
+      <c r="X10" s="174">
+        <f>IF($W10=1,N($D10)*1E14+MIN(MAX(N($U10),0),9999)*1E10+MIN(N($K10),99999)*1E5+99999-MIN(ROW(),99999),"")</f>
         <v/>
       </c>
     </row>
@@ -6999,38 +7101,41 @@
         </is>
       </c>
       <c r="M11" s="168" t="n"/>
-      <c r="N11" s="169" t="inlineStr">
+      <c r="N11" s="169" t="n"/>
+      <c r="O11" s="166" t="n"/>
+      <c r="P11" s="166" t="n"/>
+      <c r="Q11" s="170" t="inlineStr">
         <is>
           <t>Indonesia</t>
         </is>
       </c>
-      <c r="O11" s="167" t="n">
+      <c r="R11" s="167" t="n">
         <v>46318</v>
       </c>
-      <c r="P11" s="170" t="inlineStr">
+      <c r="S11" s="169" t="inlineStr">
         <is>
           <t>2026-Q4</t>
         </is>
       </c>
-      <c r="Q11" s="171" t="inlineStr">
+      <c r="T11" s="171" t="inlineStr">
         <is>
           <t>landslide, embankment</t>
         </is>
       </c>
-      <c r="R11" s="158" t="n">
+      <c r="U11" s="158" t="n">
         <v>13</v>
       </c>
-      <c r="S11" s="172" t="inlineStr">
+      <c r="V11" s="172" t="inlineStr">
         <is>
           <t>https://news.google.com/rss/articles/CBMia0FVX3lxTE45UVhrbTdIV2NXaVloOTBleGdWeThGbHNoSTJtMTE3cFlfalpoYVBnUEFoUVRJQUp5Z2pVOEZvaGZzRUtjRWtOMzY3Wll0RHJOUTB6c0JYdGEzOXk2VXltZUFkc3RURDBUYUg4?oc=5</t>
         </is>
       </c>
-      <c r="T11" s="173">
-        <f>IF($B11="",0,IF(AND(OR(OR(Dashboard!$B$5="All themes",Dashboard!$B$5=""),$C11=Dashboard!$B$5),OR(OR(Dashboard!$G$5="All uses",Dashboard!$G$5=""),$E11=Dashboard!$G$5),N($D11)&gt;=Lists!$H$2,OR(OR(Dashboard!$N$5="All windows",Dashboard!$N$5=""),$P11=Dashboard!$N$5)),1,0))</f>
-        <v/>
-      </c>
-      <c r="U11" s="174">
-        <f>IF($T11=1,N($D11)*1E14+MIN(MAX(N($R11),0),9999)*1E10+MIN(N($K11),99999)*1E5+99999-MIN(ROW(),99999),"")</f>
+      <c r="W11" s="173">
+        <f>IF($B11="",0,IF(AND(OR(OR(Dashboard!$B$5="All themes",Dashboard!$B$5=""),$C11=Dashboard!$B$5),OR(OR(Dashboard!$G$5="All uses",Dashboard!$G$5=""),$E11=Dashboard!$G$5),N($D11)&gt;=Lists!$H$2,OR(OR(Dashboard!$N$5="All windows",Dashboard!$N$5=""),$S11=Dashboard!$N$5)),1,0))</f>
+        <v/>
+      </c>
+      <c r="X11" s="174">
+        <f>IF($W11=1,N($D11)*1E14+MIN(MAX(N($U11),0),9999)*1E10+MIN(N($K11),99999)*1E5+99999-MIN(ROW(),99999),"")</f>
         <v/>
       </c>
     </row>
@@ -7082,38 +7187,41 @@
         </is>
       </c>
       <c r="M12" s="168" t="n"/>
-      <c r="N12" s="169" t="inlineStr">
+      <c r="N12" s="169" t="n"/>
+      <c r="O12" s="166" t="n"/>
+      <c r="P12" s="166" t="n"/>
+      <c r="Q12" s="170" t="inlineStr">
         <is>
           <t>Italy</t>
         </is>
       </c>
-      <c r="O12" s="167" t="n">
+      <c r="R12" s="167" t="n">
         <v>46317</v>
       </c>
-      <c r="P12" s="170" t="inlineStr">
+      <c r="S12" s="169" t="inlineStr">
         <is>
           <t>2026-Q4</t>
         </is>
       </c>
-      <c r="Q12" s="171" t="inlineStr">
+      <c r="T12" s="171" t="inlineStr">
         <is>
           <t>landslide, collapse</t>
         </is>
       </c>
-      <c r="R12" s="158" t="n">
+      <c r="U12" s="158" t="n">
         <v>11</v>
       </c>
-      <c r="S12" s="172" t="inlineStr">
+      <c r="V12" s="172" t="inlineStr">
         <is>
           <t>https://news.google.com/rss/articles/CBMi7gFBVV95cUxQTGNab2ZBb3hvUXZRVXBCeDFRX2NqU0ZfeVdFZXgtbm5WZDl4aFd0eUdSYXdjNmotcS1ReUZhM1BBc2hITEpkQlpBTmlabzRycmN1ZkQwLVlDa3NzZWJuZXhnNC1jRXlkV1EybVFoQld3VlRaZ241ZkVMazRlZHB1NWplMjVpaWJtMHA3SHBZaEhhMHU0RE01Mk0taFU1OTBaTmg0U1lFYnI5cjhwaEZPUmd2ZTdTVHpxVjBfNk9mRFREOXNWNXJTM29OTnY3NHd0dGJYNVJoaHc4LWQxaUVOajhsaTdWU3dFbVd0ZUt3?oc=5</t>
         </is>
       </c>
-      <c r="T12" s="173">
-        <f>IF($B12="",0,IF(AND(OR(OR(Dashboard!$B$5="All themes",Dashboard!$B$5=""),$C12=Dashboard!$B$5),OR(OR(Dashboard!$G$5="All uses",Dashboard!$G$5=""),$E12=Dashboard!$G$5),N($D12)&gt;=Lists!$H$2,OR(OR(Dashboard!$N$5="All windows",Dashboard!$N$5=""),$P12=Dashboard!$N$5)),1,0))</f>
-        <v/>
-      </c>
-      <c r="U12" s="174">
-        <f>IF($T12=1,N($D12)*1E14+MIN(MAX(N($R12),0),9999)*1E10+MIN(N($K12),99999)*1E5+99999-MIN(ROW(),99999),"")</f>
+      <c r="W12" s="173">
+        <f>IF($B12="",0,IF(AND(OR(OR(Dashboard!$B$5="All themes",Dashboard!$B$5=""),$C12=Dashboard!$B$5),OR(OR(Dashboard!$G$5="All uses",Dashboard!$G$5=""),$E12=Dashboard!$G$5),N($D12)&gt;=Lists!$H$2,OR(OR(Dashboard!$N$5="All windows",Dashboard!$N$5=""),$S12=Dashboard!$N$5)),1,0))</f>
+        <v/>
+      </c>
+      <c r="X12" s="174">
+        <f>IF($W12=1,N($D12)*1E14+MIN(MAX(N($U12),0),9999)*1E10+MIN(N($K12),99999)*1E5+99999-MIN(ROW(),99999),"")</f>
         <v/>
       </c>
     </row>
@@ -7165,38 +7273,41 @@
         </is>
       </c>
       <c r="M13" s="168" t="n"/>
-      <c r="N13" s="169" t="inlineStr">
+      <c r="N13" s="169" t="n"/>
+      <c r="O13" s="166" t="n"/>
+      <c r="P13" s="166" t="n"/>
+      <c r="Q13" s="170" t="inlineStr">
         <is>
           <t>Spain</t>
         </is>
       </c>
-      <c r="O13" s="167" t="n">
-        <v>46319</v>
-      </c>
-      <c r="P13" s="170" t="inlineStr">
+      <c r="R13" s="167" t="n">
+        <v>46319</v>
+      </c>
+      <c r="S13" s="169" t="inlineStr">
         <is>
           <t>2026-Q4</t>
         </is>
       </c>
-      <c r="Q13" s="171" t="inlineStr">
+      <c r="T13" s="171" t="inlineStr">
         <is>
           <t>landslide</t>
         </is>
       </c>
-      <c r="R13" s="158" t="n">
+      <c r="U13" s="158" t="n">
         <v>10</v>
       </c>
-      <c r="S13" s="172" t="inlineStr">
+      <c r="V13" s="172" t="inlineStr">
         <is>
           <t>https://news.google.com/rss/articles/CBMiogFBVV95cUxQNGhpZmtjSDF5eDFZZEJXaTdIZWo2QVZTRDVlc3E0T2pvQ2tRaURBcHpRUk5hSmFDNjNuaGV5X1pHeVdqc2RjR1dOQVhPc2tUUVRmb2RiWnB0dWNDcU96QUxGcVg1dmNxRlpfdTNmT0Z5ZG4wSXNTSmR5OUY4ZmRZcW9kNmRHS0ZaVUxyMW9ySU5TSWJlNzJCWWJaZGlrRHd1a2c?oc=5</t>
         </is>
       </c>
-      <c r="T13" s="173">
-        <f>IF($B13="",0,IF(AND(OR(OR(Dashboard!$B$5="All themes",Dashboard!$B$5=""),$C13=Dashboard!$B$5),OR(OR(Dashboard!$G$5="All uses",Dashboard!$G$5=""),$E13=Dashboard!$G$5),N($D13)&gt;=Lists!$H$2,OR(OR(Dashboard!$N$5="All windows",Dashboard!$N$5=""),$P13=Dashboard!$N$5)),1,0))</f>
-        <v/>
-      </c>
-      <c r="U13" s="174">
-        <f>IF($T13=1,N($D13)*1E14+MIN(MAX(N($R13),0),9999)*1E10+MIN(N($K13),99999)*1E5+99999-MIN(ROW(),99999),"")</f>
+      <c r="W13" s="173">
+        <f>IF($B13="",0,IF(AND(OR(OR(Dashboard!$B$5="All themes",Dashboard!$B$5=""),$C13=Dashboard!$B$5),OR(OR(Dashboard!$G$5="All uses",Dashboard!$G$5=""),$E13=Dashboard!$G$5),N($D13)&gt;=Lists!$H$2,OR(OR(Dashboard!$N$5="All windows",Dashboard!$N$5=""),$S13=Dashboard!$N$5)),1,0))</f>
+        <v/>
+      </c>
+      <c r="X13" s="174">
+        <f>IF($W13=1,N($D13)*1E14+MIN(MAX(N($U13),0),9999)*1E10+MIN(N($K13),99999)*1E5+99999-MIN(ROW(),99999),"")</f>
         <v/>
       </c>
     </row>
@@ -7248,38 +7359,41 @@
         </is>
       </c>
       <c r="M14" s="168" t="n"/>
-      <c r="N14" s="169" t="inlineStr">
+      <c r="N14" s="169" t="n"/>
+      <c r="O14" s="166" t="n"/>
+      <c r="P14" s="166" t="n"/>
+      <c r="Q14" s="170" t="inlineStr">
         <is>
           <t>Italy</t>
         </is>
       </c>
-      <c r="O14" s="167" t="n">
-        <v>46319</v>
-      </c>
-      <c r="P14" s="170" t="inlineStr">
+      <c r="R14" s="167" t="n">
+        <v>46319</v>
+      </c>
+      <c r="S14" s="169" t="inlineStr">
         <is>
           <t>2026-Q4</t>
         </is>
       </c>
-      <c r="Q14" s="171" t="inlineStr">
+      <c r="T14" s="171" t="inlineStr">
         <is>
           <t>landslide</t>
         </is>
       </c>
-      <c r="R14" s="158" t="n">
+      <c r="U14" s="158" t="n">
         <v>10</v>
       </c>
-      <c r="S14" s="172" t="inlineStr">
+      <c r="V14" s="172" t="inlineStr">
         <is>
           <t>https://news.google.com/rss/articles/CBMizAFBVV95cUxOX19SY3ozdEtSRFpyZlE3a3o4LWtuMTdJeXVsZkVtZVJIaXJzbndtWVd2T21uQncydzJ1bmZONW1yVU9DVExhUFI5VmI3RkVHbjJqTjZWSXpjd1NLeDViOHZnLWo5ZV9oYVRNZi1KN3E3OERXVC1pdzlDVlBvY3pHZE1WRm9vR0E5VnNNdXN3SU9xbFVGRzY4UkstZUpkYTlMYjJobWoxTDRDNWVqYWdlR2taRV94RG9yaFJuUExrN1VCT2ZpTkFNQllycXo?oc=5</t>
         </is>
       </c>
-      <c r="T14" s="173">
-        <f>IF($B14="",0,IF(AND(OR(OR(Dashboard!$B$5="All themes",Dashboard!$B$5=""),$C14=Dashboard!$B$5),OR(OR(Dashboard!$G$5="All uses",Dashboard!$G$5=""),$E14=Dashboard!$G$5),N($D14)&gt;=Lists!$H$2,OR(OR(Dashboard!$N$5="All windows",Dashboard!$N$5=""),$P14=Dashboard!$N$5)),1,0))</f>
-        <v/>
-      </c>
-      <c r="U14" s="174">
-        <f>IF($T14=1,N($D14)*1E14+MIN(MAX(N($R14),0),9999)*1E10+MIN(N($K14),99999)*1E5+99999-MIN(ROW(),99999),"")</f>
+      <c r="W14" s="173">
+        <f>IF($B14="",0,IF(AND(OR(OR(Dashboard!$B$5="All themes",Dashboard!$B$5=""),$C14=Dashboard!$B$5),OR(OR(Dashboard!$G$5="All uses",Dashboard!$G$5=""),$E14=Dashboard!$G$5),N($D14)&gt;=Lists!$H$2,OR(OR(Dashboard!$N$5="All windows",Dashboard!$N$5=""),$S14=Dashboard!$N$5)),1,0))</f>
+        <v/>
+      </c>
+      <c r="X14" s="174">
+        <f>IF($W14=1,N($D14)*1E14+MIN(MAX(N($U14),0),9999)*1E10+MIN(N($K14),99999)*1E5+99999-MIN(ROW(),99999),"")</f>
         <v/>
       </c>
     </row>
@@ -7331,38 +7445,41 @@
         </is>
       </c>
       <c r="M15" s="168" t="n"/>
-      <c r="N15" s="169" t="inlineStr">
+      <c r="N15" s="169" t="n"/>
+      <c r="O15" s="166" t="n"/>
+      <c r="P15" s="166" t="n"/>
+      <c r="Q15" s="170" t="inlineStr">
         <is>
           <t>Italy</t>
         </is>
       </c>
-      <c r="O15" s="167" t="n">
-        <v>46319</v>
-      </c>
-      <c r="P15" s="170" t="inlineStr">
+      <c r="R15" s="167" t="n">
+        <v>46319</v>
+      </c>
+      <c r="S15" s="169" t="inlineStr">
         <is>
           <t>2026-Q4</t>
         </is>
       </c>
-      <c r="Q15" s="171" t="inlineStr">
+      <c r="T15" s="171" t="inlineStr">
         <is>
           <t>landslide</t>
         </is>
       </c>
-      <c r="R15" s="158" t="n">
+      <c r="U15" s="158" t="n">
         <v>10</v>
       </c>
-      <c r="S15" s="172" t="inlineStr">
+      <c r="V15" s="172" t="inlineStr">
         <is>
           <t>https://news.google.com/rss/articles/CBMipwFBVV95cUxQM0JfTHl5bmwxRmJ6Y3lLZ2l6XzB1c0lkclVfRzJ2clZEV29YU25kOWNsX1hXNjFuUnJnVGNjRXBFa0V2RWlYVllQOVEzV1ZCY3VYNENpdk9wSGVNNlUtNGVwdGZhZDY5UUVTYW1OZHQ1TkFoUURUTFMwSWdoLU90QTU2VE5Md1NKOU1Rd041aXFxNUJ1OGc3QTAxLUpGbndSWXh0czMzSQ?oc=5</t>
         </is>
       </c>
-      <c r="T15" s="173">
-        <f>IF($B15="",0,IF(AND(OR(OR(Dashboard!$B$5="All themes",Dashboard!$B$5=""),$C15=Dashboard!$B$5),OR(OR(Dashboard!$G$5="All uses",Dashboard!$G$5=""),$E15=Dashboard!$G$5),N($D15)&gt;=Lists!$H$2,OR(OR(Dashboard!$N$5="All windows",Dashboard!$N$5=""),$P15=Dashboard!$N$5)),1,0))</f>
-        <v/>
-      </c>
-      <c r="U15" s="174">
-        <f>IF($T15=1,N($D15)*1E14+MIN(MAX(N($R15),0),9999)*1E10+MIN(N($K15),99999)*1E5+99999-MIN(ROW(),99999),"")</f>
+      <c r="W15" s="173">
+        <f>IF($B15="",0,IF(AND(OR(OR(Dashboard!$B$5="All themes",Dashboard!$B$5=""),$C15=Dashboard!$B$5),OR(OR(Dashboard!$G$5="All uses",Dashboard!$G$5=""),$E15=Dashboard!$G$5),N($D15)&gt;=Lists!$H$2,OR(OR(Dashboard!$N$5="All windows",Dashboard!$N$5=""),$S15=Dashboard!$N$5)),1,0))</f>
+        <v/>
+      </c>
+      <c r="X15" s="174">
+        <f>IF($W15=1,N($D15)*1E14+MIN(MAX(N($U15),0),9999)*1E10+MIN(N($K15),99999)*1E5+99999-MIN(ROW(),99999),"")</f>
         <v/>
       </c>
     </row>
@@ -7410,38 +7527,41 @@
       </c>
       <c r="L16" s="166" t="n"/>
       <c r="M16" s="168" t="n"/>
-      <c r="N16" s="169" t="inlineStr">
+      <c r="N16" s="169" t="n"/>
+      <c r="O16" s="166" t="n"/>
+      <c r="P16" s="166" t="n"/>
+      <c r="Q16" s="170" t="inlineStr">
         <is>
           <t>Italy</t>
         </is>
       </c>
-      <c r="O16" s="167" t="n">
+      <c r="R16" s="167" t="n">
         <v>46318</v>
       </c>
-      <c r="P16" s="170" t="inlineStr">
+      <c r="S16" s="169" t="inlineStr">
         <is>
           <t>2026-Q4</t>
         </is>
       </c>
-      <c r="Q16" s="171" t="inlineStr">
+      <c r="T16" s="171" t="inlineStr">
         <is>
           <t>landslide</t>
         </is>
       </c>
-      <c r="R16" s="158" t="n">
+      <c r="U16" s="158" t="n">
         <v>10</v>
       </c>
-      <c r="S16" s="172" t="inlineStr">
+      <c r="V16" s="172" t="inlineStr">
         <is>
           <t>https://news.google.com/rss/articles/CBMirwFBVV95cUxPRkxsbl9ZdlM1cmloa1JxT3ZENFdkYUI5U3pIZy1UM005NU9SVVFIVjVmZ1ZvTDNybGJkMHAtc3Ewd3RldnRYWHlrSnQ2R1hXN2xpR1BNREFxTlRlb2tFMnFJZ01VSEZqN0ZheUtlbWJEd3h2SURJb3ppVWl6dTU2Y21zZGJGR1hpMWdNUmNfdWluZDJQYzZkeC1QTHhEUFNmcVhTVWtnWWxiUDczMmtr?oc=5</t>
         </is>
       </c>
-      <c r="T16" s="173">
-        <f>IF($B16="",0,IF(AND(OR(OR(Dashboard!$B$5="All themes",Dashboard!$B$5=""),$C16=Dashboard!$B$5),OR(OR(Dashboard!$G$5="All uses",Dashboard!$G$5=""),$E16=Dashboard!$G$5),N($D16)&gt;=Lists!$H$2,OR(OR(Dashboard!$N$5="All windows",Dashboard!$N$5=""),$P16=Dashboard!$N$5)),1,0))</f>
-        <v/>
-      </c>
-      <c r="U16" s="174">
-        <f>IF($T16=1,N($D16)*1E14+MIN(MAX(N($R16),0),9999)*1E10+MIN(N($K16),99999)*1E5+99999-MIN(ROW(),99999),"")</f>
+      <c r="W16" s="173">
+        <f>IF($B16="",0,IF(AND(OR(OR(Dashboard!$B$5="All themes",Dashboard!$B$5=""),$C16=Dashboard!$B$5),OR(OR(Dashboard!$G$5="All uses",Dashboard!$G$5=""),$E16=Dashboard!$G$5),N($D16)&gt;=Lists!$H$2,OR(OR(Dashboard!$N$5="All windows",Dashboard!$N$5=""),$S16=Dashboard!$N$5)),1,0))</f>
+        <v/>
+      </c>
+      <c r="X16" s="174">
+        <f>IF($W16=1,N($D16)*1E14+MIN(MAX(N($U16),0),9999)*1E10+MIN(N($K16),99999)*1E5+99999-MIN(ROW(),99999),"")</f>
         <v/>
       </c>
     </row>
@@ -7493,38 +7613,41 @@
         </is>
       </c>
       <c r="M17" s="168" t="n"/>
-      <c r="N17" s="169" t="inlineStr">
+      <c r="N17" s="169" t="n"/>
+      <c r="O17" s="166" t="n"/>
+      <c r="P17" s="166" t="n"/>
+      <c r="Q17" s="170" t="inlineStr">
         <is>
           <t>Indonesia</t>
         </is>
       </c>
-      <c r="O17" s="167" t="n">
-        <v>46319</v>
-      </c>
-      <c r="P17" s="170" t="inlineStr">
+      <c r="R17" s="167" t="n">
+        <v>46319</v>
+      </c>
+      <c r="S17" s="169" t="inlineStr">
         <is>
           <t>2026-Q4</t>
         </is>
       </c>
-      <c r="Q17" s="171" t="inlineStr">
+      <c r="T17" s="171" t="inlineStr">
         <is>
           <t>landslide</t>
         </is>
       </c>
-      <c r="R17" s="158" t="n">
+      <c r="U17" s="158" t="n">
         <v>10</v>
       </c>
-      <c r="S17" s="172" t="inlineStr">
+      <c r="V17" s="172" t="inlineStr">
         <is>
           <t>https://news.google.com/rss/articles/CBMiogFBVV95cUxOYkthemxCdGdtc1c3TnBBbGY4MVZlMDFvWnZiX3E4UERSQ1lsX2g4R0x5VHVaVndQdnJHQTBZSy02bV8wT1d4RVZ6WHRVN2w0UUx1MFRMbDhINzgtWlJJLXFKOHIzWFRZa1VmZUVFNUNCM3hRdE9GUGZpdVNQQnd3ZmxRTWZFOGU5REFvOTg4cG40YkU1bDhlZ2pQSkR5Ti04Q1E?oc=5</t>
         </is>
       </c>
-      <c r="T17" s="173">
-        <f>IF($B17="",0,IF(AND(OR(OR(Dashboard!$B$5="All themes",Dashboard!$B$5=""),$C17=Dashboard!$B$5),OR(OR(Dashboard!$G$5="All uses",Dashboard!$G$5=""),$E17=Dashboard!$G$5),N($D17)&gt;=Lists!$H$2,OR(OR(Dashboard!$N$5="All windows",Dashboard!$N$5=""),$P17=Dashboard!$N$5)),1,0))</f>
-        <v/>
-      </c>
-      <c r="U17" s="174">
-        <f>IF($T17=1,N($D17)*1E14+MIN(MAX(N($R17),0),9999)*1E10+MIN(N($K17),99999)*1E5+99999-MIN(ROW(),99999),"")</f>
+      <c r="W17" s="173">
+        <f>IF($B17="",0,IF(AND(OR(OR(Dashboard!$B$5="All themes",Dashboard!$B$5=""),$C17=Dashboard!$B$5),OR(OR(Dashboard!$G$5="All uses",Dashboard!$G$5=""),$E17=Dashboard!$G$5),N($D17)&gt;=Lists!$H$2,OR(OR(Dashboard!$N$5="All windows",Dashboard!$N$5=""),$S17=Dashboard!$N$5)),1,0))</f>
+        <v/>
+      </c>
+      <c r="X17" s="174">
+        <f>IF($W17=1,N($D17)*1E14+MIN(MAX(N($U17),0),9999)*1E10+MIN(N($K17),99999)*1E5+99999-MIN(ROW(),99999),"")</f>
         <v/>
       </c>
     </row>
@@ -7576,38 +7699,41 @@
         </is>
       </c>
       <c r="M18" s="168" t="n"/>
-      <c r="N18" s="169" t="inlineStr">
+      <c r="N18" s="169" t="n"/>
+      <c r="O18" s="166" t="n"/>
+      <c r="P18" s="166" t="n"/>
+      <c r="Q18" s="170" t="inlineStr">
         <is>
           <t>Chile</t>
         </is>
       </c>
-      <c r="O18" s="167" t="n">
+      <c r="R18" s="167" t="n">
         <v>46317</v>
       </c>
-      <c r="P18" s="170" t="inlineStr">
+      <c r="S18" s="169" t="inlineStr">
         <is>
           <t>2026-Q4</t>
         </is>
       </c>
-      <c r="Q18" s="171" t="inlineStr">
+      <c r="T18" s="171" t="inlineStr">
         <is>
           <t>landslide, debris flow</t>
         </is>
       </c>
-      <c r="R18" s="158" t="n">
+      <c r="U18" s="158" t="n">
         <v>8</v>
       </c>
-      <c r="S18" s="172" t="inlineStr">
+      <c r="V18" s="172" t="inlineStr">
         <is>
           <t>https://news.google.com/rss/articles/CBMi4wFBVV95cUxOV1p0dUF2OVZleURvUHhJbGxjNFdrR3hCalZqUEZ0SktHbHdzLTZEMmtBT3lWYXVkY0l3SDM0TjNwWTBtM0FjdlRoYzlfQTBQLVNaLUFtWDNrMU9KbXBzLVZWekN4bGFVSzA0R1RLOFBiMlBsSnNILVBuZ1hEemQtZm9FaE1URVdSREVoRzZDM0dPZkNwdzJfQ3pMRjZ0cFJmLXB6a3ZyZ2NjcjNMTllsVmV6X0M0OVhpcHA5a3RiU0lMdnhoeXJwVGp1SDRwYlFkd3M0emJTTEkwQjVmS0VxVDNqUdIB6AFBVV95cUxObTcwd3VqRWxyLWRxRWVkWEJubW50cjBiaFhrWHl0QTQteWxtUzYxZHo5NGgzdmtVdHprVVlPcWhZX25LQXBfbU5ZM3E4UmRMU3ZLYXl1UFNfOTFvSi1mam9sMTE4MVp1aWdTWmptM2ViUThUOFZsSTBFSHZ1azFQOUN4dWtid1RwQlQwRVVRV2p1OUFhaWh2Q3RuWThaNkh4NFhhckhac1ozQzR0bzAtbExmcU5RVm15WGNzd3RTcEY4QkhwTTBvZ1JBbU9zME9qeXRrM0c1OTRKUlBzYy1DUkJ2Y2RBaW9q?oc=5</t>
         </is>
       </c>
-      <c r="T18" s="173">
-        <f>IF($B18="",0,IF(AND(OR(OR(Dashboard!$B$5="All themes",Dashboard!$B$5=""),$C18=Dashboard!$B$5),OR(OR(Dashboard!$G$5="All uses",Dashboard!$G$5=""),$E18=Dashboard!$G$5),N($D18)&gt;=Lists!$H$2,OR(OR(Dashboard!$N$5="All windows",Dashboard!$N$5=""),$P18=Dashboard!$N$5)),1,0))</f>
-        <v/>
-      </c>
-      <c r="U18" s="174">
-        <f>IF($T18=1,N($D18)*1E14+MIN(MAX(N($R18),0),9999)*1E10+MIN(N($K18),99999)*1E5+99999-MIN(ROW(),99999),"")</f>
+      <c r="W18" s="173">
+        <f>IF($B18="",0,IF(AND(OR(OR(Dashboard!$B$5="All themes",Dashboard!$B$5=""),$C18=Dashboard!$B$5),OR(OR(Dashboard!$G$5="All uses",Dashboard!$G$5=""),$E18=Dashboard!$G$5),N($D18)&gt;=Lists!$H$2,OR(OR(Dashboard!$N$5="All windows",Dashboard!$N$5=""),$S18=Dashboard!$N$5)),1,0))</f>
+        <v/>
+      </c>
+      <c r="X18" s="174">
+        <f>IF($W18=1,N($D18)*1E14+MIN(MAX(N($U18),0),9999)*1E10+MIN(N($K18),99999)*1E5+99999-MIN(ROW(),99999),"")</f>
         <v/>
       </c>
     </row>
@@ -7659,38 +7785,41 @@
         </is>
       </c>
       <c r="M19" s="168" t="n"/>
-      <c r="N19" s="169" t="inlineStr">
+      <c r="N19" s="169" t="n"/>
+      <c r="O19" s="166" t="n"/>
+      <c r="P19" s="166" t="n"/>
+      <c r="Q19" s="170" t="inlineStr">
         <is>
           <t>Vietnam</t>
         </is>
       </c>
-      <c r="O19" s="167" t="n">
+      <c r="R19" s="167" t="n">
         <v>46317</v>
       </c>
-      <c r="P19" s="170" t="inlineStr">
+      <c r="S19" s="169" t="inlineStr">
         <is>
           <t>2026-Q4</t>
         </is>
       </c>
-      <c r="Q19" s="171" t="inlineStr">
+      <c r="T19" s="171" t="inlineStr">
         <is>
           <t>landslide, rockfall</t>
         </is>
       </c>
-      <c r="R19" s="158" t="n">
+      <c r="U19" s="158" t="n">
         <v>8</v>
       </c>
-      <c r="S19" s="172" t="inlineStr">
+      <c r="V19" s="172" t="inlineStr">
         <is>
           <t>https://news.google.com/rss/articles/CBMif0FVX3lxTE4zQm1aVUtwTUM2RWlZZXpKOEdDX0xZYk41cGNLaDNFNDNlQko2SGxxTmVtLVBBQm9VZkFIOFBmUE1PSE1KclNSUHNQMDhUTGRiWnE0R0ZPcDFFV3E4R3U4M19FZzI2akVUNFRvRkgwSkxuMkZpWmU4Tlh5WTNoQ2M?oc=5</t>
         </is>
       </c>
-      <c r="T19" s="173">
-        <f>IF($B19="",0,IF(AND(OR(OR(Dashboard!$B$5="All themes",Dashboard!$B$5=""),$C19=Dashboard!$B$5),OR(OR(Dashboard!$G$5="All uses",Dashboard!$G$5=""),$E19=Dashboard!$G$5),N($D19)&gt;=Lists!$H$2,OR(OR(Dashboard!$N$5="All windows",Dashboard!$N$5=""),$P19=Dashboard!$N$5)),1,0))</f>
-        <v/>
-      </c>
-      <c r="U19" s="174">
-        <f>IF($T19=1,N($D19)*1E14+MIN(MAX(N($R19),0),9999)*1E10+MIN(N($K19),99999)*1E5+99999-MIN(ROW(),99999),"")</f>
+      <c r="W19" s="173">
+        <f>IF($B19="",0,IF(AND(OR(OR(Dashboard!$B$5="All themes",Dashboard!$B$5=""),$C19=Dashboard!$B$5),OR(OR(Dashboard!$G$5="All uses",Dashboard!$G$5=""),$E19=Dashboard!$G$5),N($D19)&gt;=Lists!$H$2,OR(OR(Dashboard!$N$5="All windows",Dashboard!$N$5=""),$S19=Dashboard!$N$5)),1,0))</f>
+        <v/>
+      </c>
+      <c r="X19" s="174">
+        <f>IF($W19=1,N($D19)*1E14+MIN(MAX(N($U19),0),9999)*1E10+MIN(N($K19),99999)*1E5+99999-MIN(ROW(),99999),"")</f>
         <v/>
       </c>
     </row>
@@ -7742,38 +7871,41 @@
         </is>
       </c>
       <c r="M20" s="168" t="n"/>
-      <c r="N20" s="169" t="inlineStr">
+      <c r="N20" s="169" t="n"/>
+      <c r="O20" s="166" t="n"/>
+      <c r="P20" s="166" t="n"/>
+      <c r="Q20" s="170" t="inlineStr">
         <is>
           <t>Russia</t>
         </is>
       </c>
-      <c r="O20" s="167" t="n">
+      <c r="R20" s="167" t="n">
         <v>46317</v>
       </c>
-      <c r="P20" s="170" t="inlineStr">
+      <c r="S20" s="169" t="inlineStr">
         <is>
           <t>2026-Q4</t>
         </is>
       </c>
-      <c r="Q20" s="171" t="inlineStr">
+      <c r="T20" s="171" t="inlineStr">
         <is>
           <t>landslide, subsidence, soil</t>
         </is>
       </c>
-      <c r="R20" s="158" t="n">
+      <c r="U20" s="158" t="n">
         <v>8</v>
       </c>
-      <c r="S20" s="172" t="inlineStr">
+      <c r="V20" s="172" t="inlineStr">
         <is>
           <t>https://news.google.com/rss/articles/CBMimwFBVV95cUxPLTkyck5DaWR1VmtTV3hIeXVJaWNDUnNpR1AzZDlLbVdzdC1kSmJfTjM3T000WGlLSWt5S2hfSzItS3Y5MkFJZWRZaktBTlNVVFFyRjNHRndpczhWYkdvNFBFY1MxbXA4VTRWWlpCeVdqTWFNbG9HTldyRlRwQkdUYVV2SDNBOGFRUU9WM3pIMG16RUZBWGttYTRmVQ?oc=5</t>
         </is>
       </c>
-      <c r="T20" s="173">
-        <f>IF($B20="",0,IF(AND(OR(OR(Dashboard!$B$5="All themes",Dashboard!$B$5=""),$C20=Dashboard!$B$5),OR(OR(Dashboard!$G$5="All uses",Dashboard!$G$5=""),$E20=Dashboard!$G$5),N($D20)&gt;=Lists!$H$2,OR(OR(Dashboard!$N$5="All windows",Dashboard!$N$5=""),$P20=Dashboard!$N$5)),1,0))</f>
-        <v/>
-      </c>
-      <c r="U20" s="174">
-        <f>IF($T20=1,N($D20)*1E14+MIN(MAX(N($R20),0),9999)*1E10+MIN(N($K20),99999)*1E5+99999-MIN(ROW(),99999),"")</f>
+      <c r="W20" s="173">
+        <f>IF($B20="",0,IF(AND(OR(OR(Dashboard!$B$5="All themes",Dashboard!$B$5=""),$C20=Dashboard!$B$5),OR(OR(Dashboard!$G$5="All uses",Dashboard!$G$5=""),$E20=Dashboard!$G$5),N($D20)&gt;=Lists!$H$2,OR(OR(Dashboard!$N$5="All windows",Dashboard!$N$5=""),$S20=Dashboard!$N$5)),1,0))</f>
+        <v/>
+      </c>
+      <c r="X20" s="174">
+        <f>IF($W20=1,N($D20)*1E14+MIN(MAX(N($U20),0),9999)*1E10+MIN(N($K20),99999)*1E5+99999-MIN(ROW(),99999),"")</f>
         <v/>
       </c>
     </row>
@@ -7821,38 +7953,41 @@
       </c>
       <c r="L21" s="166" t="n"/>
       <c r="M21" s="168" t="n"/>
-      <c r="N21" s="169" t="inlineStr">
+      <c r="N21" s="169" t="n"/>
+      <c r="O21" s="166" t="n"/>
+      <c r="P21" s="166" t="n"/>
+      <c r="Q21" s="170" t="inlineStr">
         <is>
           <t>Vietnam</t>
         </is>
       </c>
-      <c r="O21" s="167" t="n">
+      <c r="R21" s="167" t="n">
         <v>46318</v>
       </c>
-      <c r="P21" s="170" t="inlineStr">
+      <c r="S21" s="169" t="inlineStr">
         <is>
           <t>2026-Q4</t>
         </is>
       </c>
-      <c r="Q21" s="171" t="inlineStr">
+      <c r="T21" s="171" t="inlineStr">
         <is>
           <t>embankment, dike, erosion</t>
         </is>
       </c>
-      <c r="R21" s="158" t="n">
+      <c r="U21" s="158" t="n">
         <v>7</v>
       </c>
-      <c r="S21" s="172" t="inlineStr">
+      <c r="V21" s="172" t="inlineStr">
         <is>
           <t>https://news.google.com/rss/articles/CBMingFBVV95cUxQS3doM1BoVjZsRlp4V0theDZtSFZUWEhySWJwSDIzUFpjV09lV201bzV0OFFuYVZrS1lJT3BXd2ZJNVpWbWpJbm5MSlpUb004MnlwRlJYMmV3bnpNWEZSc0pocTBxaWRHcHVYc3lPdmFESG85TUc5UkJ4YVljMWZPbmJzcWlXd25iTTRuQmNjNHg3U3BHalpHTUNTWE9nQQ?oc=5</t>
         </is>
       </c>
-      <c r="T21" s="173">
-        <f>IF($B21="",0,IF(AND(OR(OR(Dashboard!$B$5="All themes",Dashboard!$B$5=""),$C21=Dashboard!$B$5),OR(OR(Dashboard!$G$5="All uses",Dashboard!$G$5=""),$E21=Dashboard!$G$5),N($D21)&gt;=Lists!$H$2,OR(OR(Dashboard!$N$5="All windows",Dashboard!$N$5=""),$P21=Dashboard!$N$5)),1,0))</f>
-        <v/>
-      </c>
-      <c r="U21" s="174">
-        <f>IF($T21=1,N($D21)*1E14+MIN(MAX(N($R21),0),9999)*1E10+MIN(N($K21),99999)*1E5+99999-MIN(ROW(),99999),"")</f>
+      <c r="W21" s="173">
+        <f>IF($B21="",0,IF(AND(OR(OR(Dashboard!$B$5="All themes",Dashboard!$B$5=""),$C21=Dashboard!$B$5),OR(OR(Dashboard!$G$5="All uses",Dashboard!$G$5=""),$E21=Dashboard!$G$5),N($D21)&gt;=Lists!$H$2,OR(OR(Dashboard!$N$5="All windows",Dashboard!$N$5=""),$S21=Dashboard!$N$5)),1,0))</f>
+        <v/>
+      </c>
+      <c r="X21" s="174">
+        <f>IF($W21=1,N($D21)*1E14+MIN(MAX(N($U21),0),9999)*1E10+MIN(N($K21),99999)*1E5+99999-MIN(ROW(),99999),"")</f>
         <v/>
       </c>
     </row>
@@ -7904,38 +8039,41 @@
         </is>
       </c>
       <c r="M22" s="168" t="n"/>
-      <c r="N22" s="169" t="inlineStr">
+      <c r="N22" s="169" t="n"/>
+      <c r="O22" s="166" t="n"/>
+      <c r="P22" s="166" t="n"/>
+      <c r="Q22" s="170" t="inlineStr">
         <is>
           <t>Russia</t>
         </is>
       </c>
-      <c r="O22" s="167" t="n">
+      <c r="R22" s="167" t="n">
         <v>46318</v>
       </c>
-      <c r="P22" s="170" t="inlineStr">
+      <c r="S22" s="169" t="inlineStr">
         <is>
           <t>2026-Q4</t>
         </is>
       </c>
-      <c r="Q22" s="171" t="inlineStr">
+      <c r="T22" s="171" t="inlineStr">
         <is>
           <t>landslide, embankment</t>
         </is>
       </c>
-      <c r="R22" s="158" t="n">
+      <c r="U22" s="158" t="n">
         <v>7</v>
       </c>
-      <c r="S22" s="172" t="inlineStr">
+      <c r="V22" s="172" t="inlineStr">
         <is>
           <t>https://news.google.com/rss/articles/CBMilwFBVV95cUxNcG13NlMtVlJSQ0ZDYTM0cGN0NmZzaEtGVDFnV2ZGNkIzM1p0MU0wdUFpbnNDdFFDa0l6M1F6NW5hX2pMNFViN2lfWE80dlJFUGpiOWRfSFhBRWN1d1g2b3o5a1kxNUhIVHRNUUJ6TG5EMXdxcnE2bG9TTWxIc2dDUjBLTlpmNjg5WFVtZE15SWhRY0sxSWtv?oc=5</t>
         </is>
       </c>
-      <c r="T22" s="173">
-        <f>IF($B22="",0,IF(AND(OR(OR(Dashboard!$B$5="All themes",Dashboard!$B$5=""),$C22=Dashboard!$B$5),OR(OR(Dashboard!$G$5="All uses",Dashboard!$G$5=""),$E22=Dashboard!$G$5),N($D22)&gt;=Lists!$H$2,OR(OR(Dashboard!$N$5="All windows",Dashboard!$N$5=""),$P22=Dashboard!$N$5)),1,0))</f>
-        <v/>
-      </c>
-      <c r="U22" s="174">
-        <f>IF($T22=1,N($D22)*1E14+MIN(MAX(N($R22),0),9999)*1E10+MIN(N($K22),99999)*1E5+99999-MIN(ROW(),99999),"")</f>
+      <c r="W22" s="173">
+        <f>IF($B22="",0,IF(AND(OR(OR(Dashboard!$B$5="All themes",Dashboard!$B$5=""),$C22=Dashboard!$B$5),OR(OR(Dashboard!$G$5="All uses",Dashboard!$G$5=""),$E22=Dashboard!$G$5),N($D22)&gt;=Lists!$H$2,OR(OR(Dashboard!$N$5="All windows",Dashboard!$N$5=""),$S22=Dashboard!$N$5)),1,0))</f>
+        <v/>
+      </c>
+      <c r="X22" s="174">
+        <f>IF($W22=1,N($D22)*1E14+MIN(MAX(N($U22),0),9999)*1E10+MIN(N($K22),99999)*1E5+99999-MIN(ROW(),99999),"")</f>
         <v/>
       </c>
     </row>
@@ -7987,38 +8125,41 @@
         </is>
       </c>
       <c r="M23" s="168" t="n"/>
-      <c r="N23" s="169" t="inlineStr">
+      <c r="N23" s="169" t="n"/>
+      <c r="O23" s="166" t="n"/>
+      <c r="P23" s="166" t="n"/>
+      <c r="Q23" s="170" t="inlineStr">
         <is>
           <t>Vietnam</t>
         </is>
       </c>
-      <c r="O23" s="167" t="n">
-        <v>46319</v>
-      </c>
-      <c r="P23" s="170" t="inlineStr">
+      <c r="R23" s="167" t="n">
+        <v>46319</v>
+      </c>
+      <c r="S23" s="169" t="inlineStr">
         <is>
           <t>2026-Q4</t>
         </is>
       </c>
-      <c r="Q23" s="171" t="inlineStr">
+      <c r="T23" s="171" t="inlineStr">
         <is>
           <t>landslide, subsidence</t>
         </is>
       </c>
-      <c r="R23" s="158" t="n">
+      <c r="U23" s="158" t="n">
         <v>7</v>
       </c>
-      <c r="S23" s="172" t="inlineStr">
+      <c r="V23" s="172" t="inlineStr">
         <is>
           <t>https://news.google.com/rss/articles/CBMiugFBVV95cUxPTWJZUVVOZ3hOTjliMDhtRWVCaFQyYnB3SzNtaDlrOGg4b1VzVnUzM3Rjc3l3T0ZrUFBXNWRWRnJNdGF4WVpJR29aS1VjSkFIZnFubFVCZnJFS3NQZW93VHlaQ2p6RUcxbFhlOUdzRmZGRDhkVHZFTkkwSk1rZm1vdWFXS0JDdkxsWDg4YzhHWVoyeEVSQnRocXlqcnRab1lSSS1GQXhNT24zSTlCTGhVU2c5NzUwaWctdXc?oc=5</t>
         </is>
       </c>
-      <c r="T23" s="173">
-        <f>IF($B23="",0,IF(AND(OR(OR(Dashboard!$B$5="All themes",Dashboard!$B$5=""),$C23=Dashboard!$B$5),OR(OR(Dashboard!$G$5="All uses",Dashboard!$G$5=""),$E23=Dashboard!$G$5),N($D23)&gt;=Lists!$H$2,OR(OR(Dashboard!$N$5="All windows",Dashboard!$N$5=""),$P23=Dashboard!$N$5)),1,0))</f>
-        <v/>
-      </c>
-      <c r="U23" s="174">
-        <f>IF($T23=1,N($D23)*1E14+MIN(MAX(N($R23),0),9999)*1E10+MIN(N($K23),99999)*1E5+99999-MIN(ROW(),99999),"")</f>
+      <c r="W23" s="173">
+        <f>IF($B23="",0,IF(AND(OR(OR(Dashboard!$B$5="All themes",Dashboard!$B$5=""),$C23=Dashboard!$B$5),OR(OR(Dashboard!$G$5="All uses",Dashboard!$G$5=""),$E23=Dashboard!$G$5),N($D23)&gt;=Lists!$H$2,OR(OR(Dashboard!$N$5="All windows",Dashboard!$N$5=""),$S23=Dashboard!$N$5)),1,0))</f>
+        <v/>
+      </c>
+      <c r="X23" s="174">
+        <f>IF($W23=1,N($D23)*1E14+MIN(MAX(N($U23),0),9999)*1E10+MIN(N($K23),99999)*1E5+99999-MIN(ROW(),99999),"")</f>
         <v/>
       </c>
     </row>
@@ -8070,38 +8211,41 @@
         </is>
       </c>
       <c r="M24" s="168" t="n"/>
-      <c r="N24" s="169" t="inlineStr">
+      <c r="N24" s="169" t="n"/>
+      <c r="O24" s="166" t="n"/>
+      <c r="P24" s="166" t="n"/>
+      <c r="Q24" s="170" t="inlineStr">
         <is>
           <t>Vietnam</t>
         </is>
       </c>
-      <c r="O24" s="167" t="n">
+      <c r="R24" s="167" t="n">
         <v>46318</v>
       </c>
-      <c r="P24" s="170" t="inlineStr">
+      <c r="S24" s="169" t="inlineStr">
         <is>
           <t>2026-Q4</t>
         </is>
       </c>
-      <c r="Q24" s="171" t="inlineStr">
+      <c r="T24" s="171" t="inlineStr">
         <is>
           <t>landslide, subsidence</t>
         </is>
       </c>
-      <c r="R24" s="158" t="n">
+      <c r="U24" s="158" t="n">
         <v>7</v>
       </c>
-      <c r="S24" s="172" t="inlineStr">
+      <c r="V24" s="172" t="inlineStr">
         <is>
           <t>https://news.google.com/rss/articles/CBMiigFBVV95cUxPZWVidFMzVlYxMDdISl9EQ2U0U3hiaVU2NmFPN09jYzZUem1CaXB3N1I4S1l0VW9Ka1l1LU9kVnY2bDQzUnFKWUFiNnF3azVkeEZoUGpxREdXNExtd2ZwRWVtNmZPTUkxUnA5TmFsczUyX3hkLUpJYmtFVU5yeTRONV9nb2VfNjVPZnc?oc=5</t>
         </is>
       </c>
-      <c r="T24" s="173">
-        <f>IF($B24="",0,IF(AND(OR(OR(Dashboard!$B$5="All themes",Dashboard!$B$5=""),$C24=Dashboard!$B$5),OR(OR(Dashboard!$G$5="All uses",Dashboard!$G$5=""),$E24=Dashboard!$G$5),N($D24)&gt;=Lists!$H$2,OR(OR(Dashboard!$N$5="All windows",Dashboard!$N$5=""),$P24=Dashboard!$N$5)),1,0))</f>
-        <v/>
-      </c>
-      <c r="U24" s="174">
-        <f>IF($T24=1,N($D24)*1E14+MIN(MAX(N($R24),0),9999)*1E10+MIN(N($K24),99999)*1E5+99999-MIN(ROW(),99999),"")</f>
+      <c r="W24" s="173">
+        <f>IF($B24="",0,IF(AND(OR(OR(Dashboard!$B$5="All themes",Dashboard!$B$5=""),$C24=Dashboard!$B$5),OR(OR(Dashboard!$G$5="All uses",Dashboard!$G$5=""),$E24=Dashboard!$G$5),N($D24)&gt;=Lists!$H$2,OR(OR(Dashboard!$N$5="All windows",Dashboard!$N$5=""),$S24=Dashboard!$N$5)),1,0))</f>
+        <v/>
+      </c>
+      <c r="X24" s="174">
+        <f>IF($W24=1,N($D24)*1E14+MIN(MAX(N($U24),0),9999)*1E10+MIN(N($K24),99999)*1E5+99999-MIN(ROW(),99999),"")</f>
         <v/>
       </c>
     </row>
@@ -8153,38 +8297,41 @@
         </is>
       </c>
       <c r="M25" s="168" t="n"/>
-      <c r="N25" s="169" t="inlineStr">
+      <c r="N25" s="169" t="n"/>
+      <c r="O25" s="166" t="n"/>
+      <c r="P25" s="166" t="n"/>
+      <c r="Q25" s="170" t="inlineStr">
         <is>
           <t>Vietnam</t>
         </is>
       </c>
-      <c r="O25" s="167" t="n">
+      <c r="R25" s="167" t="n">
         <v>46318</v>
       </c>
-      <c r="P25" s="170" t="inlineStr">
+      <c r="S25" s="169" t="inlineStr">
         <is>
           <t>2026-Q4</t>
         </is>
       </c>
-      <c r="Q25" s="171" t="inlineStr">
+      <c r="T25" s="171" t="inlineStr">
         <is>
           <t>sinkhole, subsidence</t>
         </is>
       </c>
-      <c r="R25" s="158" t="n">
+      <c r="U25" s="158" t="n">
         <v>7</v>
       </c>
-      <c r="S25" s="172" t="inlineStr">
+      <c r="V25" s="172" t="inlineStr">
         <is>
           <t>https://news.google.com/rss/articles/CBMi4wFBVV95cUxQSXAyb195dGp6RURzRWliZzhoYmI2S0RUbUJQZG10eHVNSDVFZDE0bW1naTNubEgxU1k5UWxOTV9QUjJiLXZxWlJjOVV5aTh5V1J3Tm11UFdsZ2dJMnYzWTdvekpSWXhoSG1QZGF2a2o3UXRkWjh6VTNqcS14cXBJSUd4NXplcUg1Ri1EN1IzN1dyblF3clU3ZE42YmNra1hhYVF5c1Azd2I0U3VoaFY0a1pDY1huU3NmUXhOQnAzeHVSY3BQTV9uV3hsckJxaUx1SHhPQ1VUU21kZWFVZGJVRGtzRQ?oc=5</t>
         </is>
       </c>
-      <c r="T25" s="173">
-        <f>IF($B25="",0,IF(AND(OR(OR(Dashboard!$B$5="All themes",Dashboard!$B$5=""),$C25=Dashboard!$B$5),OR(OR(Dashboard!$G$5="All uses",Dashboard!$G$5=""),$E25=Dashboard!$G$5),N($D25)&gt;=Lists!$H$2,OR(OR(Dashboard!$N$5="All windows",Dashboard!$N$5=""),$P25=Dashboard!$N$5)),1,0))</f>
-        <v/>
-      </c>
-      <c r="U25" s="174">
-        <f>IF($T25=1,N($D25)*1E14+MIN(MAX(N($R25),0),9999)*1E10+MIN(N($K25),99999)*1E5+99999-MIN(ROW(),99999),"")</f>
+      <c r="W25" s="173">
+        <f>IF($B25="",0,IF(AND(OR(OR(Dashboard!$B$5="All themes",Dashboard!$B$5=""),$C25=Dashboard!$B$5),OR(OR(Dashboard!$G$5="All uses",Dashboard!$G$5=""),$E25=Dashboard!$G$5),N($D25)&gt;=Lists!$H$2,OR(OR(Dashboard!$N$5="All windows",Dashboard!$N$5=""),$S25=Dashboard!$N$5)),1,0))</f>
+        <v/>
+      </c>
+      <c r="X25" s="174">
+        <f>IF($W25=1,N($D25)*1E14+MIN(MAX(N($U25),0),9999)*1E10+MIN(N($K25),99999)*1E5+99999-MIN(ROW(),99999),"")</f>
         <v/>
       </c>
     </row>
@@ -8236,38 +8383,41 @@
         </is>
       </c>
       <c r="M26" s="168" t="n"/>
-      <c r="N26" s="169" t="inlineStr">
+      <c r="N26" s="169" t="n"/>
+      <c r="O26" s="166" t="n"/>
+      <c r="P26" s="166" t="n"/>
+      <c r="Q26" s="170" t="inlineStr">
         <is>
           <t>Vietnam</t>
         </is>
       </c>
-      <c r="O26" s="167" t="n">
+      <c r="R26" s="167" t="n">
         <v>46317</v>
       </c>
-      <c r="P26" s="170" t="inlineStr">
+      <c r="S26" s="169" t="inlineStr">
         <is>
           <t>2026-Q4</t>
         </is>
       </c>
-      <c r="Q26" s="171" t="inlineStr">
+      <c r="T26" s="171" t="inlineStr">
         <is>
           <t>landslide, subsidence</t>
         </is>
       </c>
-      <c r="R26" s="158" t="n">
+      <c r="U26" s="158" t="n">
         <v>7</v>
       </c>
-      <c r="S26" s="172" t="inlineStr">
+      <c r="V26" s="172" t="inlineStr">
         <is>
           <t>https://news.google.com/rss/articles/CBMimwFBVV95cUxPMFBaWmJuQ3NGTklKMkNGckRqWFA0WW1sLXlvY1QxanR4YkN6YVVpejBld3ctZVREbkVPWnVab2FBOEZtTXoyeVRmTDE3TXF3ck5IRzNkNFJRZ0lmZmlqLTIwWGZhV0N0RFFiNGVPMnJBcHc4RXBBdjRqdmh5WnZSb1VkZ3B2Q3hva0JybF8tbVI0WjVQVFVsNHUxTQ?oc=5</t>
         </is>
       </c>
-      <c r="T26" s="173">
-        <f>IF($B26="",0,IF(AND(OR(OR(Dashboard!$B$5="All themes",Dashboard!$B$5=""),$C26=Dashboard!$B$5),OR(OR(Dashboard!$G$5="All uses",Dashboard!$G$5=""),$E26=Dashboard!$G$5),N($D26)&gt;=Lists!$H$2,OR(OR(Dashboard!$N$5="All windows",Dashboard!$N$5=""),$P26=Dashboard!$N$5)),1,0))</f>
-        <v/>
-      </c>
-      <c r="U26" s="174">
-        <f>IF($T26=1,N($D26)*1E14+MIN(MAX(N($R26),0),9999)*1E10+MIN(N($K26),99999)*1E5+99999-MIN(ROW(),99999),"")</f>
+      <c r="W26" s="173">
+        <f>IF($B26="",0,IF(AND(OR(OR(Dashboard!$B$5="All themes",Dashboard!$B$5=""),$C26=Dashboard!$B$5),OR(OR(Dashboard!$G$5="All uses",Dashboard!$G$5=""),$E26=Dashboard!$G$5),N($D26)&gt;=Lists!$H$2,OR(OR(Dashboard!$N$5="All windows",Dashboard!$N$5=""),$S26=Dashboard!$N$5)),1,0))</f>
+        <v/>
+      </c>
+      <c r="X26" s="174">
+        <f>IF($W26=1,N($D26)*1E14+MIN(MAX(N($U26),0),9999)*1E10+MIN(N($K26),99999)*1E5+99999-MIN(ROW(),99999),"")</f>
         <v/>
       </c>
     </row>
@@ -8319,38 +8469,41 @@
         </is>
       </c>
       <c r="M27" s="168" t="n"/>
-      <c r="N27" s="169" t="inlineStr">
+      <c r="N27" s="169" t="n"/>
+      <c r="O27" s="166" t="n"/>
+      <c r="P27" s="166" t="n"/>
+      <c r="Q27" s="170" t="inlineStr">
         <is>
           <t>South Korea</t>
         </is>
       </c>
-      <c r="O27" s="167" t="n">
-        <v>46319</v>
-      </c>
-      <c r="P27" s="170" t="inlineStr">
+      <c r="R27" s="167" t="n">
+        <v>46319</v>
+      </c>
+      <c r="S27" s="169" t="inlineStr">
         <is>
           <t>2026-Q4</t>
         </is>
       </c>
-      <c r="Q27" s="171" t="inlineStr">
+      <c r="T27" s="171" t="inlineStr">
         <is>
           <t>landslide, embankment</t>
         </is>
       </c>
-      <c r="R27" s="158" t="n">
+      <c r="U27" s="158" t="n">
         <v>7</v>
       </c>
-      <c r="S27" s="172" t="inlineStr">
+      <c r="V27" s="172" t="inlineStr">
         <is>
           <t>https://news.google.com/rss/articles/CBMia0FVX3lxTE5yN3NxbVRJdUpIaWRZaHJQMGx1MktYUTdSRHlXd0xCR0tiSkhtNEotVmltaFRvVzFvY3Qxcm1JOFVCb1RBWXVtMTZRVWRtdC1DMERha1RoblFxTjhBT01GR1hWQ1JLTlRFMW1V?oc=5</t>
         </is>
       </c>
-      <c r="T27" s="173">
-        <f>IF($B27="",0,IF(AND(OR(OR(Dashboard!$B$5="All themes",Dashboard!$B$5=""),$C27=Dashboard!$B$5),OR(OR(Dashboard!$G$5="All uses",Dashboard!$G$5=""),$E27=Dashboard!$G$5),N($D27)&gt;=Lists!$H$2,OR(OR(Dashboard!$N$5="All windows",Dashboard!$N$5=""),$P27=Dashboard!$N$5)),1,0))</f>
-        <v/>
-      </c>
-      <c r="U27" s="174">
-        <f>IF($T27=1,N($D27)*1E14+MIN(MAX(N($R27),0),9999)*1E10+MIN(N($K27),99999)*1E5+99999-MIN(ROW(),99999),"")</f>
+      <c r="W27" s="173">
+        <f>IF($B27="",0,IF(AND(OR(OR(Dashboard!$B$5="All themes",Dashboard!$B$5=""),$C27=Dashboard!$B$5),OR(OR(Dashboard!$G$5="All uses",Dashboard!$G$5=""),$E27=Dashboard!$G$5),N($D27)&gt;=Lists!$H$2,OR(OR(Dashboard!$N$5="All windows",Dashboard!$N$5=""),$S27=Dashboard!$N$5)),1,0))</f>
+        <v/>
+      </c>
+      <c r="X27" s="174">
+        <f>IF($W27=1,N($D27)*1E14+MIN(MAX(N($U27),0),9999)*1E10+MIN(N($K27),99999)*1E5+99999-MIN(ROW(),99999),"")</f>
         <v/>
       </c>
     </row>
@@ -8402,38 +8555,41 @@
         </is>
       </c>
       <c r="M28" s="168" t="n"/>
-      <c r="N28" s="169" t="inlineStr">
+      <c r="N28" s="169" t="n"/>
+      <c r="O28" s="166" t="n"/>
+      <c r="P28" s="166" t="n"/>
+      <c r="Q28" s="170" t="inlineStr">
         <is>
           <t>Vietnam</t>
         </is>
       </c>
-      <c r="O28" s="167" t="n">
+      <c r="R28" s="167" t="n">
         <v>46318</v>
       </c>
-      <c r="P28" s="170" t="inlineStr">
+      <c r="S28" s="169" t="inlineStr">
         <is>
           <t>2026-Q4</t>
         </is>
       </c>
-      <c r="Q28" s="171" t="inlineStr">
+      <c r="T28" s="171" t="inlineStr">
         <is>
           <t>landslide, slope</t>
         </is>
       </c>
-      <c r="R28" s="158" t="n">
+      <c r="U28" s="158" t="n">
         <v>6</v>
       </c>
-      <c r="S28" s="172" t="inlineStr">
+      <c r="V28" s="172" t="inlineStr">
         <is>
           <t>https://news.google.com/rss/articles/CBMikwFBVV95cUxOUmJPNnl3dVdQRml6UUt3S1Joa05VaE9sdjdhNWZZeVN6QUdqdnFIS2NiMWdGMl9KN093Wm1naTRFcDRoek1UTVQxNGJkZ2lkajUyVnhRRFF4ZTV1UlhsS3NodG80YlpGdlpuOHRaaGFnaXJ5cDN4eTd0VFZJdldPMlczVVZ1NmZZdExSemVKM3lXWUk?oc=5</t>
         </is>
       </c>
-      <c r="T28" s="173">
-        <f>IF($B28="",0,IF(AND(OR(OR(Dashboard!$B$5="All themes",Dashboard!$B$5=""),$C28=Dashboard!$B$5),OR(OR(Dashboard!$G$5="All uses",Dashboard!$G$5=""),$E28=Dashboard!$G$5),N($D28)&gt;=Lists!$H$2,OR(OR(Dashboard!$N$5="All windows",Dashboard!$N$5=""),$P28=Dashboard!$N$5)),1,0))</f>
-        <v/>
-      </c>
-      <c r="U28" s="174">
-        <f>IF($T28=1,N($D28)*1E14+MIN(MAX(N($R28),0),9999)*1E10+MIN(N($K28),99999)*1E5+99999-MIN(ROW(),99999),"")</f>
+      <c r="W28" s="173">
+        <f>IF($B28="",0,IF(AND(OR(OR(Dashboard!$B$5="All themes",Dashboard!$B$5=""),$C28=Dashboard!$B$5),OR(OR(Dashboard!$G$5="All uses",Dashboard!$G$5=""),$E28=Dashboard!$G$5),N($D28)&gt;=Lists!$H$2,OR(OR(Dashboard!$N$5="All windows",Dashboard!$N$5=""),$S28=Dashboard!$N$5)),1,0))</f>
+        <v/>
+      </c>
+      <c r="X28" s="174">
+        <f>IF($W28=1,N($D28)*1E14+MIN(MAX(N($U28),0),9999)*1E10+MIN(N($K28),99999)*1E5+99999-MIN(ROW(),99999),"")</f>
         <v/>
       </c>
     </row>
@@ -8485,38 +8641,41 @@
         </is>
       </c>
       <c r="M29" s="168" t="n"/>
-      <c r="N29" s="169" t="inlineStr">
+      <c r="N29" s="169" t="n"/>
+      <c r="O29" s="166" t="n"/>
+      <c r="P29" s="166" t="n"/>
+      <c r="Q29" s="170" t="inlineStr">
         <is>
           <t>South Korea</t>
         </is>
       </c>
-      <c r="O29" s="167" t="n">
-        <v>46319</v>
-      </c>
-      <c r="P29" s="170" t="inlineStr">
+      <c r="R29" s="167" t="n">
+        <v>46319</v>
+      </c>
+      <c r="S29" s="169" t="inlineStr">
         <is>
           <t>2026-Q4</t>
         </is>
       </c>
-      <c r="Q29" s="171" t="inlineStr">
+      <c r="T29" s="171" t="inlineStr">
         <is>
           <t>retaining wall, collapse</t>
         </is>
       </c>
-      <c r="R29" s="158" t="n">
+      <c r="U29" s="158" t="n">
         <v>5</v>
       </c>
-      <c r="S29" s="172" t="inlineStr">
+      <c r="V29" s="172" t="inlineStr">
         <is>
           <t>https://news.google.com/rss/articles/CBMiWEFVX3lxTE1USkR5eG9yOEoxdF9oR1JuMU4tOUdCNkREX0dNUFFvWWd5UXZaT0ZkQk54eUhVbFg4QlI5SF8yTHlGZFZldTBsdnpFRDY5X290bkt0YzBXOTbSAVhBVV95cUxNVEpEeXhvcjhKMXRfaEdSbjFOLTlHQjZERF9HTVBRb1lneVF2Wk9GZEJOeHlIVWxYOEJSOUhfMkx5RmRWZXUwbHZ6RUQ2OV9vdG5LdGMwVzk2?oc=5</t>
         </is>
       </c>
-      <c r="T29" s="173">
-        <f>IF($B29="",0,IF(AND(OR(OR(Dashboard!$B$5="All themes",Dashboard!$B$5=""),$C29=Dashboard!$B$5),OR(OR(Dashboard!$G$5="All uses",Dashboard!$G$5=""),$E29=Dashboard!$G$5),N($D29)&gt;=Lists!$H$2,OR(OR(Dashboard!$N$5="All windows",Dashboard!$N$5=""),$P29=Dashboard!$N$5)),1,0))</f>
-        <v/>
-      </c>
-      <c r="U29" s="174">
-        <f>IF($T29=1,N($D29)*1E14+MIN(MAX(N($R29),0),9999)*1E10+MIN(N($K29),99999)*1E5+99999-MIN(ROW(),99999),"")</f>
+      <c r="W29" s="173">
+        <f>IF($B29="",0,IF(AND(OR(OR(Dashboard!$B$5="All themes",Dashboard!$B$5=""),$C29=Dashboard!$B$5),OR(OR(Dashboard!$G$5="All uses",Dashboard!$G$5=""),$E29=Dashboard!$G$5),N($D29)&gt;=Lists!$H$2,OR(OR(Dashboard!$N$5="All windows",Dashboard!$N$5=""),$S29=Dashboard!$N$5)),1,0))</f>
+        <v/>
+      </c>
+      <c r="X29" s="174">
+        <f>IF($W29=1,N($D29)*1E14+MIN(MAX(N($U29),0),9999)*1E10+MIN(N($K29),99999)*1E5+99999-MIN(ROW(),99999),"")</f>
         <v/>
       </c>
     </row>
@@ -8568,38 +8727,41 @@
         </is>
       </c>
       <c r="M30" s="168" t="n"/>
-      <c r="N30" s="169" t="inlineStr">
+      <c r="N30" s="169" t="n"/>
+      <c r="O30" s="166" t="n"/>
+      <c r="P30" s="166" t="n"/>
+      <c r="Q30" s="170" t="inlineStr">
         <is>
           <t>South Korea</t>
         </is>
       </c>
-      <c r="O30" s="167" t="n">
+      <c r="R30" s="167" t="n">
         <v>46318</v>
       </c>
-      <c r="P30" s="170" t="inlineStr">
+      <c r="S30" s="169" t="inlineStr">
         <is>
           <t>2026-Q4</t>
         </is>
       </c>
-      <c r="Q30" s="171" t="inlineStr">
+      <c r="T30" s="171" t="inlineStr">
         <is>
           <t>retaining wall, collapse</t>
         </is>
       </c>
-      <c r="R30" s="158" t="n">
+      <c r="U30" s="158" t="n">
         <v>5</v>
       </c>
-      <c r="S30" s="172" t="inlineStr">
+      <c r="V30" s="172" t="inlineStr">
         <is>
           <t>https://news.google.com/rss/articles/CBMikgFBVV95cUxPcTFMNDFOcFc5MjJHLWgxTldJbW9TT3doRG10TDRuSzlYNGNSSU5DOU1Razc0dkRYY0IyeVN1OHoyT3U2WG9wNUh5VW81UEd6anIwMDF1Ym1yQ3VlVk4wZ05saEh2VFFBMnZqOV9nbkFud0NMbWZ6NW9UU0pha0E3enQxdHQtU3JaNktBMlNxWTg2Zw?oc=5</t>
         </is>
       </c>
-      <c r="T30" s="173">
-        <f>IF($B30="",0,IF(AND(OR(OR(Dashboard!$B$5="All themes",Dashboard!$B$5=""),$C30=Dashboard!$B$5),OR(OR(Dashboard!$G$5="All uses",Dashboard!$G$5=""),$E30=Dashboard!$G$5),N($D30)&gt;=Lists!$H$2,OR(OR(Dashboard!$N$5="All windows",Dashboard!$N$5=""),$P30=Dashboard!$N$5)),1,0))</f>
-        <v/>
-      </c>
-      <c r="U30" s="174">
-        <f>IF($T30=1,N($D30)*1E14+MIN(MAX(N($R30),0),9999)*1E10+MIN(N($K30),99999)*1E5+99999-MIN(ROW(),99999),"")</f>
+      <c r="W30" s="173">
+        <f>IF($B30="",0,IF(AND(OR(OR(Dashboard!$B$5="All themes",Dashboard!$B$5=""),$C30=Dashboard!$B$5),OR(OR(Dashboard!$G$5="All uses",Dashboard!$G$5=""),$E30=Dashboard!$G$5),N($D30)&gt;=Lists!$H$2,OR(OR(Dashboard!$N$5="All windows",Dashboard!$N$5=""),$S30=Dashboard!$N$5)),1,0))</f>
+        <v/>
+      </c>
+      <c r="X30" s="174">
+        <f>IF($W30=1,N($D30)*1E14+MIN(MAX(N($U30),0),9999)*1E10+MIN(N($K30),99999)*1E5+99999-MIN(ROW(),99999),"")</f>
         <v/>
       </c>
     </row>
@@ -8651,38 +8813,41 @@
         </is>
       </c>
       <c r="M31" s="168" t="n"/>
-      <c r="N31" s="169" t="inlineStr">
+      <c r="N31" s="169" t="n"/>
+      <c r="O31" s="166" t="n"/>
+      <c r="P31" s="166" t="n"/>
+      <c r="Q31" s="170" t="inlineStr">
         <is>
           <t>Russia</t>
         </is>
       </c>
-      <c r="O31" s="167" t="n">
+      <c r="R31" s="167" t="n">
         <v>46317</v>
       </c>
-      <c r="P31" s="170" t="inlineStr">
+      <c r="S31" s="169" t="inlineStr">
         <is>
           <t>2026-Q4</t>
         </is>
       </c>
-      <c r="Q31" s="171" t="inlineStr">
+      <c r="T31" s="171" t="inlineStr">
         <is>
           <t>retaining wall, collapse</t>
         </is>
       </c>
-      <c r="R31" s="158" t="n">
+      <c r="U31" s="158" t="n">
         <v>5</v>
       </c>
-      <c r="S31" s="172" t="inlineStr">
+      <c r="V31" s="172" t="inlineStr">
         <is>
           <t>https://news.google.com/rss/articles/CBMiUkFVX3lxTFBBaDhzbmpCUVV6Y1lGN3hyYllJRGRHNkUta1M3SVpkamJ5MGktVWZHdDJqLWloWW40SmVzTldUSWc0UXliVXJOVWR2VmJoWUtGc0E?oc=5</t>
         </is>
       </c>
-      <c r="T31" s="173">
-        <f>IF($B31="",0,IF(AND(OR(OR(Dashboard!$B$5="All themes",Dashboard!$B$5=""),$C31=Dashboard!$B$5),OR(OR(Dashboard!$G$5="All uses",Dashboard!$G$5=""),$E31=Dashboard!$G$5),N($D31)&gt;=Lists!$H$2,OR(OR(Dashboard!$N$5="All windows",Dashboard!$N$5=""),$P31=Dashboard!$N$5)),1,0))</f>
-        <v/>
-      </c>
-      <c r="U31" s="174">
-        <f>IF($T31=1,N($D31)*1E14+MIN(MAX(N($R31),0),9999)*1E10+MIN(N($K31),99999)*1E5+99999-MIN(ROW(),99999),"")</f>
+      <c r="W31" s="173">
+        <f>IF($B31="",0,IF(AND(OR(OR(Dashboard!$B$5="All themes",Dashboard!$B$5=""),$C31=Dashboard!$B$5),OR(OR(Dashboard!$G$5="All uses",Dashboard!$G$5=""),$E31=Dashboard!$G$5),N($D31)&gt;=Lists!$H$2,OR(OR(Dashboard!$N$5="All windows",Dashboard!$N$5=""),$S31=Dashboard!$N$5)),1,0))</f>
+        <v/>
+      </c>
+      <c r="X31" s="174">
+        <f>IF($W31=1,N($D31)*1E14+MIN(MAX(N($U31),0),9999)*1E10+MIN(N($K31),99999)*1E5+99999-MIN(ROW(),99999),"")</f>
         <v/>
       </c>
     </row>
@@ -8734,38 +8899,41 @@
         </is>
       </c>
       <c r="M32" s="168" t="n"/>
-      <c r="N32" s="169" t="inlineStr">
+      <c r="N32" s="169" t="n"/>
+      <c r="O32" s="166" t="n"/>
+      <c r="P32" s="166" t="n"/>
+      <c r="Q32" s="170" t="inlineStr">
         <is>
           <t>Vietnam</t>
         </is>
       </c>
-      <c r="O32" s="167" t="n">
+      <c r="R32" s="167" t="n">
         <v>46318</v>
       </c>
-      <c r="P32" s="170" t="inlineStr">
+      <c r="S32" s="169" t="inlineStr">
         <is>
           <t>2026-Q4</t>
         </is>
       </c>
-      <c r="Q32" s="171" t="inlineStr">
+      <c r="T32" s="171" t="inlineStr">
         <is>
           <t>landslide, collapse</t>
         </is>
       </c>
-      <c r="R32" s="158" t="n">
+      <c r="U32" s="158" t="n">
         <v>5</v>
       </c>
-      <c r="S32" s="172" t="inlineStr">
+      <c r="V32" s="172" t="inlineStr">
         <is>
           <t>https://news.google.com/rss/articles/CBMihgFBVV95cUxNZlBjUzdTUHFfNm9fQnZtclVPRG1ZdWtERFVpMHRYYzRrTGV1alZYeU4yR240ZnM4bFZEMkhFMEtJbk1fakR3dzgyRm12YkZZdkpnTjE4UGNBR2otMlpsbkVpdDdGbXBPbUdYaU5ldjBqUnA1c1hwcFF4Yjl3NXVFcHRacHlTZw?oc=5</t>
         </is>
       </c>
-      <c r="T32" s="173">
-        <f>IF($B32="",0,IF(AND(OR(OR(Dashboard!$B$5="All themes",Dashboard!$B$5=""),$C32=Dashboard!$B$5),OR(OR(Dashboard!$G$5="All uses",Dashboard!$G$5=""),$E32=Dashboard!$G$5),N($D32)&gt;=Lists!$H$2,OR(OR(Dashboard!$N$5="All windows",Dashboard!$N$5=""),$P32=Dashboard!$N$5)),1,0))</f>
-        <v/>
-      </c>
-      <c r="U32" s="174">
-        <f>IF($T32=1,N($D32)*1E14+MIN(MAX(N($R32),0),9999)*1E10+MIN(N($K32),99999)*1E5+99999-MIN(ROW(),99999),"")</f>
+      <c r="W32" s="173">
+        <f>IF($B32="",0,IF(AND(OR(OR(Dashboard!$B$5="All themes",Dashboard!$B$5=""),$C32=Dashboard!$B$5),OR(OR(Dashboard!$G$5="All uses",Dashboard!$G$5=""),$E32=Dashboard!$G$5),N($D32)&gt;=Lists!$H$2,OR(OR(Dashboard!$N$5="All windows",Dashboard!$N$5=""),$S32=Dashboard!$N$5)),1,0))</f>
+        <v/>
+      </c>
+      <c r="X32" s="174">
+        <f>IF($W32=1,N($D32)*1E14+MIN(MAX(N($U32),0),9999)*1E10+MIN(N($K32),99999)*1E5+99999-MIN(ROW(),99999),"")</f>
         <v/>
       </c>
     </row>
@@ -8813,38 +8981,41 @@
       </c>
       <c r="L33" s="166" t="n"/>
       <c r="M33" s="168" t="n"/>
-      <c r="N33" s="169" t="inlineStr">
+      <c r="N33" s="169" t="n"/>
+      <c r="O33" s="166" t="n"/>
+      <c r="P33" s="166" t="n"/>
+      <c r="Q33" s="170" t="inlineStr">
         <is>
           <t>United Kingdom</t>
         </is>
       </c>
-      <c r="O33" s="167" t="n">
+      <c r="R33" s="167" t="n">
         <v>46317</v>
       </c>
-      <c r="P33" s="170" t="inlineStr">
+      <c r="S33" s="169" t="inlineStr">
         <is>
           <t>2026-Q4</t>
         </is>
       </c>
-      <c r="Q33" s="171" t="inlineStr">
+      <c r="T33" s="171" t="inlineStr">
         <is>
           <t>geotechnical</t>
         </is>
       </c>
-      <c r="R33" s="158" t="n">
+      <c r="U33" s="158" t="n">
         <v>5</v>
       </c>
-      <c r="S33" s="172" t="inlineStr">
+      <c r="V33" s="172" t="inlineStr">
         <is>
           <t>https://news.google.com/rss/articles/CBMibEFVX3lxTE9qd0p2T2p3a1lzbEg5TnFXNDZ2VXRhLWIzbGk1U0pnQlFCUk1RU2tqdFFXeEt4RkM3bThuVUUyelBfNHJMdlFmMThyZG9UakhLLTFqTGJBTDBKVmN1bXlqQmYyX1U3eHIyWTNfTw?oc=5</t>
         </is>
       </c>
-      <c r="T33" s="173">
-        <f>IF($B33="",0,IF(AND(OR(OR(Dashboard!$B$5="All themes",Dashboard!$B$5=""),$C33=Dashboard!$B$5),OR(OR(Dashboard!$G$5="All uses",Dashboard!$G$5=""),$E33=Dashboard!$G$5),N($D33)&gt;=Lists!$H$2,OR(OR(Dashboard!$N$5="All windows",Dashboard!$N$5=""),$P33=Dashboard!$N$5)),1,0))</f>
-        <v/>
-      </c>
-      <c r="U33" s="174">
-        <f>IF($T33=1,N($D33)*1E14+MIN(MAX(N($R33),0),9999)*1E10+MIN(N($K33),99999)*1E5+99999-MIN(ROW(),99999),"")</f>
+      <c r="W33" s="173">
+        <f>IF($B33="",0,IF(AND(OR(OR(Dashboard!$B$5="All themes",Dashboard!$B$5=""),$C33=Dashboard!$B$5),OR(OR(Dashboard!$G$5="All uses",Dashboard!$G$5=""),$E33=Dashboard!$G$5),N($D33)&gt;=Lists!$H$2,OR(OR(Dashboard!$N$5="All windows",Dashboard!$N$5=""),$S33=Dashboard!$N$5)),1,0))</f>
+        <v/>
+      </c>
+      <c r="X33" s="174">
+        <f>IF($W33=1,N($D33)*1E14+MIN(MAX(N($U33),0),9999)*1E10+MIN(N($K33),99999)*1E5+99999-MIN(ROW(),99999),"")</f>
         <v/>
       </c>
     </row>
@@ -8892,38 +9063,41 @@
       </c>
       <c r="L34" s="166" t="n"/>
       <c r="M34" s="168" t="n"/>
-      <c r="N34" s="169" t="inlineStr">
+      <c r="N34" s="169" t="n"/>
+      <c r="O34" s="166" t="n"/>
+      <c r="P34" s="166" t="n"/>
+      <c r="Q34" s="170" t="inlineStr">
         <is>
           <t>Colombia</t>
         </is>
       </c>
-      <c r="O34" s="167" t="n">
+      <c r="R34" s="167" t="n">
         <v>46318</v>
       </c>
-      <c r="P34" s="170" t="inlineStr">
+      <c r="S34" s="169" t="inlineStr">
         <is>
           <t>2026-Q4</t>
         </is>
       </c>
-      <c r="Q34" s="171" t="inlineStr">
+      <c r="T34" s="171" t="inlineStr">
         <is>
           <t>sinkhole</t>
         </is>
       </c>
-      <c r="R34" s="158" t="n">
+      <c r="U34" s="158" t="n">
         <v>4</v>
       </c>
-      <c r="S34" s="172" t="inlineStr">
+      <c r="V34" s="172" t="inlineStr">
         <is>
           <t>https://news.google.com/rss/articles/CBMilgFBVV95cUxPaWJCQW9La1Z3UklqdWVaNWVLV3l0TFplUEg0R3h5ZzBSNlJtZnpNb2FONml5V3FqbnJGTnZvQ2JZSllHZGRoX3NWR0l6Q0oyWE02RXlncnRfREVCa0xBRnVMTDNhcWRxLURrVTNJUEl5UkdlU0RtdU9UcUpVdVFzblQ0UmdOVlR0YTBfTVpDbjZud2p5d1E?oc=5</t>
         </is>
       </c>
-      <c r="T34" s="173">
-        <f>IF($B34="",0,IF(AND(OR(OR(Dashboard!$B$5="All themes",Dashboard!$B$5=""),$C34=Dashboard!$B$5),OR(OR(Dashboard!$G$5="All uses",Dashboard!$G$5=""),$E34=Dashboard!$G$5),N($D34)&gt;=Lists!$H$2,OR(OR(Dashboard!$N$5="All windows",Dashboard!$N$5=""),$P34=Dashboard!$N$5)),1,0))</f>
-        <v/>
-      </c>
-      <c r="U34" s="174">
-        <f>IF($T34=1,N($D34)*1E14+MIN(MAX(N($R34),0),9999)*1E10+MIN(N($K34),99999)*1E5+99999-MIN(ROW(),99999),"")</f>
+      <c r="W34" s="173">
+        <f>IF($B34="",0,IF(AND(OR(OR(Dashboard!$B$5="All themes",Dashboard!$B$5=""),$C34=Dashboard!$B$5),OR(OR(Dashboard!$G$5="All uses",Dashboard!$G$5=""),$E34=Dashboard!$G$5),N($D34)&gt;=Lists!$H$2,OR(OR(Dashboard!$N$5="All windows",Dashboard!$N$5=""),$S34=Dashboard!$N$5)),1,0))</f>
+        <v/>
+      </c>
+      <c r="X34" s="174">
+        <f>IF($W34=1,N($D34)*1E14+MIN(MAX(N($U34),0),9999)*1E10+MIN(N($K34),99999)*1E5+99999-MIN(ROW(),99999),"")</f>
         <v/>
       </c>
     </row>
@@ -8975,38 +9149,41 @@
         </is>
       </c>
       <c r="M35" s="168" t="n"/>
-      <c r="N35" s="169" t="inlineStr">
+      <c r="N35" s="169" t="n"/>
+      <c r="O35" s="166" t="n"/>
+      <c r="P35" s="166" t="n"/>
+      <c r="Q35" s="170" t="inlineStr">
         <is>
           <t>Colombia</t>
         </is>
       </c>
-      <c r="O35" s="167" t="n">
+      <c r="R35" s="167" t="n">
         <v>46317</v>
       </c>
-      <c r="P35" s="170" t="inlineStr">
+      <c r="S35" s="169" t="inlineStr">
         <is>
           <t>2026-Q4</t>
         </is>
       </c>
-      <c r="Q35" s="171" t="inlineStr">
+      <c r="T35" s="171" t="inlineStr">
         <is>
           <t>sinkhole</t>
         </is>
       </c>
-      <c r="R35" s="158" t="n">
+      <c r="U35" s="158" t="n">
         <v>4</v>
       </c>
-      <c r="S35" s="172" t="inlineStr">
+      <c r="V35" s="172" t="inlineStr">
         <is>
           <t>https://news.google.com/rss/articles/CBMi4gFBVV95cUxObEFsSlpBN09veGl1WXBBcWNHZFplTFFzQlIzSVZJUFVYdGdwcV9OZVY5TTBSM2JZbTdOd2liZFJyX3lscDU5VU1iVmZwaVU0bnZTSnk3ektFWm9QNEF4Y2ZMRldYdWVabGdKaW5yc21qQWxGNWcxOVZFNkRCLS14ZHpLc29Mel9vZENjazdLRWdMRm5uUEhob0pUS09pSVJEWXNjSlV4SE9ESFZyUVdEaENkUFpRTkt2SUZWb1FDRXAyMEd2LVhHTXhiODEwa3dwV1BvVXpQc2E3aUJXc1ZtQ3d30gHiAUFVX3lxTE5sQWxKWkE3T294aXVZcEFxY0dkWmVMUXNCUjNJVklQVVh0Z3BxX05lVjlNMFIzYlltN053aWJkUnJfeWxwNTlVTWJWZnBpVTRudlNKeTd6S0Vab1A0QXhjZkxGV1h1ZVpsZ0ppbnJzbWpBbEY1ZzE5VkU2REItLXhkektzb0x6X29kQ2NrN0tFZ0xGbm5QSGhvSlRLT2lJUkRZc2NKVXhIT0RIVnJRV0RoQ2RQWlFOS3ZJRlZvUUNFcDIwR3YtWEdNeGI4MTBrd3BXUG9VelBzYTdpQldzVm1Dd3c?oc=5</t>
         </is>
       </c>
-      <c r="T35" s="173">
-        <f>IF($B35="",0,IF(AND(OR(OR(Dashboard!$B$5="All themes",Dashboard!$B$5=""),$C35=Dashboard!$B$5),OR(OR(Dashboard!$G$5="All uses",Dashboard!$G$5=""),$E35=Dashboard!$G$5),N($D35)&gt;=Lists!$H$2,OR(OR(Dashboard!$N$5="All windows",Dashboard!$N$5=""),$P35=Dashboard!$N$5)),1,0))</f>
-        <v/>
-      </c>
-      <c r="U35" s="174">
-        <f>IF($T35=1,N($D35)*1E14+MIN(MAX(N($R35),0),9999)*1E10+MIN(N($K35),99999)*1E5+99999-MIN(ROW(),99999),"")</f>
+      <c r="W35" s="173">
+        <f>IF($B35="",0,IF(AND(OR(OR(Dashboard!$B$5="All themes",Dashboard!$B$5=""),$C35=Dashboard!$B$5),OR(OR(Dashboard!$G$5="All uses",Dashboard!$G$5=""),$E35=Dashboard!$G$5),N($D35)&gt;=Lists!$H$2,OR(OR(Dashboard!$N$5="All windows",Dashboard!$N$5=""),$S35=Dashboard!$N$5)),1,0))</f>
+        <v/>
+      </c>
+      <c r="X35" s="174">
+        <f>IF($W35=1,N($D35)*1E14+MIN(MAX(N($U35),0),9999)*1E10+MIN(N($K35),99999)*1E5+99999-MIN(ROW(),99999),"")</f>
         <v/>
       </c>
     </row>
@@ -9054,38 +9231,41 @@
       </c>
       <c r="L36" s="166" t="n"/>
       <c r="M36" s="168" t="n"/>
-      <c r="N36" s="169" t="inlineStr">
+      <c r="N36" s="169" t="n"/>
+      <c r="O36" s="166" t="n"/>
+      <c r="P36" s="166" t="n"/>
+      <c r="Q36" s="170" t="inlineStr">
         <is>
           <t>Colombia</t>
         </is>
       </c>
-      <c r="O36" s="167" t="n">
+      <c r="R36" s="167" t="n">
         <v>46318</v>
       </c>
-      <c r="P36" s="170" t="inlineStr">
+      <c r="S36" s="169" t="inlineStr">
         <is>
           <t>2026-Q4</t>
         </is>
       </c>
-      <c r="Q36" s="171" t="inlineStr">
+      <c r="T36" s="171" t="inlineStr">
         <is>
           <t>sinkhole</t>
         </is>
       </c>
-      <c r="R36" s="158" t="n">
+      <c r="U36" s="158" t="n">
         <v>4</v>
       </c>
-      <c r="S36" s="172" t="inlineStr">
+      <c r="V36" s="172" t="inlineStr">
         <is>
           <t>https://news.google.com/rss/articles/CBMijgFBVV95cUxORHhvYWNuVVRGRXIybWtsektBWDRYYkhhLWlYd2FwS0pBV2wzWklDdzN3UGxXLWZpa1ZLT0lWM0RZa1RXY0ZDRS1HYUdDV1RJU2dWWFpWalZ3cEhkaGJsYjk2WUZrWXQ3M2hXTWFVSGxSYjFhUzBOVlNnSUYxdVhtMGNBellTcmV4Q295SDJ3?oc=5</t>
         </is>
       </c>
-      <c r="T36" s="173">
-        <f>IF($B36="",0,IF(AND(OR(OR(Dashboard!$B$5="All themes",Dashboard!$B$5=""),$C36=Dashboard!$B$5),OR(OR(Dashboard!$G$5="All uses",Dashboard!$G$5=""),$E36=Dashboard!$G$5),N($D36)&gt;=Lists!$H$2,OR(OR(Dashboard!$N$5="All windows",Dashboard!$N$5=""),$P36=Dashboard!$N$5)),1,0))</f>
-        <v/>
-      </c>
-      <c r="U36" s="174">
-        <f>IF($T36=1,N($D36)*1E14+MIN(MAX(N($R36),0),9999)*1E10+MIN(N($K36),99999)*1E5+99999-MIN(ROW(),99999),"")</f>
+      <c r="W36" s="173">
+        <f>IF($B36="",0,IF(AND(OR(OR(Dashboard!$B$5="All themes",Dashboard!$B$5=""),$C36=Dashboard!$B$5),OR(OR(Dashboard!$G$5="All uses",Dashboard!$G$5=""),$E36=Dashboard!$G$5),N($D36)&gt;=Lists!$H$2,OR(OR(Dashboard!$N$5="All windows",Dashboard!$N$5=""),$S36=Dashboard!$N$5)),1,0))</f>
+        <v/>
+      </c>
+      <c r="X36" s="174">
+        <f>IF($W36=1,N($D36)*1E14+MIN(MAX(N($U36),0),9999)*1E10+MIN(N($K36),99999)*1E5+99999-MIN(ROW(),99999),"")</f>
         <v/>
       </c>
     </row>
@@ -9133,38 +9313,41 @@
       </c>
       <c r="L37" s="166" t="n"/>
       <c r="M37" s="168" t="n"/>
-      <c r="N37" s="169" t="inlineStr">
+      <c r="N37" s="169" t="n"/>
+      <c r="O37" s="166" t="n"/>
+      <c r="P37" s="166" t="n"/>
+      <c r="Q37" s="170" t="inlineStr">
         <is>
           <t>United Kingdom</t>
         </is>
       </c>
-      <c r="O37" s="167" t="n">
-        <v>46319</v>
-      </c>
-      <c r="P37" s="170" t="inlineStr">
+      <c r="R37" s="167" t="n">
+        <v>46319</v>
+      </c>
+      <c r="S37" s="169" t="inlineStr">
         <is>
           <t>2026-Q4</t>
         </is>
       </c>
-      <c r="Q37" s="171" t="inlineStr">
+      <c r="T37" s="171" t="inlineStr">
         <is>
           <t>sinkhole</t>
         </is>
       </c>
-      <c r="R37" s="158" t="n">
+      <c r="U37" s="158" t="n">
         <v>4</v>
       </c>
-      <c r="S37" s="172" t="inlineStr">
+      <c r="V37" s="172" t="inlineStr">
         <is>
           <t>https://news.google.com/rss/articles/CBMizAFBVV95cUxNd2dFendqYTRDcVVfLTVONjFFenlXV3pwTHVkVEJhb2ZfYzdKbF9XTDgxVXJqY1d4QWo3bi1CR250aUV6Y2FmQTktNUtTbU1FRnA2WUVzdFRiU2lRa3M1VzdwRUxzbWF0eUJmMER5Y2Yxb1V2aVdta0M4OGpjWmV6VGFnUVFLNjlQand3S3hSaTBFTUJZQ0JfNVBvZmF6NVpLSkdEMVlBLWt5VW5wYlhSOHBrdHVjU1FVMm41cW4tN0MwbTZ2Z2dULUZJemk?oc=5</t>
         </is>
       </c>
-      <c r="T37" s="173">
-        <f>IF($B37="",0,IF(AND(OR(OR(Dashboard!$B$5="All themes",Dashboard!$B$5=""),$C37=Dashboard!$B$5),OR(OR(Dashboard!$G$5="All uses",Dashboard!$G$5=""),$E37=Dashboard!$G$5),N($D37)&gt;=Lists!$H$2,OR(OR(Dashboard!$N$5="All windows",Dashboard!$N$5=""),$P37=Dashboard!$N$5)),1,0))</f>
-        <v/>
-      </c>
-      <c r="U37" s="174">
-        <f>IF($T37=1,N($D37)*1E14+MIN(MAX(N($R37),0),9999)*1E10+MIN(N($K37),99999)*1E5+99999-MIN(ROW(),99999),"")</f>
+      <c r="W37" s="173">
+        <f>IF($B37="",0,IF(AND(OR(OR(Dashboard!$B$5="All themes",Dashboard!$B$5=""),$C37=Dashboard!$B$5),OR(OR(Dashboard!$G$5="All uses",Dashboard!$G$5=""),$E37=Dashboard!$G$5),N($D37)&gt;=Lists!$H$2,OR(OR(Dashboard!$N$5="All windows",Dashboard!$N$5=""),$S37=Dashboard!$N$5)),1,0))</f>
+        <v/>
+      </c>
+      <c r="X37" s="174">
+        <f>IF($W37=1,N($D37)*1E14+MIN(MAX(N($U37),0),9999)*1E10+MIN(N($K37),99999)*1E5+99999-MIN(ROW(),99999),"")</f>
         <v/>
       </c>
     </row>
@@ -9216,38 +9399,41 @@
         </is>
       </c>
       <c r="M38" s="168" t="n"/>
-      <c r="N38" s="169" t="inlineStr">
+      <c r="N38" s="169" t="n"/>
+      <c r="O38" s="166" t="n"/>
+      <c r="P38" s="166" t="n"/>
+      <c r="Q38" s="170" t="inlineStr">
         <is>
           <t>Colombia</t>
         </is>
       </c>
-      <c r="O38" s="167" t="n">
+      <c r="R38" s="167" t="n">
         <v>46317</v>
       </c>
-      <c r="P38" s="170" t="inlineStr">
+      <c r="S38" s="169" t="inlineStr">
         <is>
           <t>2026-Q4</t>
         </is>
       </c>
-      <c r="Q38" s="171" t="inlineStr">
+      <c r="T38" s="171" t="inlineStr">
         <is>
           <t>sinkhole</t>
         </is>
       </c>
-      <c r="R38" s="158" t="n">
+      <c r="U38" s="158" t="n">
         <v>4</v>
       </c>
-      <c r="S38" s="172" t="inlineStr">
+      <c r="V38" s="172" t="inlineStr">
         <is>
           <t>https://news.google.com/rss/articles/CBMi8wFBVV95cUxNNlBCakVVSHBHTXI5UXNfdFF4SmtBTHZaWWhZaF9TYklINTZFZVpuNHlSbE5HNHBIUmJyd1BQSlJtamZ1ZGxBU1lxVmVib2RHRVFPRmszbmFtWVNxenlGeVk2TGRpaXJRNUdPbklLUXRCY1E1ZGhhQVB2Q0pHSU9VMTZJMkVfRnh2ZHJ3V3JJTmtqUDhUX1lMMk1GX3IxVGRDY0VNbHpmY0pWcmJVN1p6eWFzLWQ5ZmdoOEZrRXBNRHNaRDFlYkpXdDZORU5iek80RHBwUzdBb1A3OF9DTExya013WnpwYTRuWjJLeFhXc3ZCUlk?oc=5</t>
         </is>
       </c>
-      <c r="T38" s="173">
-        <f>IF($B38="",0,IF(AND(OR(OR(Dashboard!$B$5="All themes",Dashboard!$B$5=""),$C38=Dashboard!$B$5),OR(OR(Dashboard!$G$5="All uses",Dashboard!$G$5=""),$E38=Dashboard!$G$5),N($D38)&gt;=Lists!$H$2,OR(OR(Dashboard!$N$5="All windows",Dashboard!$N$5=""),$P38=Dashboard!$N$5)),1,0))</f>
-        <v/>
-      </c>
-      <c r="U38" s="174">
-        <f>IF($T38=1,N($D38)*1E14+MIN(MAX(N($R38),0),9999)*1E10+MIN(N($K38),99999)*1E5+99999-MIN(ROW(),99999),"")</f>
+      <c r="W38" s="173">
+        <f>IF($B38="",0,IF(AND(OR(OR(Dashboard!$B$5="All themes",Dashboard!$B$5=""),$C38=Dashboard!$B$5),OR(OR(Dashboard!$G$5="All uses",Dashboard!$G$5=""),$E38=Dashboard!$G$5),N($D38)&gt;=Lists!$H$2,OR(OR(Dashboard!$N$5="All windows",Dashboard!$N$5=""),$S38=Dashboard!$N$5)),1,0))</f>
+        <v/>
+      </c>
+      <c r="X38" s="174">
+        <f>IF($W38=1,N($D38)*1E14+MIN(MAX(N($U38),0),9999)*1E10+MIN(N($K38),99999)*1E5+99999-MIN(ROW(),99999),"")</f>
         <v/>
       </c>
     </row>
@@ -9299,38 +9485,41 @@
         </is>
       </c>
       <c r="M39" s="168" t="n"/>
-      <c r="N39" s="169" t="inlineStr">
+      <c r="N39" s="169" t="n"/>
+      <c r="O39" s="166" t="n"/>
+      <c r="P39" s="166" t="n"/>
+      <c r="Q39" s="170" t="inlineStr">
         <is>
           <t>Colombia</t>
         </is>
       </c>
-      <c r="O39" s="167" t="n">
+      <c r="R39" s="167" t="n">
         <v>46318</v>
       </c>
-      <c r="P39" s="170" t="inlineStr">
+      <c r="S39" s="169" t="inlineStr">
         <is>
           <t>2026-Q4</t>
         </is>
       </c>
-      <c r="Q39" s="171" t="inlineStr">
+      <c r="T39" s="171" t="inlineStr">
         <is>
           <t>sinkhole</t>
         </is>
       </c>
-      <c r="R39" s="158" t="n">
+      <c r="U39" s="158" t="n">
         <v>4</v>
       </c>
-      <c r="S39" s="172" t="inlineStr">
+      <c r="V39" s="172" t="inlineStr">
         <is>
           <t>https://news.google.com/rss/articles/CBMi6AJBVV95cUxPTTNxbUF2ODR0d0dfM2ZBb3B0Y0lvRElsVjNPbk1aV0JSMF9SeHFfbGk1cFNVTTZ2TjhlTW5ldEVCcmVmdHNSM0xxN0hIbjFveHdxdVBJSl9FLUNDOUJ6a0tWcy1SQTltUWJuUHl3SDNmbzlEc2NSWW5JemxmOVJidVZBUjhwYUV2NTc1cnBKUkw4Zlg4bzJlbkJaTzA3Y1Rvel9zbVFEZ1lRVUdsaTNRLU9YZG9RbXZLcXZTQ3BaUXJLcV9BMlYxRU9DZl91YVV6OExlSnU4bnh5V0wxVWVvV29jWVdlQ2x5dTVXT202T1JTek5nbEhkdkZlMHFPd3UxZ0hUdXl0cVUxYXBybmNNcmFkS0VmeGhhNDc1V3dMRGpQelpZSDZGaFZIRnpFVGRKZTV3VURCTkNaMW5WZnpGcUd2VjlsZzd0VjJRa1BCUE1IWXNCSHZ5VHNrQlhUZUlFWjYxWHpmbzPSAfwCQVVfeXFMUEN6dkx4WFpjY3ozMFFuZnZiNEc4ZFlsSUNhemhCMXdKQi1DbEhMS1gwdzBwZTBjME9ZdjJaX2FhM0JmcWx5MnNDMHNsZC1iTDBkbmdjZHhLZjZaSVBfWGZZUmVONnpWU0RucGM4a0lKNjVsWVdyd1BJMG1mdm5lRHMyU3lhTW84am52eVJTMjNzZ2duTGpScGN0NlA0QkdBV1hTV3E0WllEc182YXE1Y1lvOUhEWHhNUXpRcHRfbGtXZFFReXZXSnE1Z3MtVWc2YXNfT0JWLW1OSkRaYWJrdWtiRU9JRU1EQjUwcTNSem1obGNocHYyV2pLQVhlbGJBZDM1RGx2UkNJVUY0VV9jR1VBZUtGOEs1OVdOQzVkZU1sYVU4RkpxSkNpdUpyeS10QmZiX0xwSUs2U0FFd0JFckY1SElKZEptMHhwUklKN0YwekFCTkpFLXRuZjBmUFpYc3pGWVQtMG9uajhwOXlUN295QllOaE9tazdSbEc?oc=5</t>
         </is>
       </c>
-      <c r="T39" s="173">
-        <f>IF($B39="",0,IF(AND(OR(OR(Dashboard!$B$5="All themes",Dashboard!$B$5=""),$C39=Dashboard!$B$5),OR(OR(Dashboard!$G$5="All uses",Dashboard!$G$5=""),$E39=Dashboard!$G$5),N($D39)&gt;=Lists!$H$2,OR(OR(Dashboard!$N$5="All windows",Dashboard!$N$5=""),$P39=Dashboard!$N$5)),1,0))</f>
-        <v/>
-      </c>
-      <c r="U39" s="174">
-        <f>IF($T39=1,N($D39)*1E14+MIN(MAX(N($R39),0),9999)*1E10+MIN(N($K39),99999)*1E5+99999-MIN(ROW(),99999),"")</f>
+      <c r="W39" s="173">
+        <f>IF($B39="",0,IF(AND(OR(OR(Dashboard!$B$5="All themes",Dashboard!$B$5=""),$C39=Dashboard!$B$5),OR(OR(Dashboard!$G$5="All uses",Dashboard!$G$5=""),$E39=Dashboard!$G$5),N($D39)&gt;=Lists!$H$2,OR(OR(Dashboard!$N$5="All windows",Dashboard!$N$5=""),$S39=Dashboard!$N$5)),1,0))</f>
+        <v/>
+      </c>
+      <c r="X39" s="174">
+        <f>IF($W39=1,N($D39)*1E14+MIN(MAX(N($U39),0),9999)*1E10+MIN(N($K39),99999)*1E5+99999-MIN(ROW(),99999),"")</f>
         <v/>
       </c>
     </row>
@@ -9382,38 +9571,41 @@
         </is>
       </c>
       <c r="M40" s="168" t="n"/>
-      <c r="N40" s="169" t="inlineStr">
+      <c r="N40" s="169" t="n"/>
+      <c r="O40" s="166" t="n"/>
+      <c r="P40" s="166" t="n"/>
+      <c r="Q40" s="170" t="inlineStr">
         <is>
           <t>Colombia</t>
         </is>
       </c>
-      <c r="O40" s="167" t="n">
-        <v>46319</v>
-      </c>
-      <c r="P40" s="170" t="inlineStr">
+      <c r="R40" s="167" t="n">
+        <v>46319</v>
+      </c>
+      <c r="S40" s="169" t="inlineStr">
         <is>
           <t>2026-Q4</t>
         </is>
       </c>
-      <c r="Q40" s="171" t="inlineStr">
+      <c r="T40" s="171" t="inlineStr">
         <is>
           <t>sinkhole</t>
         </is>
       </c>
-      <c r="R40" s="158" t="n">
+      <c r="U40" s="158" t="n">
         <v>4</v>
       </c>
-      <c r="S40" s="172" t="inlineStr">
+      <c r="V40" s="172" t="inlineStr">
         <is>
           <t>https://news.google.com/rss/articles/CBMi5AFBVV95cUxQN2dkNUMtV1kwNUFwMFA0VWRsUmN6Q3RhTDhyTWtHODFmSHhEWWdtT0Jwazg3Nk54S0ZnRF82OHpybVI2OVhIbkp0c1dQX3N1Ny1OTkZhR2hHQUMzYXJfT3BzX3I2Y3d6WndQNno2QTloWDFESzVxUTRMZDZOSDNQUzJYVTBsTks2Mll4SjZRYkZxbWxjOHByeGVkUkg5d1d3UWxmQUtBTG1lWDRTMGNOQWZnRGRtR3c4a2xiRUFHY3laMDJzX0VYUk9GZkR2akQ3bkNKeGU1aVYwb1F0WE14WVVVQ0bSAYwBQVVfeXFMT2I5Zk9zQW9sMnMteVFacFllV19JRWVQT0JfUGNTSTJ0R2FLYmpjTEhkQ3EzWTVmRDRWUWxJcTF3WmxDNnJIaUV2amNuNm5sSTJJV08wb184aWR0czBDRm5qdnN5WEM3ak5zQl9mendjUDhHaU0tbzVjQTNwY1dzNUUxT3pVU3kxeVpXa2k?oc=5</t>
         </is>
       </c>
-      <c r="T40" s="173">
-        <f>IF($B40="",0,IF(AND(OR(OR(Dashboard!$B$5="All themes",Dashboard!$B$5=""),$C40=Dashboard!$B$5),OR(OR(Dashboard!$G$5="All uses",Dashboard!$G$5=""),$E40=Dashboard!$G$5),N($D40)&gt;=Lists!$H$2,OR(OR(Dashboard!$N$5="All windows",Dashboard!$N$5=""),$P40=Dashboard!$N$5)),1,0))</f>
-        <v/>
-      </c>
-      <c r="U40" s="174">
-        <f>IF($T40=1,N($D40)*1E14+MIN(MAX(N($R40),0),9999)*1E10+MIN(N($K40),99999)*1E5+99999-MIN(ROW(),99999),"")</f>
+      <c r="W40" s="173">
+        <f>IF($B40="",0,IF(AND(OR(OR(Dashboard!$B$5="All themes",Dashboard!$B$5=""),$C40=Dashboard!$B$5),OR(OR(Dashboard!$G$5="All uses",Dashboard!$G$5=""),$E40=Dashboard!$G$5),N($D40)&gt;=Lists!$H$2,OR(OR(Dashboard!$N$5="All windows",Dashboard!$N$5=""),$S40=Dashboard!$N$5)),1,0))</f>
+        <v/>
+      </c>
+      <c r="X40" s="174">
+        <f>IF($W40=1,N($D40)*1E14+MIN(MAX(N($U40),0),9999)*1E10+MIN(N($K40),99999)*1E5+99999-MIN(ROW(),99999),"")</f>
         <v/>
       </c>
     </row>
@@ -9465,38 +9657,41 @@
         </is>
       </c>
       <c r="M41" s="168" t="n"/>
-      <c r="N41" s="169" t="inlineStr">
+      <c r="N41" s="169" t="n"/>
+      <c r="O41" s="166" t="n"/>
+      <c r="P41" s="166" t="n"/>
+      <c r="Q41" s="170" t="inlineStr">
         <is>
           <t>Colombia</t>
         </is>
       </c>
-      <c r="O41" s="167" t="n">
+      <c r="R41" s="167" t="n">
         <v>46317</v>
       </c>
-      <c r="P41" s="170" t="inlineStr">
+      <c r="S41" s="169" t="inlineStr">
         <is>
           <t>2026-Q4</t>
         </is>
       </c>
-      <c r="Q41" s="171" t="inlineStr">
+      <c r="T41" s="171" t="inlineStr">
         <is>
           <t>sinkhole</t>
         </is>
       </c>
-      <c r="R41" s="158" t="n">
+      <c r="U41" s="158" t="n">
         <v>4</v>
       </c>
-      <c r="S41" s="172" t="inlineStr">
+      <c r="V41" s="172" t="inlineStr">
         <is>
           <t>https://news.google.com/rss/articles/CBMi7AFBVV95cUxON0hLN3oxMFdMX0dlRUtVNHhVQ2Y2Nk00NHlEUUVSb1N0bmRXakNHcUNOcFcyVWl1UXp1Wm5ObjE1X0RDdThWSWJZazE2WVA5MTR0ckM0OV9BeHVOUFoySjUyRFdrN1FiVDVzd253R0JKSE9yN3ZzN0NHS1hJSGwxNmVQUzVyZlNsbURWQ3ZBdktrTkdYWElFcVBpVm5FU3pFeGZpNkl4V08zMkpGOTM2R0czXzJVS1NTcXBGcnViOXZmTmJJRFJkNXpSUTNEanFWeWpDdU9xbE9mVXFndU1zNVh2TC0zcHpuWEcwcg?oc=5</t>
         </is>
       </c>
-      <c r="T41" s="173">
-        <f>IF($B41="",0,IF(AND(OR(OR(Dashboard!$B$5="All themes",Dashboard!$B$5=""),$C41=Dashboard!$B$5),OR(OR(Dashboard!$G$5="All uses",Dashboard!$G$5=""),$E41=Dashboard!$G$5),N($D41)&gt;=Lists!$H$2,OR(OR(Dashboard!$N$5="All windows",Dashboard!$N$5=""),$P41=Dashboard!$N$5)),1,0))</f>
-        <v/>
-      </c>
-      <c r="U41" s="174">
-        <f>IF($T41=1,N($D41)*1E14+MIN(MAX(N($R41),0),9999)*1E10+MIN(N($K41),99999)*1E5+99999-MIN(ROW(),99999),"")</f>
+      <c r="W41" s="173">
+        <f>IF($B41="",0,IF(AND(OR(OR(Dashboard!$B$5="All themes",Dashboard!$B$5=""),$C41=Dashboard!$B$5),OR(OR(Dashboard!$G$5="All uses",Dashboard!$G$5=""),$E41=Dashboard!$G$5),N($D41)&gt;=Lists!$H$2,OR(OR(Dashboard!$N$5="All windows",Dashboard!$N$5=""),$S41=Dashboard!$N$5)),1,0))</f>
+        <v/>
+      </c>
+      <c r="X41" s="174">
+        <f>IF($W41=1,N($D41)*1E14+MIN(MAX(N($U41),0),9999)*1E10+MIN(N($K41),99999)*1E5+99999-MIN(ROW(),99999),"")</f>
         <v/>
       </c>
     </row>
@@ -9548,34 +9743,37 @@
         </is>
       </c>
       <c r="M42" s="168" t="n"/>
-      <c r="N42" s="169" t="inlineStr">
+      <c r="N42" s="169" t="n"/>
+      <c r="O42" s="166" t="n"/>
+      <c r="P42" s="166" t="n"/>
+      <c r="Q42" s="170" t="inlineStr">
         <is>
           <t>Egypt</t>
         </is>
       </c>
-      <c r="O42" s="167" t="n">
-        <v>46319</v>
-      </c>
-      <c r="P42" s="170" t="inlineStr">
+      <c r="R42" s="167" t="n">
+        <v>46319</v>
+      </c>
+      <c r="S42" s="169" t="inlineStr">
         <is>
           <t>2026-Q4</t>
         </is>
       </c>
-      <c r="Q42" s="171" t="n"/>
-      <c r="R42" s="158" t="n">
+      <c r="T42" s="171" t="n"/>
+      <c r="U42" s="158" t="n">
         <v>0</v>
       </c>
-      <c r="S42" s="172" t="inlineStr">
+      <c r="V42" s="172" t="inlineStr">
         <is>
           <t>https://news.google.com/rss/articles/CBMijAFBVV95cUxOLWcwOXFBTWY2NnVDYW5EVi1yMldxeWpKd3NNTjB6SjMtS2FFRjBYQUd6ek1FYkVnVndOX0J3YXk1a3dVZW9KRWFCaV9KaHc4a25tdDBTWmFXc2hnU09sWEtNb2gxVjFhQ3RJaEJpVWhURWowRjNwVlV6ZG9RWVRlb1lpYXBrUV9YU0dDOQ?oc=5</t>
         </is>
       </c>
-      <c r="T42" s="173">
-        <f>IF($B42="",0,IF(AND(OR(OR(Dashboard!$B$5="All themes",Dashboard!$B$5=""),$C42=Dashboard!$B$5),OR(OR(Dashboard!$G$5="All uses",Dashboard!$G$5=""),$E42=Dashboard!$G$5),N($D42)&gt;=Lists!$H$2,OR(OR(Dashboard!$N$5="All windows",Dashboard!$N$5=""),$P42=Dashboard!$N$5)),1,0))</f>
-        <v/>
-      </c>
-      <c r="U42" s="174">
-        <f>IF($T42=1,N($D42)*1E14+MIN(MAX(N($R42),0),9999)*1E10+MIN(N($K42),99999)*1E5+99999-MIN(ROW(),99999),"")</f>
+      <c r="W42" s="173">
+        <f>IF($B42="",0,IF(AND(OR(OR(Dashboard!$B$5="All themes",Dashboard!$B$5=""),$C42=Dashboard!$B$5),OR(OR(Dashboard!$G$5="All uses",Dashboard!$G$5=""),$E42=Dashboard!$G$5),N($D42)&gt;=Lists!$H$2,OR(OR(Dashboard!$N$5="All windows",Dashboard!$N$5=""),$S42=Dashboard!$N$5)),1,0))</f>
+        <v/>
+      </c>
+      <c r="X42" s="174">
+        <f>IF($W42=1,N($D42)*1E14+MIN(MAX(N($U42),0),9999)*1E10+MIN(N($K42),99999)*1E5+99999-MIN(ROW(),99999),"")</f>
         <v/>
       </c>
     </row>
@@ -9627,34 +9825,37 @@
         </is>
       </c>
       <c r="M43" s="168" t="n"/>
-      <c r="N43" s="169" t="inlineStr">
+      <c r="N43" s="169" t="n"/>
+      <c r="O43" s="166" t="n"/>
+      <c r="P43" s="166" t="n"/>
+      <c r="Q43" s="170" t="inlineStr">
         <is>
           <t>China</t>
         </is>
       </c>
-      <c r="O43" s="167" t="n">
+      <c r="R43" s="167" t="n">
         <v>46318</v>
       </c>
-      <c r="P43" s="170" t="inlineStr">
+      <c r="S43" s="169" t="inlineStr">
         <is>
           <t>2026-Q4</t>
         </is>
       </c>
-      <c r="Q43" s="171" t="n"/>
-      <c r="R43" s="158" t="n">
+      <c r="T43" s="171" t="n"/>
+      <c r="U43" s="158" t="n">
         <v>0</v>
       </c>
-      <c r="S43" s="172" t="inlineStr">
+      <c r="V43" s="172" t="inlineStr">
         <is>
           <t>https://news.google.com/rss/articles/CBMibkFVX3lxTE5PclBzMHZTYkNxbkRYVWFacWgzMjRTdE1JdmNYSi1xbTlBaVZLRTVjTHpCTlQ4c2lEQ2xoMk9kcEdROGxBOFI4Zk9YV3JGSXdUZDg1blVlelJzbU54VjkzTkUySEV5Z2x2aHY5R0xB?oc=5</t>
         </is>
       </c>
-      <c r="T43" s="173">
-        <f>IF($B43="",0,IF(AND(OR(OR(Dashboard!$B$5="All themes",Dashboard!$B$5=""),$C43=Dashboard!$B$5),OR(OR(Dashboard!$G$5="All uses",Dashboard!$G$5=""),$E43=Dashboard!$G$5),N($D43)&gt;=Lists!$H$2,OR(OR(Dashboard!$N$5="All windows",Dashboard!$N$5=""),$P43=Dashboard!$N$5)),1,0))</f>
-        <v/>
-      </c>
-      <c r="U43" s="174">
-        <f>IF($T43=1,N($D43)*1E14+MIN(MAX(N($R43),0),9999)*1E10+MIN(N($K43),99999)*1E5+99999-MIN(ROW(),99999),"")</f>
+      <c r="W43" s="173">
+        <f>IF($B43="",0,IF(AND(OR(OR(Dashboard!$B$5="All themes",Dashboard!$B$5=""),$C43=Dashboard!$B$5),OR(OR(Dashboard!$G$5="All uses",Dashboard!$G$5=""),$E43=Dashboard!$G$5),N($D43)&gt;=Lists!$H$2,OR(OR(Dashboard!$N$5="All windows",Dashboard!$N$5=""),$S43=Dashboard!$N$5)),1,0))</f>
+        <v/>
+      </c>
+      <c r="X43" s="174">
+        <f>IF($W43=1,N($D43)*1E14+MIN(MAX(N($U43),0),9999)*1E10+MIN(N($K43),99999)*1E5+99999-MIN(ROW(),99999),"")</f>
         <v/>
       </c>
     </row>
@@ -9706,34 +9907,37 @@
         </is>
       </c>
       <c r="M44" s="168" t="n"/>
-      <c r="N44" s="169" t="inlineStr">
+      <c r="N44" s="169" t="n"/>
+      <c r="O44" s="166" t="n"/>
+      <c r="P44" s="166" t="n"/>
+      <c r="Q44" s="170" t="inlineStr">
         <is>
           <t>Egypt</t>
         </is>
       </c>
-      <c r="O44" s="167" t="n">
+      <c r="R44" s="167" t="n">
         <v>46318</v>
       </c>
-      <c r="P44" s="170" t="inlineStr">
+      <c r="S44" s="169" t="inlineStr">
         <is>
           <t>2026-Q4</t>
         </is>
       </c>
-      <c r="Q44" s="171" t="n"/>
-      <c r="R44" s="158" t="n">
+      <c r="T44" s="171" t="n"/>
+      <c r="U44" s="158" t="n">
         <v>0</v>
       </c>
-      <c r="S44" s="172" t="inlineStr">
+      <c r="V44" s="172" t="inlineStr">
         <is>
           <t>https://news.google.com/rss/articles/CBMic0FVX3lxTE85MmNnNDd2QkUzaFV4QTZmTmJXNTAzbUZfMjdpdlNaSjEyODN0eW51ZUp0RzE3SHY2NzRuQlZtOHdtcnFQLWlBOGQ5eVQ3QTU1REJMWTRvZm1qTFZHZWZ0ZU9WTGRiYkhJNGVEaEliZW9GZWc?oc=5</t>
         </is>
       </c>
-      <c r="T44" s="173">
-        <f>IF($B44="",0,IF(AND(OR(OR(Dashboard!$B$5="All themes",Dashboard!$B$5=""),$C44=Dashboard!$B$5),OR(OR(Dashboard!$G$5="All uses",Dashboard!$G$5=""),$E44=Dashboard!$G$5),N($D44)&gt;=Lists!$H$2,OR(OR(Dashboard!$N$5="All windows",Dashboard!$N$5=""),$P44=Dashboard!$N$5)),1,0))</f>
-        <v/>
-      </c>
-      <c r="U44" s="174">
-        <f>IF($T44=1,N($D44)*1E14+MIN(MAX(N($R44),0),9999)*1E10+MIN(N($K44),99999)*1E5+99999-MIN(ROW(),99999),"")</f>
+      <c r="W44" s="173">
+        <f>IF($B44="",0,IF(AND(OR(OR(Dashboard!$B$5="All themes",Dashboard!$B$5=""),$C44=Dashboard!$B$5),OR(OR(Dashboard!$G$5="All uses",Dashboard!$G$5=""),$E44=Dashboard!$G$5),N($D44)&gt;=Lists!$H$2,OR(OR(Dashboard!$N$5="All windows",Dashboard!$N$5=""),$S44=Dashboard!$N$5)),1,0))</f>
+        <v/>
+      </c>
+      <c r="X44" s="174">
+        <f>IF($W44=1,N($D44)*1E14+MIN(MAX(N($U44),0),9999)*1E10+MIN(N($K44),99999)*1E5+99999-MIN(ROW(),99999),"")</f>
         <v/>
       </c>
     </row>
@@ -9785,34 +9989,37 @@
         </is>
       </c>
       <c r="M45" s="168" t="n"/>
-      <c r="N45" s="169" t="inlineStr">
+      <c r="N45" s="169" t="n"/>
+      <c r="O45" s="166" t="n"/>
+      <c r="P45" s="166" t="n"/>
+      <c r="Q45" s="170" t="inlineStr">
         <is>
           <t>Vietnam</t>
         </is>
       </c>
-      <c r="O45" s="167" t="n">
+      <c r="R45" s="167" t="n">
         <v>46318</v>
       </c>
-      <c r="P45" s="170" t="inlineStr">
+      <c r="S45" s="169" t="inlineStr">
         <is>
           <t>2026-Q4</t>
         </is>
       </c>
-      <c r="Q45" s="171" t="n"/>
-      <c r="R45" s="158" t="n">
+      <c r="T45" s="171" t="n"/>
+      <c r="U45" s="158" t="n">
         <v>0</v>
       </c>
-      <c r="S45" s="172" t="inlineStr">
+      <c r="V45" s="172" t="inlineStr">
         <is>
           <t>https://news.google.com/rss/articles/CBMivgFBVV95cUxOeUJHRExHRm0xT2ZMLXFqWWFjaXRUWDFrY2FpaDdYc3dlVy1tYy1GQ1hZSDk1OFZFVElOOU5NMVVia21KM2xPSUhWdnk3ZHRkTWV1emJBZkhQclp3aUtiUzRiX0dVZUZhaGRpUWlJUE8tUmhha1ZLUS1TRGM2dGlxRWJ2UWFkNGNsakZ6S1NTMWw0NGp0V0Zlc0xXTzBTRkJKaGZPT2tNcExKRHBaZXN2U3pIMkVKNTRVdy1mUkxB?oc=5</t>
         </is>
       </c>
-      <c r="T45" s="173">
-        <f>IF($B45="",0,IF(AND(OR(OR(Dashboard!$B$5="All themes",Dashboard!$B$5=""),$C45=Dashboard!$B$5),OR(OR(Dashboard!$G$5="All uses",Dashboard!$G$5=""),$E45=Dashboard!$G$5),N($D45)&gt;=Lists!$H$2,OR(OR(Dashboard!$N$5="All windows",Dashboard!$N$5=""),$P45=Dashboard!$N$5)),1,0))</f>
-        <v/>
-      </c>
-      <c r="U45" s="174">
-        <f>IF($T45=1,N($D45)*1E14+MIN(MAX(N($R45),0),9999)*1E10+MIN(N($K45),99999)*1E5+99999-MIN(ROW(),99999),"")</f>
+      <c r="W45" s="173">
+        <f>IF($B45="",0,IF(AND(OR(OR(Dashboard!$B$5="All themes",Dashboard!$B$5=""),$C45=Dashboard!$B$5),OR(OR(Dashboard!$G$5="All uses",Dashboard!$G$5=""),$E45=Dashboard!$G$5),N($D45)&gt;=Lists!$H$2,OR(OR(Dashboard!$N$5="All windows",Dashboard!$N$5=""),$S45=Dashboard!$N$5)),1,0))</f>
+        <v/>
+      </c>
+      <c r="X45" s="174">
+        <f>IF($W45=1,N($D45)*1E14+MIN(MAX(N($U45),0),9999)*1E10+MIN(N($K45),99999)*1E5+99999-MIN(ROW(),99999),"")</f>
         <v/>
       </c>
     </row>
@@ -9864,34 +10071,37 @@
         </is>
       </c>
       <c r="M46" s="168" t="n"/>
-      <c r="N46" s="169" t="inlineStr">
+      <c r="N46" s="169" t="n"/>
+      <c r="O46" s="166" t="n"/>
+      <c r="P46" s="166" t="n"/>
+      <c r="Q46" s="170" t="inlineStr">
         <is>
           <t>Vietnam</t>
         </is>
       </c>
-      <c r="O46" s="167" t="n">
+      <c r="R46" s="167" t="n">
         <v>46318</v>
       </c>
-      <c r="P46" s="170" t="inlineStr">
+      <c r="S46" s="169" t="inlineStr">
         <is>
           <t>2026-Q4</t>
         </is>
       </c>
-      <c r="Q46" s="171" t="n"/>
-      <c r="R46" s="158" t="n">
+      <c r="T46" s="171" t="n"/>
+      <c r="U46" s="158" t="n">
         <v>0</v>
       </c>
-      <c r="S46" s="172" t="inlineStr">
+      <c r="V46" s="172" t="inlineStr">
         <is>
           <t>https://news.google.com/rss/articles/CBMioAFBVV95cUxQdGo5XzZaLXUtaGVxUE5qb0ltRENoMjhVWlN4b0dqZFpPREJTNGw4Rld2bmtEX2VnSlB4TkJYVkxPUjdzZXYxZ2tWOG5kaWpUSFF1UGRjaUNKY3NOTkpVeFZpOFhMOW1QYkZIQXZ0ZTV4NjBseUVBYzdBdDNPTGNtc0pMRXFSWWM0SmVhS05Ld2hVemp5bHdkX290ZFltU3NC?oc=5</t>
         </is>
       </c>
-      <c r="T46" s="173">
-        <f>IF($B46="",0,IF(AND(OR(OR(Dashboard!$B$5="All themes",Dashboard!$B$5=""),$C46=Dashboard!$B$5),OR(OR(Dashboard!$G$5="All uses",Dashboard!$G$5=""),$E46=Dashboard!$G$5),N($D46)&gt;=Lists!$H$2,OR(OR(Dashboard!$N$5="All windows",Dashboard!$N$5=""),$P46=Dashboard!$N$5)),1,0))</f>
-        <v/>
-      </c>
-      <c r="U46" s="174">
-        <f>IF($T46=1,N($D46)*1E14+MIN(MAX(N($R46),0),9999)*1E10+MIN(N($K46),99999)*1E5+99999-MIN(ROW(),99999),"")</f>
+      <c r="W46" s="173">
+        <f>IF($B46="",0,IF(AND(OR(OR(Dashboard!$B$5="All themes",Dashboard!$B$5=""),$C46=Dashboard!$B$5),OR(OR(Dashboard!$G$5="All uses",Dashboard!$G$5=""),$E46=Dashboard!$G$5),N($D46)&gt;=Lists!$H$2,OR(OR(Dashboard!$N$5="All windows",Dashboard!$N$5=""),$S46=Dashboard!$N$5)),1,0))</f>
+        <v/>
+      </c>
+      <c r="X46" s="174">
+        <f>IF($W46=1,N($D46)*1E14+MIN(MAX(N($U46),0),9999)*1E10+MIN(N($K46),99999)*1E5+99999-MIN(ROW(),99999),"")</f>
         <v/>
       </c>
     </row>
@@ -9944,33 +10154,36 @@
         </is>
       </c>
       <c r="N47" s="169" t="n"/>
-      <c r="O47" s="167" t="n">
+      <c r="O47" s="166" t="n"/>
+      <c r="P47" s="166" t="n"/>
+      <c r="Q47" s="170" t="n"/>
+      <c r="R47" s="167" t="n">
         <v>46318</v>
       </c>
-      <c r="P47" s="170" t="inlineStr">
+      <c r="S47" s="169" t="inlineStr">
         <is>
           <t>2026-Q4</t>
         </is>
       </c>
-      <c r="Q47" s="171" t="inlineStr">
+      <c r="T47" s="171" t="inlineStr">
         <is>
           <t>excavation, tbm, tunnelling, tunnel</t>
         </is>
       </c>
-      <c r="R47" s="158" t="n">
+      <c r="U47" s="158" t="n">
         <v>10</v>
       </c>
-      <c r="S47" s="172" t="inlineStr">
+      <c r="V47" s="172" t="inlineStr">
         <is>
           <t>https://www.tunnelsandtunnelling.com/news/snowy-2-0-cost-and-completion-date-revised/</t>
         </is>
       </c>
-      <c r="T47" s="173">
-        <f>IF($B47="",0,IF(AND(OR(OR(Dashboard!$B$5="All themes",Dashboard!$B$5=""),$C47=Dashboard!$B$5),OR(OR(Dashboard!$G$5="All uses",Dashboard!$G$5=""),$E47=Dashboard!$G$5),N($D47)&gt;=Lists!$H$2,OR(OR(Dashboard!$N$5="All windows",Dashboard!$N$5=""),$P47=Dashboard!$N$5)),1,0))</f>
-        <v/>
-      </c>
-      <c r="U47" s="174">
-        <f>IF($T47=1,N($D47)*1E14+MIN(MAX(N($R47),0),9999)*1E10+MIN(N($K47),99999)*1E5+99999-MIN(ROW(),99999),"")</f>
+      <c r="W47" s="173">
+        <f>IF($B47="",0,IF(AND(OR(OR(Dashboard!$B$5="All themes",Dashboard!$B$5=""),$C47=Dashboard!$B$5),OR(OR(Dashboard!$G$5="All uses",Dashboard!$G$5=""),$E47=Dashboard!$G$5),N($D47)&gt;=Lists!$H$2,OR(OR(Dashboard!$N$5="All windows",Dashboard!$N$5=""),$S47=Dashboard!$N$5)),1,0))</f>
+        <v/>
+      </c>
+      <c r="X47" s="174">
+        <f>IF($W47=1,N($D47)*1E14+MIN(MAX(N($U47),0),9999)*1E10+MIN(N($K47),99999)*1E5+99999-MIN(ROW(),99999),"")</f>
         <v/>
       </c>
     </row>
@@ -10023,33 +10236,36 @@
         </is>
       </c>
       <c r="N48" s="169" t="n"/>
-      <c r="O48" s="167" t="n">
+      <c r="O48" s="166" t="n"/>
+      <c r="P48" s="166" t="n"/>
+      <c r="Q48" s="170" t="n"/>
+      <c r="R48" s="167" t="n">
         <v>46317</v>
       </c>
-      <c r="P48" s="170" t="inlineStr">
+      <c r="S48" s="169" t="inlineStr">
         <is>
           <t>2026-Q4</t>
         </is>
       </c>
-      <c r="Q48" s="171" t="inlineStr">
+      <c r="T48" s="171" t="inlineStr">
         <is>
           <t>tunnelling, tunnel</t>
         </is>
       </c>
-      <c r="R48" s="158" t="n">
+      <c r="U48" s="158" t="n">
         <v>7</v>
       </c>
-      <c r="S48" s="172" t="inlineStr">
+      <c r="V48" s="172" t="inlineStr">
         <is>
           <t>https://tunnellingjournal.com/mobile-shield-deployed-for-a14-vinci-tunnel-reconstruction/</t>
         </is>
       </c>
-      <c r="T48" s="173">
-        <f>IF($B48="",0,IF(AND(OR(OR(Dashboard!$B$5="All themes",Dashboard!$B$5=""),$C48=Dashboard!$B$5),OR(OR(Dashboard!$G$5="All uses",Dashboard!$G$5=""),$E48=Dashboard!$G$5),N($D48)&gt;=Lists!$H$2,OR(OR(Dashboard!$N$5="All windows",Dashboard!$N$5=""),$P48=Dashboard!$N$5)),1,0))</f>
-        <v/>
-      </c>
-      <c r="U48" s="174">
-        <f>IF($T48=1,N($D48)*1E14+MIN(MAX(N($R48),0),9999)*1E10+MIN(N($K48),99999)*1E5+99999-MIN(ROW(),99999),"")</f>
+      <c r="W48" s="173">
+        <f>IF($B48="",0,IF(AND(OR(OR(Dashboard!$B$5="All themes",Dashboard!$B$5=""),$C48=Dashboard!$B$5),OR(OR(Dashboard!$G$5="All uses",Dashboard!$G$5=""),$E48=Dashboard!$G$5),N($D48)&gt;=Lists!$H$2,OR(OR(Dashboard!$N$5="All windows",Dashboard!$N$5=""),$S48=Dashboard!$N$5)),1,0))</f>
+        <v/>
+      </c>
+      <c r="X48" s="174">
+        <f>IF($W48=1,N($D48)*1E14+MIN(MAX(N($U48),0),9999)*1E10+MIN(N($K48),99999)*1E5+99999-MIN(ROW(),99999),"")</f>
         <v/>
       </c>
     </row>
@@ -10101,34 +10317,37 @@
         </is>
       </c>
       <c r="M49" s="168" t="n"/>
-      <c r="N49" s="169" t="inlineStr">
+      <c r="N49" s="169" t="n"/>
+      <c r="O49" s="166" t="n"/>
+      <c r="P49" s="166" t="n"/>
+      <c r="Q49" s="170" t="inlineStr">
         <is>
           <t>Indonesia</t>
         </is>
       </c>
-      <c r="O49" s="167" t="n">
-        <v>46319</v>
-      </c>
-      <c r="P49" s="170" t="inlineStr">
+      <c r="R49" s="167" t="n">
+        <v>46319</v>
+      </c>
+      <c r="S49" s="169" t="inlineStr">
         <is>
           <t>2026-Q4</t>
         </is>
       </c>
-      <c r="Q49" s="171" t="n"/>
-      <c r="R49" s="158" t="n">
+      <c r="T49" s="171" t="n"/>
+      <c r="U49" s="158" t="n">
         <v>6</v>
       </c>
-      <c r="S49" s="172" t="inlineStr">
+      <c r="V49" s="172" t="inlineStr">
         <is>
           <t>https://news.google.com/rss/articles/CBMilgFBVV95cUxPbVV1NmdrOGFidElfXzZzV1ppbDBCOEc5V0luUWxOSTAwMXNGdmhVMkoxMjUwSUpmbU5lQlBuNkFVTXZGMk5IRzd5Y0taREt0ckRUT3VqSjBfbGFPTmRjUTZFS18wLTQ5Wi1ZdnFtYWd1QmN0U0Nsekx4ZzR0YVk0dmhhTXVpTW1rdEpCbGlKLTZNVXVzMEE?oc=5</t>
         </is>
       </c>
-      <c r="T49" s="173">
-        <f>IF($B49="",0,IF(AND(OR(OR(Dashboard!$B$5="All themes",Dashboard!$B$5=""),$C49=Dashboard!$B$5),OR(OR(Dashboard!$G$5="All uses",Dashboard!$G$5=""),$E49=Dashboard!$G$5),N($D49)&gt;=Lists!$H$2,OR(OR(Dashboard!$N$5="All windows",Dashboard!$N$5=""),$P49=Dashboard!$N$5)),1,0))</f>
-        <v/>
-      </c>
-      <c r="U49" s="174">
-        <f>IF($T49=1,N($D49)*1E14+MIN(MAX(N($R49),0),9999)*1E10+MIN(N($K49),99999)*1E5+99999-MIN(ROW(),99999),"")</f>
+      <c r="W49" s="173">
+        <f>IF($B49="",0,IF(AND(OR(OR(Dashboard!$B$5="All themes",Dashboard!$B$5=""),$C49=Dashboard!$B$5),OR(OR(Dashboard!$G$5="All uses",Dashboard!$G$5=""),$E49=Dashboard!$G$5),N($D49)&gt;=Lists!$H$2,OR(OR(Dashboard!$N$5="All windows",Dashboard!$N$5=""),$S49=Dashboard!$N$5)),1,0))</f>
+        <v/>
+      </c>
+      <c r="X49" s="174">
+        <f>IF($W49=1,N($D49)*1E14+MIN(MAX(N($U49),0),9999)*1E10+MIN(N($K49),99999)*1E5+99999-MIN(ROW(),99999),"")</f>
         <v/>
       </c>
     </row>
@@ -10181,33 +10400,36 @@
         </is>
       </c>
       <c r="N50" s="169" t="n"/>
-      <c r="O50" s="167" t="n">
+      <c r="O50" s="166" t="n"/>
+      <c r="P50" s="166" t="n"/>
+      <c r="Q50" s="170" t="n"/>
+      <c r="R50" s="167" t="n">
         <v>46318</v>
       </c>
-      <c r="P50" s="170" t="inlineStr">
+      <c r="S50" s="169" t="inlineStr">
         <is>
           <t>2026-Q4</t>
         </is>
       </c>
-      <c r="Q50" s="171" t="inlineStr">
+      <c r="T50" s="171" t="inlineStr">
         <is>
           <t>tunnelling, tunnel</t>
         </is>
       </c>
-      <c r="R50" s="158" t="n">
+      <c r="U50" s="158" t="n">
         <v>5</v>
       </c>
-      <c r="S50" s="172" t="inlineStr">
+      <c r="V50" s="172" t="inlineStr">
         <is>
           <t>https://www.tunnelsandtunnelling.com/news/abergeldie-awarded-patent-for-underground-hydrogen-storage-solution/</t>
         </is>
       </c>
-      <c r="T50" s="173">
-        <f>IF($B50="",0,IF(AND(OR(OR(Dashboard!$B$5="All themes",Dashboard!$B$5=""),$C50=Dashboard!$B$5),OR(OR(Dashboard!$G$5="All uses",Dashboard!$G$5=""),$E50=Dashboard!$G$5),N($D50)&gt;=Lists!$H$2,OR(OR(Dashboard!$N$5="All windows",Dashboard!$N$5=""),$P50=Dashboard!$N$5)),1,0))</f>
-        <v/>
-      </c>
-      <c r="U50" s="174">
-        <f>IF($T50=1,N($D50)*1E14+MIN(MAX(N($R50),0),9999)*1E10+MIN(N($K50),99999)*1E5+99999-MIN(ROW(),99999),"")</f>
+      <c r="W50" s="173">
+        <f>IF($B50="",0,IF(AND(OR(OR(Dashboard!$B$5="All themes",Dashboard!$B$5=""),$C50=Dashboard!$B$5),OR(OR(Dashboard!$G$5="All uses",Dashboard!$G$5=""),$E50=Dashboard!$G$5),N($D50)&gt;=Lists!$H$2,OR(OR(Dashboard!$N$5="All windows",Dashboard!$N$5=""),$S50=Dashboard!$N$5)),1,0))</f>
+        <v/>
+      </c>
+      <c r="X50" s="174">
+        <f>IF($W50=1,N($D50)*1E14+MIN(MAX(N($U50),0),9999)*1E10+MIN(N($K50),99999)*1E5+99999-MIN(ROW(),99999),"")</f>
         <v/>
       </c>
     </row>
@@ -10260,33 +10482,36 @@
         </is>
       </c>
       <c r="N51" s="169" t="n"/>
-      <c r="O51" s="167" t="n">
+      <c r="O51" s="166" t="n"/>
+      <c r="P51" s="166" t="n"/>
+      <c r="Q51" s="170" t="n"/>
+      <c r="R51" s="167" t="n">
         <v>46318</v>
       </c>
-      <c r="P51" s="170" t="inlineStr">
+      <c r="S51" s="169" t="inlineStr">
         <is>
           <t>2026-Q4</t>
         </is>
       </c>
-      <c r="Q51" s="171" t="inlineStr">
+      <c r="T51" s="171" t="inlineStr">
         <is>
           <t>tunnelling</t>
         </is>
       </c>
-      <c r="R51" s="158" t="n">
+      <c r="U51" s="158" t="n">
         <v>5</v>
       </c>
-      <c r="S51" s="172" t="inlineStr">
+      <c r="V51" s="172" t="inlineStr">
         <is>
           <t>https://tunnellingjournal.com/snowy-2-0-cost-rises-to-a22-2bn-as-tunnelling-reaches-65-completion/</t>
         </is>
       </c>
-      <c r="T51" s="173">
-        <f>IF($B51="",0,IF(AND(OR(OR(Dashboard!$B$5="All themes",Dashboard!$B$5=""),$C51=Dashboard!$B$5),OR(OR(Dashboard!$G$5="All uses",Dashboard!$G$5=""),$E51=Dashboard!$G$5),N($D51)&gt;=Lists!$H$2,OR(OR(Dashboard!$N$5="All windows",Dashboard!$N$5=""),$P51=Dashboard!$N$5)),1,0))</f>
-        <v/>
-      </c>
-      <c r="U51" s="174">
-        <f>IF($T51=1,N($D51)*1E14+MIN(MAX(N($R51),0),9999)*1E10+MIN(N($K51),99999)*1E5+99999-MIN(ROW(),99999),"")</f>
+      <c r="W51" s="173">
+        <f>IF($B51="",0,IF(AND(OR(OR(Dashboard!$B$5="All themes",Dashboard!$B$5=""),$C51=Dashboard!$B$5),OR(OR(Dashboard!$G$5="All uses",Dashboard!$G$5=""),$E51=Dashboard!$G$5),N($D51)&gt;=Lists!$H$2,OR(OR(Dashboard!$N$5="All windows",Dashboard!$N$5=""),$S51=Dashboard!$N$5)),1,0))</f>
+        <v/>
+      </c>
+      <c r="X51" s="174">
+        <f>IF($W51=1,N($D51)*1E14+MIN(MAX(N($U51),0),9999)*1E10+MIN(N($K51),99999)*1E5+99999-MIN(ROW(),99999),"")</f>
         <v/>
       </c>
     </row>
@@ -10338,38 +10563,41 @@
         </is>
       </c>
       <c r="M52" s="168" t="n"/>
-      <c r="N52" s="169" t="inlineStr">
+      <c r="N52" s="169" t="n"/>
+      <c r="O52" s="166" t="n"/>
+      <c r="P52" s="166" t="n"/>
+      <c r="Q52" s="170" t="inlineStr">
         <is>
           <t>Peru</t>
         </is>
       </c>
-      <c r="O52" s="167" t="n">
+      <c r="R52" s="167" t="n">
         <v>46318</v>
       </c>
-      <c r="P52" s="170" t="inlineStr">
+      <c r="S52" s="169" t="inlineStr">
         <is>
           <t>2026-Q4</t>
         </is>
       </c>
-      <c r="Q52" s="171" t="inlineStr">
+      <c r="T52" s="171" t="inlineStr">
         <is>
           <t>site investigation, soil</t>
         </is>
       </c>
-      <c r="R52" s="158" t="n">
+      <c r="U52" s="158" t="n">
         <v>5</v>
       </c>
-      <c r="S52" s="172" t="inlineStr">
+      <c r="V52" s="172" t="inlineStr">
         <is>
           <t>https://news.google.com/rss/articles/CBMiygFBVV95cUxNYnltUmU0VEdCNDdXUG4xWjNBYXRMUEdlU2dIanhJeHFBalFBOG9DaWx0Tk5KVnZqeGZSMkxZQTNNSkdzWTJHZl9oSDRRWXZOb2YwNFVLNWw5ZjBUY0ZZdTNpOWg5RlQ3M2xDMkt6bkRvMFhXc1k3bTZmVmpVLU9zdTEtQ1R6U1hvWmlPVHA3WjFwc1IwNldOSHV6UGI5VldtdS01bjQ4ZXl4d0N2bjBtWVFqRktLUkZtMFhtVmhrUUVkSEhBbmtJMjJ3?oc=5</t>
         </is>
       </c>
-      <c r="T52" s="173">
-        <f>IF($B52="",0,IF(AND(OR(OR(Dashboard!$B$5="All themes",Dashboard!$B$5=""),$C52=Dashboard!$B$5),OR(OR(Dashboard!$G$5="All uses",Dashboard!$G$5=""),$E52=Dashboard!$G$5),N($D52)&gt;=Lists!$H$2,OR(OR(Dashboard!$N$5="All windows",Dashboard!$N$5=""),$P52=Dashboard!$N$5)),1,0))</f>
-        <v/>
-      </c>
-      <c r="U52" s="174">
-        <f>IF($T52=1,N($D52)*1E14+MIN(MAX(N($R52),0),9999)*1E10+MIN(N($K52),99999)*1E5+99999-MIN(ROW(),99999),"")</f>
+      <c r="W52" s="173">
+        <f>IF($B52="",0,IF(AND(OR(OR(Dashboard!$B$5="All themes",Dashboard!$B$5=""),$C52=Dashboard!$B$5),OR(OR(Dashboard!$G$5="All uses",Dashboard!$G$5=""),$E52=Dashboard!$G$5),N($D52)&gt;=Lists!$H$2,OR(OR(Dashboard!$N$5="All windows",Dashboard!$N$5=""),$S52=Dashboard!$N$5)),1,0))</f>
+        <v/>
+      </c>
+      <c r="X52" s="174">
+        <f>IF($W52=1,N($D52)*1E14+MIN(MAX(N($U52),0),9999)*1E10+MIN(N($K52),99999)*1E5+99999-MIN(ROW(),99999),"")</f>
         <v/>
       </c>
     </row>
@@ -10421,38 +10649,41 @@
         </is>
       </c>
       <c r="M53" s="168" t="n"/>
-      <c r="N53" s="169" t="inlineStr">
+      <c r="N53" s="169" t="n"/>
+      <c r="O53" s="166" t="n"/>
+      <c r="P53" s="166" t="n"/>
+      <c r="Q53" s="170" t="inlineStr">
         <is>
           <t>Colombia</t>
         </is>
       </c>
-      <c r="O53" s="167" t="n">
+      <c r="R53" s="167" t="n">
         <v>46317</v>
       </c>
-      <c r="P53" s="170" t="inlineStr">
+      <c r="S53" s="169" t="inlineStr">
         <is>
           <t>2026-Q4</t>
         </is>
       </c>
-      <c r="Q53" s="171" t="inlineStr">
+      <c r="T53" s="171" t="inlineStr">
         <is>
           <t>sinkhole</t>
         </is>
       </c>
-      <c r="R53" s="158" t="n">
+      <c r="U53" s="158" t="n">
         <v>4</v>
       </c>
-      <c r="S53" s="172" t="inlineStr">
+      <c r="V53" s="172" t="inlineStr">
         <is>
           <t>https://news.google.com/rss/articles/CBMixwFBVV95cUxPZGJXSXRVamN6M3Z6Ymc2NnU0ODdaRThOc2tqRWNRQ0VLeklmMTViYzh1RVZESzNZOUlwVkZBUS0zcDB5UFFXdlB1TUM0N0NSU1BJZFNSRERhdnBSeS1jU1B3aVFUQmh6bkxCbUFROEJ1NS0wUDVuMUhFeGNleWtCVUxBendKR0dFekxHQVFNejlTN0hOcGZadDZmWGRiZHdGZ0xNZVRuc21BYnpUWHg3LWx4UzJPbHNxVUJpWWxLdUtWVEhBcnBr?oc=5</t>
         </is>
       </c>
-      <c r="T53" s="173">
-        <f>IF($B53="",0,IF(AND(OR(OR(Dashboard!$B$5="All themes",Dashboard!$B$5=""),$C53=Dashboard!$B$5),OR(OR(Dashboard!$G$5="All uses",Dashboard!$G$5=""),$E53=Dashboard!$G$5),N($D53)&gt;=Lists!$H$2,OR(OR(Dashboard!$N$5="All windows",Dashboard!$N$5=""),$P53=Dashboard!$N$5)),1,0))</f>
-        <v/>
-      </c>
-      <c r="U53" s="174">
-        <f>IF($T53=1,N($D53)*1E14+MIN(MAX(N($R53),0),9999)*1E10+MIN(N($K53),99999)*1E5+99999-MIN(ROW(),99999),"")</f>
+      <c r="W53" s="173">
+        <f>IF($B53="",0,IF(AND(OR(OR(Dashboard!$B$5="All themes",Dashboard!$B$5=""),$C53=Dashboard!$B$5),OR(OR(Dashboard!$G$5="All uses",Dashboard!$G$5=""),$E53=Dashboard!$G$5),N($D53)&gt;=Lists!$H$2,OR(OR(Dashboard!$N$5="All windows",Dashboard!$N$5=""),$S53=Dashboard!$N$5)),1,0))</f>
+        <v/>
+      </c>
+      <c r="X53" s="174">
+        <f>IF($W53=1,N($D53)*1E14+MIN(MAX(N($U53),0),9999)*1E10+MIN(N($K53),99999)*1E5+99999-MIN(ROW(),99999),"")</f>
         <v/>
       </c>
     </row>
@@ -10504,38 +10735,41 @@
         </is>
       </c>
       <c r="M54" s="168" t="n"/>
-      <c r="N54" s="169" t="inlineStr">
+      <c r="N54" s="169" t="n"/>
+      <c r="O54" s="166" t="n"/>
+      <c r="P54" s="166" t="n"/>
+      <c r="Q54" s="170" t="inlineStr">
         <is>
           <t>Colombia</t>
         </is>
       </c>
-      <c r="O54" s="167" t="n">
-        <v>46319</v>
-      </c>
-      <c r="P54" s="170" t="inlineStr">
+      <c r="R54" s="167" t="n">
+        <v>46319</v>
+      </c>
+      <c r="S54" s="169" t="inlineStr">
         <is>
           <t>2026-Q4</t>
         </is>
       </c>
-      <c r="Q54" s="171" t="inlineStr">
+      <c r="T54" s="171" t="inlineStr">
         <is>
           <t>sinkhole</t>
         </is>
       </c>
-      <c r="R54" s="158" t="n">
+      <c r="U54" s="158" t="n">
         <v>4</v>
       </c>
-      <c r="S54" s="172" t="inlineStr">
+      <c r="V54" s="172" t="inlineStr">
         <is>
           <t>https://news.google.com/rss/articles/CBMi0gFBVV95cUxNcGZlMTE5MjVLdXpRZjFKNzcxQnZ5YmFUQ0xkeGljcmdESFNjZE1xai1JR196X3BEcTl6eWZmWjlPU3ZpQktHM3hWSmJvVEtUaGlSb2hNUWtmcjNpbV9hZXhRdVR1UEdMeC1fMTducHM4bElIOGFLZFhvZnZIMXM5OHRYdEJ4N2NVNGhGa181Qm8zTTd6d2dTQjVkSUZrRHdwcE5LVUxxY3JhSnN2di15NFVXWXJDU011NW5uejZQVmNtcHpvOU9NOXFzbVJNVU9TdnfSAeYBQVVfeXFMTXdwTjRSMVRXVjFOUGJEU1dkVDB2c1dCc0c0MnZIN1hZVHl4Z24taWFocko0SldESnk3LWltclY2TU94d0liMXM3YkxiVndZQVhCWFc5ZEROYjdCNFRCVmlEaTl0X2ZOXzRJQmtKSTFPWTVsNjZncVBudnBmckRjX1M3OEUwSVNYT2RtUF9SYzgxQlJHMWgxYVRkcUYwck9IOXBzeUE2Yi01QXRVeG1IQTFvOUxsaU9TNlVobzJROUhFVmV3bng5NFZnSlV3SFNiQXFkTGFMVFBwZUp2dUhIV1Z1RU5rNFE?oc=5</t>
         </is>
       </c>
-      <c r="T54" s="173">
-        <f>IF($B54="",0,IF(AND(OR(OR(Dashboard!$B$5="All themes",Dashboard!$B$5=""),$C54=Dashboard!$B$5),OR(OR(Dashboard!$G$5="All uses",Dashboard!$G$5=""),$E54=Dashboard!$G$5),N($D54)&gt;=Lists!$H$2,OR(OR(Dashboard!$N$5="All windows",Dashboard!$N$5=""),$P54=Dashboard!$N$5)),1,0))</f>
-        <v/>
-      </c>
-      <c r="U54" s="174">
-        <f>IF($T54=1,N($D54)*1E14+MIN(MAX(N($R54),0),9999)*1E10+MIN(N($K54),99999)*1E5+99999-MIN(ROW(),99999),"")</f>
+      <c r="W54" s="173">
+        <f>IF($B54="",0,IF(AND(OR(OR(Dashboard!$B$5="All themes",Dashboard!$B$5=""),$C54=Dashboard!$B$5),OR(OR(Dashboard!$G$5="All uses",Dashboard!$G$5=""),$E54=Dashboard!$G$5),N($D54)&gt;=Lists!$H$2,OR(OR(Dashboard!$N$5="All windows",Dashboard!$N$5=""),$S54=Dashboard!$N$5)),1,0))</f>
+        <v/>
+      </c>
+      <c r="X54" s="174">
+        <f>IF($W54=1,N($D54)*1E14+MIN(MAX(N($U54),0),9999)*1E10+MIN(N($K54),99999)*1E5+99999-MIN(ROW(),99999),"")</f>
         <v/>
       </c>
     </row>
@@ -10587,38 +10821,41 @@
         </is>
       </c>
       <c r="M55" s="168" t="n"/>
-      <c r="N55" s="169" t="inlineStr">
+      <c r="N55" s="169" t="n"/>
+      <c r="O55" s="166" t="n"/>
+      <c r="P55" s="166" t="n"/>
+      <c r="Q55" s="170" t="inlineStr">
         <is>
           <t>Russia</t>
         </is>
       </c>
-      <c r="O55" s="167" t="n">
+      <c r="R55" s="167" t="n">
         <v>46318</v>
       </c>
-      <c r="P55" s="170" t="inlineStr">
+      <c r="S55" s="169" t="inlineStr">
         <is>
           <t>2026-Q4</t>
         </is>
       </c>
-      <c r="Q55" s="171" t="inlineStr">
+      <c r="T55" s="171" t="inlineStr">
         <is>
           <t>retaining wall</t>
         </is>
       </c>
-      <c r="R55" s="158" t="n">
+      <c r="U55" s="158" t="n">
         <v>4</v>
       </c>
-      <c r="S55" s="172" t="inlineStr">
+      <c r="V55" s="172" t="inlineStr">
         <is>
           <t>https://news.google.com/rss/articles/CBMiREFVX3lxTE9KcGh5bWlxWEhKT3FXdU5qVjNOd3c3clQ1bGw1YWFmaHljV0U3ckZYcndLVTgtakJFSHZZQ3ViYXg2QnV4?oc=5</t>
         </is>
       </c>
-      <c r="T55" s="173">
-        <f>IF($B55="",0,IF(AND(OR(OR(Dashboard!$B$5="All themes",Dashboard!$B$5=""),$C55=Dashboard!$B$5),OR(OR(Dashboard!$G$5="All uses",Dashboard!$G$5=""),$E55=Dashboard!$G$5),N($D55)&gt;=Lists!$H$2,OR(OR(Dashboard!$N$5="All windows",Dashboard!$N$5=""),$P55=Dashboard!$N$5)),1,0))</f>
-        <v/>
-      </c>
-      <c r="U55" s="174">
-        <f>IF($T55=1,N($D55)*1E14+MIN(MAX(N($R55),0),9999)*1E10+MIN(N($K55),99999)*1E5+99999-MIN(ROW(),99999),"")</f>
+      <c r="W55" s="173">
+        <f>IF($B55="",0,IF(AND(OR(OR(Dashboard!$B$5="All themes",Dashboard!$B$5=""),$C55=Dashboard!$B$5),OR(OR(Dashboard!$G$5="All uses",Dashboard!$G$5=""),$E55=Dashboard!$G$5),N($D55)&gt;=Lists!$H$2,OR(OR(Dashboard!$N$5="All windows",Dashboard!$N$5=""),$S55=Dashboard!$N$5)),1,0))</f>
+        <v/>
+      </c>
+      <c r="X55" s="174">
+        <f>IF($W55=1,N($D55)*1E14+MIN(MAX(N($U55),0),9999)*1E10+MIN(N($K55),99999)*1E5+99999-MIN(ROW(),99999),"")</f>
         <v/>
       </c>
     </row>
@@ -10670,38 +10907,41 @@
         </is>
       </c>
       <c r="M56" s="168" t="n"/>
-      <c r="N56" s="169" t="inlineStr">
+      <c r="N56" s="169" t="n"/>
+      <c r="O56" s="166" t="n"/>
+      <c r="P56" s="166" t="n"/>
+      <c r="Q56" s="170" t="inlineStr">
         <is>
           <t>Colombia</t>
         </is>
       </c>
-      <c r="O56" s="167" t="n">
-        <v>46319</v>
-      </c>
-      <c r="P56" s="170" t="inlineStr">
+      <c r="R56" s="167" t="n">
+        <v>46319</v>
+      </c>
+      <c r="S56" s="169" t="inlineStr">
         <is>
           <t>2026-Q4</t>
         </is>
       </c>
-      <c r="Q56" s="171" t="inlineStr">
+      <c r="T56" s="171" t="inlineStr">
         <is>
           <t>sinkhole</t>
         </is>
       </c>
-      <c r="R56" s="158" t="n">
+      <c r="U56" s="158" t="n">
         <v>4</v>
       </c>
-      <c r="S56" s="172" t="inlineStr">
+      <c r="V56" s="172" t="inlineStr">
         <is>
           <t>https://news.google.com/rss/articles/CBMijAFBVV95cUxQdDFPZ1hLdVRrLUxWRTkyRWtWTjdrMTlTMi1EdW5meVA1dG5ZUWxNZ09MRThFeTk0OThLTDg4QkhBRlQwMzZkTnRBWnh2ZjdTWkhVWTcxX0QxYnNrMW9XOHNyVFZxeHpJMkthZDJRbGtsV0VuTjkwLXFTN0JSS2k2NU85em9uLWgtTjBjUQ?oc=5</t>
         </is>
       </c>
-      <c r="T56" s="173">
-        <f>IF($B56="",0,IF(AND(OR(OR(Dashboard!$B$5="All themes",Dashboard!$B$5=""),$C56=Dashboard!$B$5),OR(OR(Dashboard!$G$5="All uses",Dashboard!$G$5=""),$E56=Dashboard!$G$5),N($D56)&gt;=Lists!$H$2,OR(OR(Dashboard!$N$5="All windows",Dashboard!$N$5=""),$P56=Dashboard!$N$5)),1,0))</f>
-        <v/>
-      </c>
-      <c r="U56" s="174">
-        <f>IF($T56=1,N($D56)*1E14+MIN(MAX(N($R56),0),9999)*1E10+MIN(N($K56),99999)*1E5+99999-MIN(ROW(),99999),"")</f>
+      <c r="W56" s="173">
+        <f>IF($B56="",0,IF(AND(OR(OR(Dashboard!$B$5="All themes",Dashboard!$B$5=""),$C56=Dashboard!$B$5),OR(OR(Dashboard!$G$5="All uses",Dashboard!$G$5=""),$E56=Dashboard!$G$5),N($D56)&gt;=Lists!$H$2,OR(OR(Dashboard!$N$5="All windows",Dashboard!$N$5=""),$S56=Dashboard!$N$5)),1,0))</f>
+        <v/>
+      </c>
+      <c r="X56" s="174">
+        <f>IF($W56=1,N($D56)*1E14+MIN(MAX(N($U56),0),9999)*1E10+MIN(N($K56),99999)*1E5+99999-MIN(ROW(),99999),"")</f>
         <v/>
       </c>
     </row>
@@ -10753,38 +10993,41 @@
         </is>
       </c>
       <c r="M57" s="168" t="n"/>
-      <c r="N57" s="169" t="inlineStr">
+      <c r="N57" s="169" t="n"/>
+      <c r="O57" s="166" t="n"/>
+      <c r="P57" s="166" t="n"/>
+      <c r="Q57" s="170" t="inlineStr">
         <is>
           <t>Colombia</t>
         </is>
       </c>
-      <c r="O57" s="167" t="n">
-        <v>46319</v>
-      </c>
-      <c r="P57" s="170" t="inlineStr">
+      <c r="R57" s="167" t="n">
+        <v>46319</v>
+      </c>
+      <c r="S57" s="169" t="inlineStr">
         <is>
           <t>2026-Q4</t>
         </is>
       </c>
-      <c r="Q57" s="171" t="inlineStr">
+      <c r="T57" s="171" t="inlineStr">
         <is>
           <t>sinkhole</t>
         </is>
       </c>
-      <c r="R57" s="158" t="n">
+      <c r="U57" s="158" t="n">
         <v>4</v>
       </c>
-      <c r="S57" s="172" t="inlineStr">
+      <c r="V57" s="172" t="inlineStr">
         <is>
           <t>https://news.google.com/rss/articles/CBMic0FVX3lxTE56eFFxMjNpU2dPWkppM1RsMEJJbThwdXcyYk1id0t2V1RCYUFMQTJzVGRGMFBxODZlSi1IVERlM29jWGtJRUtkb1M5em1ISlMwd1hBVnkwNEVOb1hiWlkzNU9JZUJJbWZXNUFZWTh5YkE5SE0?oc=5</t>
         </is>
       </c>
-      <c r="T57" s="173">
-        <f>IF($B57="",0,IF(AND(OR(OR(Dashboard!$B$5="All themes",Dashboard!$B$5=""),$C57=Dashboard!$B$5),OR(OR(Dashboard!$G$5="All uses",Dashboard!$G$5=""),$E57=Dashboard!$G$5),N($D57)&gt;=Lists!$H$2,OR(OR(Dashboard!$N$5="All windows",Dashboard!$N$5=""),$P57=Dashboard!$N$5)),1,0))</f>
-        <v/>
-      </c>
-      <c r="U57" s="174">
-        <f>IF($T57=1,N($D57)*1E14+MIN(MAX(N($R57),0),9999)*1E10+MIN(N($K57),99999)*1E5+99999-MIN(ROW(),99999),"")</f>
+      <c r="W57" s="173">
+        <f>IF($B57="",0,IF(AND(OR(OR(Dashboard!$B$5="All themes",Dashboard!$B$5=""),$C57=Dashboard!$B$5),OR(OR(Dashboard!$G$5="All uses",Dashboard!$G$5=""),$E57=Dashboard!$G$5),N($D57)&gt;=Lists!$H$2,OR(OR(Dashboard!$N$5="All windows",Dashboard!$N$5=""),$S57=Dashboard!$N$5)),1,0))</f>
+        <v/>
+      </c>
+      <c r="X57" s="174">
+        <f>IF($W57=1,N($D57)*1E14+MIN(MAX(N($U57),0),9999)*1E10+MIN(N($K57),99999)*1E5+99999-MIN(ROW(),99999),"")</f>
         <v/>
       </c>
     </row>
@@ -10836,38 +11079,41 @@
         </is>
       </c>
       <c r="M58" s="168" t="n"/>
-      <c r="N58" s="169" t="inlineStr">
+      <c r="N58" s="169" t="n"/>
+      <c r="O58" s="166" t="n"/>
+      <c r="P58" s="166" t="n"/>
+      <c r="Q58" s="170" t="inlineStr">
         <is>
           <t>Colombia</t>
         </is>
       </c>
-      <c r="O58" s="167" t="n">
+      <c r="R58" s="167" t="n">
         <v>46318</v>
       </c>
-      <c r="P58" s="170" t="inlineStr">
+      <c r="S58" s="169" t="inlineStr">
         <is>
           <t>2026-Q4</t>
         </is>
       </c>
-      <c r="Q58" s="171" t="inlineStr">
+      <c r="T58" s="171" t="inlineStr">
         <is>
           <t>sinkhole</t>
         </is>
       </c>
-      <c r="R58" s="158" t="n">
+      <c r="U58" s="158" t="n">
         <v>4</v>
       </c>
-      <c r="S58" s="172" t="inlineStr">
+      <c r="V58" s="172" t="inlineStr">
         <is>
           <t>https://news.google.com/rss/articles/CBMi0AFBVV95cUxNZm5rakRuTlVuWjFiMGV5Z2p4SmRJUTlTc3E4S0g0WnVzaEcwRTVTWjdrVVlBRl84ckNvRUpXQjh2bTY2R2RnNFZGOG5uVnpDZnBpSUM1S3JVd05lQUd0cVNNaG4zYUdNSjUyVmZ5TnZfM2RZN0UxUFFMeUJxSEgxSC16bFBlcG52cEN4RVh3dC1EM3g5R1ZTS2tuNVczZEJNRDdfaTZrMXRXb0cwS1NrdS1lb0VITjU5ajZfeXpINS1PVjNNeTNkNkJlX0o3R3NO?oc=5</t>
         </is>
       </c>
-      <c r="T58" s="173">
-        <f>IF($B58="",0,IF(AND(OR(OR(Dashboard!$B$5="All themes",Dashboard!$B$5=""),$C58=Dashboard!$B$5),OR(OR(Dashboard!$G$5="All uses",Dashboard!$G$5=""),$E58=Dashboard!$G$5),N($D58)&gt;=Lists!$H$2,OR(OR(Dashboard!$N$5="All windows",Dashboard!$N$5=""),$P58=Dashboard!$N$5)),1,0))</f>
-        <v/>
-      </c>
-      <c r="U58" s="174">
-        <f>IF($T58=1,N($D58)*1E14+MIN(MAX(N($R58),0),9999)*1E10+MIN(N($K58),99999)*1E5+99999-MIN(ROW(),99999),"")</f>
+      <c r="W58" s="173">
+        <f>IF($B58="",0,IF(AND(OR(OR(Dashboard!$B$5="All themes",Dashboard!$B$5=""),$C58=Dashboard!$B$5),OR(OR(Dashboard!$G$5="All uses",Dashboard!$G$5=""),$E58=Dashboard!$G$5),N($D58)&gt;=Lists!$H$2,OR(OR(Dashboard!$N$5="All windows",Dashboard!$N$5=""),$S58=Dashboard!$N$5)),1,0))</f>
+        <v/>
+      </c>
+      <c r="X58" s="174">
+        <f>IF($W58=1,N($D58)*1E14+MIN(MAX(N($U58),0),9999)*1E10+MIN(N($K58),99999)*1E5+99999-MIN(ROW(),99999),"")</f>
         <v/>
       </c>
     </row>
@@ -10919,38 +11165,41 @@
         </is>
       </c>
       <c r="M59" s="168" t="n"/>
-      <c r="N59" s="169" t="inlineStr">
+      <c r="N59" s="169" t="n"/>
+      <c r="O59" s="166" t="n"/>
+      <c r="P59" s="166" t="n"/>
+      <c r="Q59" s="170" t="inlineStr">
         <is>
           <t>Colombia</t>
         </is>
       </c>
-      <c r="O59" s="167" t="n">
+      <c r="R59" s="167" t="n">
         <v>46318</v>
       </c>
-      <c r="P59" s="170" t="inlineStr">
+      <c r="S59" s="169" t="inlineStr">
         <is>
           <t>2026-Q4</t>
         </is>
       </c>
-      <c r="Q59" s="171" t="inlineStr">
+      <c r="T59" s="171" t="inlineStr">
         <is>
           <t>sinkhole</t>
         </is>
       </c>
-      <c r="R59" s="158" t="n">
+      <c r="U59" s="158" t="n">
         <v>4</v>
       </c>
-      <c r="S59" s="172" t="inlineStr">
+      <c r="V59" s="172" t="inlineStr">
         <is>
           <t>https://news.google.com/rss/articles/CBMieEFVX3lxTE5YeFpJbnV5Wkk5VGczTmxUT3Vod1U2UWltZHhMQmtKclRjcURMSGpiSjRHSWNNMjJUWmM2Z1JlUkNHNlgwU09XZXFaNEpKWEoyRG5pdzVvMFQ0aGc4VjdfZG1uWl9FWlVpNnJPTGZRam11WUtBaHdwVNIBfkFVX3lxTFBVV01qejl4ci1ZT3FCdDUtc1ppR3Y3UDM2Y0FjZFpYUEN4UUltSWgwd0Y4Y0lJY1UwTkI0Tm9YeFN2N19qMmhKaGpyQXNKN2hvOFpkZ2VWdno5NmFyOVY3WE9PdXNfTGJpVm9xUThadkdmV0xLNGZhTjFjdkFEQQ?oc=5</t>
         </is>
       </c>
-      <c r="T59" s="173">
-        <f>IF($B59="",0,IF(AND(OR(OR(Dashboard!$B$5="All themes",Dashboard!$B$5=""),$C59=Dashboard!$B$5),OR(OR(Dashboard!$G$5="All uses",Dashboard!$G$5=""),$E59=Dashboard!$G$5),N($D59)&gt;=Lists!$H$2,OR(OR(Dashboard!$N$5="All windows",Dashboard!$N$5=""),$P59=Dashboard!$N$5)),1,0))</f>
-        <v/>
-      </c>
-      <c r="U59" s="174">
-        <f>IF($T59=1,N($D59)*1E14+MIN(MAX(N($R59),0),9999)*1E10+MIN(N($K59),99999)*1E5+99999-MIN(ROW(),99999),"")</f>
+      <c r="W59" s="173">
+        <f>IF($B59="",0,IF(AND(OR(OR(Dashboard!$B$5="All themes",Dashboard!$B$5=""),$C59=Dashboard!$B$5),OR(OR(Dashboard!$G$5="All uses",Dashboard!$G$5=""),$E59=Dashboard!$G$5),N($D59)&gt;=Lists!$H$2,OR(OR(Dashboard!$N$5="All windows",Dashboard!$N$5=""),$S59=Dashboard!$N$5)),1,0))</f>
+        <v/>
+      </c>
+      <c r="X59" s="174">
+        <f>IF($W59=1,N($D59)*1E14+MIN(MAX(N($U59),0),9999)*1E10+MIN(N($K59),99999)*1E5+99999-MIN(ROW(),99999),"")</f>
         <v/>
       </c>
     </row>
@@ -11002,34 +11251,37 @@
         </is>
       </c>
       <c r="M60" s="168" t="n"/>
-      <c r="N60" s="169" t="inlineStr">
+      <c r="N60" s="169" t="n"/>
+      <c r="O60" s="166" t="n"/>
+      <c r="P60" s="166" t="n"/>
+      <c r="Q60" s="170" t="inlineStr">
         <is>
           <t>Egypt</t>
         </is>
       </c>
-      <c r="O60" s="167" t="n">
+      <c r="R60" s="167" t="n">
         <v>46318</v>
       </c>
-      <c r="P60" s="170" t="inlineStr">
+      <c r="S60" s="169" t="inlineStr">
         <is>
           <t>2026-Q4</t>
         </is>
       </c>
-      <c r="Q60" s="171" t="n"/>
-      <c r="R60" s="158" t="n">
+      <c r="T60" s="171" t="n"/>
+      <c r="U60" s="158" t="n">
         <v>0</v>
       </c>
-      <c r="S60" s="172" t="inlineStr">
+      <c r="V60" s="172" t="inlineStr">
         <is>
           <t>https://news.google.com/rss/articles/CBMijgFBVV95cUxNdzRhVnVlVUVUU1k4S3pUQVo2RFJENXlEM1V6Z2FrVzRMQ2cxb0pZNkJpWUY5UWFHd1ZIUEZmU2x4SGtydEtXN3k2bTBIYWQ3VmZNZkNTRkhfRFctd3JZdThkRW1HTWIxYmVXRDZsazFZVTJsUzVjTWk0R2FIUElZRG5lLUpaeXpHRlZSdFBn?oc=5</t>
         </is>
       </c>
-      <c r="T60" s="173">
-        <f>IF($B60="",0,IF(AND(OR(OR(Dashboard!$B$5="All themes",Dashboard!$B$5=""),$C60=Dashboard!$B$5),OR(OR(Dashboard!$G$5="All uses",Dashboard!$G$5=""),$E60=Dashboard!$G$5),N($D60)&gt;=Lists!$H$2,OR(OR(Dashboard!$N$5="All windows",Dashboard!$N$5=""),$P60=Dashboard!$N$5)),1,0))</f>
-        <v/>
-      </c>
-      <c r="U60" s="174">
-        <f>IF($T60=1,N($D60)*1E14+MIN(MAX(N($R60),0),9999)*1E10+MIN(N($K60),99999)*1E5+99999-MIN(ROW(),99999),"")</f>
+      <c r="W60" s="173">
+        <f>IF($B60="",0,IF(AND(OR(OR(Dashboard!$B$5="All themes",Dashboard!$B$5=""),$C60=Dashboard!$B$5),OR(OR(Dashboard!$G$5="All uses",Dashboard!$G$5=""),$E60=Dashboard!$G$5),N($D60)&gt;=Lists!$H$2,OR(OR(Dashboard!$N$5="All windows",Dashboard!$N$5=""),$S60=Dashboard!$N$5)),1,0))</f>
+        <v/>
+      </c>
+      <c r="X60" s="174">
+        <f>IF($W60=1,N($D60)*1E14+MIN(MAX(N($U60),0),9999)*1E10+MIN(N($K60),99999)*1E5+99999-MIN(ROW(),99999),"")</f>
         <v/>
       </c>
     </row>
@@ -11081,34 +11333,37 @@
         </is>
       </c>
       <c r="M61" s="168" t="n"/>
-      <c r="N61" s="169" t="inlineStr">
+      <c r="N61" s="169" t="n"/>
+      <c r="O61" s="166" t="n"/>
+      <c r="P61" s="166" t="n"/>
+      <c r="Q61" s="170" t="inlineStr">
         <is>
           <t>Brazil</t>
         </is>
       </c>
-      <c r="O61" s="167" t="n">
-        <v>46319</v>
-      </c>
-      <c r="P61" s="170" t="inlineStr">
+      <c r="R61" s="167" t="n">
+        <v>46319</v>
+      </c>
+      <c r="S61" s="169" t="inlineStr">
         <is>
           <t>2026-Q4</t>
         </is>
       </c>
-      <c r="Q61" s="171" t="n"/>
-      <c r="R61" s="158" t="n">
+      <c r="T61" s="171" t="n"/>
+      <c r="U61" s="158" t="n">
         <v>0</v>
       </c>
-      <c r="S61" s="172" t="inlineStr">
+      <c r="V61" s="172" t="inlineStr">
         <is>
           <t>https://news.google.com/rss/articles/CBMilgFBVV95cUxNS29sd2RXaDlmWXJYMzNQSnJKZGpCWmJpOE9kVEdWQ2RFcUd0UHBGdHdRczJLbFRwTHFDb0ZPY1lHOHNsRGtTLXhTb081eGdyWF9YcmcxZkFrc2VNNzBJOUxNU1ppYnZtWlZBTTlZcXNfa2xNVUZWRTUyMkRlTHRUMmJ4Nk95a1kybUNTTmVPaklQSHktWUE?oc=5</t>
         </is>
       </c>
-      <c r="T61" s="173">
-        <f>IF($B61="",0,IF(AND(OR(OR(Dashboard!$B$5="All themes",Dashboard!$B$5=""),$C61=Dashboard!$B$5),OR(OR(Dashboard!$G$5="All uses",Dashboard!$G$5=""),$E61=Dashboard!$G$5),N($D61)&gt;=Lists!$H$2,OR(OR(Dashboard!$N$5="All windows",Dashboard!$N$5=""),$P61=Dashboard!$N$5)),1,0))</f>
-        <v/>
-      </c>
-      <c r="U61" s="174">
-        <f>IF($T61=1,N($D61)*1E14+MIN(MAX(N($R61),0),9999)*1E10+MIN(N($K61),99999)*1E5+99999-MIN(ROW(),99999),"")</f>
+      <c r="W61" s="173">
+        <f>IF($B61="",0,IF(AND(OR(OR(Dashboard!$B$5="All themes",Dashboard!$B$5=""),$C61=Dashboard!$B$5),OR(OR(Dashboard!$G$5="All uses",Dashboard!$G$5=""),$E61=Dashboard!$G$5),N($D61)&gt;=Lists!$H$2,OR(OR(Dashboard!$N$5="All windows",Dashboard!$N$5=""),$S61=Dashboard!$N$5)),1,0))</f>
+        <v/>
+      </c>
+      <c r="X61" s="174">
+        <f>IF($W61=1,N($D61)*1E14+MIN(MAX(N($U61),0),9999)*1E10+MIN(N($K61),99999)*1E5+99999-MIN(ROW(),99999),"")</f>
         <v/>
       </c>
     </row>
@@ -11156,34 +11411,37 @@
       </c>
       <c r="L62" s="166" t="n"/>
       <c r="M62" s="168" t="n"/>
-      <c r="N62" s="169" t="inlineStr">
+      <c r="N62" s="169" t="n"/>
+      <c r="O62" s="166" t="n"/>
+      <c r="P62" s="166" t="n"/>
+      <c r="Q62" s="170" t="inlineStr">
         <is>
           <t>Argentina</t>
         </is>
       </c>
-      <c r="O62" s="167" t="n">
+      <c r="R62" s="167" t="n">
         <v>46317</v>
       </c>
-      <c r="P62" s="170" t="inlineStr">
+      <c r="S62" s="169" t="inlineStr">
         <is>
           <t>2026-Q4</t>
         </is>
       </c>
-      <c r="Q62" s="171" t="n"/>
-      <c r="R62" s="158" t="n">
+      <c r="T62" s="171" t="n"/>
+      <c r="U62" s="158" t="n">
         <v>0</v>
       </c>
-      <c r="S62" s="172" t="inlineStr">
+      <c r="V62" s="172" t="inlineStr">
         <is>
           <t>https://news.google.com/rss/articles/CBMizAFBVV95cUxOX3FrTEZHRzR0dFNpaDRjdm9hSlZqREtnQ0Nhak51bmpSbTdqOWtyeDNxV0RmekhHR1JNRjlOSXNzb295b0ZjdVJRb29aaUJLbE9JbDJlLUFkMHg4MnZpVkVnVE9pMW1pM3U5YlBjVmZGTVBxVlBtTkJOeHNleHBoQldIRGdNQXo5UExaQ2tqYmZ5Rnd1aEtuakUxalItUnk3ak83Nm5YNDFVZXo4bFBETEZ6czd4N2I1aE1jZnB3OE80Ym1EM2prQkZXMTc?oc=5</t>
         </is>
       </c>
-      <c r="T62" s="173">
-        <f>IF($B62="",0,IF(AND(OR(OR(Dashboard!$B$5="All themes",Dashboard!$B$5=""),$C62=Dashboard!$B$5),OR(OR(Dashboard!$G$5="All uses",Dashboard!$G$5=""),$E62=Dashboard!$G$5),N($D62)&gt;=Lists!$H$2,OR(OR(Dashboard!$N$5="All windows",Dashboard!$N$5=""),$P62=Dashboard!$N$5)),1,0))</f>
-        <v/>
-      </c>
-      <c r="U62" s="174">
-        <f>IF($T62=1,N($D62)*1E14+MIN(MAX(N($R62),0),9999)*1E10+MIN(N($K62),99999)*1E5+99999-MIN(ROW(),99999),"")</f>
+      <c r="W62" s="173">
+        <f>IF($B62="",0,IF(AND(OR(OR(Dashboard!$B$5="All themes",Dashboard!$B$5=""),$C62=Dashboard!$B$5),OR(OR(Dashboard!$G$5="All uses",Dashboard!$G$5=""),$E62=Dashboard!$G$5),N($D62)&gt;=Lists!$H$2,OR(OR(Dashboard!$N$5="All windows",Dashboard!$N$5=""),$S62=Dashboard!$N$5)),1,0))</f>
+        <v/>
+      </c>
+      <c r="X62" s="174">
+        <f>IF($W62=1,N($D62)*1E14+MIN(MAX(N($U62),0),9999)*1E10+MIN(N($K62),99999)*1E5+99999-MIN(ROW(),99999),"")</f>
         <v/>
       </c>
     </row>
@@ -11231,34 +11489,37 @@
       </c>
       <c r="L63" s="166" t="n"/>
       <c r="M63" s="168" t="n"/>
-      <c r="N63" s="169" t="inlineStr">
+      <c r="N63" s="169" t="n"/>
+      <c r="O63" s="166" t="n"/>
+      <c r="P63" s="166" t="n"/>
+      <c r="Q63" s="170" t="inlineStr">
         <is>
           <t>Argentina</t>
         </is>
       </c>
-      <c r="O63" s="167" t="n">
+      <c r="R63" s="167" t="n">
         <v>46318</v>
       </c>
-      <c r="P63" s="170" t="inlineStr">
+      <c r="S63" s="169" t="inlineStr">
         <is>
           <t>2026-Q4</t>
         </is>
       </c>
-      <c r="Q63" s="171" t="n"/>
-      <c r="R63" s="158" t="n">
+      <c r="T63" s="171" t="n"/>
+      <c r="U63" s="158" t="n">
         <v>0</v>
       </c>
-      <c r="S63" s="172" t="inlineStr">
+      <c r="V63" s="172" t="inlineStr">
         <is>
           <t>https://news.google.com/rss/articles/CBMixgFBVV95cUxOVi1Wa2xtWXg5NW1rUUJDa2xWblVjTVpQY3QwdFdWVzJnQzBFcVJKSUtIdFdlMXZmdVhTX2FETTJOREZwVVJ0Yk5TdHVPdjhfX2tvV08yMVhBYVROS0hlalBzMWtuSHBmTWRNcTJhNTN4a0w3b1BIdnVxajVyOER5OGo4dmthTS1nM2ZqOG5Ja1ZkRTR1MFVvWXNhQ3ctX3FfZF9wdjJ6cEppVmc5OXRlWEp6NmRaWllSdGRDQmF6N2RWR3VVZnc?oc=5</t>
         </is>
       </c>
-      <c r="T63" s="173">
-        <f>IF($B63="",0,IF(AND(OR(OR(Dashboard!$B$5="All themes",Dashboard!$B$5=""),$C63=Dashboard!$B$5),OR(OR(Dashboard!$G$5="All uses",Dashboard!$G$5=""),$E63=Dashboard!$G$5),N($D63)&gt;=Lists!$H$2,OR(OR(Dashboard!$N$5="All windows",Dashboard!$N$5=""),$P63=Dashboard!$N$5)),1,0))</f>
-        <v/>
-      </c>
-      <c r="U63" s="174">
-        <f>IF($T63=1,N($D63)*1E14+MIN(MAX(N($R63),0),9999)*1E10+MIN(N($K63),99999)*1E5+99999-MIN(ROW(),99999),"")</f>
+      <c r="W63" s="173">
+        <f>IF($B63="",0,IF(AND(OR(OR(Dashboard!$B$5="All themes",Dashboard!$B$5=""),$C63=Dashboard!$B$5),OR(OR(Dashboard!$G$5="All uses",Dashboard!$G$5=""),$E63=Dashboard!$G$5),N($D63)&gt;=Lists!$H$2,OR(OR(Dashboard!$N$5="All windows",Dashboard!$N$5=""),$S63=Dashboard!$N$5)),1,0))</f>
+        <v/>
+      </c>
+      <c r="X63" s="174">
+        <f>IF($W63=1,N($D63)*1E14+MIN(MAX(N($U63),0),9999)*1E10+MIN(N($K63),99999)*1E5+99999-MIN(ROW(),99999),"")</f>
         <v/>
       </c>
     </row>
@@ -11280,7 +11541,7 @@
       <formula>"Not used"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A4:S63">
+  <conditionalFormatting sqref="A4:V63">
     <cfRule type="expression" priority="6" dxfId="15">
       <formula>$F4="Not used"</formula>
     </cfRule>
@@ -16069,6 +16330,465 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
+    <tabColor rgb="00D38B00"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:I15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="13" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="52" customWidth="1" min="3" max="3"/>
+    <col width="19" customWidth="1" min="4" max="4"/>
+    <col width="26" customWidth="1" min="5" max="5"/>
+    <col width="22" customWidth="1" min="6" max="6"/>
+    <col width="28" customWidth="1" min="7" max="7"/>
+    <col width="34" customWidth="1" min="8" max="8"/>
+    <col width="34" customWidth="1" min="9" max="9"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="26" customHeight="1">
+      <c r="A1" s="152" t="inlineStr">
+        <is>
+          <t>Events · 6 upcoming, 0 open deadlines</t>
+        </is>
+      </c>
+      <c r="D1" s="153" t="inlineStr">
+        <is>
+          <t>← Dashboard</t>
+        </is>
+      </c>
+      <c r="E1" s="153" t="inlineStr">
+        <is>
+          <t>↑ Start here</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="16" customHeight="1">
+      <c r="A2" s="154" t="inlineStr">
+        <is>
+          <t>From the website's events calendar on 24 Oct 2026: ISSMGE conferences, other conferences, courses and webinars, kept by the editors (data/events.yaml) and found by the weekly refresh. Check the dates on each event's website before you publish them.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="22" customHeight="1">
+      <c r="A4" s="7" t="inlineStr">
+        <is>
+          <t>Call-for-papers deadlines (0)</t>
+        </is>
+      </c>
+      <c r="B4" s="8" t="n"/>
+      <c r="C4" s="8" t="n"/>
+      <c r="D4" s="8" t="n"/>
+      <c r="E4" s="8" t="n"/>
+      <c r="F4" s="8" t="n"/>
+      <c r="G4" s="8" t="n"/>
+      <c r="H4" s="8" t="n"/>
+      <c r="I4" s="8" t="n"/>
+    </row>
+    <row r="5" ht="20" customHeight="1">
+      <c r="A5" s="71" t="inlineStr">
+        <is>
+          <t>Deadline</t>
+        </is>
+      </c>
+      <c r="B5" s="71" t="inlineStr">
+        <is>
+          <t>Days left</t>
+        </is>
+      </c>
+      <c r="C5" s="71" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
+      </c>
+      <c r="D5" s="71" t="inlineStr">
+        <is>
+          <t>Kind</t>
+        </is>
+      </c>
+      <c r="E5" s="71" t="inlineStr">
+        <is>
+          <t>Place</t>
+        </is>
+      </c>
+      <c r="F5" s="71" t="inlineStr">
+        <is>
+          <t>Event dates</t>
+        </is>
+      </c>
+      <c r="G5" s="71" t="inlineStr">
+        <is>
+          <t>Organiser</t>
+        </is>
+      </c>
+      <c r="H5" s="71" t="inlineStr">
+        <is>
+          <t>What is due</t>
+        </is>
+      </c>
+      <c r="I5" s="71" t="inlineStr">
+        <is>
+          <t>Website</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="C6" s="234" t="inlineStr">
+        <is>
+          <t>No call-for-papers deadline is open at the moment.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="22" customHeight="1">
+      <c r="A8" s="7" t="inlineStr">
+        <is>
+          <t>Upcoming events (6)</t>
+        </is>
+      </c>
+      <c r="B8" s="8" t="n"/>
+      <c r="C8" s="8" t="n"/>
+      <c r="D8" s="8" t="n"/>
+      <c r="E8" s="8" t="n"/>
+      <c r="F8" s="8" t="n"/>
+      <c r="G8" s="8" t="n"/>
+      <c r="H8" s="8" t="n"/>
+      <c r="I8" s="8" t="n"/>
+    </row>
+    <row r="9" ht="20" customHeight="1">
+      <c r="A9" s="71" t="inlineStr">
+        <is>
+          <t>Starts</t>
+        </is>
+      </c>
+      <c r="B9" s="71" t="inlineStr">
+        <is>
+          <t>ISSMGE</t>
+        </is>
+      </c>
+      <c r="C9" s="71" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
+      </c>
+      <c r="D9" s="71" t="inlineStr">
+        <is>
+          <t>Kind</t>
+        </is>
+      </c>
+      <c r="E9" s="71" t="inlineStr">
+        <is>
+          <t>Place</t>
+        </is>
+      </c>
+      <c r="F9" s="71" t="inlineStr">
+        <is>
+          <t>Dates</t>
+        </is>
+      </c>
+      <c r="G9" s="71" t="inlineStr">
+        <is>
+          <t>Organiser</t>
+        </is>
+      </c>
+      <c r="H9" s="71" t="inlineStr">
+        <is>
+          <t>Deadlines</t>
+        </is>
+      </c>
+      <c r="I9" s="71" t="inlineStr">
+        <is>
+          <t>Website</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="17.5" customHeight="1">
+      <c r="A10" s="235" t="n">
+        <v>46447</v>
+      </c>
+      <c r="B10" s="236" t="n"/>
+      <c r="C10" s="229" t="inlineStr">
+        <is>
+          <t>Geo-Congress 2027, part of ASCE2027</t>
+        </is>
+      </c>
+      <c r="D10" s="237" t="inlineStr">
+        <is>
+          <t>Other conference</t>
+        </is>
+      </c>
+      <c r="E10" s="166" t="inlineStr">
+        <is>
+          <t>Philadelphia, United States</t>
+        </is>
+      </c>
+      <c r="F10" s="166" t="inlineStr">
+        <is>
+          <t>1–5 Mar 2027</t>
+        </is>
+      </c>
+      <c r="G10" s="230" t="inlineStr">
+        <is>
+          <t>ASCE Geo-Institute</t>
+        </is>
+      </c>
+      <c r="H10" s="230" t="inlineStr">
+        <is>
+          <t>Abstracts: 4 Mar 2026</t>
+        </is>
+      </c>
+      <c r="I10" s="238" t="inlineStr">
+        <is>
+          <t>https://geoinstitute.org/news/call-abstract-geo-congress-2027-part-asce2027</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="30" customHeight="1">
+      <c r="A11" s="235" t="n">
+        <v>46489</v>
+      </c>
+      <c r="B11" s="236" t="inlineStr">
+        <is>
+          <t>ISSMGE</t>
+        </is>
+      </c>
+      <c r="C11" s="229" t="inlineStr">
+        <is>
+          <t>2nd International Symposium on Ground Improvement (IS-GI 2027)</t>
+        </is>
+      </c>
+      <c r="D11" s="239" t="inlineStr">
+        <is>
+          <t>ISSMGE-supported</t>
+        </is>
+      </c>
+      <c r="E11" s="166" t="inlineStr">
+        <is>
+          <t>Lyon, France</t>
+        </is>
+      </c>
+      <c r="F11" s="166" t="inlineStr">
+        <is>
+          <t>12–14 Apr 2027</t>
+        </is>
+      </c>
+      <c r="G11" s="230" t="inlineStr">
+        <is>
+          <t>ISSMGE TC211</t>
+        </is>
+      </c>
+      <c r="H11" s="230" t="inlineStr">
+        <is>
+          <t>Abstracts: 15 May 2026</t>
+        </is>
+      </c>
+      <c r="I11" s="238" t="inlineStr">
+        <is>
+          <t>https://www.issmge.org/news/2nd-is-gi-2027-lyon-call-for-abstracts</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="30" customHeight="1">
+      <c r="A12" s="235" t="n">
+        <v>46500</v>
+      </c>
+      <c r="B12" s="236" t="n"/>
+      <c r="C12" s="229" t="inlineStr">
+        <is>
+          <t>ITA-AITES World Tunnel Congress 2027 (WTC 2027)</t>
+        </is>
+      </c>
+      <c r="D12" s="237" t="inlineStr">
+        <is>
+          <t>Other conference</t>
+        </is>
+      </c>
+      <c r="E12" s="166" t="inlineStr">
+        <is>
+          <t>Antwerp, Belgium</t>
+        </is>
+      </c>
+      <c r="F12" s="166" t="inlineStr">
+        <is>
+          <t>23–29 Apr 2027</t>
+        </is>
+      </c>
+      <c r="G12" s="230" t="inlineStr">
+        <is>
+          <t>ITA-AITES with the Belgian Tunnel Association</t>
+        </is>
+      </c>
+      <c r="H12" s="230" t="inlineStr">
+        <is>
+          <t>Abstracts: 10 Jun 2026</t>
+        </is>
+      </c>
+      <c r="I12" s="238" t="inlineStr">
+        <is>
+          <t>https://about.ita-aites.org/future-events/2350/world-tunnel-congress-wtc-2027</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="30" customHeight="1">
+      <c r="A13" s="235" t="n">
+        <v>46566</v>
+      </c>
+      <c r="B13" s="236" t="inlineStr">
+        <is>
+          <t>ISSMGE</t>
+        </is>
+      </c>
+      <c r="C13" s="229" t="inlineStr">
+        <is>
+          <t>International Conference on Sustainability in Geotechnical Engineering (ICSGE 2027)</t>
+        </is>
+      </c>
+      <c r="D13" s="239" t="inlineStr">
+        <is>
+          <t>ISSMGE-supported</t>
+        </is>
+      </c>
+      <c r="E13" s="166" t="inlineStr">
+        <is>
+          <t>Lisbon, Portugal</t>
+        </is>
+      </c>
+      <c r="F13" s="166" t="inlineStr">
+        <is>
+          <t>28 Jun – 1 Jul 2027</t>
+        </is>
+      </c>
+      <c r="G13" s="230" t="inlineStr">
+        <is>
+          <t>ISSMGE TC307 and LNEC</t>
+        </is>
+      </c>
+      <c r="H13" s="230" t="inlineStr">
+        <is>
+          <t>Abstracts: 15 Jul 2026</t>
+        </is>
+      </c>
+      <c r="I13" s="238" t="inlineStr">
+        <is>
+          <t>https://www.issmge.org/news/tc223-june-news-update</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="30" customHeight="1">
+      <c r="A14" s="235" t="n">
+        <v>46644</v>
+      </c>
+      <c r="B14" s="236" t="inlineStr">
+        <is>
+          <t>ISSMGE</t>
+        </is>
+      </c>
+      <c r="C14" s="229" t="inlineStr">
+        <is>
+          <t>9th International Symposium on Deformation Characteristics of Geomaterials (IS-Ankara 2027)</t>
+        </is>
+      </c>
+      <c r="D14" s="239" t="inlineStr">
+        <is>
+          <t>ISSMGE-supported</t>
+        </is>
+      </c>
+      <c r="E14" s="166" t="inlineStr">
+        <is>
+          <t>Ankara, Türkiye</t>
+        </is>
+      </c>
+      <c r="F14" s="166" t="inlineStr">
+        <is>
+          <t>14–17 Sep 2027</t>
+        </is>
+      </c>
+      <c r="G14" s="230" t="inlineStr">
+        <is>
+          <t>ISSMGE TC101, Middle East Technical University (METU)</t>
+        </is>
+      </c>
+      <c r="H14" s="230" t="inlineStr">
+        <is>
+          <t>Abstracts: 21 Sep 2026</t>
+        </is>
+      </c>
+      <c r="I14" s="238" t="inlineStr">
+        <is>
+          <t>https://www.issmge.org/news/tc223-june-news-update</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="30" customHeight="1">
+      <c r="A15" s="235" t="n">
+        <v>46700</v>
+      </c>
+      <c r="B15" s="236" t="inlineStr">
+        <is>
+          <t>ISSMGE</t>
+        </is>
+      </c>
+      <c r="C15" s="229" t="inlineStr">
+        <is>
+          <t>18th Asian Regional Conference on Soil Mechanics and Geotechnical Engineering (18ARC)</t>
+        </is>
+      </c>
+      <c r="D15" s="240" t="inlineStr">
+        <is>
+          <t>ISSMGE conference</t>
+        </is>
+      </c>
+      <c r="E15" s="166" t="inlineStr">
+        <is>
+          <t>Bangkok, Thailand</t>
+        </is>
+      </c>
+      <c r="F15" s="166" t="inlineStr">
+        <is>
+          <t>9–13 Nov 2027</t>
+        </is>
+      </c>
+      <c r="G15" s="230" t="inlineStr">
+        <is>
+          <t>Thai Geotechnical Society, under the auspices of ISSMGE</t>
+        </is>
+      </c>
+      <c r="H15" s="230" t="n"/>
+      <c r="I15" s="238" t="inlineStr">
+        <is>
+          <t>https://www.issmge.org/events/18arc</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <hyperlinks>
+    <hyperlink ref="D1" location="'Dashboard'!A1" display="← Dashboard"/>
+    <hyperlink ref="E1" location="'Start here'!A1" display="↑ Start here"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I10" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I11" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I12" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I13" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I14" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I15" r:id="rId6"/>
+  </hyperlinks>
+  <printOptions horizontalCentered="1"/>
+  <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.55" header="0.25" footer="0.25"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;L&amp;"Arial"&amp;8 &amp;A&amp;R&amp;"Arial"&amp;8 Page &amp;P of &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
     <tabColor rgb="000B97A5"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
@@ -16164,25 +16884,25 @@
           <t>Vietnam.vn</t>
         </is>
       </c>
-      <c r="B4" s="234" t="n">
+      <c r="B4" s="241" t="n">
         <v>16</v>
       </c>
-      <c r="C4" s="235">
-        <f>SUMPRODUCT(Stories!$T$4:$T$63,--(Stories!$J$4:$J$63=$A4))</f>
-        <v/>
-      </c>
-      <c r="D4" s="236" t="n">
+      <c r="C4" s="242">
+        <f>SUMPRODUCT(Stories!$W$4:$W$63,--(Stories!$J$4:$J$63=$A4))</f>
+        <v/>
+      </c>
+      <c r="D4" s="243" t="n">
         <v>3.9</v>
       </c>
-      <c r="E4" s="234" t="n">
+      <c r="E4" s="241" t="n">
         <v>13</v>
       </c>
-      <c r="F4" s="237" t="inlineStr">
+      <c r="F4" s="244" t="inlineStr">
         <is>
           <t>Hazards &amp; Resilience</t>
         </is>
       </c>
-      <c r="G4" s="234" t="n">
+      <c r="G4" s="241" t="n">
         <v>5</v>
       </c>
       <c r="H4" s="171" t="inlineStr">
@@ -16190,7 +16910,7 @@
           <t>Vietnam, Egypt, Indonesia, Russia, Colombia, Spain, South Korea, Brazil</t>
         </is>
       </c>
-      <c r="I4" s="238" t="n">
+      <c r="I4" s="245" t="n">
         <v>46319</v>
       </c>
     </row>
@@ -16200,29 +16920,29 @@
           <t>Ground Engineering</t>
         </is>
       </c>
-      <c r="B5" s="234" t="n">
+      <c r="B5" s="241" t="n">
         <v>2</v>
       </c>
-      <c r="C5" s="235">
-        <f>SUMPRODUCT(Stories!$T$4:$T$63,--(Stories!$J$4:$J$63=$A5))</f>
-        <v/>
-      </c>
-      <c r="D5" s="236" t="n">
+      <c r="C5" s="242">
+        <f>SUMPRODUCT(Stories!$W$4:$W$63,--(Stories!$J$4:$J$63=$A5))</f>
+        <v/>
+      </c>
+      <c r="D5" s="243" t="n">
         <v>4.5</v>
       </c>
-      <c r="E5" s="234" t="n">
+      <c r="E5" s="241" t="n">
         <v>2</v>
       </c>
-      <c r="F5" s="239" t="inlineStr">
+      <c r="F5" s="246" t="inlineStr">
         <is>
           <t>Offshore, Coasts &amp; Water</t>
         </is>
       </c>
-      <c r="G5" s="234" t="n">
+      <c r="G5" s="241" t="n">
         <v>2</v>
       </c>
       <c r="H5" s="171" t="inlineStr"/>
-      <c r="I5" s="238" t="n">
+      <c r="I5" s="245" t="n">
         <v>46319</v>
       </c>
     </row>
@@ -16232,29 +16952,29 @@
           <t>Tunnelling Journal</t>
         </is>
       </c>
-      <c r="B6" s="234" t="n">
+      <c r="B6" s="241" t="n">
         <v>2</v>
       </c>
-      <c r="C6" s="235">
-        <f>SUMPRODUCT(Stories!$T$4:$T$63,--(Stories!$J$4:$J$63=$A6))</f>
-        <v/>
-      </c>
-      <c r="D6" s="236" t="n">
+      <c r="C6" s="242">
+        <f>SUMPRODUCT(Stories!$W$4:$W$63,--(Stories!$J$4:$J$63=$A6))</f>
+        <v/>
+      </c>
+      <c r="D6" s="243" t="n">
         <v>3</v>
       </c>
-      <c r="E6" s="234" t="n">
+      <c r="E6" s="241" t="n">
         <v>0</v>
       </c>
-      <c r="F6" s="240" t="inlineStr">
+      <c r="F6" s="247" t="inlineStr">
         <is>
           <t>Infrastructure &amp; the Underground City</t>
         </is>
       </c>
-      <c r="G6" s="234" t="n">
+      <c r="G6" s="241" t="n">
         <v>2</v>
       </c>
       <c r="H6" s="171" t="inlineStr"/>
-      <c r="I6" s="238" t="n">
+      <c r="I6" s="245" t="n">
         <v>46319</v>
       </c>
     </row>
@@ -16264,29 +16984,29 @@
           <t>Tunnels &amp; Tunnelling</t>
         </is>
       </c>
-      <c r="B7" s="234" t="n">
+      <c r="B7" s="241" t="n">
         <v>2</v>
       </c>
-      <c r="C7" s="235">
-        <f>SUMPRODUCT(Stories!$T$4:$T$63,--(Stories!$J$4:$J$63=$A7))</f>
-        <v/>
-      </c>
-      <c r="D7" s="236" t="n">
+      <c r="C7" s="242">
+        <f>SUMPRODUCT(Stories!$W$4:$W$63,--(Stories!$J$4:$J$63=$A7))</f>
+        <v/>
+      </c>
+      <c r="D7" s="243" t="n">
         <v>3</v>
       </c>
-      <c r="E7" s="234" t="n">
+      <c r="E7" s="241" t="n">
         <v>0</v>
       </c>
-      <c r="F7" s="241" t="inlineStr">
+      <c r="F7" s="248" t="inlineStr">
         <is>
           <t>Sustainability &amp; the Energy Transition</t>
         </is>
       </c>
-      <c r="G7" s="234" t="n">
+      <c r="G7" s="241" t="n">
         <v>1</v>
       </c>
       <c r="H7" s="171" t="inlineStr"/>
-      <c r="I7" s="238" t="n">
+      <c r="I7" s="245" t="n">
         <v>46319</v>
       </c>
     </row>
@@ -16296,25 +17016,25 @@
           <t>生物通</t>
         </is>
       </c>
-      <c r="B8" s="234" t="n">
+      <c r="B8" s="241" t="n">
         <v>2</v>
       </c>
-      <c r="C8" s="235">
-        <f>SUMPRODUCT(Stories!$T$4:$T$63,--(Stories!$J$4:$J$63=$A8))</f>
-        <v/>
-      </c>
-      <c r="D8" s="236" t="n">
+      <c r="C8" s="242">
+        <f>SUMPRODUCT(Stories!$W$4:$W$63,--(Stories!$J$4:$J$63=$A8))</f>
+        <v/>
+      </c>
+      <c r="D8" s="243" t="n">
         <v>4.5</v>
       </c>
-      <c r="E8" s="234" t="n">
+      <c r="E8" s="241" t="n">
         <v>2</v>
       </c>
-      <c r="F8" s="242" t="inlineStr">
+      <c r="F8" s="249" t="inlineStr">
         <is>
           <t>Digital Geotechnics</t>
         </is>
       </c>
-      <c r="G8" s="234" t="n">
+      <c r="G8" s="241" t="n">
         <v>2</v>
       </c>
       <c r="H8" s="171" t="inlineStr">
@@ -16322,7 +17042,7 @@
           <t>China</t>
         </is>
       </c>
-      <c r="I8" s="238" t="n">
+      <c r="I8" s="245" t="n">
         <v>46319</v>
       </c>
     </row>
@@ -16332,25 +17052,25 @@
           <t>:: Foro Coatza ::</t>
         </is>
       </c>
-      <c r="B9" s="234" t="n">
+      <c r="B9" s="241" t="n">
         <v>1</v>
       </c>
-      <c r="C9" s="235">
-        <f>SUMPRODUCT(Stories!$T$4:$T$63,--(Stories!$J$4:$J$63=$A9))</f>
-        <v/>
-      </c>
-      <c r="D9" s="236" t="n">
+      <c r="C9" s="242">
+        <f>SUMPRODUCT(Stories!$W$4:$W$63,--(Stories!$J$4:$J$63=$A9))</f>
+        <v/>
+      </c>
+      <c r="D9" s="243" t="n">
         <v>3</v>
       </c>
-      <c r="E9" s="234" t="n">
+      <c r="E9" s="241" t="n">
         <v>0</v>
       </c>
-      <c r="F9" s="239" t="inlineStr">
+      <c r="F9" s="246" t="inlineStr">
         <is>
           <t>Offshore, Coasts &amp; Water</t>
         </is>
       </c>
-      <c r="G9" s="234" t="n">
+      <c r="G9" s="241" t="n">
         <v>1</v>
       </c>
       <c r="H9" s="171" t="inlineStr">
@@ -16358,7 +17078,7 @@
           <t>Argentina</t>
         </is>
       </c>
-      <c r="I9" s="238" t="n">
+      <c r="I9" s="245" t="n">
         <v>46319</v>
       </c>
     </row>
@@ -16368,25 +17088,25 @@
           <t>agenzia giornalistica opinione</t>
         </is>
       </c>
-      <c r="B10" s="234" t="n">
+      <c r="B10" s="241" t="n">
         <v>1</v>
       </c>
-      <c r="C10" s="235">
-        <f>SUMPRODUCT(Stories!$T$4:$T$63,--(Stories!$J$4:$J$63=$A10))</f>
-        <v/>
-      </c>
-      <c r="D10" s="236" t="n">
+      <c r="C10" s="242">
+        <f>SUMPRODUCT(Stories!$W$4:$W$63,--(Stories!$J$4:$J$63=$A10))</f>
+        <v/>
+      </c>
+      <c r="D10" s="243" t="n">
         <v>4</v>
       </c>
-      <c r="E10" s="234" t="n">
+      <c r="E10" s="241" t="n">
         <v>1</v>
       </c>
-      <c r="F10" s="237" t="inlineStr">
+      <c r="F10" s="244" t="inlineStr">
         <is>
           <t>Hazards &amp; Resilience</t>
         </is>
       </c>
-      <c r="G10" s="234" t="n">
+      <c r="G10" s="241" t="n">
         <v>1</v>
       </c>
       <c r="H10" s="171" t="inlineStr">
@@ -16394,7 +17114,7 @@
           <t>Italy</t>
         </is>
       </c>
-      <c r="I10" s="238" t="n">
+      <c r="I10" s="245" t="n">
         <v>46319</v>
       </c>
     </row>
@@ -16404,25 +17124,25 @@
           <t>Baolangson.vn</t>
         </is>
       </c>
-      <c r="B11" s="234" t="n">
+      <c r="B11" s="241" t="n">
         <v>1</v>
       </c>
-      <c r="C11" s="235">
-        <f>SUMPRODUCT(Stories!$T$4:$T$63,--(Stories!$J$4:$J$63=$A11))</f>
-        <v/>
-      </c>
-      <c r="D11" s="236" t="n">
+      <c r="C11" s="242">
+        <f>SUMPRODUCT(Stories!$W$4:$W$63,--(Stories!$J$4:$J$63=$A11))</f>
+        <v/>
+      </c>
+      <c r="D11" s="243" t="n">
         <v>4</v>
       </c>
-      <c r="E11" s="234" t="n">
+      <c r="E11" s="241" t="n">
         <v>1</v>
       </c>
-      <c r="F11" s="237" t="inlineStr">
+      <c r="F11" s="244" t="inlineStr">
         <is>
           <t>Hazards &amp; Resilience</t>
         </is>
       </c>
-      <c r="G11" s="234" t="n">
+      <c r="G11" s="241" t="n">
         <v>1</v>
       </c>
       <c r="H11" s="171" t="inlineStr">
@@ -16430,7 +17150,7 @@
           <t>Vietnam</t>
         </is>
       </c>
-      <c r="I11" s="238" t="n">
+      <c r="I11" s="245" t="n">
         <v>46319</v>
       </c>
     </row>
@@ -16440,25 +17160,25 @@
           <t>BioBioChile</t>
         </is>
       </c>
-      <c r="B12" s="234" t="n">
+      <c r="B12" s="241" t="n">
         <v>1</v>
       </c>
-      <c r="C12" s="235">
-        <f>SUMPRODUCT(Stories!$T$4:$T$63,--(Stories!$J$4:$J$63=$A12))</f>
-        <v/>
-      </c>
-      <c r="D12" s="236" t="n">
+      <c r="C12" s="242">
+        <f>SUMPRODUCT(Stories!$W$4:$W$63,--(Stories!$J$4:$J$63=$A12))</f>
+        <v/>
+      </c>
+      <c r="D12" s="243" t="n">
         <v>4</v>
       </c>
-      <c r="E12" s="234" t="n">
+      <c r="E12" s="241" t="n">
         <v>1</v>
       </c>
-      <c r="F12" s="240" t="inlineStr">
+      <c r="F12" s="247" t="inlineStr">
         <is>
           <t>Infrastructure &amp; the Underground City</t>
         </is>
       </c>
-      <c r="G12" s="234" t="n">
+      <c r="G12" s="241" t="n">
         <v>1</v>
       </c>
       <c r="H12" s="171" t="inlineStr">
@@ -16466,7 +17186,7 @@
           <t>Colombia</t>
         </is>
       </c>
-      <c r="I12" s="238" t="n">
+      <c r="I12" s="245" t="n">
         <v>46319</v>
       </c>
     </row>
@@ -16476,25 +17196,25 @@
           <t>Boyacá 7 Días</t>
         </is>
       </c>
-      <c r="B13" s="234" t="n">
+      <c r="B13" s="241" t="n">
         <v>1</v>
       </c>
-      <c r="C13" s="235">
-        <f>SUMPRODUCT(Stories!$T$4:$T$63,--(Stories!$J$4:$J$63=$A13))</f>
-        <v/>
-      </c>
-      <c r="D13" s="236" t="n">
+      <c r="C13" s="242">
+        <f>SUMPRODUCT(Stories!$W$4:$W$63,--(Stories!$J$4:$J$63=$A13))</f>
+        <v/>
+      </c>
+      <c r="D13" s="243" t="n">
         <v>3</v>
       </c>
-      <c r="E13" s="234" t="n">
+      <c r="E13" s="241" t="n">
         <v>0</v>
       </c>
-      <c r="F13" s="243" t="inlineStr">
+      <c r="F13" s="250" t="inlineStr">
         <is>
           <t>Geotechnics &amp; Society</t>
         </is>
       </c>
-      <c r="G13" s="234" t="n">
+      <c r="G13" s="241" t="n">
         <v>1</v>
       </c>
       <c r="H13" s="171" t="inlineStr">
@@ -16502,7 +17222,7 @@
           <t>Colombia</t>
         </is>
       </c>
-      <c r="I13" s="238" t="n">
+      <c r="I13" s="245" t="n">
         <v>46319</v>
       </c>
     </row>
@@ -16512,25 +17232,25 @@
           <t>Báo Thanh Niên</t>
         </is>
       </c>
-      <c r="B14" s="234" t="n">
+      <c r="B14" s="241" t="n">
         <v>1</v>
       </c>
-      <c r="C14" s="235">
-        <f>SUMPRODUCT(Stories!$T$4:$T$63,--(Stories!$J$4:$J$63=$A14))</f>
-        <v/>
-      </c>
-      <c r="D14" s="236" t="n">
+      <c r="C14" s="242">
+        <f>SUMPRODUCT(Stories!$W$4:$W$63,--(Stories!$J$4:$J$63=$A14))</f>
+        <v/>
+      </c>
+      <c r="D14" s="243" t="n">
         <v>4</v>
       </c>
-      <c r="E14" s="234" t="n">
+      <c r="E14" s="241" t="n">
         <v>1</v>
       </c>
-      <c r="F14" s="237" t="inlineStr">
+      <c r="F14" s="244" t="inlineStr">
         <is>
           <t>Hazards &amp; Resilience</t>
         </is>
       </c>
-      <c r="G14" s="234" t="n">
+      <c r="G14" s="241" t="n">
         <v>1</v>
       </c>
       <c r="H14" s="171" t="inlineStr">
@@ -16538,7 +17258,7 @@
           <t>Vietnam</t>
         </is>
       </c>
-      <c r="I14" s="238" t="n">
+      <c r="I14" s="245" t="n">
         <v>46319</v>
       </c>
     </row>
@@ -16548,25 +17268,25 @@
           <t>Báo và phát thanh, truyền hình Đồng Tháp</t>
         </is>
       </c>
-      <c r="B15" s="234" t="n">
+      <c r="B15" s="241" t="n">
         <v>1</v>
       </c>
-      <c r="C15" s="235">
-        <f>SUMPRODUCT(Stories!$T$4:$T$63,--(Stories!$J$4:$J$63=$A15))</f>
-        <v/>
-      </c>
-      <c r="D15" s="236" t="n">
+      <c r="C15" s="242">
+        <f>SUMPRODUCT(Stories!$W$4:$W$63,--(Stories!$J$4:$J$63=$A15))</f>
+        <v/>
+      </c>
+      <c r="D15" s="243" t="n">
         <v>4</v>
       </c>
-      <c r="E15" s="234" t="n">
+      <c r="E15" s="241" t="n">
         <v>1</v>
       </c>
-      <c r="F15" s="237" t="inlineStr">
+      <c r="F15" s="244" t="inlineStr">
         <is>
           <t>Hazards &amp; Resilience</t>
         </is>
       </c>
-      <c r="G15" s="234" t="n">
+      <c r="G15" s="241" t="n">
         <v>1</v>
       </c>
       <c r="H15" s="171" t="inlineStr">
@@ -16574,7 +17294,7 @@
           <t>Vietnam</t>
         </is>
       </c>
-      <c r="I15" s="238" t="n">
+      <c r="I15" s="245" t="n">
         <v>46319</v>
       </c>
     </row>
@@ -16584,25 +17304,25 @@
           <t>Cooperativa</t>
         </is>
       </c>
-      <c r="B16" s="234" t="n">
+      <c r="B16" s="241" t="n">
         <v>1</v>
       </c>
-      <c r="C16" s="235">
-        <f>SUMPRODUCT(Stories!$T$4:$T$63,--(Stories!$J$4:$J$63=$A16))</f>
-        <v/>
-      </c>
-      <c r="D16" s="236" t="n">
+      <c r="C16" s="242">
+        <f>SUMPRODUCT(Stories!$W$4:$W$63,--(Stories!$J$4:$J$63=$A16))</f>
+        <v/>
+      </c>
+      <c r="D16" s="243" t="n">
         <v>4</v>
       </c>
-      <c r="E16" s="234" t="n">
+      <c r="E16" s="241" t="n">
         <v>1</v>
       </c>
-      <c r="F16" s="240" t="inlineStr">
+      <c r="F16" s="247" t="inlineStr">
         <is>
           <t>Infrastructure &amp; the Underground City</t>
         </is>
       </c>
-      <c r="G16" s="234" t="n">
+      <c r="G16" s="241" t="n">
         <v>1</v>
       </c>
       <c r="H16" s="171" t="inlineStr">
@@ -16610,7 +17330,7 @@
           <t>Colombia</t>
         </is>
       </c>
-      <c r="I16" s="238" t="n">
+      <c r="I16" s="245" t="n">
         <v>46319</v>
       </c>
     </row>
@@ -16620,25 +17340,25 @@
           <t>Debate</t>
         </is>
       </c>
-      <c r="B17" s="234" t="n">
+      <c r="B17" s="241" t="n">
         <v>1</v>
       </c>
-      <c r="C17" s="235">
-        <f>SUMPRODUCT(Stories!$T$4:$T$63,--(Stories!$J$4:$J$63=$A17))</f>
-        <v/>
-      </c>
-      <c r="D17" s="236" t="n">
+      <c r="C17" s="242">
+        <f>SUMPRODUCT(Stories!$W$4:$W$63,--(Stories!$J$4:$J$63=$A17))</f>
+        <v/>
+      </c>
+      <c r="D17" s="243" t="n">
         <v>4</v>
       </c>
-      <c r="E17" s="234" t="n">
+      <c r="E17" s="241" t="n">
         <v>1</v>
       </c>
-      <c r="F17" s="240" t="inlineStr">
+      <c r="F17" s="247" t="inlineStr">
         <is>
           <t>Infrastructure &amp; the Underground City</t>
         </is>
       </c>
-      <c r="G17" s="234" t="n">
+      <c r="G17" s="241" t="n">
         <v>1</v>
       </c>
       <c r="H17" s="171" t="inlineStr">
@@ -16646,7 +17366,7 @@
           <t>Colombia</t>
         </is>
       </c>
-      <c r="I17" s="238" t="n">
+      <c r="I17" s="245" t="n">
         <v>46319</v>
       </c>
     </row>
@@ -16656,25 +17376,25 @@
           <t>Detona, Real News</t>
         </is>
       </c>
-      <c r="B18" s="234" t="n">
+      <c r="B18" s="241" t="n">
         <v>1</v>
       </c>
-      <c r="C18" s="235">
-        <f>SUMPRODUCT(Stories!$T$4:$T$63,--(Stories!$J$4:$J$63=$A18))</f>
-        <v/>
-      </c>
-      <c r="D18" s="236" t="n">
+      <c r="C18" s="242">
+        <f>SUMPRODUCT(Stories!$W$4:$W$63,--(Stories!$J$4:$J$63=$A18))</f>
+        <v/>
+      </c>
+      <c r="D18" s="243" t="n">
         <v>3</v>
       </c>
-      <c r="E18" s="234" t="n">
+      <c r="E18" s="241" t="n">
         <v>0</v>
       </c>
-      <c r="F18" s="240" t="inlineStr">
+      <c r="F18" s="247" t="inlineStr">
         <is>
           <t>Infrastructure &amp; the Underground City</t>
         </is>
       </c>
-      <c r="G18" s="234" t="n">
+      <c r="G18" s="241" t="n">
         <v>1</v>
       </c>
       <c r="H18" s="171" t="inlineStr">
@@ -16682,7 +17402,7 @@
           <t>Colombia</t>
         </is>
       </c>
-      <c r="I18" s="238" t="n">
+      <c r="I18" s="245" t="n">
         <v>46319</v>
       </c>
     </row>
@@ -16692,25 +17412,25 @@
           <t>El Litoral | Novedades de Corrientes</t>
         </is>
       </c>
-      <c r="B19" s="234" t="n">
+      <c r="B19" s="241" t="n">
         <v>1</v>
       </c>
-      <c r="C19" s="235">
-        <f>SUMPRODUCT(Stories!$T$4:$T$63,--(Stories!$J$4:$J$63=$A19))</f>
-        <v/>
-      </c>
-      <c r="D19" s="236" t="n">
+      <c r="C19" s="242">
+        <f>SUMPRODUCT(Stories!$W$4:$W$63,--(Stories!$J$4:$J$63=$A19))</f>
+        <v/>
+      </c>
+      <c r="D19" s="243" t="n">
         <v>3</v>
       </c>
-      <c r="E19" s="234" t="n">
+      <c r="E19" s="241" t="n">
         <v>0</v>
       </c>
-      <c r="F19" s="239" t="inlineStr">
+      <c r="F19" s="246" t="inlineStr">
         <is>
           <t>Offshore, Coasts &amp; Water</t>
         </is>
       </c>
-      <c r="G19" s="234" t="n">
+      <c r="G19" s="241" t="n">
         <v>1</v>
       </c>
       <c r="H19" s="171" t="inlineStr">
@@ -16718,7 +17438,7 @@
           <t>Argentina</t>
         </is>
       </c>
-      <c r="I19" s="238" t="n">
+      <c r="I19" s="245" t="n">
         <v>46319</v>
       </c>
     </row>
@@ -16728,25 +17448,25 @@
           <t>El Siglo de Torreón</t>
         </is>
       </c>
-      <c r="B20" s="234" t="n">
+      <c r="B20" s="241" t="n">
         <v>1</v>
       </c>
-      <c r="C20" s="235">
-        <f>SUMPRODUCT(Stories!$T$4:$T$63,--(Stories!$J$4:$J$63=$A20))</f>
-        <v/>
-      </c>
-      <c r="D20" s="236" t="n">
+      <c r="C20" s="242">
+        <f>SUMPRODUCT(Stories!$W$4:$W$63,--(Stories!$J$4:$J$63=$A20))</f>
+        <v/>
+      </c>
+      <c r="D20" s="243" t="n">
         <v>3</v>
       </c>
-      <c r="E20" s="234" t="n">
+      <c r="E20" s="241" t="n">
         <v>0</v>
       </c>
-      <c r="F20" s="240" t="inlineStr">
+      <c r="F20" s="247" t="inlineStr">
         <is>
           <t>Infrastructure &amp; the Underground City</t>
         </is>
       </c>
-      <c r="G20" s="234" t="n">
+      <c r="G20" s="241" t="n">
         <v>1</v>
       </c>
       <c r="H20" s="171" t="inlineStr">
@@ -16754,7 +17474,7 @@
           <t>Colombia</t>
         </is>
       </c>
-      <c r="I20" s="238" t="n">
+      <c r="I20" s="245" t="n">
         <v>46319</v>
       </c>
     </row>
@@ -16764,25 +17484,25 @@
           <t>El Universal</t>
         </is>
       </c>
-      <c r="B21" s="234" t="n">
+      <c r="B21" s="241" t="n">
         <v>1</v>
       </c>
-      <c r="C21" s="235">
-        <f>SUMPRODUCT(Stories!$T$4:$T$63,--(Stories!$J$4:$J$63=$A21))</f>
-        <v/>
-      </c>
-      <c r="D21" s="236" t="n">
+      <c r="C21" s="242">
+        <f>SUMPRODUCT(Stories!$W$4:$W$63,--(Stories!$J$4:$J$63=$A21))</f>
+        <v/>
+      </c>
+      <c r="D21" s="243" t="n">
         <v>3</v>
       </c>
-      <c r="E21" s="234" t="n">
+      <c r="E21" s="241" t="n">
         <v>0</v>
       </c>
-      <c r="F21" s="239" t="inlineStr">
+      <c r="F21" s="246" t="inlineStr">
         <is>
           <t>Offshore, Coasts &amp; Water</t>
         </is>
       </c>
-      <c r="G21" s="234" t="n">
+      <c r="G21" s="241" t="n">
         <v>1</v>
       </c>
       <c r="H21" s="171" t="inlineStr">
@@ -16790,7 +17510,7 @@
           <t>Colombia</t>
         </is>
       </c>
-      <c r="I21" s="238" t="n">
+      <c r="I21" s="245" t="n">
         <v>46319</v>
       </c>
     </row>
@@ -16800,25 +17520,25 @@
           <t>El Universo</t>
         </is>
       </c>
-      <c r="B22" s="234" t="n">
+      <c r="B22" s="241" t="n">
         <v>1</v>
       </c>
-      <c r="C22" s="235">
-        <f>SUMPRODUCT(Stories!$T$4:$T$63,--(Stories!$J$4:$J$63=$A22))</f>
-        <v/>
-      </c>
-      <c r="D22" s="236" t="n">
+      <c r="C22" s="242">
+        <f>SUMPRODUCT(Stories!$W$4:$W$63,--(Stories!$J$4:$J$63=$A22))</f>
+        <v/>
+      </c>
+      <c r="D22" s="243" t="n">
         <v>4</v>
       </c>
-      <c r="E22" s="234" t="n">
+      <c r="E22" s="241" t="n">
         <v>1</v>
       </c>
-      <c r="F22" s="240" t="inlineStr">
+      <c r="F22" s="247" t="inlineStr">
         <is>
           <t>Infrastructure &amp; the Underground City</t>
         </is>
       </c>
-      <c r="G22" s="234" t="n">
+      <c r="G22" s="241" t="n">
         <v>1</v>
       </c>
       <c r="H22" s="171" t="inlineStr">
@@ -16826,7 +17546,7 @@
           <t>Colombia</t>
         </is>
       </c>
-      <c r="I22" s="238" t="n">
+      <c r="I22" s="245" t="n">
         <v>46319</v>
       </c>
     </row>
@@ -16836,25 +17556,25 @@
           <t>Geoengineer.org</t>
         </is>
       </c>
-      <c r="B23" s="234" t="n">
+      <c r="B23" s="241" t="n">
         <v>1</v>
       </c>
-      <c r="C23" s="235">
-        <f>SUMPRODUCT(Stories!$T$4:$T$63,--(Stories!$J$4:$J$63=$A23))</f>
-        <v/>
-      </c>
-      <c r="D23" s="236" t="n">
+      <c r="C23" s="242">
+        <f>SUMPRODUCT(Stories!$W$4:$W$63,--(Stories!$J$4:$J$63=$A23))</f>
+        <v/>
+      </c>
+      <c r="D23" s="243" t="n">
         <v>5</v>
       </c>
-      <c r="E23" s="234" t="n">
+      <c r="E23" s="241" t="n">
         <v>1</v>
       </c>
-      <c r="F23" s="244" t="inlineStr">
+      <c r="F23" s="251" t="inlineStr">
         <is>
           <t>Ground Improvement &amp; Innovation</t>
         </is>
       </c>
-      <c r="G23" s="234" t="n">
+      <c r="G23" s="241" t="n">
         <v>1</v>
       </c>
       <c r="H23" s="171" t="inlineStr">
@@ -16862,7 +17582,7 @@
           <t>United States</t>
         </is>
       </c>
-      <c r="I23" s="238" t="n">
+      <c r="I23" s="245" t="n">
         <v>46319</v>
       </c>
     </row>
@@ -16872,25 +17592,25 @@
           <t>Il Giornale dei Castelli Romani</t>
         </is>
       </c>
-      <c r="B24" s="234" t="n">
+      <c r="B24" s="241" t="n">
         <v>1</v>
       </c>
-      <c r="C24" s="235">
-        <f>SUMPRODUCT(Stories!$T$4:$T$63,--(Stories!$J$4:$J$63=$A24))</f>
-        <v/>
-      </c>
-      <c r="D24" s="236" t="n">
+      <c r="C24" s="242">
+        <f>SUMPRODUCT(Stories!$W$4:$W$63,--(Stories!$J$4:$J$63=$A24))</f>
+        <v/>
+      </c>
+      <c r="D24" s="243" t="n">
         <v>4</v>
       </c>
-      <c r="E24" s="234" t="n">
+      <c r="E24" s="241" t="n">
         <v>1</v>
       </c>
-      <c r="F24" s="237" t="inlineStr">
+      <c r="F24" s="244" t="inlineStr">
         <is>
           <t>Hazards &amp; Resilience</t>
         </is>
       </c>
-      <c r="G24" s="234" t="n">
+      <c r="G24" s="241" t="n">
         <v>1</v>
       </c>
       <c r="H24" s="171" t="inlineStr">
@@ -16898,7 +17618,7 @@
           <t>Italy</t>
         </is>
       </c>
-      <c r="I24" s="238" t="n">
+      <c r="I24" s="245" t="n">
         <v>46319</v>
       </c>
     </row>
@@ -16908,25 +17628,25 @@
           <t>Kenh14.vn</t>
         </is>
       </c>
-      <c r="B25" s="234" t="n">
+      <c r="B25" s="241" t="n">
         <v>1</v>
       </c>
-      <c r="C25" s="235">
-        <f>SUMPRODUCT(Stories!$T$4:$T$63,--(Stories!$J$4:$J$63=$A25))</f>
-        <v/>
-      </c>
-      <c r="D25" s="236" t="n">
+      <c r="C25" s="242">
+        <f>SUMPRODUCT(Stories!$W$4:$W$63,--(Stories!$J$4:$J$63=$A25))</f>
+        <v/>
+      </c>
+      <c r="D25" s="243" t="n">
         <v>4</v>
       </c>
-      <c r="E25" s="234" t="n">
+      <c r="E25" s="241" t="n">
         <v>1</v>
       </c>
-      <c r="F25" s="237" t="inlineStr">
+      <c r="F25" s="244" t="inlineStr">
         <is>
           <t>Hazards &amp; Resilience</t>
         </is>
       </c>
-      <c r="G25" s="234" t="n">
+      <c r="G25" s="241" t="n">
         <v>1</v>
       </c>
       <c r="H25" s="171" t="inlineStr">
@@ -16934,7 +17654,7 @@
           <t>Vietnam</t>
         </is>
       </c>
-      <c r="I25" s="238" t="n">
+      <c r="I25" s="245" t="n">
         <v>46319</v>
       </c>
     </row>
@@ -16944,25 +17664,25 @@
           <t>Meganoticias</t>
         </is>
       </c>
-      <c r="B26" s="234" t="n">
+      <c r="B26" s="241" t="n">
         <v>1</v>
       </c>
-      <c r="C26" s="235">
-        <f>SUMPRODUCT(Stories!$T$4:$T$63,--(Stories!$J$4:$J$63=$A26))</f>
-        <v/>
-      </c>
-      <c r="D26" s="236" t="n">
+      <c r="C26" s="242">
+        <f>SUMPRODUCT(Stories!$W$4:$W$63,--(Stories!$J$4:$J$63=$A26))</f>
+        <v/>
+      </c>
+      <c r="D26" s="243" t="n">
         <v>4</v>
       </c>
-      <c r="E26" s="234" t="n">
+      <c r="E26" s="241" t="n">
         <v>1</v>
       </c>
-      <c r="F26" s="237" t="inlineStr">
+      <c r="F26" s="244" t="inlineStr">
         <is>
           <t>Hazards &amp; Resilience</t>
         </is>
       </c>
-      <c r="G26" s="234" t="n">
+      <c r="G26" s="241" t="n">
         <v>1</v>
       </c>
       <c r="H26" s="171" t="inlineStr">
@@ -16970,7 +17690,7 @@
           <t>Chile</t>
         </is>
       </c>
-      <c r="I26" s="238" t="n">
+      <c r="I26" s="245" t="n">
         <v>46319</v>
       </c>
     </row>
@@ -16980,25 +17700,25 @@
           <t>Naver Blog</t>
         </is>
       </c>
-      <c r="B27" s="234" t="n">
+      <c r="B27" s="241" t="n">
         <v>1</v>
       </c>
-      <c r="C27" s="235">
-        <f>SUMPRODUCT(Stories!$T$4:$T$63,--(Stories!$J$4:$J$63=$A27))</f>
-        <v/>
-      </c>
-      <c r="D27" s="236" t="n">
+      <c r="C27" s="242">
+        <f>SUMPRODUCT(Stories!$W$4:$W$63,--(Stories!$J$4:$J$63=$A27))</f>
+        <v/>
+      </c>
+      <c r="D27" s="243" t="n">
         <v>4</v>
       </c>
-      <c r="E27" s="234" t="n">
+      <c r="E27" s="241" t="n">
         <v>1</v>
       </c>
-      <c r="F27" s="240" t="inlineStr">
+      <c r="F27" s="247" t="inlineStr">
         <is>
           <t>Infrastructure &amp; the Underground City</t>
         </is>
       </c>
-      <c r="G27" s="234" t="n">
+      <c r="G27" s="241" t="n">
         <v>1</v>
       </c>
       <c r="H27" s="171" t="inlineStr">
@@ -17006,7 +17726,7 @@
           <t>South Korea</t>
         </is>
       </c>
-      <c r="I27" s="238" t="n">
+      <c r="I27" s="245" t="n">
         <v>46319</v>
       </c>
     </row>
@@ -17016,25 +17736,25 @@
           <t>Người Đưa Tin</t>
         </is>
       </c>
-      <c r="B28" s="234" t="n">
+      <c r="B28" s="241" t="n">
         <v>1</v>
       </c>
-      <c r="C28" s="235">
-        <f>SUMPRODUCT(Stories!$T$4:$T$63,--(Stories!$J$4:$J$63=$A28))</f>
-        <v/>
-      </c>
-      <c r="D28" s="236" t="n">
+      <c r="C28" s="242">
+        <f>SUMPRODUCT(Stories!$W$4:$W$63,--(Stories!$J$4:$J$63=$A28))</f>
+        <v/>
+      </c>
+      <c r="D28" s="243" t="n">
         <v>4</v>
       </c>
-      <c r="E28" s="234" t="n">
+      <c r="E28" s="241" t="n">
         <v>1</v>
       </c>
-      <c r="F28" s="239" t="inlineStr">
+      <c r="F28" s="246" t="inlineStr">
         <is>
           <t>Offshore, Coasts &amp; Water</t>
         </is>
       </c>
-      <c r="G28" s="234" t="n">
+      <c r="G28" s="241" t="n">
         <v>1</v>
       </c>
       <c r="H28" s="171" t="inlineStr">
@@ -17042,7 +17762,7 @@
           <t>Vietnam</t>
         </is>
       </c>
-      <c r="I28" s="238" t="n">
+      <c r="I28" s="245" t="n">
         <v>46319</v>
       </c>
     </row>
@@ -17052,25 +17772,25 @@
           <t>Realidad Sanmartinense</t>
         </is>
       </c>
-      <c r="B29" s="234" t="n">
+      <c r="B29" s="241" t="n">
         <v>1</v>
       </c>
-      <c r="C29" s="235">
-        <f>SUMPRODUCT(Stories!$T$4:$T$63,--(Stories!$J$4:$J$63=$A29))</f>
-        <v/>
-      </c>
-      <c r="D29" s="236" t="n">
+      <c r="C29" s="242">
+        <f>SUMPRODUCT(Stories!$W$4:$W$63,--(Stories!$J$4:$J$63=$A29))</f>
+        <v/>
+      </c>
+      <c r="D29" s="243" t="n">
         <v>3</v>
       </c>
-      <c r="E29" s="234" t="n">
+      <c r="E29" s="241" t="n">
         <v>0</v>
       </c>
-      <c r="F29" s="240" t="inlineStr">
+      <c r="F29" s="247" t="inlineStr">
         <is>
           <t>Infrastructure &amp; the Underground City</t>
         </is>
       </c>
-      <c r="G29" s="234" t="n">
+      <c r="G29" s="241" t="n">
         <v>1</v>
       </c>
       <c r="H29" s="171" t="inlineStr">
@@ -17078,7 +17798,7 @@
           <t>Colombia</t>
         </is>
       </c>
-      <c r="I29" s="238" t="n">
+      <c r="I29" s="245" t="n">
         <v>46319</v>
       </c>
     </row>
@@ -17088,25 +17808,25 @@
           <t>RRI.co.id</t>
         </is>
       </c>
-      <c r="B30" s="234" t="n">
+      <c r="B30" s="241" t="n">
         <v>1</v>
       </c>
-      <c r="C30" s="235">
-        <f>SUMPRODUCT(Stories!$T$4:$T$63,--(Stories!$J$4:$J$63=$A30))</f>
-        <v/>
-      </c>
-      <c r="D30" s="236" t="n">
+      <c r="C30" s="242">
+        <f>SUMPRODUCT(Stories!$W$4:$W$63,--(Stories!$J$4:$J$63=$A30))</f>
+        <v/>
+      </c>
+      <c r="D30" s="243" t="n">
         <v>4</v>
       </c>
-      <c r="E30" s="234" t="n">
+      <c r="E30" s="241" t="n">
         <v>1</v>
       </c>
-      <c r="F30" s="237" t="inlineStr">
+      <c r="F30" s="244" t="inlineStr">
         <is>
           <t>Hazards &amp; Resilience</t>
         </is>
       </c>
-      <c r="G30" s="234" t="n">
+      <c r="G30" s="241" t="n">
         <v>1</v>
       </c>
       <c r="H30" s="171" t="inlineStr">
@@ -17114,7 +17834,7 @@
           <t>Indonesia</t>
         </is>
       </c>
-      <c r="I30" s="238" t="n">
+      <c r="I30" s="245" t="n">
         <v>46319</v>
       </c>
     </row>
@@ -17124,25 +17844,25 @@
           <t>Sciencepost</t>
         </is>
       </c>
-      <c r="B31" s="234" t="n">
+      <c r="B31" s="241" t="n">
         <v>1</v>
       </c>
-      <c r="C31" s="235">
-        <f>SUMPRODUCT(Stories!$T$4:$T$63,--(Stories!$J$4:$J$63=$A31))</f>
-        <v/>
-      </c>
-      <c r="D31" s="236" t="n">
+      <c r="C31" s="242">
+        <f>SUMPRODUCT(Stories!$W$4:$W$63,--(Stories!$J$4:$J$63=$A31))</f>
+        <v/>
+      </c>
+      <c r="D31" s="243" t="n">
         <v>5</v>
       </c>
-      <c r="E31" s="234" t="n">
+      <c r="E31" s="241" t="n">
         <v>1</v>
       </c>
-      <c r="F31" s="244" t="inlineStr">
+      <c r="F31" s="251" t="inlineStr">
         <is>
           <t>Ground Improvement &amp; Innovation</t>
         </is>
       </c>
-      <c r="G31" s="234" t="n">
+      <c r="G31" s="241" t="n">
         <v>1</v>
       </c>
       <c r="H31" s="171" t="inlineStr">
@@ -17150,7 +17870,7 @@
           <t>Senegal</t>
         </is>
       </c>
-      <c r="I31" s="238" t="n">
+      <c r="I31" s="245" t="n">
         <v>46319</v>
       </c>
     </row>
@@ -17160,25 +17880,25 @@
           <t>Tabasco HOY</t>
         </is>
       </c>
-      <c r="B32" s="234" t="n">
+      <c r="B32" s="241" t="n">
         <v>1</v>
       </c>
-      <c r="C32" s="235">
-        <f>SUMPRODUCT(Stories!$T$4:$T$63,--(Stories!$J$4:$J$63=$A32))</f>
-        <v/>
-      </c>
-      <c r="D32" s="236" t="n">
+      <c r="C32" s="242">
+        <f>SUMPRODUCT(Stories!$W$4:$W$63,--(Stories!$J$4:$J$63=$A32))</f>
+        <v/>
+      </c>
+      <c r="D32" s="243" t="n">
         <v>3</v>
       </c>
-      <c r="E32" s="234" t="n">
+      <c r="E32" s="241" t="n">
         <v>0</v>
       </c>
-      <c r="F32" s="240" t="inlineStr">
+      <c r="F32" s="247" t="inlineStr">
         <is>
           <t>Infrastructure &amp; the Underground City</t>
         </is>
       </c>
-      <c r="G32" s="234" t="n">
+      <c r="G32" s="241" t="n">
         <v>1</v>
       </c>
       <c r="H32" s="171" t="inlineStr">
@@ -17186,7 +17906,7 @@
           <t>Colombia</t>
         </is>
       </c>
-      <c r="I32" s="238" t="n">
+      <c r="I32" s="245" t="n">
         <v>46319</v>
       </c>
     </row>
@@ -17196,25 +17916,25 @@
           <t>Trade-news.cl</t>
         </is>
       </c>
-      <c r="B33" s="234" t="n">
+      <c r="B33" s="241" t="n">
         <v>1</v>
       </c>
-      <c r="C33" s="235">
-        <f>SUMPRODUCT(Stories!$T$4:$T$63,--(Stories!$J$4:$J$63=$A33))</f>
-        <v/>
-      </c>
-      <c r="D33" s="236" t="n">
+      <c r="C33" s="242">
+        <f>SUMPRODUCT(Stories!$W$4:$W$63,--(Stories!$J$4:$J$63=$A33))</f>
+        <v/>
+      </c>
+      <c r="D33" s="243" t="n">
         <v>3</v>
       </c>
-      <c r="E33" s="234" t="n">
+      <c r="E33" s="241" t="n">
         <v>0</v>
       </c>
-      <c r="F33" s="245" t="inlineStr">
+      <c r="F33" s="252" t="inlineStr">
         <is>
           <t>Characterisation &amp; Modelling</t>
         </is>
       </c>
-      <c r="G33" s="234" t="n">
+      <c r="G33" s="241" t="n">
         <v>1</v>
       </c>
       <c r="H33" s="171" t="inlineStr">
@@ -17222,7 +17942,7 @@
           <t>Peru</t>
         </is>
       </c>
-      <c r="I33" s="238" t="n">
+      <c r="I33" s="245" t="n">
         <v>46319</v>
       </c>
     </row>
@@ -17232,25 +17952,25 @@
           <t>Tv7 Benevento</t>
         </is>
       </c>
-      <c r="B34" s="234" t="n">
+      <c r="B34" s="241" t="n">
         <v>1</v>
       </c>
-      <c r="C34" s="235">
-        <f>SUMPRODUCT(Stories!$T$4:$T$63,--(Stories!$J$4:$J$63=$A34))</f>
-        <v/>
-      </c>
-      <c r="D34" s="236" t="n">
+      <c r="C34" s="242">
+        <f>SUMPRODUCT(Stories!$W$4:$W$63,--(Stories!$J$4:$J$63=$A34))</f>
+        <v/>
+      </c>
+      <c r="D34" s="243" t="n">
         <v>4</v>
       </c>
-      <c r="E34" s="234" t="n">
+      <c r="E34" s="241" t="n">
         <v>1</v>
       </c>
-      <c r="F34" s="237" t="inlineStr">
+      <c r="F34" s="244" t="inlineStr">
         <is>
           <t>Hazards &amp; Resilience</t>
         </is>
       </c>
-      <c r="G34" s="234" t="n">
+      <c r="G34" s="241" t="n">
         <v>1</v>
       </c>
       <c r="H34" s="171" t="inlineStr">
@@ -17258,7 +17978,7 @@
           <t>Italy</t>
         </is>
       </c>
-      <c r="I34" s="238" t="n">
+      <c r="I34" s="245" t="n">
         <v>46319</v>
       </c>
     </row>
@@ -17268,25 +17988,25 @@
           <t>VnExpress International</t>
         </is>
       </c>
-      <c r="B35" s="234" t="n">
+      <c r="B35" s="241" t="n">
         <v>1</v>
       </c>
-      <c r="C35" s="235">
-        <f>SUMPRODUCT(Stories!$T$4:$T$63,--(Stories!$J$4:$J$63=$A35))</f>
-        <v/>
-      </c>
-      <c r="D35" s="236" t="n">
+      <c r="C35" s="242">
+        <f>SUMPRODUCT(Stories!$W$4:$W$63,--(Stories!$J$4:$J$63=$A35))</f>
+        <v/>
+      </c>
+      <c r="D35" s="243" t="n">
         <v>4</v>
       </c>
-      <c r="E35" s="234" t="n">
+      <c r="E35" s="241" t="n">
         <v>1</v>
       </c>
-      <c r="F35" s="245" t="inlineStr">
+      <c r="F35" s="252" t="inlineStr">
         <is>
           <t>Characterisation &amp; Modelling</t>
         </is>
       </c>
-      <c r="G35" s="234" t="n">
+      <c r="G35" s="241" t="n">
         <v>1</v>
       </c>
       <c r="H35" s="171" t="inlineStr">
@@ -17294,7 +18014,7 @@
           <t>United Kingdom</t>
         </is>
       </c>
-      <c r="I35" s="238" t="n">
+      <c r="I35" s="245" t="n">
         <v>46319</v>
       </c>
     </row>
@@ -17304,25 +18024,25 @@
           <t>VOH</t>
         </is>
       </c>
-      <c r="B36" s="234" t="n">
+      <c r="B36" s="241" t="n">
         <v>1</v>
       </c>
-      <c r="C36" s="235">
-        <f>SUMPRODUCT(Stories!$T$4:$T$63,--(Stories!$J$4:$J$63=$A36))</f>
-        <v/>
-      </c>
-      <c r="D36" s="236" t="n">
+      <c r="C36" s="242">
+        <f>SUMPRODUCT(Stories!$W$4:$W$63,--(Stories!$J$4:$J$63=$A36))</f>
+        <v/>
+      </c>
+      <c r="D36" s="243" t="n">
         <v>4</v>
       </c>
-      <c r="E36" s="234" t="n">
+      <c r="E36" s="241" t="n">
         <v>1</v>
       </c>
-      <c r="F36" s="240" t="inlineStr">
+      <c r="F36" s="247" t="inlineStr">
         <is>
           <t>Infrastructure &amp; the Underground City</t>
         </is>
       </c>
-      <c r="G36" s="234" t="n">
+      <c r="G36" s="241" t="n">
         <v>1</v>
       </c>
       <c r="H36" s="171" t="inlineStr">
@@ -17330,7 +18050,7 @@
           <t>Vietnam</t>
         </is>
       </c>
-      <c r="I36" s="238" t="n">
+      <c r="I36" s="245" t="n">
         <v>46319</v>
       </c>
     </row>
@@ -17340,25 +18060,25 @@
           <t>VTV.vn</t>
         </is>
       </c>
-      <c r="B37" s="234" t="n">
+      <c r="B37" s="241" t="n">
         <v>1</v>
       </c>
-      <c r="C37" s="235">
-        <f>SUMPRODUCT(Stories!$T$4:$T$63,--(Stories!$J$4:$J$63=$A37))</f>
-        <v/>
-      </c>
-      <c r="D37" s="236" t="n">
+      <c r="C37" s="242">
+        <f>SUMPRODUCT(Stories!$W$4:$W$63,--(Stories!$J$4:$J$63=$A37))</f>
+        <v/>
+      </c>
+      <c r="D37" s="243" t="n">
         <v>4</v>
       </c>
-      <c r="E37" s="234" t="n">
+      <c r="E37" s="241" t="n">
         <v>1</v>
       </c>
-      <c r="F37" s="239" t="inlineStr">
+      <c r="F37" s="246" t="inlineStr">
         <is>
           <t>Offshore, Coasts &amp; Water</t>
         </is>
       </c>
-      <c r="G37" s="234" t="n">
+      <c r="G37" s="241" t="n">
         <v>1</v>
       </c>
       <c r="H37" s="171" t="inlineStr">
@@ -17366,7 +18086,7 @@
           <t>Vietnam</t>
         </is>
       </c>
-      <c r="I37" s="238" t="n">
+      <c r="I37" s="245" t="n">
         <v>46319</v>
       </c>
     </row>
@@ -17376,25 +18096,25 @@
           <t>www.noroeste.com.mx</t>
         </is>
       </c>
-      <c r="B38" s="234" t="n">
+      <c r="B38" s="241" t="n">
         <v>1</v>
       </c>
-      <c r="C38" s="235">
-        <f>SUMPRODUCT(Stories!$T$4:$T$63,--(Stories!$J$4:$J$63=$A38))</f>
-        <v/>
-      </c>
-      <c r="D38" s="236" t="n">
+      <c r="C38" s="242">
+        <f>SUMPRODUCT(Stories!$W$4:$W$63,--(Stories!$J$4:$J$63=$A38))</f>
+        <v/>
+      </c>
+      <c r="D38" s="243" t="n">
         <v>4</v>
       </c>
-      <c r="E38" s="234" t="n">
+      <c r="E38" s="241" t="n">
         <v>1</v>
       </c>
-      <c r="F38" s="243" t="inlineStr">
+      <c r="F38" s="250" t="inlineStr">
         <is>
           <t>Geotechnics &amp; Society</t>
         </is>
       </c>
-      <c r="G38" s="234" t="n">
+      <c r="G38" s="241" t="n">
         <v>1</v>
       </c>
       <c r="H38" s="171" t="inlineStr">
@@ -17402,7 +18122,7 @@
           <t>Colombia</t>
         </is>
       </c>
-      <c r="I38" s="238" t="n">
+      <c r="I38" s="245" t="n">
         <v>46319</v>
       </c>
     </row>
@@ -17412,25 +18132,25 @@
           <t>Zazoom Social News</t>
         </is>
       </c>
-      <c r="B39" s="234" t="n">
+      <c r="B39" s="241" t="n">
         <v>1</v>
       </c>
-      <c r="C39" s="235">
-        <f>SUMPRODUCT(Stories!$T$4:$T$63,--(Stories!$J$4:$J$63=$A39))</f>
-        <v/>
-      </c>
-      <c r="D39" s="236" t="n">
+      <c r="C39" s="242">
+        <f>SUMPRODUCT(Stories!$W$4:$W$63,--(Stories!$J$4:$J$63=$A39))</f>
+        <v/>
+      </c>
+      <c r="D39" s="243" t="n">
         <v>4</v>
       </c>
-      <c r="E39" s="234" t="n">
+      <c r="E39" s="241" t="n">
         <v>1</v>
       </c>
-      <c r="F39" s="237" t="inlineStr">
+      <c r="F39" s="244" t="inlineStr">
         <is>
           <t>Hazards &amp; Resilience</t>
         </is>
       </c>
-      <c r="G39" s="234" t="n">
+      <c r="G39" s="241" t="n">
         <v>1</v>
       </c>
       <c r="H39" s="171" t="inlineStr">
@@ -17438,7 +18158,7 @@
           <t>Italy</t>
         </is>
       </c>
-      <c r="I39" s="238" t="n">
+      <c r="I39" s="245" t="n">
         <v>46319</v>
       </c>
     </row>
@@ -17448,25 +18168,25 @@
           <t>Крыминформ</t>
         </is>
       </c>
-      <c r="B40" s="234" t="n">
+      <c r="B40" s="241" t="n">
         <v>1</v>
       </c>
-      <c r="C40" s="235">
-        <f>SUMPRODUCT(Stories!$T$4:$T$63,--(Stories!$J$4:$J$63=$A40))</f>
-        <v/>
-      </c>
-      <c r="D40" s="236" t="n">
+      <c r="C40" s="242">
+        <f>SUMPRODUCT(Stories!$W$4:$W$63,--(Stories!$J$4:$J$63=$A40))</f>
+        <v/>
+      </c>
+      <c r="D40" s="243" t="n">
         <v>4</v>
       </c>
-      <c r="E40" s="234" t="n">
+      <c r="E40" s="241" t="n">
         <v>1</v>
       </c>
-      <c r="F40" s="240" t="inlineStr">
+      <c r="F40" s="247" t="inlineStr">
         <is>
           <t>Infrastructure &amp; the Underground City</t>
         </is>
       </c>
-      <c r="G40" s="234" t="n">
+      <c r="G40" s="241" t="n">
         <v>1</v>
       </c>
       <c r="H40" s="171" t="inlineStr">
@@ -17474,7 +18194,7 @@
           <t>Russia</t>
         </is>
       </c>
-      <c r="I40" s="238" t="n">
+      <c r="I40" s="245" t="n">
         <v>46319</v>
       </c>
     </row>
@@ -17484,25 +18204,25 @@
           <t>Самарская газета</t>
         </is>
       </c>
-      <c r="B41" s="234" t="n">
+      <c r="B41" s="241" t="n">
         <v>1</v>
       </c>
-      <c r="C41" s="235">
-        <f>SUMPRODUCT(Stories!$T$4:$T$63,--(Stories!$J$4:$J$63=$A41))</f>
-        <v/>
-      </c>
-      <c r="D41" s="236" t="n">
+      <c r="C41" s="242">
+        <f>SUMPRODUCT(Stories!$W$4:$W$63,--(Stories!$J$4:$J$63=$A41))</f>
+        <v/>
+      </c>
+      <c r="D41" s="243" t="n">
         <v>3</v>
       </c>
-      <c r="E41" s="234" t="n">
+      <c r="E41" s="241" t="n">
         <v>0</v>
       </c>
-      <c r="F41" s="240" t="inlineStr">
+      <c r="F41" s="247" t="inlineStr">
         <is>
           <t>Infrastructure &amp; the Underground City</t>
         </is>
       </c>
-      <c r="G41" s="234" t="n">
+      <c r="G41" s="241" t="n">
         <v>1</v>
       </c>
       <c r="H41" s="171" t="inlineStr">
@@ -17510,7 +18230,7 @@
           <t>Russia</t>
         </is>
       </c>
-      <c r="I41" s="238" t="n">
+      <c r="I41" s="245" t="n">
         <v>46319</v>
       </c>
     </row>
@@ -17520,25 +18240,25 @@
           <t>아시아경제</t>
         </is>
       </c>
-      <c r="B42" s="234" t="n">
+      <c r="B42" s="241" t="n">
         <v>1</v>
       </c>
-      <c r="C42" s="235">
-        <f>SUMPRODUCT(Stories!$T$4:$T$63,--(Stories!$J$4:$J$63=$A42))</f>
-        <v/>
-      </c>
-      <c r="D42" s="236" t="n">
+      <c r="C42" s="242">
+        <f>SUMPRODUCT(Stories!$W$4:$W$63,--(Stories!$J$4:$J$63=$A42))</f>
+        <v/>
+      </c>
+      <c r="D42" s="243" t="n">
         <v>4</v>
       </c>
-      <c r="E42" s="234" t="n">
+      <c r="E42" s="241" t="n">
         <v>1</v>
       </c>
-      <c r="F42" s="240" t="inlineStr">
+      <c r="F42" s="247" t="inlineStr">
         <is>
           <t>Infrastructure &amp; the Underground City</t>
         </is>
       </c>
-      <c r="G42" s="234" t="n">
+      <c r="G42" s="241" t="n">
         <v>1</v>
       </c>
       <c r="H42" s="171" t="inlineStr">
@@ -17546,7 +18266,7 @@
           <t>United Kingdom</t>
         </is>
       </c>
-      <c r="I42" s="238" t="n">
+      <c r="I42" s="245" t="n">
         <v>46319</v>
       </c>
     </row>
@@ -17556,25 +18276,25 @@
           <t>아주경제</t>
         </is>
       </c>
-      <c r="B43" s="234" t="n">
+      <c r="B43" s="241" t="n">
         <v>1</v>
       </c>
-      <c r="C43" s="235">
-        <f>SUMPRODUCT(Stories!$T$4:$T$63,--(Stories!$J$4:$J$63=$A43))</f>
-        <v/>
-      </c>
-      <c r="D43" s="236" t="n">
+      <c r="C43" s="242">
+        <f>SUMPRODUCT(Stories!$W$4:$W$63,--(Stories!$J$4:$J$63=$A43))</f>
+        <v/>
+      </c>
+      <c r="D43" s="243" t="n">
         <v>4</v>
       </c>
-      <c r="E43" s="234" t="n">
+      <c r="E43" s="241" t="n">
         <v>1</v>
       </c>
-      <c r="F43" s="240" t="inlineStr">
+      <c r="F43" s="247" t="inlineStr">
         <is>
           <t>Infrastructure &amp; the Underground City</t>
         </is>
       </c>
-      <c r="G43" s="234" t="n">
+      <c r="G43" s="241" t="n">
         <v>1</v>
       </c>
       <c r="H43" s="171" t="inlineStr">
@@ -17582,7 +18302,7 @@
           <t>South Korea</t>
         </is>
       </c>
-      <c r="I43" s="238" t="n">
+      <c r="I43" s="245" t="n">
         <v>46319</v>
       </c>
     </row>
@@ -17592,25 +18312,25 @@
           <t>충청신문</t>
         </is>
       </c>
-      <c r="B44" s="234" t="n">
+      <c r="B44" s="241" t="n">
         <v>1</v>
       </c>
-      <c r="C44" s="235">
-        <f>SUMPRODUCT(Stories!$T$4:$T$63,--(Stories!$J$4:$J$63=$A44))</f>
-        <v/>
-      </c>
-      <c r="D44" s="236" t="n">
+      <c r="C44" s="242">
+        <f>SUMPRODUCT(Stories!$W$4:$W$63,--(Stories!$J$4:$J$63=$A44))</f>
+        <v/>
+      </c>
+      <c r="D44" s="243" t="n">
         <v>5</v>
       </c>
-      <c r="E44" s="234" t="n">
+      <c r="E44" s="241" t="n">
         <v>1</v>
       </c>
-      <c r="F44" s="240" t="inlineStr">
+      <c r="F44" s="247" t="inlineStr">
         <is>
           <t>Infrastructure &amp; the Underground City</t>
         </is>
       </c>
-      <c r="G44" s="234" t="n">
+      <c r="G44" s="241" t="n">
         <v>1</v>
       </c>
       <c r="H44" s="171" t="inlineStr">
@@ -17618,7 +18338,7 @@
           <t>South Korea</t>
         </is>
       </c>
-      <c r="I44" s="238" t="n">
+      <c r="I44" s="245" t="n">
         <v>46319</v>
       </c>
     </row>
@@ -17653,7 +18373,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="00B8C0CA"/>
@@ -17675,462 +18395,462 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="246" t="inlineStr">
+      <c r="A1" s="253" t="inlineStr">
         <is>
           <t>Theme selector</t>
         </is>
       </c>
-      <c r="B1" s="246" t="inlineStr">
+      <c r="B1" s="253" t="inlineStr">
         <is>
           <t>Use selector</t>
         </is>
       </c>
-      <c r="C1" s="246" t="inlineStr">
+      <c r="C1" s="253" t="inlineStr">
         <is>
           <t>Relevance selector</t>
         </is>
       </c>
-      <c r="D1" s="246" t="inlineStr">
+      <c r="D1" s="253" t="inlineStr">
         <is>
           <t>Window selector</t>
         </is>
       </c>
-      <c r="E1" s="246" t="inlineStr">
+      <c r="E1" s="253" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="G1" s="246" t="inlineStr">
+      <c r="G1" s="253" t="inlineStr">
         <is>
           <t>Setting</t>
         </is>
       </c>
-      <c r="H1" s="246" t="inlineStr">
+      <c r="H1" s="253" t="inlineStr">
         <is>
           <t>Value</t>
         </is>
       </c>
-      <c r="J1" s="246" t="inlineStr">
+      <c r="J1" s="253" t="inlineStr">
         <is>
           <t>Digest date</t>
         </is>
       </c>
-      <c r="K1" s="246" t="inlineStr">
+      <c r="K1" s="253" t="inlineStr">
         <is>
           <t>Stories in the selection</t>
         </is>
       </c>
-      <c r="M1" s="246" t="inlineStr">
+      <c r="M1" s="253" t="inlineStr">
         <is>
           <t>Rank</t>
         </is>
       </c>
-      <c r="N1" s="246" t="inlineStr">
+      <c r="N1" s="253" t="inlineStr">
         <is>
           <t>Key</t>
         </is>
       </c>
-      <c r="O1" s="246" t="inlineStr">
+      <c r="O1" s="253" t="inlineStr">
         <is>
           <t>Row in Stories</t>
         </is>
       </c>
-      <c r="P1" s="246" t="inlineStr">
+      <c r="P1" s="253" t="inlineStr">
         <is>
           <t>Article URL</t>
         </is>
       </c>
-      <c r="Q1" s="246" t="inlineStr">
+      <c r="Q1" s="253" t="inlineStr">
         <is>
           <t>Headline shown</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="247" t="inlineStr">
+      <c r="A2" s="254" t="inlineStr">
         <is>
           <t>All themes</t>
         </is>
       </c>
-      <c r="B2" s="247" t="inlineStr">
+      <c r="B2" s="254" t="inlineStr">
         <is>
           <t>All uses</t>
         </is>
       </c>
-      <c r="C2" s="247" t="inlineStr">
+      <c r="C2" s="254" t="inlineStr">
         <is>
           <t>Any</t>
         </is>
       </c>
-      <c r="D2" s="247" t="inlineStr">
+      <c r="D2" s="254" t="inlineStr">
         <is>
           <t>All windows</t>
         </is>
       </c>
-      <c r="E2" s="247" t="inlineStr">
+      <c r="E2" s="254" t="inlineStr">
         <is>
           <t>To review</t>
         </is>
       </c>
-      <c r="G2" s="247" t="inlineStr">
+      <c r="G2" s="254" t="inlineStr">
         <is>
           <t>Minimum relevance (number)</t>
         </is>
       </c>
-      <c r="H2" s="247">
+      <c r="H2" s="254">
         <f>IF(ISNUMBER(Dashboard!$K$5),Dashboard!$K$5,IFERROR(VALUE(Dashboard!$K$5),0))</f>
         <v/>
       </c>
-      <c r="J2" s="248" t="n">
-        <v>46319</v>
-      </c>
-      <c r="K2" s="247">
-        <f>COUNTIFS(Stories!$T$4:$T$63,1,Stories!$K$4:$K$63,J2)</f>
-        <v/>
-      </c>
-      <c r="M2" s="247" t="n">
+      <c r="J2" s="255" t="n">
+        <v>46319</v>
+      </c>
+      <c r="K2" s="254">
+        <f>COUNTIFS(Stories!$W$4:$W$63,1,Stories!$K$4:$K$63,J2)</f>
+        <v/>
+      </c>
+      <c r="M2" s="254" t="n">
         <v>1</v>
       </c>
-      <c r="N2" s="249">
-        <f>IFERROR(LARGE(Stories!$U$4:$U$63,M2),"")</f>
-        <v/>
-      </c>
-      <c r="O2" s="247">
-        <f>IF(N2="","",MATCH(N2,Stories!$U$4:$U$63,0))</f>
-        <v/>
-      </c>
-      <c r="P2" s="247">
-        <f>IF(O2="","",INDEX(Stories!$S$4:$S$63,O2)&amp;"")</f>
-        <v/>
-      </c>
-      <c r="Q2" s="247">
+      <c r="N2" s="256">
+        <f>IFERROR(LARGE(Stories!$X$4:$X$63,M2),"")</f>
+        <v/>
+      </c>
+      <c r="O2" s="254">
+        <f>IF(N2="","",MATCH(N2,Stories!$X$4:$X$63,0))</f>
+        <v/>
+      </c>
+      <c r="P2" s="254">
+        <f>IF(O2="","",INDEX(Stories!$V$4:$V$63,O2)&amp;"")</f>
+        <v/>
+      </c>
+      <c r="Q2" s="254">
         <f>IF(O2="","",IF(LEN(INDEX(Stories!$B$4:$B$63,O2))&gt;120,LEFT(INDEX(Stories!$B$4:$B$63,O2),118)&amp;"…",INDEX(Stories!$B$4:$B$63,O2)&amp;""))</f>
         <v/>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="247" t="inlineStr">
+      <c r="A3" s="254" t="inlineStr">
         <is>
           <t>Sustainability &amp; the Energy Transition</t>
         </is>
       </c>
-      <c r="B3" s="247" t="inlineStr">
+      <c r="B3" s="254" t="inlineStr">
         <is>
           <t>Feature lead</t>
         </is>
       </c>
-      <c r="C3" s="247" t="n">
+      <c r="C3" s="254" t="n">
         <v>3</v>
       </c>
-      <c r="D3" s="247" t="inlineStr">
+      <c r="D3" s="254" t="inlineStr">
         <is>
           <t>2026-Q4</t>
         </is>
       </c>
-      <c r="E3" s="247" t="inlineStr">
+      <c r="E3" s="254" t="inlineStr">
         <is>
           <t>Shortlisted</t>
         </is>
       </c>
-      <c r="G3" s="247" t="inlineStr">
+      <c r="G3" s="254" t="inlineStr">
         <is>
           <t>Daily digests in this workbook</t>
         </is>
       </c>
-      <c r="H3" s="247" t="n">
+      <c r="H3" s="254" t="n">
         <v>1</v>
       </c>
-      <c r="M3" s="247" t="n">
+      <c r="M3" s="254" t="n">
         <v>2</v>
       </c>
-      <c r="N3" s="249">
-        <f>IFERROR(LARGE(Stories!$U$4:$U$63,M3),"")</f>
-        <v/>
-      </c>
-      <c r="O3" s="247">
-        <f>IF(N3="","",MATCH(N3,Stories!$U$4:$U$63,0))</f>
-        <v/>
-      </c>
-      <c r="P3" s="247">
-        <f>IF(O3="","",INDEX(Stories!$S$4:$S$63,O3)&amp;"")</f>
-        <v/>
-      </c>
-      <c r="Q3" s="247">
+      <c r="N3" s="256">
+        <f>IFERROR(LARGE(Stories!$X$4:$X$63,M3),"")</f>
+        <v/>
+      </c>
+      <c r="O3" s="254">
+        <f>IF(N3="","",MATCH(N3,Stories!$X$4:$X$63,0))</f>
+        <v/>
+      </c>
+      <c r="P3" s="254">
+        <f>IF(O3="","",INDEX(Stories!$V$4:$V$63,O3)&amp;"")</f>
+        <v/>
+      </c>
+      <c r="Q3" s="254">
         <f>IF(O3="","",IF(LEN(INDEX(Stories!$B$4:$B$63,O3))&gt;120,LEFT(INDEX(Stories!$B$4:$B$63,O3),118)&amp;"…",INDEX(Stories!$B$4:$B$63,O3)&amp;""))</f>
         <v/>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="247" t="inlineStr">
+      <c r="A4" s="254" t="inlineStr">
         <is>
           <t>Digital Geotechnics</t>
         </is>
       </c>
-      <c r="B4" s="247" t="inlineStr">
+      <c r="B4" s="254" t="inlineStr">
         <is>
           <t>News brief</t>
         </is>
       </c>
-      <c r="C4" s="247" t="n">
+      <c r="C4" s="254" t="n">
         <v>4</v>
       </c>
-      <c r="E4" s="247" t="inlineStr">
+      <c r="E4" s="254" t="inlineStr">
         <is>
           <t>Commissioned</t>
         </is>
       </c>
-      <c r="G4" s="247" t="inlineStr">
+      <c r="G4" s="254" t="inlineStr">
         <is>
           <t>Stories in this workbook</t>
         </is>
       </c>
-      <c r="H4" s="247" t="n">
+      <c r="H4" s="254" t="n">
         <v>60</v>
       </c>
-      <c r="M4" s="247" t="n">
+      <c r="M4" s="254" t="n">
         <v>3</v>
       </c>
-      <c r="N4" s="249">
-        <f>IFERROR(LARGE(Stories!$U$4:$U$63,M4),"")</f>
-        <v/>
-      </c>
-      <c r="O4" s="247">
-        <f>IF(N4="","",MATCH(N4,Stories!$U$4:$U$63,0))</f>
-        <v/>
-      </c>
-      <c r="P4" s="247">
-        <f>IF(O4="","",INDEX(Stories!$S$4:$S$63,O4)&amp;"")</f>
-        <v/>
-      </c>
-      <c r="Q4" s="247">
+      <c r="N4" s="256">
+        <f>IFERROR(LARGE(Stories!$X$4:$X$63,M4),"")</f>
+        <v/>
+      </c>
+      <c r="O4" s="254">
+        <f>IF(N4="","",MATCH(N4,Stories!$X$4:$X$63,0))</f>
+        <v/>
+      </c>
+      <c r="P4" s="254">
+        <f>IF(O4="","",INDEX(Stories!$V$4:$V$63,O4)&amp;"")</f>
+        <v/>
+      </c>
+      <c r="Q4" s="254">
         <f>IF(O4="","",IF(LEN(INDEX(Stories!$B$4:$B$63,O4))&gt;120,LEFT(INDEX(Stories!$B$4:$B$63,O4),118)&amp;"…",INDEX(Stories!$B$4:$B$63,O4)&amp;""))</f>
         <v/>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="247" t="inlineStr">
+      <c r="A5" s="254" t="inlineStr">
         <is>
           <t>Hazards &amp; Resilience</t>
         </is>
       </c>
-      <c r="B5" s="247" t="inlineStr">
+      <c r="B5" s="254" t="inlineStr">
         <is>
           <t>Academia-to-Industry topic</t>
         </is>
       </c>
-      <c r="C5" s="247" t="n">
+      <c r="C5" s="254" t="n">
         <v>5</v>
       </c>
-      <c r="E5" s="247" t="inlineStr">
+      <c r="E5" s="254" t="inlineStr">
         <is>
           <t>Published</t>
         </is>
       </c>
-      <c r="G5" s="247" t="inlineStr">
+      <c r="G5" s="254" t="inlineStr">
         <is>
           <t>No selector set</t>
         </is>
       </c>
-      <c r="H5" s="247">
+      <c r="H5" s="254">
         <f>AND(OR(Dashboard!$B$5="All themes",Dashboard!$B$5=""),OR(Dashboard!$G$5="All uses",Dashboard!$G$5=""),$H$2=0,OR(Dashboard!$N$5="All windows",Dashboard!$N$5=""))</f>
         <v/>
       </c>
-      <c r="M5" s="247" t="n">
+      <c r="M5" s="254" t="n">
         <v>4</v>
       </c>
-      <c r="N5" s="249">
-        <f>IFERROR(LARGE(Stories!$U$4:$U$63,M5),"")</f>
-        <v/>
-      </c>
-      <c r="O5" s="247">
-        <f>IF(N5="","",MATCH(N5,Stories!$U$4:$U$63,0))</f>
-        <v/>
-      </c>
-      <c r="P5" s="247">
-        <f>IF(O5="","",INDEX(Stories!$S$4:$S$63,O5)&amp;"")</f>
-        <v/>
-      </c>
-      <c r="Q5" s="247">
+      <c r="N5" s="256">
+        <f>IFERROR(LARGE(Stories!$X$4:$X$63,M5),"")</f>
+        <v/>
+      </c>
+      <c r="O5" s="254">
+        <f>IF(N5="","",MATCH(N5,Stories!$X$4:$X$63,0))</f>
+        <v/>
+      </c>
+      <c r="P5" s="254">
+        <f>IF(O5="","",INDEX(Stories!$V$4:$V$63,O5)&amp;"")</f>
+        <v/>
+      </c>
+      <c r="Q5" s="254">
         <f>IF(O5="","",IF(LEN(INDEX(Stories!$B$4:$B$63,O5))&gt;120,LEFT(INDEX(Stories!$B$4:$B$63,O5),118)&amp;"…",INDEX(Stories!$B$4:$B$63,O5)&amp;""))</f>
         <v/>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="247" t="inlineStr">
+      <c r="A6" s="254" t="inlineStr">
         <is>
           <t>Ground Improvement &amp; Innovation</t>
         </is>
       </c>
-      <c r="B6" s="247" t="inlineStr">
+      <c r="B6" s="254" t="inlineStr">
         <is>
           <t>Regional insight</t>
         </is>
       </c>
-      <c r="E6" s="247" t="inlineStr">
+      <c r="E6" s="254" t="inlineStr">
         <is>
           <t>Not used</t>
         </is>
       </c>
-      <c r="G6" s="247" t="inlineStr">
+      <c r="G6" s="254" t="inlineStr">
         <is>
           <t>Stories in the selection</t>
         </is>
       </c>
-      <c r="H6" s="247">
-        <f>COUNTIF(Stories!$T$4:$T$63,1)</f>
-        <v/>
-      </c>
-      <c r="M6" s="247" t="n">
+      <c r="H6" s="254">
+        <f>COUNTIF(Stories!$W$4:$W$63,1)</f>
+        <v/>
+      </c>
+      <c r="M6" s="254" t="n">
         <v>5</v>
       </c>
-      <c r="N6" s="249">
-        <f>IFERROR(LARGE(Stories!$U$4:$U$63,M6),"")</f>
-        <v/>
-      </c>
-      <c r="O6" s="247">
-        <f>IF(N6="","",MATCH(N6,Stories!$U$4:$U$63,0))</f>
-        <v/>
-      </c>
-      <c r="P6" s="247">
-        <f>IF(O6="","",INDEX(Stories!$S$4:$S$63,O6)&amp;"")</f>
-        <v/>
-      </c>
-      <c r="Q6" s="247">
+      <c r="N6" s="256">
+        <f>IFERROR(LARGE(Stories!$X$4:$X$63,M6),"")</f>
+        <v/>
+      </c>
+      <c r="O6" s="254">
+        <f>IF(N6="","",MATCH(N6,Stories!$X$4:$X$63,0))</f>
+        <v/>
+      </c>
+      <c r="P6" s="254">
+        <f>IF(O6="","",INDEX(Stories!$V$4:$V$63,O6)&amp;"")</f>
+        <v/>
+      </c>
+      <c r="Q6" s="254">
         <f>IF(O6="","",IF(LEN(INDEX(Stories!$B$4:$B$63,O6))&gt;120,LEFT(INDEX(Stories!$B$4:$B$63,O6),118)&amp;"…",INDEX(Stories!$B$4:$B$63,O6)&amp;""))</f>
         <v/>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="247" t="inlineStr">
+      <c r="A7" s="254" t="inlineStr">
         <is>
           <t>Infrastructure &amp; the Underground City</t>
         </is>
       </c>
-      <c r="B7" s="247" t="inlineStr">
+      <c r="B7" s="254" t="inlineStr">
         <is>
           <t>Watch only</t>
         </is>
       </c>
-      <c r="M7" s="247" t="n">
+      <c r="M7" s="254" t="n">
         <v>6</v>
       </c>
-      <c r="N7" s="249">
-        <f>IFERROR(LARGE(Stories!$U$4:$U$63,M7),"")</f>
-        <v/>
-      </c>
-      <c r="O7" s="247">
-        <f>IF(N7="","",MATCH(N7,Stories!$U$4:$U$63,0))</f>
-        <v/>
-      </c>
-      <c r="P7" s="247">
-        <f>IF(O7="","",INDEX(Stories!$S$4:$S$63,O7)&amp;"")</f>
-        <v/>
-      </c>
-      <c r="Q7" s="247">
+      <c r="N7" s="256">
+        <f>IFERROR(LARGE(Stories!$X$4:$X$63,M7),"")</f>
+        <v/>
+      </c>
+      <c r="O7" s="254">
+        <f>IF(N7="","",MATCH(N7,Stories!$X$4:$X$63,0))</f>
+        <v/>
+      </c>
+      <c r="P7" s="254">
+        <f>IF(O7="","",INDEX(Stories!$V$4:$V$63,O7)&amp;"")</f>
+        <v/>
+      </c>
+      <c r="Q7" s="254">
         <f>IF(O7="","",IF(LEN(INDEX(Stories!$B$4:$B$63,O7))&gt;120,LEFT(INDEX(Stories!$B$4:$B$63,O7),118)&amp;"…",INDEX(Stories!$B$4:$B$63,O7)&amp;""))</f>
         <v/>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="247" t="inlineStr">
+      <c r="A8" s="254" t="inlineStr">
         <is>
           <t>Offshore, Coasts &amp; Water</t>
         </is>
       </c>
-      <c r="M8" s="247" t="n">
+      <c r="M8" s="254" t="n">
         <v>7</v>
       </c>
-      <c r="N8" s="249">
-        <f>IFERROR(LARGE(Stories!$U$4:$U$63,M8),"")</f>
-        <v/>
-      </c>
-      <c r="O8" s="247">
-        <f>IF(N8="","",MATCH(N8,Stories!$U$4:$U$63,0))</f>
-        <v/>
-      </c>
-      <c r="P8" s="247">
-        <f>IF(O8="","",INDEX(Stories!$S$4:$S$63,O8)&amp;"")</f>
-        <v/>
-      </c>
-      <c r="Q8" s="247">
+      <c r="N8" s="256">
+        <f>IFERROR(LARGE(Stories!$X$4:$X$63,M8),"")</f>
+        <v/>
+      </c>
+      <c r="O8" s="254">
+        <f>IF(N8="","",MATCH(N8,Stories!$X$4:$X$63,0))</f>
+        <v/>
+      </c>
+      <c r="P8" s="254">
+        <f>IF(O8="","",INDEX(Stories!$V$4:$V$63,O8)&amp;"")</f>
+        <v/>
+      </c>
+      <c r="Q8" s="254">
         <f>IF(O8="","",IF(LEN(INDEX(Stories!$B$4:$B$63,O8))&gt;120,LEFT(INDEX(Stories!$B$4:$B$63,O8),118)&amp;"…",INDEX(Stories!$B$4:$B$63,O8)&amp;""))</f>
         <v/>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="247" t="inlineStr">
+      <c r="A9" s="254" t="inlineStr">
         <is>
           <t>Characterisation &amp; Modelling</t>
         </is>
       </c>
-      <c r="M9" s="247" t="n">
+      <c r="M9" s="254" t="n">
         <v>8</v>
       </c>
-      <c r="N9" s="249">
-        <f>IFERROR(LARGE(Stories!$U$4:$U$63,M9),"")</f>
-        <v/>
-      </c>
-      <c r="O9" s="247">
-        <f>IF(N9="","",MATCH(N9,Stories!$U$4:$U$63,0))</f>
-        <v/>
-      </c>
-      <c r="P9" s="247">
-        <f>IF(O9="","",INDEX(Stories!$S$4:$S$63,O9)&amp;"")</f>
-        <v/>
-      </c>
-      <c r="Q9" s="247">
+      <c r="N9" s="256">
+        <f>IFERROR(LARGE(Stories!$X$4:$X$63,M9),"")</f>
+        <v/>
+      </c>
+      <c r="O9" s="254">
+        <f>IF(N9="","",MATCH(N9,Stories!$X$4:$X$63,0))</f>
+        <v/>
+      </c>
+      <c r="P9" s="254">
+        <f>IF(O9="","",INDEX(Stories!$V$4:$V$63,O9)&amp;"")</f>
+        <v/>
+      </c>
+      <c r="Q9" s="254">
         <f>IF(O9="","",IF(LEN(INDEX(Stories!$B$4:$B$63,O9))&gt;120,LEFT(INDEX(Stories!$B$4:$B$63,O9),118)&amp;"…",INDEX(Stories!$B$4:$B$63,O9)&amp;""))</f>
         <v/>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="247" t="inlineStr">
+      <c r="A10" s="254" t="inlineStr">
         <is>
           <t>Geotechnics &amp; Society</t>
         </is>
       </c>
-      <c r="M10" s="247" t="n">
+      <c r="M10" s="254" t="n">
         <v>9</v>
       </c>
-      <c r="N10" s="249">
-        <f>IFERROR(LARGE(Stories!$U$4:$U$63,M10),"")</f>
-        <v/>
-      </c>
-      <c r="O10" s="247">
-        <f>IF(N10="","",MATCH(N10,Stories!$U$4:$U$63,0))</f>
-        <v/>
-      </c>
-      <c r="P10" s="247">
-        <f>IF(O10="","",INDEX(Stories!$S$4:$S$63,O10)&amp;"")</f>
-        <v/>
-      </c>
-      <c r="Q10" s="247">
+      <c r="N10" s="256">
+        <f>IFERROR(LARGE(Stories!$X$4:$X$63,M10),"")</f>
+        <v/>
+      </c>
+      <c r="O10" s="254">
+        <f>IF(N10="","",MATCH(N10,Stories!$X$4:$X$63,0))</f>
+        <v/>
+      </c>
+      <c r="P10" s="254">
+        <f>IF(O10="","",INDEX(Stories!$V$4:$V$63,O10)&amp;"")</f>
+        <v/>
+      </c>
+      <c r="Q10" s="254">
         <f>IF(O10="","",IF(LEN(INDEX(Stories!$B$4:$B$63,O10))&gt;120,LEFT(INDEX(Stories!$B$4:$B$63,O10),118)&amp;"…",INDEX(Stories!$B$4:$B$63,O10)&amp;""))</f>
         <v/>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="247" t="inlineStr">
+      <c r="A11" s="254" t="inlineStr">
         <is>
           <t>General</t>
         </is>
       </c>
-      <c r="M11" s="247" t="n">
+      <c r="M11" s="254" t="n">
         <v>10</v>
       </c>
-      <c r="N11" s="249">
-        <f>IFERROR(LARGE(Stories!$U$4:$U$63,M11),"")</f>
-        <v/>
-      </c>
-      <c r="O11" s="247">
-        <f>IF(N11="","",MATCH(N11,Stories!$U$4:$U$63,0))</f>
-        <v/>
-      </c>
-      <c r="P11" s="247">
-        <f>IF(O11="","",INDEX(Stories!$S$4:$S$63,O11)&amp;"")</f>
-        <v/>
-      </c>
-      <c r="Q11" s="247">
+      <c r="N11" s="256">
+        <f>IFERROR(LARGE(Stories!$X$4:$X$63,M11),"")</f>
+        <v/>
+      </c>
+      <c r="O11" s="254">
+        <f>IF(N11="","",MATCH(N11,Stories!$X$4:$X$63,0))</f>
+        <v/>
+      </c>
+      <c r="P11" s="254">
+        <f>IF(O11="","",INDEX(Stories!$V$4:$V$63,O11)&amp;"")</f>
+        <v/>
+      </c>
+      <c r="Q11" s="254">
         <f>IF(O11="","",IF(LEN(INDEX(Stories!$B$4:$B$63,O11))&gt;120,LEFT(INDEX(Stories!$B$4:$B$63,O11),118)&amp;"…",INDEX(Stories!$B$4:$B$63,O11)&amp;""))</f>
         <v/>
       </c>

--- a/docs/exports/geotech-news-archive.xlsx
+++ b/docs/exports/geotech-news-archive.xlsx
@@ -3552,7 +3552,7 @@
       <c r="A2" s="3" t="n"/>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>All 1 issue windows · generated 24 Oct 2026</t>
+          <t>All 1 issue windows · generated 25 Oct 2026</t>
         </is>
       </c>
       <c r="C2" s="3" t="n"/>
@@ -3634,7 +3634,7 @@
       </c>
       <c r="D11" s="11" t="n"/>
     </row>
-    <row r="12" ht="31" customHeight="1">
+    <row r="12" ht="44" customHeight="1">
       <c r="B12" s="9" t="inlineStr">
         <is>
           <t>Events →</t>
@@ -3642,7 +3642,7 @@
       </c>
       <c r="C12" s="10" t="inlineStr">
         <is>
-          <t>The events calendar on 24 Oct 2026: 0 open call-for-papers deadlines with the days left, and 6 upcoming events (ISSMGE conferences, other conferences, courses and webinars), each linked to its website.</t>
+          <t>The events calendar on 25 Oct 2026: 0 open deadlines (calls for papers, registration) with the days left, and 6 upcoming events (ISSMGE conferences, other conferences, courses and webinars), each linked to its website.</t>
         </is>
       </c>
       <c r="D12" s="11" t="n"/>
@@ -4201,7 +4201,7 @@
       <c r="A2" s="3" t="n"/>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>All 1 issue windows · generated 24 Oct 2026</t>
+          <t>All 1 issue windows · generated 25 Oct 2026</t>
         </is>
       </c>
       <c r="C2" s="3" t="n"/>
@@ -16368,14 +16368,14 @@
     <row r="2" ht="16" customHeight="1">
       <c r="A2" s="154" t="inlineStr">
         <is>
-          <t>From the website's events calendar on 24 Oct 2026: ISSMGE conferences, other conferences, courses and webinars, kept by the editors (data/events.yaml) and found by the weekly refresh. Check the dates on each event's website before you publish them.</t>
+          <t>From the website's events calendar on 25 Oct 2026: ISSMGE conferences, other conferences, courses and webinars, kept by the editors (data/events.yaml) and found by the weekly refresh. Check the dates on each event's website before you publish them.</t>
         </is>
       </c>
     </row>
     <row r="4" ht="22" customHeight="1">
       <c r="A4" s="7" t="inlineStr">
         <is>
-          <t>Call-for-papers deadlines (0)</t>
+          <t>Open deadlines: calls for papers, registration (0)</t>
         </is>
       </c>
       <c r="B4" s="8" t="n"/>
@@ -16437,7 +16437,7 @@
     <row r="6">
       <c r="C6" s="234" t="inlineStr">
         <is>
-          <t>No call-for-papers deadline is open at the moment.</t>
+          <t>No deadline is open at the moment.</t>
         </is>
       </c>
     </row>
@@ -16535,7 +16535,7 @@
       </c>
       <c r="H10" s="230" t="inlineStr">
         <is>
-          <t>Abstracts: 4 Mar 2026</t>
+          <t>Abstracts: 4 Mar 2026 (passed)</t>
         </is>
       </c>
       <c r="I10" s="238" t="inlineStr">
@@ -16580,7 +16580,7 @@
       </c>
       <c r="H11" s="230" t="inlineStr">
         <is>
-          <t>Abstracts: 15 May 2026</t>
+          <t>Abstracts: 15 May 2026 (passed)</t>
         </is>
       </c>
       <c r="I11" s="238" t="inlineStr">
@@ -16621,7 +16621,7 @@
       </c>
       <c r="H12" s="230" t="inlineStr">
         <is>
-          <t>Abstracts: 10 Jun 2026</t>
+          <t>Abstracts: 10 Jun 2026 (passed)</t>
         </is>
       </c>
       <c r="I12" s="238" t="inlineStr">
@@ -16666,7 +16666,7 @@
       </c>
       <c r="H13" s="230" t="inlineStr">
         <is>
-          <t>Abstracts: 15 Jul 2026</t>
+          <t>Abstracts: 15 Jul 2026 (passed)</t>
         </is>
       </c>
       <c r="I13" s="238" t="inlineStr">
@@ -16711,7 +16711,7 @@
       </c>
       <c r="H14" s="230" t="inlineStr">
         <is>
-          <t>Abstracts: 21 Sep 2026</t>
+          <t>Abstracts: 21 Sep 2026 (passed)</t>
         </is>
       </c>
       <c r="I14" s="238" t="inlineStr">

--- a/docs/exports/geotech-news-archive.xlsx
+++ b/docs/exports/geotech-news-archive.xlsx
@@ -34,15 +34,16 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="6">
+  <numFmts count="7">
     <numFmt numFmtId="164" formatCode="0;-0;&quot;–&quot;"/>
     <numFmt numFmtId="165" formatCode="yyyy-mm-dd"/>
     <numFmt numFmtId="166" formatCode="dd mmm yyyy"/>
     <numFmt numFmtId="167" formatCode="&quot;✓&quot;;&quot;&quot;;&quot;&quot;"/>
     <numFmt numFmtId="168" formatCode="0.0"/>
-    <numFmt numFmtId="169" formatCode="dd mmm yy;;"/>
+    <numFmt numFmtId="169" formatCode="0;&quot;passed&quot;;&quot;today&quot;"/>
+    <numFmt numFmtId="170" formatCode="dd mmm yy;;"/>
   </numFmts>
-  <fonts count="74">
+  <fonts count="76">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -243,6 +244,24 @@
     <font>
       <name val="Arial"/>
       <b val="1"/>
+      <color rgb="00B4321B"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="000A6D78"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <color rgb="001D5A8A"/>
+      <sz val="9"/>
+      <u val="single"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
       <color rgb="00C9A227"/>
       <sz val="9"/>
     </font>
@@ -254,14 +273,8 @@
     </font>
     <font>
       <name val="Arial"/>
-      <color rgb="001D5A8A"/>
-      <sz val="9"/>
-      <u val="single"/>
-    </font>
-    <font>
-      <name val="Arial"/>
       <b val="1"/>
-      <color rgb="000A6D78"/>
+      <color rgb="005137B0"/>
       <sz val="9"/>
     </font>
     <font>
@@ -950,18 +963,18 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="259">
+  <cellXfs count="260">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="39" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="41" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="29" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="40" fillId="29" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="42" fillId="29" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="65" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="67" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="31" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -978,19 +991,19 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="59" fillId="37" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="61" fillId="37" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="60" fillId="38" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="62" fillId="38" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="61" fillId="39" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="63" fillId="39" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="62" fillId="40" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="64" fillId="40" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="63" fillId="41" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="65" fillId="41" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="33" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -1011,44 +1024,44 @@
     <xf numFmtId="0" fontId="9" fillId="46" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="66" fillId="14" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="68" fillId="14" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="67" fillId="16" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="69" fillId="16" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="68" fillId="18" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="70" fillId="18" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="69" fillId="20" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="71" fillId="20" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="70" fillId="22" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="72" fillId="22" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="71" fillId="24" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="73" fillId="24" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="72" fillId="26" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="74" fillId="26" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="73" fillId="28" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="75" fillId="28" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="52" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="54" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="41" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="43" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="bottom"/>
     </xf>
-    <xf numFmtId="0" fontId="43" fillId="31" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="45" fillId="31" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="31" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="42" fillId="30" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="44" fillId="30" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="30" borderId="12" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -1056,51 +1069,51 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="3" fontId="44" fillId="2" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="3" fontId="46" fillId="2" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="14" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="3" fontId="44" fillId="23" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="3" fontId="46" fillId="23" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="23" borderId="14" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="3" fontId="44" fillId="33" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="3" fontId="46" fillId="33" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="33" borderId="14" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="3" fontId="44" fillId="19" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="3" fontId="46" fillId="19" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="19" borderId="14" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="3" fontId="44" fillId="15" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="3" fontId="46" fillId="15" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="15" borderId="14" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="3" fontId="44" fillId="21" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="3" fontId="46" fillId="21" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="21" borderId="14" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="45" fillId="32" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="47" fillId="32" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="32" borderId="14" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="46" fillId="24" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="48" fillId="24" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="24" borderId="14" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="47" fillId="34" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="49" fillId="34" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="34" borderId="14" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="48" fillId="20" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="50" fillId="20" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="20" borderId="14" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="49" fillId="16" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="51" fillId="16" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="16" borderId="14" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="50" fillId="22" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="52" fillId="22" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="22" borderId="14" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -1128,17 +1141,17 @@
     <xf numFmtId="0" fontId="32" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="51" fillId="35" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="53" fillId="35" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="52" fillId="35" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="54" fillId="35" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="35" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="169" fontId="13" fillId="35" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="170" fontId="13" fillId="35" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="53" fillId="35" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="55" fillId="35" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1" indent="1"/>
     </xf>
     <xf numFmtId="164" fontId="9" fillId="35" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -1150,20 +1163,20 @@
     <xf numFmtId="0" fontId="6" fillId="35" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="54" fillId="35" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="56" fillId="35" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="51" fillId="31" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="53" fillId="31" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="52" fillId="31" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="54" fillId="31" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="31" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="169" fontId="13" fillId="31" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="170" fontId="13" fillId="31" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="53" fillId="31" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="55" fillId="31" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1" indent="1"/>
     </xf>
     <xf numFmtId="164" fontId="9" fillId="31" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -1175,10 +1188,10 @@
     <xf numFmtId="0" fontId="6" fillId="31" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="54" fillId="31" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="56" fillId="31" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="43" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="45" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="27" fillId="14" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -1222,7 +1235,7 @@
       <alignment vertical="center" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="28" borderId="22" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="55" fillId="36" borderId="23" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="57" fillId="36" borderId="23" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="36" borderId="23" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -1232,41 +1245,41 @@
     <xf numFmtId="0" fontId="15" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="59" fillId="37" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="61" fillId="37" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="37" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="26" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="57" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="59" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="60" fillId="38" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="62" fillId="38" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="38" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="28" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="58" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="60" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="61" fillId="39" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="63" fillId="39" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="39" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="27" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="62" fillId="40" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="64" fillId="40" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="40" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="56" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="58" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="63" fillId="41" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="65" fillId="41" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="41" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -1305,14 +1318,14 @@
       <alignment vertical="center" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="22" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="55" fillId="0" borderId="23" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="57" fillId="0" borderId="23" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="23" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="64" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="66" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -1413,7 +1426,7 @@
     <xf numFmtId="0" fontId="22" fillId="12" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="38" fillId="13" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="40" fillId="13" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="13" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -1450,7 +1463,7 @@
     <xf numFmtId="0" fontId="19" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="38" fillId="15" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="40" fillId="15" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="15" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -1463,7 +1476,7 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="38" fillId="17" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="40" fillId="17" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="17" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -1476,7 +1489,7 @@
     <xf numFmtId="0" fontId="22" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="38" fillId="19" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="40" fillId="19" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="19" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -1486,7 +1499,7 @@
     <xf numFmtId="0" fontId="10" fillId="20" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="38" fillId="21" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="40" fillId="21" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="21" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -1499,7 +1512,7 @@
     <xf numFmtId="0" fontId="21" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="38" fillId="23" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="40" fillId="23" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="23" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -1509,7 +1522,7 @@
     <xf numFmtId="0" fontId="17" fillId="24" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="38" fillId="25" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="40" fillId="25" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="25" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -1519,7 +1532,7 @@
     <xf numFmtId="0" fontId="18" fillId="26" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="38" fillId="27" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="40" fillId="27" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="27" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -1547,11 +1560,10 @@
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="166" fontId="9" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="33" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="169" fontId="33" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="34" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -1561,9 +1573,15 @@
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="36" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="37" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="38" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -3654,7 +3672,7 @@
       </c>
       <c r="C12" s="10" t="inlineStr">
         <is>
-          <t>The events calendar on 25 Oct 2026: 0 open deadlines (calls for papers, registration) with the days left, and 6 upcoming events (ISSMGE conferences, other conferences, courses and webinars), each linked to its website.</t>
+          <t>The events calendar on 25 Oct 2026: 3 open deadlines (calls for papers, registration) with the days left, and 45 upcoming events (ISSMGE conferences, other conferences, courses and webinars), each linked to its website.</t>
         </is>
       </c>
       <c r="D12" s="11" t="n"/>
@@ -22300,7 +22318,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I15"/>
+  <dimension ref="A1:I56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -22317,7 +22335,7 @@
     <row r="1" ht="26" customHeight="1">
       <c r="A1" s="152" t="inlineStr">
         <is>
-          <t>Events · 6 upcoming, 0 open deadlines</t>
+          <t>Events · 45 upcoming, 3 open deadlines</t>
         </is>
       </c>
       <c r="D1" s="153" t="inlineStr">
@@ -22341,7 +22359,7 @@
     <row r="4" ht="22" customHeight="1">
       <c r="A4" s="7" t="inlineStr">
         <is>
-          <t>Open deadlines: calls for papers, registration (0)</t>
+          <t>Open deadlines: calls for papers, registration (3)</t>
         </is>
       </c>
       <c r="B4" s="8" t="n"/>
@@ -22400,330 +22418,1842 @@
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="C6" s="236" t="inlineStr">
-        <is>
-          <t>No deadline is open at the moment.</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="22" customHeight="1">
-      <c r="A8" s="7" t="inlineStr">
-        <is>
-          <t>Upcoming events (6)</t>
-        </is>
-      </c>
-      <c r="B8" s="8" t="n"/>
-      <c r="C8" s="8" t="n"/>
-      <c r="D8" s="8" t="n"/>
-      <c r="E8" s="8" t="n"/>
-      <c r="F8" s="8" t="n"/>
-      <c r="G8" s="8" t="n"/>
-      <c r="H8" s="8" t="n"/>
-      <c r="I8" s="8" t="n"/>
-    </row>
-    <row r="9" ht="20" customHeight="1">
-      <c r="A9" s="71" t="inlineStr">
+    <row r="6" ht="55" customHeight="1">
+      <c r="A6" s="236" t="n">
+        <v>46367</v>
+      </c>
+      <c r="B6" s="237">
+        <f>A6-TODAY()</f>
+        <v/>
+      </c>
+      <c r="C6" s="231" t="inlineStr">
+        <is>
+          <t>11th European Conference on Numerical Methods in Geotechnical Engineering (NUMGE 2027)</t>
+        </is>
+      </c>
+      <c r="D6" s="238" t="inlineStr">
+        <is>
+          <t>ISSMGE-supported</t>
+        </is>
+      </c>
+      <c r="E6" s="166" t="inlineStr">
+        <is>
+          <t>Graz, Austria</t>
+        </is>
+      </c>
+      <c r="F6" s="166" t="inlineStr">
+        <is>
+          <t>21–24 Sep 2027</t>
+        </is>
+      </c>
+      <c r="G6" s="232" t="inlineStr">
+        <is>
+          <t>Institute of Soil Mechanics, Foundation Engineering and Computational Geotechnics, Graz University of Technology</t>
+        </is>
+      </c>
+      <c r="H6" s="231" t="inlineStr">
+        <is>
+          <t>Notification of accepted abstracts</t>
+        </is>
+      </c>
+      <c r="I6" s="239" t="inlineStr">
+        <is>
+          <t>https://www.issmge.org/events/numge2027</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="55" customHeight="1">
+      <c r="A7" s="236" t="n">
+        <v>46465</v>
+      </c>
+      <c r="B7" s="237">
+        <f>A7-TODAY()</f>
+        <v/>
+      </c>
+      <c r="C7" s="231" t="inlineStr">
+        <is>
+          <t>11th European Conference on Numerical Methods in Geotechnical Engineering (NUMGE 2027)</t>
+        </is>
+      </c>
+      <c r="D7" s="238" t="inlineStr">
+        <is>
+          <t>ISSMGE-supported</t>
+        </is>
+      </c>
+      <c r="E7" s="166" t="inlineStr">
+        <is>
+          <t>Graz, Austria</t>
+        </is>
+      </c>
+      <c r="F7" s="166" t="inlineStr">
+        <is>
+          <t>21–24 Sep 2027</t>
+        </is>
+      </c>
+      <c r="G7" s="232" t="inlineStr">
+        <is>
+          <t>Institute of Soil Mechanics, Foundation Engineering and Computational Geotechnics, Graz University of Technology</t>
+        </is>
+      </c>
+      <c r="H7" s="231" t="inlineStr">
+        <is>
+          <t>Manuscripts</t>
+        </is>
+      </c>
+      <c r="I7" s="239" t="inlineStr">
+        <is>
+          <t>https://www.issmge.org/events/numge2027</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="55" customHeight="1">
+      <c r="A8" s="236" t="n">
+        <v>46537</v>
+      </c>
+      <c r="B8" s="237">
+        <f>A8-TODAY()</f>
+        <v/>
+      </c>
+      <c r="C8" s="231" t="inlineStr">
+        <is>
+          <t>11th European Conference on Numerical Methods in Geotechnical Engineering (NUMGE 2027)</t>
+        </is>
+      </c>
+      <c r="D8" s="238" t="inlineStr">
+        <is>
+          <t>ISSMGE-supported</t>
+        </is>
+      </c>
+      <c r="E8" s="166" t="inlineStr">
+        <is>
+          <t>Graz, Austria</t>
+        </is>
+      </c>
+      <c r="F8" s="166" t="inlineStr">
+        <is>
+          <t>21–24 Sep 2027</t>
+        </is>
+      </c>
+      <c r="G8" s="232" t="inlineStr">
+        <is>
+          <t>Institute of Soil Mechanics, Foundation Engineering and Computational Geotechnics, Graz University of Technology</t>
+        </is>
+      </c>
+      <c r="H8" s="231" t="inlineStr">
+        <is>
+          <t>Final papers</t>
+        </is>
+      </c>
+      <c r="I8" s="239" t="inlineStr">
+        <is>
+          <t>https://www.issmge.org/events/numge2027</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="22" customHeight="1">
+      <c r="A10" s="7" t="inlineStr">
+        <is>
+          <t>Upcoming events (45)</t>
+        </is>
+      </c>
+      <c r="B10" s="8" t="n"/>
+      <c r="C10" s="8" t="n"/>
+      <c r="D10" s="8" t="n"/>
+      <c r="E10" s="8" t="n"/>
+      <c r="F10" s="8" t="n"/>
+      <c r="G10" s="8" t="n"/>
+      <c r="H10" s="8" t="n"/>
+      <c r="I10" s="8" t="n"/>
+    </row>
+    <row r="11" ht="20" customHeight="1">
+      <c r="A11" s="71" t="inlineStr">
         <is>
           <t>Starts</t>
         </is>
       </c>
-      <c r="B9" s="71" t="inlineStr">
+      <c r="B11" s="71" t="inlineStr">
         <is>
           <t>ISSMGE</t>
         </is>
       </c>
-      <c r="C9" s="71" t="inlineStr">
+      <c r="C11" s="71" t="inlineStr">
         <is>
           <t>Event</t>
         </is>
       </c>
-      <c r="D9" s="71" t="inlineStr">
+      <c r="D11" s="71" t="inlineStr">
         <is>
           <t>Kind</t>
         </is>
       </c>
-      <c r="E9" s="71" t="inlineStr">
+      <c r="E11" s="71" t="inlineStr">
         <is>
           <t>Place</t>
         </is>
       </c>
-      <c r="F9" s="71" t="inlineStr">
+      <c r="F11" s="71" t="inlineStr">
         <is>
           <t>Dates</t>
         </is>
       </c>
-      <c r="G9" s="71" t="inlineStr">
+      <c r="G11" s="71" t="inlineStr">
         <is>
           <t>Organiser</t>
         </is>
       </c>
-      <c r="H9" s="71" t="inlineStr">
+      <c r="H11" s="71" t="inlineStr">
         <is>
           <t>Deadlines</t>
         </is>
       </c>
-      <c r="I9" s="71" t="inlineStr">
+      <c r="I11" s="71" t="inlineStr">
         <is>
           <t>Website</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="17.5" customHeight="1">
-      <c r="A10" s="237" t="n">
+    <row r="12" ht="30" customHeight="1">
+      <c r="A12" s="236" t="n">
+        <v>46321</v>
+      </c>
+      <c r="B12" s="240" t="n"/>
+      <c r="C12" s="231" t="inlineStr">
+        <is>
+          <t>Slope Stability 2026 – Slope for Safety Performance – an ISRM Specialized Conference</t>
+        </is>
+      </c>
+      <c r="D12" s="241" t="inlineStr">
+        <is>
+          <t>Other conference</t>
+        </is>
+      </c>
+      <c r="E12" s="166" t="inlineStr">
+        <is>
+          <t>Lima, Peru</t>
+        </is>
+      </c>
+      <c r="F12" s="166" t="inlineStr">
+        <is>
+          <t>26–29 Oct 2026</t>
+        </is>
+      </c>
+      <c r="G12" s="232" t="inlineStr">
+        <is>
+          <t>ISRM</t>
+        </is>
+      </c>
+      <c r="H12" s="232" t="n"/>
+      <c r="I12" s="239" t="inlineStr">
+        <is>
+          <t>https://isrm.net/conference/show/6392</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="30" customHeight="1">
+      <c r="A13" s="236" t="n">
+        <v>46328</v>
+      </c>
+      <c r="B13" s="240" t="n"/>
+      <c r="C13" s="231" t="inlineStr">
+        <is>
+          <t>DFI's 51st Annual Conference on Deep Foundations (DFI51)</t>
+        </is>
+      </c>
+      <c r="D13" s="241" t="inlineStr">
+        <is>
+          <t>Other conference</t>
+        </is>
+      </c>
+      <c r="E13" s="166" t="inlineStr">
+        <is>
+          <t>Orlando, United States</t>
+        </is>
+      </c>
+      <c r="F13" s="166" t="inlineStr">
+        <is>
+          <t>2–5 Nov 2026</t>
+        </is>
+      </c>
+      <c r="G13" s="232" t="inlineStr">
+        <is>
+          <t>Deep Foundations Institute (DFI)</t>
+        </is>
+      </c>
+      <c r="H13" s="232" t="n"/>
+      <c r="I13" s="239" t="inlineStr">
+        <is>
+          <t>https://dfi-events.org/dfi51/</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="42.5" customHeight="1">
+      <c r="A14" s="236" t="n">
+        <v>46330</v>
+      </c>
+      <c r="B14" s="240" t="n"/>
+      <c r="C14" s="231" t="inlineStr">
+        <is>
+          <t>2026 Geotechnical Engineering Proceedings Lecture: Strains in sprayed concrete tunnel linings at Heathrow Terminal 4 and back-calculation of stress</t>
+        </is>
+      </c>
+      <c r="D14" s="242" t="inlineStr">
+        <is>
+          <t>Course / webinar</t>
+        </is>
+      </c>
+      <c r="E14" s="166" t="inlineStr">
+        <is>
+          <t>London, United Kingdom</t>
+        </is>
+      </c>
+      <c r="F14" s="166" t="inlineStr">
+        <is>
+          <t>4 Nov 2026</t>
+        </is>
+      </c>
+      <c r="G14" s="232" t="inlineStr">
+        <is>
+          <t>British Geotechnical Association (BGA)</t>
+        </is>
+      </c>
+      <c r="H14" s="232" t="n"/>
+      <c r="I14" s="239" t="inlineStr">
+        <is>
+          <t>https://www.britishgeotech.org/event/the-2026-geotechnical-engineering-proceedings-lecture-strains-in-sprayed-concrete-tunnel-linings-at-heathrow-terminal-4-and-back-calculation-of-stress/</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="30" customHeight="1">
+      <c r="A15" s="236" t="n">
+        <v>46330</v>
+      </c>
+      <c r="B15" s="240" t="inlineStr">
+        <is>
+          <t>ISSMGE</t>
+        </is>
+      </c>
+      <c r="C15" s="231" t="inlineStr">
+        <is>
+          <t>International Conference on Performance-Based Design in Earthquake Geotechnical Engineering (PBD-V 2026)</t>
+        </is>
+      </c>
+      <c r="D15" s="238" t="inlineStr">
+        <is>
+          <t>ISSMGE-supported</t>
+        </is>
+      </c>
+      <c r="E15" s="166" t="inlineStr">
+        <is>
+          <t>Puerto Varas, Chile</t>
+        </is>
+      </c>
+      <c r="F15" s="166" t="inlineStr">
+        <is>
+          <t>4–6 Nov 2026</t>
+        </is>
+      </c>
+      <c r="G15" s="232" t="n"/>
+      <c r="H15" s="232" t="n"/>
+      <c r="I15" s="239" t="inlineStr">
+        <is>
+          <t>https://www.issmge.org/events/pbd-v-conference-2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="30" customHeight="1">
+      <c r="A16" s="236" t="n">
+        <v>46336</v>
+      </c>
+      <c r="B16" s="240" t="n"/>
+      <c r="C16" s="231" t="inlineStr">
+        <is>
+          <t>BGA ECG Advanced Laboratory Testing &amp; Dynamic Behaviour of Soils</t>
+        </is>
+      </c>
+      <c r="D16" s="242" t="inlineStr">
+        <is>
+          <t>Course / webinar</t>
+        </is>
+      </c>
+      <c r="E16" s="166" t="inlineStr">
+        <is>
+          <t>Online</t>
+        </is>
+      </c>
+      <c r="F16" s="166" t="inlineStr">
+        <is>
+          <t>10 Nov 2026</t>
+        </is>
+      </c>
+      <c r="G16" s="232" t="inlineStr">
+        <is>
+          <t>BGA Early Career Group</t>
+        </is>
+      </c>
+      <c r="H16" s="232" t="n"/>
+      <c r="I16" s="239" t="inlineStr">
+        <is>
+          <t>https://www.britishgeotech.org/event/bga-ecg-advanced-laboratory-testing-dynamic-behaviour-of-soils/</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="17.5" customHeight="1">
+      <c r="A17" s="236" t="n">
+        <v>46336</v>
+      </c>
+      <c r="B17" s="240" t="n"/>
+      <c r="C17" s="231" t="inlineStr">
+        <is>
+          <t>ITACET Lunchtime Lecture Series #60</t>
+        </is>
+      </c>
+      <c r="D17" s="242" t="inlineStr">
+        <is>
+          <t>Course / webinar</t>
+        </is>
+      </c>
+      <c r="E17" s="166" t="n"/>
+      <c r="F17" s="166" t="inlineStr">
+        <is>
+          <t>10 Nov 2026</t>
+        </is>
+      </c>
+      <c r="G17" s="232" t="inlineStr">
+        <is>
+          <t>ITA-AITES / ITACET Foundation</t>
+        </is>
+      </c>
+      <c r="H17" s="232" t="n"/>
+      <c r="I17" s="239" t="inlineStr">
+        <is>
+          <t>https://about.ita-aites.org/future-events/2671/itacet-lunchtime-lecture-series-60?tmpl=component</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="42.5" customHeight="1">
+      <c r="A18" s="236" t="n">
+        <v>46336</v>
+      </c>
+      <c r="B18" s="240" t="inlineStr">
+        <is>
+          <t>ISSMGE</t>
+        </is>
+      </c>
+      <c r="C18" s="231" t="inlineStr">
+        <is>
+          <t>Woh Hup Distinguished Lecture by Prof. Kenichi Soga</t>
+        </is>
+      </c>
+      <c r="D18" s="242" t="inlineStr">
+        <is>
+          <t>Course / webinar</t>
+        </is>
+      </c>
+      <c r="E18" s="166" t="n"/>
+      <c r="F18" s="166" t="inlineStr">
+        <is>
+          <t>10 Nov 2026</t>
+        </is>
+      </c>
+      <c r="G18" s="232" t="inlineStr">
+        <is>
+          <t>National University of Singapore, co-organised by ISSMGE TC207</t>
+        </is>
+      </c>
+      <c r="H18" s="232" t="n"/>
+      <c r="I18" s="239" t="inlineStr">
+        <is>
+          <t>https://www.issmge.org/news/distinguished-lecture-by-prof-kenichi-soga-co-organised-by-issmge-tc207-10-nov-2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="42.5" customHeight="1">
+      <c r="A19" s="236" t="n">
+        <v>46338</v>
+      </c>
+      <c r="B19" s="240" t="n"/>
+      <c r="C19" s="231" t="inlineStr">
+        <is>
+          <t>10th Conference of the Croatian Geotechnical Society: Geotechnical Engineering in Soft Rocks and Heterogeneous Rock Masses – an ISRM Specialized Conference</t>
+        </is>
+      </c>
+      <c r="D19" s="241" t="inlineStr">
+        <is>
+          <t>Other conference</t>
+        </is>
+      </c>
+      <c r="E19" s="166" t="inlineStr">
+        <is>
+          <t>Split, Croatia</t>
+        </is>
+      </c>
+      <c r="F19" s="166" t="inlineStr">
+        <is>
+          <t>12–14 Nov 2026</t>
+        </is>
+      </c>
+      <c r="G19" s="232" t="inlineStr">
+        <is>
+          <t>Croatian Geotechnical Society</t>
+        </is>
+      </c>
+      <c r="H19" s="232" t="n"/>
+      <c r="I19" s="239" t="inlineStr">
+        <is>
+          <t>https://isrm.net/conference/show/6404</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="17.5" customHeight="1">
+      <c r="A20" s="236" t="n">
+        <v>46338</v>
+      </c>
+      <c r="B20" s="240" t="n"/>
+      <c r="C20" s="231" t="inlineStr">
+        <is>
+          <t>Tunnel Turkey 2026</t>
+        </is>
+      </c>
+      <c r="D20" s="241" t="inlineStr">
+        <is>
+          <t>Other conference</t>
+        </is>
+      </c>
+      <c r="E20" s="166" t="inlineStr">
+        <is>
+          <t>Türkiye</t>
+        </is>
+      </c>
+      <c r="F20" s="166" t="inlineStr">
+        <is>
+          <t>12 Nov 2026</t>
+        </is>
+      </c>
+      <c r="G20" s="232" t="n"/>
+      <c r="H20" s="232" t="n"/>
+      <c r="I20" s="239" t="inlineStr">
+        <is>
+          <t>https://about.ita-aites.org/future-events/2558/tunnel-turkey-2026?tmpl=component</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="30" customHeight="1">
+      <c r="A21" s="236" t="n">
+        <v>46343</v>
+      </c>
+      <c r="B21" s="240" t="n"/>
+      <c r="C21" s="231" t="inlineStr">
+        <is>
+          <t>BGA Touring Lecture – Beyond Automation: Responsible AI Workflows in Geotechnical Modelling and Monitoring</t>
+        </is>
+      </c>
+      <c r="D21" s="242" t="inlineStr">
+        <is>
+          <t>Course / webinar</t>
+        </is>
+      </c>
+      <c r="E21" s="166" t="inlineStr">
+        <is>
+          <t>Leeds, United Kingdom</t>
+        </is>
+      </c>
+      <c r="F21" s="166" t="inlineStr">
+        <is>
+          <t>17–19 Nov 2026</t>
+        </is>
+      </c>
+      <c r="G21" s="232" t="inlineStr">
+        <is>
+          <t>British Geotechnical Association (BGA)</t>
+        </is>
+      </c>
+      <c r="H21" s="232" t="n"/>
+      <c r="I21" s="239" t="inlineStr">
+        <is>
+          <t>https://www.britishgeotech.org/event/bga-touring-lecture-beyond-automation-responsible-ai-workflows-in-geotechnical-modelling-and-monitoring/</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="55" customHeight="1">
+      <c r="A22" s="236" t="n">
+        <v>46348</v>
+      </c>
+      <c r="B22" s="240" t="n"/>
+      <c r="C22" s="231" t="inlineStr">
+        <is>
+          <t>ARMS14 – 14th Asian Rock Mechanics Symposium – Rock Mechanics for the Next Generation – Innovations, Sustainability, and Resilience – the 2026 ISRM International Symposium</t>
+        </is>
+      </c>
+      <c r="D22" s="241" t="inlineStr">
+        <is>
+          <t>Other conference</t>
+        </is>
+      </c>
+      <c r="E22" s="166" t="inlineStr">
+        <is>
+          <t>Fukuoka, Japan</t>
+        </is>
+      </c>
+      <c r="F22" s="166" t="inlineStr">
+        <is>
+          <t>22–26 Nov 2026</t>
+        </is>
+      </c>
+      <c r="G22" s="232" t="inlineStr">
+        <is>
+          <t>ISRM</t>
+        </is>
+      </c>
+      <c r="H22" s="232" t="n"/>
+      <c r="I22" s="239" t="inlineStr">
+        <is>
+          <t>https://isrm.net/conference/show/6382</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="17.5" customHeight="1">
+      <c r="A23" s="236" t="n">
+        <v>46352</v>
+      </c>
+      <c r="B23" s="240" t="n"/>
+      <c r="C23" s="231" t="inlineStr">
+        <is>
+          <t>Italian Underground Conference / Congress</t>
+        </is>
+      </c>
+      <c r="D23" s="241" t="inlineStr">
+        <is>
+          <t>Other conference</t>
+        </is>
+      </c>
+      <c r="E23" s="166" t="n"/>
+      <c r="F23" s="166" t="inlineStr">
+        <is>
+          <t>26 Nov 2026</t>
+        </is>
+      </c>
+      <c r="G23" s="232" t="n"/>
+      <c r="H23" s="232" t="n"/>
+      <c r="I23" s="239" t="inlineStr">
+        <is>
+          <t>https://about.ita-aites.org/future-events/2652/italian-underground-conference-congress?tmpl=component</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="42.5" customHeight="1">
+      <c r="A24" s="236" t="n">
+        <v>46352</v>
+      </c>
+      <c r="B24" s="240" t="inlineStr">
+        <is>
+          <t>ISSMGE</t>
+        </is>
+      </c>
+      <c r="C24" s="231" t="inlineStr">
+        <is>
+          <t>The 6th International Conference on Geotechnics for Sustainable Infrastructure Development (GEOTEC HANOI 2026)</t>
+        </is>
+      </c>
+      <c r="D24" s="238" t="inlineStr">
+        <is>
+          <t>ISSMGE-supported</t>
+        </is>
+      </c>
+      <c r="E24" s="166" t="inlineStr">
+        <is>
+          <t>Hanoi, Vietnam</t>
+        </is>
+      </c>
+      <c r="F24" s="166" t="inlineStr">
+        <is>
+          <t>26 Nov 2026</t>
+        </is>
+      </c>
+      <c r="G24" s="232" t="n"/>
+      <c r="H24" s="232" t="n"/>
+      <c r="I24" s="239" t="inlineStr">
+        <is>
+          <t>https://www.issmge.org/events/geotec-hanoi-2026-gh2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="30" customHeight="1">
+      <c r="A25" s="236" t="n">
+        <v>46357</v>
+      </c>
+      <c r="B25" s="240" t="n"/>
+      <c r="C25" s="231" t="inlineStr">
+        <is>
+          <t>BGA Fleming Award Event 2026</t>
+        </is>
+      </c>
+      <c r="D25" s="242" t="inlineStr">
+        <is>
+          <t>Course / webinar</t>
+        </is>
+      </c>
+      <c r="E25" s="166" t="inlineStr">
+        <is>
+          <t>London, United Kingdom</t>
+        </is>
+      </c>
+      <c r="F25" s="166" t="inlineStr">
+        <is>
+          <t>1 Dec 2026</t>
+        </is>
+      </c>
+      <c r="G25" s="232" t="inlineStr">
+        <is>
+          <t>British Geotechnical Association (BGA)</t>
+        </is>
+      </c>
+      <c r="H25" s="232" t="n"/>
+      <c r="I25" s="239" t="inlineStr">
+        <is>
+          <t>https://www.britishgeotech.org/event/bga-fleming-award-event-2026/</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="30" customHeight="1">
+      <c r="A26" s="236" t="n">
+        <v>46359</v>
+      </c>
+      <c r="B26" s="240" t="n"/>
+      <c r="C26" s="231" t="inlineStr">
+        <is>
+          <t>TUNNELLING ASIA 2026: International Conference &amp; Exhibition</t>
+        </is>
+      </c>
+      <c r="D26" s="241" t="inlineStr">
+        <is>
+          <t>Other conference</t>
+        </is>
+      </c>
+      <c r="E26" s="166" t="n"/>
+      <c r="F26" s="166" t="inlineStr">
+        <is>
+          <t>3 Dec 2026</t>
+        </is>
+      </c>
+      <c r="G26" s="232" t="n"/>
+      <c r="H26" s="232" t="n"/>
+      <c r="I26" s="239" t="inlineStr">
+        <is>
+          <t>https://about.ita-aites.org/future-events/2654/tunnelling-asia-2026-international-conference-exhibition?tmpl=component</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="30" customHeight="1">
+      <c r="A27" s="236" t="n">
+        <v>46363</v>
+      </c>
+      <c r="B27" s="240" t="n"/>
+      <c r="C27" s="231" t="inlineStr">
+        <is>
+          <t>World Tunnel Day 2026 – ITAym</t>
+        </is>
+      </c>
+      <c r="D27" s="242" t="inlineStr">
+        <is>
+          <t>Course / webinar</t>
+        </is>
+      </c>
+      <c r="E27" s="166" t="n"/>
+      <c r="F27" s="166" t="inlineStr">
+        <is>
+          <t>7 Dec 2026</t>
+        </is>
+      </c>
+      <c r="G27" s="232" t="inlineStr">
+        <is>
+          <t>ITA-AITES Young Members (ITAym)</t>
+        </is>
+      </c>
+      <c r="H27" s="232" t="n"/>
+      <c r="I27" s="239" t="inlineStr">
+        <is>
+          <t>https://about.ita-aites.org/future-events/2658/world-tunnel-day-2026-itaym?tmpl=component</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="30" customHeight="1">
+      <c r="A28" s="236" t="n">
+        <v>46364</v>
+      </c>
+      <c r="B28" s="240" t="inlineStr">
+        <is>
+          <t>ISSMGE</t>
+        </is>
+      </c>
+      <c r="C28" s="231" t="inlineStr">
+        <is>
+          <t>Colloque National sur la Géotechnique (National Colloquium on Geotechnics)</t>
+        </is>
+      </c>
+      <c r="D28" s="238" t="inlineStr">
+        <is>
+          <t>ISSMGE-supported</t>
+        </is>
+      </c>
+      <c r="E28" s="166" t="inlineStr">
+        <is>
+          <t>Marrakech, Morocco</t>
+        </is>
+      </c>
+      <c r="F28" s="166" t="inlineStr">
+        <is>
+          <t>8 Dec 2026</t>
+        </is>
+      </c>
+      <c r="G28" s="232" t="n"/>
+      <c r="H28" s="232" t="n"/>
+      <c r="I28" s="239" t="inlineStr">
+        <is>
+          <t>https://www.issmge.org/events/colloque-national-sur-la-gotechnique</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="17.5" customHeight="1">
+      <c r="A29" s="236" t="n">
+        <v>46366</v>
+      </c>
+      <c r="B29" s="240" t="n"/>
+      <c r="C29" s="231" t="inlineStr">
+        <is>
+          <t>Nepal Tunnelling Conference 2026</t>
+        </is>
+      </c>
+      <c r="D29" s="241" t="inlineStr">
+        <is>
+          <t>Other conference</t>
+        </is>
+      </c>
+      <c r="E29" s="166" t="inlineStr">
+        <is>
+          <t>Nepal</t>
+        </is>
+      </c>
+      <c r="F29" s="166" t="inlineStr">
+        <is>
+          <t>10 Dec 2026</t>
+        </is>
+      </c>
+      <c r="G29" s="232" t="n"/>
+      <c r="H29" s="232" t="n"/>
+      <c r="I29" s="239" t="inlineStr">
+        <is>
+          <t>https://about.ita-aites.org/future-events/2666/nepal-tunnelling-conference-2026?tmpl=component</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="30" customHeight="1">
+      <c r="A30" s="236" t="n">
+        <v>46406</v>
+      </c>
+      <c r="B30" s="240" t="n"/>
+      <c r="C30" s="231" t="inlineStr">
+        <is>
+          <t>Underground Construction Association (UCA) 2027 George A. Fox Conference</t>
+        </is>
+      </c>
+      <c r="D30" s="241" t="inlineStr">
+        <is>
+          <t>Other conference</t>
+        </is>
+      </c>
+      <c r="E30" s="166" t="inlineStr">
+        <is>
+          <t>New York, United States</t>
+        </is>
+      </c>
+      <c r="F30" s="166" t="inlineStr">
+        <is>
+          <t>19 Jan 2027</t>
+        </is>
+      </c>
+      <c r="G30" s="232" t="inlineStr">
+        <is>
+          <t>Underground Construction Association (UCA)</t>
+        </is>
+      </c>
+      <c r="H30" s="232" t="n"/>
+      <c r="I30" s="239" t="inlineStr">
+        <is>
+          <t>https://about.ita-aites.org/future-events/2656/underground-construction-association-uca-2027-george-a-fox-conference?tmpl=component</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="42.5" customHeight="1">
+      <c r="A31" s="236" t="n">
+        <v>46428</v>
+      </c>
+      <c r="B31" s="240" t="inlineStr">
+        <is>
+          <t>ISSMGE</t>
+        </is>
+      </c>
+      <c r="C31" s="231" t="inlineStr">
+        <is>
+          <t>The III International Research and Practical Conference "Geotechnical Engineering in Cold Regions. The Basis of Infrastructure Safety in Global Changes"</t>
+        </is>
+      </c>
+      <c r="D31" s="238" t="inlineStr">
+        <is>
+          <t>ISSMGE-supported</t>
+        </is>
+      </c>
+      <c r="E31" s="166" t="inlineStr">
+        <is>
+          <t>Moscow, Russia</t>
+        </is>
+      </c>
+      <c r="F31" s="166" t="inlineStr">
+        <is>
+          <t>10–12 Feb 2027</t>
+        </is>
+      </c>
+      <c r="G31" s="232" t="n"/>
+      <c r="H31" s="232" t="n"/>
+      <c r="I31" s="239" t="inlineStr">
+        <is>
+          <t>https://www.issmge.org/events/the-iii-international-research-and-practical-conference-on-geotechnical-engineering-in-cold-regions-the-basis-of-infrastructure-safety-in-global-changes</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="17.5" customHeight="1">
+      <c r="A32" s="236" t="n">
         <v>46447</v>
       </c>
-      <c r="B10" s="238" t="n"/>
-      <c r="C10" s="231" t="inlineStr">
+      <c r="B32" s="240" t="n"/>
+      <c r="C32" s="231" t="inlineStr">
         <is>
           <t>Geo-Congress 2027, part of ASCE2027</t>
         </is>
       </c>
-      <c r="D10" s="239" t="inlineStr">
+      <c r="D32" s="241" t="inlineStr">
         <is>
           <t>Other conference</t>
         </is>
       </c>
-      <c r="E10" s="166" t="inlineStr">
+      <c r="E32" s="166" t="inlineStr">
         <is>
           <t>Philadelphia, United States</t>
         </is>
       </c>
-      <c r="F10" s="166" t="inlineStr">
+      <c r="F32" s="166" t="inlineStr">
         <is>
           <t>1–5 Mar 2027</t>
         </is>
       </c>
-      <c r="G10" s="232" t="inlineStr">
+      <c r="G32" s="232" t="inlineStr">
         <is>
           <t>ASCE Geo-Institute</t>
         </is>
       </c>
-      <c r="H10" s="232" t="inlineStr">
+      <c r="H32" s="232" t="inlineStr">
         <is>
           <t>Abstracts: 4 Mar 2026 (passed)</t>
         </is>
       </c>
-      <c r="I10" s="240" t="inlineStr">
+      <c r="I32" s="239" t="inlineStr">
         <is>
           <t>https://geoinstitute.org/news/call-abstract-geo-congress-2027-part-asce2027</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="30" customHeight="1">
-      <c r="A11" s="237" t="n">
+    <row r="33" ht="42.5" customHeight="1">
+      <c r="A33" s="236" t="n">
+        <v>46463</v>
+      </c>
+      <c r="B33" s="240" t="n"/>
+      <c r="C33" s="231" t="inlineStr">
+        <is>
+          <t>7th International Conference on Grouting and Deep Mixing (Grout27)</t>
+        </is>
+      </c>
+      <c r="D33" s="241" t="inlineStr">
+        <is>
+          <t>Other conference</t>
+        </is>
+      </c>
+      <c r="E33" s="166" t="n"/>
+      <c r="F33" s="166" t="inlineStr">
+        <is>
+          <t>17–19 Mar 2027</t>
+        </is>
+      </c>
+      <c r="G33" s="232" t="inlineStr">
+        <is>
+          <t>Deep Foundations Institute (DFI) with the International Conference on Grouting (ICOG)</t>
+        </is>
+      </c>
+      <c r="H33" s="232" t="n"/>
+      <c r="I33" s="239" t="inlineStr">
+        <is>
+          <t>https://dfi-events.org/grout27/</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="30" customHeight="1">
+      <c r="A34" s="236" t="n">
+        <v>46463</v>
+      </c>
+      <c r="B34" s="240" t="inlineStr">
+        <is>
+          <t>ISSMGE</t>
+        </is>
+      </c>
+      <c r="C34" s="231" t="inlineStr">
+        <is>
+          <t>GeoMandu 2027, 11th AYGEC and 1st SACG: Mountain Geotechnics for Infrastructure Development</t>
+        </is>
+      </c>
+      <c r="D34" s="238" t="inlineStr">
+        <is>
+          <t>ISSMGE-supported</t>
+        </is>
+      </c>
+      <c r="E34" s="166" t="inlineStr">
+        <is>
+          <t>Kathmandu, Nepal</t>
+        </is>
+      </c>
+      <c r="F34" s="166" t="inlineStr">
+        <is>
+          <t>17 Mar 2027</t>
+        </is>
+      </c>
+      <c r="G34" s="232" t="n"/>
+      <c r="H34" s="232" t="n"/>
+      <c r="I34" s="239" t="inlineStr">
+        <is>
+          <t>https://www.issmge.org/events/geomandu-2027-11th-aygec-and-1st-sacg-mountain-geotechnics-for-infrastructure-development</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="30" customHeight="1">
+      <c r="A35" s="236" t="n">
         <v>46489</v>
       </c>
-      <c r="B11" s="238" t="inlineStr">
+      <c r="B35" s="240" t="inlineStr">
         <is>
           <t>ISSMGE</t>
         </is>
       </c>
-      <c r="C11" s="231" t="inlineStr">
+      <c r="C35" s="231" t="inlineStr">
         <is>
           <t>2nd International Symposium on Ground Improvement (IS-GI 2027)</t>
         </is>
       </c>
-      <c r="D11" s="241" t="inlineStr">
+      <c r="D35" s="238" t="inlineStr">
         <is>
           <t>ISSMGE-supported</t>
         </is>
       </c>
-      <c r="E11" s="166" t="inlineStr">
+      <c r="E35" s="166" t="inlineStr">
         <is>
           <t>Lyon, France</t>
         </is>
       </c>
-      <c r="F11" s="166" t="inlineStr">
+      <c r="F35" s="166" t="inlineStr">
         <is>
           <t>12–14 Apr 2027</t>
         </is>
       </c>
-      <c r="G11" s="232" t="inlineStr">
+      <c r="G35" s="232" t="inlineStr">
         <is>
           <t>ISSMGE TC211</t>
         </is>
       </c>
-      <c r="H11" s="232" t="inlineStr">
+      <c r="H35" s="232" t="inlineStr">
         <is>
           <t>Abstracts: 15 May 2026 (passed)</t>
         </is>
       </c>
-      <c r="I11" s="240" t="inlineStr">
+      <c r="I35" s="239" t="inlineStr">
         <is>
           <t>https://www.issmge.org/news/2nd-is-gi-2027-lyon-call-for-abstracts</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="30" customHeight="1">
-      <c r="A12" s="237" t="n">
+    <row r="36" ht="17.5" customHeight="1">
+      <c r="A36" s="236" t="n">
+        <v>46497</v>
+      </c>
+      <c r="B36" s="240" t="n"/>
+      <c r="C36" s="231" t="inlineStr">
+        <is>
+          <t>Young Professionals Think Deep Programme – Antwerp</t>
+        </is>
+      </c>
+      <c r="D36" s="242" t="inlineStr">
+        <is>
+          <t>Course / webinar</t>
+        </is>
+      </c>
+      <c r="E36" s="166" t="inlineStr">
+        <is>
+          <t>Antwerp, Belgium</t>
+        </is>
+      </c>
+      <c r="F36" s="166" t="inlineStr">
+        <is>
+          <t>20 Apr 2027</t>
+        </is>
+      </c>
+      <c r="G36" s="232" t="inlineStr">
+        <is>
+          <t>ITA-AITES</t>
+        </is>
+      </c>
+      <c r="H36" s="232" t="n"/>
+      <c r="I36" s="239" t="inlineStr">
+        <is>
+          <t>https://about.ita-aites.org/future-events/2665/young-professionals-think-deep-programme-antwerp?tmpl=component</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="30" customHeight="1">
+      <c r="A37" s="236" t="n">
         <v>46500</v>
       </c>
-      <c r="B12" s="238" t="n"/>
-      <c r="C12" s="231" t="inlineStr">
+      <c r="B37" s="240" t="n"/>
+      <c r="C37" s="231" t="inlineStr">
         <is>
           <t>ITA-AITES World Tunnel Congress 2027 (WTC 2027)</t>
         </is>
       </c>
-      <c r="D12" s="239" t="inlineStr">
+      <c r="D37" s="241" t="inlineStr">
         <is>
           <t>Other conference</t>
         </is>
       </c>
-      <c r="E12" s="166" t="inlineStr">
+      <c r="E37" s="166" t="inlineStr">
         <is>
           <t>Antwerp, Belgium</t>
         </is>
       </c>
-      <c r="F12" s="166" t="inlineStr">
+      <c r="F37" s="166" t="inlineStr">
         <is>
           <t>23–29 Apr 2027</t>
         </is>
       </c>
-      <c r="G12" s="232" t="inlineStr">
+      <c r="G37" s="232" t="inlineStr">
         <is>
           <t>ITA-AITES with the Belgian Tunnel Association</t>
         </is>
       </c>
-      <c r="H12" s="232" t="inlineStr">
+      <c r="H37" s="232" t="inlineStr">
         <is>
           <t>Abstracts: 10 Jun 2026 (passed)</t>
         </is>
       </c>
-      <c r="I12" s="240" t="inlineStr">
+      <c r="I37" s="239" t="inlineStr">
         <is>
           <t>https://about.ita-aites.org/future-events/2350/world-tunnel-congress-wtc-2027</t>
         </is>
       </c>
     </row>
-    <row r="13" ht="30" customHeight="1">
-      <c r="A13" s="237" t="n">
+    <row r="38" ht="30" customHeight="1">
+      <c r="A38" s="236" t="n">
+        <v>46518</v>
+      </c>
+      <c r="B38" s="240" t="n"/>
+      <c r="C38" s="231" t="inlineStr">
+        <is>
+          <t>International Foundations Congress and Equipment Expo 2027 (IFCEE 2027)</t>
+        </is>
+      </c>
+      <c r="D38" s="241" t="inlineStr">
+        <is>
+          <t>Other conference</t>
+        </is>
+      </c>
+      <c r="E38" s="166" t="n"/>
+      <c r="F38" s="166" t="inlineStr">
+        <is>
+          <t>11–14 May 2027</t>
+        </is>
+      </c>
+      <c r="G38" s="232" t="inlineStr">
+        <is>
+          <t>Deep Foundations Institute (DFI)</t>
+        </is>
+      </c>
+      <c r="H38" s="232" t="n"/>
+      <c r="I38" s="239" t="inlineStr">
+        <is>
+          <t>https://www.ifcee.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="30" customHeight="1">
+      <c r="A39" s="236" t="n">
+        <v>46518</v>
+      </c>
+      <c r="B39" s="240" t="n"/>
+      <c r="C39" s="231" t="inlineStr">
+        <is>
+          <t>SDC2027 – 5th International Conference on Shaft Design &amp; Construction</t>
+        </is>
+      </c>
+      <c r="D39" s="241" t="inlineStr">
+        <is>
+          <t>Other conference</t>
+        </is>
+      </c>
+      <c r="E39" s="166" t="n"/>
+      <c r="F39" s="166" t="inlineStr">
+        <is>
+          <t>11 May 2027</t>
+        </is>
+      </c>
+      <c r="G39" s="232" t="n"/>
+      <c r="H39" s="232" t="n"/>
+      <c r="I39" s="239" t="inlineStr">
+        <is>
+          <t>https://about.ita-aites.org/future-events/2549/sdc2027-5th-international-conference-on-shaft-design-construction?tmpl=component</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="30" customHeight="1">
+      <c r="A40" s="236" t="n">
+        <v>46519</v>
+      </c>
+      <c r="B40" s="240" t="n"/>
+      <c r="C40" s="231" t="inlineStr">
+        <is>
+          <t>CPT'27: International Symposium on Cone Penetration Testing</t>
+        </is>
+      </c>
+      <c r="D40" s="241" t="inlineStr">
+        <is>
+          <t>Other conference</t>
+        </is>
+      </c>
+      <c r="E40" s="166" t="inlineStr">
+        <is>
+          <t>Vancouver, Canada</t>
+        </is>
+      </c>
+      <c r="F40" s="166" t="inlineStr">
+        <is>
+          <t>12 May 2027</t>
+        </is>
+      </c>
+      <c r="G40" s="232" t="n"/>
+      <c r="H40" s="232" t="n"/>
+      <c r="I40" s="239" t="inlineStr">
+        <is>
+          <t>https://www.issmge.org/events/cpt27-international-symposium-on-cone-penetration-testing</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="30" customHeight="1">
+      <c r="A41" s="236" t="n">
+        <v>46540</v>
+      </c>
+      <c r="B41" s="240" t="n"/>
+      <c r="C41" s="231" t="inlineStr">
+        <is>
+          <t>The 4th International Conference on Press-in Engineering 2027 (ICPE2027)</t>
+        </is>
+      </c>
+      <c r="D41" s="241" t="inlineStr">
+        <is>
+          <t>Other conference</t>
+        </is>
+      </c>
+      <c r="E41" s="166" t="inlineStr">
+        <is>
+          <t>Papendrecht, Netherlands</t>
+        </is>
+      </c>
+      <c r="F41" s="166" t="inlineStr">
+        <is>
+          <t>2 Jun 2027</t>
+        </is>
+      </c>
+      <c r="G41" s="232" t="n"/>
+      <c r="H41" s="232" t="n"/>
+      <c r="I41" s="239" t="inlineStr">
+        <is>
+          <t>https://www.issmge.org/events/the-4th-international-conference-on-press-in-engineering-2027-icpe2027</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="30" customHeight="1">
+      <c r="A42" s="236" t="n">
+        <v>46547</v>
+      </c>
+      <c r="B42" s="240" t="inlineStr">
+        <is>
+          <t>ISSMGE</t>
+        </is>
+      </c>
+      <c r="C42" s="231" t="inlineStr">
+        <is>
+          <t>XVIII Danube-European Conference on Geotechnical Engineering</t>
+        </is>
+      </c>
+      <c r="D42" s="243" t="inlineStr">
+        <is>
+          <t>ISSMGE conference</t>
+        </is>
+      </c>
+      <c r="E42" s="166" t="inlineStr">
+        <is>
+          <t>Budapest, Hungary</t>
+        </is>
+      </c>
+      <c r="F42" s="166" t="inlineStr">
+        <is>
+          <t>9 Jun 2027</t>
+        </is>
+      </c>
+      <c r="G42" s="232" t="n"/>
+      <c r="H42" s="232" t="n"/>
+      <c r="I42" s="239" t="inlineStr">
+        <is>
+          <t>https://www.issmge.org/events/xviii-danube-european-conference-on-geotechnical-engineering</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="30" customHeight="1">
+      <c r="A43" s="236" t="n">
+        <v>46552</v>
+      </c>
+      <c r="B43" s="240" t="n"/>
+      <c r="C43" s="231" t="inlineStr">
+        <is>
+          <t>9th International Conference on Debris Flow Hazard Mitigation (DFHM9)</t>
+        </is>
+      </c>
+      <c r="D43" s="241" t="inlineStr">
+        <is>
+          <t>Other conference</t>
+        </is>
+      </c>
+      <c r="E43" s="166" t="inlineStr">
+        <is>
+          <t>Daejeon, South Korea</t>
+        </is>
+      </c>
+      <c r="F43" s="166" t="inlineStr">
+        <is>
+          <t>14 Jun 2027</t>
+        </is>
+      </c>
+      <c r="G43" s="232" t="n"/>
+      <c r="H43" s="232" t="n"/>
+      <c r="I43" s="239" t="inlineStr">
+        <is>
+          <t>https://www.issmge.org/events/9th-international-conference-on-debris-flow-hazard-mitigation-dfhm9</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="30" customHeight="1">
+      <c r="A44" s="236" t="n">
         <v>46566</v>
       </c>
-      <c r="B13" s="238" t="inlineStr">
+      <c r="B44" s="240" t="inlineStr">
         <is>
           <t>ISSMGE</t>
         </is>
       </c>
-      <c r="C13" s="231" t="inlineStr">
+      <c r="C44" s="231" t="inlineStr">
         <is>
           <t>International Conference on Sustainability in Geotechnical Engineering (ICSGE 2027)</t>
         </is>
       </c>
-      <c r="D13" s="241" t="inlineStr">
+      <c r="D44" s="238" t="inlineStr">
         <is>
           <t>ISSMGE-supported</t>
         </is>
       </c>
-      <c r="E13" s="166" t="inlineStr">
+      <c r="E44" s="166" t="inlineStr">
         <is>
           <t>Lisbon, Portugal</t>
         </is>
       </c>
-      <c r="F13" s="166" t="inlineStr">
+      <c r="F44" s="166" t="inlineStr">
         <is>
           <t>28 Jun – 1 Jul 2027</t>
         </is>
       </c>
-      <c r="G13" s="232" t="inlineStr">
+      <c r="G44" s="232" t="inlineStr">
         <is>
           <t>ISSMGE TC307 and LNEC</t>
         </is>
       </c>
-      <c r="H13" s="232" t="inlineStr">
+      <c r="H44" s="232" t="inlineStr">
         <is>
           <t>Abstracts: 15 Jul 2026 (passed)</t>
         </is>
       </c>
-      <c r="I13" s="240" t="inlineStr">
+      <c r="I44" s="239" t="inlineStr">
         <is>
           <t>https://www.issmge.org/news/tc223-june-news-update</t>
         </is>
       </c>
     </row>
-    <row r="14" ht="30" customHeight="1">
-      <c r="A14" s="237" t="n">
+    <row r="45" ht="30" customHeight="1">
+      <c r="A45" s="236" t="n">
+        <v>46609</v>
+      </c>
+      <c r="B45" s="240" t="n"/>
+      <c r="C45" s="231" t="inlineStr">
+        <is>
+          <t>S3 2027</t>
+        </is>
+      </c>
+      <c r="D45" s="241" t="inlineStr">
+        <is>
+          <t>Other conference</t>
+        </is>
+      </c>
+      <c r="E45" s="166" t="n"/>
+      <c r="F45" s="166" t="inlineStr">
+        <is>
+          <t>10–12 Aug 2027</t>
+        </is>
+      </c>
+      <c r="G45" s="232" t="inlineStr">
+        <is>
+          <t>Deep Foundations Institute (DFI)</t>
+        </is>
+      </c>
+      <c r="H45" s="232" t="n"/>
+      <c r="I45" s="239" t="inlineStr">
+        <is>
+          <t>https://dfi-events.org/s3-27/</t>
+        </is>
+      </c>
+    </row>
+    <row r="46" ht="30" customHeight="1">
+      <c r="A46" s="236" t="n">
+        <v>46631</v>
+      </c>
+      <c r="B46" s="240" t="inlineStr">
+        <is>
+          <t>ISSMGE</t>
+        </is>
+      </c>
+      <c r="C46" s="231" t="inlineStr">
+        <is>
+          <t>30th European Young Geotechnical Engineers Conference (EYGEC 2027)</t>
+        </is>
+      </c>
+      <c r="D46" s="238" t="inlineStr">
+        <is>
+          <t>ISSMGE-supported</t>
+        </is>
+      </c>
+      <c r="E46" s="166" t="inlineStr">
+        <is>
+          <t>Sofia, Bulgaria</t>
+        </is>
+      </c>
+      <c r="F46" s="166" t="inlineStr">
+        <is>
+          <t>1 Sep 2027</t>
+        </is>
+      </c>
+      <c r="G46" s="232" t="n"/>
+      <c r="H46" s="232" t="n"/>
+      <c r="I46" s="239" t="inlineStr">
+        <is>
+          <t>https://www.issmge.org/events/30th-european-young-geotechnical-engineers-conference-eygec-2027</t>
+        </is>
+      </c>
+    </row>
+    <row r="47" ht="30" customHeight="1">
+      <c r="A47" s="236" t="n">
         <v>46644</v>
       </c>
-      <c r="B14" s="238" t="inlineStr">
+      <c r="B47" s="240" t="inlineStr">
         <is>
           <t>ISSMGE</t>
         </is>
       </c>
-      <c r="C14" s="231" t="inlineStr">
+      <c r="C47" s="231" t="inlineStr">
         <is>
           <t>9th International Symposium on Deformation Characteristics of Geomaterials (IS-Ankara 2027)</t>
         </is>
       </c>
-      <c r="D14" s="241" t="inlineStr">
+      <c r="D47" s="238" t="inlineStr">
         <is>
           <t>ISSMGE-supported</t>
         </is>
       </c>
-      <c r="E14" s="166" t="inlineStr">
+      <c r="E47" s="166" t="inlineStr">
         <is>
           <t>Ankara, Türkiye</t>
         </is>
       </c>
-      <c r="F14" s="166" t="inlineStr">
+      <c r="F47" s="166" t="inlineStr">
         <is>
           <t>14–17 Sep 2027</t>
         </is>
       </c>
-      <c r="G14" s="232" t="inlineStr">
+      <c r="G47" s="232" t="inlineStr">
         <is>
           <t>ISSMGE TC101, Middle East Technical University (METU)</t>
         </is>
       </c>
-      <c r="H14" s="232" t="inlineStr">
+      <c r="H47" s="232" t="inlineStr">
         <is>
           <t>Abstracts: 21 Sep 2026 (passed)</t>
         </is>
       </c>
-      <c r="I14" s="240" t="inlineStr">
+      <c r="I47" s="239" t="inlineStr">
         <is>
           <t>https://www.issmge.org/news/tc223-june-news-update</t>
         </is>
       </c>
     </row>
-    <row r="15" ht="30" customHeight="1">
-      <c r="A15" s="237" t="n">
+    <row r="48" ht="30" customHeight="1">
+      <c r="A48" s="236" t="n">
+        <v>46644</v>
+      </c>
+      <c r="B48" s="240" t="n"/>
+      <c r="C48" s="231" t="inlineStr">
+        <is>
+          <t>Energy Geotechnics</t>
+        </is>
+      </c>
+      <c r="D48" s="241" t="inlineStr">
+        <is>
+          <t>Other conference</t>
+        </is>
+      </c>
+      <c r="E48" s="166" t="inlineStr">
+        <is>
+          <t>Leeds, United Kingdom</t>
+        </is>
+      </c>
+      <c r="F48" s="166" t="inlineStr">
+        <is>
+          <t>14 Sep 2027</t>
+        </is>
+      </c>
+      <c r="G48" s="232" t="inlineStr">
+        <is>
+          <t>British Geotechnical Association (BGA)</t>
+        </is>
+      </c>
+      <c r="H48" s="232" t="n"/>
+      <c r="I48" s="239" t="inlineStr">
+        <is>
+          <t>https://www.britishgeotech.org/event/energy-geotechnics/</t>
+        </is>
+      </c>
+    </row>
+    <row r="49" ht="67.5" customHeight="1">
+      <c r="A49" s="236" t="n">
+        <v>46651</v>
+      </c>
+      <c r="B49" s="240" t="inlineStr">
+        <is>
+          <t>ISSMGE</t>
+        </is>
+      </c>
+      <c r="C49" s="231" t="inlineStr">
+        <is>
+          <t>11th European Conference on Numerical Methods in Geotechnical Engineering (NUMGE 2027)</t>
+        </is>
+      </c>
+      <c r="D49" s="238" t="inlineStr">
+        <is>
+          <t>ISSMGE-supported</t>
+        </is>
+      </c>
+      <c r="E49" s="166" t="inlineStr">
+        <is>
+          <t>Graz, Austria</t>
+        </is>
+      </c>
+      <c r="F49" s="166" t="inlineStr">
+        <is>
+          <t>21–24 Sep 2027</t>
+        </is>
+      </c>
+      <c r="G49" s="232" t="inlineStr">
+        <is>
+          <t>Institute of Soil Mechanics, Foundation Engineering and Computational Geotechnics, Graz University of Technology</t>
+        </is>
+      </c>
+      <c r="H49" s="232" t="inlineStr">
+        <is>
+          <t>Sessions and workshops (closed): 14 Aug 2026 (passed)
+Abstracts (closed): 1 Sep 2026 (passed)
+Notification of accepted abstracts: 11 Dec 2026
+Manuscripts: 19 Mar 2027
+Final papers: 30 May 2027</t>
+        </is>
+      </c>
+      <c r="I49" s="239" t="inlineStr">
+        <is>
+          <t>https://www.issmge.org/events/numge2027</t>
+        </is>
+      </c>
+    </row>
+    <row r="50" ht="30" customHeight="1">
+      <c r="A50" s="236" t="n">
+        <v>46692</v>
+      </c>
+      <c r="B50" s="240" t="n"/>
+      <c r="C50" s="231" t="inlineStr">
+        <is>
+          <t>DFI's 52nd Annual Conference on Deep Foundations (DFI52)</t>
+        </is>
+      </c>
+      <c r="D50" s="241" t="inlineStr">
+        <is>
+          <t>Other conference</t>
+        </is>
+      </c>
+      <c r="E50" s="166" t="n"/>
+      <c r="F50" s="166" t="inlineStr">
+        <is>
+          <t>1–4 Nov 2027</t>
+        </is>
+      </c>
+      <c r="G50" s="232" t="inlineStr">
+        <is>
+          <t>Deep Foundations Institute (DFI)</t>
+        </is>
+      </c>
+      <c r="H50" s="232" t="n"/>
+      <c r="I50" s="239" t="inlineStr">
+        <is>
+          <t>https://dfi-events.org/dfi52/</t>
+        </is>
+      </c>
+    </row>
+    <row r="51" ht="30" customHeight="1">
+      <c r="A51" s="236" t="n">
+        <v>46692</v>
+      </c>
+      <c r="B51" s="240" t="inlineStr">
+        <is>
+          <t>ISSMGE</t>
+        </is>
+      </c>
+      <c r="C51" s="231" t="inlineStr">
+        <is>
+          <t>The 10th International Congress on Environmental Geotechnics (10ICEG)</t>
+        </is>
+      </c>
+      <c r="D51" s="238" t="inlineStr">
+        <is>
+          <t>ISSMGE-supported</t>
+        </is>
+      </c>
+      <c r="E51" s="166" t="inlineStr">
+        <is>
+          <t>Kyoto, Japan</t>
+        </is>
+      </c>
+      <c r="F51" s="166" t="inlineStr">
+        <is>
+          <t>1 Nov 2027</t>
+        </is>
+      </c>
+      <c r="G51" s="232" t="n"/>
+      <c r="H51" s="232" t="n"/>
+      <c r="I51" s="239" t="inlineStr">
+        <is>
+          <t>https://www.issmge.org/events/10iceg</t>
+        </is>
+      </c>
+    </row>
+    <row r="52" ht="30" customHeight="1">
+      <c r="A52" s="236" t="n">
         <v>46700</v>
       </c>
-      <c r="B15" s="238" t="inlineStr">
+      <c r="B52" s="240" t="inlineStr">
         <is>
           <t>ISSMGE</t>
         </is>
       </c>
-      <c r="C15" s="231" t="inlineStr">
+      <c r="C52" s="231" t="inlineStr">
         <is>
           <t>18th Asian Regional Conference on Soil Mechanics and Geotechnical Engineering (18ARC)</t>
         </is>
       </c>
-      <c r="D15" s="242" t="inlineStr">
+      <c r="D52" s="243" t="inlineStr">
         <is>
           <t>ISSMGE conference</t>
         </is>
       </c>
-      <c r="E15" s="166" t="inlineStr">
+      <c r="E52" s="166" t="inlineStr">
         <is>
           <t>Bangkok, Thailand</t>
         </is>
       </c>
-      <c r="F15" s="166" t="inlineStr">
+      <c r="F52" s="166" t="inlineStr">
         <is>
           <t>9–13 Nov 2027</t>
         </is>
       </c>
-      <c r="G15" s="232" t="inlineStr">
+      <c r="G52" s="232" t="inlineStr">
         <is>
           <t>Thai Geotechnical Society, under the auspices of ISSMGE</t>
         </is>
       </c>
-      <c r="H15" s="232" t="n"/>
-      <c r="I15" s="240" t="inlineStr">
+      <c r="H52" s="232" t="n"/>
+      <c r="I52" s="239" t="inlineStr">
         <is>
           <t>https://www.issmge.org/events/18arc</t>
+        </is>
+      </c>
+    </row>
+    <row r="53" ht="30" customHeight="1">
+      <c r="A53" s="236" t="n">
+        <v>46716</v>
+      </c>
+      <c r="B53" s="240" t="n"/>
+      <c r="C53" s="231" t="inlineStr">
+        <is>
+          <t>The Fourth Vietnam Symposium on Advances in Offshore Engineering (VSOE 2027)</t>
+        </is>
+      </c>
+      <c r="D53" s="241" t="inlineStr">
+        <is>
+          <t>Other conference</t>
+        </is>
+      </c>
+      <c r="E53" s="166" t="inlineStr">
+        <is>
+          <t>Ho Chi Minh City, Vietnam</t>
+        </is>
+      </c>
+      <c r="F53" s="166" t="inlineStr">
+        <is>
+          <t>25 Nov 2027</t>
+        </is>
+      </c>
+      <c r="G53" s="232" t="n"/>
+      <c r="H53" s="232" t="n"/>
+      <c r="I53" s="239" t="inlineStr">
+        <is>
+          <t>https://www.issmge.org/events/the-fourth-vietnam-symposium-on-advances-in-offshore-engineering-vsoe-2027</t>
+        </is>
+      </c>
+    </row>
+    <row r="54" ht="17.5" customHeight="1">
+      <c r="A54" s="236" t="n">
+        <v>46722</v>
+      </c>
+      <c r="B54" s="240" t="inlineStr">
+        <is>
+          <t>ISSMGE</t>
+        </is>
+      </c>
+      <c r="C54" s="231" t="inlineStr">
+        <is>
+          <t>XIII Chilean Geotechnical Conference</t>
+        </is>
+      </c>
+      <c r="D54" s="238" t="inlineStr">
+        <is>
+          <t>ISSMGE-supported</t>
+        </is>
+      </c>
+      <c r="E54" s="166" t="inlineStr">
+        <is>
+          <t>Punta Arenas, Chile</t>
+        </is>
+      </c>
+      <c r="F54" s="166" t="inlineStr">
+        <is>
+          <t>1 Dec 2027</t>
+        </is>
+      </c>
+      <c r="G54" s="232" t="n"/>
+      <c r="H54" s="232" t="n"/>
+      <c r="I54" s="239" t="inlineStr">
+        <is>
+          <t>https://www.issmge.org/events/xiii-chilean-geotechnical-conference</t>
+        </is>
+      </c>
+    </row>
+    <row r="55" ht="30" customHeight="1">
+      <c r="A55" s="236" t="n">
+        <v>46924</v>
+      </c>
+      <c r="B55" s="240" t="inlineStr">
+        <is>
+          <t>ISSMGE</t>
+        </is>
+      </c>
+      <c r="C55" s="231" t="inlineStr">
+        <is>
+          <t>6th European Conference on Physical Modelling in Geotechnics (ECPMG 2028)</t>
+        </is>
+      </c>
+      <c r="D55" s="238" t="inlineStr">
+        <is>
+          <t>ISSMGE-supported</t>
+        </is>
+      </c>
+      <c r="E55" s="166" t="inlineStr">
+        <is>
+          <t>Southampton, United Kingdom</t>
+        </is>
+      </c>
+      <c r="F55" s="166" t="inlineStr">
+        <is>
+          <t>20 Jun 2028</t>
+        </is>
+      </c>
+      <c r="G55" s="232" t="n"/>
+      <c r="H55" s="232" t="n"/>
+      <c r="I55" s="239" t="inlineStr">
+        <is>
+          <t>https://www.issmge.org/events/ecpmg-2028</t>
+        </is>
+      </c>
+    </row>
+    <row r="56" ht="42.5" customHeight="1">
+      <c r="A56" s="236" t="n">
+        <v>46985</v>
+      </c>
+      <c r="B56" s="240" t="inlineStr">
+        <is>
+          <t>ISSMGE</t>
+        </is>
+      </c>
+      <c r="C56" s="231" t="inlineStr">
+        <is>
+          <t>19th European Conference on Soil Mechanics and Geotechnical Engineering (ECSMGE 2028)</t>
+        </is>
+      </c>
+      <c r="D56" s="243" t="inlineStr">
+        <is>
+          <t>ISSMGE conference</t>
+        </is>
+      </c>
+      <c r="E56" s="166" t="inlineStr">
+        <is>
+          <t>Istanbul, Türkiye</t>
+        </is>
+      </c>
+      <c r="F56" s="166" t="inlineStr">
+        <is>
+          <t>20–25 Aug 2028</t>
+        </is>
+      </c>
+      <c r="G56" s="232" t="inlineStr">
+        <is>
+          <t>Turkish Society for Soil Mechanics and Geotechnical Engineering</t>
+        </is>
+      </c>
+      <c r="H56" s="232" t="n"/>
+      <c r="I56" s="239" t="inlineStr">
+        <is>
+          <t>https://www.ecsmge-2028.com/</t>
         </is>
       </c>
     </row>
@@ -22731,12 +24261,54 @@
   <hyperlinks>
     <hyperlink ref="D1" location="'Dashboard'!A1" display="← Dashboard"/>
     <hyperlink ref="E1" location="'Start here'!A1" display="↑ Start here"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I10" r:id="rId1"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I11" r:id="rId2"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I12" r:id="rId3"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I13" r:id="rId4"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I14" r:id="rId5"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I15" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I6" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I7" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I8" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I12" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I13" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I14" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I15" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I16" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I17" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I18" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I19" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I20" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I21" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I22" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I23" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I24" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I25" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I26" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I27" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I28" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I29" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I30" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I31" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I32" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I33" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I34" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I35" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I36" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I37" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I38" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I39" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I40" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I41" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I42" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I43" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I44" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I45" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I46" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I47" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I48" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I49" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I50" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I51" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I52" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I53" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I54" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I55" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I56" r:id="rId48"/>
   </hyperlinks>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.55" header="0.25" footer="0.25"/>
@@ -22850,25 +24422,25 @@
           <t>Vietnam.vn</t>
         </is>
       </c>
-      <c r="B4" s="243" t="n">
+      <c r="B4" s="244" t="n">
         <v>25</v>
       </c>
-      <c r="C4" s="244">
+      <c r="C4" s="245">
         <f>SUMPRODUCT(Stories!$W$4:$W$103,--(Stories!$J$4:$J$103=$A4))</f>
         <v/>
       </c>
-      <c r="D4" s="245" t="n">
+      <c r="D4" s="246" t="n">
         <v>3.8</v>
       </c>
-      <c r="E4" s="243" t="n">
+      <c r="E4" s="244" t="n">
         <v>19</v>
       </c>
-      <c r="F4" s="246" t="inlineStr">
+      <c r="F4" s="247" t="inlineStr">
         <is>
           <t>Hazards &amp; Resilience</t>
         </is>
       </c>
-      <c r="G4" s="243" t="n">
+      <c r="G4" s="244" t="n">
         <v>6</v>
       </c>
       <c r="H4" s="171" t="inlineStr">
@@ -22876,7 +24448,7 @@
           <t>Indonesia, Vietnam, South Korea, Egypt, France, Russia, Colombia, United Kingdom, Italy, China, Spain, Brazil</t>
         </is>
       </c>
-      <c r="I4" s="247" t="n">
+      <c r="I4" s="248" t="n">
         <v>46320</v>
       </c>
     </row>
@@ -22886,25 +24458,25 @@
           <t>Cooperativa</t>
         </is>
       </c>
-      <c r="B5" s="243" t="n">
+      <c r="B5" s="244" t="n">
         <v>2</v>
       </c>
-      <c r="C5" s="244">
+      <c r="C5" s="245">
         <f>SUMPRODUCT(Stories!$W$4:$W$103,--(Stories!$J$4:$J$103=$A5))</f>
         <v/>
       </c>
-      <c r="D5" s="245" t="n">
+      <c r="D5" s="246" t="n">
         <v>4</v>
       </c>
-      <c r="E5" s="243" t="n">
+      <c r="E5" s="244" t="n">
         <v>2</v>
       </c>
-      <c r="F5" s="246" t="inlineStr">
+      <c r="F5" s="247" t="inlineStr">
         <is>
           <t>Hazards &amp; Resilience</t>
         </is>
       </c>
-      <c r="G5" s="243" t="n">
+      <c r="G5" s="244" t="n">
         <v>2</v>
       </c>
       <c r="H5" s="171" t="inlineStr">
@@ -22912,7 +24484,7 @@
           <t>Chile, Colombia</t>
         </is>
       </c>
-      <c r="I5" s="247" t="n">
+      <c r="I5" s="248" t="n">
         <v>46320</v>
       </c>
     </row>
@@ -22922,29 +24494,29 @@
           <t>Ground Engineering</t>
         </is>
       </c>
-      <c r="B6" s="243" t="n">
+      <c r="B6" s="244" t="n">
         <v>2</v>
       </c>
-      <c r="C6" s="244">
+      <c r="C6" s="245">
         <f>SUMPRODUCT(Stories!$W$4:$W$103,--(Stories!$J$4:$J$103=$A6))</f>
         <v/>
       </c>
-      <c r="D6" s="245" t="n">
+      <c r="D6" s="246" t="n">
         <v>4.5</v>
       </c>
-      <c r="E6" s="243" t="n">
+      <c r="E6" s="244" t="n">
         <v>2</v>
       </c>
-      <c r="F6" s="248" t="inlineStr">
+      <c r="F6" s="249" t="inlineStr">
         <is>
           <t>Offshore, Coasts &amp; Water</t>
         </is>
       </c>
-      <c r="G6" s="243" t="n">
+      <c r="G6" s="244" t="n">
         <v>2</v>
       </c>
       <c r="H6" s="171" t="inlineStr"/>
-      <c r="I6" s="247" t="n">
+      <c r="I6" s="248" t="n">
         <v>46319</v>
       </c>
     </row>
@@ -22954,25 +24526,25 @@
           <t>Infobae</t>
         </is>
       </c>
-      <c r="B7" s="243" t="n">
+      <c r="B7" s="244" t="n">
         <v>2</v>
       </c>
-      <c r="C7" s="244">
+      <c r="C7" s="245">
         <f>SUMPRODUCT(Stories!$W$4:$W$103,--(Stories!$J$4:$J$103=$A7))</f>
         <v/>
       </c>
-      <c r="D7" s="245" t="n">
+      <c r="D7" s="246" t="n">
         <v>4</v>
       </c>
-      <c r="E7" s="243" t="n">
+      <c r="E7" s="244" t="n">
         <v>1</v>
       </c>
-      <c r="F7" s="246" t="inlineStr">
+      <c r="F7" s="247" t="inlineStr">
         <is>
           <t>Hazards &amp; Resilience</t>
         </is>
       </c>
-      <c r="G7" s="243" t="n">
+      <c r="G7" s="244" t="n">
         <v>2</v>
       </c>
       <c r="H7" s="171" t="inlineStr">
@@ -22980,7 +24552,7 @@
           <t>Argentina, Colombia</t>
         </is>
       </c>
-      <c r="I7" s="247" t="n">
+      <c r="I7" s="248" t="n">
         <v>46320</v>
       </c>
     </row>
@@ -22990,25 +24562,25 @@
           <t>Laodong.vn</t>
         </is>
       </c>
-      <c r="B8" s="243" t="n">
+      <c r="B8" s="244" t="n">
         <v>2</v>
       </c>
-      <c r="C8" s="244">
+      <c r="C8" s="245">
         <f>SUMPRODUCT(Stories!$W$4:$W$103,--(Stories!$J$4:$J$103=$A8))</f>
         <v/>
       </c>
-      <c r="D8" s="245" t="n">
+      <c r="D8" s="246" t="n">
         <v>4</v>
       </c>
-      <c r="E8" s="243" t="n">
+      <c r="E8" s="244" t="n">
         <v>2</v>
       </c>
-      <c r="F8" s="249" t="inlineStr">
+      <c r="F8" s="250" t="inlineStr">
         <is>
           <t>Characterisation &amp; Modelling</t>
         </is>
       </c>
-      <c r="G8" s="243" t="n">
+      <c r="G8" s="244" t="n">
         <v>2</v>
       </c>
       <c r="H8" s="171" t="inlineStr">
@@ -23016,7 +24588,7 @@
           <t>South Korea, France</t>
         </is>
       </c>
-      <c r="I8" s="247" t="n">
+      <c r="I8" s="248" t="n">
         <v>46320</v>
       </c>
     </row>
@@ -23026,29 +24598,29 @@
           <t>Tunnelling Journal</t>
         </is>
       </c>
-      <c r="B9" s="243" t="n">
+      <c r="B9" s="244" t="n">
         <v>2</v>
       </c>
-      <c r="C9" s="244">
+      <c r="C9" s="245">
         <f>SUMPRODUCT(Stories!$W$4:$W$103,--(Stories!$J$4:$J$103=$A9))</f>
         <v/>
       </c>
-      <c r="D9" s="245" t="n">
+      <c r="D9" s="246" t="n">
         <v>3</v>
       </c>
-      <c r="E9" s="243" t="n">
+      <c r="E9" s="244" t="n">
         <v>0</v>
       </c>
-      <c r="F9" s="250" t="inlineStr">
+      <c r="F9" s="251" t="inlineStr">
         <is>
           <t>Infrastructure &amp; the Underground City</t>
         </is>
       </c>
-      <c r="G9" s="243" t="n">
+      <c r="G9" s="244" t="n">
         <v>2</v>
       </c>
       <c r="H9" s="171" t="inlineStr"/>
-      <c r="I9" s="247" t="n">
+      <c r="I9" s="248" t="n">
         <v>46319</v>
       </c>
     </row>
@@ -23058,29 +24630,29 @@
           <t>Tunnels &amp; Tunnelling</t>
         </is>
       </c>
-      <c r="B10" s="243" t="n">
+      <c r="B10" s="244" t="n">
         <v>2</v>
       </c>
-      <c r="C10" s="244">
+      <c r="C10" s="245">
         <f>SUMPRODUCT(Stories!$W$4:$W$103,--(Stories!$J$4:$J$103=$A10))</f>
         <v/>
       </c>
-      <c r="D10" s="245" t="n">
+      <c r="D10" s="246" t="n">
         <v>3</v>
       </c>
-      <c r="E10" s="243" t="n">
+      <c r="E10" s="244" t="n">
         <v>0</v>
       </c>
-      <c r="F10" s="251" t="inlineStr">
+      <c r="F10" s="252" t="inlineStr">
         <is>
           <t>Sustainability &amp; the Energy Transition</t>
         </is>
       </c>
-      <c r="G10" s="243" t="n">
+      <c r="G10" s="244" t="n">
         <v>1</v>
       </c>
       <c r="H10" s="171" t="inlineStr"/>
-      <c r="I10" s="247" t="n">
+      <c r="I10" s="248" t="n">
         <v>46319</v>
       </c>
     </row>
@@ -23090,25 +24662,25 @@
           <t>生物通</t>
         </is>
       </c>
-      <c r="B11" s="243" t="n">
+      <c r="B11" s="244" t="n">
         <v>2</v>
       </c>
-      <c r="C11" s="244">
+      <c r="C11" s="245">
         <f>SUMPRODUCT(Stories!$W$4:$W$103,--(Stories!$J$4:$J$103=$A11))</f>
         <v/>
       </c>
-      <c r="D11" s="245" t="n">
+      <c r="D11" s="246" t="n">
         <v>4.5</v>
       </c>
-      <c r="E11" s="243" t="n">
+      <c r="E11" s="244" t="n">
         <v>2</v>
       </c>
-      <c r="F11" s="252" t="inlineStr">
+      <c r="F11" s="253" t="inlineStr">
         <is>
           <t>Digital Geotechnics</t>
         </is>
       </c>
-      <c r="G11" s="243" t="n">
+      <c r="G11" s="244" t="n">
         <v>2</v>
       </c>
       <c r="H11" s="171" t="inlineStr">
@@ -23116,7 +24688,7 @@
           <t>China</t>
         </is>
       </c>
-      <c r="I11" s="247" t="n">
+      <c r="I11" s="248" t="n">
         <v>46319</v>
       </c>
     </row>
@@ -23126,25 +24698,25 @@
           <t>:: Foro Coatza ::</t>
         </is>
       </c>
-      <c r="B12" s="243" t="n">
+      <c r="B12" s="244" t="n">
         <v>1</v>
       </c>
-      <c r="C12" s="244">
+      <c r="C12" s="245">
         <f>SUMPRODUCT(Stories!$W$4:$W$103,--(Stories!$J$4:$J$103=$A12))</f>
         <v/>
       </c>
-      <c r="D12" s="245" t="n">
+      <c r="D12" s="246" t="n">
         <v>3</v>
       </c>
-      <c r="E12" s="243" t="n">
+      <c r="E12" s="244" t="n">
         <v>0</v>
       </c>
-      <c r="F12" s="248" t="inlineStr">
+      <c r="F12" s="249" t="inlineStr">
         <is>
           <t>Offshore, Coasts &amp; Water</t>
         </is>
       </c>
-      <c r="G12" s="243" t="n">
+      <c r="G12" s="244" t="n">
         <v>1</v>
       </c>
       <c r="H12" s="171" t="inlineStr">
@@ -23152,7 +24724,7 @@
           <t>Argentina</t>
         </is>
       </c>
-      <c r="I12" s="247" t="n">
+      <c r="I12" s="248" t="n">
         <v>46319</v>
       </c>
     </row>
@@ -23162,25 +24734,25 @@
           <t>ABC27</t>
         </is>
       </c>
-      <c r="B13" s="243" t="n">
+      <c r="B13" s="244" t="n">
         <v>1</v>
       </c>
-      <c r="C13" s="244">
+      <c r="C13" s="245">
         <f>SUMPRODUCT(Stories!$W$4:$W$103,--(Stories!$J$4:$J$103=$A13))</f>
         <v/>
       </c>
-      <c r="D13" s="245" t="n">
+      <c r="D13" s="246" t="n">
         <v>3</v>
       </c>
-      <c r="E13" s="243" t="n">
+      <c r="E13" s="244" t="n">
         <v>0</v>
       </c>
-      <c r="F13" s="250" t="inlineStr">
+      <c r="F13" s="251" t="inlineStr">
         <is>
           <t>Infrastructure &amp; the Underground City</t>
         </is>
       </c>
-      <c r="G13" s="243" t="n">
+      <c r="G13" s="244" t="n">
         <v>1</v>
       </c>
       <c r="H13" s="171" t="inlineStr">
@@ -23188,7 +24760,7 @@
           <t>United Kingdom</t>
         </is>
       </c>
-      <c r="I13" s="247" t="n">
+      <c r="I13" s="248" t="n">
         <v>46320</v>
       </c>
     </row>
@@ -23198,25 +24770,25 @@
           <t>agenzia giornalistica opinione</t>
         </is>
       </c>
-      <c r="B14" s="243" t="n">
+      <c r="B14" s="244" t="n">
         <v>1</v>
       </c>
-      <c r="C14" s="244">
+      <c r="C14" s="245">
         <f>SUMPRODUCT(Stories!$W$4:$W$103,--(Stories!$J$4:$J$103=$A14))</f>
         <v/>
       </c>
-      <c r="D14" s="245" t="n">
+      <c r="D14" s="246" t="n">
         <v>4</v>
       </c>
-      <c r="E14" s="243" t="n">
+      <c r="E14" s="244" t="n">
         <v>1</v>
       </c>
-      <c r="F14" s="246" t="inlineStr">
+      <c r="F14" s="247" t="inlineStr">
         <is>
           <t>Hazards &amp; Resilience</t>
         </is>
       </c>
-      <c r="G14" s="243" t="n">
+      <c r="G14" s="244" t="n">
         <v>1</v>
       </c>
       <c r="H14" s="171" t="inlineStr">
@@ -23224,7 +24796,7 @@
           <t>Italy</t>
         </is>
       </c>
-      <c r="I14" s="247" t="n">
+      <c r="I14" s="248" t="n">
         <v>46319</v>
       </c>
     </row>
@@ -23234,25 +24806,25 @@
           <t>Baolangson.vn</t>
         </is>
       </c>
-      <c r="B15" s="243" t="n">
+      <c r="B15" s="244" t="n">
         <v>1</v>
       </c>
-      <c r="C15" s="244">
+      <c r="C15" s="245">
         <f>SUMPRODUCT(Stories!$W$4:$W$103,--(Stories!$J$4:$J$103=$A15))</f>
         <v/>
       </c>
-      <c r="D15" s="245" t="n">
+      <c r="D15" s="246" t="n">
         <v>4</v>
       </c>
-      <c r="E15" s="243" t="n">
+      <c r="E15" s="244" t="n">
         <v>1</v>
       </c>
-      <c r="F15" s="246" t="inlineStr">
+      <c r="F15" s="247" t="inlineStr">
         <is>
           <t>Hazards &amp; Resilience</t>
         </is>
       </c>
-      <c r="G15" s="243" t="n">
+      <c r="G15" s="244" t="n">
         <v>1</v>
       </c>
       <c r="H15" s="171" t="inlineStr">
@@ -23260,7 +24832,7 @@
           <t>Vietnam</t>
         </is>
       </c>
-      <c r="I15" s="247" t="n">
+      <c r="I15" s="248" t="n">
         <v>46319</v>
       </c>
     </row>
@@ -23270,25 +24842,25 @@
           <t>BioBioChile</t>
         </is>
       </c>
-      <c r="B16" s="243" t="n">
+      <c r="B16" s="244" t="n">
         <v>1</v>
       </c>
-      <c r="C16" s="244">
+      <c r="C16" s="245">
         <f>SUMPRODUCT(Stories!$W$4:$W$103,--(Stories!$J$4:$J$103=$A16))</f>
         <v/>
       </c>
-      <c r="D16" s="245" t="n">
+      <c r="D16" s="246" t="n">
         <v>4</v>
       </c>
-      <c r="E16" s="243" t="n">
+      <c r="E16" s="244" t="n">
         <v>1</v>
       </c>
-      <c r="F16" s="250" t="inlineStr">
+      <c r="F16" s="251" t="inlineStr">
         <is>
           <t>Infrastructure &amp; the Underground City</t>
         </is>
       </c>
-      <c r="G16" s="243" t="n">
+      <c r="G16" s="244" t="n">
         <v>1</v>
       </c>
       <c r="H16" s="171" t="inlineStr">
@@ -23296,7 +24868,7 @@
           <t>Colombia</t>
         </is>
       </c>
-      <c r="I16" s="247" t="n">
+      <c r="I16" s="248" t="n">
         <v>46319</v>
       </c>
     </row>
@@ -23306,25 +24878,25 @@
           <t>Boyacá 7 Días</t>
         </is>
       </c>
-      <c r="B17" s="243" t="n">
+      <c r="B17" s="244" t="n">
         <v>1</v>
       </c>
-      <c r="C17" s="244">
+      <c r="C17" s="245">
         <f>SUMPRODUCT(Stories!$W$4:$W$103,--(Stories!$J$4:$J$103=$A17))</f>
         <v/>
       </c>
-      <c r="D17" s="245" t="n">
+      <c r="D17" s="246" t="n">
         <v>3</v>
       </c>
-      <c r="E17" s="243" t="n">
+      <c r="E17" s="244" t="n">
         <v>0</v>
       </c>
-      <c r="F17" s="253" t="inlineStr">
+      <c r="F17" s="254" t="inlineStr">
         <is>
           <t>Geotechnics &amp; Society</t>
         </is>
       </c>
-      <c r="G17" s="243" t="n">
+      <c r="G17" s="244" t="n">
         <v>1</v>
       </c>
       <c r="H17" s="171" t="inlineStr">
@@ -23332,7 +24904,7 @@
           <t>Colombia</t>
         </is>
       </c>
-      <c r="I17" s="247" t="n">
+      <c r="I17" s="248" t="n">
         <v>46319</v>
       </c>
     </row>
@@ -23342,25 +24914,25 @@
           <t>Báo Nhân Dân điện tử</t>
         </is>
       </c>
-      <c r="B18" s="243" t="n">
+      <c r="B18" s="244" t="n">
         <v>1</v>
       </c>
-      <c r="C18" s="244">
+      <c r="C18" s="245">
         <f>SUMPRODUCT(Stories!$W$4:$W$103,--(Stories!$J$4:$J$103=$A18))</f>
         <v/>
       </c>
-      <c r="D18" s="245" t="n">
+      <c r="D18" s="246" t="n">
         <v>4</v>
       </c>
-      <c r="E18" s="243" t="n">
+      <c r="E18" s="244" t="n">
         <v>1</v>
       </c>
-      <c r="F18" s="248" t="inlineStr">
+      <c r="F18" s="249" t="inlineStr">
         <is>
           <t>Offshore, Coasts &amp; Water</t>
         </is>
       </c>
-      <c r="G18" s="243" t="n">
+      <c r="G18" s="244" t="n">
         <v>1</v>
       </c>
       <c r="H18" s="171" t="inlineStr">
@@ -23368,7 +24940,7 @@
           <t>Vietnam</t>
         </is>
       </c>
-      <c r="I18" s="247" t="n">
+      <c r="I18" s="248" t="n">
         <v>46320</v>
       </c>
     </row>
@@ -23378,25 +24950,25 @@
           <t>Báo Thanh Niên</t>
         </is>
       </c>
-      <c r="B19" s="243" t="n">
+      <c r="B19" s="244" t="n">
         <v>1</v>
       </c>
-      <c r="C19" s="244">
+      <c r="C19" s="245">
         <f>SUMPRODUCT(Stories!$W$4:$W$103,--(Stories!$J$4:$J$103=$A19))</f>
         <v/>
       </c>
-      <c r="D19" s="245" t="n">
+      <c r="D19" s="246" t="n">
         <v>4</v>
       </c>
-      <c r="E19" s="243" t="n">
+      <c r="E19" s="244" t="n">
         <v>1</v>
       </c>
-      <c r="F19" s="246" t="inlineStr">
+      <c r="F19" s="247" t="inlineStr">
         <is>
           <t>Hazards &amp; Resilience</t>
         </is>
       </c>
-      <c r="G19" s="243" t="n">
+      <c r="G19" s="244" t="n">
         <v>1</v>
       </c>
       <c r="H19" s="171" t="inlineStr">
@@ -23404,7 +24976,7 @@
           <t>Vietnam</t>
         </is>
       </c>
-      <c r="I19" s="247" t="n">
+      <c r="I19" s="248" t="n">
         <v>46319</v>
       </c>
     </row>
@@ -23414,25 +24986,25 @@
           <t>Báo và phát thanh, truyền hình Đồng Tháp</t>
         </is>
       </c>
-      <c r="B20" s="243" t="n">
+      <c r="B20" s="244" t="n">
         <v>1</v>
       </c>
-      <c r="C20" s="244">
+      <c r="C20" s="245">
         <f>SUMPRODUCT(Stories!$W$4:$W$103,--(Stories!$J$4:$J$103=$A20))</f>
         <v/>
       </c>
-      <c r="D20" s="245" t="n">
+      <c r="D20" s="246" t="n">
         <v>4</v>
       </c>
-      <c r="E20" s="243" t="n">
+      <c r="E20" s="244" t="n">
         <v>1</v>
       </c>
-      <c r="F20" s="246" t="inlineStr">
+      <c r="F20" s="247" t="inlineStr">
         <is>
           <t>Hazards &amp; Resilience</t>
         </is>
       </c>
-      <c r="G20" s="243" t="n">
+      <c r="G20" s="244" t="n">
         <v>1</v>
       </c>
       <c r="H20" s="171" t="inlineStr">
@@ -23440,7 +25012,7 @@
           <t>Vietnam</t>
         </is>
       </c>
-      <c r="I20" s="247" t="n">
+      <c r="I20" s="248" t="n">
         <v>46319</v>
       </c>
     </row>
@@ -23450,25 +25022,25 @@
           <t>Debate</t>
         </is>
       </c>
-      <c r="B21" s="243" t="n">
+      <c r="B21" s="244" t="n">
         <v>1</v>
       </c>
-      <c r="C21" s="244">
+      <c r="C21" s="245">
         <f>SUMPRODUCT(Stories!$W$4:$W$103,--(Stories!$J$4:$J$103=$A21))</f>
         <v/>
       </c>
-      <c r="D21" s="245" t="n">
+      <c r="D21" s="246" t="n">
         <v>4</v>
       </c>
-      <c r="E21" s="243" t="n">
+      <c r="E21" s="244" t="n">
         <v>1</v>
       </c>
-      <c r="F21" s="250" t="inlineStr">
+      <c r="F21" s="251" t="inlineStr">
         <is>
           <t>Infrastructure &amp; the Underground City</t>
         </is>
       </c>
-      <c r="G21" s="243" t="n">
+      <c r="G21" s="244" t="n">
         <v>1</v>
       </c>
       <c r="H21" s="171" t="inlineStr">
@@ -23476,7 +25048,7 @@
           <t>Colombia</t>
         </is>
       </c>
-      <c r="I21" s="247" t="n">
+      <c r="I21" s="248" t="n">
         <v>46319</v>
       </c>
     </row>
@@ -23486,25 +25058,25 @@
           <t>Detona, Real News</t>
         </is>
       </c>
-      <c r="B22" s="243" t="n">
+      <c r="B22" s="244" t="n">
         <v>1</v>
       </c>
-      <c r="C22" s="244">
+      <c r="C22" s="245">
         <f>SUMPRODUCT(Stories!$W$4:$W$103,--(Stories!$J$4:$J$103=$A22))</f>
         <v/>
       </c>
-      <c r="D22" s="245" t="n">
+      <c r="D22" s="246" t="n">
         <v>3</v>
       </c>
-      <c r="E22" s="243" t="n">
+      <c r="E22" s="244" t="n">
         <v>0</v>
       </c>
-      <c r="F22" s="250" t="inlineStr">
+      <c r="F22" s="251" t="inlineStr">
         <is>
           <t>Infrastructure &amp; the Underground City</t>
         </is>
       </c>
-      <c r="G22" s="243" t="n">
+      <c r="G22" s="244" t="n">
         <v>1</v>
       </c>
       <c r="H22" s="171" t="inlineStr">
@@ -23512,7 +25084,7 @@
           <t>Colombia</t>
         </is>
       </c>
-      <c r="I22" s="247" t="n">
+      <c r="I22" s="248" t="n">
         <v>46319</v>
       </c>
     </row>
@@ -23522,25 +25094,25 @@
           <t>Diario 13 San Juan</t>
         </is>
       </c>
-      <c r="B23" s="243" t="n">
+      <c r="B23" s="244" t="n">
         <v>1</v>
       </c>
-      <c r="C23" s="244">
+      <c r="C23" s="245">
         <f>SUMPRODUCT(Stories!$W$4:$W$103,--(Stories!$J$4:$J$103=$A23))</f>
         <v/>
       </c>
-      <c r="D23" s="245" t="n">
+      <c r="D23" s="246" t="n">
         <v>4</v>
       </c>
-      <c r="E23" s="243" t="n">
+      <c r="E23" s="244" t="n">
         <v>1</v>
       </c>
-      <c r="F23" s="246" t="inlineStr">
+      <c r="F23" s="247" t="inlineStr">
         <is>
           <t>Hazards &amp; Resilience</t>
         </is>
       </c>
-      <c r="G23" s="243" t="n">
+      <c r="G23" s="244" t="n">
         <v>1</v>
       </c>
       <c r="H23" s="171" t="inlineStr">
@@ -23548,7 +25120,7 @@
           <t>Chile</t>
         </is>
       </c>
-      <c r="I23" s="247" t="n">
+      <c r="I23" s="248" t="n">
         <v>46320</v>
       </c>
     </row>
@@ -23558,25 +25130,25 @@
           <t>Diario 1588</t>
         </is>
       </c>
-      <c r="B24" s="243" t="n">
+      <c r="B24" s="244" t="n">
         <v>1</v>
       </c>
-      <c r="C24" s="244">
+      <c r="C24" s="245">
         <f>SUMPRODUCT(Stories!$W$4:$W$103,--(Stories!$J$4:$J$103=$A24))</f>
         <v/>
       </c>
-      <c r="D24" s="245" t="n">
+      <c r="D24" s="246" t="n">
         <v>3</v>
       </c>
-      <c r="E24" s="243" t="n">
+      <c r="E24" s="244" t="n">
         <v>0</v>
       </c>
-      <c r="F24" s="248" t="inlineStr">
+      <c r="F24" s="249" t="inlineStr">
         <is>
           <t>Offshore, Coasts &amp; Water</t>
         </is>
       </c>
-      <c r="G24" s="243" t="n">
+      <c r="G24" s="244" t="n">
         <v>1</v>
       </c>
       <c r="H24" s="171" t="inlineStr">
@@ -23584,7 +25156,7 @@
           <t>Argentina</t>
         </is>
       </c>
-      <c r="I24" s="247" t="n">
+      <c r="I24" s="248" t="n">
         <v>46320</v>
       </c>
     </row>
@@ -23594,25 +25166,25 @@
           <t>Diario 7 lagos</t>
         </is>
       </c>
-      <c r="B25" s="243" t="n">
+      <c r="B25" s="244" t="n">
         <v>1</v>
       </c>
-      <c r="C25" s="244">
+      <c r="C25" s="245">
         <f>SUMPRODUCT(Stories!$W$4:$W$103,--(Stories!$J$4:$J$103=$A25))</f>
         <v/>
       </c>
-      <c r="D25" s="245" t="n">
+      <c r="D25" s="246" t="n">
         <v>3</v>
       </c>
-      <c r="E25" s="243" t="n">
+      <c r="E25" s="244" t="n">
         <v>0</v>
       </c>
-      <c r="F25" s="250" t="inlineStr">
+      <c r="F25" s="251" t="inlineStr">
         <is>
           <t>Infrastructure &amp; the Underground City</t>
         </is>
       </c>
-      <c r="G25" s="243" t="n">
+      <c r="G25" s="244" t="n">
         <v>1</v>
       </c>
       <c r="H25" s="171" t="inlineStr">
@@ -23620,7 +25192,7 @@
           <t>Colombia</t>
         </is>
       </c>
-      <c r="I25" s="247" t="n">
+      <c r="I25" s="248" t="n">
         <v>46320</v>
       </c>
     </row>
@@ -23630,25 +25202,25 @@
           <t>Diário do Sudoeste</t>
         </is>
       </c>
-      <c r="B26" s="243" t="n">
+      <c r="B26" s="244" t="n">
         <v>1</v>
       </c>
-      <c r="C26" s="244">
+      <c r="C26" s="245">
         <f>SUMPRODUCT(Stories!$W$4:$W$103,--(Stories!$J$4:$J$103=$A26))</f>
         <v/>
       </c>
-      <c r="D26" s="245" t="n">
+      <c r="D26" s="246" t="n">
         <v>4</v>
       </c>
-      <c r="E26" s="243" t="n">
+      <c r="E26" s="244" t="n">
         <v>1</v>
       </c>
-      <c r="F26" s="246" t="inlineStr">
+      <c r="F26" s="247" t="inlineStr">
         <is>
           <t>Hazards &amp; Resilience</t>
         </is>
       </c>
-      <c r="G26" s="243" t="n">
+      <c r="G26" s="244" t="n">
         <v>1</v>
       </c>
       <c r="H26" s="171" t="inlineStr">
@@ -23656,7 +25228,7 @@
           <t>Brazil</t>
         </is>
       </c>
-      <c r="I26" s="247" t="n">
+      <c r="I26" s="248" t="n">
         <v>46320</v>
       </c>
     </row>
@@ -23666,25 +25238,25 @@
           <t>DTiNews</t>
         </is>
       </c>
-      <c r="B27" s="243" t="n">
+      <c r="B27" s="244" t="n">
         <v>1</v>
       </c>
-      <c r="C27" s="244">
+      <c r="C27" s="245">
         <f>SUMPRODUCT(Stories!$W$4:$W$103,--(Stories!$J$4:$J$103=$A27))</f>
         <v/>
       </c>
-      <c r="D27" s="245" t="n">
+      <c r="D27" s="246" t="n">
         <v>3</v>
       </c>
-      <c r="E27" s="243" t="n">
+      <c r="E27" s="244" t="n">
         <v>0</v>
       </c>
-      <c r="F27" s="249" t="inlineStr">
+      <c r="F27" s="250" t="inlineStr">
         <is>
           <t>Characterisation &amp; Modelling</t>
         </is>
       </c>
-      <c r="G27" s="243" t="n">
+      <c r="G27" s="244" t="n">
         <v>1</v>
       </c>
       <c r="H27" s="171" t="inlineStr">
@@ -23692,7 +25264,7 @@
           <t>United Kingdom</t>
         </is>
       </c>
-      <c r="I27" s="247" t="n">
+      <c r="I27" s="248" t="n">
         <v>46320</v>
       </c>
     </row>
@@ -23702,25 +25274,25 @@
           <t>El Litoral | Novedades de Corrientes</t>
         </is>
       </c>
-      <c r="B28" s="243" t="n">
+      <c r="B28" s="244" t="n">
         <v>1</v>
       </c>
-      <c r="C28" s="244">
+      <c r="C28" s="245">
         <f>SUMPRODUCT(Stories!$W$4:$W$103,--(Stories!$J$4:$J$103=$A28))</f>
         <v/>
       </c>
-      <c r="D28" s="245" t="n">
+      <c r="D28" s="246" t="n">
         <v>3</v>
       </c>
-      <c r="E28" s="243" t="n">
+      <c r="E28" s="244" t="n">
         <v>0</v>
       </c>
-      <c r="F28" s="248" t="inlineStr">
+      <c r="F28" s="249" t="inlineStr">
         <is>
           <t>Offshore, Coasts &amp; Water</t>
         </is>
       </c>
-      <c r="G28" s="243" t="n">
+      <c r="G28" s="244" t="n">
         <v>1</v>
       </c>
       <c r="H28" s="171" t="inlineStr">
@@ -23728,7 +25300,7 @@
           <t>Argentina</t>
         </is>
       </c>
-      <c r="I28" s="247" t="n">
+      <c r="I28" s="248" t="n">
         <v>46319</v>
       </c>
     </row>
@@ -23738,25 +25310,25 @@
           <t>El Siglo de Torreón</t>
         </is>
       </c>
-      <c r="B29" s="243" t="n">
+      <c r="B29" s="244" t="n">
         <v>1</v>
       </c>
-      <c r="C29" s="244">
+      <c r="C29" s="245">
         <f>SUMPRODUCT(Stories!$W$4:$W$103,--(Stories!$J$4:$J$103=$A29))</f>
         <v/>
       </c>
-      <c r="D29" s="245" t="n">
+      <c r="D29" s="246" t="n">
         <v>3</v>
       </c>
-      <c r="E29" s="243" t="n">
+      <c r="E29" s="244" t="n">
         <v>0</v>
       </c>
-      <c r="F29" s="250" t="inlineStr">
+      <c r="F29" s="251" t="inlineStr">
         <is>
           <t>Infrastructure &amp; the Underground City</t>
         </is>
       </c>
-      <c r="G29" s="243" t="n">
+      <c r="G29" s="244" t="n">
         <v>1</v>
       </c>
       <c r="H29" s="171" t="inlineStr">
@@ -23764,7 +25336,7 @@
           <t>Colombia</t>
         </is>
       </c>
-      <c r="I29" s="247" t="n">
+      <c r="I29" s="248" t="n">
         <v>46319</v>
       </c>
     </row>
@@ -23774,25 +25346,25 @@
           <t>El Sol de México</t>
         </is>
       </c>
-      <c r="B30" s="243" t="n">
+      <c r="B30" s="244" t="n">
         <v>1</v>
       </c>
-      <c r="C30" s="244">
+      <c r="C30" s="245">
         <f>SUMPRODUCT(Stories!$W$4:$W$103,--(Stories!$J$4:$J$103=$A30))</f>
         <v/>
       </c>
-      <c r="D30" s="245" t="n">
+      <c r="D30" s="246" t="n">
         <v>3</v>
       </c>
-      <c r="E30" s="243" t="n">
+      <c r="E30" s="244" t="n">
         <v>0</v>
       </c>
-      <c r="F30" s="250" t="inlineStr">
+      <c r="F30" s="251" t="inlineStr">
         <is>
           <t>Infrastructure &amp; the Underground City</t>
         </is>
       </c>
-      <c r="G30" s="243" t="n">
+      <c r="G30" s="244" t="n">
         <v>1</v>
       </c>
       <c r="H30" s="171" t="inlineStr">
@@ -23800,7 +25372,7 @@
           <t>Colombia</t>
         </is>
       </c>
-      <c r="I30" s="247" t="n">
+      <c r="I30" s="248" t="n">
         <v>46320</v>
       </c>
     </row>
@@ -23810,25 +25382,25 @@
           <t>El Universal</t>
         </is>
       </c>
-      <c r="B31" s="243" t="n">
+      <c r="B31" s="244" t="n">
         <v>1</v>
       </c>
-      <c r="C31" s="244">
+      <c r="C31" s="245">
         <f>SUMPRODUCT(Stories!$W$4:$W$103,--(Stories!$J$4:$J$103=$A31))</f>
         <v/>
       </c>
-      <c r="D31" s="245" t="n">
+      <c r="D31" s="246" t="n">
         <v>3</v>
       </c>
-      <c r="E31" s="243" t="n">
+      <c r="E31" s="244" t="n">
         <v>0</v>
       </c>
-      <c r="F31" s="248" t="inlineStr">
+      <c r="F31" s="249" t="inlineStr">
         <is>
           <t>Offshore, Coasts &amp; Water</t>
         </is>
       </c>
-      <c r="G31" s="243" t="n">
+      <c r="G31" s="244" t="n">
         <v>1</v>
       </c>
       <c r="H31" s="171" t="inlineStr">
@@ -23836,7 +25408,7 @@
           <t>Colombia</t>
         </is>
       </c>
-      <c r="I31" s="247" t="n">
+      <c r="I31" s="248" t="n">
         <v>46319</v>
       </c>
     </row>
@@ -23846,25 +25418,25 @@
           <t>El Universo</t>
         </is>
       </c>
-      <c r="B32" s="243" t="n">
+      <c r="B32" s="244" t="n">
         <v>1</v>
       </c>
-      <c r="C32" s="244">
+      <c r="C32" s="245">
         <f>SUMPRODUCT(Stories!$W$4:$W$103,--(Stories!$J$4:$J$103=$A32))</f>
         <v/>
       </c>
-      <c r="D32" s="245" t="n">
+      <c r="D32" s="246" t="n">
         <v>4</v>
       </c>
-      <c r="E32" s="243" t="n">
+      <c r="E32" s="244" t="n">
         <v>1</v>
       </c>
-      <c r="F32" s="250" t="inlineStr">
+      <c r="F32" s="251" t="inlineStr">
         <is>
           <t>Infrastructure &amp; the Underground City</t>
         </is>
       </c>
-      <c r="G32" s="243" t="n">
+      <c r="G32" s="244" t="n">
         <v>1</v>
       </c>
       <c r="H32" s="171" t="inlineStr">
@@ -23872,7 +25444,7 @@
           <t>Colombia</t>
         </is>
       </c>
-      <c r="I32" s="247" t="n">
+      <c r="I32" s="248" t="n">
         <v>46319</v>
       </c>
     </row>
@@ -23882,25 +25454,25 @@
           <t>emsavalles.com</t>
         </is>
       </c>
-      <c r="B33" s="243" t="n">
+      <c r="B33" s="244" t="n">
         <v>1</v>
       </c>
-      <c r="C33" s="244">
+      <c r="C33" s="245">
         <f>SUMPRODUCT(Stories!$W$4:$W$103,--(Stories!$J$4:$J$103=$A33))</f>
         <v/>
       </c>
-      <c r="D33" s="245" t="n">
+      <c r="D33" s="246" t="n">
         <v>3</v>
       </c>
-      <c r="E33" s="243" t="n">
+      <c r="E33" s="244" t="n">
         <v>0</v>
       </c>
-      <c r="F33" s="250" t="inlineStr">
+      <c r="F33" s="251" t="inlineStr">
         <is>
           <t>Infrastructure &amp; the Underground City</t>
         </is>
       </c>
-      <c r="G33" s="243" t="n">
+      <c r="G33" s="244" t="n">
         <v>1</v>
       </c>
       <c r="H33" s="171" t="inlineStr">
@@ -23908,7 +25480,7 @@
           <t>Colombia</t>
         </is>
       </c>
-      <c r="I33" s="247" t="n">
+      <c r="I33" s="248" t="n">
         <v>46320</v>
       </c>
     </row>
@@ -23918,25 +25490,25 @@
           <t>FNNプライムオンライン</t>
         </is>
       </c>
-      <c r="B34" s="243" t="n">
+      <c r="B34" s="244" t="n">
         <v>1</v>
       </c>
-      <c r="C34" s="244">
+      <c r="C34" s="245">
         <f>SUMPRODUCT(Stories!$W$4:$W$103,--(Stories!$J$4:$J$103=$A34))</f>
         <v/>
       </c>
-      <c r="D34" s="245" t="n">
+      <c r="D34" s="246" t="n">
         <v>4</v>
       </c>
-      <c r="E34" s="243" t="n">
+      <c r="E34" s="244" t="n">
         <v>1</v>
       </c>
-      <c r="F34" s="246" t="inlineStr">
+      <c r="F34" s="247" t="inlineStr">
         <is>
           <t>Hazards &amp; Resilience</t>
         </is>
       </c>
-      <c r="G34" s="243" t="n">
+      <c r="G34" s="244" t="n">
         <v>1</v>
       </c>
       <c r="H34" s="171" t="inlineStr">
@@ -23944,7 +25516,7 @@
           <t>Japan</t>
         </is>
       </c>
-      <c r="I34" s="247" t="n">
+      <c r="I34" s="248" t="n">
         <v>46320</v>
       </c>
     </row>
@@ -23954,25 +25526,25 @@
           <t>Geoengineer.org</t>
         </is>
       </c>
-      <c r="B35" s="243" t="n">
+      <c r="B35" s="244" t="n">
         <v>1</v>
       </c>
-      <c r="C35" s="244">
+      <c r="C35" s="245">
         <f>SUMPRODUCT(Stories!$W$4:$W$103,--(Stories!$J$4:$J$103=$A35))</f>
         <v/>
       </c>
-      <c r="D35" s="245" t="n">
+      <c r="D35" s="246" t="n">
         <v>5</v>
       </c>
-      <c r="E35" s="243" t="n">
+      <c r="E35" s="244" t="n">
         <v>1</v>
       </c>
-      <c r="F35" s="254" t="inlineStr">
+      <c r="F35" s="255" t="inlineStr">
         <is>
           <t>Ground Improvement &amp; Innovation</t>
         </is>
       </c>
-      <c r="G35" s="243" t="n">
+      <c r="G35" s="244" t="n">
         <v>1</v>
       </c>
       <c r="H35" s="171" t="inlineStr">
@@ -23980,7 +25552,7 @@
           <t>United States</t>
         </is>
       </c>
-      <c r="I35" s="247" t="n">
+      <c r="I35" s="248" t="n">
         <v>46319</v>
       </c>
     </row>
@@ -23990,25 +25562,25 @@
           <t>Il Giornale dei Castelli Romani</t>
         </is>
       </c>
-      <c r="B36" s="243" t="n">
+      <c r="B36" s="244" t="n">
         <v>1</v>
       </c>
-      <c r="C36" s="244">
+      <c r="C36" s="245">
         <f>SUMPRODUCT(Stories!$W$4:$W$103,--(Stories!$J$4:$J$103=$A36))</f>
         <v/>
       </c>
-      <c r="D36" s="245" t="n">
+      <c r="D36" s="246" t="n">
         <v>4</v>
       </c>
-      <c r="E36" s="243" t="n">
+      <c r="E36" s="244" t="n">
         <v>1</v>
       </c>
-      <c r="F36" s="246" t="inlineStr">
+      <c r="F36" s="247" t="inlineStr">
         <is>
           <t>Hazards &amp; Resilience</t>
         </is>
       </c>
-      <c r="G36" s="243" t="n">
+      <c r="G36" s="244" t="n">
         <v>1</v>
       </c>
       <c r="H36" s="171" t="inlineStr">
@@ -24016,7 +25588,7 @@
           <t>Italy</t>
         </is>
       </c>
-      <c r="I36" s="247" t="n">
+      <c r="I36" s="248" t="n">
         <v>46319</v>
       </c>
     </row>
@@ -24026,25 +25598,25 @@
           <t>Kenh14.vn</t>
         </is>
       </c>
-      <c r="B37" s="243" t="n">
+      <c r="B37" s="244" t="n">
         <v>1</v>
       </c>
-      <c r="C37" s="244">
+      <c r="C37" s="245">
         <f>SUMPRODUCT(Stories!$W$4:$W$103,--(Stories!$J$4:$J$103=$A37))</f>
         <v/>
       </c>
-      <c r="D37" s="245" t="n">
+      <c r="D37" s="246" t="n">
         <v>4</v>
       </c>
-      <c r="E37" s="243" t="n">
+      <c r="E37" s="244" t="n">
         <v>1</v>
       </c>
-      <c r="F37" s="246" t="inlineStr">
+      <c r="F37" s="247" t="inlineStr">
         <is>
           <t>Hazards &amp; Resilience</t>
         </is>
       </c>
-      <c r="G37" s="243" t="n">
+      <c r="G37" s="244" t="n">
         <v>1</v>
       </c>
       <c r="H37" s="171" t="inlineStr">
@@ -24052,7 +25624,7 @@
           <t>Vietnam</t>
         </is>
       </c>
-      <c r="I37" s="247" t="n">
+      <c r="I37" s="248" t="n">
         <v>46319</v>
       </c>
     </row>
@@ -24062,25 +25634,25 @@
           <t>La FM</t>
         </is>
       </c>
-      <c r="B38" s="243" t="n">
+      <c r="B38" s="244" t="n">
         <v>1</v>
       </c>
-      <c r="C38" s="244">
+      <c r="C38" s="245">
         <f>SUMPRODUCT(Stories!$W$4:$W$103,--(Stories!$J$4:$J$103=$A38))</f>
         <v/>
       </c>
-      <c r="D38" s="245" t="n">
+      <c r="D38" s="246" t="n">
         <v>4</v>
       </c>
-      <c r="E38" s="243" t="n">
+      <c r="E38" s="244" t="n">
         <v>1</v>
       </c>
-      <c r="F38" s="246" t="inlineStr">
+      <c r="F38" s="247" t="inlineStr">
         <is>
           <t>Hazards &amp; Resilience</t>
         </is>
       </c>
-      <c r="G38" s="243" t="n">
+      <c r="G38" s="244" t="n">
         <v>1</v>
       </c>
       <c r="H38" s="171" t="inlineStr">
@@ -24088,7 +25660,7 @@
           <t>Spain</t>
         </is>
       </c>
-      <c r="I38" s="247" t="n">
+      <c r="I38" s="248" t="n">
         <v>46320</v>
       </c>
     </row>
@@ -24098,25 +25670,25 @@
           <t>MarketScreener España</t>
         </is>
       </c>
-      <c r="B39" s="243" t="n">
+      <c r="B39" s="244" t="n">
         <v>1</v>
       </c>
-      <c r="C39" s="244">
+      <c r="C39" s="245">
         <f>SUMPRODUCT(Stories!$W$4:$W$103,--(Stories!$J$4:$J$103=$A39))</f>
         <v/>
       </c>
-      <c r="D39" s="245" t="n">
+      <c r="D39" s="246" t="n">
         <v>4</v>
       </c>
-      <c r="E39" s="243" t="n">
+      <c r="E39" s="244" t="n">
         <v>1</v>
       </c>
-      <c r="F39" s="250" t="inlineStr">
+      <c r="F39" s="251" t="inlineStr">
         <is>
           <t>Infrastructure &amp; the Underground City</t>
         </is>
       </c>
-      <c r="G39" s="243" t="n">
+      <c r="G39" s="244" t="n">
         <v>1</v>
       </c>
       <c r="H39" s="171" t="inlineStr">
@@ -24124,7 +25696,7 @@
           <t>Argentina</t>
         </is>
       </c>
-      <c r="I39" s="247" t="n">
+      <c r="I39" s="248" t="n">
         <v>46320</v>
       </c>
     </row>
@@ -24134,25 +25706,25 @@
           <t>Meganoticias</t>
         </is>
       </c>
-      <c r="B40" s="243" t="n">
+      <c r="B40" s="244" t="n">
         <v>1</v>
       </c>
-      <c r="C40" s="244">
+      <c r="C40" s="245">
         <f>SUMPRODUCT(Stories!$W$4:$W$103,--(Stories!$J$4:$J$103=$A40))</f>
         <v/>
       </c>
-      <c r="D40" s="245" t="n">
+      <c r="D40" s="246" t="n">
         <v>4</v>
       </c>
-      <c r="E40" s="243" t="n">
+      <c r="E40" s="244" t="n">
         <v>1</v>
       </c>
-      <c r="F40" s="246" t="inlineStr">
+      <c r="F40" s="247" t="inlineStr">
         <is>
           <t>Hazards &amp; Resilience</t>
         </is>
       </c>
-      <c r="G40" s="243" t="n">
+      <c r="G40" s="244" t="n">
         <v>1</v>
       </c>
       <c r="H40" s="171" t="inlineStr">
@@ -24160,7 +25732,7 @@
           <t>Chile</t>
         </is>
       </c>
-      <c r="I40" s="247" t="n">
+      <c r="I40" s="248" t="n">
         <v>46319</v>
       </c>
     </row>
@@ -24170,25 +25742,25 @@
           <t>Naver Blog</t>
         </is>
       </c>
-      <c r="B41" s="243" t="n">
+      <c r="B41" s="244" t="n">
         <v>1</v>
       </c>
-      <c r="C41" s="244">
+      <c r="C41" s="245">
         <f>SUMPRODUCT(Stories!$W$4:$W$103,--(Stories!$J$4:$J$103=$A41))</f>
         <v/>
       </c>
-      <c r="D41" s="245" t="n">
+      <c r="D41" s="246" t="n">
         <v>4</v>
       </c>
-      <c r="E41" s="243" t="n">
+      <c r="E41" s="244" t="n">
         <v>1</v>
       </c>
-      <c r="F41" s="250" t="inlineStr">
+      <c r="F41" s="251" t="inlineStr">
         <is>
           <t>Infrastructure &amp; the Underground City</t>
         </is>
       </c>
-      <c r="G41" s="243" t="n">
+      <c r="G41" s="244" t="n">
         <v>1</v>
       </c>
       <c r="H41" s="171" t="inlineStr">
@@ -24196,7 +25768,7 @@
           <t>South Korea</t>
         </is>
       </c>
-      <c r="I41" s="247" t="n">
+      <c r="I41" s="248" t="n">
         <v>46319</v>
       </c>
     </row>
@@ -24206,25 +25778,25 @@
           <t>NDT Noticias de Tijuana</t>
         </is>
       </c>
-      <c r="B42" s="243" t="n">
+      <c r="B42" s="244" t="n">
         <v>1</v>
       </c>
-      <c r="C42" s="244">
+      <c r="C42" s="245">
         <f>SUMPRODUCT(Stories!$W$4:$W$103,--(Stories!$J$4:$J$103=$A42))</f>
         <v/>
       </c>
-      <c r="D42" s="245" t="n">
+      <c r="D42" s="246" t="n">
         <v>4</v>
       </c>
-      <c r="E42" s="243" t="n">
+      <c r="E42" s="244" t="n">
         <v>1</v>
       </c>
-      <c r="F42" s="250" t="inlineStr">
+      <c r="F42" s="251" t="inlineStr">
         <is>
           <t>Infrastructure &amp; the Underground City</t>
         </is>
       </c>
-      <c r="G42" s="243" t="n">
+      <c r="G42" s="244" t="n">
         <v>1</v>
       </c>
       <c r="H42" s="171" t="inlineStr">
@@ -24232,7 +25804,7 @@
           <t>Colombia</t>
         </is>
       </c>
-      <c r="I42" s="247" t="n">
+      <c r="I42" s="248" t="n">
         <v>46320</v>
       </c>
     </row>
@@ -24242,25 +25814,25 @@
           <t>Người Đưa Tin</t>
         </is>
       </c>
-      <c r="B43" s="243" t="n">
+      <c r="B43" s="244" t="n">
         <v>1</v>
       </c>
-      <c r="C43" s="244">
+      <c r="C43" s="245">
         <f>SUMPRODUCT(Stories!$W$4:$W$103,--(Stories!$J$4:$J$103=$A43))</f>
         <v/>
       </c>
-      <c r="D43" s="245" t="n">
+      <c r="D43" s="246" t="n">
         <v>4</v>
       </c>
-      <c r="E43" s="243" t="n">
+      <c r="E43" s="244" t="n">
         <v>1</v>
       </c>
-      <c r="F43" s="248" t="inlineStr">
+      <c r="F43" s="249" t="inlineStr">
         <is>
           <t>Offshore, Coasts &amp; Water</t>
         </is>
       </c>
-      <c r="G43" s="243" t="n">
+      <c r="G43" s="244" t="n">
         <v>1</v>
       </c>
       <c r="H43" s="171" t="inlineStr">
@@ -24268,7 +25840,7 @@
           <t>Vietnam</t>
         </is>
       </c>
-      <c r="I43" s="247" t="n">
+      <c r="I43" s="248" t="n">
         <v>46319</v>
       </c>
     </row>
@@ -24278,25 +25850,25 @@
           <t>Onmanorama</t>
         </is>
       </c>
-      <c r="B44" s="243" t="n">
+      <c r="B44" s="244" t="n">
         <v>1</v>
       </c>
-      <c r="C44" s="244">
+      <c r="C44" s="245">
         <f>SUMPRODUCT(Stories!$W$4:$W$103,--(Stories!$J$4:$J$103=$A44))</f>
         <v/>
       </c>
-      <c r="D44" s="245" t="n">
+      <c r="D44" s="246" t="n">
         <v>5</v>
       </c>
-      <c r="E44" s="243" t="n">
+      <c r="E44" s="244" t="n">
         <v>1</v>
       </c>
-      <c r="F44" s="246" t="inlineStr">
+      <c r="F44" s="247" t="inlineStr">
         <is>
           <t>Hazards &amp; Resilience</t>
         </is>
       </c>
-      <c r="G44" s="243" t="n">
+      <c r="G44" s="244" t="n">
         <v>1</v>
       </c>
       <c r="H44" s="171" t="inlineStr">
@@ -24304,7 +25876,7 @@
           <t>South Africa</t>
         </is>
       </c>
-      <c r="I44" s="247" t="n">
+      <c r="I44" s="248" t="n">
         <v>46320</v>
       </c>
     </row>
@@ -24314,25 +25886,25 @@
           <t>Publimicro</t>
         </is>
       </c>
-      <c r="B45" s="243" t="n">
+      <c r="B45" s="244" t="n">
         <v>1</v>
       </c>
-      <c r="C45" s="244">
+      <c r="C45" s="245">
         <f>SUMPRODUCT(Stories!$W$4:$W$103,--(Stories!$J$4:$J$103=$A45))</f>
         <v/>
       </c>
-      <c r="D45" s="245" t="n">
+      <c r="D45" s="246" t="n">
         <v>5</v>
       </c>
-      <c r="E45" s="243" t="n">
+      <c r="E45" s="244" t="n">
         <v>1</v>
       </c>
-      <c r="F45" s="246" t="inlineStr">
+      <c r="F45" s="247" t="inlineStr">
         <is>
           <t>Hazards &amp; Resilience</t>
         </is>
       </c>
-      <c r="G45" s="243" t="n">
+      <c r="G45" s="244" t="n">
         <v>1</v>
       </c>
       <c r="H45" s="171" t="inlineStr">
@@ -24340,7 +25912,7 @@
           <t>Colombia</t>
         </is>
       </c>
-      <c r="I45" s="247" t="n">
+      <c r="I45" s="248" t="n">
         <v>46320</v>
       </c>
     </row>
@@ -24350,25 +25922,25 @@
           <t>Quintana Roo Hoy</t>
         </is>
       </c>
-      <c r="B46" s="243" t="n">
+      <c r="B46" s="244" t="n">
         <v>1</v>
       </c>
-      <c r="C46" s="244">
+      <c r="C46" s="245">
         <f>SUMPRODUCT(Stories!$W$4:$W$103,--(Stories!$J$4:$J$103=$A46))</f>
         <v/>
       </c>
-      <c r="D46" s="245" t="n">
+      <c r="D46" s="246" t="n">
         <v>4</v>
       </c>
-      <c r="E46" s="243" t="n">
+      <c r="E46" s="244" t="n">
         <v>1</v>
       </c>
-      <c r="F46" s="250" t="inlineStr">
+      <c r="F46" s="251" t="inlineStr">
         <is>
           <t>Infrastructure &amp; the Underground City</t>
         </is>
       </c>
-      <c r="G46" s="243" t="n">
+      <c r="G46" s="244" t="n">
         <v>1</v>
       </c>
       <c r="H46" s="171" t="inlineStr">
@@ -24376,7 +25948,7 @@
           <t>Colombia</t>
         </is>
       </c>
-      <c r="I46" s="247" t="n">
+      <c r="I46" s="248" t="n">
         <v>46320</v>
       </c>
     </row>
@@ -24386,25 +25958,25 @@
           <t>Radio-Canada</t>
         </is>
       </c>
-      <c r="B47" s="243" t="n">
+      <c r="B47" s="244" t="n">
         <v>1</v>
       </c>
-      <c r="C47" s="244">
+      <c r="C47" s="245">
         <f>SUMPRODUCT(Stories!$W$4:$W$103,--(Stories!$J$4:$J$103=$A47))</f>
         <v/>
       </c>
-      <c r="D47" s="245" t="n">
+      <c r="D47" s="246" t="n">
         <v>4</v>
       </c>
-      <c r="E47" s="243" t="n">
+      <c r="E47" s="244" t="n">
         <v>1</v>
       </c>
-      <c r="F47" s="246" t="inlineStr">
+      <c r="F47" s="247" t="inlineStr">
         <is>
           <t>Hazards &amp; Resilience</t>
         </is>
       </c>
-      <c r="G47" s="243" t="n">
+      <c r="G47" s="244" t="n">
         <v>1</v>
       </c>
       <c r="H47" s="171" t="inlineStr">
@@ -24412,7 +25984,7 @@
           <t>France</t>
         </is>
       </c>
-      <c r="I47" s="247" t="n">
+      <c r="I47" s="248" t="n">
         <v>46320</v>
       </c>
     </row>
@@ -24422,25 +25994,25 @@
           <t>Realidad Sanmartinense</t>
         </is>
       </c>
-      <c r="B48" s="243" t="n">
+      <c r="B48" s="244" t="n">
         <v>1</v>
       </c>
-      <c r="C48" s="244">
+      <c r="C48" s="245">
         <f>SUMPRODUCT(Stories!$W$4:$W$103,--(Stories!$J$4:$J$103=$A48))</f>
         <v/>
       </c>
-      <c r="D48" s="245" t="n">
+      <c r="D48" s="246" t="n">
         <v>3</v>
       </c>
-      <c r="E48" s="243" t="n">
+      <c r="E48" s="244" t="n">
         <v>0</v>
       </c>
-      <c r="F48" s="250" t="inlineStr">
+      <c r="F48" s="251" t="inlineStr">
         <is>
           <t>Infrastructure &amp; the Underground City</t>
         </is>
       </c>
-      <c r="G48" s="243" t="n">
+      <c r="G48" s="244" t="n">
         <v>1</v>
       </c>
       <c r="H48" s="171" t="inlineStr">
@@ -24448,7 +26020,7 @@
           <t>Colombia</t>
         </is>
       </c>
-      <c r="I48" s="247" t="n">
+      <c r="I48" s="248" t="n">
         <v>46319</v>
       </c>
     </row>
@@ -24458,25 +26030,25 @@
           <t>Revista Digital Minera REDIMIN</t>
         </is>
       </c>
-      <c r="B49" s="243" t="n">
+      <c r="B49" s="244" t="n">
         <v>1</v>
       </c>
-      <c r="C49" s="244">
+      <c r="C49" s="245">
         <f>SUMPRODUCT(Stories!$W$4:$W$103,--(Stories!$J$4:$J$103=$A49))</f>
         <v/>
       </c>
-      <c r="D49" s="245" t="n">
+      <c r="D49" s="246" t="n">
         <v>5</v>
       </c>
-      <c r="E49" s="243" t="n">
+      <c r="E49" s="244" t="n">
         <v>1</v>
       </c>
-      <c r="F49" s="246" t="inlineStr">
+      <c r="F49" s="247" t="inlineStr">
         <is>
           <t>Hazards &amp; Resilience</t>
         </is>
       </c>
-      <c r="G49" s="243" t="n">
+      <c r="G49" s="244" t="n">
         <v>1</v>
       </c>
       <c r="H49" s="171" t="inlineStr">
@@ -24484,7 +26056,7 @@
           <t>Argentina</t>
         </is>
       </c>
-      <c r="I49" s="247" t="n">
+      <c r="I49" s="248" t="n">
         <v>46320</v>
       </c>
     </row>
@@ -24494,25 +26066,25 @@
           <t>RRI.co.id</t>
         </is>
       </c>
-      <c r="B50" s="243" t="n">
+      <c r="B50" s="244" t="n">
         <v>1</v>
       </c>
-      <c r="C50" s="244">
+      <c r="C50" s="245">
         <f>SUMPRODUCT(Stories!$W$4:$W$103,--(Stories!$J$4:$J$103=$A50))</f>
         <v/>
       </c>
-      <c r="D50" s="245" t="n">
+      <c r="D50" s="246" t="n">
         <v>4</v>
       </c>
-      <c r="E50" s="243" t="n">
+      <c r="E50" s="244" t="n">
         <v>1</v>
       </c>
-      <c r="F50" s="246" t="inlineStr">
+      <c r="F50" s="247" t="inlineStr">
         <is>
           <t>Hazards &amp; Resilience</t>
         </is>
       </c>
-      <c r="G50" s="243" t="n">
+      <c r="G50" s="244" t="n">
         <v>1</v>
       </c>
       <c r="H50" s="171" t="inlineStr">
@@ -24520,7 +26092,7 @@
           <t>Indonesia</t>
         </is>
       </c>
-      <c r="I50" s="247" t="n">
+      <c r="I50" s="248" t="n">
         <v>46319</v>
       </c>
     </row>
@@ -24530,25 +26102,25 @@
           <t>Sciencepost</t>
         </is>
       </c>
-      <c r="B51" s="243" t="n">
+      <c r="B51" s="244" t="n">
         <v>1</v>
       </c>
-      <c r="C51" s="244">
+      <c r="C51" s="245">
         <f>SUMPRODUCT(Stories!$W$4:$W$103,--(Stories!$J$4:$J$103=$A51))</f>
         <v/>
       </c>
-      <c r="D51" s="245" t="n">
+      <c r="D51" s="246" t="n">
         <v>5</v>
       </c>
-      <c r="E51" s="243" t="n">
+      <c r="E51" s="244" t="n">
         <v>1</v>
       </c>
-      <c r="F51" s="254" t="inlineStr">
+      <c r="F51" s="255" t="inlineStr">
         <is>
           <t>Ground Improvement &amp; Innovation</t>
         </is>
       </c>
-      <c r="G51" s="243" t="n">
+      <c r="G51" s="244" t="n">
         <v>1</v>
       </c>
       <c r="H51" s="171" t="inlineStr">
@@ -24556,7 +26128,7 @@
           <t>Senegal</t>
         </is>
       </c>
-      <c r="I51" s="247" t="n">
+      <c r="I51" s="248" t="n">
         <v>46319</v>
       </c>
     </row>
@@ -24566,25 +26138,25 @@
           <t>StabiaChannel.it</t>
         </is>
       </c>
-      <c r="B52" s="243" t="n">
+      <c r="B52" s="244" t="n">
         <v>1</v>
       </c>
-      <c r="C52" s="244">
+      <c r="C52" s="245">
         <f>SUMPRODUCT(Stories!$W$4:$W$103,--(Stories!$J$4:$J$103=$A52))</f>
         <v/>
       </c>
-      <c r="D52" s="245" t="n">
+      <c r="D52" s="246" t="n">
         <v>4</v>
       </c>
-      <c r="E52" s="243" t="n">
+      <c r="E52" s="244" t="n">
         <v>1</v>
       </c>
-      <c r="F52" s="246" t="inlineStr">
+      <c r="F52" s="247" t="inlineStr">
         <is>
           <t>Hazards &amp; Resilience</t>
         </is>
       </c>
-      <c r="G52" s="243" t="n">
+      <c r="G52" s="244" t="n">
         <v>1</v>
       </c>
       <c r="H52" s="171" t="inlineStr">
@@ -24592,7 +26164,7 @@
           <t>Italy</t>
         </is>
       </c>
-      <c r="I52" s="247" t="n">
+      <c r="I52" s="248" t="n">
         <v>46320</v>
       </c>
     </row>
@@ -24602,25 +26174,25 @@
           <t>Tabasco HOY</t>
         </is>
       </c>
-      <c r="B53" s="243" t="n">
+      <c r="B53" s="244" t="n">
         <v>1</v>
       </c>
-      <c r="C53" s="244">
+      <c r="C53" s="245">
         <f>SUMPRODUCT(Stories!$W$4:$W$103,--(Stories!$J$4:$J$103=$A53))</f>
         <v/>
       </c>
-      <c r="D53" s="245" t="n">
+      <c r="D53" s="246" t="n">
         <v>3</v>
       </c>
-      <c r="E53" s="243" t="n">
+      <c r="E53" s="244" t="n">
         <v>0</v>
       </c>
-      <c r="F53" s="250" t="inlineStr">
+      <c r="F53" s="251" t="inlineStr">
         <is>
           <t>Infrastructure &amp; the Underground City</t>
         </is>
       </c>
-      <c r="G53" s="243" t="n">
+      <c r="G53" s="244" t="n">
         <v>1</v>
       </c>
       <c r="H53" s="171" t="inlineStr">
@@ -24628,7 +26200,7 @@
           <t>Colombia</t>
         </is>
       </c>
-      <c r="I53" s="247" t="n">
+      <c r="I53" s="248" t="n">
         <v>46319</v>
       </c>
     </row>
@@ -24638,25 +26210,25 @@
           <t>The Hindu</t>
         </is>
       </c>
-      <c r="B54" s="243" t="n">
+      <c r="B54" s="244" t="n">
         <v>1</v>
       </c>
-      <c r="C54" s="244">
+      <c r="C54" s="245">
         <f>SUMPRODUCT(Stories!$W$4:$W$103,--(Stories!$J$4:$J$103=$A54))</f>
         <v/>
       </c>
-      <c r="D54" s="245" t="n">
+      <c r="D54" s="246" t="n">
         <v>3</v>
       </c>
-      <c r="E54" s="243" t="n">
+      <c r="E54" s="244" t="n">
         <v>0</v>
       </c>
-      <c r="F54" s="250" t="inlineStr">
+      <c r="F54" s="251" t="inlineStr">
         <is>
           <t>Infrastructure &amp; the Underground City</t>
         </is>
       </c>
-      <c r="G54" s="243" t="n">
+      <c r="G54" s="244" t="n">
         <v>1</v>
       </c>
       <c r="H54" s="171" t="inlineStr">
@@ -24664,7 +26236,7 @@
           <t>United Kingdom</t>
         </is>
       </c>
-      <c r="I54" s="247" t="n">
+      <c r="I54" s="248" t="n">
         <v>46320</v>
       </c>
     </row>
@@ -24674,25 +26246,25 @@
           <t>The Star</t>
         </is>
       </c>
-      <c r="B55" s="243" t="n">
+      <c r="B55" s="244" t="n">
         <v>1</v>
       </c>
-      <c r="C55" s="244">
+      <c r="C55" s="245">
         <f>SUMPRODUCT(Stories!$W$4:$W$103,--(Stories!$J$4:$J$103=$A55))</f>
         <v/>
       </c>
-      <c r="D55" s="245" t="n">
+      <c r="D55" s="246" t="n">
         <v>4</v>
       </c>
-      <c r="E55" s="243" t="n">
+      <c r="E55" s="244" t="n">
         <v>1</v>
       </c>
-      <c r="F55" s="246" t="inlineStr">
+      <c r="F55" s="247" t="inlineStr">
         <is>
           <t>Hazards &amp; Resilience</t>
         </is>
       </c>
-      <c r="G55" s="243" t="n">
+      <c r="G55" s="244" t="n">
         <v>1</v>
       </c>
       <c r="H55" s="171" t="inlineStr">
@@ -24700,7 +26272,7 @@
           <t>United Kingdom</t>
         </is>
       </c>
-      <c r="I55" s="247" t="n">
+      <c r="I55" s="248" t="n">
         <v>46320</v>
       </c>
     </row>
@@ -24710,25 +26282,25 @@
           <t>The Weekend Leader</t>
         </is>
       </c>
-      <c r="B56" s="243" t="n">
+      <c r="B56" s="244" t="n">
         <v>1</v>
       </c>
-      <c r="C56" s="244">
+      <c r="C56" s="245">
         <f>SUMPRODUCT(Stories!$W$4:$W$103,--(Stories!$J$4:$J$103=$A56))</f>
         <v/>
       </c>
-      <c r="D56" s="245" t="n">
+      <c r="D56" s="246" t="n">
         <v>4</v>
       </c>
-      <c r="E56" s="243" t="n">
+      <c r="E56" s="244" t="n">
         <v>1</v>
       </c>
-      <c r="F56" s="246" t="inlineStr">
+      <c r="F56" s="247" t="inlineStr">
         <is>
           <t>Hazards &amp; Resilience</t>
         </is>
       </c>
-      <c r="G56" s="243" t="n">
+      <c r="G56" s="244" t="n">
         <v>1</v>
       </c>
       <c r="H56" s="171" t="inlineStr">
@@ -24736,7 +26308,7 @@
           <t>South Africa</t>
         </is>
       </c>
-      <c r="I56" s="247" t="n">
+      <c r="I56" s="248" t="n">
         <v>46320</v>
       </c>
     </row>
@@ -24746,25 +26318,25 @@
           <t>tin.skydoor.net</t>
         </is>
       </c>
-      <c r="B57" s="243" t="n">
+      <c r="B57" s="244" t="n">
         <v>1</v>
       </c>
-      <c r="C57" s="244">
+      <c r="C57" s="245">
         <f>SUMPRODUCT(Stories!$W$4:$W$103,--(Stories!$J$4:$J$103=$A57))</f>
         <v/>
       </c>
-      <c r="D57" s="245" t="n">
+      <c r="D57" s="246" t="n">
         <v>4</v>
       </c>
-      <c r="E57" s="243" t="n">
+      <c r="E57" s="244" t="n">
         <v>1</v>
       </c>
-      <c r="F57" s="248" t="inlineStr">
+      <c r="F57" s="249" t="inlineStr">
         <is>
           <t>Offshore, Coasts &amp; Water</t>
         </is>
       </c>
-      <c r="G57" s="243" t="n">
+      <c r="G57" s="244" t="n">
         <v>1</v>
       </c>
       <c r="H57" s="171" t="inlineStr">
@@ -24772,7 +26344,7 @@
           <t>Vietnam</t>
         </is>
       </c>
-      <c r="I57" s="247" t="n">
+      <c r="I57" s="248" t="n">
         <v>46320</v>
       </c>
     </row>
@@ -24782,25 +26354,25 @@
           <t>Trade-news.cl</t>
         </is>
       </c>
-      <c r="B58" s="243" t="n">
+      <c r="B58" s="244" t="n">
         <v>1</v>
       </c>
-      <c r="C58" s="244">
+      <c r="C58" s="245">
         <f>SUMPRODUCT(Stories!$W$4:$W$103,--(Stories!$J$4:$J$103=$A58))</f>
         <v/>
       </c>
-      <c r="D58" s="245" t="n">
+      <c r="D58" s="246" t="n">
         <v>3</v>
       </c>
-      <c r="E58" s="243" t="n">
+      <c r="E58" s="244" t="n">
         <v>0</v>
       </c>
-      <c r="F58" s="249" t="inlineStr">
+      <c r="F58" s="250" t="inlineStr">
         <is>
           <t>Characterisation &amp; Modelling</t>
         </is>
       </c>
-      <c r="G58" s="243" t="n">
+      <c r="G58" s="244" t="n">
         <v>1</v>
       </c>
       <c r="H58" s="171" t="inlineStr">
@@ -24808,7 +26380,7 @@
           <t>Peru</t>
         </is>
       </c>
-      <c r="I58" s="247" t="n">
+      <c r="I58" s="248" t="n">
         <v>46319</v>
       </c>
     </row>
@@ -24818,25 +26390,25 @@
           <t>Trigno.net</t>
         </is>
       </c>
-      <c r="B59" s="243" t="n">
+      <c r="B59" s="244" t="n">
         <v>1</v>
       </c>
-      <c r="C59" s="244">
+      <c r="C59" s="245">
         <f>SUMPRODUCT(Stories!$W$4:$W$103,--(Stories!$J$4:$J$103=$A59))</f>
         <v/>
       </c>
-      <c r="D59" s="245" t="n">
+      <c r="D59" s="246" t="n">
         <v>3</v>
       </c>
-      <c r="E59" s="243" t="n">
+      <c r="E59" s="244" t="n">
         <v>0</v>
       </c>
-      <c r="F59" s="253" t="inlineStr">
+      <c r="F59" s="254" t="inlineStr">
         <is>
           <t>Geotechnics &amp; Society</t>
         </is>
       </c>
-      <c r="G59" s="243" t="n">
+      <c r="G59" s="244" t="n">
         <v>1</v>
       </c>
       <c r="H59" s="171" t="inlineStr">
@@ -24844,7 +26416,7 @@
           <t>Italy</t>
         </is>
       </c>
-      <c r="I59" s="247" t="n">
+      <c r="I59" s="248" t="n">
         <v>46320</v>
       </c>
     </row>
@@ -24854,25 +26426,25 @@
           <t>Tv7 Benevento</t>
         </is>
       </c>
-      <c r="B60" s="243" t="n">
+      <c r="B60" s="244" t="n">
         <v>1</v>
       </c>
-      <c r="C60" s="244">
+      <c r="C60" s="245">
         <f>SUMPRODUCT(Stories!$W$4:$W$103,--(Stories!$J$4:$J$103=$A60))</f>
         <v/>
       </c>
-      <c r="D60" s="245" t="n">
+      <c r="D60" s="246" t="n">
         <v>4</v>
       </c>
-      <c r="E60" s="243" t="n">
+      <c r="E60" s="244" t="n">
         <v>1</v>
       </c>
-      <c r="F60" s="246" t="inlineStr">
+      <c r="F60" s="247" t="inlineStr">
         <is>
           <t>Hazards &amp; Resilience</t>
         </is>
       </c>
-      <c r="G60" s="243" t="n">
+      <c r="G60" s="244" t="n">
         <v>1</v>
       </c>
       <c r="H60" s="171" t="inlineStr">
@@ -24880,7 +26452,7 @@
           <t>Italy</t>
         </is>
       </c>
-      <c r="I60" s="247" t="n">
+      <c r="I60" s="248" t="n">
         <v>46319</v>
       </c>
     </row>
@@ -24890,25 +26462,25 @@
           <t>VnExpress International</t>
         </is>
       </c>
-      <c r="B61" s="243" t="n">
+      <c r="B61" s="244" t="n">
         <v>1</v>
       </c>
-      <c r="C61" s="244">
+      <c r="C61" s="245">
         <f>SUMPRODUCT(Stories!$W$4:$W$103,--(Stories!$J$4:$J$103=$A61))</f>
         <v/>
       </c>
-      <c r="D61" s="245" t="n">
+      <c r="D61" s="246" t="n">
         <v>4</v>
       </c>
-      <c r="E61" s="243" t="n">
+      <c r="E61" s="244" t="n">
         <v>1</v>
       </c>
-      <c r="F61" s="249" t="inlineStr">
+      <c r="F61" s="250" t="inlineStr">
         <is>
           <t>Characterisation &amp; Modelling</t>
         </is>
       </c>
-      <c r="G61" s="243" t="n">
+      <c r="G61" s="244" t="n">
         <v>1</v>
       </c>
       <c r="H61" s="171" t="inlineStr">
@@ -24916,7 +26488,7 @@
           <t>United Kingdom</t>
         </is>
       </c>
-      <c r="I61" s="247" t="n">
+      <c r="I61" s="248" t="n">
         <v>46319</v>
       </c>
     </row>
@@ -24926,25 +26498,25 @@
           <t>VOH</t>
         </is>
       </c>
-      <c r="B62" s="243" t="n">
+      <c r="B62" s="244" t="n">
         <v>1</v>
       </c>
-      <c r="C62" s="244">
+      <c r="C62" s="245">
         <f>SUMPRODUCT(Stories!$W$4:$W$103,--(Stories!$J$4:$J$103=$A62))</f>
         <v/>
       </c>
-      <c r="D62" s="245" t="n">
+      <c r="D62" s="246" t="n">
         <v>4</v>
       </c>
-      <c r="E62" s="243" t="n">
+      <c r="E62" s="244" t="n">
         <v>1</v>
       </c>
-      <c r="F62" s="250" t="inlineStr">
+      <c r="F62" s="251" t="inlineStr">
         <is>
           <t>Infrastructure &amp; the Underground City</t>
         </is>
       </c>
-      <c r="G62" s="243" t="n">
+      <c r="G62" s="244" t="n">
         <v>1</v>
       </c>
       <c r="H62" s="171" t="inlineStr">
@@ -24952,7 +26524,7 @@
           <t>Vietnam</t>
         </is>
       </c>
-      <c r="I62" s="247" t="n">
+      <c r="I62" s="248" t="n">
         <v>46319</v>
       </c>
     </row>
@@ -24962,25 +26534,25 @@
           <t>VTV.vn</t>
         </is>
       </c>
-      <c r="B63" s="243" t="n">
+      <c r="B63" s="244" t="n">
         <v>1</v>
       </c>
-      <c r="C63" s="244">
+      <c r="C63" s="245">
         <f>SUMPRODUCT(Stories!$W$4:$W$103,--(Stories!$J$4:$J$103=$A63))</f>
         <v/>
       </c>
-      <c r="D63" s="245" t="n">
+      <c r="D63" s="246" t="n">
         <v>4</v>
       </c>
-      <c r="E63" s="243" t="n">
+      <c r="E63" s="244" t="n">
         <v>1</v>
       </c>
-      <c r="F63" s="248" t="inlineStr">
+      <c r="F63" s="249" t="inlineStr">
         <is>
           <t>Offshore, Coasts &amp; Water</t>
         </is>
       </c>
-      <c r="G63" s="243" t="n">
+      <c r="G63" s="244" t="n">
         <v>1</v>
       </c>
       <c r="H63" s="171" t="inlineStr">
@@ -24988,7 +26560,7 @@
           <t>Vietnam</t>
         </is>
       </c>
-      <c r="I63" s="247" t="n">
+      <c r="I63" s="248" t="n">
         <v>46319</v>
       </c>
     </row>
@@ -24998,25 +26570,25 @@
           <t>www.noroeste.com.mx</t>
         </is>
       </c>
-      <c r="B64" s="243" t="n">
+      <c r="B64" s="244" t="n">
         <v>1</v>
       </c>
-      <c r="C64" s="244">
+      <c r="C64" s="245">
         <f>SUMPRODUCT(Stories!$W$4:$W$103,--(Stories!$J$4:$J$103=$A64))</f>
         <v/>
       </c>
-      <c r="D64" s="245" t="n">
+      <c r="D64" s="246" t="n">
         <v>4</v>
       </c>
-      <c r="E64" s="243" t="n">
+      <c r="E64" s="244" t="n">
         <v>1</v>
       </c>
-      <c r="F64" s="253" t="inlineStr">
+      <c r="F64" s="254" t="inlineStr">
         <is>
           <t>Geotechnics &amp; Society</t>
         </is>
       </c>
-      <c r="G64" s="243" t="n">
+      <c r="G64" s="244" t="n">
         <v>1</v>
       </c>
       <c r="H64" s="171" t="inlineStr">
@@ -25024,7 +26596,7 @@
           <t>Colombia</t>
         </is>
       </c>
-      <c r="I64" s="247" t="n">
+      <c r="I64" s="248" t="n">
         <v>46319</v>
       </c>
     </row>
@@ -25034,25 +26606,25 @@
           <t>Zazoom Social News</t>
         </is>
       </c>
-      <c r="B65" s="243" t="n">
+      <c r="B65" s="244" t="n">
         <v>1</v>
       </c>
-      <c r="C65" s="244">
+      <c r="C65" s="245">
         <f>SUMPRODUCT(Stories!$W$4:$W$103,--(Stories!$J$4:$J$103=$A65))</f>
         <v/>
       </c>
-      <c r="D65" s="245" t="n">
+      <c r="D65" s="246" t="n">
         <v>4</v>
       </c>
-      <c r="E65" s="243" t="n">
+      <c r="E65" s="244" t="n">
         <v>1</v>
       </c>
-      <c r="F65" s="246" t="inlineStr">
+      <c r="F65" s="247" t="inlineStr">
         <is>
           <t>Hazards &amp; Resilience</t>
         </is>
       </c>
-      <c r="G65" s="243" t="n">
+      <c r="G65" s="244" t="n">
         <v>1</v>
       </c>
       <c r="H65" s="171" t="inlineStr">
@@ -25060,7 +26632,7 @@
           <t>Italy</t>
         </is>
       </c>
-      <c r="I65" s="247" t="n">
+      <c r="I65" s="248" t="n">
         <v>46319</v>
       </c>
     </row>
@@ -25070,25 +26642,25 @@
           <t>Крыминформ</t>
         </is>
       </c>
-      <c r="B66" s="243" t="n">
+      <c r="B66" s="244" t="n">
         <v>1</v>
       </c>
-      <c r="C66" s="244">
+      <c r="C66" s="245">
         <f>SUMPRODUCT(Stories!$W$4:$W$103,--(Stories!$J$4:$J$103=$A66))</f>
         <v/>
       </c>
-      <c r="D66" s="245" t="n">
+      <c r="D66" s="246" t="n">
         <v>4</v>
       </c>
-      <c r="E66" s="243" t="n">
+      <c r="E66" s="244" t="n">
         <v>1</v>
       </c>
-      <c r="F66" s="250" t="inlineStr">
+      <c r="F66" s="251" t="inlineStr">
         <is>
           <t>Infrastructure &amp; the Underground City</t>
         </is>
       </c>
-      <c r="G66" s="243" t="n">
+      <c r="G66" s="244" t="n">
         <v>1</v>
       </c>
       <c r="H66" s="171" t="inlineStr">
@@ -25096,7 +26668,7 @@
           <t>Russia</t>
         </is>
       </c>
-      <c r="I66" s="247" t="n">
+      <c r="I66" s="248" t="n">
         <v>46319</v>
       </c>
     </row>
@@ -25106,25 +26678,25 @@
           <t>Самарская газета</t>
         </is>
       </c>
-      <c r="B67" s="243" t="n">
+      <c r="B67" s="244" t="n">
         <v>1</v>
       </c>
-      <c r="C67" s="244">
+      <c r="C67" s="245">
         <f>SUMPRODUCT(Stories!$W$4:$W$103,--(Stories!$J$4:$J$103=$A67))</f>
         <v/>
       </c>
-      <c r="D67" s="245" t="n">
+      <c r="D67" s="246" t="n">
         <v>3</v>
       </c>
-      <c r="E67" s="243" t="n">
+      <c r="E67" s="244" t="n">
         <v>0</v>
       </c>
-      <c r="F67" s="250" t="inlineStr">
+      <c r="F67" s="251" t="inlineStr">
         <is>
           <t>Infrastructure &amp; the Underground City</t>
         </is>
       </c>
-      <c r="G67" s="243" t="n">
+      <c r="G67" s="244" t="n">
         <v>1</v>
       </c>
       <c r="H67" s="171" t="inlineStr">
@@ -25132,7 +26704,7 @@
           <t>Russia</t>
         </is>
       </c>
-      <c r="I67" s="247" t="n">
+      <c r="I67" s="248" t="n">
         <v>46319</v>
       </c>
     </row>
@@ -25142,25 +26714,25 @@
           <t>千葉日報オンライン</t>
         </is>
       </c>
-      <c r="B68" s="243" t="n">
+      <c r="B68" s="244" t="n">
         <v>1</v>
       </c>
-      <c r="C68" s="244">
+      <c r="C68" s="245">
         <f>SUMPRODUCT(Stories!$W$4:$W$103,--(Stories!$J$4:$J$103=$A68))</f>
         <v/>
       </c>
-      <c r="D68" s="245" t="n">
+      <c r="D68" s="246" t="n">
         <v>4</v>
       </c>
-      <c r="E68" s="243" t="n">
+      <c r="E68" s="244" t="n">
         <v>1</v>
       </c>
-      <c r="F68" s="246" t="inlineStr">
+      <c r="F68" s="247" t="inlineStr">
         <is>
           <t>Hazards &amp; Resilience</t>
         </is>
       </c>
-      <c r="G68" s="243" t="n">
+      <c r="G68" s="244" t="n">
         <v>1</v>
       </c>
       <c r="H68" s="171" t="inlineStr">
@@ -25168,7 +26740,7 @@
           <t>Japan</t>
         </is>
       </c>
-      <c r="I68" s="247" t="n">
+      <c r="I68" s="248" t="n">
         <v>46320</v>
       </c>
     </row>
@@ -25178,25 +26750,25 @@
           <t>山陽新聞</t>
         </is>
       </c>
-      <c r="B69" s="243" t="n">
+      <c r="B69" s="244" t="n">
         <v>1</v>
       </c>
-      <c r="C69" s="244">
+      <c r="C69" s="245">
         <f>SUMPRODUCT(Stories!$W$4:$W$103,--(Stories!$J$4:$J$103=$A69))</f>
         <v/>
       </c>
-      <c r="D69" s="245" t="n">
+      <c r="D69" s="246" t="n">
         <v>5</v>
       </c>
-      <c r="E69" s="243" t="n">
+      <c r="E69" s="244" t="n">
         <v>1</v>
       </c>
-      <c r="F69" s="246" t="inlineStr">
+      <c r="F69" s="247" t="inlineStr">
         <is>
           <t>Hazards &amp; Resilience</t>
         </is>
       </c>
-      <c r="G69" s="243" t="n">
+      <c r="G69" s="244" t="n">
         <v>1</v>
       </c>
       <c r="H69" s="171" t="inlineStr">
@@ -25204,7 +26776,7 @@
           <t>Japan</t>
         </is>
       </c>
-      <c r="I69" s="247" t="n">
+      <c r="I69" s="248" t="n">
         <v>46320</v>
       </c>
     </row>
@@ -25214,25 +26786,25 @@
           <t>아시아경제</t>
         </is>
       </c>
-      <c r="B70" s="243" t="n">
+      <c r="B70" s="244" t="n">
         <v>1</v>
       </c>
-      <c r="C70" s="244">
+      <c r="C70" s="245">
         <f>SUMPRODUCT(Stories!$W$4:$W$103,--(Stories!$J$4:$J$103=$A70))</f>
         <v/>
       </c>
-      <c r="D70" s="245" t="n">
+      <c r="D70" s="246" t="n">
         <v>4</v>
       </c>
-      <c r="E70" s="243" t="n">
+      <c r="E70" s="244" t="n">
         <v>1</v>
       </c>
-      <c r="F70" s="250" t="inlineStr">
+      <c r="F70" s="251" t="inlineStr">
         <is>
           <t>Infrastructure &amp; the Underground City</t>
         </is>
       </c>
-      <c r="G70" s="243" t="n">
+      <c r="G70" s="244" t="n">
         <v>1</v>
       </c>
       <c r="H70" s="171" t="inlineStr">
@@ -25240,7 +26812,7 @@
           <t>United Kingdom</t>
         </is>
       </c>
-      <c r="I70" s="247" t="n">
+      <c r="I70" s="248" t="n">
         <v>46319</v>
       </c>
     </row>
@@ -25250,25 +26822,25 @@
           <t>아주경제</t>
         </is>
       </c>
-      <c r="B71" s="243" t="n">
+      <c r="B71" s="244" t="n">
         <v>1</v>
       </c>
-      <c r="C71" s="244">
+      <c r="C71" s="245">
         <f>SUMPRODUCT(Stories!$W$4:$W$103,--(Stories!$J$4:$J$103=$A71))</f>
         <v/>
       </c>
-      <c r="D71" s="245" t="n">
+      <c r="D71" s="246" t="n">
         <v>4</v>
       </c>
-      <c r="E71" s="243" t="n">
+      <c r="E71" s="244" t="n">
         <v>1</v>
       </c>
-      <c r="F71" s="250" t="inlineStr">
+      <c r="F71" s="251" t="inlineStr">
         <is>
           <t>Infrastructure &amp; the Underground City</t>
         </is>
       </c>
-      <c r="G71" s="243" t="n">
+      <c r="G71" s="244" t="n">
         <v>1</v>
       </c>
       <c r="H71" s="171" t="inlineStr">
@@ -25276,7 +26848,7 @@
           <t>South Korea</t>
         </is>
       </c>
-      <c r="I71" s="247" t="n">
+      <c r="I71" s="248" t="n">
         <v>46319</v>
       </c>
     </row>
@@ -25286,25 +26858,25 @@
           <t>충청신문</t>
         </is>
       </c>
-      <c r="B72" s="243" t="n">
+      <c r="B72" s="244" t="n">
         <v>1</v>
       </c>
-      <c r="C72" s="244">
+      <c r="C72" s="245">
         <f>SUMPRODUCT(Stories!$W$4:$W$103,--(Stories!$J$4:$J$103=$A72))</f>
         <v/>
       </c>
-      <c r="D72" s="245" t="n">
+      <c r="D72" s="246" t="n">
         <v>5</v>
       </c>
-      <c r="E72" s="243" t="n">
+      <c r="E72" s="244" t="n">
         <v>1</v>
       </c>
-      <c r="F72" s="250" t="inlineStr">
+      <c r="F72" s="251" t="inlineStr">
         <is>
           <t>Infrastructure &amp; the Underground City</t>
         </is>
       </c>
-      <c r="G72" s="243" t="n">
+      <c r="G72" s="244" t="n">
         <v>1</v>
       </c>
       <c r="H72" s="171" t="inlineStr">
@@ -25312,7 +26884,7 @@
           <t>South Korea</t>
         </is>
       </c>
-      <c r="I72" s="247" t="n">
+      <c r="I72" s="248" t="n">
         <v>46319</v>
       </c>
     </row>
@@ -25369,469 +26941,469 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="255" t="inlineStr">
+      <c r="A1" s="256" t="inlineStr">
         <is>
           <t>Theme selector</t>
         </is>
       </c>
-      <c r="B1" s="255" t="inlineStr">
+      <c r="B1" s="256" t="inlineStr">
         <is>
           <t>Use selector</t>
         </is>
       </c>
-      <c r="C1" s="255" t="inlineStr">
+      <c r="C1" s="256" t="inlineStr">
         <is>
           <t>Relevance selector</t>
         </is>
       </c>
-      <c r="D1" s="255" t="inlineStr">
+      <c r="D1" s="256" t="inlineStr">
         <is>
           <t>Window selector</t>
         </is>
       </c>
-      <c r="E1" s="255" t="inlineStr">
+      <c r="E1" s="256" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="G1" s="255" t="inlineStr">
+      <c r="G1" s="256" t="inlineStr">
         <is>
           <t>Setting</t>
         </is>
       </c>
-      <c r="H1" s="255" t="inlineStr">
+      <c r="H1" s="256" t="inlineStr">
         <is>
           <t>Value</t>
         </is>
       </c>
-      <c r="J1" s="255" t="inlineStr">
+      <c r="J1" s="256" t="inlineStr">
         <is>
           <t>Digest date</t>
         </is>
       </c>
-      <c r="K1" s="255" t="inlineStr">
+      <c r="K1" s="256" t="inlineStr">
         <is>
           <t>Stories in the selection</t>
         </is>
       </c>
-      <c r="M1" s="255" t="inlineStr">
+      <c r="M1" s="256" t="inlineStr">
         <is>
           <t>Rank</t>
         </is>
       </c>
-      <c r="N1" s="255" t="inlineStr">
+      <c r="N1" s="256" t="inlineStr">
         <is>
           <t>Key</t>
         </is>
       </c>
-      <c r="O1" s="255" t="inlineStr">
+      <c r="O1" s="256" t="inlineStr">
         <is>
           <t>Row in Stories</t>
         </is>
       </c>
-      <c r="P1" s="255" t="inlineStr">
+      <c r="P1" s="256" t="inlineStr">
         <is>
           <t>Article URL</t>
         </is>
       </c>
-      <c r="Q1" s="255" t="inlineStr">
+      <c r="Q1" s="256" t="inlineStr">
         <is>
           <t>Headline shown</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="256" t="inlineStr">
+      <c r="A2" s="257" t="inlineStr">
         <is>
           <t>All themes</t>
         </is>
       </c>
-      <c r="B2" s="256" t="inlineStr">
+      <c r="B2" s="257" t="inlineStr">
         <is>
           <t>All uses</t>
         </is>
       </c>
-      <c r="C2" s="256" t="inlineStr">
+      <c r="C2" s="257" t="inlineStr">
         <is>
           <t>Any</t>
         </is>
       </c>
-      <c r="D2" s="256" t="inlineStr">
+      <c r="D2" s="257" t="inlineStr">
         <is>
           <t>All windows</t>
         </is>
       </c>
-      <c r="E2" s="256" t="inlineStr">
+      <c r="E2" s="257" t="inlineStr">
         <is>
           <t>To review</t>
         </is>
       </c>
-      <c r="G2" s="256" t="inlineStr">
+      <c r="G2" s="257" t="inlineStr">
         <is>
           <t>Minimum relevance (number)</t>
         </is>
       </c>
-      <c r="H2" s="256">
+      <c r="H2" s="257">
         <f>IF(ISNUMBER(Dashboard!$K$5),Dashboard!$K$5,IFERROR(VALUE(Dashboard!$K$5),0))</f>
         <v/>
       </c>
-      <c r="J2" s="257" t="n">
+      <c r="J2" s="258" t="n">
         <v>46320</v>
       </c>
-      <c r="K2" s="256">
+      <c r="K2" s="257">
         <f>COUNTIFS(Stories!$W$4:$W$103,1,Stories!$K$4:$K$103,J2)</f>
         <v/>
       </c>
-      <c r="M2" s="256" t="n">
+      <c r="M2" s="257" t="n">
         <v>1</v>
       </c>
-      <c r="N2" s="258">
+      <c r="N2" s="259">
         <f>IFERROR(LARGE(Stories!$X$4:$X$103,M2),"")</f>
         <v/>
       </c>
-      <c r="O2" s="256">
+      <c r="O2" s="257">
         <f>IF(N2="","",MATCH(N2,Stories!$X$4:$X$103,0))</f>
         <v/>
       </c>
-      <c r="P2" s="256">
+      <c r="P2" s="257">
         <f>IF(O2="","",INDEX(Stories!$V$4:$V$103,O2)&amp;"")</f>
         <v/>
       </c>
-      <c r="Q2" s="256">
+      <c r="Q2" s="257">
         <f>IF(O2="","",IF(LEN(INDEX(Stories!$B$4:$B$103,O2))&gt;120,LEFT(INDEX(Stories!$B$4:$B$103,O2),118)&amp;"…",INDEX(Stories!$B$4:$B$103,O2)&amp;""))</f>
         <v/>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="256" t="inlineStr">
+      <c r="A3" s="257" t="inlineStr">
         <is>
           <t>Sustainability &amp; the Energy Transition</t>
         </is>
       </c>
-      <c r="B3" s="256" t="inlineStr">
+      <c r="B3" s="257" t="inlineStr">
         <is>
           <t>Feature lead</t>
         </is>
       </c>
-      <c r="C3" s="256" t="n">
+      <c r="C3" s="257" t="n">
         <v>3</v>
       </c>
-      <c r="D3" s="256" t="inlineStr">
+      <c r="D3" s="257" t="inlineStr">
         <is>
           <t>2026-Q4</t>
         </is>
       </c>
-      <c r="E3" s="256" t="inlineStr">
+      <c r="E3" s="257" t="inlineStr">
         <is>
           <t>Shortlisted</t>
         </is>
       </c>
-      <c r="G3" s="256" t="inlineStr">
+      <c r="G3" s="257" t="inlineStr">
         <is>
           <t>Daily digests in this workbook</t>
         </is>
       </c>
-      <c r="H3" s="256" t="n">
+      <c r="H3" s="257" t="n">
         <v>2</v>
       </c>
-      <c r="J3" s="257" t="n">
+      <c r="J3" s="258" t="n">
         <v>46319</v>
       </c>
-      <c r="K3" s="256">
+      <c r="K3" s="257">
         <f>COUNTIFS(Stories!$W$4:$W$103,1,Stories!$K$4:$K$103,J3)</f>
         <v/>
       </c>
-      <c r="M3" s="256" t="n">
+      <c r="M3" s="257" t="n">
         <v>2</v>
       </c>
-      <c r="N3" s="258">
+      <c r="N3" s="259">
         <f>IFERROR(LARGE(Stories!$X$4:$X$103,M3),"")</f>
         <v/>
       </c>
-      <c r="O3" s="256">
+      <c r="O3" s="257">
         <f>IF(N3="","",MATCH(N3,Stories!$X$4:$X$103,0))</f>
         <v/>
       </c>
-      <c r="P3" s="256">
+      <c r="P3" s="257">
         <f>IF(O3="","",INDEX(Stories!$V$4:$V$103,O3)&amp;"")</f>
         <v/>
       </c>
-      <c r="Q3" s="256">
+      <c r="Q3" s="257">
         <f>IF(O3="","",IF(LEN(INDEX(Stories!$B$4:$B$103,O3))&gt;120,LEFT(INDEX(Stories!$B$4:$B$103,O3),118)&amp;"…",INDEX(Stories!$B$4:$B$103,O3)&amp;""))</f>
         <v/>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="256" t="inlineStr">
+      <c r="A4" s="257" t="inlineStr">
         <is>
           <t>Digital Geotechnics</t>
         </is>
       </c>
-      <c r="B4" s="256" t="inlineStr">
+      <c r="B4" s="257" t="inlineStr">
         <is>
           <t>News brief</t>
         </is>
       </c>
-      <c r="C4" s="256" t="n">
+      <c r="C4" s="257" t="n">
         <v>4</v>
       </c>
-      <c r="E4" s="256" t="inlineStr">
+      <c r="E4" s="257" t="inlineStr">
         <is>
           <t>Commissioned</t>
         </is>
       </c>
-      <c r="G4" s="256" t="inlineStr">
+      <c r="G4" s="257" t="inlineStr">
         <is>
           <t>Stories in this workbook</t>
         </is>
       </c>
-      <c r="H4" s="256" t="n">
+      <c r="H4" s="257" t="n">
         <v>100</v>
       </c>
-      <c r="M4" s="256" t="n">
+      <c r="M4" s="257" t="n">
         <v>3</v>
       </c>
-      <c r="N4" s="258">
+      <c r="N4" s="259">
         <f>IFERROR(LARGE(Stories!$X$4:$X$103,M4),"")</f>
         <v/>
       </c>
-      <c r="O4" s="256">
+      <c r="O4" s="257">
         <f>IF(N4="","",MATCH(N4,Stories!$X$4:$X$103,0))</f>
         <v/>
       </c>
-      <c r="P4" s="256">
+      <c r="P4" s="257">
         <f>IF(O4="","",INDEX(Stories!$V$4:$V$103,O4)&amp;"")</f>
         <v/>
       </c>
-      <c r="Q4" s="256">
+      <c r="Q4" s="257">
         <f>IF(O4="","",IF(LEN(INDEX(Stories!$B$4:$B$103,O4))&gt;120,LEFT(INDEX(Stories!$B$4:$B$103,O4),118)&amp;"…",INDEX(Stories!$B$4:$B$103,O4)&amp;""))</f>
         <v/>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="256" t="inlineStr">
+      <c r="A5" s="257" t="inlineStr">
         <is>
           <t>Hazards &amp; Resilience</t>
         </is>
       </c>
-      <c r="B5" s="256" t="inlineStr">
+      <c r="B5" s="257" t="inlineStr">
         <is>
           <t>Academia-to-Industry topic</t>
         </is>
       </c>
-      <c r="C5" s="256" t="n">
+      <c r="C5" s="257" t="n">
         <v>5</v>
       </c>
-      <c r="E5" s="256" t="inlineStr">
+      <c r="E5" s="257" t="inlineStr">
         <is>
           <t>Published</t>
         </is>
       </c>
-      <c r="G5" s="256" t="inlineStr">
+      <c r="G5" s="257" t="inlineStr">
         <is>
           <t>No selector set</t>
         </is>
       </c>
-      <c r="H5" s="256">
+      <c r="H5" s="257">
         <f>AND(OR(Dashboard!$B$5="All themes",Dashboard!$B$5=""),OR(Dashboard!$G$5="All uses",Dashboard!$G$5=""),$H$2=0,OR(Dashboard!$N$5="All windows",Dashboard!$N$5=""))</f>
         <v/>
       </c>
-      <c r="M5" s="256" t="n">
+      <c r="M5" s="257" t="n">
         <v>4</v>
       </c>
-      <c r="N5" s="258">
+      <c r="N5" s="259">
         <f>IFERROR(LARGE(Stories!$X$4:$X$103,M5),"")</f>
         <v/>
       </c>
-      <c r="O5" s="256">
+      <c r="O5" s="257">
         <f>IF(N5="","",MATCH(N5,Stories!$X$4:$X$103,0))</f>
         <v/>
       </c>
-      <c r="P5" s="256">
+      <c r="P5" s="257">
         <f>IF(O5="","",INDEX(Stories!$V$4:$V$103,O5)&amp;"")</f>
         <v/>
       </c>
-      <c r="Q5" s="256">
+      <c r="Q5" s="257">
         <f>IF(O5="","",IF(LEN(INDEX(Stories!$B$4:$B$103,O5))&gt;120,LEFT(INDEX(Stories!$B$4:$B$103,O5),118)&amp;"…",INDEX(Stories!$B$4:$B$103,O5)&amp;""))</f>
         <v/>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="256" t="inlineStr">
+      <c r="A6" s="257" t="inlineStr">
         <is>
           <t>Ground Improvement &amp; Innovation</t>
         </is>
       </c>
-      <c r="B6" s="256" t="inlineStr">
+      <c r="B6" s="257" t="inlineStr">
         <is>
           <t>Regional insight</t>
         </is>
       </c>
-      <c r="E6" s="256" t="inlineStr">
+      <c r="E6" s="257" t="inlineStr">
         <is>
           <t>Not used</t>
         </is>
       </c>
-      <c r="G6" s="256" t="inlineStr">
+      <c r="G6" s="257" t="inlineStr">
         <is>
           <t>Stories in the selection</t>
         </is>
       </c>
-      <c r="H6" s="256">
+      <c r="H6" s="257">
         <f>COUNTIF(Stories!$W$4:$W$103,1)</f>
         <v/>
       </c>
-      <c r="M6" s="256" t="n">
+      <c r="M6" s="257" t="n">
         <v>5</v>
       </c>
-      <c r="N6" s="258">
+      <c r="N6" s="259">
         <f>IFERROR(LARGE(Stories!$X$4:$X$103,M6),"")</f>
         <v/>
       </c>
-      <c r="O6" s="256">
+      <c r="O6" s="257">
         <f>IF(N6="","",MATCH(N6,Stories!$X$4:$X$103,0))</f>
         <v/>
       </c>
-      <c r="P6" s="256">
+      <c r="P6" s="257">
         <f>IF(O6="","",INDEX(Stories!$V$4:$V$103,O6)&amp;"")</f>
         <v/>
       </c>
-      <c r="Q6" s="256">
+      <c r="Q6" s="257">
         <f>IF(O6="","",IF(LEN(INDEX(Stories!$B$4:$B$103,O6))&gt;120,LEFT(INDEX(Stories!$B$4:$B$103,O6),118)&amp;"…",INDEX(Stories!$B$4:$B$103,O6)&amp;""))</f>
         <v/>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="256" t="inlineStr">
+      <c r="A7" s="257" t="inlineStr">
         <is>
           <t>Infrastructure &amp; the Underground City</t>
         </is>
       </c>
-      <c r="B7" s="256" t="inlineStr">
+      <c r="B7" s="257" t="inlineStr">
         <is>
           <t>Watch only</t>
         </is>
       </c>
-      <c r="M7" s="256" t="n">
+      <c r="M7" s="257" t="n">
         <v>6</v>
       </c>
-      <c r="N7" s="258">
+      <c r="N7" s="259">
         <f>IFERROR(LARGE(Stories!$X$4:$X$103,M7),"")</f>
         <v/>
       </c>
-      <c r="O7" s="256">
+      <c r="O7" s="257">
         <f>IF(N7="","",MATCH(N7,Stories!$X$4:$X$103,0))</f>
         <v/>
       </c>
-      <c r="P7" s="256">
+      <c r="P7" s="257">
         <f>IF(O7="","",INDEX(Stories!$V$4:$V$103,O7)&amp;"")</f>
         <v/>
       </c>
-      <c r="Q7" s="256">
+      <c r="Q7" s="257">
         <f>IF(O7="","",IF(LEN(INDEX(Stories!$B$4:$B$103,O7))&gt;120,LEFT(INDEX(Stories!$B$4:$B$103,O7),118)&amp;"…",INDEX(Stories!$B$4:$B$103,O7)&amp;""))</f>
         <v/>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="256" t="inlineStr">
+      <c r="A8" s="257" t="inlineStr">
         <is>
           <t>Offshore, Coasts &amp; Water</t>
         </is>
       </c>
-      <c r="M8" s="256" t="n">
+      <c r="M8" s="257" t="n">
         <v>7</v>
       </c>
-      <c r="N8" s="258">
+      <c r="N8" s="259">
         <f>IFERROR(LARGE(Stories!$X$4:$X$103,M8),"")</f>
         <v/>
       </c>
-      <c r="O8" s="256">
+      <c r="O8" s="257">
         <f>IF(N8="","",MATCH(N8,Stories!$X$4:$X$103,0))</f>
         <v/>
       </c>
-      <c r="P8" s="256">
+      <c r="P8" s="257">
         <f>IF(O8="","",INDEX(Stories!$V$4:$V$103,O8)&amp;"")</f>
         <v/>
       </c>
-      <c r="Q8" s="256">
+      <c r="Q8" s="257">
         <f>IF(O8="","",IF(LEN(INDEX(Stories!$B$4:$B$103,O8))&gt;120,LEFT(INDEX(Stories!$B$4:$B$103,O8),118)&amp;"…",INDEX(Stories!$B$4:$B$103,O8)&amp;""))</f>
         <v/>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="256" t="inlineStr">
+      <c r="A9" s="257" t="inlineStr">
         <is>
           <t>Characterisation &amp; Modelling</t>
         </is>
       </c>
-      <c r="M9" s="256" t="n">
+      <c r="M9" s="257" t="n">
         <v>8</v>
       </c>
-      <c r="N9" s="258">
+      <c r="N9" s="259">
         <f>IFERROR(LARGE(Stories!$X$4:$X$103,M9),"")</f>
         <v/>
       </c>
-      <c r="O9" s="256">
+      <c r="O9" s="257">
         <f>IF(N9="","",MATCH(N9,Stories!$X$4:$X$103,0))</f>
         <v/>
       </c>
-      <c r="P9" s="256">
+      <c r="P9" s="257">
         <f>IF(O9="","",INDEX(Stories!$V$4:$V$103,O9)&amp;"")</f>
         <v/>
       </c>
-      <c r="Q9" s="256">
+      <c r="Q9" s="257">
         <f>IF(O9="","",IF(LEN(INDEX(Stories!$B$4:$B$103,O9))&gt;120,LEFT(INDEX(Stories!$B$4:$B$103,O9),118)&amp;"…",INDEX(Stories!$B$4:$B$103,O9)&amp;""))</f>
         <v/>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="256" t="inlineStr">
+      <c r="A10" s="257" t="inlineStr">
         <is>
           <t>Geotechnics &amp; Society</t>
         </is>
       </c>
-      <c r="M10" s="256" t="n">
+      <c r="M10" s="257" t="n">
         <v>9</v>
       </c>
-      <c r="N10" s="258">
+      <c r="N10" s="259">
         <f>IFERROR(LARGE(Stories!$X$4:$X$103,M10),"")</f>
         <v/>
       </c>
-      <c r="O10" s="256">
+      <c r="O10" s="257">
         <f>IF(N10="","",MATCH(N10,Stories!$X$4:$X$103,0))</f>
         <v/>
       </c>
-      <c r="P10" s="256">
+      <c r="P10" s="257">
         <f>IF(O10="","",INDEX(Stories!$V$4:$V$103,O10)&amp;"")</f>
         <v/>
       </c>
-      <c r="Q10" s="256">
+      <c r="Q10" s="257">
         <f>IF(O10="","",IF(LEN(INDEX(Stories!$B$4:$B$103,O10))&gt;120,LEFT(INDEX(Stories!$B$4:$B$103,O10),118)&amp;"…",INDEX(Stories!$B$4:$B$103,O10)&amp;""))</f>
         <v/>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="256" t="inlineStr">
+      <c r="A11" s="257" t="inlineStr">
         <is>
           <t>General</t>
         </is>
       </c>
-      <c r="M11" s="256" t="n">
+      <c r="M11" s="257" t="n">
         <v>10</v>
       </c>
-      <c r="N11" s="258">
+      <c r="N11" s="259">
         <f>IFERROR(LARGE(Stories!$X$4:$X$103,M11),"")</f>
         <v/>
       </c>
-      <c r="O11" s="256">
+      <c r="O11" s="257">
         <f>IF(N11="","",MATCH(N11,Stories!$X$4:$X$103,0))</f>
         <v/>
       </c>
-      <c r="P11" s="256">
+      <c r="P11" s="257">
         <f>IF(O11="","",INDEX(Stories!$V$4:$V$103,O11)&amp;"")</f>
         <v/>
       </c>
-      <c r="Q11" s="256">
+      <c r="Q11" s="257">
         <f>IF(O11="","",IF(LEN(INDEX(Stories!$B$4:$B$103,O11))&gt;120,LEFT(INDEX(Stories!$B$4:$B$103,O11),118)&amp;"…",INDEX(Stories!$B$4:$B$103,O11)&amp;""))</f>
         <v/>
       </c>

--- a/docs/exports/geotech-news-archive.xlsx
+++ b/docs/exports/geotech-news-archive.xlsx
@@ -17417,7 +17417,7 @@
         </is>
       </c>
     </row>
-    <row r="26" outlineLevel="1" ht="66.5" customHeight="1">
+    <row r="26" outlineLevel="1" ht="104" customHeight="1">
       <c r="A26" s="190" t="n">
         <v>57</v>
       </c>
@@ -17908,7 +17908,7 @@
         </is>
       </c>
     </row>
-    <row r="38" outlineLevel="1" ht="66.5" customHeight="1">
+    <row r="38" outlineLevel="1" ht="79" customHeight="1">
       <c r="A38" s="190" t="n">
         <v>70</v>
       </c>
@@ -18031,7 +18031,7 @@
         </is>
       </c>
     </row>
-    <row r="41" outlineLevel="1" ht="66.5" customHeight="1">
+    <row r="41" outlineLevel="1" ht="79" customHeight="1">
       <c r="A41" s="190" t="n">
         <v>17</v>
       </c>
@@ -18582,7 +18582,7 @@
         </is>
       </c>
     </row>
-    <row r="56" outlineLevel="1" ht="66.5" customHeight="1">
+    <row r="56" outlineLevel="1" ht="79" customHeight="1">
       <c r="A56" s="190" t="n">
         <v>51</v>
       </c>
@@ -18768,7 +18768,7 @@
         </is>
       </c>
     </row>
-    <row r="62" outlineLevel="1" ht="66.5" customHeight="1">
+    <row r="62" outlineLevel="1" ht="79" customHeight="1">
       <c r="A62" s="190" t="n">
         <v>74</v>
       </c>
@@ -19013,7 +19013,7 @@
         </is>
       </c>
     </row>
-    <row r="68" outlineLevel="1" ht="66.5" customHeight="1">
+    <row r="68" outlineLevel="1" ht="91.5" customHeight="1">
       <c r="A68" s="190" t="n">
         <v>83</v>
       </c>
@@ -19829,7 +19829,7 @@
         </is>
       </c>
     </row>
-    <row r="88" outlineLevel="1" ht="66.5" customHeight="1">
+    <row r="88" outlineLevel="1" ht="91.5" customHeight="1">
       <c r="A88" s="190" t="n">
         <v>44</v>
       </c>

--- a/docs/exports/geotech-news-archive.xlsx
+++ b/docs/exports/geotech-news-archive.xlsx
@@ -7448,7 +7448,7 @@
       </c>
       <c r="B13" s="160" t="inlineStr">
         <is>
-          <t>Deslizamiento de talud afecta sótanos y locales de plaza comercial en Cuajimalpa</t>
+          <t>Slope collapse affects basements and shops of a shopping plaza in Cuajimalpa</t>
         </is>
       </c>
       <c r="C13" s="161" t="inlineStr">
@@ -7484,7 +7484,11 @@
       <c r="K13" s="168" t="n">
         <v>46321</v>
       </c>
-      <c r="L13" s="167" t="n"/>
+      <c r="L13" s="167" t="inlineStr">
+        <is>
+          <t>Deslizamiento de talud afecta sótanos y locales de plaza comercial en Cuajimalpa</t>
+        </is>
+      </c>
       <c r="M13" s="167" t="inlineStr">
         <is>
           <t>Mexico City Protección Civil and the borough's building authority</t>
@@ -7542,7 +7546,7 @@
       </c>
       <c r="B14" s="160" t="inlineStr">
         <is>
-          <t>Fuerte deslave en Centro Santa Fe: colapsa talud de 30 metros y afecta locales</t>
+          <t>Heavy landslide at Centro Santa Fe: 30-meter slope collapses and affects shops</t>
         </is>
       </c>
       <c r="C14" s="161" t="inlineStr">
@@ -7578,7 +7582,11 @@
       <c r="K14" s="168" t="n">
         <v>46321</v>
       </c>
-      <c r="L14" s="167" t="n"/>
+      <c r="L14" s="167" t="inlineStr">
+        <is>
+          <t>Fuerte deslave en Centro Santa Fe: colapsa talud de 30 metros y afecta locales</t>
+        </is>
+      </c>
       <c r="M14" s="167" t="inlineStr">
         <is>
           <t>Mexico City Protección Civil and the developer's geotechnical consultant</t>
@@ -8028,7 +8036,7 @@
       </c>
       <c r="B19" s="160" t="inlineStr">
         <is>
-          <t>В Пенанге оползень обрушился на дом, погиб 73-летний мужчина — Channel NewsAsia</t>
+          <t>In Penang, a landslide hit a house and killed a 73-year-old man — Channel NewsAsia</t>
         </is>
       </c>
       <c r="C19" s="161" t="inlineStr">
@@ -8064,7 +8072,11 @@
       <c r="K19" s="168" t="n">
         <v>46321</v>
       </c>
-      <c r="L19" s="167" t="n"/>
+      <c r="L19" s="167" t="inlineStr">
+        <is>
+          <t>В Пенанге оползень обрушился на дом, погиб 73-летний мужчина — Channel NewsAsia</t>
+        </is>
+      </c>
       <c r="M19" s="167" t="inlineStr">
         <is>
           <t>Penang state authorities and Penang Municipal Council (MBPP)</t>
@@ -8126,7 +8138,7 @@
       </c>
       <c r="B20" s="160" t="inlineStr">
         <is>
-          <t>Fuerte oleaje provoca un socavón y daños en un malecón emblemático de México</t>
+          <t>Strong waves cause a sinkhole and damage to an emblematic seafront promenade in Mexico</t>
         </is>
       </c>
       <c r="C20" s="179" t="inlineStr">
@@ -8162,7 +8174,11 @@
       <c r="K20" s="168" t="n">
         <v>46321</v>
       </c>
-      <c r="L20" s="167" t="n"/>
+      <c r="L20" s="167" t="inlineStr">
+        <is>
+          <t>Fuerte oleaje provoca un socavón y daños en un malecón emblemático de México</t>
+        </is>
+      </c>
       <c r="M20" s="167" t="inlineStr">
         <is>
           <t>Mazatlán municipal government and Sinaloa civil protection</t>
@@ -8224,7 +8240,7 @@
       </c>
       <c r="B21" s="160" t="inlineStr">
         <is>
-          <t>Inician reparación de socavón provocado por fuerte oleaje junto al Monumento a la Mujer Mazatleca</t>
+          <t>Repair of sinkhole caused by strong waves begins next to the Monument to the Mazatlan Woman</t>
         </is>
       </c>
       <c r="C21" s="179" t="inlineStr">
@@ -8260,7 +8276,11 @@
       <c r="K21" s="168" t="n">
         <v>46321</v>
       </c>
-      <c r="L21" s="167" t="n"/>
+      <c r="L21" s="167" t="inlineStr">
+        <is>
+          <t>Inician reparación de socavón provocado por fuerte oleaje junto al Monumento a la Mujer Mazatleca</t>
+        </is>
+      </c>
       <c r="M21" s="167" t="inlineStr">
         <is>
           <t>Mazatlán municipal government</t>
@@ -8322,7 +8342,7 @@
       </c>
       <c r="B22" s="160" t="inlineStr">
         <is>
-          <t>Ayuntamiento atiende más de 50 socavones su reparación cuesta hasta 700 mil pesos por punto</t>
+          <t>City council attends to over 50 sinkholes; repair costs up to 700,000 pesos per point</t>
         </is>
       </c>
       <c r="C22" s="177" t="inlineStr">
@@ -8358,7 +8378,11 @@
       <c r="K22" s="168" t="n">
         <v>46321</v>
       </c>
-      <c r="L22" s="167" t="n"/>
+      <c r="L22" s="167" t="inlineStr">
+        <is>
+          <t>Ayuntamiento atiende más de 50 socavones su reparación cuesta hasta 700 mil pesos por punto</t>
+        </is>
+      </c>
       <c r="M22" s="167" t="inlineStr">
         <is>
           <t>San Luis Potosí municipal government</t>
@@ -8416,7 +8440,7 @@
       </c>
       <c r="B23" s="160" t="inlineStr">
         <is>
-          <t>Ica: nuevo huaico podría repetir el bloqueo de la Panamericana Sur por falta de puente en Ocucaje</t>
+          <t>Ica: new debris flow could repeat blockage of the Panamericana Sur due to lack of bridge in Ocucaje</t>
         </is>
       </c>
       <c r="C23" s="177" t="inlineStr">
@@ -8452,7 +8476,11 @@
       <c r="K23" s="168" t="n">
         <v>46321</v>
       </c>
-      <c r="L23" s="167" t="n"/>
+      <c r="L23" s="167" t="inlineStr">
+        <is>
+          <t>Ica: nuevo huaico podría repetir el bloqueo de la Panamericana Sur por falta de puente en Ocucaje</t>
+        </is>
+      </c>
       <c r="M23" s="167" t="inlineStr">
         <is>
           <t>Provías Nacional (MTC)</t>
@@ -8510,7 +8538,7 @@
       </c>
       <c r="B24" s="160" t="inlineStr">
         <is>
-          <t>Panamá interviene antigua mina de oro tras deslizamiento que amenaza fuentes de agua</t>
+          <t>Panama intervenes at former gold mine after landslide threatens water sources</t>
         </is>
       </c>
       <c r="C24" s="161" t="inlineStr">
@@ -8546,7 +8574,11 @@
       <c r="K24" s="168" t="n">
         <v>46321</v>
       </c>
-      <c r="L24" s="167" t="n"/>
+      <c r="L24" s="167" t="inlineStr">
+        <is>
+          <t>Panamá interviene antigua mina de oro tras deslizamiento que amenaza fuentes de agua</t>
+        </is>
+      </c>
       <c r="M24" s="167" t="inlineStr">
         <is>
           <t>Panama's environment ministry (MiAmbiente)</t>
@@ -8604,7 +8636,7 @@
       </c>
       <c r="B25" s="160" t="inlineStr">
         <is>
-          <t>Socavón amenaza con dejar incomunicadas a dos barriadas en Arraiján</t>
+          <t>Sinkhole threatens to isolate two neighborhoods in Arraiján</t>
         </is>
       </c>
       <c r="C25" s="161" t="inlineStr">
@@ -8640,7 +8672,11 @@
       <c r="K25" s="168" t="n">
         <v>46321</v>
       </c>
-      <c r="L25" s="167" t="n"/>
+      <c r="L25" s="167" t="inlineStr">
+        <is>
+          <t>Socavón amenaza con dejar incomunicadas a dos barriadas en Arraiján</t>
+        </is>
+      </c>
       <c r="M25" s="167" t="inlineStr">
         <is>
           <t>Arraiján municipality and Panama's public works ministry (MOP)</t>
@@ -8698,7 +8734,7 @@
       </c>
       <c r="B26" s="160" t="inlineStr">
         <is>
-          <t>Reportan caída de cuatro huéspedes en socavón de hotel Occidental de Cozumel</t>
+          <t>Four guests reportedly fall into sinkhole at Occidental hotel in Cozumel</t>
         </is>
       </c>
       <c r="C26" s="161" t="inlineStr">
@@ -8734,7 +8770,11 @@
       <c r="K26" s="168" t="n">
         <v>46321</v>
       </c>
-      <c r="L26" s="167" t="n"/>
+      <c r="L26" s="167" t="inlineStr">
+        <is>
+          <t>Reportan caída de cuatro huéspedes en socavón de hotel Occidental de Cozumel</t>
+        </is>
+      </c>
       <c r="M26" s="167" t="inlineStr">
         <is>
           <t>Hotel Occidental Cozumel management and Quintana Roo civil protection</t>
@@ -8796,7 +8836,7 @@
       </c>
       <c r="B27" s="160" t="inlineStr">
         <is>
-          <t>Alertas SMS, señaléticas y rutas de evacuación: el plan de La Reina ante futuros aluviones</t>
+          <t>SMS alerts, signage and evacuation routes: La Reina's plan for future floods</t>
         </is>
       </c>
       <c r="C27" s="161" t="inlineStr">
@@ -8832,7 +8872,11 @@
       <c r="K27" s="168" t="n">
         <v>46321</v>
       </c>
-      <c r="L27" s="167" t="n"/>
+      <c r="L27" s="167" t="inlineStr">
+        <is>
+          <t>Alertas SMS, señaléticas y rutas de evacuación: el plan de La Reina ante futuros aluviones</t>
+        </is>
+      </c>
       <c r="M27" s="167" t="inlineStr">
         <is>
           <t>La Reina municipality and Senapred</t>
@@ -8890,7 +8934,7 @@
       </c>
       <c r="B28" s="160" t="inlineStr">
         <is>
-          <t>ANA instala 12 barreras para reducir el impacto de huaicos en Lima y Huarochirí</t>
+          <t>ANA installs 12 barriers to reduce impact of debris flows in Lima and Huarochirí</t>
         </is>
       </c>
       <c r="C28" s="161" t="inlineStr">
@@ -8926,7 +8970,11 @@
       <c r="K28" s="168" t="n">
         <v>46321</v>
       </c>
-      <c r="L28" s="167" t="n"/>
+      <c r="L28" s="167" t="inlineStr">
+        <is>
+          <t>ANA instala 12 barreras para reducir el impacto de huaicos en Lima y Huarochirí</t>
+        </is>
+      </c>
       <c r="M28" s="167" t="inlineStr">
         <is>
           <t>Autoridad Nacional del Agua (ANA)</t>
@@ -9078,7 +9126,7 @@
       </c>
       <c r="B30" s="160" t="inlineStr">
         <is>
-          <t>Anuncia Ayuntamiento de Cuernavaca cierre temporal de Avenida Universidad por revisión de hundimiento</t>
+          <t>Cuernavaca city council announces temporary closure of Avenida Universidad for subsidence review</t>
         </is>
       </c>
       <c r="C30" s="177" t="inlineStr">
@@ -9114,7 +9162,11 @@
       <c r="K30" s="168" t="n">
         <v>46321</v>
       </c>
-      <c r="L30" s="167" t="n"/>
+      <c r="L30" s="167" t="inlineStr">
+        <is>
+          <t>Anuncia Ayuntamiento de Cuernavaca cierre temporal de Avenida Universidad por revisión de hundimiento</t>
+        </is>
+      </c>
       <c r="M30" s="167" t="inlineStr">
         <is>
           <t>the Cuernavaca city council</t>
@@ -9356,7 +9408,7 @@
       </c>
       <c r="B33" s="160" t="inlineStr">
         <is>
-          <t>Concentrer les ressources sur le relogement des personnes vivant dans les zones à risque de glissements de terrain.</t>
+          <t>Focus resources on relocating people living in areas at risk of landslides.</t>
         </is>
       </c>
       <c r="C33" s="183" t="inlineStr">
@@ -9392,7 +9444,11 @@
       <c r="K33" s="168" t="n">
         <v>46321</v>
       </c>
-      <c r="L33" s="167" t="n"/>
+      <c r="L33" s="167" t="inlineStr">
+        <is>
+          <t>Concentrer les ressources sur le relogement des personnes vivant dans les zones à risque de glissements de terrain.</t>
+        </is>
+      </c>
       <c r="M33" s="167" t="inlineStr">
         <is>
           <t>Vietnam's ministry responsible for disaster prevention</t>
@@ -9736,7 +9792,7 @@
       </c>
       <c r="B37" s="160" t="inlineStr">
         <is>
-          <t>Vía Alóag-Santo Domingo tiene paso controlado tras deslizamiento en el km 35</t>
+          <t>Alóag-Santo Domingo road has controlled passage after landslide at km 35</t>
         </is>
       </c>
       <c r="C37" s="177" t="inlineStr">
@@ -9772,7 +9828,11 @@
       <c r="K37" s="168" t="n">
         <v>46321</v>
       </c>
-      <c r="L37" s="167" t="n"/>
+      <c r="L37" s="167" t="inlineStr">
+        <is>
+          <t>Vía Alóag-Santo Domingo tiene paso controlado tras deslizamiento en el km 35</t>
+        </is>
+      </c>
       <c r="M37" s="167" t="inlineStr">
         <is>
           <t>Ecuador's transport ministry (MTOP)</t>
@@ -9830,7 +9890,7 @@
       </c>
       <c r="B38" s="160" t="inlineStr">
         <is>
-          <t>Vía Riobamba–Penipe–Baños fue habilitada tras deslizamiento</t>
+          <t>Riobamba–Penipe–Baños road reopened after landslide</t>
         </is>
       </c>
       <c r="C38" s="177" t="inlineStr">
@@ -9866,7 +9926,11 @@
       <c r="K38" s="168" t="n">
         <v>46321</v>
       </c>
-      <c r="L38" s="167" t="n"/>
+      <c r="L38" s="167" t="inlineStr">
+        <is>
+          <t>Vía Riobamba–Penipe–Baños fue habilitada tras deslizamiento</t>
+        </is>
+      </c>
       <c r="M38" s="167" t="inlineStr">
         <is>
           <t>Chimborazo provincial road authority (MTOP)</t>
@@ -9924,7 +9988,7 @@
       </c>
       <c r="B39" s="160" t="inlineStr">
         <is>
-          <t>Áncash: deslizamiento de tierra dañó 15 metros de vía vecinal en Shupluy -</t>
+          <t>Áncash: landslide damaged 15 meters of local road in Shupluy</t>
         </is>
       </c>
       <c r="C39" s="177" t="inlineStr">
@@ -9960,7 +10024,11 @@
       <c r="K39" s="168" t="n">
         <v>46321</v>
       </c>
-      <c r="L39" s="167" t="n"/>
+      <c r="L39" s="167" t="inlineStr">
+        <is>
+          <t>Áncash: deslizamiento de tierra dañó 15 metros de vía vecinal en Shupluy -</t>
+        </is>
+      </c>
       <c r="M39" s="167" t="inlineStr">
         <is>
           <t>Áncash regional government road authority</t>
@@ -10018,7 +10086,7 @@
       </c>
       <c r="B40" s="160" t="inlineStr">
         <is>
-          <t>Camioneta varada en socavón de la colonia Fronteriza en Juárez</t>
+          <t>Pickup truck stranded in sinkhole in Fronteriza neighborhood in Juárez</t>
         </is>
       </c>
       <c r="C40" s="177" t="inlineStr">
@@ -10054,7 +10122,11 @@
       <c r="K40" s="168" t="n">
         <v>46321</v>
       </c>
-      <c r="L40" s="167" t="n"/>
+      <c r="L40" s="167" t="inlineStr">
+        <is>
+          <t>Camioneta varada en socavón de la colonia Fronteriza en Juárez</t>
+        </is>
+      </c>
       <c r="M40" s="167" t="inlineStr">
         <is>
           <t>Ciudad Juárez municipal government</t>
@@ -10112,7 +10184,7 @@
       </c>
       <c r="B41" s="160" t="inlineStr">
         <is>
-          <t>Mañana inicia la reparación del socavón en el puente Terrazas del Valle</t>
+          <t>Repair of sinkhole on Terrazas del Valle bridge starts tomorrow</t>
         </is>
       </c>
       <c r="C41" s="177" t="inlineStr">
@@ -10148,7 +10220,11 @@
       <c r="K41" s="168" t="n">
         <v>46321</v>
       </c>
-      <c r="L41" s="167" t="n"/>
+      <c r="L41" s="167" t="inlineStr">
+        <is>
+          <t>Mañana inicia la reparación del socavón en el puente Terrazas del Valle</t>
+        </is>
+      </c>
       <c r="M41" s="167" t="inlineStr">
         <is>
           <t>municipal public works department</t>
@@ -10210,7 +10286,7 @@
       </c>
       <c r="B42" s="160" t="inlineStr">
         <is>
-          <t>Fortes chuvas provocam deslizamento de terra em acesso da SP-294 em Garça</t>
+          <t>Heavy rains cause landslide on access to SP-294 in Garça</t>
         </is>
       </c>
       <c r="C42" s="177" t="inlineStr">
@@ -10246,7 +10322,11 @@
       <c r="K42" s="168" t="n">
         <v>46321</v>
       </c>
-      <c r="L42" s="167" t="n"/>
+      <c r="L42" s="167" t="inlineStr">
+        <is>
+          <t>Fortes chuvas provocam deslizamento de terra em acesso da SP-294 em Garça</t>
+        </is>
+      </c>
       <c r="M42" s="167" t="inlineStr">
         <is>
           <t>DER-SP (São Paulo state roads department)</t>
@@ -10304,7 +10384,7 @@
       </c>
       <c r="B43" s="160" t="inlineStr">
         <is>
-          <t>Deslizamento de terra e árvores bloqueia rodovia entre Tatuí e Boituva</t>
+          <t>Landslide and trees block highway between Tatuí and Boituva</t>
         </is>
       </c>
       <c r="C43" s="177" t="inlineStr">
@@ -10340,7 +10420,11 @@
       <c r="K43" s="168" t="n">
         <v>46321</v>
       </c>
-      <c r="L43" s="167" t="n"/>
+      <c r="L43" s="167" t="inlineStr">
+        <is>
+          <t>Deslizamento de terra e árvores bloqueia rodovia entre Tatuí e Boituva</t>
+        </is>
+      </c>
       <c r="M43" s="167" t="inlineStr">
         <is>
           <t>DER-SP (São Paulo state roads department)</t>
@@ -10398,7 +10482,7 @@
       </c>
       <c r="B44" s="160" t="inlineStr">
         <is>
-          <t>Deslizamento de terra interdita rodovia entre Realeza e Planalto</t>
+          <t>Landslide closes highway between Realeza and Planalto</t>
         </is>
       </c>
       <c r="C44" s="177" t="inlineStr">
@@ -10434,7 +10518,11 @@
       <c r="K44" s="168" t="n">
         <v>46321</v>
       </c>
-      <c r="L44" s="167" t="n"/>
+      <c r="L44" s="167" t="inlineStr">
+        <is>
+          <t>Deslizamento de terra interdita rodovia entre Realeza e Planalto</t>
+        </is>
+      </c>
       <c r="M44" s="167" t="inlineStr">
         <is>
           <t>DER-PR (Paraná state roads department)</t>
@@ -10492,7 +10580,7 @@
       </c>
       <c r="B45" s="160" t="inlineStr">
         <is>
-          <t>BR-277 é liberada após deslizamento de terra na Serra da Esperança, em Guarapuava</t>
+          <t>BR-277 reopened after landslide in Serra da Esperança, in Guarapuava</t>
         </is>
       </c>
       <c r="C45" s="177" t="inlineStr">
@@ -10528,7 +10616,11 @@
       <c r="K45" s="168" t="n">
         <v>46321</v>
       </c>
-      <c r="L45" s="167" t="n"/>
+      <c r="L45" s="167" t="inlineStr">
+        <is>
+          <t>BR-277 é liberada após deslizamento de terra na Serra da Esperança, em Guarapuava</t>
+        </is>
+      </c>
       <c r="M45" s="167" t="inlineStr">
         <is>
           <t>DNIT and the BR-277 concessionaire</t>
@@ -10586,7 +10678,7 @@
       </c>
       <c r="B46" s="160" t="inlineStr">
         <is>
-          <t>Deslizamento de terra no Km 43, em Cajamar, coloca motoristas em alerta</t>
+          <t>Landslide at Km 43 in Cajamar puts drivers on alert</t>
         </is>
       </c>
       <c r="C46" s="177" t="inlineStr">
@@ -10622,7 +10714,11 @@
       <c r="K46" s="168" t="n">
         <v>46321</v>
       </c>
-      <c r="L46" s="167" t="n"/>
+      <c r="L46" s="167" t="inlineStr">
+        <is>
+          <t>Deslizamento de terra no Km 43, em Cajamar, coloca motoristas em alerta</t>
+        </is>
+      </c>
       <c r="M46" s="167" t="inlineStr">
         <is>
           <t>DER-SP and the road concessionaire</t>
@@ -13982,7 +14078,7 @@
       </c>
       <c r="B82" s="160" t="inlineStr">
         <is>
-          <t>Un socavón en Cerro se llena de agua y amenaza a peatones y conductores tras las lluvias</t>
+          <t>A sinkhole in Cerro fills with water and threatens pedestrians and drivers after rains</t>
         </is>
       </c>
       <c r="C82" s="177" t="inlineStr">
@@ -14018,7 +14114,11 @@
       <c r="K82" s="168" t="n">
         <v>46320</v>
       </c>
-      <c r="L82" s="167" t="n"/>
+      <c r="L82" s="167" t="inlineStr">
+        <is>
+          <t>Un socavón en Cerro se llena de agua y amenaza a peatones y conductores tras las lluvias</t>
+        </is>
+      </c>
       <c r="M82" s="167" t="n"/>
       <c r="N82" s="169" t="n"/>
       <c r="O82" s="167" t="inlineStr">
@@ -16146,7 +16246,7 @@
       </c>
       <c r="B106" s="160" t="inlineStr">
         <is>
-          <t>La frana del Cencione Tra fango e polemiche Le ruspe sono al lavoro</t>
+          <t>The Cencione landslide: amid mud and controversy, bulldozers are at work</t>
         </is>
       </c>
       <c r="C106" s="161" t="inlineStr">
@@ -16182,7 +16282,11 @@
       <c r="K106" s="168" t="n">
         <v>46319</v>
       </c>
-      <c r="L106" s="167" t="n"/>
+      <c r="L106" s="167" t="inlineStr">
+        <is>
+          <t>La frana del Cencione Tra fango e polemiche Le ruspe sono al lavoro</t>
+        </is>
+      </c>
       <c r="M106" s="167" t="n"/>
       <c r="N106" s="169" t="inlineStr">
         <is>
@@ -17830,7 +17934,7 @@
       </c>
       <c r="B124" s="160" t="inlineStr">
         <is>
-          <t>Se ha descubierto un socavón del tamaño de casi tres campos de fútbol en Phong Nha Ke Bang.</t>
+          <t>A sinkhole nearly three football fields in size has been discovered in Phong Nha-Ke Bang.</t>
         </is>
       </c>
       <c r="C124" s="184" t="inlineStr">
@@ -17866,7 +17970,11 @@
       <c r="K124" s="168" t="n">
         <v>46319</v>
       </c>
-      <c r="L124" s="167" t="n"/>
+      <c r="L124" s="167" t="inlineStr">
+        <is>
+          <t>Se ha descubierto un socavón del tamaño de casi tres campos de fútbol en Phong Nha Ke Bang.</t>
+        </is>
+      </c>
       <c r="M124" s="167" t="n"/>
       <c r="N124" s="169" t="inlineStr">
         <is>
@@ -18014,7 +18122,7 @@
       </c>
       <c r="B126" s="160" t="inlineStr">
         <is>
-          <t>Vista de cerca del gigantesco socavón de 120 metros de profundidad descubierto recientemente en Vietnam.</t>
+          <t>Close look at the giant 120-meter-deep sinkhole recently discovered in Vietnam.</t>
         </is>
       </c>
       <c r="C126" s="184" t="inlineStr">
@@ -18050,7 +18158,11 @@
       <c r="K126" s="168" t="n">
         <v>46319</v>
       </c>
-      <c r="L126" s="167" t="n"/>
+      <c r="L126" s="167" t="inlineStr">
+        <is>
+          <t>Vista de cerca del gigantesco socavón de 120 metros de profundidad descubierto recientemente en Vietnam.</t>
+        </is>
+      </c>
       <c r="M126" s="167" t="n"/>
       <c r="N126" s="169" t="inlineStr">
         <is>
@@ -20386,7 +20498,7 @@
       </c>
       <c r="B152" s="160" t="inlineStr">
         <is>
-          <t>Cerraron un sector de la costanera de una ciudad correntina por hundimiento</t>
+          <t>A section of the coastal road in a Corrientes city was closed due to subsidence</t>
         </is>
       </c>
       <c r="C152" s="179" t="inlineStr">
@@ -20422,7 +20534,11 @@
       <c r="K152" s="168" t="n">
         <v>46319</v>
       </c>
-      <c r="L152" s="167" t="n"/>
+      <c r="L152" s="167" t="inlineStr">
+        <is>
+          <t>Cerraron un sector de la costanera de una ciudad correntina por hundimiento</t>
+        </is>
+      </c>
       <c r="M152" s="167" t="n"/>
       <c r="N152" s="169" t="inlineStr">
         <is>
@@ -20476,7 +20592,7 @@
       </c>
       <c r="B153" s="160" t="inlineStr">
         <is>
-          <t>Inician rehabilitación tras hundimiento de losa en el Malecón Costero de Coatzacoalcos</t>
+          <t>Rehabilitation begins after slab subsidence on the Malecón Costero in Coatzacoalcos</t>
         </is>
       </c>
       <c r="C153" s="179" t="inlineStr">
@@ -20512,7 +20628,11 @@
       <c r="K153" s="168" t="n">
         <v>46319</v>
       </c>
-      <c r="L153" s="167" t="n"/>
+      <c r="L153" s="167" t="inlineStr">
+        <is>
+          <t>Inician rehabilitación tras hundimiento de losa en el Malecón Costero de Coatzacoalcos</t>
+        </is>
+      </c>
       <c r="M153" s="167" t="n"/>
       <c r="N153" s="169" t="inlineStr">
         <is>
@@ -22164,7 +22284,7 @@
         </is>
       </c>
     </row>
-    <row r="40" outlineLevel="1" ht="41.5" customHeight="1">
+    <row r="40" outlineLevel="1" ht="66.5" customHeight="1">
       <c r="A40" s="190" t="n">
         <v>103</v>
       </c>
@@ -22173,7 +22293,8 @@
       </c>
       <c r="C40" s="192" t="inlineStr">
         <is>
-          <t>La frana del Cencione Tra fango e polemiche Le ruspe sono al lavoro</t>
+          <t>The Cencione landslide: amid mud and controversy, bulldozers are at work
+(English headline translated by Claude · Original: La frana del Cencione Tra fango e polemiche Le ruspe sono al lavoro)</t>
         </is>
       </c>
       <c r="D40" s="193" t="inlineStr">
@@ -22254,7 +22375,8 @@
       </c>
       <c r="C42" s="192" t="inlineStr">
         <is>
-          <t>Deslizamiento de talud afecta sótanos y locales de plaza comercial en Cuajimalpa</t>
+          <t>Slope collapse affects basements and shops of a shopping plaza in Cuajimalpa
+(English headline translated by Claude · Original: Deslizamiento de talud afecta sótanos y locales de plaza comercial en Cuajimalpa)</t>
         </is>
       </c>
       <c r="D42" s="193" t="inlineStr">
@@ -22295,7 +22417,8 @@
       </c>
       <c r="C43" s="192" t="inlineStr">
         <is>
-          <t>Fuerte deslave en Centro Santa Fe: colapsa talud de 30 metros y afecta locales</t>
+          <t>Heavy landslide at Centro Santa Fe: 30-meter slope collapses and affects shops
+(English headline translated by Claude · Original: Fuerte deslave en Centro Santa Fe: colapsa talud de 30 metros y afecta locales)</t>
         </is>
       </c>
       <c r="D43" s="193" t="inlineStr">
@@ -22829,7 +22952,8 @@
       </c>
       <c r="C56" s="192" t="inlineStr">
         <is>
-          <t>В Пенанге оползень обрушился на дом, погиб 73-летний мужчина — Channel NewsAsia</t>
+          <t>In Penang, a landslide hit a house and killed a 73-year-old man — Channel NewsAsia
+(English headline translated by Claude · Original: В Пенанге оползень обрушился на дом, погиб 73-летний мужчина — Channel NewsAsia)</t>
         </is>
       </c>
       <c r="D56" s="193" t="inlineStr">
@@ -22911,7 +23035,8 @@
       </c>
       <c r="C58" s="192" t="inlineStr">
         <is>
-          <t>Panamá interviene antigua mina de oro tras deslizamiento que amenaza fuentes de agua</t>
+          <t>Panama intervenes at former gold mine after landslide threatens water sources
+(English headline translated by Claude · Original: Panamá interviene antigua mina de oro tras deslizamiento que amenaza fuentes de agua)</t>
         </is>
       </c>
       <c r="D58" s="193" t="inlineStr">
@@ -22943,7 +23068,7 @@
         </is>
       </c>
     </row>
-    <row r="59" outlineLevel="1" ht="66.5" customHeight="1">
+    <row r="59" outlineLevel="1" ht="79" customHeight="1">
       <c r="A59" s="190" t="n">
         <v>22</v>
       </c>
@@ -22952,7 +23077,8 @@
       </c>
       <c r="C59" s="192" t="inlineStr">
         <is>
-          <t>Socavón amenaza con dejar incomunicadas a dos barriadas en Arraiján</t>
+          <t>Sinkhole threatens to isolate two neighborhoods in Arraiján
+(English headline translated by Claude · Original: Socavón amenaza con dejar incomunicadas a dos barriadas en Arraiján)</t>
         </is>
       </c>
       <c r="D59" s="193" t="inlineStr">
@@ -22984,7 +23110,7 @@
         </is>
       </c>
     </row>
-    <row r="60" outlineLevel="1" ht="66.5" customHeight="1">
+    <row r="60" outlineLevel="1" ht="79" customHeight="1">
       <c r="A60" s="190" t="n">
         <v>23</v>
       </c>
@@ -22993,7 +23119,8 @@
       </c>
       <c r="C60" s="192" t="inlineStr">
         <is>
-          <t>Reportan caída de cuatro huéspedes en socavón de hotel Occidental de Cozumel</t>
+          <t>Four guests reportedly fall into sinkhole at Occidental hotel in Cozumel
+(English headline translated by Claude · Original: Reportan caída de cuatro huéspedes en socavón de hotel Occidental de Cozumel)</t>
         </is>
       </c>
       <c r="D60" s="193" t="inlineStr">
@@ -23034,7 +23161,8 @@
       </c>
       <c r="C61" s="192" t="inlineStr">
         <is>
-          <t>Alertas SMS, señaléticas y rutas de evacuación: el plan de La Reina ante futuros aluviones</t>
+          <t>SMS alerts, signage and evacuation routes: La Reina's plan for future floods
+(English headline translated by Claude · Original: Alertas SMS, señaléticas y rutas de evacuación: el plan de La Reina ante futuros aluviones)</t>
         </is>
       </c>
       <c r="D61" s="193" t="inlineStr">
@@ -23075,7 +23203,8 @@
       </c>
       <c r="C62" s="192" t="inlineStr">
         <is>
-          <t>ANA instala 12 barreras para reducir el impacto de huaicos en Lima y Huarochirí</t>
+          <t>ANA installs 12 barriers to reduce impact of debris flows in Lima and Huarochirí
+(English headline translated by Claude · Original: ANA instala 12 barreras para reducir el impacto de huaicos en Lima y Huarochirí)</t>
         </is>
       </c>
       <c r="D62" s="193" t="inlineStr">
@@ -24058,7 +24187,8 @@
       </c>
       <c r="C89" s="192" t="inlineStr">
         <is>
-          <t>Ayuntamiento atiende más de 50 socavones su reparación cuesta hasta 700 mil pesos por punto</t>
+          <t>City council attends to over 50 sinkholes; repair costs up to 700,000 pesos per point
+(English headline translated by Claude · Original: Ayuntamiento atiende más de 50 socavones su reparación cuesta hasta 700 mil pesos por punto)</t>
         </is>
       </c>
       <c r="D89" s="193" t="inlineStr">
@@ -24099,7 +24229,8 @@
       </c>
       <c r="C90" s="192" t="inlineStr">
         <is>
-          <t>Ica: nuevo huaico podría repetir el bloqueo de la Panamericana Sur por falta de puente en Ocucaje</t>
+          <t>Ica: new debris flow could repeat blockage of the Panamericana Sur due to lack of bridge in Ocucaje
+(English headline translated by Claude · Original: Ica: nuevo huaico podría repetir el bloqueo de la Panamericana Sur por falta de puente en Ocucaje)</t>
         </is>
       </c>
       <c r="D90" s="193" t="inlineStr">
@@ -24418,7 +24549,7 @@
         </is>
       </c>
     </row>
-    <row r="98" outlineLevel="1" ht="54" customHeight="1">
+    <row r="98" outlineLevel="1" ht="66.5" customHeight="1">
       <c r="A98" s="190" t="n">
         <v>27</v>
       </c>
@@ -24427,7 +24558,8 @@
       </c>
       <c r="C98" s="192" t="inlineStr">
         <is>
-          <t>Anuncia Ayuntamiento de Cuernavaca cierre temporal de Avenida Universidad por revisión de hundimiento</t>
+          <t>Cuernavaca city council announces temporary closure of Avenida Universidad for subsidence review
+(English headline translated by Claude · Original: Anuncia Ayuntamiento de Cuernavaca cierre temporal de Avenida Universidad por revisión de hundimiento)</t>
         </is>
       </c>
       <c r="D98" s="193" t="inlineStr">
@@ -24789,7 +24921,7 @@
         </is>
       </c>
     </row>
-    <row r="107" outlineLevel="1" ht="54" customHeight="1">
+    <row r="107" outlineLevel="1" ht="66.5" customHeight="1">
       <c r="A107" s="190" t="n">
         <v>34</v>
       </c>
@@ -24798,7 +24930,8 @@
       </c>
       <c r="C107" s="192" t="inlineStr">
         <is>
-          <t>Vía Alóag-Santo Domingo tiene paso controlado tras deslizamiento en el km 35</t>
+          <t>Alóag-Santo Domingo road has controlled passage after landslide at km 35
+(English headline translated by Claude · Original: Vía Alóag-Santo Domingo tiene paso controlado tras deslizamiento en el km 35)</t>
         </is>
       </c>
       <c r="D107" s="193" t="inlineStr">
@@ -24839,7 +24972,8 @@
       </c>
       <c r="C108" s="192" t="inlineStr">
         <is>
-          <t>Vía Riobamba–Penipe–Baños fue habilitada tras deslizamiento</t>
+          <t>Riobamba–Penipe–Baños road reopened after landslide
+(English headline translated by Claude · Original: Vía Riobamba–Penipe–Baños fue habilitada tras deslizamiento)</t>
         </is>
       </c>
       <c r="D108" s="193" t="inlineStr">
@@ -24880,7 +25014,8 @@
       </c>
       <c r="C109" s="192" t="inlineStr">
         <is>
-          <t>Áncash: deslizamiento de tierra dañó 15 metros de vía vecinal en Shupluy -</t>
+          <t>Áncash: landslide damaged 15 meters of local road in Shupluy
+(English headline translated by Claude · Original: Áncash: deslizamiento de tierra dañó 15 metros de vía vecinal en Shupluy -)</t>
         </is>
       </c>
       <c r="D109" s="193" t="inlineStr">
@@ -24921,7 +25056,8 @@
       </c>
       <c r="C110" s="192" t="inlineStr">
         <is>
-          <t>Camioneta varada en socavón de la colonia Fronteriza en Juárez</t>
+          <t>Pickup truck stranded in sinkhole in Fronteriza neighborhood in Juárez
+(English headline translated by Claude · Original: Camioneta varada en socavón de la colonia Fronteriza en Juárez)</t>
         </is>
       </c>
       <c r="D110" s="193" t="inlineStr">
@@ -24962,7 +25098,8 @@
       </c>
       <c r="C111" s="192" t="inlineStr">
         <is>
-          <t>Mañana inicia la reparación del socavón en el puente Terrazas del Valle</t>
+          <t>Repair of sinkhole on Terrazas del Valle bridge starts tomorrow
+(English headline translated by Claude · Original: Mañana inicia la reparación del socavón en el puente Terrazas del Valle)</t>
         </is>
       </c>
       <c r="D111" s="193" t="inlineStr">
@@ -25003,7 +25140,8 @@
       </c>
       <c r="C112" s="192" t="inlineStr">
         <is>
-          <t>Fortes chuvas provocam deslizamento de terra em acesso da SP-294 em Garça</t>
+          <t>Heavy rains cause landslide on access to SP-294 in Garça
+(English headline translated by Claude · Original: Fortes chuvas provocam deslizamento de terra em acesso da SP-294 em Garça)</t>
         </is>
       </c>
       <c r="D112" s="193" t="inlineStr">
@@ -25044,7 +25182,8 @@
       </c>
       <c r="C113" s="192" t="inlineStr">
         <is>
-          <t>Deslizamento de terra e árvores bloqueia rodovia entre Tatuí e Boituva</t>
+          <t>Landslide and trees block highway between Tatuí and Boituva
+(English headline translated by Claude · Original: Deslizamento de terra e árvores bloqueia rodovia entre Tatuí e Boituva)</t>
         </is>
       </c>
       <c r="D113" s="193" t="inlineStr">
@@ -25085,7 +25224,8 @@
       </c>
       <c r="C114" s="192" t="inlineStr">
         <is>
-          <t>Deslizamento de terra interdita rodovia entre Realeza e Planalto</t>
+          <t>Landslide closes highway between Realeza and Planalto
+(English headline translated by Claude · Original: Deslizamento de terra interdita rodovia entre Realeza e Planalto)</t>
         </is>
       </c>
       <c r="D114" s="193" t="inlineStr">
@@ -25117,7 +25257,7 @@
         </is>
       </c>
     </row>
-    <row r="115" outlineLevel="1" ht="54" customHeight="1">
+    <row r="115" outlineLevel="1" ht="66.5" customHeight="1">
       <c r="A115" s="190" t="n">
         <v>42</v>
       </c>
@@ -25126,7 +25266,8 @@
       </c>
       <c r="C115" s="192" t="inlineStr">
         <is>
-          <t>BR-277 é liberada após deslizamento de terra na Serra da Esperança, em Guarapuava</t>
+          <t>BR-277 reopened after landslide in Serra da Esperança, in Guarapuava
+(English headline translated by Claude · Original: BR-277 é liberada após deslizamento de terra na Serra da Esperança, em Guarapuava)</t>
         </is>
       </c>
       <c r="D115" s="193" t="inlineStr">
@@ -25167,7 +25308,8 @@
       </c>
       <c r="C116" s="192" t="inlineStr">
         <is>
-          <t>Deslizamento de terra no Km 43, em Cajamar, coloca motoristas em alerta</t>
+          <t>Landslide at Km 43 in Cajamar puts drivers on alert
+(English headline translated by Claude · Original: Deslizamento de terra no Km 43, em Cajamar, coloca motoristas em alerta)</t>
         </is>
       </c>
       <c r="D116" s="193" t="inlineStr">
@@ -25199,7 +25341,7 @@
         </is>
       </c>
     </row>
-    <row r="117" outlineLevel="1" ht="41.5" customHeight="1">
+    <row r="117" outlineLevel="1" ht="66.5" customHeight="1">
       <c r="A117" s="190" t="n">
         <v>79</v>
       </c>
@@ -25208,7 +25350,8 @@
       </c>
       <c r="C117" s="192" t="inlineStr">
         <is>
-          <t>Un socavón en Cerro se llena de agua y amenaza a peatones y conductores tras las lluvias</t>
+          <t>A sinkhole in Cerro fills with water and threatens pedestrians and drivers after rains
+(English headline translated by Claude · Original: Un socavón en Cerro se llena de agua y amenaza a peatones y conductores tras las lluvias)</t>
         </is>
       </c>
       <c r="D117" s="193" t="inlineStr">
@@ -26159,7 +26302,7 @@
         </is>
       </c>
     </row>
-    <row r="142" outlineLevel="1" ht="66.5" customHeight="1">
+    <row r="142" outlineLevel="1" ht="79" customHeight="1">
       <c r="A142" s="190" t="n">
         <v>17</v>
       </c>
@@ -26168,7 +26311,8 @@
       </c>
       <c r="C142" s="192" t="inlineStr">
         <is>
-          <t>Fuerte oleaje provoca un socavón y daños en un malecón emblemático de México</t>
+          <t>Strong waves cause a sinkhole and damage to an emblematic seafront promenade in Mexico
+(English headline translated by Claude · Original: Fuerte oleaje provoca un socavón y daños en un malecón emblemático de México)</t>
         </is>
       </c>
       <c r="D142" s="193" t="inlineStr">
@@ -26209,7 +26353,8 @@
       </c>
       <c r="C143" s="192" t="inlineStr">
         <is>
-          <t>Inician reparación de socavón provocado por fuerte oleaje junto al Monumento a la Mujer Mazatleca</t>
+          <t>Repair of sinkhole caused by strong waves begins next to the Monument to the Mazatlan Woman
+(English headline translated by Claude · Original: Inician reparación de socavón provocado por fuerte oleaje junto al Monumento a la Mujer Mazatleca)</t>
         </is>
       </c>
       <c r="D143" s="193" t="inlineStr">
@@ -26610,7 +26755,7 @@
         </is>
       </c>
     </row>
-    <row r="153" outlineLevel="1" ht="41.5" customHeight="1">
+    <row r="153" outlineLevel="1" ht="66.5" customHeight="1">
       <c r="A153" s="190" t="n">
         <v>149</v>
       </c>
@@ -26619,7 +26764,8 @@
       </c>
       <c r="C153" s="192" t="inlineStr">
         <is>
-          <t>Cerraron un sector de la costanera de una ciudad correntina por hundimiento</t>
+          <t>A section of the coastal road in a Corrientes city was closed due to subsidence
+(English headline translated by Claude · Original: Cerraron un sector de la costanera de una ciudad correntina por hundimiento)</t>
         </is>
       </c>
       <c r="D153" s="193" t="inlineStr">
@@ -26650,7 +26796,7 @@
         </is>
       </c>
     </row>
-    <row r="154" outlineLevel="1" ht="41.5" customHeight="1">
+    <row r="154" outlineLevel="1" ht="66.5" customHeight="1">
       <c r="A154" s="190" t="n">
         <v>150</v>
       </c>
@@ -26659,7 +26805,8 @@
       </c>
       <c r="C154" s="192" t="inlineStr">
         <is>
-          <t>Inician rehabilitación tras hundimiento de losa en el Malecón Costero de Coatzacoalcos</t>
+          <t>Rehabilitation begins after slab subsidence on the Malecón Costero in Coatzacoalcos
+(English headline translated by Claude · Original: Inician rehabilitación tras hundimiento de losa en el Malecón Costero de Coatzacoalcos)</t>
         </is>
       </c>
       <c r="D154" s="193" t="inlineStr">
@@ -26835,7 +26982,7 @@
         </is>
       </c>
     </row>
-    <row r="160" outlineLevel="1" ht="41.5" customHeight="1">
+    <row r="160" outlineLevel="1" ht="66.5" customHeight="1">
       <c r="A160" s="190" t="n">
         <v>121</v>
       </c>
@@ -26844,7 +26991,8 @@
       </c>
       <c r="C160" s="192" t="inlineStr">
         <is>
-          <t>Se ha descubierto un socavón del tamaño de casi tres campos de fútbol en Phong Nha Ke Bang.</t>
+          <t>A sinkhole nearly three football fields in size has been discovered in Phong Nha-Ke Bang.
+(English headline translated by Claude · Original: Se ha descubierto un socavón del tamaño de casi tres campos de fútbol en Phong Nha Ke Bang.)</t>
         </is>
       </c>
       <c r="D160" s="193" t="inlineStr">
@@ -26875,7 +27023,7 @@
         </is>
       </c>
     </row>
-    <row r="161" outlineLevel="1" ht="41.5" customHeight="1">
+    <row r="161" outlineLevel="1" ht="66.5" customHeight="1">
       <c r="A161" s="190" t="n">
         <v>123</v>
       </c>
@@ -26884,7 +27032,8 @@
       </c>
       <c r="C161" s="192" t="inlineStr">
         <is>
-          <t>Vista de cerca del gigantesco socavón de 120 metros de profundidad descubierto recientemente en Vietnam.</t>
+          <t>Close look at the giant 120-meter-deep sinkhole recently discovered in Vietnam.
+(English headline translated by Claude · Original: Vista de cerca del gigantesco socavón de 120 metros de profundidad descubierto recientemente en Vietnam.)</t>
         </is>
       </c>
       <c r="D161" s="193" t="inlineStr">
@@ -27231,7 +27380,8 @@
       </c>
       <c r="C171" s="192" t="inlineStr">
         <is>
-          <t>Concentrer les ressources sur le relogement des personnes vivant dans les zones à risque de glissements de terrain.</t>
+          <t>Focus resources on relocating people living in areas at risk of landslides.
+(English headline translated by Claude · Original: Concentrer les ressources sur le relogement des personnes vivant dans les zones à risque de glissements de terrain.)</t>
         </is>
       </c>
       <c r="D171" s="193" t="inlineStr">
